--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$631</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$668</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4417" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4674" uniqueCount="1189">
   <si>
     <t>Enseignements</t>
   </si>
@@ -3348,6 +3348,255 @@
   </si>
   <si>
     <t>Unité creuse MCIL3</t>
+  </si>
+  <si>
+    <t>Cours-Commande électrique</t>
+  </si>
+  <si>
+    <t>Cours-CE-ING4EI</t>
+  </si>
+  <si>
+    <t>ING4EI</t>
+  </si>
+  <si>
+    <t>TD-Commande électrique</t>
+  </si>
+  <si>
+    <t>TD-CE-ING4EI</t>
+  </si>
+  <si>
+    <t>Cours-Electronique de puissance II</t>
+  </si>
+  <si>
+    <t>Cours-EPII-ING4EI</t>
+  </si>
+  <si>
+    <t>F.GHEZAL</t>
+  </si>
+  <si>
+    <t>Cours-Protection des réseaux électriques</t>
+  </si>
+  <si>
+    <t>Cours-PRE-ING4EI</t>
+  </si>
+  <si>
+    <t>TD-Protection des réseaux électriques</t>
+  </si>
+  <si>
+    <t>TD-PRE-ING4EI</t>
+  </si>
+  <si>
+    <t>15h30-17h00</t>
+  </si>
+  <si>
+    <t>Cours-Réseaux de transport et distribution</t>
+  </si>
+  <si>
+    <t>Cours-RTD-ING4EI</t>
+  </si>
+  <si>
+    <t>TD-Réseaux de transport et distribution</t>
+  </si>
+  <si>
+    <t>TD-RTD-ING4EI</t>
+  </si>
+  <si>
+    <t>Cours-MEA-ING4EI</t>
+  </si>
+  <si>
+    <t>TD-MEA-ING4EI</t>
+  </si>
+  <si>
+    <t>TP-MEA-ING4EI</t>
+  </si>
+  <si>
+    <t>Labo machine</t>
+  </si>
+  <si>
+    <t>Cours-Automatisme Industriels 1</t>
+  </si>
+  <si>
+    <t>Cours-AI1-ING4EI</t>
+  </si>
+  <si>
+    <t>K.KLOUCHA</t>
+  </si>
+  <si>
+    <t>TP-Automatisme Industriels 1</t>
+  </si>
+  <si>
+    <t>TP-AI1-ING4EI</t>
+  </si>
+  <si>
+    <t>Labo AUTO</t>
+  </si>
+  <si>
+    <t>Cours-Normes en électrotechnique</t>
+  </si>
+  <si>
+    <t>Cours-NE-ING4EI</t>
+  </si>
+  <si>
+    <t>TP-Electronique de puissance II</t>
+  </si>
+  <si>
+    <t>TP-EPII-ING4EI</t>
+  </si>
+  <si>
+    <t>Labo ELN-P</t>
+  </si>
+  <si>
+    <t>TP-Commande électrique</t>
+  </si>
+  <si>
+    <t>TP-CE-ING4EI</t>
+  </si>
+  <si>
+    <t>Labo commande</t>
+  </si>
+  <si>
+    <t>TP-Programmation Avancée en Python</t>
+  </si>
+  <si>
+    <t>TP-PAP-ING4EI</t>
+  </si>
+  <si>
+    <t>Salle micros</t>
+  </si>
+  <si>
+    <t>Projet-Projet Personnel Professionnel</t>
+  </si>
+  <si>
+    <t>Projet-PPP-ING4EI</t>
+  </si>
+  <si>
+    <t>Salle projet</t>
+  </si>
+  <si>
+    <t>TD-Electronique de puissance II</t>
+  </si>
+  <si>
+    <t>TD-EPII-ING4EI</t>
+  </si>
+  <si>
+    <t>Cours-Réseaux électriques Industriels</t>
+  </si>
+  <si>
+    <t>Cours-REI-ING5RSE</t>
+  </si>
+  <si>
+    <t>ING5RSE</t>
+  </si>
+  <si>
+    <t>TD-Réseaux électriques Industriels</t>
+  </si>
+  <si>
+    <t>TD-REI-ING5RSE</t>
+  </si>
+  <si>
+    <t>Cours-Systèmes solaires thermiques</t>
+  </si>
+  <si>
+    <t>Cours-SST-ING5RSE</t>
+  </si>
+  <si>
+    <t>TP-Dimensionnement des systèmes à énergies renouvelables</t>
+  </si>
+  <si>
+    <t>TP-DSEER-ING5RSE</t>
+  </si>
+  <si>
+    <t>Labo PV</t>
+  </si>
+  <si>
+    <t>Cours-Techniques de haute tension</t>
+  </si>
+  <si>
+    <t>Cours-THT-ING5RSE</t>
+  </si>
+  <si>
+    <t>Cours-Dimensionnement des systèmes à énergies renouvelables</t>
+  </si>
+  <si>
+    <t>Cours-DSEER-ING5RSE</t>
+  </si>
+  <si>
+    <t>TD-Dimensionnement des systèmes à énergies renouvelables</t>
+  </si>
+  <si>
+    <t>TD-DSEER-ING5RSE</t>
+  </si>
+  <si>
+    <t>Cours-Planification des réseaux électriques</t>
+  </si>
+  <si>
+    <t>Cours-PRE-ING5RSE</t>
+  </si>
+  <si>
+    <t>TD-Planification des réseaux électriques</t>
+  </si>
+  <si>
+    <t>TD-PRE-ING5RSE</t>
+  </si>
+  <si>
+    <t>TP-Techniques de haute tension</t>
+  </si>
+  <si>
+    <t>TP-THT-ING5RSE</t>
+  </si>
+  <si>
+    <t>Labo HT</t>
+  </si>
+  <si>
+    <t>Cours-IERR-ING5RSE</t>
+  </si>
+  <si>
+    <t>TD-IERR-ING5RSE</t>
+  </si>
+  <si>
+    <t>Cours-Diagnostic et maintenance des systèmes électriques</t>
+  </si>
+  <si>
+    <t>Cours-DMSE-ING5RSE</t>
+  </si>
+  <si>
+    <t>TP-Conception industrielle et prototypage</t>
+  </si>
+  <si>
+    <t>TP-CIP-ING5RSE</t>
+  </si>
+  <si>
+    <t>Labo proto</t>
+  </si>
+  <si>
+    <t>TD-Diagnostic et maintenance des systèmes électriques</t>
+  </si>
+  <si>
+    <t>TD-DMSE-ING5RSE</t>
+  </si>
+  <si>
+    <t>Cours-REI2-ING5RSE</t>
+  </si>
+  <si>
+    <t>Cours-Stockage de l'énergie</t>
+  </si>
+  <si>
+    <t>Cours-SE-ING5RSE</t>
+  </si>
+  <si>
+    <t>Cours-Recherche documentaire et Conception de mémoire</t>
+  </si>
+  <si>
+    <t>Cours-RDCM-ING5RSE</t>
+  </si>
+  <si>
+    <t>TP-Réseaux électriques Industriels</t>
+  </si>
+  <si>
+    <t>TP-REI-ING5RSE</t>
+  </si>
+  <si>
+    <t>Labo réseaux</t>
   </si>
 </sst>
 </file>
@@ -4332,7 +4581,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G631"/>
+  <dimension ref="A1:G668"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="29.8571428571429" customWidth="1"/>
@@ -18857,9 +19106,856 @@
         <v>1073</v>
       </c>
     </row>
+    <row r="632" spans="1:7">
+      <c r="A632" s="6" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B632" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C632" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D632" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E632" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F632" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G632" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7">
+      <c r="A633" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B633" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C633" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D633" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E633" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F633" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G633" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7">
+      <c r="A634" s="6" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B634" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C634" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D634" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E634" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F634" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G634" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7">
+      <c r="A635" s="6" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B635" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C635" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D635" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E635" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F635" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G635" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7">
+      <c r="A636" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B636" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C636" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D636" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E636" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F636" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G636" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7">
+      <c r="A637" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B637" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C637" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="D637" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E637" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F637" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G637" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7">
+      <c r="A638" s="6" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B638" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C638" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="D638" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E638" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F638" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="G638" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="639" spans="1:7">
+      <c r="A639" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="B639" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C639" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="D639" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E639" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F639" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G639" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7">
+      <c r="A640" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B640" s="6" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C640" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="D640" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E640" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F640" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="G640" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="641" spans="1:7">
+      <c r="A641" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B641" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C641" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="D641" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E641" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F641" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G641" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="642" spans="1:7">
+      <c r="A642" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B642" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C642" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D642" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E642" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F642" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G642" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="643" spans="1:7">
+      <c r="A643" s="6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B643" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C643" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D643" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E643" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F643" s="6" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G643" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="644" spans="1:7">
+      <c r="A644" s="6" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B644" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C644" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D644" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E644" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F644" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G644" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7">
+      <c r="A645" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B645" s="6" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C645" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D645" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E645" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F645" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G645" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="646" spans="1:7">
+      <c r="A646" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B646" s="6" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C646" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D646" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E646" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F646" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G646" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="647" spans="1:7">
+      <c r="A647" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B647" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C647" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D647" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E647" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F647" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G647" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="648" spans="1:7">
+      <c r="A648" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B648" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C648" s="6"/>
+      <c r="D648" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E648" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F648" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G648" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="649" spans="1:7">
+      <c r="A649" s="6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B649" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C649" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D649" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E649" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F649" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="G649" s="6" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="650" spans="1:7">
+      <c r="A650" s="6" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B650" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C650" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D650" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E650" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F650" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G650" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="651" spans="1:7">
+      <c r="A651" s="6" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B651" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C651" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D651" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E651" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F651" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G651" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="652" spans="1:7">
+      <c r="A652" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B652" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C652" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="D652" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E652" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F652" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G652" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="653" spans="1:7">
+      <c r="A653" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B653" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C653" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D653" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E653" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F653" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G653" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="654" spans="1:7">
+      <c r="A654" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B654" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C654" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="D654" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E654" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F654" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G654" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="655" spans="1:7">
+      <c r="A655" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B655" s="6" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C655" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D655" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E655" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F655" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G655" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="656" spans="1:7">
+      <c r="A656" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B656" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C656" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D656" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E656" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F656" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G656" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="657" spans="1:7">
+      <c r="A657" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B657" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C657" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="D657" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E657" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F657" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G657" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="658" spans="1:7">
+      <c r="A658" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B658" s="6" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C658" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="D658" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E658" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F658" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G658" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="659" spans="1:7">
+      <c r="A659" s="6" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B659" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C659" s="6" t="s">
+        <v>896</v>
+      </c>
+      <c r="D659" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E659" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F659" s="6" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G659" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="660" spans="1:7">
+      <c r="A660" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="B660" s="6" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C660" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D660" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E660" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F660" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G660" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="661" spans="1:7">
+      <c r="A661" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="B661" s="6" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C661" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D661" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E661" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F661" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G661" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="662" spans="1:7">
+      <c r="A662" s="6" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B662" s="6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C662" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="D662" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E662" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F662" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G662" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="663" spans="1:7">
+      <c r="A663" s="6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B663" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C663" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="D663" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E663" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F663" s="6" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G663" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="664" spans="1:7">
+      <c r="A664" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B664" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C664" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="D664" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E664" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F664" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G664" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="665" spans="1:7">
+      <c r="A665" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="B665" s="6" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C665" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D665" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E665" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F665" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G665" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="666" spans="1:7">
+      <c r="A666" s="6" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B666" s="6" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C666" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="D666" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E666" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F666" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G666" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="667" spans="1:7">
+      <c r="A667" s="6" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B667" s="6" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C667" s="6"/>
+      <c r="D667" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E667" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F667" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="G667" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="668" spans="1:7">
+      <c r="A668" s="6" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B668" s="6" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C668" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D668" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E668" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F668" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G668" s="6" t="s">
+        <v>1151</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G631" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:G631">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G668" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:G668">
       <sortCondition ref="G1"/>
     </sortState>
     <extLst/>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4674" uniqueCount="1189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4674" uniqueCount="1188">
   <si>
     <t>Enseignements</t>
   </si>
@@ -434,7 +434,7 @@
     <t>TD-LS-Ing3</t>
   </si>
   <si>
-    <t>F.Ghezal</t>
+    <t>GHAZEL FATIHA</t>
   </si>
   <si>
     <t>Cours-Systèmes Asservis 1</t>
@@ -3369,9 +3369,6 @@
   </si>
   <si>
     <t>Cours-EPII-ING4EI</t>
-  </si>
-  <si>
-    <t>F.GHEZAL</t>
   </si>
   <si>
     <t>Cours-Protection des réseaux électriques</t>
@@ -3609,14 +3606,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4093,13 +4083,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4108,118 +4101,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4234,7 +4224,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4580,7 +4570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr filterMode="1" codeName="Sheet1"/>
   <dimension ref="A1:G668"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
@@ -4616,7 +4606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" hidden="1" spans="1:7">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -4639,7 +4629,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" hidden="1" spans="1:7">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
@@ -4662,7 +4652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" hidden="1" spans="1:7">
       <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
@@ -4685,7 +4675,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" hidden="1" spans="1:7">
       <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
@@ -4708,7 +4698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" hidden="1" spans="1:7">
       <c r="A6" s="6" t="s">
         <v>18</v>
       </c>
@@ -4731,7 +4721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" hidden="1" spans="1:7">
       <c r="A7" s="6" t="s">
         <v>24</v>
       </c>
@@ -4754,7 +4744,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" hidden="1" spans="1:7">
       <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
@@ -4777,7 +4767,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" hidden="1" spans="1:7">
       <c r="A9" s="6" t="s">
         <v>24</v>
       </c>
@@ -4800,7 +4790,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" hidden="1" spans="1:7">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -4823,7 +4813,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" hidden="1" spans="1:7">
       <c r="A11" s="6" t="s">
         <v>24</v>
       </c>
@@ -4846,7 +4836,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" hidden="1" spans="1:7">
       <c r="A12" s="6" t="s">
         <v>24</v>
       </c>
@@ -4869,7 +4859,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" hidden="1" spans="1:7">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
@@ -4892,7 +4882,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" hidden="1" spans="1:7">
       <c r="A14" s="6" t="s">
         <v>24</v>
       </c>
@@ -4915,7 +4905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" hidden="1" spans="1:7">
       <c r="A15" s="6" t="s">
         <v>32</v>
       </c>
@@ -4938,7 +4928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" hidden="1" spans="1:7">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -4961,7 +4951,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" hidden="1" spans="1:7">
       <c r="A17" s="6" t="s">
         <v>38</v>
       </c>
@@ -4984,7 +4974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" hidden="1" spans="1:7">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -5007,7 +4997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" hidden="1" spans="1:7">
       <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
@@ -5030,7 +5020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" hidden="1" spans="1:7">
       <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
@@ -5053,7 +5043,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" hidden="1" spans="1:7">
       <c r="A21" s="6" t="s">
         <v>44</v>
       </c>
@@ -5076,7 +5066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" hidden="1" spans="1:7">
       <c r="A22" s="6" t="s">
         <v>47</v>
       </c>
@@ -5099,7 +5089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" hidden="1" spans="1:7">
       <c r="A23" s="6" t="s">
         <v>50</v>
       </c>
@@ -5122,7 +5112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" hidden="1" spans="1:7">
       <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
@@ -5145,7 +5135,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" hidden="1" spans="1:7">
       <c r="A25" s="6" t="s">
         <v>53</v>
       </c>
@@ -5168,7 +5158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" hidden="1" spans="1:7">
       <c r="A26" s="6" t="s">
         <v>50</v>
       </c>
@@ -5191,7 +5181,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" hidden="1" spans="1:7">
       <c r="A27" s="6" t="s">
         <v>50</v>
       </c>
@@ -5214,7 +5204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" hidden="1" spans="1:7">
       <c r="A28" s="6" t="s">
         <v>58</v>
       </c>
@@ -5237,7 +5227,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" hidden="1" spans="1:7">
       <c r="A29" s="6" t="s">
         <v>58</v>
       </c>
@@ -5260,7 +5250,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" hidden="1" spans="1:7">
       <c r="A30" s="6" t="s">
         <v>62</v>
       </c>
@@ -5283,7 +5273,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" hidden="1" spans="1:7">
       <c r="A31" s="6" t="s">
         <v>66</v>
       </c>
@@ -5306,7 +5296,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" hidden="1" spans="1:7">
       <c r="A32" s="6" t="s">
         <v>70</v>
       </c>
@@ -5329,7 +5319,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" hidden="1" spans="1:7">
       <c r="A33" s="6" t="s">
         <v>73</v>
       </c>
@@ -5352,7 +5342,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" hidden="1" spans="1:7">
       <c r="A34" s="6" t="s">
         <v>76</v>
       </c>
@@ -5375,7 +5365,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" hidden="1" spans="1:7">
       <c r="A35" s="6" t="s">
         <v>76</v>
       </c>
@@ -5398,7 +5388,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" hidden="1" spans="1:7">
       <c r="A36" s="6" t="s">
         <v>79</v>
       </c>
@@ -5421,7 +5411,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" hidden="1" spans="1:7">
       <c r="A37" s="6" t="s">
         <v>79</v>
       </c>
@@ -5444,7 +5434,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" hidden="1" spans="1:7">
       <c r="A38" s="6" t="s">
         <v>82</v>
       </c>
@@ -5467,7 +5457,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" hidden="1" spans="1:7">
       <c r="A39" s="6" t="s">
         <v>73</v>
       </c>
@@ -5490,7 +5480,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" hidden="1" spans="1:7">
       <c r="A40" s="6" t="s">
         <v>85</v>
       </c>
@@ -5513,7 +5503,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" hidden="1" spans="1:7">
       <c r="A41" s="6" t="s">
         <v>88</v>
       </c>
@@ -5536,7 +5526,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" hidden="1" spans="1:7">
       <c r="A42" s="6" t="s">
         <v>88</v>
       </c>
@@ -5559,7 +5549,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" hidden="1" spans="1:7">
       <c r="A43" s="6" t="s">
         <v>91</v>
       </c>
@@ -5582,7 +5572,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" hidden="1" spans="1:7">
       <c r="A44" s="6" t="s">
         <v>91</v>
       </c>
@@ -5605,7 +5595,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" hidden="1" spans="1:7">
       <c r="A45" s="6" t="s">
         <v>95</v>
       </c>
@@ -5628,7 +5618,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" hidden="1" spans="1:7">
       <c r="A46" s="6" t="s">
         <v>98</v>
       </c>
@@ -5651,7 +5641,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" hidden="1" spans="1:7">
       <c r="A47" s="6" t="s">
         <v>101</v>
       </c>
@@ -5674,7 +5664,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" hidden="1" spans="1:7">
       <c r="A48" s="6" t="s">
         <v>101</v>
       </c>
@@ -5697,7 +5687,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" hidden="1" spans="1:7">
       <c r="A49" s="6" t="s">
         <v>103</v>
       </c>
@@ -5720,7 +5710,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" hidden="1" spans="1:7">
       <c r="A50" s="6" t="s">
         <v>105</v>
       </c>
@@ -5743,7 +5733,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" hidden="1" spans="1:7">
       <c r="A51" s="6" t="s">
         <v>108</v>
       </c>
@@ -5766,7 +5756,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" hidden="1" spans="1:7">
       <c r="A52" s="6" t="s">
         <v>110</v>
       </c>
@@ -5789,7 +5779,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" hidden="1" spans="1:7">
       <c r="A53" s="6" t="s">
         <v>62</v>
       </c>
@@ -5812,7 +5802,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" hidden="1" spans="1:7">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
@@ -5835,7 +5825,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" hidden="1" spans="1:7">
       <c r="A55" s="6" t="s">
         <v>62</v>
       </c>
@@ -5858,7 +5848,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" hidden="1" spans="1:7">
       <c r="A56" s="6" t="s">
         <v>62</v>
       </c>
@@ -5881,7 +5871,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" hidden="1" spans="1:7">
       <c r="A57" s="6" t="s">
         <v>113</v>
       </c>
@@ -5904,7 +5894,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" hidden="1" spans="1:7">
       <c r="A58" s="6" t="s">
         <v>117</v>
       </c>
@@ -5927,7 +5917,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" hidden="1" spans="1:7">
       <c r="A59" s="6" t="s">
         <v>117</v>
       </c>
@@ -5950,7 +5940,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" hidden="1" spans="1:7">
       <c r="A60" s="6" t="s">
         <v>121</v>
       </c>
@@ -5973,7 +5963,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" hidden="1" spans="1:7">
       <c r="A61" s="6" t="s">
         <v>123</v>
       </c>
@@ -5996,7 +5986,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" hidden="1" spans="1:7">
       <c r="A62" s="6" t="s">
         <v>126</v>
       </c>
@@ -6019,7 +6009,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" hidden="1" spans="1:7">
       <c r="A63" s="6" t="s">
         <v>128</v>
       </c>
@@ -6042,7 +6032,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" hidden="1" spans="1:7">
       <c r="A64" s="6" t="s">
         <v>128</v>
       </c>
@@ -6088,7 +6078,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" hidden="1" spans="1:7">
       <c r="A66" s="6" t="s">
         <v>135</v>
       </c>
@@ -6111,7 +6101,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" hidden="1" spans="1:7">
       <c r="A67" s="6" t="s">
         <v>138</v>
       </c>
@@ -6134,7 +6124,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" hidden="1" spans="1:7">
       <c r="A68" s="6" t="s">
         <v>140</v>
       </c>
@@ -6157,7 +6147,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" hidden="1" spans="1:7">
       <c r="A69" s="6" t="s">
         <v>140</v>
       </c>
@@ -6180,7 +6170,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" hidden="1" spans="1:7">
       <c r="A70" s="6" t="s">
         <v>143</v>
       </c>
@@ -6203,7 +6193,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" hidden="1" spans="1:7">
       <c r="A71" s="6" t="s">
         <v>146</v>
       </c>
@@ -6226,7 +6216,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" hidden="1" spans="1:7">
       <c r="A72" s="6" t="s">
         <v>148</v>
       </c>
@@ -6249,7 +6239,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" hidden="1" spans="1:7">
       <c r="A73" s="6" t="s">
         <v>151</v>
       </c>
@@ -6272,7 +6262,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" hidden="1" spans="1:7">
       <c r="A74" s="6" t="s">
         <v>88</v>
       </c>
@@ -6295,7 +6285,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" hidden="1" spans="1:7">
       <c r="A75" s="6" t="s">
         <v>88</v>
       </c>
@@ -6318,7 +6308,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" hidden="1" spans="1:7">
       <c r="A76" s="6" t="s">
         <v>103</v>
       </c>
@@ -6341,7 +6331,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" hidden="1" spans="1:7">
       <c r="A77" s="6" t="s">
         <v>88</v>
       </c>
@@ -6364,7 +6354,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" hidden="1" spans="1:7">
       <c r="A78" s="6" t="s">
         <v>88</v>
       </c>
@@ -6387,7 +6377,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" hidden="1" spans="1:7">
       <c r="A79" s="6" t="s">
         <v>160</v>
       </c>
@@ -6410,7 +6400,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" hidden="1" spans="1:7">
       <c r="A80" s="6" t="s">
         <v>164</v>
       </c>
@@ -6433,7 +6423,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" hidden="1" spans="1:7">
       <c r="A81" s="6" t="s">
         <v>62</v>
       </c>
@@ -6456,7 +6446,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" hidden="1" spans="1:7">
       <c r="A82" s="6" t="s">
         <v>62</v>
       </c>
@@ -6479,7 +6469,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" hidden="1" spans="1:7">
       <c r="A83" s="6" t="s">
         <v>62</v>
       </c>
@@ -6502,7 +6492,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" hidden="1" spans="1:7">
       <c r="A84" s="6" t="s">
         <v>62</v>
       </c>
@@ -6525,7 +6515,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" hidden="1" spans="1:7">
       <c r="A85" s="6" t="s">
         <v>62</v>
       </c>
@@ -6548,7 +6538,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" hidden="1" spans="1:7">
       <c r="A86" s="6" t="s">
         <v>62</v>
       </c>
@@ -6571,7 +6561,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" hidden="1" spans="1:7">
       <c r="A87" s="6" t="s">
         <v>168</v>
       </c>
@@ -6594,7 +6584,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" hidden="1" spans="1:7">
       <c r="A88" s="6" t="s">
         <v>173</v>
       </c>
@@ -6617,7 +6607,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" hidden="1" spans="1:7">
       <c r="A89" s="6" t="s">
         <v>173</v>
       </c>
@@ -6640,7 +6630,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" hidden="1" spans="1:7">
       <c r="A90" s="6" t="s">
         <v>176</v>
       </c>
@@ -6663,7 +6653,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" hidden="1" spans="1:7">
       <c r="A91" s="6" t="s">
         <v>179</v>
       </c>
@@ -6686,7 +6676,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" hidden="1" spans="1:7">
       <c r="A92" s="6" t="s">
         <v>182</v>
       </c>
@@ -6709,7 +6699,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" hidden="1" spans="1:7">
       <c r="A93" s="6" t="s">
         <v>182</v>
       </c>
@@ -6732,7 +6722,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" hidden="1" spans="1:7">
       <c r="A94" s="6" t="s">
         <v>184</v>
       </c>
@@ -6755,7 +6745,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" hidden="1" spans="1:7">
       <c r="A95" s="6" t="s">
         <v>184</v>
       </c>
@@ -6778,7 +6768,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" hidden="1" spans="1:7">
       <c r="A96" s="6" t="s">
         <v>187</v>
       </c>
@@ -6801,7 +6791,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" hidden="1" spans="1:7">
       <c r="A97" s="6" t="s">
         <v>190</v>
       </c>
@@ -6824,7 +6814,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" hidden="1" spans="1:7">
       <c r="A98" s="6" t="s">
         <v>193</v>
       </c>
@@ -6847,7 +6837,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" hidden="1" spans="1:7">
       <c r="A99" s="6" t="s">
         <v>193</v>
       </c>
@@ -6870,7 +6860,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" hidden="1" spans="1:7">
       <c r="A100" s="6" t="s">
         <v>196</v>
       </c>
@@ -6893,7 +6883,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" hidden="1" spans="1:7">
       <c r="A101" s="6" t="s">
         <v>200</v>
       </c>
@@ -6916,7 +6906,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" hidden="1" spans="1:7">
       <c r="A102" s="6" t="s">
         <v>203</v>
       </c>
@@ -6939,7 +6929,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" hidden="1" spans="1:7">
       <c r="A103" s="6" t="s">
         <v>203</v>
       </c>
@@ -6962,7 +6952,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" hidden="1" spans="1:7">
       <c r="A104" s="6" t="s">
         <v>206</v>
       </c>
@@ -6985,7 +6975,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" hidden="1" spans="1:7">
       <c r="A105" s="6" t="s">
         <v>209</v>
       </c>
@@ -7008,7 +6998,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" hidden="1" spans="1:7">
       <c r="A106" s="6" t="s">
         <v>209</v>
       </c>
@@ -7031,7 +7021,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" hidden="1" spans="1:7">
       <c r="A107" s="6" t="s">
         <v>211</v>
       </c>
@@ -7054,7 +7044,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" hidden="1" spans="1:7">
       <c r="A108" s="6" t="s">
         <v>211</v>
       </c>
@@ -7077,7 +7067,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" hidden="1" spans="1:7">
       <c r="A109" s="6" t="s">
         <v>214</v>
       </c>
@@ -7100,7 +7090,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" hidden="1" spans="1:7">
       <c r="A110" s="6" t="s">
         <v>217</v>
       </c>
@@ -7123,7 +7113,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" hidden="1" spans="1:7">
       <c r="A111" s="6" t="s">
         <v>219</v>
       </c>
@@ -7146,7 +7136,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" hidden="1" spans="1:7">
       <c r="A112" s="6" t="s">
         <v>224</v>
       </c>
@@ -7169,7 +7159,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" hidden="1" spans="1:7">
       <c r="A113" s="6" t="s">
         <v>226</v>
       </c>
@@ -7192,7 +7182,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" hidden="1" spans="1:7">
       <c r="A114" s="6" t="s">
         <v>229</v>
       </c>
@@ -7215,7 +7205,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" hidden="1" spans="1:7">
       <c r="A115" s="6" t="s">
         <v>231</v>
       </c>
@@ -7238,7 +7228,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" hidden="1" spans="1:7">
       <c r="A116" s="6" t="s">
         <v>231</v>
       </c>
@@ -7261,7 +7251,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" hidden="1" spans="1:7">
       <c r="A117" s="6" t="s">
         <v>235</v>
       </c>
@@ -7284,7 +7274,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" hidden="1" spans="1:7">
       <c r="A118" s="6" t="s">
         <v>235</v>
       </c>
@@ -7307,7 +7297,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" hidden="1" spans="1:7">
       <c r="A119" s="6" t="s">
         <v>239</v>
       </c>
@@ -7330,7 +7320,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" hidden="1" spans="1:7">
       <c r="A120" s="6" t="s">
         <v>243</v>
       </c>
@@ -7353,7 +7343,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" hidden="1" spans="1:7">
       <c r="A121" s="6" t="s">
         <v>246</v>
       </c>
@@ -7376,7 +7366,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" hidden="1" spans="1:7">
       <c r="A122" s="6" t="s">
         <v>249</v>
       </c>
@@ -7399,7 +7389,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" hidden="1" spans="1:7">
       <c r="A123" s="6" t="s">
         <v>251</v>
       </c>
@@ -7422,7 +7412,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" hidden="1" spans="1:7">
       <c r="A124" s="6" t="s">
         <v>254</v>
       </c>
@@ -7445,7 +7435,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" hidden="1" spans="1:7">
       <c r="A125" s="6" t="s">
         <v>256</v>
       </c>
@@ -7468,7 +7458,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" hidden="1" spans="1:7">
       <c r="A126" s="6" t="s">
         <v>259</v>
       </c>
@@ -7491,7 +7481,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" hidden="1" spans="1:7">
       <c r="A127" s="6" t="s">
         <v>259</v>
       </c>
@@ -7514,7 +7504,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" hidden="1" spans="1:7">
       <c r="A128" s="6" t="s">
         <v>259</v>
       </c>
@@ -7537,7 +7527,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" hidden="1" spans="1:7">
       <c r="A129" s="6" t="s">
         <v>261</v>
       </c>
@@ -7560,7 +7550,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" hidden="1" spans="1:7">
       <c r="A130" s="6" t="s">
         <v>264</v>
       </c>
@@ -7583,7 +7573,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" hidden="1" spans="1:7">
       <c r="A131" s="6" t="s">
         <v>266</v>
       </c>
@@ -7606,7 +7596,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" hidden="1" spans="1:7">
       <c r="A132" s="6" t="s">
         <v>266</v>
       </c>
@@ -7629,7 +7619,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" hidden="1" spans="1:7">
       <c r="A133" s="6" t="s">
         <v>270</v>
       </c>
@@ -7652,7 +7642,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" hidden="1" spans="1:7">
       <c r="A134" s="6" t="s">
         <v>273</v>
       </c>
@@ -7675,7 +7665,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" hidden="1" spans="1:7">
       <c r="A135" s="6" t="s">
         <v>62</v>
       </c>
@@ -7698,7 +7688,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" hidden="1" spans="1:7">
       <c r="A136" s="6" t="s">
         <v>62</v>
       </c>
@@ -7721,7 +7711,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" hidden="1" spans="1:7">
       <c r="A137" s="6" t="s">
         <v>62</v>
       </c>
@@ -7744,7 +7734,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" hidden="1" spans="1:7">
       <c r="A138" s="6" t="s">
         <v>277</v>
       </c>
@@ -7767,7 +7757,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" hidden="1" spans="1:7">
       <c r="A139" s="6" t="s">
         <v>282</v>
       </c>
@@ -7790,7 +7780,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" hidden="1" spans="1:7">
       <c r="A140" s="6" t="s">
         <v>286</v>
       </c>
@@ -7813,7 +7803,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" hidden="1" spans="1:7">
       <c r="A141" s="6" t="s">
         <v>286</v>
       </c>
@@ -7836,7 +7826,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" hidden="1" spans="1:7">
       <c r="A142" s="6" t="s">
         <v>292</v>
       </c>
@@ -7859,7 +7849,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" hidden="1" spans="1:7">
       <c r="A143" s="6" t="s">
         <v>292</v>
       </c>
@@ -7882,7 +7872,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" hidden="1" spans="1:7">
       <c r="A144" s="6" t="s">
         <v>297</v>
       </c>
@@ -7905,7 +7895,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" hidden="1" spans="1:7">
       <c r="A145" s="6" t="s">
         <v>297</v>
       </c>
@@ -7928,7 +7918,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" hidden="1" spans="1:7">
       <c r="A146" s="6" t="s">
         <v>304</v>
       </c>
@@ -7951,7 +7941,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" hidden="1" spans="1:7">
       <c r="A147" s="6" t="s">
         <v>308</v>
       </c>
@@ -7974,7 +7964,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" hidden="1" spans="1:7">
       <c r="A148" s="6" t="s">
         <v>308</v>
       </c>
@@ -7997,7 +7987,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" hidden="1" spans="1:7">
       <c r="A149" s="6" t="s">
         <v>308</v>
       </c>
@@ -8020,7 +8010,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" hidden="1" spans="1:7">
       <c r="A150" s="6" t="s">
         <v>308</v>
       </c>
@@ -8043,7 +8033,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" hidden="1" spans="1:7">
       <c r="A151" s="6" t="s">
         <v>321</v>
       </c>
@@ -8066,7 +8056,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" hidden="1" spans="1:7">
       <c r="A152" s="6" t="s">
         <v>321</v>
       </c>
@@ -8089,7 +8079,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" hidden="1" spans="1:7">
       <c r="A153" s="6" t="s">
         <v>321</v>
       </c>
@@ -8112,7 +8102,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" hidden="1" spans="1:7">
       <c r="A154" s="6" t="s">
         <v>321</v>
       </c>
@@ -8135,7 +8125,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" hidden="1" spans="1:7">
       <c r="A155" s="6" t="s">
         <v>331</v>
       </c>
@@ -8158,7 +8148,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" hidden="1" spans="1:7">
       <c r="A156" s="6" t="s">
         <v>331</v>
       </c>
@@ -8181,7 +8171,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" hidden="1" spans="1:7">
       <c r="A157" s="6" t="s">
         <v>277</v>
       </c>
@@ -8204,7 +8194,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" hidden="1" spans="1:7">
       <c r="A158" s="6" t="s">
         <v>338</v>
       </c>
@@ -8227,7 +8217,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" hidden="1" spans="1:7">
       <c r="A159" s="6" t="s">
         <v>286</v>
       </c>
@@ -8250,7 +8240,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" hidden="1" spans="1:7">
       <c r="A160" s="6" t="s">
         <v>286</v>
       </c>
@@ -8273,7 +8263,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" hidden="1" spans="1:7">
       <c r="A161" s="6" t="s">
         <v>292</v>
       </c>
@@ -8296,7 +8286,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" hidden="1" spans="1:7">
       <c r="A162" s="6" t="s">
         <v>292</v>
       </c>
@@ -8319,7 +8309,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" hidden="1" spans="1:7">
       <c r="A163" s="6" t="s">
         <v>297</v>
       </c>
@@ -8342,7 +8332,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" hidden="1" spans="1:7">
       <c r="A164" s="6" t="s">
         <v>304</v>
       </c>
@@ -8365,7 +8355,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" hidden="1" spans="1:7">
       <c r="A165" s="6" t="s">
         <v>304</v>
       </c>
@@ -8388,7 +8378,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" hidden="1" spans="1:7">
       <c r="A166" s="6" t="s">
         <v>308</v>
       </c>
@@ -8411,7 +8401,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" hidden="1" spans="1:7">
       <c r="A167" s="6" t="s">
         <v>308</v>
       </c>
@@ -8434,7 +8424,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" hidden="1" spans="1:7">
       <c r="A168" s="6" t="s">
         <v>321</v>
       </c>
@@ -8457,7 +8447,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" hidden="1" spans="1:7">
       <c r="A169" s="6" t="s">
         <v>321</v>
       </c>
@@ -8480,7 +8470,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" hidden="1" spans="1:7">
       <c r="A170" s="6" t="s">
         <v>321</v>
       </c>
@@ -8503,7 +8493,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" hidden="1" spans="1:7">
       <c r="A171" s="6" t="s">
         <v>321</v>
       </c>
@@ -8526,7 +8516,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" hidden="1" spans="1:7">
       <c r="A172" s="6" t="s">
         <v>331</v>
       </c>
@@ -8549,7 +8539,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" hidden="1" spans="1:7">
       <c r="A173" s="6" t="s">
         <v>331</v>
       </c>
@@ -8572,7 +8562,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" hidden="1" spans="1:7">
       <c r="A174" s="6" t="s">
         <v>374</v>
       </c>
@@ -8595,7 +8585,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" hidden="1" spans="1:7">
       <c r="A175" s="6" t="s">
         <v>377</v>
       </c>
@@ -8618,7 +8608,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" hidden="1" spans="1:7">
       <c r="A176" s="6" t="s">
         <v>380</v>
       </c>
@@ -8641,7 +8631,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" hidden="1" spans="1:7">
       <c r="A177" s="6" t="s">
         <v>286</v>
       </c>
@@ -8664,7 +8654,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" hidden="1" spans="1:7">
       <c r="A178" s="6" t="s">
         <v>286</v>
       </c>
@@ -8687,7 +8677,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" hidden="1" spans="1:7">
       <c r="A179" s="6" t="s">
         <v>292</v>
       </c>
@@ -8710,7 +8700,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" hidden="1" spans="1:7">
       <c r="A180" s="6" t="s">
         <v>297</v>
       </c>
@@ -8733,7 +8723,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" hidden="1" spans="1:7">
       <c r="A181" s="6" t="s">
         <v>297</v>
       </c>
@@ -8756,7 +8746,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" hidden="1" spans="1:7">
       <c r="A182" s="6" t="s">
         <v>304</v>
       </c>
@@ -8779,7 +8769,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" hidden="1" spans="1:7">
       <c r="A183" s="6" t="s">
         <v>331</v>
       </c>
@@ -8802,7 +8792,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" hidden="1" spans="1:7">
       <c r="A184" s="6" t="s">
         <v>331</v>
       </c>
@@ -8825,7 +8815,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" hidden="1" spans="1:7">
       <c r="A185" s="6" t="s">
         <v>331</v>
       </c>
@@ -8848,7 +8838,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" hidden="1" spans="1:7">
       <c r="A186" s="6" t="s">
         <v>331</v>
       </c>
@@ -8871,7 +8861,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" hidden="1" spans="1:7">
       <c r="A187" s="6" t="s">
         <v>308</v>
       </c>
@@ -8894,7 +8884,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" hidden="1" spans="1:7">
       <c r="A188" s="6" t="s">
         <v>308</v>
       </c>
@@ -8917,7 +8907,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" hidden="1" spans="1:7">
       <c r="A189" s="6" t="s">
         <v>308</v>
       </c>
@@ -8940,7 +8930,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" hidden="1" spans="1:7">
       <c r="A190" s="6" t="s">
         <v>308</v>
       </c>
@@ -8963,7 +8953,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" hidden="1" spans="1:7">
       <c r="A191" s="6" t="s">
         <v>321</v>
       </c>
@@ -8986,7 +8976,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" hidden="1" spans="1:7">
       <c r="A192" s="6" t="s">
         <v>321</v>
       </c>
@@ -9009,7 +8999,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" hidden="1" spans="1:7">
       <c r="A193" s="6" t="s">
         <v>374</v>
       </c>
@@ -9032,7 +9022,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" hidden="1" spans="1:7">
       <c r="A194" s="6" t="s">
         <v>416</v>
       </c>
@@ -9055,7 +9045,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" hidden="1" spans="1:7">
       <c r="A195" s="6" t="s">
         <v>286</v>
       </c>
@@ -9078,7 +9068,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" hidden="1" spans="1:7">
       <c r="A196" s="6" t="s">
         <v>292</v>
       </c>
@@ -9101,7 +9091,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" hidden="1" spans="1:7">
       <c r="A197" s="6" t="s">
         <v>292</v>
       </c>
@@ -9124,7 +9114,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" hidden="1" spans="1:7">
       <c r="A198" s="6" t="s">
         <v>297</v>
       </c>
@@ -9147,7 +9137,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" hidden="1" spans="1:7">
       <c r="A199" s="6" t="s">
         <v>304</v>
       </c>
@@ -9170,7 +9160,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" hidden="1" spans="1:7">
       <c r="A200" s="6" t="s">
         <v>304</v>
       </c>
@@ -9193,7 +9183,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" hidden="1" spans="1:7">
       <c r="A201" s="6" t="s">
         <v>308</v>
       </c>
@@ -9216,7 +9206,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" hidden="1" spans="1:7">
       <c r="A202" s="6" t="s">
         <v>308</v>
       </c>
@@ -9239,7 +9229,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" hidden="1" spans="1:7">
       <c r="A203" s="6" t="s">
         <v>321</v>
       </c>
@@ -9262,7 +9252,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" hidden="1" spans="1:7">
       <c r="A204" s="6" t="s">
         <v>321</v>
       </c>
@@ -9285,7 +9275,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" hidden="1" spans="1:7">
       <c r="A205" s="6" t="s">
         <v>321</v>
       </c>
@@ -9308,7 +9298,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" hidden="1" spans="1:7">
       <c r="A206" s="6" t="s">
         <v>321</v>
       </c>
@@ -9331,7 +9321,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" hidden="1" spans="1:7">
       <c r="A207" s="6" t="s">
         <v>331</v>
       </c>
@@ -9354,7 +9344,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" hidden="1" spans="1:7">
       <c r="A208" s="6" t="s">
         <v>331</v>
       </c>
@@ -9377,7 +9367,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" hidden="1" spans="1:7">
       <c r="A209" s="6" t="s">
         <v>331</v>
       </c>
@@ -9400,7 +9390,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" hidden="1" spans="1:7">
       <c r="A210" s="6" t="s">
         <v>331</v>
       </c>
@@ -9423,7 +9413,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" hidden="1" spans="1:7">
       <c r="A211" s="6" t="s">
         <v>282</v>
       </c>
@@ -9446,7 +9436,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" hidden="1" spans="1:7">
       <c r="A212" s="6" t="s">
         <v>44</v>
       </c>
@@ -9469,7 +9459,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" hidden="1" spans="1:7">
       <c r="A213" s="6" t="s">
         <v>286</v>
       </c>
@@ -9492,7 +9482,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" hidden="1" spans="1:7">
       <c r="A214" s="6" t="s">
         <v>292</v>
       </c>
@@ -9515,7 +9505,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" hidden="1" spans="1:7">
       <c r="A215" s="6" t="s">
         <v>297</v>
       </c>
@@ -9538,7 +9528,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" hidden="1" spans="1:7">
       <c r="A216" s="6" t="s">
         <v>297</v>
       </c>
@@ -9561,7 +9551,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" hidden="1" spans="1:7">
       <c r="A217" s="6" t="s">
         <v>304</v>
       </c>
@@ -9584,7 +9574,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" hidden="1" spans="1:7">
       <c r="A218" s="6" t="s">
         <v>304</v>
       </c>
@@ -9607,7 +9597,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" hidden="1" spans="1:7">
       <c r="A219" s="6" t="s">
         <v>308</v>
       </c>
@@ -9630,7 +9620,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" hidden="1" spans="1:7">
       <c r="A220" s="6" t="s">
         <v>308</v>
       </c>
@@ -9653,7 +9643,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" hidden="1" spans="1:7">
       <c r="A221" s="6" t="s">
         <v>308</v>
       </c>
@@ -9676,7 +9666,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" hidden="1" spans="1:7">
       <c r="A222" s="6" t="s">
         <v>308</v>
       </c>
@@ -9699,7 +9689,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" hidden="1" spans="1:7">
       <c r="A223" s="6" t="s">
         <v>321</v>
       </c>
@@ -9722,7 +9712,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" hidden="1" spans="1:7">
       <c r="A224" s="6" t="s">
         <v>321</v>
       </c>
@@ -9745,7 +9735,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" hidden="1" spans="1:7">
       <c r="A225" s="6" t="s">
         <v>331</v>
       </c>
@@ -9768,7 +9758,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" hidden="1" spans="1:7">
       <c r="A226" s="6" t="s">
         <v>331</v>
       </c>
@@ -9791,7 +9781,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" hidden="1" spans="1:7">
       <c r="A227" s="6" t="s">
         <v>331</v>
       </c>
@@ -9814,7 +9804,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" hidden="1" spans="1:7">
       <c r="A228" s="6" t="s">
         <v>331</v>
       </c>
@@ -9837,7 +9827,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" hidden="1" spans="1:7">
       <c r="A229" s="6" t="s">
         <v>481</v>
       </c>
@@ -9860,7 +9850,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" hidden="1" spans="1:7">
       <c r="A230" s="6" t="s">
         <v>484</v>
       </c>
@@ -9883,7 +9873,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" hidden="1" spans="1:7">
       <c r="A231" s="6" t="s">
         <v>484</v>
       </c>
@@ -9906,7 +9896,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" hidden="1" spans="1:7">
       <c r="A232" s="6" t="s">
         <v>488</v>
       </c>
@@ -9929,7 +9919,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" hidden="1" spans="1:7">
       <c r="A233" s="6" t="s">
         <v>492</v>
       </c>
@@ -9952,7 +9942,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" hidden="1" spans="1:7">
       <c r="A234" s="6" t="s">
         <v>76</v>
       </c>
@@ -9975,7 +9965,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" hidden="1" spans="1:7">
       <c r="A235" s="6" t="s">
         <v>76</v>
       </c>
@@ -9998,7 +9988,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" hidden="1" spans="1:7">
       <c r="A236" s="6" t="s">
         <v>76</v>
       </c>
@@ -10021,7 +10011,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" hidden="1" spans="1:7">
       <c r="A237" s="6" t="s">
         <v>79</v>
       </c>
@@ -10044,7 +10034,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" hidden="1" spans="1:7">
       <c r="A238" s="6" t="s">
         <v>79</v>
       </c>
@@ -10067,7 +10057,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" hidden="1" spans="1:7">
       <c r="A239" s="6" t="s">
         <v>502</v>
       </c>
@@ -10090,7 +10080,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" hidden="1" spans="1:7">
       <c r="A240" s="6" t="s">
         <v>502</v>
       </c>
@@ -10113,7 +10103,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" hidden="1" spans="1:7">
       <c r="A241" s="6" t="s">
         <v>502</v>
       </c>
@@ -10136,7 +10126,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" hidden="1" spans="1:7">
       <c r="A242" s="6" t="s">
         <v>506</v>
       </c>
@@ -10159,7 +10149,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" hidden="1" spans="1:7">
       <c r="A243" s="6" t="s">
         <v>506</v>
       </c>
@@ -10182,7 +10172,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" hidden="1" spans="1:7">
       <c r="A244" s="6" t="s">
         <v>510</v>
       </c>
@@ -10205,7 +10195,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" hidden="1" spans="1:7">
       <c r="A245" s="6" t="s">
         <v>510</v>
       </c>
@@ -10228,7 +10218,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" hidden="1" spans="1:7">
       <c r="A246" s="6" t="s">
         <v>514</v>
       </c>
@@ -10251,7 +10241,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" hidden="1" spans="1:7">
       <c r="A247" s="6" t="s">
         <v>518</v>
       </c>
@@ -10274,7 +10264,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" hidden="1" spans="1:7">
       <c r="A248" s="6" t="s">
         <v>518</v>
       </c>
@@ -10297,7 +10287,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" hidden="1" spans="1:7">
       <c r="A249" s="6" t="s">
         <v>521</v>
       </c>
@@ -10320,7 +10310,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" hidden="1" spans="1:7">
       <c r="A250" s="6" t="s">
         <v>521</v>
       </c>
@@ -10343,7 +10333,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" hidden="1" spans="1:7">
       <c r="A251" s="6" t="s">
         <v>525</v>
       </c>
@@ -10366,7 +10356,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" hidden="1" spans="1:7">
       <c r="A252" s="6" t="s">
         <v>521</v>
       </c>
@@ -10389,7 +10379,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" hidden="1" spans="1:7">
       <c r="A253" s="6" t="s">
         <v>510</v>
       </c>
@@ -10412,7 +10402,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" hidden="1" spans="1:7">
       <c r="A254" s="6" t="s">
         <v>79</v>
       </c>
@@ -10435,7 +10425,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" hidden="1" spans="1:7">
       <c r="A255" s="6" t="s">
         <v>79</v>
       </c>
@@ -10458,7 +10448,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" hidden="1" spans="1:7">
       <c r="A256" s="6" t="s">
         <v>530</v>
       </c>
@@ -10481,7 +10471,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" hidden="1" spans="1:7">
       <c r="A257" s="6" t="s">
         <v>484</v>
       </c>
@@ -10504,7 +10494,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" hidden="1" spans="1:7">
       <c r="A258" s="6" t="s">
         <v>110</v>
       </c>
@@ -10527,7 +10517,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" hidden="1" spans="1:7">
       <c r="A259" s="6" t="s">
         <v>110</v>
       </c>
@@ -10550,7 +10540,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" hidden="1" spans="1:7">
       <c r="A260" s="6" t="s">
         <v>110</v>
       </c>
@@ -10573,7 +10563,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" hidden="1" spans="1:7">
       <c r="A261" s="6" t="s">
         <v>536</v>
       </c>
@@ -10596,7 +10586,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" hidden="1" spans="1:7">
       <c r="A262" s="6" t="s">
         <v>536</v>
       </c>
@@ -10619,7 +10609,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" hidden="1" spans="1:7">
       <c r="A263" s="6" t="s">
         <v>536</v>
       </c>
@@ -10642,7 +10632,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" hidden="1" spans="1:7">
       <c r="A264" s="6" t="s">
         <v>79</v>
       </c>
@@ -10665,7 +10655,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" hidden="1" spans="1:7">
       <c r="A265" s="6" t="s">
         <v>79</v>
       </c>
@@ -10688,7 +10678,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" hidden="1" spans="1:7">
       <c r="A266" s="6" t="s">
         <v>79</v>
       </c>
@@ -10711,7 +10701,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" hidden="1" spans="1:7">
       <c r="A267" s="6" t="s">
         <v>541</v>
       </c>
@@ -10734,7 +10724,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" hidden="1" spans="1:7">
       <c r="A268" s="6" t="s">
         <v>108</v>
       </c>
@@ -10757,7 +10747,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" hidden="1" spans="1:7">
       <c r="A269" s="6" t="s">
         <v>76</v>
       </c>
@@ -10780,7 +10770,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" hidden="1" spans="1:7">
       <c r="A270" s="6" t="s">
         <v>76</v>
       </c>
@@ -10803,7 +10793,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" hidden="1" spans="1:7">
       <c r="A271" s="6" t="s">
         <v>544</v>
       </c>
@@ -10826,7 +10816,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" hidden="1" spans="1:7">
       <c r="A272" s="6" t="s">
         <v>549</v>
       </c>
@@ -10849,7 +10839,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" hidden="1" spans="1:7">
       <c r="A273" s="6" t="s">
         <v>552</v>
       </c>
@@ -10872,7 +10862,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" hidden="1" spans="1:7">
       <c r="A274" s="6" t="s">
         <v>552</v>
       </c>
@@ -10895,7 +10885,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" hidden="1" spans="1:7">
       <c r="A275" s="6" t="s">
         <v>552</v>
       </c>
@@ -10918,7 +10908,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" hidden="1" spans="1:7">
       <c r="A276" s="6" t="s">
         <v>552</v>
       </c>
@@ -10941,7 +10931,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" hidden="1" spans="1:7">
       <c r="A277" s="6" t="s">
         <v>556</v>
       </c>
@@ -10964,7 +10954,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" hidden="1" spans="1:7">
       <c r="A278" s="6" t="s">
         <v>556</v>
       </c>
@@ -10987,7 +10977,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" hidden="1" spans="1:7">
       <c r="A279" s="6" t="s">
         <v>559</v>
       </c>
@@ -11010,7 +11000,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" hidden="1" spans="1:7">
       <c r="A280" s="6" t="s">
         <v>148</v>
       </c>
@@ -11033,7 +11023,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" hidden="1" spans="1:7">
       <c r="A281" s="6" t="s">
         <v>151</v>
       </c>
@@ -11056,7 +11046,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" hidden="1" spans="1:7">
       <c r="A282" s="6" t="s">
         <v>151</v>
       </c>
@@ -11079,7 +11069,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" hidden="1" spans="1:7">
       <c r="A283" s="6" t="s">
         <v>567</v>
       </c>
@@ -11102,7 +11092,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" hidden="1" spans="1:7">
       <c r="A284" s="6" t="s">
         <v>567</v>
       </c>
@@ -11125,7 +11115,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" hidden="1" spans="1:7">
       <c r="A285" s="6" t="s">
         <v>570</v>
       </c>
@@ -11148,7 +11138,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" hidden="1" spans="1:7">
       <c r="A286" s="6" t="s">
         <v>570</v>
       </c>
@@ -11171,7 +11161,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" hidden="1" spans="1:7">
       <c r="A287" s="6" t="s">
         <v>574</v>
       </c>
@@ -11194,7 +11184,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" hidden="1" spans="1:7">
       <c r="A288" s="6" t="s">
         <v>574</v>
       </c>
@@ -11217,7 +11207,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" hidden="1" spans="1:7">
       <c r="A289" s="6" t="s">
         <v>574</v>
       </c>
@@ -11240,7 +11230,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" hidden="1" spans="1:7">
       <c r="A290" s="6" t="s">
         <v>556</v>
       </c>
@@ -11263,7 +11253,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" hidden="1" spans="1:7">
       <c r="A291" s="6" t="s">
         <v>556</v>
       </c>
@@ -11286,7 +11276,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" hidden="1" spans="1:7">
       <c r="A292" s="6" t="s">
         <v>556</v>
       </c>
@@ -11309,7 +11299,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" hidden="1" spans="1:7">
       <c r="A293" s="6" t="s">
         <v>556</v>
       </c>
@@ -11332,7 +11322,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" hidden="1" spans="1:7">
       <c r="A294" s="6" t="s">
         <v>584</v>
       </c>
@@ -11355,7 +11345,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" hidden="1" spans="1:7">
       <c r="A295" s="6" t="s">
         <v>567</v>
       </c>
@@ -11378,7 +11368,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" hidden="1" spans="1:7">
       <c r="A296" s="6" t="s">
         <v>567</v>
       </c>
@@ -11424,7 +11414,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" hidden="1" spans="1:7">
       <c r="A298" s="6" t="s">
         <v>151</v>
       </c>
@@ -11447,7 +11437,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" hidden="1" spans="1:7">
       <c r="A299" s="6" t="s">
         <v>592</v>
       </c>
@@ -11470,7 +11460,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" hidden="1" spans="1:7">
       <c r="A300" s="6" t="s">
         <v>595</v>
       </c>
@@ -11493,7 +11483,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" hidden="1" spans="1:7">
       <c r="A301" s="6" t="s">
         <v>595</v>
       </c>
@@ -11516,7 +11506,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" hidden="1" spans="1:7">
       <c r="A302" s="6" t="s">
         <v>595</v>
       </c>
@@ -11539,7 +11529,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" hidden="1" spans="1:7">
       <c r="A303" s="6" t="s">
         <v>595</v>
       </c>
@@ -11562,7 +11552,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" hidden="1" spans="1:7">
       <c r="A304" s="6" t="s">
         <v>600</v>
       </c>
@@ -11585,7 +11575,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" hidden="1" spans="1:7">
       <c r="A305" s="6" t="s">
         <v>600</v>
       </c>
@@ -11608,7 +11598,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" hidden="1" spans="1:7">
       <c r="A306" s="6" t="s">
         <v>151</v>
       </c>
@@ -11631,7 +11621,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" hidden="1" spans="1:7">
       <c r="A307" s="6" t="s">
         <v>604</v>
       </c>
@@ -11654,7 +11644,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" hidden="1" spans="1:7">
       <c r="A308" s="6" t="s">
         <v>570</v>
       </c>
@@ -11677,7 +11667,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" hidden="1" spans="1:7">
       <c r="A309" s="6" t="s">
         <v>570</v>
       </c>
@@ -11700,7 +11690,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" hidden="1" spans="1:7">
       <c r="A310" s="6" t="s">
         <v>549</v>
       </c>
@@ -11723,7 +11713,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" hidden="1" spans="1:7">
       <c r="A311" s="6" t="s">
         <v>608</v>
       </c>
@@ -11746,7 +11736,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" hidden="1" spans="1:7">
       <c r="A312" s="6" t="s">
         <v>610</v>
       </c>
@@ -11769,7 +11759,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" hidden="1" spans="1:7">
       <c r="A313" s="6" t="s">
         <v>613</v>
       </c>
@@ -11792,7 +11782,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" hidden="1" spans="1:7">
       <c r="A314" s="6" t="s">
         <v>613</v>
       </c>
@@ -11815,7 +11805,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" hidden="1" spans="1:7">
       <c r="A315" s="6" t="s">
         <v>62</v>
       </c>
@@ -11838,7 +11828,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" hidden="1" spans="1:7">
       <c r="A316" s="6" t="s">
         <v>62</v>
       </c>
@@ -11861,7 +11851,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" hidden="1" spans="1:7">
       <c r="A317" s="6" t="s">
         <v>62</v>
       </c>
@@ -11884,7 +11874,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" hidden="1" spans="1:7">
       <c r="A318" s="6" t="s">
         <v>62</v>
       </c>
@@ -11907,7 +11897,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" hidden="1" spans="1:7">
       <c r="A319" s="6" t="s">
         <v>617</v>
       </c>
@@ -11930,7 +11920,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" hidden="1" spans="1:7">
       <c r="A320" s="6" t="s">
         <v>617</v>
       </c>
@@ -11953,7 +11943,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" hidden="1" spans="1:7">
       <c r="A321" s="6" t="s">
         <v>617</v>
       </c>
@@ -11976,7 +11966,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" hidden="1" spans="1:7">
       <c r="A322" s="6" t="s">
         <v>617</v>
       </c>
@@ -11999,7 +11989,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" hidden="1" spans="1:7">
       <c r="A323" s="6" t="s">
         <v>622</v>
       </c>
@@ -12022,7 +12012,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" hidden="1" spans="1:7">
       <c r="A324" s="6" t="s">
         <v>625</v>
       </c>
@@ -12045,7 +12035,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" hidden="1" spans="1:7">
       <c r="A325" s="6" t="s">
         <v>627</v>
       </c>
@@ -12068,7 +12058,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" hidden="1" spans="1:7">
       <c r="A326" s="6" t="s">
         <v>627</v>
       </c>
@@ -12091,7 +12081,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" hidden="1" spans="1:7">
       <c r="A327" s="6" t="s">
         <v>630</v>
       </c>
@@ -12114,7 +12104,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" hidden="1" spans="1:7">
       <c r="A328" s="6" t="s">
         <v>633</v>
       </c>
@@ -12137,7 +12127,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" hidden="1" spans="1:7">
       <c r="A329" s="6" t="s">
         <v>636</v>
       </c>
@@ -12160,7 +12150,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" hidden="1" spans="1:7">
       <c r="A330" s="6" t="s">
         <v>639</v>
       </c>
@@ -12183,7 +12173,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" hidden="1" spans="1:7">
       <c r="A331" s="6" t="s">
         <v>639</v>
       </c>
@@ -12298,7 +12288,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" hidden="1" spans="1:7">
       <c r="A336" s="6" t="s">
         <v>649</v>
       </c>
@@ -12321,7 +12311,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" hidden="1" spans="1:7">
       <c r="A337" s="6" t="s">
         <v>651</v>
       </c>
@@ -12344,7 +12334,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" hidden="1" spans="1:7">
       <c r="A338" s="6" t="s">
         <v>653</v>
       </c>
@@ -12367,7 +12357,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" hidden="1" spans="1:7">
       <c r="A339" s="6" t="s">
         <v>653</v>
       </c>
@@ -12390,7 +12380,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" hidden="1" spans="1:7">
       <c r="A340" s="6" t="s">
         <v>656</v>
       </c>
@@ -12413,7 +12403,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" hidden="1" spans="1:7">
       <c r="A341" s="6" t="s">
         <v>653</v>
       </c>
@@ -12436,7 +12426,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" hidden="1" spans="1:7">
       <c r="A342" s="6" t="s">
         <v>653</v>
       </c>
@@ -12459,7 +12449,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" hidden="1" spans="1:7">
       <c r="A343" s="6" t="s">
         <v>658</v>
       </c>
@@ -12482,7 +12472,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" hidden="1" spans="1:7">
       <c r="A344" s="6" t="s">
         <v>661</v>
       </c>
@@ -12505,7 +12495,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" hidden="1" spans="1:7">
       <c r="A345" s="6" t="s">
         <v>661</v>
       </c>
@@ -12528,7 +12518,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" hidden="1" spans="1:7">
       <c r="A346" s="6" t="s">
         <v>636</v>
       </c>
@@ -12551,7 +12541,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" hidden="1" spans="1:7">
       <c r="A347" s="6" t="s">
         <v>666</v>
       </c>
@@ -12574,7 +12564,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" hidden="1" spans="1:7">
       <c r="A348" s="6" t="s">
         <v>666</v>
       </c>
@@ -12597,7 +12587,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" hidden="1" spans="1:7">
       <c r="A349" s="6" t="s">
         <v>622</v>
       </c>
@@ -12620,7 +12610,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" hidden="1" spans="1:7">
       <c r="A350" s="6" t="s">
         <v>625</v>
       </c>
@@ -12643,7 +12633,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" hidden="1" spans="1:7">
       <c r="A351" s="6" t="s">
         <v>671</v>
       </c>
@@ -12666,7 +12656,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" hidden="1" spans="1:7">
       <c r="A352" s="6" t="s">
         <v>671</v>
       </c>
@@ -12689,7 +12679,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" hidden="1" spans="1:7">
       <c r="A353" s="6" t="s">
         <v>673</v>
       </c>
@@ -12712,7 +12702,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" hidden="1" spans="1:7">
       <c r="A354" s="6" t="s">
         <v>633</v>
       </c>
@@ -12827,7 +12817,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" hidden="1" spans="1:7">
       <c r="A359" s="6" t="s">
         <v>649</v>
       </c>
@@ -12850,7 +12840,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" hidden="1" spans="1:7">
       <c r="A360" s="6" t="s">
         <v>651</v>
       </c>
@@ -12873,7 +12863,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" hidden="1" spans="1:7">
       <c r="A361" s="6" t="s">
         <v>683</v>
       </c>
@@ -12896,7 +12886,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" hidden="1" spans="1:7">
       <c r="A362" s="6" t="s">
         <v>683</v>
       </c>
@@ -12919,7 +12909,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" hidden="1" spans="1:7">
       <c r="A363" s="6" t="s">
         <v>686</v>
       </c>
@@ -12942,7 +12932,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" hidden="1" spans="1:7">
       <c r="A364" s="6" t="s">
         <v>688</v>
       </c>
@@ -12965,7 +12955,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" hidden="1" spans="1:7">
       <c r="A365" s="6" t="s">
         <v>688</v>
       </c>
@@ -12988,7 +12978,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" hidden="1" spans="1:7">
       <c r="A366" s="6" t="s">
         <v>690</v>
       </c>
@@ -13011,7 +13001,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" hidden="1" spans="1:7">
       <c r="A367" s="6" t="s">
         <v>690</v>
       </c>
@@ -13034,7 +13024,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" hidden="1" spans="1:7">
       <c r="A368" s="6" t="s">
         <v>658</v>
       </c>
@@ -13057,7 +13047,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" hidden="1" spans="1:7">
       <c r="A369" s="6" t="s">
         <v>693</v>
       </c>
@@ -13080,7 +13070,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" hidden="1" spans="1:7">
       <c r="A370" s="6" t="s">
         <v>697</v>
       </c>
@@ -13103,7 +13093,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" hidden="1" spans="1:7">
       <c r="A371" s="6" t="s">
         <v>666</v>
       </c>
@@ -13126,7 +13116,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" hidden="1" spans="1:7">
       <c r="A372" s="6" t="s">
         <v>666</v>
       </c>
@@ -13149,7 +13139,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" hidden="1" spans="1:7">
       <c r="A373" s="6" t="s">
         <v>701</v>
       </c>
@@ -13172,7 +13162,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" hidden="1" spans="1:7">
       <c r="A374" s="6" t="s">
         <v>704</v>
       </c>
@@ -13195,7 +13185,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" hidden="1" spans="1:7">
       <c r="A375" s="6" t="s">
         <v>705</v>
       </c>
@@ -13218,7 +13208,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" hidden="1" spans="1:7">
       <c r="A376" s="6" t="s">
         <v>707</v>
       </c>
@@ -13241,7 +13231,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" hidden="1" spans="1:7">
       <c r="A377" s="6" t="s">
         <v>678</v>
       </c>
@@ -13264,7 +13254,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" hidden="1" spans="1:7">
       <c r="A378" s="6" t="s">
         <v>678</v>
       </c>
@@ -13287,7 +13277,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" hidden="1" spans="1:7">
       <c r="A379" s="6" t="s">
         <v>666</v>
       </c>
@@ -13310,7 +13300,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" hidden="1" spans="1:7">
       <c r="A380" s="6" t="s">
         <v>666</v>
       </c>
@@ -13333,7 +13323,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" hidden="1" spans="1:7">
       <c r="A381" s="6" t="s">
         <v>630</v>
       </c>
@@ -13356,7 +13346,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" hidden="1" spans="1:7">
       <c r="A382" s="6" t="s">
         <v>630</v>
       </c>
@@ -13379,7 +13369,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" hidden="1" spans="1:7">
       <c r="A383" s="6" t="s">
         <v>678</v>
       </c>
@@ -13402,7 +13392,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" hidden="1" spans="1:7">
       <c r="A384" s="6" t="s">
         <v>678</v>
       </c>
@@ -13425,7 +13415,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" hidden="1" spans="1:7">
       <c r="A385" s="6" t="s">
         <v>713</v>
       </c>
@@ -13448,7 +13438,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" hidden="1" spans="1:7">
       <c r="A386" s="6" t="s">
         <v>713</v>
       </c>
@@ -13471,7 +13461,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" hidden="1" spans="1:7">
       <c r="A387" s="6" t="s">
         <v>715</v>
       </c>
@@ -13494,7 +13484,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" hidden="1" spans="1:7">
       <c r="A388" s="6" t="s">
         <v>715</v>
       </c>
@@ -13517,7 +13507,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" hidden="1" spans="1:7">
       <c r="A389" s="6" t="s">
         <v>686</v>
       </c>
@@ -13540,7 +13530,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390" s="6" t="s">
         <v>720</v>
       </c>
@@ -13563,7 +13553,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" hidden="1" spans="1:7">
       <c r="A391" s="6" t="s">
         <v>723</v>
       </c>
@@ -13586,7 +13576,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" hidden="1" spans="1:7">
       <c r="A392" s="6" t="s">
         <v>226</v>
       </c>
@@ -13609,7 +13599,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" hidden="1" spans="1:7">
       <c r="A393" s="6" t="s">
         <v>229</v>
       </c>
@@ -13632,7 +13622,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" hidden="1" spans="1:7">
       <c r="A394" s="6" t="s">
         <v>636</v>
       </c>
@@ -13655,7 +13645,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" hidden="1" spans="1:7">
       <c r="A395" s="6" t="s">
         <v>658</v>
       </c>
@@ -13678,7 +13668,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" hidden="1" spans="1:7">
       <c r="A396" s="6" t="s">
         <v>630</v>
       </c>
@@ -13701,7 +13691,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" hidden="1" spans="1:7">
       <c r="A397" s="6" t="s">
         <v>633</v>
       </c>
@@ -13724,7 +13714,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" hidden="1" spans="1:7">
       <c r="A398" s="6" t="s">
         <v>678</v>
       </c>
@@ -13747,7 +13737,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" hidden="1" spans="1:7">
       <c r="A399" s="6" t="s">
         <v>678</v>
       </c>
@@ -13770,7 +13760,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" hidden="1" spans="1:7">
       <c r="A400" s="6" t="s">
         <v>649</v>
       </c>
@@ -13793,7 +13783,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" hidden="1" spans="1:7">
       <c r="A401" s="6" t="s">
         <v>736</v>
       </c>
@@ -13816,7 +13806,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" hidden="1" spans="1:7">
       <c r="A402" s="6" t="s">
         <v>736</v>
       </c>
@@ -13839,7 +13829,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" hidden="1" spans="1:7">
       <c r="A403" s="6" t="s">
         <v>651</v>
       </c>
@@ -13862,7 +13852,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
+    <row r="404" hidden="1" spans="1:7">
       <c r="A404" s="6" t="s">
         <v>690</v>
       </c>
@@ -13885,7 +13875,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" hidden="1" spans="1:7">
       <c r="A405" s="6" t="s">
         <v>690</v>
       </c>
@@ -13908,7 +13898,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" hidden="1" spans="1:7">
       <c r="A406" s="6" t="s">
         <v>686</v>
       </c>
@@ -13931,7 +13921,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
+    <row r="407" hidden="1" spans="1:7">
       <c r="A407" s="6" t="s">
         <v>678</v>
       </c>
@@ -13954,7 +13944,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" hidden="1" spans="1:7">
       <c r="A408" s="6" t="s">
         <v>666</v>
       </c>
@@ -13977,7 +13967,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" hidden="1" spans="1:7">
       <c r="A409" s="6" t="s">
         <v>666</v>
       </c>
@@ -14000,7 +13990,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" hidden="1" spans="1:7">
       <c r="A410" s="6" t="s">
         <v>746</v>
       </c>
@@ -14023,7 +14013,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" hidden="1" spans="1:7">
       <c r="A411" s="6" t="s">
         <v>226</v>
       </c>
@@ -14046,7 +14036,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" hidden="1" spans="1:7">
       <c r="A412" s="6" t="s">
         <v>229</v>
       </c>
@@ -14069,7 +14059,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" hidden="1" spans="1:7">
       <c r="A413" s="6" t="s">
         <v>622</v>
       </c>
@@ -14092,7 +14082,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" hidden="1" spans="1:7">
       <c r="A414" s="6" t="s">
         <v>625</v>
       </c>
@@ -14115,7 +14105,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" hidden="1" spans="1:7">
       <c r="A415" s="6" t="s">
         <v>671</v>
       </c>
@@ -14138,7 +14128,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" hidden="1" spans="1:7">
       <c r="A416" s="6" t="s">
         <v>671</v>
       </c>
@@ -14161,7 +14151,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" hidden="1" spans="1:7">
       <c r="A417" s="6" t="s">
         <v>754</v>
       </c>
@@ -14184,7 +14174,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" hidden="1" spans="1:7">
       <c r="A418" s="6" t="s">
         <v>758</v>
       </c>
@@ -14207,7 +14197,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" hidden="1" spans="1:7">
       <c r="A419" s="6" t="s">
         <v>761</v>
       </c>
@@ -14230,7 +14220,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" hidden="1" spans="1:7">
       <c r="A420" s="6" t="s">
         <v>678</v>
       </c>
@@ -14253,7 +14243,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" hidden="1" spans="1:7">
       <c r="A421" s="6" t="s">
         <v>678</v>
       </c>
@@ -14276,7 +14266,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" hidden="1" spans="1:7">
       <c r="A422" s="6" t="s">
         <v>765</v>
       </c>
@@ -14299,7 +14289,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" hidden="1" spans="1:7">
       <c r="A423" s="6" t="s">
         <v>736</v>
       </c>
@@ -14322,7 +14312,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" hidden="1" spans="1:7">
       <c r="A424" s="6" t="s">
         <v>736</v>
       </c>
@@ -14345,7 +14335,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" hidden="1" spans="1:7">
       <c r="A425" s="6" t="s">
         <v>651</v>
       </c>
@@ -14368,7 +14358,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" hidden="1" spans="1:7">
       <c r="A426" s="6" t="s">
         <v>770</v>
       </c>
@@ -14391,7 +14381,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" hidden="1" spans="1:7">
       <c r="A427" s="6" t="s">
         <v>772</v>
       </c>
@@ -14414,7 +14404,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" hidden="1" spans="1:7">
       <c r="A428" s="6" t="s">
         <v>686</v>
       </c>
@@ -14437,7 +14427,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" hidden="1" spans="1:7">
       <c r="A429" s="6" t="s">
         <v>666</v>
       </c>
@@ -14460,7 +14450,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" hidden="1" spans="1:7">
       <c r="A430" s="6" t="s">
         <v>666</v>
       </c>
@@ -14483,7 +14473,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" hidden="1" spans="1:7">
       <c r="A431" s="6" t="s">
         <v>777</v>
       </c>
@@ -14506,7 +14496,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" hidden="1" spans="1:7">
       <c r="A432" s="6" t="s">
         <v>779</v>
       </c>
@@ -14529,7 +14519,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" hidden="1" spans="1:7">
       <c r="A433" s="6" t="s">
         <v>780</v>
       </c>
@@ -14552,7 +14542,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" hidden="1" spans="1:7">
       <c r="A434" s="6" t="s">
         <v>780</v>
       </c>
@@ -14575,7 +14565,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" hidden="1" spans="1:7">
       <c r="A435" s="6" t="s">
         <v>622</v>
       </c>
@@ -14598,7 +14588,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" hidden="1" spans="1:7">
       <c r="A436" s="6" t="s">
         <v>701</v>
       </c>
@@ -14621,7 +14611,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" hidden="1" spans="1:7">
       <c r="A437" s="6" t="s">
         <v>671</v>
       </c>
@@ -14644,7 +14634,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" hidden="1" spans="1:7">
       <c r="A438" s="6" t="s">
         <v>671</v>
       </c>
@@ -14667,7 +14657,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" hidden="1" spans="1:7">
       <c r="A439" s="6" t="s">
         <v>786</v>
       </c>
@@ -14690,7 +14680,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="440" spans="1:7">
+    <row r="440" hidden="1" spans="1:7">
       <c r="A440" s="6" t="s">
         <v>786</v>
       </c>
@@ -14713,7 +14703,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="441" spans="1:7">
+    <row r="441" hidden="1" spans="1:7">
       <c r="A441" s="6" t="s">
         <v>791</v>
       </c>
@@ -14736,7 +14726,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" hidden="1" spans="1:7">
       <c r="A442" s="6" t="s">
         <v>793</v>
       </c>
@@ -14759,7 +14749,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="443" spans="1:7">
+    <row r="443" hidden="1" spans="1:7">
       <c r="A443" s="6" t="s">
         <v>793</v>
       </c>
@@ -14782,7 +14772,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="444" spans="1:7">
+    <row r="444" hidden="1" spans="1:7">
       <c r="A444" s="6" t="s">
         <v>795</v>
       </c>
@@ -14805,7 +14795,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="445" spans="1:7">
+    <row r="445" hidden="1" spans="1:7">
       <c r="A445" s="6" t="s">
         <v>797</v>
       </c>
@@ -14828,7 +14818,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="446" spans="1:7">
+    <row r="446" hidden="1" spans="1:7">
       <c r="A446" s="6" t="s">
         <v>797</v>
       </c>
@@ -14851,7 +14841,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
+    <row r="447" hidden="1" spans="1:7">
       <c r="A447" s="6" t="s">
         <v>802</v>
       </c>
@@ -14874,7 +14864,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" hidden="1" spans="1:7">
       <c r="A448" s="6" t="s">
         <v>805</v>
       </c>
@@ -14897,7 +14887,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" hidden="1" spans="1:7">
       <c r="A449" s="6" t="s">
         <v>807</v>
       </c>
@@ -14920,7 +14910,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" hidden="1" spans="1:7">
       <c r="A450" s="6" t="s">
         <v>807</v>
       </c>
@@ -14943,7 +14933,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" hidden="1" spans="1:7">
       <c r="A451" s="6" t="s">
         <v>809</v>
       </c>
@@ -14966,7 +14956,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="452" spans="1:7">
+    <row r="452" hidden="1" spans="1:7">
       <c r="A452" s="6" t="s">
         <v>811</v>
       </c>
@@ -14989,7 +14979,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="453" spans="1:7">
+    <row r="453" hidden="1" spans="1:7">
       <c r="A453" s="6" t="s">
         <v>814</v>
       </c>
@@ -15012,7 +15002,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="454" spans="1:7">
+    <row r="454" hidden="1" spans="1:7">
       <c r="A454" s="6" t="s">
         <v>814</v>
       </c>
@@ -15035,7 +15025,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="455" spans="1:7">
+    <row r="455" hidden="1" spans="1:7">
       <c r="A455" s="6" t="s">
         <v>816</v>
       </c>
@@ -15058,7 +15048,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" hidden="1" spans="1:7">
       <c r="A456" s="6" t="s">
         <v>816</v>
       </c>
@@ -15081,7 +15071,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="457" spans="1:7">
+    <row r="457" hidden="1" spans="1:7">
       <c r="A457" s="6" t="s">
         <v>786</v>
       </c>
@@ -15104,7 +15094,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="458" spans="1:7">
+    <row r="458" hidden="1" spans="1:7">
       <c r="A458" s="6" t="s">
         <v>786</v>
       </c>
@@ -15127,7 +15117,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="459" spans="1:7">
+    <row r="459" hidden="1" spans="1:7">
       <c r="A459" s="6" t="s">
         <v>820</v>
       </c>
@@ -15150,7 +15140,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" hidden="1" spans="1:7">
       <c r="A460" s="6" t="s">
         <v>822</v>
       </c>
@@ -15173,7 +15163,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" hidden="1" spans="1:7">
       <c r="A461" s="6" t="s">
         <v>824</v>
       </c>
@@ -15196,7 +15186,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="462" spans="1:7">
+    <row r="462" hidden="1" spans="1:7">
       <c r="A462" s="6" t="s">
         <v>824</v>
       </c>
@@ -15219,7 +15209,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="463" spans="1:7">
+    <row r="463" hidden="1" spans="1:7">
       <c r="A463" s="6" t="s">
         <v>827</v>
       </c>
@@ -15242,7 +15232,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="464" spans="1:7">
+    <row r="464" hidden="1" spans="1:7">
       <c r="A464" s="6" t="s">
         <v>829</v>
       </c>
@@ -15265,7 +15255,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="465" spans="1:7">
+    <row r="465" hidden="1" spans="1:7">
       <c r="A465" s="6" t="s">
         <v>832</v>
       </c>
@@ -15288,7 +15278,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="466" spans="1:7">
+    <row r="466" hidden="1" spans="1:7">
       <c r="A466" s="6" t="s">
         <v>834</v>
       </c>
@@ -15311,7 +15301,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="467" spans="1:7">
+    <row r="467" hidden="1" spans="1:7">
       <c r="A467" s="6" t="s">
         <v>838</v>
       </c>
@@ -15334,7 +15324,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="468" spans="1:7">
+    <row r="468" hidden="1" spans="1:7">
       <c r="A468" s="6" t="s">
         <v>840</v>
       </c>
@@ -15357,7 +15347,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="469" spans="1:7">
+    <row r="469" hidden="1" spans="1:7">
       <c r="A469" s="6" t="s">
         <v>842</v>
       </c>
@@ -15380,7 +15370,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="470" spans="1:7">
+    <row r="470" hidden="1" spans="1:7">
       <c r="A470" s="6" t="s">
         <v>844</v>
       </c>
@@ -15403,7 +15393,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="471" spans="1:7">
+    <row r="471" hidden="1" spans="1:7">
       <c r="A471" s="6" t="s">
         <v>846</v>
       </c>
@@ -15426,7 +15416,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="472" spans="1:7">
+    <row r="472" hidden="1" spans="1:7">
       <c r="A472" s="6" t="s">
         <v>846</v>
       </c>
@@ -15449,7 +15439,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="473" spans="1:7">
+    <row r="473" hidden="1" spans="1:7">
       <c r="A473" s="6" t="s">
         <v>850</v>
       </c>
@@ -15472,7 +15462,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="474" spans="1:7">
+    <row r="474" hidden="1" spans="1:7">
       <c r="A474" s="6" t="s">
         <v>852</v>
       </c>
@@ -15495,7 +15485,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="475" spans="1:7">
+    <row r="475" hidden="1" spans="1:7">
       <c r="A475" s="6" t="s">
         <v>854</v>
       </c>
@@ -15518,7 +15508,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="476" spans="1:7">
+    <row r="476" hidden="1" spans="1:7">
       <c r="A476" s="6" t="s">
         <v>856</v>
       </c>
@@ -15541,7 +15531,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="477" spans="1:7">
+    <row r="477" hidden="1" spans="1:7">
       <c r="A477" s="6" t="s">
         <v>858</v>
       </c>
@@ -15564,7 +15554,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="478" spans="1:7">
+    <row r="478" hidden="1" spans="1:7">
       <c r="A478" s="6" t="s">
         <v>860</v>
       </c>
@@ -15587,7 +15577,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="479" spans="1:7">
+    <row r="479" hidden="1" spans="1:7">
       <c r="A479" s="6" t="s">
         <v>860</v>
       </c>
@@ -15610,7 +15600,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="480" spans="1:7">
+    <row r="480" hidden="1" spans="1:7">
       <c r="A480" s="6" t="s">
         <v>865</v>
       </c>
@@ -15633,7 +15623,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="481" spans="1:7">
+    <row r="481" hidden="1" spans="1:7">
       <c r="A481" s="6" t="s">
         <v>868</v>
       </c>
@@ -15656,7 +15646,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="482" spans="1:7">
+    <row r="482" hidden="1" spans="1:7">
       <c r="A482" s="6" t="s">
         <v>869</v>
       </c>
@@ -15679,7 +15669,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="483" spans="1:7">
+    <row r="483" hidden="1" spans="1:7">
       <c r="A483" s="6" t="s">
         <v>827</v>
       </c>
@@ -15702,7 +15692,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="484" spans="1:7">
+    <row r="484" hidden="1" spans="1:7">
       <c r="A484" s="6" t="s">
         <v>873</v>
       </c>
@@ -15725,7 +15715,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="485" spans="1:7">
+    <row r="485" hidden="1" spans="1:7">
       <c r="A485" s="6" t="s">
         <v>876</v>
       </c>
@@ -15748,7 +15738,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="486" spans="1:7">
+    <row r="486" hidden="1" spans="1:7">
       <c r="A486" s="6" t="s">
         <v>879</v>
       </c>
@@ -15771,7 +15761,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="487" spans="1:7">
+    <row r="487" hidden="1" spans="1:7">
       <c r="A487" s="6" t="s">
         <v>881</v>
       </c>
@@ -15794,7 +15784,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="488" spans="1:7">
+    <row r="488" hidden="1" spans="1:7">
       <c r="A488" s="6" t="s">
         <v>885</v>
       </c>
@@ -15817,7 +15807,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="489" spans="1:7">
+    <row r="489" hidden="1" spans="1:7">
       <c r="A489" s="6" t="s">
         <v>795</v>
       </c>
@@ -15840,7 +15830,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="490" spans="1:7">
+    <row r="490" hidden="1" spans="1:7">
       <c r="A490" s="6" t="s">
         <v>888</v>
       </c>
@@ -15863,7 +15853,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="491" spans="1:7">
+    <row r="491" hidden="1" spans="1:7">
       <c r="A491" s="6" t="s">
         <v>890</v>
       </c>
@@ -15886,7 +15876,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="492" spans="1:7">
+    <row r="492" hidden="1" spans="1:7">
       <c r="A492" s="6" t="s">
         <v>892</v>
       </c>
@@ -15909,7 +15899,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="493" spans="1:7">
+    <row r="493" hidden="1" spans="1:7">
       <c r="A493" s="6" t="s">
         <v>894</v>
       </c>
@@ -15932,7 +15922,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="494" spans="1:7">
+    <row r="494" hidden="1" spans="1:7">
       <c r="A494" s="6" t="s">
         <v>898</v>
       </c>
@@ -15955,7 +15945,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="495" spans="1:7">
+    <row r="495" hidden="1" spans="1:7">
       <c r="A495" s="6" t="s">
         <v>900</v>
       </c>
@@ -15978,7 +15968,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="496" spans="1:7">
+    <row r="496" hidden="1" spans="1:7">
       <c r="A496" s="6" t="s">
         <v>902</v>
       </c>
@@ -16001,7 +15991,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="497" spans="1:7">
+    <row r="497" hidden="1" spans="1:7">
       <c r="A497" s="6" t="s">
         <v>904</v>
       </c>
@@ -16024,7 +16014,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="498" spans="1:7">
+    <row r="498" hidden="1" spans="1:7">
       <c r="A498" s="6" t="s">
         <v>827</v>
       </c>
@@ -16047,7 +16037,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="499" spans="1:7">
+    <row r="499" hidden="1" spans="1:7">
       <c r="A499" s="6" t="s">
         <v>907</v>
       </c>
@@ -16070,7 +16060,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="500" spans="1:7">
+    <row r="500" hidden="1" spans="1:7">
       <c r="A500" s="6" t="s">
         <v>910</v>
       </c>
@@ -16093,7 +16083,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="501" spans="1:7">
+    <row r="501" hidden="1" spans="1:7">
       <c r="A501" s="6" t="s">
         <v>912</v>
       </c>
@@ -16116,7 +16106,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="502" spans="1:7">
+    <row r="502" hidden="1" spans="1:7">
       <c r="A502" s="6" t="s">
         <v>915</v>
       </c>
@@ -16139,7 +16129,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="503" spans="1:7">
+    <row r="503" hidden="1" spans="1:7">
       <c r="A503" s="6" t="s">
         <v>270</v>
       </c>
@@ -16162,7 +16152,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="504" spans="1:7">
+    <row r="504" hidden="1" spans="1:7">
       <c r="A504" s="6" t="s">
         <v>273</v>
       </c>
@@ -16185,7 +16175,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="505" spans="1:7">
+    <row r="505" hidden="1" spans="1:7">
       <c r="A505" s="6" t="s">
         <v>919</v>
       </c>
@@ -16208,7 +16198,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="506" spans="1:7">
+    <row r="506" hidden="1" spans="1:7">
       <c r="A506" s="6" t="s">
         <v>922</v>
       </c>
@@ -16231,7 +16221,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="507" spans="1:7">
+    <row r="507" hidden="1" spans="1:7">
       <c r="A507" s="6" t="s">
         <v>924</v>
       </c>
@@ -16254,7 +16244,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="508" spans="1:7">
+    <row r="508" hidden="1" spans="1:7">
       <c r="A508" s="6" t="s">
         <v>924</v>
       </c>
@@ -16277,7 +16267,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="509" spans="1:7">
+    <row r="509" hidden="1" spans="1:7">
       <c r="A509" s="6" t="s">
         <v>928</v>
       </c>
@@ -16300,7 +16290,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="510" spans="1:7">
+    <row r="510" hidden="1" spans="1:7">
       <c r="A510" s="6" t="s">
         <v>931</v>
       </c>
@@ -16323,7 +16313,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="511" spans="1:7">
+    <row r="511" hidden="1" spans="1:7">
       <c r="A511" s="6" t="s">
         <v>933</v>
       </c>
@@ -16346,7 +16336,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="512" spans="1:7">
+    <row r="512" hidden="1" spans="1:7">
       <c r="A512" s="6" t="s">
         <v>933</v>
       </c>
@@ -16369,7 +16359,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="513" spans="1:7">
+    <row r="513" hidden="1" spans="1:7">
       <c r="A513" s="6" t="s">
         <v>935</v>
       </c>
@@ -16392,7 +16382,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="514" spans="1:7">
+    <row r="514" hidden="1" spans="1:7">
       <c r="A514" s="6" t="s">
         <v>795</v>
       </c>
@@ -16415,7 +16405,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="515" spans="1:7">
+    <row r="515" hidden="1" spans="1:7">
       <c r="A515" s="6" t="s">
         <v>938</v>
       </c>
@@ -16438,7 +16428,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="516" spans="1:7">
+    <row r="516" hidden="1" spans="1:7">
       <c r="A516" s="6" t="s">
         <v>940</v>
       </c>
@@ -16461,7 +16451,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="517" spans="1:7">
+    <row r="517" hidden="1" spans="1:7">
       <c r="A517" s="6" t="s">
         <v>942</v>
       </c>
@@ -16484,7 +16474,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="518" spans="1:7">
+    <row r="518" hidden="1" spans="1:7">
       <c r="A518" s="6" t="s">
         <v>945</v>
       </c>
@@ -16507,7 +16497,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="519" spans="1:7">
+    <row r="519" hidden="1" spans="1:7">
       <c r="A519" s="6" t="s">
         <v>946</v>
       </c>
@@ -16530,7 +16520,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="520" spans="1:7">
+    <row r="520" hidden="1" spans="1:7">
       <c r="A520" s="6" t="s">
         <v>949</v>
       </c>
@@ -16553,7 +16543,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="521" spans="1:7">
+    <row r="521" hidden="1" spans="1:7">
       <c r="A521" s="6" t="s">
         <v>951</v>
       </c>
@@ -16576,7 +16566,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="522" spans="1:7">
+    <row r="522" hidden="1" spans="1:7">
       <c r="A522" s="6" t="s">
         <v>953</v>
       </c>
@@ -16599,7 +16589,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="523" spans="1:7">
+    <row r="523" hidden="1" spans="1:7">
       <c r="A523" s="6" t="s">
         <v>956</v>
       </c>
@@ -16622,7 +16612,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="524" spans="1:7">
+    <row r="524" hidden="1" spans="1:7">
       <c r="A524" s="6" t="s">
         <v>957</v>
       </c>
@@ -16645,7 +16635,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="525" spans="1:7">
+    <row r="525" hidden="1" spans="1:7">
       <c r="A525" s="6" t="s">
         <v>959</v>
       </c>
@@ -16668,7 +16658,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="526" spans="1:7">
+    <row r="526" hidden="1" spans="1:7">
       <c r="A526" s="6" t="s">
         <v>961</v>
       </c>
@@ -16691,7 +16681,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="527" spans="1:7">
+    <row r="527" hidden="1" spans="1:7">
       <c r="A527" s="6" t="s">
         <v>964</v>
       </c>
@@ -16714,7 +16704,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="528" spans="1:7">
+    <row r="528" hidden="1" spans="1:7">
       <c r="A528" s="6" t="s">
         <v>965</v>
       </c>
@@ -16737,7 +16727,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="529" spans="1:7">
+    <row r="529" hidden="1" spans="1:7">
       <c r="A529" s="6" t="s">
         <v>942</v>
       </c>
@@ -16760,7 +16750,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="530" spans="1:7">
+    <row r="530" hidden="1" spans="1:7">
       <c r="A530" s="6" t="s">
         <v>945</v>
       </c>
@@ -16783,7 +16773,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="531" spans="1:7">
+    <row r="531" hidden="1" spans="1:7">
       <c r="A531" s="6" t="s">
         <v>968</v>
       </c>
@@ -16806,7 +16796,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="532" spans="1:7">
+    <row r="532" hidden="1" spans="1:7">
       <c r="A532" s="6" t="s">
         <v>971</v>
       </c>
@@ -16829,7 +16819,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="533" spans="1:7">
+    <row r="533" hidden="1" spans="1:7">
       <c r="A533" s="6" t="s">
         <v>973</v>
       </c>
@@ -16852,7 +16842,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="534" spans="1:7">
+    <row r="534" hidden="1" spans="1:7">
       <c r="A534" s="6" t="s">
         <v>975</v>
       </c>
@@ -16875,7 +16865,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="535" spans="1:7">
+    <row r="535" hidden="1" spans="1:7">
       <c r="A535" s="6" t="s">
         <v>977</v>
       </c>
@@ -16898,7 +16888,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="536" spans="1:7">
+    <row r="536" hidden="1" spans="1:7">
       <c r="A536" s="6" t="s">
         <v>979</v>
       </c>
@@ -16921,7 +16911,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="537" spans="1:7">
+    <row r="537" hidden="1" spans="1:7">
       <c r="A537" s="6" t="s">
         <v>795</v>
       </c>
@@ -16944,7 +16934,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="538" spans="1:7">
+    <row r="538" hidden="1" spans="1:7">
       <c r="A538" s="6" t="s">
         <v>982</v>
       </c>
@@ -16967,7 +16957,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="539" spans="1:7">
+    <row r="539" hidden="1" spans="1:7">
       <c r="A539" s="6" t="s">
         <v>984</v>
       </c>
@@ -16990,7 +16980,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="540" spans="1:7">
+    <row r="540" hidden="1" spans="1:7">
       <c r="A540" s="6" t="s">
         <v>986</v>
       </c>
@@ -17013,7 +17003,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="541" spans="1:7">
+    <row r="541" hidden="1" spans="1:7">
       <c r="A541" s="6" t="s">
         <v>827</v>
       </c>
@@ -17036,7 +17026,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="542" spans="1:7">
+    <row r="542" hidden="1" spans="1:7">
       <c r="A542" s="6" t="s">
         <v>988</v>
       </c>
@@ -17059,7 +17049,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="543" spans="1:7">
+    <row r="543" hidden="1" spans="1:7">
       <c r="A543" s="6" t="s">
         <v>990</v>
       </c>
@@ -17082,7 +17072,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="544" spans="1:7">
+    <row r="544" hidden="1" spans="1:7">
       <c r="A544" s="6" t="s">
         <v>991</v>
       </c>
@@ -17105,7 +17095,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="545" spans="1:7">
+    <row r="545" hidden="1" spans="1:7">
       <c r="A545" s="6" t="s">
         <v>993</v>
       </c>
@@ -17128,7 +17118,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="546" spans="1:7">
+    <row r="546" hidden="1" spans="1:7">
       <c r="A546" s="6" t="s">
         <v>829</v>
       </c>
@@ -17151,7 +17141,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="547" spans="1:7">
+    <row r="547" hidden="1" spans="1:7">
       <c r="A547" s="6" t="s">
         <v>270</v>
       </c>
@@ -17174,7 +17164,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="548" spans="1:7">
+    <row r="548" hidden="1" spans="1:7">
       <c r="A548" s="6" t="s">
         <v>273</v>
       </c>
@@ -17197,7 +17187,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="549" spans="1:7">
+    <row r="549" hidden="1" spans="1:7">
       <c r="A549" s="6" t="s">
         <v>998</v>
       </c>
@@ -17220,7 +17210,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="550" spans="1:7">
+    <row r="550" hidden="1" spans="1:7">
       <c r="A550" s="6" t="s">
         <v>1001</v>
       </c>
@@ -17243,7 +17233,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="551" spans="1:7">
+    <row r="551" hidden="1" spans="1:7">
       <c r="A551" s="6" t="s">
         <v>1003</v>
       </c>
@@ -17266,7 +17256,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="552" spans="1:7">
+    <row r="552" hidden="1" spans="1:7">
       <c r="A552" s="6" t="s">
         <v>76</v>
       </c>
@@ -17289,7 +17279,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="553" spans="1:7">
+    <row r="553" hidden="1" spans="1:7">
       <c r="A553" s="6" t="s">
         <v>76</v>
       </c>
@@ -17312,7 +17302,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="554" spans="1:7">
+    <row r="554" hidden="1" spans="1:7">
       <c r="A554" s="6" t="s">
         <v>76</v>
       </c>
@@ -17335,7 +17325,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="555" spans="1:7">
+    <row r="555" hidden="1" spans="1:7">
       <c r="A555" s="6" t="s">
         <v>76</v>
       </c>
@@ -17358,7 +17348,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="556" spans="1:7">
+    <row r="556" hidden="1" spans="1:7">
       <c r="A556" s="6" t="s">
         <v>76</v>
       </c>
@@ -17381,7 +17371,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="557" spans="1:7">
+    <row r="557" hidden="1" spans="1:7">
       <c r="A557" s="6" t="s">
         <v>79</v>
       </c>
@@ -17404,7 +17394,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="558" spans="1:7">
+    <row r="558" hidden="1" spans="1:7">
       <c r="A558" s="6" t="s">
         <v>79</v>
       </c>
@@ -17427,7 +17417,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="559" spans="1:7">
+    <row r="559" hidden="1" spans="1:7">
       <c r="A559" s="6" t="s">
         <v>530</v>
       </c>
@@ -17450,7 +17440,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="560" spans="1:7">
+    <row r="560" hidden="1" spans="1:7">
       <c r="A560" s="6" t="s">
         <v>1020</v>
       </c>
@@ -17473,7 +17463,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="561" spans="1:7">
+    <row r="561" hidden="1" spans="1:7">
       <c r="A561" s="6" t="s">
         <v>1023</v>
       </c>
@@ -17496,7 +17486,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="562" spans="1:7">
+    <row r="562" hidden="1" spans="1:7">
       <c r="A562" s="6" t="s">
         <v>1023</v>
       </c>
@@ -17519,7 +17509,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="563" spans="1:7">
+    <row r="563" hidden="1" spans="1:7">
       <c r="A563" s="6" t="s">
         <v>1023</v>
       </c>
@@ -17542,7 +17532,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="564" spans="1:7">
+    <row r="564" hidden="1" spans="1:7">
       <c r="A564" s="6" t="s">
         <v>1023</v>
       </c>
@@ -17565,7 +17555,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="565" spans="1:7">
+    <row r="565" hidden="1" spans="1:7">
       <c r="A565" s="6" t="s">
         <v>1029</v>
       </c>
@@ -17588,7 +17578,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="566" spans="1:7">
+    <row r="566" hidden="1" spans="1:7">
       <c r="A566" s="6" t="s">
         <v>1031</v>
       </c>
@@ -17611,7 +17601,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="567" spans="1:7">
+    <row r="567" hidden="1" spans="1:7">
       <c r="A567" s="6" t="s">
         <v>1031</v>
       </c>
@@ -17634,7 +17624,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="568" spans="1:7">
+    <row r="568" hidden="1" spans="1:7">
       <c r="A568" s="6" t="s">
         <v>1035</v>
       </c>
@@ -17657,7 +17647,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="569" spans="1:7">
+    <row r="569" hidden="1" spans="1:7">
       <c r="A569" s="6" t="s">
         <v>1035</v>
       </c>
@@ -17680,7 +17670,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="570" spans="1:7">
+    <row r="570" hidden="1" spans="1:7">
       <c r="A570" s="6" t="s">
         <v>1035</v>
       </c>
@@ -17703,7 +17693,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="571" spans="1:7">
+    <row r="571" hidden="1" spans="1:7">
       <c r="A571" s="6" t="s">
         <v>1039</v>
       </c>
@@ -17726,7 +17716,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="572" spans="1:7">
+    <row r="572" hidden="1" spans="1:7">
       <c r="A572" s="6" t="s">
         <v>1039</v>
       </c>
@@ -17749,7 +17739,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="573" spans="1:7">
+    <row r="573" hidden="1" spans="1:7">
       <c r="A573" s="6" t="s">
         <v>1003</v>
       </c>
@@ -17772,7 +17762,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="574" spans="1:7">
+    <row r="574" hidden="1" spans="1:7">
       <c r="A574" s="6" t="s">
         <v>79</v>
       </c>
@@ -17795,7 +17785,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="575" spans="1:7">
+    <row r="575" hidden="1" spans="1:7">
       <c r="A575" s="6" t="s">
         <v>79</v>
       </c>
@@ -17818,7 +17808,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="576" spans="1:7">
+    <row r="576" hidden="1" spans="1:7">
       <c r="A576" s="6" t="s">
         <v>95</v>
       </c>
@@ -17841,7 +17831,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="577" spans="1:7">
+    <row r="577" hidden="1" spans="1:7">
       <c r="A577" s="6" t="s">
         <v>1035</v>
       </c>
@@ -17864,7 +17854,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="578" spans="1:7">
+    <row r="578" hidden="1" spans="1:7">
       <c r="A578" s="6" t="s">
         <v>79</v>
       </c>
@@ -17887,7 +17877,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="579" spans="1:7">
+    <row r="579" hidden="1" spans="1:7">
       <c r="A579" s="6" t="s">
         <v>79</v>
       </c>
@@ -17910,7 +17900,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="580" spans="1:7">
+    <row r="580" hidden="1" spans="1:7">
       <c r="A580" s="6" t="s">
         <v>1052</v>
       </c>
@@ -17933,7 +17923,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="581" spans="1:7">
+    <row r="581" hidden="1" spans="1:7">
       <c r="A581" s="6" t="s">
         <v>1052</v>
       </c>
@@ -17956,7 +17946,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="582" spans="1:7">
+    <row r="582" hidden="1" spans="1:7">
       <c r="A582" s="6" t="s">
         <v>110</v>
       </c>
@@ -17979,7 +17969,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="583" spans="1:7">
+    <row r="583" hidden="1" spans="1:7">
       <c r="A583" s="6" t="s">
         <v>110</v>
       </c>
@@ -18002,7 +17992,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="584" spans="1:7">
+    <row r="584" hidden="1" spans="1:7">
       <c r="A584" s="6" t="s">
         <v>110</v>
       </c>
@@ -18025,7 +18015,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="585" spans="1:7">
+    <row r="585" hidden="1" spans="1:7">
       <c r="A585" s="6" t="s">
         <v>536</v>
       </c>
@@ -18048,7 +18038,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="586" spans="1:7">
+    <row r="586" hidden="1" spans="1:7">
       <c r="A586" s="6" t="s">
         <v>536</v>
       </c>
@@ -18071,7 +18061,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="587" spans="1:7">
+    <row r="587" hidden="1" spans="1:7">
       <c r="A587" s="6" t="s">
         <v>536</v>
       </c>
@@ -18094,7 +18084,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="588" spans="1:7">
+    <row r="588" hidden="1" spans="1:7">
       <c r="A588" s="6" t="s">
         <v>536</v>
       </c>
@@ -18117,7 +18107,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="589" spans="1:7">
+    <row r="589" hidden="1" spans="1:7">
       <c r="A589" s="6" t="s">
         <v>1060</v>
       </c>
@@ -18140,7 +18130,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="590" spans="1:7">
+    <row r="590" hidden="1" spans="1:7">
       <c r="A590" s="6" t="s">
         <v>1060</v>
       </c>
@@ -18163,7 +18153,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="591" spans="1:7">
+    <row r="591" hidden="1" spans="1:7">
       <c r="A591" s="6" t="s">
         <v>1060</v>
       </c>
@@ -18186,7 +18176,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="592" spans="1:7">
+    <row r="592" hidden="1" spans="1:7">
       <c r="A592" s="6" t="s">
         <v>1060</v>
       </c>
@@ -18209,7 +18199,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="593" spans="1:7">
+    <row r="593" hidden="1" spans="1:7">
       <c r="A593" s="6" t="s">
         <v>1023</v>
       </c>
@@ -18232,7 +18222,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="594" spans="1:7">
+    <row r="594" hidden="1" spans="1:7">
       <c r="A594" s="6" t="s">
         <v>1023</v>
       </c>
@@ -18255,7 +18245,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="595" spans="1:7">
+    <row r="595" hidden="1" spans="1:7">
       <c r="A595" s="6" t="s">
         <v>82</v>
       </c>
@@ -18278,7 +18268,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="596" spans="1:7">
+    <row r="596" hidden="1" spans="1:7">
       <c r="A596" s="6" t="s">
         <v>1003</v>
       </c>
@@ -18301,7 +18291,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="597" spans="1:7">
+    <row r="597" hidden="1" spans="1:7">
       <c r="A597" s="6" t="s">
         <v>1067</v>
       </c>
@@ -18324,7 +18314,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="598" spans="1:7">
+    <row r="598" hidden="1" spans="1:7">
       <c r="A598" s="6" t="s">
         <v>1052</v>
       </c>
@@ -18347,7 +18337,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="599" spans="1:7">
+    <row r="599" hidden="1" spans="1:7">
       <c r="A599" s="6" t="s">
         <v>1052</v>
       </c>
@@ -18370,7 +18360,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="600" spans="1:7">
+    <row r="600" hidden="1" spans="1:7">
       <c r="A600" s="6" t="s">
         <v>108</v>
       </c>
@@ -18393,7 +18383,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="601" spans="1:7">
+    <row r="601" hidden="1" spans="1:7">
       <c r="A601" s="6" t="s">
         <v>1003</v>
       </c>
@@ -18416,7 +18406,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="602" spans="1:7">
+    <row r="602" hidden="1" spans="1:7">
       <c r="A602" s="6" t="s">
         <v>110</v>
       </c>
@@ -18439,7 +18429,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="603" spans="1:7">
+    <row r="603" hidden="1" spans="1:7">
       <c r="A603" s="6" t="s">
         <v>128</v>
       </c>
@@ -18462,7 +18452,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="604" spans="1:7">
+    <row r="604" hidden="1" spans="1:7">
       <c r="A604" s="6" t="s">
         <v>128</v>
       </c>
@@ -18485,7 +18475,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="605" spans="1:7">
+    <row r="605" hidden="1" spans="1:7">
       <c r="A605" s="6" t="s">
         <v>1075</v>
       </c>
@@ -18508,7 +18498,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="606" spans="1:7">
+    <row r="606" hidden="1" spans="1:7">
       <c r="A606" s="6" t="s">
         <v>1075</v>
       </c>
@@ -18531,7 +18521,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="607" spans="1:7">
+    <row r="607" hidden="1" spans="1:7">
       <c r="A607" s="6" t="s">
         <v>1077</v>
       </c>
@@ -18554,7 +18544,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="608" spans="1:7">
+    <row r="608" hidden="1" spans="1:7">
       <c r="A608" s="6" t="s">
         <v>556</v>
       </c>
@@ -18577,7 +18567,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="609" spans="1:7">
+    <row r="609" hidden="1" spans="1:7">
       <c r="A609" s="6" t="s">
         <v>556</v>
       </c>
@@ -18600,7 +18590,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="610" spans="1:7">
+    <row r="610" hidden="1" spans="1:7">
       <c r="A610" s="6" t="s">
         <v>544</v>
       </c>
@@ -18623,7 +18613,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="611" spans="1:7">
+    <row r="611" hidden="1" spans="1:7">
       <c r="A611" s="6" t="s">
         <v>549</v>
       </c>
@@ -18646,7 +18636,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="612" spans="1:7">
+    <row r="612" hidden="1" spans="1:7">
       <c r="A612" s="6" t="s">
         <v>140</v>
       </c>
@@ -18669,7 +18659,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="613" spans="1:7">
+    <row r="613" hidden="1" spans="1:7">
       <c r="A613" s="6" t="s">
         <v>140</v>
       </c>
@@ -18692,7 +18682,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="614" spans="1:7">
+    <row r="614" hidden="1" spans="1:7">
       <c r="A614" s="6" t="s">
         <v>1086</v>
       </c>
@@ -18715,7 +18705,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="615" spans="1:7">
+    <row r="615" hidden="1" spans="1:7">
       <c r="A615" s="6" t="s">
         <v>1088</v>
       </c>
@@ -18738,7 +18728,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="616" spans="1:7">
+    <row r="616" hidden="1" spans="1:7">
       <c r="A616" s="6" t="s">
         <v>1088</v>
       </c>
@@ -18761,7 +18751,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="617" spans="1:7">
+    <row r="617" hidden="1" spans="1:7">
       <c r="A617" s="6" t="s">
         <v>148</v>
       </c>
@@ -18784,7 +18774,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="618" spans="1:7">
+    <row r="618" hidden="1" spans="1:7">
       <c r="A618" s="6" t="s">
         <v>151</v>
       </c>
@@ -18807,7 +18797,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="619" spans="1:7">
+    <row r="619" hidden="1" spans="1:7">
       <c r="A619" s="6" t="s">
         <v>1093</v>
       </c>
@@ -18830,7 +18820,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="620" spans="1:7">
+    <row r="620" hidden="1" spans="1:7">
       <c r="A620" s="6" t="s">
         <v>1095</v>
       </c>
@@ -18853,7 +18843,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="621" spans="1:7">
+    <row r="621" hidden="1" spans="1:7">
       <c r="A621" s="6" t="s">
         <v>1097</v>
       </c>
@@ -18876,7 +18866,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="622" spans="1:7">
+    <row r="622" hidden="1" spans="1:7">
       <c r="A622" s="6" t="s">
         <v>1097</v>
       </c>
@@ -18899,7 +18889,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="623" spans="1:7">
+    <row r="623" hidden="1" spans="1:7">
       <c r="A623" s="6" t="s">
         <v>1099</v>
       </c>
@@ -18922,7 +18912,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="624" spans="1:7">
+    <row r="624" hidden="1" spans="1:7">
       <c r="A624" s="6" t="s">
         <v>1101</v>
       </c>
@@ -18945,7 +18935,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="625" spans="1:7">
+    <row r="625" hidden="1" spans="1:7">
       <c r="A625" s="6" t="s">
         <v>1103</v>
       </c>
@@ -18968,7 +18958,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="626" spans="1:7">
+    <row r="626" hidden="1" spans="1:7">
       <c r="A626" s="6" t="s">
         <v>62</v>
       </c>
@@ -18991,7 +18981,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="627" spans="1:7">
+    <row r="627" hidden="1" spans="1:7">
       <c r="A627" s="6" t="s">
         <v>62</v>
       </c>
@@ -19014,7 +19004,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="628" spans="1:7">
+    <row r="628" hidden="1" spans="1:7">
       <c r="A628" s="6" t="s">
         <v>62</v>
       </c>
@@ -19037,7 +19027,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="629" spans="1:7">
+    <row r="629" hidden="1" spans="1:7">
       <c r="A629" s="6" t="s">
         <v>62</v>
       </c>
@@ -19060,7 +19050,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="630" spans="1:7">
+    <row r="630" hidden="1" spans="1:7">
       <c r="A630" s="6" t="s">
         <v>62</v>
       </c>
@@ -19083,7 +19073,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="631" spans="1:7">
+    <row r="631" hidden="1" spans="1:7">
       <c r="A631" s="6" t="s">
         <v>62</v>
       </c>
@@ -19106,7 +19096,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="632" spans="1:7">
+    <row r="632" hidden="1" spans="1:7">
       <c r="A632" s="6" t="s">
         <v>1106</v>
       </c>
@@ -19129,7 +19119,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="633" spans="1:7">
+    <row r="633" hidden="1" spans="1:7">
       <c r="A633" s="6" t="s">
         <v>1109</v>
       </c>
@@ -19160,7 +19150,7 @@
         <v>1112</v>
       </c>
       <c r="C634" s="6" t="s">
-        <v>1113</v>
+        <v>134</v>
       </c>
       <c r="D634" s="6" t="s">
         <v>23</v>
@@ -19175,12 +19165,12 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="635" spans="1:7">
+    <row r="635" hidden="1" spans="1:7">
       <c r="A635" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B635" s="6" t="s">
         <v>1114</v>
-      </c>
-      <c r="B635" s="6" t="s">
-        <v>1115</v>
       </c>
       <c r="C635" s="6" t="s">
         <v>272</v>
@@ -19198,18 +19188,18 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="636" spans="1:7">
+    <row r="636" hidden="1" spans="1:7">
       <c r="A636" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B636" s="6" t="s">
         <v>1116</v>
-      </c>
-      <c r="B636" s="6" t="s">
-        <v>1117</v>
       </c>
       <c r="C636" s="6" t="s">
         <v>272</v>
       </c>
       <c r="D636" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E636" s="6" t="s">
         <v>29</v>
@@ -19221,12 +19211,12 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="637" spans="1:7">
+    <row r="637" hidden="1" spans="1:7">
       <c r="A637" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B637" s="6" t="s">
         <v>1119</v>
-      </c>
-      <c r="B637" s="6" t="s">
-        <v>1120</v>
       </c>
       <c r="C637" s="6" t="s">
         <v>638</v>
@@ -19244,12 +19234,12 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="638" spans="1:7">
+    <row r="638" hidden="1" spans="1:7">
       <c r="A638" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B638" s="6" t="s">
         <v>1121</v>
-      </c>
-      <c r="B638" s="6" t="s">
-        <v>1122</v>
       </c>
       <c r="C638" s="6" t="s">
         <v>638</v>
@@ -19267,12 +19257,12 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="639" spans="1:7">
+    <row r="639" hidden="1" spans="1:7">
       <c r="A639" s="6" t="s">
         <v>630</v>
       </c>
       <c r="B639" s="6" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C639" s="6" t="s">
         <v>632</v>
@@ -19290,12 +19280,12 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="640" spans="1:7">
+    <row r="640" hidden="1" spans="1:7">
       <c r="A640" s="6" t="s">
         <v>633</v>
       </c>
       <c r="B640" s="6" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C640" s="6" t="s">
         <v>632</v>
@@ -19313,38 +19303,38 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="641" spans="1:7">
+    <row r="641" hidden="1" spans="1:7">
       <c r="A641" s="6" t="s">
         <v>639</v>
       </c>
       <c r="B641" s="6" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C641" s="6" t="s">
         <v>632</v>
       </c>
       <c r="D641" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E641" s="6" t="s">
         <v>21</v>
       </c>
       <c r="F641" s="6" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G641" s="6" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="642" spans="1:7">
+    <row r="642" hidden="1" spans="1:7">
       <c r="A642" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B642" s="6" t="s">
         <v>1127</v>
       </c>
-      <c r="B642" s="6" t="s">
+      <c r="C642" s="6" t="s">
         <v>1128</v>
-      </c>
-      <c r="C642" s="6" t="s">
-        <v>1129</v>
       </c>
       <c r="D642" s="6" t="s">
         <v>10</v>
@@ -19359,15 +19349,15 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="643" spans="1:7">
+    <row r="643" hidden="1" spans="1:7">
       <c r="A643" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B643" s="6" t="s">
         <v>1130</v>
       </c>
-      <c r="B643" s="6" t="s">
-        <v>1131</v>
-      </c>
       <c r="C643" s="6" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D643" s="6" t="s">
         <v>285</v>
@@ -19376,18 +19366,18 @@
         <v>43</v>
       </c>
       <c r="F643" s="6" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G643" s="6" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="644" spans="1:7">
+    <row r="644" hidden="1" spans="1:7">
       <c r="A644" s="6" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B644" s="6" t="s">
         <v>1133</v>
-      </c>
-      <c r="B644" s="6" t="s">
-        <v>1134</v>
       </c>
       <c r="C644" s="6" t="s">
         <v>87</v>
@@ -19407,13 +19397,13 @@
     </row>
     <row r="645" spans="1:7">
       <c r="A645" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B645" s="6" t="s">
         <v>1135</v>
       </c>
-      <c r="B645" s="6" t="s">
-        <v>1136</v>
-      </c>
       <c r="C645" s="6" t="s">
-        <v>1113</v>
+        <v>134</v>
       </c>
       <c r="D645" s="6" t="s">
         <v>20</v>
@@ -19422,41 +19412,41 @@
         <v>43</v>
       </c>
       <c r="F645" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G645" s="6" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="646" spans="1:7">
+    <row r="646" hidden="1" spans="1:7">
       <c r="A646" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B646" s="6" t="s">
         <v>1138</v>
-      </c>
-      <c r="B646" s="6" t="s">
-        <v>1139</v>
       </c>
       <c r="C646" s="6" t="s">
         <v>208</v>
       </c>
       <c r="D646" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E646" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F646" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G646" s="6" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="647" spans="1:7">
+    <row r="647" hidden="1" spans="1:7">
       <c r="A647" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B647" s="6" t="s">
         <v>1141</v>
-      </c>
-      <c r="B647" s="6" t="s">
-        <v>1142</v>
       </c>
       <c r="C647" s="6" t="s">
         <v>87</v>
@@ -19468,18 +19458,18 @@
         <v>11</v>
       </c>
       <c r="F647" s="6" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G647" s="6" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="648" spans="1:7">
+    <row r="648" hidden="1" spans="1:7">
       <c r="A648" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B648" s="6" t="s">
         <v>1144</v>
-      </c>
-      <c r="B648" s="6" t="s">
-        <v>1145</v>
       </c>
       <c r="C648" s="6"/>
       <c r="D648" s="6" t="s">
@@ -19489,7 +19479,7 @@
         <v>11</v>
       </c>
       <c r="F648" s="6" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G648" s="6" t="s">
         <v>1108</v>
@@ -19497,13 +19487,13 @@
     </row>
     <row r="649" spans="1:7">
       <c r="A649" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B649" s="6" t="s">
         <v>1147</v>
       </c>
-      <c r="B649" s="6" t="s">
-        <v>1148</v>
-      </c>
       <c r="C649" s="6" t="s">
-        <v>1113</v>
+        <v>134</v>
       </c>
       <c r="D649" s="6" t="s">
         <v>20</v>
@@ -19518,12 +19508,12 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="650" spans="1:7">
+    <row r="650" hidden="1" spans="1:7">
       <c r="A650" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B650" s="6" t="s">
         <v>1149</v>
-      </c>
-      <c r="B650" s="6" t="s">
-        <v>1150</v>
       </c>
       <c r="C650" s="6" t="s">
         <v>253</v>
@@ -19538,15 +19528,15 @@
         <v>836</v>
       </c>
       <c r="G650" s="6" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="651" hidden="1" spans="1:7">
+      <c r="A651" s="6" t="s">
         <v>1151</v>
       </c>
-    </row>
-    <row r="651" spans="1:7">
-      <c r="A651" s="6" t="s">
+      <c r="B651" s="6" t="s">
         <v>1152</v>
-      </c>
-      <c r="B651" s="6" t="s">
-        <v>1153</v>
       </c>
       <c r="C651" s="6" t="s">
         <v>253</v>
@@ -19561,15 +19551,15 @@
         <v>836</v>
       </c>
       <c r="G651" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="652" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="652" hidden="1" spans="1:7">
       <c r="A652" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B652" s="6" t="s">
         <v>1154</v>
-      </c>
-      <c r="B652" s="6" t="s">
-        <v>1155</v>
       </c>
       <c r="C652" s="6" t="s">
         <v>862</v>
@@ -19584,15 +19574,15 @@
         <v>836</v>
       </c>
       <c r="G652" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="653" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="653" hidden="1" spans="1:7">
       <c r="A653" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B653" s="6" t="s">
         <v>1156</v>
-      </c>
-      <c r="B653" s="6" t="s">
-        <v>1157</v>
       </c>
       <c r="C653" s="6" t="s">
         <v>237</v>
@@ -19604,24 +19594,24 @@
         <v>29</v>
       </c>
       <c r="F653" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G653" s="6" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="654" hidden="1" spans="1:7">
+      <c r="A654" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="G653" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="654" spans="1:7">
-      <c r="A654" s="6" t="s">
+      <c r="B654" s="6" t="s">
         <v>1159</v>
-      </c>
-      <c r="B654" s="6" t="s">
-        <v>1160</v>
       </c>
       <c r="C654" s="6" t="s">
         <v>561</v>
       </c>
       <c r="D654" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E654" s="6" t="s">
         <v>29</v>
@@ -19630,15 +19620,15 @@
         <v>836</v>
       </c>
       <c r="G654" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="655" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="655" hidden="1" spans="1:7">
       <c r="A655" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B655" s="6" t="s">
         <v>1161</v>
-      </c>
-      <c r="B655" s="6" t="s">
-        <v>1162</v>
       </c>
       <c r="C655" s="6" t="s">
         <v>237</v>
@@ -19653,15 +19643,15 @@
         <v>836</v>
       </c>
       <c r="G655" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="656" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="656" hidden="1" spans="1:7">
       <c r="A656" s="6" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B656" s="6" t="s">
         <v>1163</v>
-      </c>
-      <c r="B656" s="6" t="s">
-        <v>1164</v>
       </c>
       <c r="C656" s="6" t="s">
         <v>237</v>
@@ -19676,15 +19666,15 @@
         <v>836</v>
       </c>
       <c r="G656" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="657" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="657" hidden="1" spans="1:7">
       <c r="A657" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B657" s="6" t="s">
         <v>1165</v>
-      </c>
-      <c r="B657" s="6" t="s">
-        <v>1166</v>
       </c>
       <c r="C657" s="6" t="s">
         <v>914</v>
@@ -19699,15 +19689,15 @@
         <v>836</v>
       </c>
       <c r="G657" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="658" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="658" hidden="1" spans="1:7">
       <c r="A658" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B658" s="6" t="s">
         <v>1167</v>
-      </c>
-      <c r="B658" s="6" t="s">
-        <v>1168</v>
       </c>
       <c r="C658" s="6" t="s">
         <v>914</v>
@@ -19722,38 +19712,38 @@
         <v>836</v>
       </c>
       <c r="G658" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="659" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="659" hidden="1" spans="1:7">
       <c r="A659" s="6" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B659" s="6" t="s">
         <v>1169</v>
-      </c>
-      <c r="B659" s="6" t="s">
-        <v>1170</v>
       </c>
       <c r="C659" s="6" t="s">
         <v>896</v>
       </c>
       <c r="D659" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E659" s="6" t="s">
         <v>21</v>
       </c>
       <c r="F659" s="6" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G659" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="660" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="660" hidden="1" spans="1:7">
       <c r="A660" s="6" t="s">
         <v>850</v>
       </c>
       <c r="B660" s="6" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C660" s="6" t="s">
         <v>245</v>
@@ -19768,15 +19758,15 @@
         <v>836</v>
       </c>
       <c r="G660" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="661" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="661" hidden="1" spans="1:7">
       <c r="A661" s="6" t="s">
         <v>852</v>
       </c>
       <c r="B661" s="6" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C661" s="6" t="s">
         <v>245</v>
@@ -19791,15 +19781,15 @@
         <v>836</v>
       </c>
       <c r="G661" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="662" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="662" hidden="1" spans="1:7">
       <c r="A662" s="6" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B662" s="6" t="s">
         <v>1174</v>
-      </c>
-      <c r="B662" s="6" t="s">
-        <v>1175</v>
       </c>
       <c r="C662" s="6" t="s">
         <v>875</v>
@@ -19814,15 +19804,15 @@
         <v>836</v>
       </c>
       <c r="G662" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="663" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="663" hidden="1" spans="1:7">
       <c r="A663" s="6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B663" s="6" t="s">
         <v>1176</v>
-      </c>
-      <c r="B663" s="6" t="s">
-        <v>1177</v>
       </c>
       <c r="C663" s="6" t="s">
         <v>799</v>
@@ -19834,24 +19824,24 @@
         <v>43</v>
       </c>
       <c r="F663" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G663" s="6" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="664" hidden="1" spans="1:7">
+      <c r="A664" s="6" t="s">
         <v>1178</v>
       </c>
-      <c r="G663" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="664" spans="1:7">
-      <c r="A664" s="6" t="s">
+      <c r="B664" s="6" t="s">
         <v>1179</v>
-      </c>
-      <c r="B664" s="6" t="s">
-        <v>1180</v>
       </c>
       <c r="C664" s="6" t="s">
         <v>875</v>
       </c>
       <c r="D664" s="6" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E664" s="6" t="s">
         <v>43</v>
@@ -19860,15 +19850,15 @@
         <v>836</v>
       </c>
       <c r="G664" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="665" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="665" hidden="1" spans="1:7">
       <c r="A665" s="6" t="s">
         <v>982</v>
       </c>
       <c r="B665" s="6" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C665" s="6" t="s">
         <v>150</v>
@@ -19883,15 +19873,15 @@
         <v>836</v>
       </c>
       <c r="G665" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="666" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="666" hidden="1" spans="1:7">
       <c r="A666" s="6" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B666" s="6" t="s">
         <v>1182</v>
-      </c>
-      <c r="B666" s="6" t="s">
-        <v>1183</v>
       </c>
       <c r="C666" s="6" t="s">
         <v>871</v>
@@ -19906,15 +19896,15 @@
         <v>836</v>
       </c>
       <c r="G666" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="667" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="667" hidden="1" spans="1:7">
       <c r="A667" s="6" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B667" s="6" t="s">
         <v>1184</v>
-      </c>
-      <c r="B667" s="6" t="s">
-        <v>1185</v>
       </c>
       <c r="C667" s="6"/>
       <c r="D667" s="6" t="s">
@@ -19927,15 +19917,15 @@
         <v>836</v>
       </c>
       <c r="G667" s="6" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="668" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="668" hidden="1" spans="1:7">
       <c r="A668" s="6" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B668" s="6" t="s">
         <v>1186</v>
-      </c>
-      <c r="B668" s="6" t="s">
-        <v>1187</v>
       </c>
       <c r="C668" s="6" t="s">
         <v>253</v>
@@ -19947,15 +19937,20 @@
         <v>11</v>
       </c>
       <c r="F668" s="6" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G668" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G668" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:G668">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="F.Ghezal"/>
+      </filters>
+    </filterColumn>
+    <sortState ref="A1:G668">
       <sortCondition ref="G1"/>
     </sortState>
     <extLst/>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4674" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4674" uniqueCount="1187">
   <si>
     <t>Enseignements</t>
   </si>
@@ -98,7 +98,7 @@
     <t>Lundi</t>
   </si>
   <si>
-    <t>15h30 -17h00</t>
+    <t>15h30-17h</t>
   </si>
   <si>
     <t>11h-12h30</t>
@@ -3381,9 +3381,6 @@
   </si>
   <si>
     <t>TD-PRE-ING4EI</t>
-  </si>
-  <si>
-    <t>15h30-17h00</t>
   </si>
   <si>
     <t>Cours-Réseaux de transport et distribution</t>
@@ -4213,7 +4210,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4225,6 +4222,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4662,7 +4660,7 @@
       <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -4675,7 +4673,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:7">
+    <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
@@ -4915,7 +4913,7 @@
       <c r="C15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -4928,7 +4926,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:7">
+    <row r="16" spans="1:7">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -4951,7 +4949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:7">
+    <row r="17" spans="1:7">
       <c r="A17" s="6" t="s">
         <v>38</v>
       </c>
@@ -4984,7 +4982,7 @@
       <c r="C18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -5053,7 +5051,7 @@
       <c r="C21" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="6" t="s">
@@ -5214,7 +5212,7 @@
       <c r="C28" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="6" t="s">
@@ -5250,7 +5248,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:7">
+    <row r="30" spans="1:7">
       <c r="A30" s="6" t="s">
         <v>62</v>
       </c>
@@ -5306,7 +5304,7 @@
       <c r="C32" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E32" s="6" t="s">
@@ -5513,7 +5511,7 @@
       <c r="C41" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="6" t="s">
@@ -5526,7 +5524,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:7">
+    <row r="42" spans="1:7">
       <c r="A42" s="6" t="s">
         <v>88</v>
       </c>
@@ -5559,7 +5557,7 @@
       <c r="C43" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="6" t="s">
@@ -5572,7 +5570,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:7">
+    <row r="44" spans="1:7">
       <c r="A44" s="6" t="s">
         <v>91</v>
       </c>
@@ -5789,7 +5787,7 @@
       <c r="C53" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="6" t="s">
@@ -5802,7 +5800,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:7">
+    <row r="54" spans="1:7">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
@@ -5835,7 +5833,7 @@
       <c r="C55" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E55" s="6" t="s">
@@ -5848,7 +5846,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:7">
+    <row r="56" spans="1:7">
       <c r="A56" s="6" t="s">
         <v>62</v>
       </c>
@@ -5894,7 +5892,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:7">
+    <row r="58" spans="1:7">
       <c r="A58" s="6" t="s">
         <v>117</v>
       </c>
@@ -5927,7 +5925,7 @@
       <c r="C59" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="6" t="s">
@@ -6009,7 +6007,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:7">
+    <row r="63" spans="1:7">
       <c r="A63" s="6" t="s">
         <v>128</v>
       </c>
@@ -6042,7 +6040,7 @@
       <c r="C64" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E64" s="6" t="s">
@@ -6055,7 +6053,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" hidden="1" spans="1:7">
       <c r="A65" s="6" t="s">
         <v>85</v>
       </c>
@@ -6065,7 +6063,7 @@
       <c r="C65" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E65" s="6" t="s">
@@ -6272,7 +6270,7 @@
       <c r="C74" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E74" s="6" t="s">
@@ -6285,7 +6283,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:7">
+    <row r="75" spans="1:7">
       <c r="A75" s="6" t="s">
         <v>88</v>
       </c>
@@ -6331,7 +6329,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:7">
+    <row r="77" spans="1:7">
       <c r="A77" s="6" t="s">
         <v>88</v>
       </c>
@@ -6364,7 +6362,7 @@
       <c r="C78" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E78" s="6" t="s">
@@ -6400,7 +6398,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:7">
+    <row r="80" spans="1:7">
       <c r="A80" s="6" t="s">
         <v>164</v>
       </c>
@@ -6433,7 +6431,7 @@
       <c r="C81" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E81" s="6" t="s">
@@ -6469,7 +6467,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:7">
+    <row r="83" spans="1:7">
       <c r="A83" s="6" t="s">
         <v>62</v>
       </c>
@@ -6502,7 +6500,7 @@
       <c r="C84" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E84" s="6" t="s">
@@ -6538,7 +6536,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:7">
+    <row r="86" spans="1:7">
       <c r="A86" s="6" t="s">
         <v>62</v>
       </c>
@@ -6594,7 +6592,7 @@
       <c r="C88" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E88" s="6" t="s">
@@ -6607,7 +6605,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:7">
+    <row r="89" spans="1:7">
       <c r="A89" s="6" t="s">
         <v>173</v>
       </c>
@@ -6824,7 +6822,7 @@
       <c r="C98" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E98" s="6" t="s">
@@ -6837,7 +6835,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:7">
+    <row r="99" spans="1:7">
       <c r="A99" s="6" t="s">
         <v>193</v>
       </c>
@@ -6870,7 +6868,7 @@
       <c r="C100" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E100" s="6" t="s">
@@ -6916,7 +6914,7 @@
       <c r="C102" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E102" s="6" t="s">
@@ -6929,7 +6927,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:7">
+    <row r="103" spans="1:7">
       <c r="A103" s="6" t="s">
         <v>203</v>
       </c>
@@ -6985,7 +6983,7 @@
       <c r="C105" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E105" s="6" t="s">
@@ -6998,7 +6996,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:7">
+    <row r="106" spans="1:7">
       <c r="A106" s="6" t="s">
         <v>209</v>
       </c>
@@ -7090,7 +7088,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:7">
+    <row r="110" spans="1:7">
       <c r="A110" s="6" t="s">
         <v>217</v>
       </c>
@@ -7123,7 +7121,7 @@
       <c r="C111" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E111" s="6" t="s">
@@ -7136,7 +7134,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:7">
+    <row r="112" spans="1:7">
       <c r="A112" s="6" t="s">
         <v>224</v>
       </c>
@@ -7261,7 +7259,7 @@
       <c r="C117" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E117" s="6" t="s">
@@ -7274,7 +7272,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:7">
+    <row r="118" spans="1:7">
       <c r="A118" s="6" t="s">
         <v>235</v>
       </c>
@@ -7307,7 +7305,7 @@
       <c r="C119" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="D119" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E119" s="6" t="s">
@@ -7445,7 +7443,7 @@
       <c r="C125" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D125" s="6" t="s">
+      <c r="D125" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E125" s="6" t="s">
@@ -7458,7 +7456,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:7">
+    <row r="126" spans="1:7">
       <c r="A126" s="6" t="s">
         <v>259</v>
       </c>
@@ -7652,7 +7650,7 @@
       <c r="C134" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="D134" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E134" s="6" t="s">
@@ -7688,7 +7686,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:7">
+    <row r="136" spans="1:7">
       <c r="A136" s="6" t="s">
         <v>62</v>
       </c>
@@ -7711,7 +7709,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="137" hidden="1" spans="1:7">
+    <row r="137" spans="1:7">
       <c r="A137" s="6" t="s">
         <v>62</v>
       </c>
@@ -9827,7 +9825,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="229" hidden="1" spans="1:7">
+    <row r="229" spans="1:7">
       <c r="A229" s="6" t="s">
         <v>481</v>
       </c>
@@ -9850,7 +9848,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="230" hidden="1" spans="1:7">
+    <row r="230" spans="1:7">
       <c r="A230" s="6" t="s">
         <v>484</v>
       </c>
@@ -9883,7 +9881,7 @@
       <c r="C231" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D231" s="6" t="s">
+      <c r="D231" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E231" s="6" t="s">
@@ -10057,7 +10055,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="239" hidden="1" spans="1:7">
+    <row r="239" spans="1:7">
       <c r="A239" s="6" t="s">
         <v>502</v>
       </c>
@@ -10090,7 +10088,7 @@
       <c r="C240" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D240" s="6" t="s">
+      <c r="D240" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E240" s="6" t="s">
@@ -10182,7 +10180,7 @@
       <c r="C244" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="D244" s="6" t="s">
+      <c r="D244" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E244" s="6" t="s">
@@ -10228,7 +10226,7 @@
       <c r="C246" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="D246" s="6" t="s">
+      <c r="D246" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E246" s="6" t="s">
@@ -10379,7 +10377,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="253" hidden="1" spans="1:7">
+    <row r="253" spans="1:7">
       <c r="A253" s="6" t="s">
         <v>510</v>
       </c>
@@ -10458,7 +10456,7 @@
       <c r="C256" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D256" s="6" t="s">
+      <c r="D256" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E256" s="6" t="s">
@@ -10481,7 +10479,7 @@
       <c r="C257" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D257" s="6" t="s">
+      <c r="D257" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E257" s="6" t="s">
@@ -10504,7 +10502,7 @@
       <c r="C258" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D258" s="6" t="s">
+      <c r="D258" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E258" s="6" t="s">
@@ -10527,7 +10525,7 @@
       <c r="C259" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D259" s="6" t="s">
+      <c r="D259" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E259" s="6" t="s">
@@ -10540,7 +10538,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="260" hidden="1" spans="1:7">
+    <row r="260" spans="1:7">
       <c r="A260" s="6" t="s">
         <v>110</v>
       </c>
@@ -10563,7 +10561,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="261" hidden="1" spans="1:7">
+    <row r="261" spans="1:7">
       <c r="A261" s="6" t="s">
         <v>536</v>
       </c>
@@ -10596,7 +10594,7 @@
       <c r="C262" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D262" s="6" t="s">
+      <c r="D262" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E262" s="6" t="s">
@@ -10609,7 +10607,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="263" hidden="1" spans="1:7">
+    <row r="263" spans="1:7">
       <c r="A263" s="6" t="s">
         <v>536</v>
       </c>
@@ -10849,7 +10847,7 @@
       <c r="C273" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="D273" s="6" t="s">
+      <c r="D273" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E273" s="6" t="s">
@@ -10862,7 +10860,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="274" hidden="1" spans="1:7">
+    <row r="274" spans="1:7">
       <c r="A274" s="6" t="s">
         <v>552</v>
       </c>
@@ -10895,7 +10893,7 @@
       <c r="C275" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="D275" s="6" t="s">
+      <c r="D275" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E275" s="6" t="s">
@@ -10908,7 +10906,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="276" hidden="1" spans="1:7">
+    <row r="276" spans="1:7">
       <c r="A276" s="6" t="s">
         <v>552</v>
       </c>
@@ -10931,7 +10929,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="277" hidden="1" spans="1:7">
+    <row r="277" spans="1:7">
       <c r="A277" s="6" t="s">
         <v>556</v>
       </c>
@@ -10964,7 +10962,7 @@
       <c r="C278" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="D278" s="6" t="s">
+      <c r="D278" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E278" s="6" t="s">
@@ -11069,7 +11067,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="283" hidden="1" spans="1:7">
+    <row r="283" spans="1:7">
       <c r="A283" s="6" t="s">
         <v>567</v>
       </c>
@@ -11102,7 +11100,7 @@
       <c r="C284" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="D284" s="6" t="s">
+      <c r="D284" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E284" s="6" t="s">
@@ -11115,7 +11113,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="285" hidden="1" spans="1:7">
+    <row r="285" spans="1:7">
       <c r="A285" s="6" t="s">
         <v>570</v>
       </c>
@@ -11148,7 +11146,7 @@
       <c r="C286" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="D286" s="6" t="s">
+      <c r="D286" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E286" s="6" t="s">
@@ -11230,7 +11228,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="290" hidden="1" spans="1:7">
+    <row r="290" spans="1:7">
       <c r="A290" s="6" t="s">
         <v>556</v>
       </c>
@@ -11263,7 +11261,7 @@
       <c r="C291" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="D291" s="6" t="s">
+      <c r="D291" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E291" s="6" t="s">
@@ -11276,7 +11274,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="292" hidden="1" spans="1:7">
+    <row r="292" spans="1:7">
       <c r="A292" s="6" t="s">
         <v>556</v>
       </c>
@@ -11309,7 +11307,7 @@
       <c r="C293" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="D293" s="6" t="s">
+      <c r="D293" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E293" s="6" t="s">
@@ -11355,7 +11353,7 @@
       <c r="C295" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D295" s="6" t="s">
+      <c r="D295" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E295" s="6" t="s">
@@ -11368,7 +11366,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="296" hidden="1" spans="1:7">
+    <row r="296" spans="1:7">
       <c r="A296" s="6" t="s">
         <v>567</v>
       </c>
@@ -11391,7 +11389,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" hidden="1" spans="1:7">
       <c r="A297" s="6" t="s">
         <v>549</v>
       </c>
@@ -11470,7 +11468,7 @@
       <c r="C300" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="D300" s="6" t="s">
+      <c r="D300" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E300" s="6" t="s">
@@ -11483,7 +11481,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="301" hidden="1" spans="1:7">
+    <row r="301" spans="1:7">
       <c r="A301" s="6" t="s">
         <v>595</v>
       </c>
@@ -11516,7 +11514,7 @@
       <c r="C302" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="D302" s="6" t="s">
+      <c r="D302" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E302" s="6" t="s">
@@ -11529,7 +11527,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="303" hidden="1" spans="1:7">
+    <row r="303" spans="1:7">
       <c r="A303" s="6" t="s">
         <v>595</v>
       </c>
@@ -11644,7 +11642,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="308" hidden="1" spans="1:7">
+    <row r="308" spans="1:7">
       <c r="A308" s="6" t="s">
         <v>570</v>
       </c>
@@ -11677,7 +11675,7 @@
       <c r="C309" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D309" s="6" t="s">
+      <c r="D309" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E309" s="6" t="s">
@@ -11792,7 +11790,7 @@
       <c r="C314" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D314" s="6" t="s">
+      <c r="D314" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E314" s="6" t="s">
@@ -11861,7 +11859,7 @@
       <c r="C317" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D317" s="6" t="s">
+      <c r="D317" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E317" s="6" t="s">
@@ -11874,7 +11872,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="318" hidden="1" spans="1:7">
+    <row r="318" spans="1:7">
       <c r="A318" s="6" t="s">
         <v>62</v>
       </c>
@@ -12012,7 +12010,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="324" hidden="1" spans="1:7">
+    <row r="324" spans="1:7">
       <c r="A324" s="6" t="s">
         <v>625</v>
       </c>
@@ -12035,7 +12033,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="325" hidden="1" spans="1:7">
+    <row r="325" spans="1:7">
       <c r="A325" s="6" t="s">
         <v>627</v>
       </c>
@@ -12068,7 +12066,7 @@
       <c r="C326" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D326" s="6" t="s">
+      <c r="D326" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E326" s="6" t="s">
@@ -12137,7 +12135,7 @@
       <c r="C329" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="D329" s="6" t="s">
+      <c r="D329" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E329" s="6" t="s">
@@ -12196,7 +12194,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" hidden="1" spans="1:7">
       <c r="A332" s="6" t="s">
         <v>226</v>
       </c>
@@ -12219,7 +12217,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" hidden="1" spans="1:7">
       <c r="A333" s="6" t="s">
         <v>229</v>
       </c>
@@ -12242,7 +12240,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" hidden="1" spans="1:7">
       <c r="A334" s="6" t="s">
         <v>231</v>
       </c>
@@ -12252,7 +12250,7 @@
       <c r="C334" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D334" s="6" t="s">
+      <c r="D334" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E334" s="6" t="s">
@@ -12482,7 +12480,7 @@
       <c r="C344" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="D344" s="6" t="s">
+      <c r="D344" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E344" s="6" t="s">
@@ -12495,7 +12493,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="345" hidden="1" spans="1:7">
+    <row r="345" spans="1:7">
       <c r="A345" s="6" t="s">
         <v>661</v>
       </c>
@@ -12528,7 +12526,7 @@
       <c r="C346" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="D346" s="6" t="s">
+      <c r="D346" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E346" s="6" t="s">
@@ -12643,7 +12641,7 @@
       <c r="C351" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D351" s="6" t="s">
+      <c r="D351" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E351" s="6" t="s">
@@ -12656,7 +12654,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="352" hidden="1" spans="1:7">
+    <row r="352" spans="1:7">
       <c r="A352" s="6" t="s">
         <v>671</v>
       </c>
@@ -12725,7 +12723,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" hidden="1" spans="1:7">
       <c r="A355" s="6" t="s">
         <v>226</v>
       </c>
@@ -12748,7 +12746,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" hidden="1" spans="1:7">
       <c r="A356" s="6" t="s">
         <v>229</v>
       </c>
@@ -12771,7 +12769,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" hidden="1" spans="1:7">
       <c r="A357" s="6" t="s">
         <v>678</v>
       </c>
@@ -12794,7 +12792,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" hidden="1" spans="1:7">
       <c r="A358" s="6" t="s">
         <v>678</v>
       </c>
@@ -12873,7 +12871,7 @@
       <c r="C361" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D361" s="6" t="s">
+      <c r="D361" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E361" s="6" t="s">
@@ -12886,7 +12884,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:7">
+    <row r="362" spans="1:7">
       <c r="A362" s="6" t="s">
         <v>683</v>
       </c>
@@ -12942,7 +12940,7 @@
       <c r="C364" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D364" s="6" t="s">
+      <c r="D364" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E364" s="6" t="s">
@@ -12955,7 +12953,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:7">
+    <row r="365" spans="1:7">
       <c r="A365" s="6" t="s">
         <v>688</v>
       </c>
@@ -12988,7 +12986,7 @@
       <c r="C366" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="D366" s="6" t="s">
+      <c r="D366" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E366" s="6" t="s">
@@ -13001,7 +12999,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:7">
+    <row r="367" spans="1:7">
       <c r="A367" s="6" t="s">
         <v>690</v>
       </c>
@@ -13057,7 +13055,7 @@
       <c r="C369" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D369" s="6" t="s">
+      <c r="D369" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E369" s="6" t="s">
@@ -13070,7 +13068,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:7">
+    <row r="370" spans="1:7">
       <c r="A370" s="6" t="s">
         <v>697</v>
       </c>
@@ -13208,7 +13206,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="376" hidden="1" spans="1:7">
+    <row r="376" spans="1:7">
       <c r="A376" s="6" t="s">
         <v>707</v>
       </c>
@@ -13241,7 +13239,7 @@
       <c r="C377" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D377" s="6" t="s">
+      <c r="D377" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E377" s="6" t="s">
@@ -13254,7 +13252,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="378" hidden="1" spans="1:7">
+    <row r="378" spans="1:7">
       <c r="A378" s="6" t="s">
         <v>678</v>
       </c>
@@ -13379,7 +13377,7 @@
       <c r="C383" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="D383" s="6" t="s">
+      <c r="D383" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E383" s="6" t="s">
@@ -13392,7 +13390,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:7">
+    <row r="384" spans="1:7">
       <c r="A384" s="6" t="s">
         <v>678</v>
       </c>
@@ -13471,7 +13469,7 @@
       <c r="C387" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="D387" s="6" t="s">
+      <c r="D387" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E387" s="6" t="s">
@@ -13484,7 +13482,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:7">
+    <row r="388" spans="1:7">
       <c r="A388" s="6" t="s">
         <v>715</v>
       </c>
@@ -13530,7 +13528,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:7">
+    <row r="390" spans="1:7">
       <c r="A390" s="6" t="s">
         <v>720</v>
       </c>
@@ -13563,7 +13561,7 @@
       <c r="C391" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D391" s="6" t="s">
+      <c r="D391" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E391" s="6" t="s">
@@ -13609,7 +13607,7 @@
       <c r="C393" s="6" t="s">
         <v>726</v>
       </c>
-      <c r="D393" s="6" t="s">
+      <c r="D393" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E393" s="6" t="s">
@@ -13632,7 +13630,7 @@
       <c r="C394" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="D394" s="6" t="s">
+      <c r="D394" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E394" s="6" t="s">
@@ -13645,7 +13643,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="395" hidden="1" spans="1:7">
+    <row r="395" spans="1:7">
       <c r="A395" s="6" t="s">
         <v>658</v>
       </c>
@@ -13691,7 +13689,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="397" hidden="1" spans="1:7">
+    <row r="397" spans="1:7">
       <c r="A397" s="6" t="s">
         <v>633</v>
       </c>
@@ -13714,7 +13712,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="398" hidden="1" spans="1:7">
+    <row r="398" spans="1:7">
       <c r="A398" s="6" t="s">
         <v>678</v>
       </c>
@@ -13747,7 +13745,7 @@
       <c r="C399" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D399" s="6" t="s">
+      <c r="D399" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E399" s="6" t="s">
@@ -13783,7 +13781,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="401" hidden="1" spans="1:7">
+    <row r="401" spans="1:7">
       <c r="A401" s="6" t="s">
         <v>736</v>
       </c>
@@ -13816,7 +13814,7 @@
       <c r="C402" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D402" s="6" t="s">
+      <c r="D402" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E402" s="6" t="s">
@@ -13954,7 +13952,7 @@
       <c r="C408" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="D408" s="6" t="s">
+      <c r="D408" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E408" s="6" t="s">
@@ -13967,7 +13965,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="409" hidden="1" spans="1:7">
+    <row r="409" spans="1:7">
       <c r="A409" s="6" t="s">
         <v>666</v>
       </c>
@@ -14105,7 +14103,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="415" hidden="1" spans="1:7">
+    <row r="415" spans="1:7">
       <c r="A415" s="6" t="s">
         <v>671</v>
       </c>
@@ -14138,7 +14136,7 @@
       <c r="C416" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="D416" s="6" t="s">
+      <c r="D416" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E416" s="6" t="s">
@@ -14207,7 +14205,7 @@
       <c r="C419" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="D419" s="6" t="s">
+      <c r="D419" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E419" s="6" t="s">
@@ -14230,7 +14228,7 @@
       <c r="C420" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D420" s="6" t="s">
+      <c r="D420" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E420" s="6" t="s">
@@ -14243,7 +14241,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="421" hidden="1" spans="1:7">
+    <row r="421" spans="1:7">
       <c r="A421" s="6" t="s">
         <v>678</v>
       </c>
@@ -14437,7 +14435,7 @@
       <c r="C429" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="D429" s="6" t="s">
+      <c r="D429" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E429" s="6" t="s">
@@ -14450,7 +14448,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:7">
+    <row r="430" spans="1:7">
       <c r="A430" s="6" t="s">
         <v>666</v>
       </c>
@@ -14621,7 +14619,7 @@
       <c r="C437" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="D437" s="6" t="s">
+      <c r="D437" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E437" s="6" t="s">
@@ -14634,7 +14632,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:7">
+    <row r="438" spans="1:7">
       <c r="A438" s="6" t="s">
         <v>671</v>
       </c>
@@ -14657,7 +14655,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="439" hidden="1" spans="1:7">
+    <row r="439" spans="1:7">
       <c r="A439" s="6" t="s">
         <v>786</v>
       </c>
@@ -14690,7 +14688,7 @@
       <c r="C440" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D440" s="6" t="s">
+      <c r="D440" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E440" s="6" t="s">
@@ -14805,7 +14803,7 @@
       <c r="C445" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="D445" s="6" t="s">
+      <c r="D445" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E445" s="6" t="s">
@@ -14818,7 +14816,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="446" hidden="1" spans="1:7">
+    <row r="446" spans="1:7">
       <c r="A446" s="6" t="s">
         <v>797</v>
       </c>
@@ -14851,7 +14849,7 @@
       <c r="C447" s="6" t="s">
         <v>804</v>
       </c>
-      <c r="D447" s="6" t="s">
+      <c r="D447" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E447" s="6" t="s">
@@ -14864,7 +14862,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="448" hidden="1" spans="1:7">
+    <row r="448" spans="1:7">
       <c r="A448" s="6" t="s">
         <v>805</v>
       </c>
@@ -15071,7 +15069,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="457" hidden="1" spans="1:7">
+    <row r="457" spans="1:7">
       <c r="A457" s="6" t="s">
         <v>786</v>
       </c>
@@ -15104,7 +15102,7 @@
       <c r="C458" s="6" t="s">
         <v>819</v>
       </c>
-      <c r="D458" s="6" t="s">
+      <c r="D458" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E458" s="6" t="s">
@@ -15150,7 +15148,7 @@
       <c r="C460" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D460" s="6" t="s">
+      <c r="D460" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E460" s="6" t="s">
@@ -15242,7 +15240,7 @@
       <c r="C464" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="D464" s="6" t="s">
+      <c r="D464" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E464" s="6" t="s">
@@ -15255,7 +15253,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="465" hidden="1" spans="1:7">
+    <row r="465" spans="1:7">
       <c r="A465" s="6" t="s">
         <v>832</v>
       </c>
@@ -15403,7 +15401,7 @@
       <c r="C471" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="D471" s="6" t="s">
+      <c r="D471" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E471" s="6" t="s">
@@ -15416,7 +15414,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="472" hidden="1" spans="1:7">
+    <row r="472" spans="1:7">
       <c r="A472" s="6" t="s">
         <v>846</v>
       </c>
@@ -15564,7 +15562,7 @@
       <c r="C478" s="6" t="s">
         <v>862</v>
       </c>
-      <c r="D478" s="6" t="s">
+      <c r="D478" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E478" s="6" t="s">
@@ -15577,7 +15575,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="479" hidden="1" spans="1:7">
+    <row r="479" spans="1:7">
       <c r="A479" s="6" t="s">
         <v>860</v>
       </c>
@@ -15600,7 +15598,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="480" hidden="1" spans="1:7">
+    <row r="480" spans="1:7">
       <c r="A480" s="6" t="s">
         <v>865</v>
       </c>
@@ -15633,7 +15631,7 @@
       <c r="C481" s="6" t="s">
         <v>862</v>
       </c>
-      <c r="D481" s="6" t="s">
+      <c r="D481" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E481" s="6" t="s">
@@ -15715,7 +15713,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="485" hidden="1" spans="1:7">
+    <row r="485" spans="1:7">
       <c r="A485" s="6" t="s">
         <v>876</v>
       </c>
@@ -15748,7 +15746,7 @@
       <c r="C486" s="6" t="s">
         <v>875</v>
       </c>
-      <c r="D486" s="6" t="s">
+      <c r="D486" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E486" s="6" t="s">
@@ -15840,7 +15838,7 @@
       <c r="C490" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D490" s="6" t="s">
+      <c r="D490" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E490" s="6" t="s">
@@ -15853,7 +15851,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="491" hidden="1" spans="1:7">
+    <row r="491" spans="1:7">
       <c r="A491" s="6" t="s">
         <v>890</v>
       </c>
@@ -15899,7 +15897,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="493" hidden="1" spans="1:7">
+    <row r="493" spans="1:7">
       <c r="A493" s="6" t="s">
         <v>894</v>
       </c>
@@ -15929,10 +15927,10 @@
       <c r="B494" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="C494" s="6" t="s">
+      <c r="C494" s="7" t="s">
         <v>896</v>
       </c>
-      <c r="D494" s="6" t="s">
+      <c r="D494" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E494" s="6" t="s">
@@ -15955,7 +15953,7 @@
       <c r="C495" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D495" s="6" t="s">
+      <c r="D495" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E495" s="6" t="s">
@@ -15968,7 +15966,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="496" hidden="1" spans="1:7">
+    <row r="496" spans="1:7">
       <c r="A496" s="6" t="s">
         <v>902</v>
       </c>
@@ -16037,7 +16035,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="499" hidden="1" spans="1:7">
+    <row r="499" spans="1:7">
       <c r="A499" s="6" t="s">
         <v>907</v>
       </c>
@@ -16070,7 +16068,7 @@
       <c r="C500" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="D500" s="6" t="s">
+      <c r="D500" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E500" s="6" t="s">
@@ -16093,7 +16091,7 @@
       <c r="C501" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="D501" s="6" t="s">
+      <c r="D501" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E501" s="6" t="s">
@@ -16106,7 +16104,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="502" hidden="1" spans="1:7">
+    <row r="502" spans="1:7">
       <c r="A502" s="6" t="s">
         <v>915</v>
       </c>
@@ -16415,7 +16413,7 @@
       <c r="C515" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="D515" s="6" t="s">
+      <c r="D515" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E515" s="6" t="s">
@@ -16428,7 +16426,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="516" hidden="1" spans="1:7">
+    <row r="516" spans="1:7">
       <c r="A516" s="6" t="s">
         <v>940</v>
       </c>
@@ -16461,7 +16459,7 @@
       <c r="C517" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="D517" s="6" t="s">
+      <c r="D517" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E517" s="6" t="s">
@@ -16474,7 +16472,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="518" hidden="1" spans="1:7">
+    <row r="518" spans="1:7">
       <c r="A518" s="6" t="s">
         <v>945</v>
       </c>
@@ -16576,7 +16574,7 @@
       <c r="C522" s="6" t="s">
         <v>948</v>
       </c>
-      <c r="D522" s="6" t="s">
+      <c r="D522" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E522" s="6" t="s">
@@ -16589,7 +16587,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="523" hidden="1" spans="1:7">
+    <row r="523" spans="1:7">
       <c r="A523" s="6" t="s">
         <v>956</v>
       </c>
@@ -16668,7 +16666,7 @@
       <c r="C526" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="D526" s="6" t="s">
+      <c r="D526" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E526" s="6" t="s">
@@ -16681,7 +16679,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="527" hidden="1" spans="1:7">
+    <row r="527" spans="1:7">
       <c r="A527" s="6" t="s">
         <v>964</v>
       </c>
@@ -16737,7 +16735,7 @@
       <c r="C529" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D529" s="6" t="s">
+      <c r="D529" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E529" s="6" t="s">
@@ -16750,7 +16748,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="530" hidden="1" spans="1:7">
+    <row r="530" spans="1:7">
       <c r="A530" s="6" t="s">
         <v>945</v>
       </c>
@@ -16783,7 +16781,7 @@
       <c r="C531" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="D531" s="6" t="s">
+      <c r="D531" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E531" s="6" t="s">
@@ -16796,7 +16794,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="532" hidden="1" spans="1:7">
+    <row r="532" spans="1:7">
       <c r="A532" s="6" t="s">
         <v>971</v>
       </c>
@@ -16829,7 +16827,7 @@
       <c r="C533" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="D533" s="6" t="s">
+      <c r="D533" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E533" s="6" t="s">
@@ -16842,7 +16840,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="534" hidden="1" spans="1:7">
+    <row r="534" spans="1:7">
       <c r="A534" s="6" t="s">
         <v>975</v>
       </c>
@@ -16964,10 +16962,10 @@
       <c r="B539" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="C539" s="6" t="s">
+      <c r="C539" s="7" t="s">
         <v>896</v>
       </c>
-      <c r="D539" s="6" t="s">
+      <c r="D539" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E539" s="6" t="s">
@@ -16980,7 +16978,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="540" hidden="1" spans="1:7">
+    <row r="540" spans="1:7">
       <c r="A540" s="6" t="s">
         <v>986</v>
       </c>
@@ -17233,7 +17231,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="551" hidden="1" spans="1:7">
+    <row r="551" spans="1:7">
       <c r="A551" s="6" t="s">
         <v>1003</v>
       </c>
@@ -17266,7 +17264,7 @@
       <c r="C552" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="D552" s="6" t="s">
+      <c r="D552" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E552" s="6" t="s">
@@ -17289,7 +17287,7 @@
       <c r="C553" s="6" t="s">
         <v>1009</v>
       </c>
-      <c r="D553" s="6" t="s">
+      <c r="D553" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E553" s="6" t="s">
@@ -17371,7 +17369,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="557" hidden="1" spans="1:7">
+    <row r="557" spans="1:7">
       <c r="A557" s="6" t="s">
         <v>79</v>
       </c>
@@ -17404,7 +17402,7 @@
       <c r="C558" s="6" t="s">
         <v>1015</v>
       </c>
-      <c r="D558" s="6" t="s">
+      <c r="D558" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E558" s="6" t="s">
@@ -17634,7 +17632,7 @@
       <c r="C568" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D568" s="6" t="s">
+      <c r="D568" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E568" s="6" t="s">
@@ -17670,7 +17668,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="570" hidden="1" spans="1:7">
+    <row r="570" spans="1:7">
       <c r="A570" s="6" t="s">
         <v>1035</v>
       </c>
@@ -17693,7 +17691,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="571" hidden="1" spans="1:7">
+    <row r="571" spans="1:7">
       <c r="A571" s="6" t="s">
         <v>1039</v>
       </c>
@@ -17726,7 +17724,7 @@
       <c r="C572" s="6" t="s">
         <v>1041</v>
       </c>
-      <c r="D572" s="6" t="s">
+      <c r="D572" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E572" s="6" t="s">
@@ -17749,7 +17747,7 @@
       <c r="C573" s="6" t="s">
         <v>1043</v>
       </c>
-      <c r="D573" s="6" t="s">
+      <c r="D573" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E573" s="6" t="s">
@@ -17841,7 +17839,7 @@
       <c r="C577" s="6" t="s">
         <v>1050</v>
       </c>
-      <c r="D577" s="6" t="s">
+      <c r="D577" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E577" s="6" t="s">
@@ -17969,7 +17967,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="583" hidden="1" spans="1:7">
+    <row r="583" spans="1:7">
       <c r="A583" s="6" t="s">
         <v>110</v>
       </c>
@@ -18002,7 +18000,7 @@
       <c r="C584" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D584" s="6" t="s">
+      <c r="D584" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E584" s="6" t="s">
@@ -18015,7 +18013,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="585" hidden="1" spans="1:7">
+    <row r="585" spans="1:7">
       <c r="A585" s="6" t="s">
         <v>536</v>
       </c>
@@ -18038,7 +18036,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="586" hidden="1" spans="1:7">
+    <row r="586" spans="1:7">
       <c r="A586" s="6" t="s">
         <v>536</v>
       </c>
@@ -18071,7 +18069,7 @@
       <c r="C587" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D587" s="6" t="s">
+      <c r="D587" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E587" s="6" t="s">
@@ -18094,7 +18092,7 @@
       <c r="C588" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D588" s="6" t="s">
+      <c r="D588" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E588" s="6" t="s">
@@ -18140,7 +18138,7 @@
       <c r="C590" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D590" s="6" t="s">
+      <c r="D590" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E590" s="6" t="s">
@@ -18199,7 +18197,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="593" hidden="1" spans="1:7">
+    <row r="593" spans="1:7">
       <c r="A593" s="6" t="s">
         <v>1023</v>
       </c>
@@ -18232,7 +18230,7 @@
       <c r="C594" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D594" s="6" t="s">
+      <c r="D594" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E594" s="6" t="s">
@@ -18324,7 +18322,7 @@
       <c r="C598" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D598" s="6" t="s">
+      <c r="D598" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E598" s="6" t="s">
@@ -18337,7 +18335,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="599" hidden="1" spans="1:7">
+    <row r="599" spans="1:7">
       <c r="A599" s="6" t="s">
         <v>1052</v>
       </c>
@@ -18383,7 +18381,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="601" hidden="1" spans="1:7">
+    <row r="601" spans="1:7">
       <c r="A601" s="6" t="s">
         <v>1003</v>
       </c>
@@ -18646,7 +18644,7 @@
       <c r="C612" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D612" s="6" t="s">
+      <c r="D612" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E612" s="6" t="s">
@@ -18659,7 +18657,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="613" hidden="1" spans="1:7">
+    <row r="613" spans="1:7">
       <c r="A613" s="6" t="s">
         <v>140</v>
       </c>
@@ -18715,7 +18713,7 @@
       <c r="C615" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="D615" s="6" t="s">
+      <c r="D615" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E615" s="6" t="s">
@@ -18728,7 +18726,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="616" hidden="1" spans="1:7">
+    <row r="616" spans="1:7">
       <c r="A616" s="6" t="s">
         <v>1088</v>
       </c>
@@ -18853,7 +18851,7 @@
       <c r="C621" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D621" s="6" t="s">
+      <c r="D621" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E621" s="6" t="s">
@@ -18866,7 +18864,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="622" hidden="1" spans="1:7">
+    <row r="622" spans="1:7">
       <c r="A622" s="6" t="s">
         <v>1097</v>
       </c>
@@ -18922,7 +18920,7 @@
       <c r="C624" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D624" s="6" t="s">
+      <c r="D624" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E624" s="6" t="s">
@@ -18935,7 +18933,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="625" hidden="1" spans="1:7">
+    <row r="625" spans="1:7">
       <c r="A625" s="6" t="s">
         <v>1103</v>
       </c>
@@ -18968,7 +18966,7 @@
       <c r="C626" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D626" s="6" t="s">
+      <c r="D626" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E626" s="6" t="s">
@@ -18981,7 +18979,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="627" hidden="1" spans="1:7">
+    <row r="627" spans="1:7">
       <c r="A627" s="6" t="s">
         <v>62</v>
       </c>
@@ -19004,7 +19002,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="628" hidden="1" spans="1:7">
+    <row r="628" spans="1:7">
       <c r="A628" s="6" t="s">
         <v>62</v>
       </c>
@@ -19083,7 +19081,7 @@
       <c r="C631" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D631" s="6" t="s">
+      <c r="D631" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E631" s="6" t="s">
@@ -19142,7 +19140,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="634" spans="1:7">
+    <row r="634" hidden="1" spans="1:7">
       <c r="A634" s="6" t="s">
         <v>1111</v>
       </c>
@@ -19175,7 +19173,7 @@
       <c r="C635" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D635" s="6" t="s">
+      <c r="D635" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E635" s="6" t="s">
@@ -19188,7 +19186,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="636" hidden="1" spans="1:7">
+    <row r="636" spans="1:7">
       <c r="A636" s="6" t="s">
         <v>1115</v>
       </c>
@@ -19199,7 +19197,7 @@
         <v>272</v>
       </c>
       <c r="D636" s="6" t="s">
-        <v>1117</v>
+        <v>22</v>
       </c>
       <c r="E636" s="6" t="s">
         <v>29</v>
@@ -19213,10 +19211,10 @@
     </row>
     <row r="637" hidden="1" spans="1:7">
       <c r="A637" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B637" s="6" t="s">
         <v>1118</v>
-      </c>
-      <c r="B637" s="6" t="s">
-        <v>1119</v>
       </c>
       <c r="C637" s="6" t="s">
         <v>638</v>
@@ -19236,10 +19234,10 @@
     </row>
     <row r="638" hidden="1" spans="1:7">
       <c r="A638" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B638" s="6" t="s">
         <v>1120</v>
-      </c>
-      <c r="B638" s="6" t="s">
-        <v>1121</v>
       </c>
       <c r="C638" s="6" t="s">
         <v>638</v>
@@ -19262,7 +19260,7 @@
         <v>630</v>
       </c>
       <c r="B639" s="6" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C639" s="6" t="s">
         <v>632</v>
@@ -19285,12 +19283,12 @@
         <v>633</v>
       </c>
       <c r="B640" s="6" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C640" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="D640" s="6" t="s">
+      <c r="D640" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E640" s="6" t="s">
@@ -19303,24 +19301,24 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="641" hidden="1" spans="1:7">
+    <row r="641" spans="1:7">
       <c r="A641" s="6" t="s">
         <v>639</v>
       </c>
       <c r="B641" s="6" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C641" s="6" t="s">
         <v>632</v>
       </c>
       <c r="D641" s="6" t="s">
-        <v>1117</v>
+        <v>22</v>
       </c>
       <c r="E641" s="6" t="s">
         <v>21</v>
       </c>
       <c r="F641" s="6" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G641" s="6" t="s">
         <v>1108</v>
@@ -19328,13 +19326,13 @@
     </row>
     <row r="642" hidden="1" spans="1:7">
       <c r="A642" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B642" s="6" t="s">
         <v>1126</v>
       </c>
-      <c r="B642" s="6" t="s">
+      <c r="C642" s="6" t="s">
         <v>1127</v>
-      </c>
-      <c r="C642" s="6" t="s">
-        <v>1128</v>
       </c>
       <c r="D642" s="6" t="s">
         <v>10</v>
@@ -19351,13 +19349,13 @@
     </row>
     <row r="643" hidden="1" spans="1:7">
       <c r="A643" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B643" s="6" t="s">
         <v>1129</v>
       </c>
-      <c r="B643" s="6" t="s">
-        <v>1130</v>
-      </c>
       <c r="C643" s="6" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D643" s="6" t="s">
         <v>285</v>
@@ -19366,7 +19364,7 @@
         <v>43</v>
       </c>
       <c r="F643" s="6" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G643" s="6" t="s">
         <v>1108</v>
@@ -19374,10 +19372,10 @@
     </row>
     <row r="644" hidden="1" spans="1:7">
       <c r="A644" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B644" s="6" t="s">
         <v>1132</v>
-      </c>
-      <c r="B644" s="6" t="s">
-        <v>1133</v>
       </c>
       <c r="C644" s="6" t="s">
         <v>87</v>
@@ -19395,47 +19393,47 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="645" spans="1:7">
+    <row r="645" hidden="1" spans="1:7">
       <c r="A645" s="6" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B645" s="6" t="s">
         <v>1134</v>
-      </c>
-      <c r="B645" s="6" t="s">
-        <v>1135</v>
       </c>
       <c r="C645" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D645" s="6" t="s">
+      <c r="D645" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E645" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F645" s="6" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G645" s="6" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="646" hidden="1" spans="1:7">
+    <row r="646" spans="1:7">
       <c r="A646" s="6" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B646" s="6" t="s">
         <v>1137</v>
-      </c>
-      <c r="B646" s="6" t="s">
-        <v>1138</v>
       </c>
       <c r="C646" s="6" t="s">
         <v>208</v>
       </c>
       <c r="D646" s="6" t="s">
-        <v>1117</v>
+        <v>22</v>
       </c>
       <c r="E646" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F646" s="6" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G646" s="6" t="s">
         <v>1108</v>
@@ -19443,10 +19441,10 @@
     </row>
     <row r="647" hidden="1" spans="1:7">
       <c r="A647" s="6" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B647" s="6" t="s">
         <v>1140</v>
-      </c>
-      <c r="B647" s="6" t="s">
-        <v>1141</v>
       </c>
       <c r="C647" s="6" t="s">
         <v>87</v>
@@ -19458,7 +19456,7 @@
         <v>11</v>
       </c>
       <c r="F647" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G647" s="6" t="s">
         <v>1108</v>
@@ -19466,10 +19464,10 @@
     </row>
     <row r="648" hidden="1" spans="1:7">
       <c r="A648" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B648" s="6" t="s">
         <v>1143</v>
-      </c>
-      <c r="B648" s="6" t="s">
-        <v>1144</v>
       </c>
       <c r="C648" s="6"/>
       <c r="D648" s="6" t="s">
@@ -19479,23 +19477,23 @@
         <v>11</v>
       </c>
       <c r="F648" s="6" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G648" s="6" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="649" spans="1:7">
+    <row r="649" hidden="1" spans="1:7">
       <c r="A649" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B649" s="6" t="s">
         <v>1146</v>
-      </c>
-      <c r="B649" s="6" t="s">
-        <v>1147</v>
       </c>
       <c r="C649" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D649" s="6" t="s">
+      <c r="D649" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E649" s="6" t="s">
@@ -19510,10 +19508,10 @@
     </row>
     <row r="650" hidden="1" spans="1:7">
       <c r="A650" s="6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B650" s="6" t="s">
         <v>1148</v>
-      </c>
-      <c r="B650" s="6" t="s">
-        <v>1149</v>
       </c>
       <c r="C650" s="6" t="s">
         <v>253</v>
@@ -19528,15 +19526,15 @@
         <v>836</v>
       </c>
       <c r="G650" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="651" hidden="1" spans="1:7">
       <c r="A651" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B651" s="6" t="s">
         <v>1151</v>
-      </c>
-      <c r="B651" s="6" t="s">
-        <v>1152</v>
       </c>
       <c r="C651" s="6" t="s">
         <v>253</v>
@@ -19551,15 +19549,15 @@
         <v>836</v>
       </c>
       <c r="G651" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="652" hidden="1" spans="1:7">
       <c r="A652" s="6" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B652" s="6" t="s">
         <v>1153</v>
-      </c>
-      <c r="B652" s="6" t="s">
-        <v>1154</v>
       </c>
       <c r="C652" s="6" t="s">
         <v>862</v>
@@ -19574,44 +19572,44 @@
         <v>836</v>
       </c>
       <c r="G652" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="653" hidden="1" spans="1:7">
       <c r="A653" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B653" s="6" t="s">
         <v>1155</v>
-      </c>
-      <c r="B653" s="6" t="s">
-        <v>1156</v>
       </c>
       <c r="C653" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D653" s="6" t="s">
+      <c r="D653" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E653" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F653" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G653" s="6" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="654" spans="1:7">
+      <c r="A654" s="6" t="s">
         <v>1157</v>
       </c>
-      <c r="G653" s="6" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="654" hidden="1" spans="1:7">
-      <c r="A654" s="6" t="s">
+      <c r="B654" s="6" t="s">
         <v>1158</v>
-      </c>
-      <c r="B654" s="6" t="s">
-        <v>1159</v>
       </c>
       <c r="C654" s="6" t="s">
         <v>561</v>
       </c>
       <c r="D654" s="6" t="s">
-        <v>1117</v>
+        <v>22</v>
       </c>
       <c r="E654" s="6" t="s">
         <v>29</v>
@@ -19620,15 +19618,15 @@
         <v>836</v>
       </c>
       <c r="G654" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="655" hidden="1" spans="1:7">
       <c r="A655" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B655" s="6" t="s">
         <v>1160</v>
-      </c>
-      <c r="B655" s="6" t="s">
-        <v>1161</v>
       </c>
       <c r="C655" s="6" t="s">
         <v>237</v>
@@ -19643,15 +19641,15 @@
         <v>836</v>
       </c>
       <c r="G655" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="656" hidden="1" spans="1:7">
       <c r="A656" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B656" s="6" t="s">
         <v>1162</v>
-      </c>
-      <c r="B656" s="6" t="s">
-        <v>1163</v>
       </c>
       <c r="C656" s="6" t="s">
         <v>237</v>
@@ -19666,15 +19664,15 @@
         <v>836</v>
       </c>
       <c r="G656" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="657" hidden="1" spans="1:7">
       <c r="A657" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B657" s="6" t="s">
         <v>1164</v>
-      </c>
-      <c r="B657" s="6" t="s">
-        <v>1165</v>
       </c>
       <c r="C657" s="6" t="s">
         <v>914</v>
@@ -19689,20 +19687,20 @@
         <v>836</v>
       </c>
       <c r="G657" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="658" hidden="1" spans="1:7">
       <c r="A658" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B658" s="6" t="s">
         <v>1166</v>
-      </c>
-      <c r="B658" s="6" t="s">
-        <v>1167</v>
       </c>
       <c r="C658" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="D658" s="6" t="s">
+      <c r="D658" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E658" s="6" t="s">
@@ -19712,30 +19710,30 @@
         <v>836</v>
       </c>
       <c r="G658" s="6" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="659" hidden="1" spans="1:7">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="659" spans="1:7">
       <c r="A659" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B659" s="6" t="s">
         <v>1168</v>
-      </c>
-      <c r="B659" s="6" t="s">
-        <v>1169</v>
       </c>
       <c r="C659" s="6" t="s">
         <v>896</v>
       </c>
       <c r="D659" s="6" t="s">
-        <v>1117</v>
+        <v>22</v>
       </c>
       <c r="E659" s="6" t="s">
         <v>21</v>
       </c>
       <c r="F659" s="6" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G659" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="660" hidden="1" spans="1:7">
@@ -19743,7 +19741,7 @@
         <v>850</v>
       </c>
       <c r="B660" s="6" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C660" s="6" t="s">
         <v>245</v>
@@ -19758,7 +19756,7 @@
         <v>836</v>
       </c>
       <c r="G660" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="661" hidden="1" spans="1:7">
@@ -19766,7 +19764,7 @@
         <v>852</v>
       </c>
       <c r="B661" s="6" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C661" s="6" t="s">
         <v>245</v>
@@ -19781,15 +19779,15 @@
         <v>836</v>
       </c>
       <c r="G661" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="662" hidden="1" spans="1:7">
       <c r="A662" s="6" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B662" s="6" t="s">
         <v>1173</v>
-      </c>
-      <c r="B662" s="6" t="s">
-        <v>1174</v>
       </c>
       <c r="C662" s="6" t="s">
         <v>875</v>
@@ -19804,44 +19802,44 @@
         <v>836</v>
       </c>
       <c r="G662" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="663" hidden="1" spans="1:7">
       <c r="A663" s="6" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B663" s="6" t="s">
         <v>1175</v>
-      </c>
-      <c r="B663" s="6" t="s">
-        <v>1176</v>
       </c>
       <c r="C663" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="D663" s="6" t="s">
+      <c r="D663" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E663" s="6" t="s">
         <v>43</v>
       </c>
       <c r="F663" s="6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G663" s="6" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="664" spans="1:7">
+      <c r="A664" s="6" t="s">
         <v>1177</v>
       </c>
-      <c r="G663" s="6" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="664" hidden="1" spans="1:7">
-      <c r="A664" s="6" t="s">
+      <c r="B664" s="6" t="s">
         <v>1178</v>
-      </c>
-      <c r="B664" s="6" t="s">
-        <v>1179</v>
       </c>
       <c r="C664" s="6" t="s">
         <v>875</v>
       </c>
       <c r="D664" s="6" t="s">
-        <v>1117</v>
+        <v>22</v>
       </c>
       <c r="E664" s="6" t="s">
         <v>43</v>
@@ -19850,7 +19848,7 @@
         <v>836</v>
       </c>
       <c r="G664" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="665" hidden="1" spans="1:7">
@@ -19858,7 +19856,7 @@
         <v>982</v>
       </c>
       <c r="B665" s="6" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C665" s="6" t="s">
         <v>150</v>
@@ -19873,15 +19871,15 @@
         <v>836</v>
       </c>
       <c r="G665" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="666" hidden="1" spans="1:7">
       <c r="A666" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B666" s="6" t="s">
         <v>1181</v>
-      </c>
-      <c r="B666" s="6" t="s">
-        <v>1182</v>
       </c>
       <c r="C666" s="6" t="s">
         <v>871</v>
@@ -19896,15 +19894,15 @@
         <v>836</v>
       </c>
       <c r="G666" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="667" hidden="1" spans="1:7">
       <c r="A667" s="6" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B667" s="6" t="s">
         <v>1183</v>
-      </c>
-      <c r="B667" s="6" t="s">
-        <v>1184</v>
       </c>
       <c r="C667" s="6"/>
       <c r="D667" s="6" t="s">
@@ -19917,37 +19915,38 @@
         <v>836</v>
       </c>
       <c r="G667" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="668" hidden="1" spans="1:7">
       <c r="A668" s="6" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B668" s="6" t="s">
         <v>1185</v>
-      </c>
-      <c r="B668" s="6" t="s">
-        <v>1186</v>
       </c>
       <c r="C668" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D668" s="6" t="s">
+      <c r="D668" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E668" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F668" s="6" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G668" s="6" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G668" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="2">
+    <filterColumn colId="3">
       <filters>
-        <filter val="F.Ghezal"/>
+        <filter val="15h30 -17h00"/>
+        <filter val="15h30-17h00"/>
       </filters>
     </filterColumn>
     <sortState ref="A1:G668">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$669</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -68,7 +71,7 @@
     <t>Amphi 03</t>
   </si>
   <si>
-    <t>ING2ST</t>
+    <t>ING2</t>
   </si>
   <si>
     <t>TD-Electricité fondamentale</t>
@@ -263,7 +266,7 @@
     <t>Cours-OV-ING2TM</t>
   </si>
   <si>
-    <t>ING2TM</t>
+    <t>ING2RSE</t>
   </si>
   <si>
     <t>TD-EF-ING2TM</t>
@@ -653,7 +656,7 @@
     <t>Salle micro bis</t>
   </si>
   <si>
-    <t>Ing1</t>
+    <t>ING1</t>
   </si>
   <si>
     <t>12h30-14h</t>
@@ -800,7 +803,7 @@
     <t>Salle-micros 01 G1/G2</t>
   </si>
   <si>
-    <t>Ing3</t>
+    <t>ING3EI</t>
   </si>
   <si>
     <t>Unité creuse Ing3</t>
@@ -971,7 +974,7 @@
     <t>S08bis/Section</t>
   </si>
   <si>
-    <t>Ing3TM</t>
+    <t>ING3TM</t>
   </si>
   <si>
     <t>TP-Automates Programmables Industriels PLC</t>
@@ -1121,7 +1124,7 @@
     <t>S12</t>
   </si>
   <si>
-    <t>Ing4</t>
+    <t>ING4RSE</t>
   </si>
   <si>
     <t>Cours-Systèmes de conversion de l'énergie éolienne</t>
@@ -3720,14 +3723,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4183,28 +4179,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4213,118 +4212,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4678,6 +4674,10 @@
   <sheetPr/>
   <dimension ref="A1:G669"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="36.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="26.2857142857143" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -20067,6 +20067,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G669" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$674</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$675</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4718" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4725" uniqueCount="1128">
   <si>
     <t>Enseignements</t>
   </si>
@@ -1643,7 +1643,7 @@
     <t>A08</t>
   </si>
   <si>
-    <t>Cours-ELT Fondamentale 1</t>
+    <t>Cours-Electrotechnique Fondamentale 1</t>
   </si>
   <si>
     <t>Cours-ELT1-L2ELT</t>
@@ -1724,7 +1724,7 @@
     <t>Cours-PST-L2ELT</t>
   </si>
   <si>
-    <t>Cours-État de l'art du GE</t>
+    <t>Cours-État de l'art du Génie électrique</t>
   </si>
   <si>
     <t>Cours-EGE-L2ELT</t>
@@ -1787,7 +1787,7 @@
     <t>S06/G1</t>
   </si>
   <si>
-    <t>Cours-ELN Fondamentale 1</t>
+    <t>Cours-Electronique Fondamentale 1</t>
   </si>
   <si>
     <t>Cours-ELN1-L2ELT</t>
@@ -1862,7 +1862,7 @@
     <t>Labo ELN-P SG31</t>
   </si>
   <si>
-    <t>TP-Shémas et Appareillage</t>
+    <t>TP-Shémas et Appareillage électrique</t>
   </si>
   <si>
     <t>TP-S &amp; A-3ELT</t>
@@ -1874,7 +1874,7 @@
     <t>Labo Shémas SG21 &amp; SG11/SG12</t>
   </si>
   <si>
-    <t>TP-capteurs</t>
+    <t>TP-Capteurs</t>
   </si>
   <si>
     <t>TP-Cap-3ELT</t>
@@ -1916,9 +1916,6 @@
     <t>Salle08BIS G3</t>
   </si>
   <si>
-    <t>TDThéorie du champ</t>
-  </si>
-  <si>
     <t>TD-TC-3ELT</t>
   </si>
   <si>
@@ -1928,24 +1925,24 @@
     <t>Labo Réseaux SG21</t>
   </si>
   <si>
+    <t>S14 G3</t>
+  </si>
+  <si>
+    <t>Labo Réseaux SG22</t>
+  </si>
+  <si>
+    <t>Cours-RE-3ELT</t>
+  </si>
+  <si>
+    <t>S04 G3</t>
+  </si>
+  <si>
+    <t>Salle8Bis G2</t>
+  </si>
+  <si>
     <t>TD-Théorie du champ</t>
   </si>
   <si>
-    <t>S14 G3</t>
-  </si>
-  <si>
-    <t>Labo Réseaux SG22</t>
-  </si>
-  <si>
-    <t>Cours-RE-3ELT</t>
-  </si>
-  <si>
-    <t>S04 G3</t>
-  </si>
-  <si>
-    <t>Salle8Bis G2</t>
-  </si>
-  <si>
     <t>A12 G1</t>
   </si>
   <si>
@@ -1973,15 +1970,12 @@
     <t>Labo ELN-P SG11</t>
   </si>
   <si>
-    <t>Cours-Shémas et Appareillage</t>
+    <t>Cours-Shémas et Appareillage électrique</t>
   </si>
   <si>
     <t>Cours-S &amp; A</t>
   </si>
   <si>
-    <t>Cours-Théorie du champ</t>
-  </si>
-  <si>
     <t>Cours-Tc-3ELT</t>
   </si>
   <si>
@@ -3380,9 +3374,6 @@
     <t>TD-MRE-MCIL3</t>
   </si>
   <si>
-    <t>TP-Capteurs</t>
-  </si>
-  <si>
     <t>TP-SE-MCIL3</t>
   </si>
   <si>
@@ -3420,6 +3411,9 @@
   </si>
   <si>
     <t>Salle-micros 02 Auto G2</t>
+  </si>
+  <si>
+    <t>Cours-Ppython-L2ELT</t>
   </si>
 </sst>
 </file>
@@ -4388,11 +4382,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G674"/>
+  <dimension ref="A1:G675"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="39.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="23.8571428571429" customWidth="1"/>
+    <col min="1" max="1" width="44.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -12033,10 +12026,10 @@
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
+        <v>252</v>
+      </c>
+      <c r="B333" t="s">
         <v>628</v>
-      </c>
-      <c r="B333" t="s">
-        <v>629</v>
       </c>
       <c r="C333" t="s">
         <v>181</v>
@@ -12048,7 +12041,7 @@
         <v>36</v>
       </c>
       <c r="F333" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G333" t="s">
         <v>593</v>
@@ -12071,7 +12064,7 @@
         <v>36</v>
       </c>
       <c r="F334" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G334" t="s">
         <v>593</v>
@@ -12079,10 +12072,10 @@
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>632</v>
+        <v>252</v>
       </c>
       <c r="B335" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C335" t="s">
         <v>181</v>
@@ -12094,7 +12087,7 @@
         <v>36</v>
       </c>
       <c r="F335" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G335" t="s">
         <v>593</v>
@@ -12117,7 +12110,7 @@
         <v>36</v>
       </c>
       <c r="F336" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G336" t="s">
         <v>593</v>
@@ -12128,7 +12121,7 @@
         <v>617</v>
       </c>
       <c r="B337" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C337" t="s">
         <v>227</v>
@@ -12163,7 +12156,7 @@
         <v>36</v>
       </c>
       <c r="F338" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G338" t="s">
         <v>593</v>
@@ -12186,7 +12179,7 @@
         <v>36</v>
       </c>
       <c r="F339" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G339" t="s">
         <v>593</v>
@@ -12194,10 +12187,10 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B340" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C340" t="s">
         <v>181</v>
@@ -12209,7 +12202,7 @@
         <v>36</v>
       </c>
       <c r="F340" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G340" t="s">
         <v>593</v>
@@ -12217,10 +12210,10 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
+        <v>638</v>
+      </c>
+      <c r="B341" t="s">
         <v>639</v>
-      </c>
-      <c r="B341" t="s">
-        <v>640</v>
       </c>
       <c r="C341" t="s">
         <v>164</v>
@@ -12232,7 +12225,7 @@
         <v>47</v>
       </c>
       <c r="F341" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G341" t="s">
         <v>593</v>
@@ -12255,7 +12248,7 @@
         <v>47</v>
       </c>
       <c r="F342" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G342" t="s">
         <v>593</v>
@@ -12266,7 +12259,7 @@
         <v>606</v>
       </c>
       <c r="B343" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C343" t="s">
         <v>164</v>
@@ -12278,7 +12271,7 @@
         <v>47</v>
       </c>
       <c r="F343" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G343" t="s">
         <v>593</v>
@@ -12301,7 +12294,7 @@
         <v>47</v>
       </c>
       <c r="F344" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G344" t="s">
         <v>593</v>
@@ -12312,7 +12305,7 @@
         <v>606</v>
       </c>
       <c r="B345" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C345" t="s">
         <v>164</v>
@@ -12324,7 +12317,7 @@
         <v>47</v>
       </c>
       <c r="F345" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G345" t="s">
         <v>593</v>
@@ -12332,10 +12325,10 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
+        <v>646</v>
+      </c>
+      <c r="B346" t="s">
         <v>647</v>
-      </c>
-      <c r="B346" t="s">
-        <v>648</v>
       </c>
       <c r="C346" t="s">
         <v>227</v>
@@ -12347,7 +12340,7 @@
         <v>47</v>
       </c>
       <c r="F346" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G346" t="s">
         <v>593</v>
@@ -12355,10 +12348,10 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>649</v>
+        <v>222</v>
       </c>
       <c r="B347" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C347" t="s">
         <v>174</v>
@@ -12370,7 +12363,7 @@
         <v>47</v>
       </c>
       <c r="F347" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G347" t="s">
         <v>593</v>
@@ -12378,10 +12371,10 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B348" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C348" t="s">
         <v>372</v>
@@ -12416,7 +12409,7 @@
         <v>54</v>
       </c>
       <c r="F349" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G349" t="s">
         <v>593</v>
@@ -12439,7 +12432,7 @@
         <v>54</v>
       </c>
       <c r="F350" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G350" t="s">
         <v>593</v>
@@ -12462,7 +12455,7 @@
         <v>54</v>
       </c>
       <c r="F351" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G351" t="s">
         <v>593</v>
@@ -12485,7 +12478,7 @@
         <v>54</v>
       </c>
       <c r="F352" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G352" t="s">
         <v>593</v>
@@ -12508,7 +12501,7 @@
         <v>54</v>
       </c>
       <c r="F353" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G353" t="s">
         <v>593</v>
@@ -12531,7 +12524,7 @@
         <v>54</v>
       </c>
       <c r="F354" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G354" t="s">
         <v>593</v>
@@ -12554,7 +12547,7 @@
         <v>54</v>
       </c>
       <c r="F355" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G355" t="s">
         <v>593</v>
@@ -12565,7 +12558,7 @@
         <v>170</v>
       </c>
       <c r="B356" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C356" t="s">
         <v>608</v>
@@ -12600,7 +12593,7 @@
         <v>54</v>
       </c>
       <c r="F357" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G357" t="s">
         <v>593</v>
@@ -12623,7 +12616,7 @@
         <v>54</v>
       </c>
       <c r="F358" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G358" t="s">
         <v>593</v>
@@ -12634,7 +12627,7 @@
         <v>341</v>
       </c>
       <c r="B359" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C359" t="s">
         <v>178</v>
@@ -12646,18 +12639,18 @@
         <v>11</v>
       </c>
       <c r="F359" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G359" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B360" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C360" t="s">
         <v>280</v>
@@ -12672,15 +12665,15 @@
         <v>258</v>
       </c>
       <c r="G360" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B361" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C361" t="s">
         <v>318</v>
@@ -12695,15 +12688,15 @@
         <v>309</v>
       </c>
       <c r="G361" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="362" spans="1:7">
       <c r="A362" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B362" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C362" t="s">
         <v>280</v>
@@ -12715,10 +12708,10 @@
         <v>11</v>
       </c>
       <c r="F362" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G362" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -12726,7 +12719,7 @@
         <v>316</v>
       </c>
       <c r="B363" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C363" t="s">
         <v>178</v>
@@ -12741,18 +12734,18 @@
         <v>258</v>
       </c>
       <c r="G363" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="364" spans="1:7">
       <c r="A364" t="s">
+        <v>669</v>
+      </c>
+      <c r="B364" t="s">
+        <v>670</v>
+      </c>
+      <c r="C364" t="s">
         <v>671</v>
-      </c>
-      <c r="B364" t="s">
-        <v>672</v>
-      </c>
-      <c r="C364" t="s">
-        <v>673</v>
       </c>
       <c r="D364" t="s">
         <v>10</v>
@@ -12761,18 +12754,18 @@
         <v>27</v>
       </c>
       <c r="F364" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G364" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="365" spans="1:7">
       <c r="A365" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B365" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C365" t="s">
         <v>9</v>
@@ -12784,18 +12777,18 @@
         <v>27</v>
       </c>
       <c r="F365" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G365" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="366" spans="1:7">
       <c r="A366" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B366" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C366" t="s">
         <v>285</v>
@@ -12807,21 +12800,21 @@
         <v>27</v>
       </c>
       <c r="F366" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G366" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" t="s">
+        <v>669</v>
+      </c>
+      <c r="B367" t="s">
+        <v>670</v>
+      </c>
+      <c r="C367" t="s">
         <v>671</v>
-      </c>
-      <c r="B367" t="s">
-        <v>672</v>
-      </c>
-      <c r="C367" t="s">
-        <v>673</v>
       </c>
       <c r="D367" t="s">
         <v>26</v>
@@ -12830,18 +12823,18 @@
         <v>27</v>
       </c>
       <c r="F367" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G367" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B368" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C368" t="s">
         <v>9</v>
@@ -12853,18 +12846,18 @@
         <v>27</v>
       </c>
       <c r="F368" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G368" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B369" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C369" t="s">
         <v>318</v>
@@ -12876,18 +12869,18 @@
         <v>36</v>
       </c>
       <c r="F369" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G369" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B370" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C370" t="s">
         <v>318</v>
@@ -12899,10 +12892,10 @@
         <v>36</v>
       </c>
       <c r="F370" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G370" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="371" spans="1:7">
@@ -12910,7 +12903,7 @@
         <v>269</v>
       </c>
       <c r="B371" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C371" t="s">
         <v>271</v>
@@ -12925,7 +12918,7 @@
         <v>258</v>
       </c>
       <c r="G371" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -12933,7 +12926,7 @@
         <v>272</v>
       </c>
       <c r="B372" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C372" t="s">
         <v>271</v>
@@ -12948,15 +12941,15 @@
         <v>274</v>
       </c>
       <c r="G372" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B373" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C373" t="s">
         <v>318</v>
@@ -12971,15 +12964,15 @@
         <v>258</v>
       </c>
       <c r="G373" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B374" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C374" t="s">
         <v>308</v>
@@ -12991,10 +12984,10 @@
         <v>47</v>
       </c>
       <c r="F374" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G374" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -13002,10 +12995,10 @@
         <v>275</v>
       </c>
       <c r="B375" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C375" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D375" t="s">
         <v>10</v>
@@ -13014,18 +13007,18 @@
         <v>54</v>
       </c>
       <c r="F375" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G375" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B376" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C376" t="s">
         <v>251</v>
@@ -13037,18 +13030,18 @@
         <v>54</v>
       </c>
       <c r="F376" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G376" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B377" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C377" t="s">
         <v>17</v>
@@ -13060,10 +13053,10 @@
         <v>54</v>
       </c>
       <c r="F377" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G377" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -13071,7 +13064,7 @@
         <v>327</v>
       </c>
       <c r="B378" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C378" t="s">
         <v>178</v>
@@ -13083,18 +13076,18 @@
         <v>54</v>
       </c>
       <c r="F378" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G378" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B379" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C379" t="s">
         <v>280</v>
@@ -13106,10 +13099,10 @@
         <v>54</v>
       </c>
       <c r="F379" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G379" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -13117,7 +13110,7 @@
         <v>327</v>
       </c>
       <c r="B380" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C380" t="s">
         <v>178</v>
@@ -13129,18 +13122,18 @@
         <v>54</v>
       </c>
       <c r="F380" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G380" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B381" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C381" t="s">
         <v>280</v>
@@ -13152,18 +13145,18 @@
         <v>54</v>
       </c>
       <c r="F381" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G381" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B382" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C382" t="s">
         <v>17</v>
@@ -13178,7 +13171,7 @@
         <v>258</v>
       </c>
       <c r="G382" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -13186,10 +13179,10 @@
         <v>275</v>
       </c>
       <c r="B383" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C383" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D383" t="s">
         <v>26</v>
@@ -13198,18 +13191,18 @@
         <v>54</v>
       </c>
       <c r="F383" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G383" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B384" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C384" t="s">
         <v>251</v>
@@ -13221,18 +13214,18 @@
         <v>54</v>
       </c>
       <c r="F384" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G384" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B385" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C385" t="s">
         <v>17</v>
@@ -13244,18 +13237,18 @@
         <v>54</v>
       </c>
       <c r="F385" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G385" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B386" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C386" t="s">
         <v>285</v>
@@ -13270,15 +13263,15 @@
         <v>258</v>
       </c>
       <c r="G386" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B387" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C387" t="s">
         <v>280</v>
@@ -13293,7 +13286,7 @@
         <v>258</v>
       </c>
       <c r="G387" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -13301,7 +13294,7 @@
         <v>341</v>
       </c>
       <c r="B388" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C388" t="s">
         <v>178</v>
@@ -13316,7 +13309,7 @@
         <v>258</v>
       </c>
       <c r="G388" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="389" spans="1:7">
@@ -13324,7 +13317,7 @@
         <v>316</v>
       </c>
       <c r="B389" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C389" t="s">
         <v>178</v>
@@ -13339,15 +13332,15 @@
         <v>258</v>
       </c>
       <c r="G389" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B390" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C390" t="s">
         <v>22</v>
@@ -13359,18 +13352,18 @@
         <v>27</v>
       </c>
       <c r="F390" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="G390" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B391" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C391" t="s">
         <v>22</v>
@@ -13382,10 +13375,10 @@
         <v>27</v>
       </c>
       <c r="F391" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="G391" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -13393,7 +13386,7 @@
         <v>272</v>
       </c>
       <c r="B392" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C392" t="s">
         <v>271</v>
@@ -13408,15 +13401,15 @@
         <v>258</v>
       </c>
       <c r="G392" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="393" spans="1:7">
       <c r="A393" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B393" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C393" t="s">
         <v>271</v>
@@ -13431,15 +13424,15 @@
         <v>258</v>
       </c>
       <c r="G393" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="394" spans="1:7">
       <c r="A394" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B394" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C394" t="s">
         <v>318</v>
@@ -13454,15 +13447,15 @@
         <v>258</v>
       </c>
       <c r="G394" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="395" spans="1:7">
       <c r="A395" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B395" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C395" t="s">
         <v>318</v>
@@ -13477,15 +13470,15 @@
         <v>258</v>
       </c>
       <c r="G395" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="396" spans="1:7">
       <c r="A396" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B396" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C396" t="s">
         <v>318</v>
@@ -13497,18 +13490,18 @@
         <v>47</v>
       </c>
       <c r="F396" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G396" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B397" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C397" t="s">
         <v>280</v>
@@ -13520,18 +13513,18 @@
         <v>47</v>
       </c>
       <c r="F397" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G397" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="398" spans="1:7">
       <c r="A398" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B398" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C398" t="s">
         <v>318</v>
@@ -13543,18 +13536,18 @@
         <v>47</v>
       </c>
       <c r="F398" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G398" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="399" spans="1:7">
       <c r="A399" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B399" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C399" t="s">
         <v>280</v>
@@ -13566,18 +13559,18 @@
         <v>47</v>
       </c>
       <c r="F399" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G399" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="400" spans="1:7">
       <c r="A400" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B400" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C400" t="s">
         <v>308</v>
@@ -13589,18 +13582,18 @@
         <v>47</v>
       </c>
       <c r="F400" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G400" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="401" spans="1:7">
       <c r="A401" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B401" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C401" t="s">
         <v>280</v>
@@ -13615,15 +13608,15 @@
         <v>258</v>
       </c>
       <c r="G401" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="402" spans="1:7">
       <c r="A402" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B402" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C402" t="s">
         <v>313</v>
@@ -13635,18 +13628,18 @@
         <v>54</v>
       </c>
       <c r="F402" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="G402" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="403" spans="1:7">
       <c r="A403" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B403" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C403" t="s">
         <v>178</v>
@@ -13658,18 +13651,18 @@
         <v>54</v>
       </c>
       <c r="F403" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G403" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="404" spans="1:7">
       <c r="A404" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B404" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C404" t="s">
         <v>17</v>
@@ -13681,18 +13674,18 @@
         <v>54</v>
       </c>
       <c r="F404" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G404" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="405" spans="1:7">
       <c r="A405" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B405" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C405" t="s">
         <v>17</v>
@@ -13704,18 +13697,18 @@
         <v>54</v>
       </c>
       <c r="F405" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G405" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="406" spans="1:7">
       <c r="A406" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B406" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C406" t="s">
         <v>17</v>
@@ -13730,15 +13723,15 @@
         <v>258</v>
       </c>
       <c r="G406" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="407" spans="1:7">
       <c r="A407" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B407" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C407" t="s">
         <v>313</v>
@@ -13750,18 +13743,18 @@
         <v>54</v>
       </c>
       <c r="F407" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="G407" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="408" spans="1:7">
       <c r="A408" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B408" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C408" t="s">
         <v>178</v>
@@ -13773,18 +13766,18 @@
         <v>54</v>
       </c>
       <c r="F408" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G408" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="409" spans="1:7">
       <c r="A409" t="s">
+        <v>726</v>
+      </c>
+      <c r="B409" t="s">
         <v>728</v>
-      </c>
-      <c r="B409" t="s">
-        <v>730</v>
       </c>
       <c r="C409" t="s">
         <v>17</v>
@@ -13796,18 +13789,18 @@
         <v>11</v>
       </c>
       <c r="F409" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G409" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="410" spans="1:7">
       <c r="A410" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B410" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C410" t="s">
         <v>9</v>
@@ -13819,18 +13812,18 @@
         <v>11</v>
       </c>
       <c r="F410" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G410" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="411" spans="1:7">
       <c r="A411" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B411" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C411" t="s">
         <v>17</v>
@@ -13842,18 +13835,18 @@
         <v>11</v>
       </c>
       <c r="F411" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G411" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="412" spans="1:7">
       <c r="A412" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B412" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C412" t="s">
         <v>9</v>
@@ -13865,18 +13858,18 @@
         <v>11</v>
       </c>
       <c r="F412" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="G412" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="413" spans="1:7">
       <c r="A413" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B413" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C413" t="s">
         <v>17</v>
@@ -13888,10 +13881,10 @@
         <v>11</v>
       </c>
       <c r="F413" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G413" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="414" spans="1:7">
@@ -13899,7 +13892,7 @@
         <v>269</v>
       </c>
       <c r="B414" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C414" t="s">
         <v>207</v>
@@ -13911,18 +13904,18 @@
         <v>11</v>
       </c>
       <c r="F414" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G414" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="415" spans="1:7">
       <c r="A415" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B415" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C415" t="s">
         <v>338</v>
@@ -13934,18 +13927,18 @@
         <v>11</v>
       </c>
       <c r="F415" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G415" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="416" spans="1:7">
       <c r="A416" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B416" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C416" t="s">
         <v>197</v>
@@ -13957,21 +13950,21 @@
         <v>36</v>
       </c>
       <c r="F416" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G416" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="417" spans="1:7">
       <c r="A417" t="s">
+        <v>746</v>
+      </c>
+      <c r="B417" t="s">
+        <v>747</v>
+      </c>
+      <c r="C417" t="s">
         <v>748</v>
-      </c>
-      <c r="B417" t="s">
-        <v>749</v>
-      </c>
-      <c r="C417" t="s">
-        <v>750</v>
       </c>
       <c r="D417" t="s">
         <v>18</v>
@@ -13980,21 +13973,21 @@
         <v>36</v>
       </c>
       <c r="F417" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G417" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
+        <v>746</v>
+      </c>
+      <c r="B418" t="s">
+        <v>747</v>
+      </c>
+      <c r="C418" t="s">
         <v>748</v>
-      </c>
-      <c r="B418" t="s">
-        <v>749</v>
-      </c>
-      <c r="C418" t="s">
-        <v>750</v>
       </c>
       <c r="D418" t="s">
         <v>23</v>
@@ -14003,18 +13996,18 @@
         <v>36</v>
       </c>
       <c r="F418" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G418" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="419" spans="1:7">
       <c r="A419" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B419" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C419" t="s">
         <v>313</v>
@@ -14026,21 +14019,21 @@
         <v>36</v>
       </c>
       <c r="F419" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G419" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="420" spans="1:7">
       <c r="A420" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B420" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C420" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D420" t="s">
         <v>25</v>
@@ -14049,18 +14042,18 @@
         <v>36</v>
       </c>
       <c r="F420" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G420" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="421" spans="1:7">
       <c r="A421" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B421" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C421" t="s">
         <v>313</v>
@@ -14072,21 +14065,21 @@
         <v>36</v>
       </c>
       <c r="F421" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G421" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="422" spans="1:7">
       <c r="A422" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B422" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C422" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D422" t="s">
         <v>26</v>
@@ -14095,10 +14088,10 @@
         <v>36</v>
       </c>
       <c r="F422" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G422" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -14106,7 +14099,7 @@
         <v>269</v>
       </c>
       <c r="B423" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C423" t="s">
         <v>207</v>
@@ -14118,10 +14111,10 @@
         <v>47</v>
       </c>
       <c r="F423" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G423" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="424" spans="1:7">
@@ -14129,10 +14122,10 @@
         <v>341</v>
       </c>
       <c r="B424" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C424" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D424" t="s">
         <v>18</v>
@@ -14141,18 +14134,18 @@
         <v>47</v>
       </c>
       <c r="F424" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G424" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="425" spans="1:7">
       <c r="A425" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B425" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C425" t="s">
         <v>197</v>
@@ -14164,18 +14157,18 @@
         <v>47</v>
       </c>
       <c r="F425" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G425" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="426" spans="1:7">
       <c r="A426" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B426" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C426" t="s">
         <v>318</v>
@@ -14187,18 +14180,18 @@
         <v>47</v>
       </c>
       <c r="F426" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G426" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="427" spans="1:7">
       <c r="A427" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B427" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C427" t="s">
         <v>318</v>
@@ -14210,10 +14203,10 @@
         <v>47</v>
       </c>
       <c r="F427" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G427" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="428" spans="1:7">
@@ -14221,10 +14214,10 @@
         <v>316</v>
       </c>
       <c r="B428" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C428" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D428" t="s">
         <v>10</v>
@@ -14233,18 +14226,18 @@
         <v>54</v>
       </c>
       <c r="F428" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G428" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="429" spans="1:7">
       <c r="A429" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B429" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C429" t="s">
         <v>556</v>
@@ -14256,21 +14249,21 @@
         <v>54</v>
       </c>
       <c r="F429" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G429" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="430" spans="1:7">
       <c r="A430" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B430" t="s">
+        <v>760</v>
+      </c>
+      <c r="C430" t="s">
         <v>762</v>
-      </c>
-      <c r="C430" t="s">
-        <v>764</v>
       </c>
       <c r="D430" t="s">
         <v>18</v>
@@ -14279,18 +14272,18 @@
         <v>54</v>
       </c>
       <c r="F430" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G430" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="431" spans="1:7">
       <c r="A431" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B431" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C431" t="s">
         <v>556</v>
@@ -14302,21 +14295,21 @@
         <v>54</v>
       </c>
       <c r="F431" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G431" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="432" spans="1:7">
       <c r="A432" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B432" t="s">
+        <v>760</v>
+      </c>
+      <c r="C432" t="s">
         <v>762</v>
-      </c>
-      <c r="C432" t="s">
-        <v>764</v>
       </c>
       <c r="D432" t="s">
         <v>23</v>
@@ -14325,18 +14318,18 @@
         <v>54</v>
       </c>
       <c r="F432" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G432" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="433" spans="1:7">
       <c r="A433" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B433" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C433" t="s">
         <v>566</v>
@@ -14348,18 +14341,18 @@
         <v>54</v>
       </c>
       <c r="F433" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G433" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="434" spans="1:7">
       <c r="A434" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B434" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C434" t="s">
         <v>285</v>
@@ -14374,15 +14367,15 @@
         <v>258</v>
       </c>
       <c r="G434" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="435" spans="1:7">
       <c r="A435" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B435" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C435" t="s">
         <v>280</v>
@@ -14397,15 +14390,15 @@
         <v>258</v>
       </c>
       <c r="G435" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="436" spans="1:7">
       <c r="A436" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B436" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C436" t="s">
         <v>280</v>
@@ -14420,7 +14413,7 @@
         <v>258</v>
       </c>
       <c r="G436" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -14428,10 +14421,10 @@
         <v>316</v>
       </c>
       <c r="B437" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C437" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D437" t="s">
         <v>25</v>
@@ -14440,10 +14433,10 @@
         <v>11</v>
       </c>
       <c r="F437" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G437" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -14451,10 +14444,10 @@
         <v>341</v>
       </c>
       <c r="B438" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C438" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D438" t="s">
         <v>26</v>
@@ -14463,18 +14456,18 @@
         <v>11</v>
       </c>
       <c r="F438" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G438" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="439" spans="1:7">
       <c r="A439" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B439" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C439" t="s">
         <v>285</v>
@@ -14486,18 +14479,18 @@
         <v>27</v>
       </c>
       <c r="F439" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G439" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="440" spans="1:7">
       <c r="A440" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B440" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C440" t="s">
         <v>285</v>
@@ -14509,21 +14502,21 @@
         <v>27</v>
       </c>
       <c r="F440" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G440" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="441" spans="1:7">
       <c r="A441" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B441" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C441" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D441" t="s">
         <v>10</v>
@@ -14532,21 +14525,21 @@
         <v>36</v>
       </c>
       <c r="F441" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G441" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="442" spans="1:7">
       <c r="A442" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B442" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C442" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D442" t="s">
         <v>18</v>
@@ -14555,21 +14548,21 @@
         <v>36</v>
       </c>
       <c r="F442" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G442" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="443" spans="1:7">
       <c r="A443" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B443" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C443" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D443" t="s">
         <v>23</v>
@@ -14578,21 +14571,21 @@
         <v>36</v>
       </c>
       <c r="F443" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G443" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="444" spans="1:7">
       <c r="A444" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B444" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C444" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D444" t="s">
         <v>10</v>
@@ -14601,21 +14594,21 @@
         <v>47</v>
       </c>
       <c r="F444" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G444" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="445" spans="1:7">
       <c r="A445" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B445" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C445" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D445" t="s">
         <v>10</v>
@@ -14624,18 +14617,18 @@
         <v>47</v>
       </c>
       <c r="F445" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G445" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="446" spans="1:7">
       <c r="A446" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B446" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C446" t="s">
         <v>556</v>
@@ -14647,21 +14640,21 @@
         <v>47</v>
       </c>
       <c r="F446" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G446" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="447" spans="1:7">
       <c r="A447" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B447" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C447" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D447" t="s">
         <v>18</v>
@@ -14670,18 +14663,18 @@
         <v>47</v>
       </c>
       <c r="F447" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G447" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="448" spans="1:7">
       <c r="A448" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B448" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C448" t="s">
         <v>556</v>
@@ -14693,21 +14686,21 @@
         <v>47</v>
       </c>
       <c r="F448" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G448" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="449" spans="1:7">
       <c r="A449" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B449" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C449" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D449" t="s">
         <v>23</v>
@@ -14716,18 +14709,18 @@
         <v>47</v>
       </c>
       <c r="F449" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G449" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="450" spans="1:7">
       <c r="A450" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B450" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C450" t="s">
         <v>308</v>
@@ -14739,21 +14732,21 @@
         <v>47</v>
       </c>
       <c r="F450" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G450" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="451" spans="1:7">
       <c r="A451" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B451" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C451" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D451" t="s">
         <v>26</v>
@@ -14762,21 +14755,21 @@
         <v>47</v>
       </c>
       <c r="F451" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G451" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="452" spans="1:7">
       <c r="A452" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B452" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C452" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D452" t="s">
         <v>26</v>
@@ -14785,10 +14778,10 @@
         <v>47</v>
       </c>
       <c r="F452" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G452" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="453" spans="1:7">
@@ -14796,7 +14789,7 @@
         <v>269</v>
       </c>
       <c r="B453" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C453" t="s">
         <v>271</v>
@@ -14808,10 +14801,10 @@
         <v>54</v>
       </c>
       <c r="F453" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G453" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="454" spans="1:7">
@@ -14819,7 +14812,7 @@
         <v>272</v>
       </c>
       <c r="B454" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C454" t="s">
         <v>271</v>
@@ -14834,18 +14827,18 @@
         <v>309</v>
       </c>
       <c r="G454" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="455" spans="1:7">
       <c r="A455" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B455" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C455" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D455" t="s">
         <v>25</v>
@@ -14854,21 +14847,21 @@
         <v>54</v>
       </c>
       <c r="F455" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G455" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="456" spans="1:7">
       <c r="A456" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B456" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C456" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D456" t="s">
         <v>26</v>
@@ -14877,18 +14870,18 @@
         <v>54</v>
       </c>
       <c r="F456" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G456" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="457" spans="1:7">
       <c r="A457" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B457" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C457" t="s">
         <v>227</v>
@@ -14903,18 +14896,18 @@
         <v>19</v>
       </c>
       <c r="G457" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="458" spans="1:7">
       <c r="A458" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B458" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C458" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D458" t="s">
         <v>18</v>
@@ -14923,21 +14916,21 @@
         <v>11</v>
       </c>
       <c r="F458" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G458" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="459" spans="1:7">
       <c r="A459" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B459" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C459" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D459" t="s">
         <v>18</v>
@@ -14946,21 +14939,21 @@
         <v>11</v>
       </c>
       <c r="F459" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="G459" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="460" spans="1:7">
       <c r="A460" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B460" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C460" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D460" t="s">
         <v>23</v>
@@ -14969,21 +14962,21 @@
         <v>11</v>
       </c>
       <c r="F460" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G460" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="461" spans="1:7">
       <c r="A461" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B461" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C461" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D461" t="s">
         <v>23</v>
@@ -14992,21 +14985,21 @@
         <v>11</v>
       </c>
       <c r="F461" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="G461" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="462" spans="1:7">
       <c r="A462" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B462" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C462" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D462" t="s">
         <v>25</v>
@@ -15015,18 +15008,18 @@
         <v>11</v>
       </c>
       <c r="F462" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G462" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B463" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C463" t="s">
         <v>227</v>
@@ -15041,15 +15034,15 @@
         <v>19</v>
       </c>
       <c r="G463" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="464" spans="1:7">
       <c r="A464" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B464" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C464" t="s">
         <v>285</v>
@@ -15061,18 +15054,18 @@
         <v>27</v>
       </c>
       <c r="F464" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="G464" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="465" spans="1:7">
       <c r="A465" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B465" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C465" t="s">
         <v>285</v>
@@ -15084,18 +15077,18 @@
         <v>27</v>
       </c>
       <c r="F465" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G465" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="466" spans="1:7">
       <c r="A466" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B466" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C466" t="s">
         <v>285</v>
@@ -15107,21 +15100,21 @@
         <v>27</v>
       </c>
       <c r="F466" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="G466" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="467" spans="1:7">
       <c r="A467" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B467" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C467" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D467" t="s">
         <v>10</v>
@@ -15130,18 +15123,18 @@
         <v>36</v>
       </c>
       <c r="F467" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G467" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="468" spans="1:7">
       <c r="A468" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B468" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C468" t="s">
         <v>556</v>
@@ -15153,18 +15146,18 @@
         <v>36</v>
       </c>
       <c r="F468" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G468" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="469" spans="1:7">
       <c r="A469" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B469" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C469" t="s">
         <v>556</v>
@@ -15176,18 +15169,18 @@
         <v>36</v>
       </c>
       <c r="F469" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G469" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="470" spans="1:7">
       <c r="A470" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B470" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C470" t="s">
         <v>280</v>
@@ -15199,21 +15192,21 @@
         <v>36</v>
       </c>
       <c r="F470" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="G470" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="471" spans="1:7">
       <c r="A471" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B471" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C471" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D471" t="s">
         <v>25</v>
@@ -15222,18 +15215,18 @@
         <v>36</v>
       </c>
       <c r="F471" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G471" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="472" spans="1:7">
       <c r="A472" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B472" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C472" t="s">
         <v>280</v>
@@ -15245,21 +15238,21 @@
         <v>36</v>
       </c>
       <c r="F472" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="G472" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="473" spans="1:7">
       <c r="A473" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B473" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C473" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D473" t="s">
         <v>26</v>
@@ -15268,21 +15261,21 @@
         <v>36</v>
       </c>
       <c r="F473" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G473" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="474" spans="1:7">
       <c r="A474" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B474" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C474" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D474" t="s">
         <v>10</v>
@@ -15291,18 +15284,18 @@
         <v>47</v>
       </c>
       <c r="F474" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G474" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="475" spans="1:7">
       <c r="A475" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B475" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C475" t="s">
         <v>308</v>
@@ -15314,21 +15307,21 @@
         <v>47</v>
       </c>
       <c r="F475" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G475" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="476" spans="1:7">
       <c r="A476" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B476" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C476" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D476" t="s">
         <v>26</v>
@@ -15337,18 +15330,18 @@
         <v>47</v>
       </c>
       <c r="F476" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G476" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="477" spans="1:7">
       <c r="A477" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B477" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C477" t="s">
         <v>271</v>
@@ -15360,21 +15353,21 @@
         <v>54</v>
       </c>
       <c r="F477" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G477" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="478" spans="1:7">
       <c r="A478" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B478" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C478" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D478" t="s">
         <v>25</v>
@@ -15383,18 +15376,18 @@
         <v>54</v>
       </c>
       <c r="F478" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G478" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="479" spans="1:7">
       <c r="A479" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B479" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C479" t="s">
         <v>530</v>
@@ -15406,18 +15399,18 @@
         <v>11</v>
       </c>
       <c r="F479" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G479" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="480" spans="1:7">
       <c r="A480" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B480" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C480" t="s">
         <v>212</v>
@@ -15429,18 +15422,18 @@
         <v>11</v>
       </c>
       <c r="F480" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G480" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="481" spans="1:7">
       <c r="A481" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B481" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C481" t="s">
         <v>395</v>
@@ -15452,21 +15445,21 @@
         <v>11</v>
       </c>
       <c r="F481" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="G481" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="482" spans="1:7">
       <c r="A482" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B482" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C482" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D482" t="s">
         <v>18</v>
@@ -15475,18 +15468,18 @@
         <v>11</v>
       </c>
       <c r="F482" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G482" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="483" spans="1:7">
       <c r="A483" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B483" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C483" t="s">
         <v>212</v>
@@ -15498,18 +15491,18 @@
         <v>11</v>
       </c>
       <c r="F483" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G483" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="484" spans="1:7">
       <c r="A484" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B484" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C484" t="s">
         <v>395</v>
@@ -15521,21 +15514,21 @@
         <v>11</v>
       </c>
       <c r="F484" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G484" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="485" spans="1:7">
       <c r="A485" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B485" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C485" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D485" t="s">
         <v>23</v>
@@ -15544,21 +15537,21 @@
         <v>11</v>
       </c>
       <c r="F485" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G485" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="486" spans="1:7">
       <c r="A486" t="s">
+        <v>834</v>
+      </c>
+      <c r="B486" t="s">
+        <v>835</v>
+      </c>
+      <c r="C486" t="s">
         <v>836</v>
-      </c>
-      <c r="B486" t="s">
-        <v>837</v>
-      </c>
-      <c r="C486" t="s">
-        <v>838</v>
       </c>
       <c r="D486" t="s">
         <v>25</v>
@@ -15567,18 +15560,18 @@
         <v>11</v>
       </c>
       <c r="F486" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G486" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="487" spans="1:7">
       <c r="A487" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B487" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C487" t="s">
         <v>207</v>
@@ -15590,21 +15583,21 @@
         <v>11</v>
       </c>
       <c r="F487" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G487" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="488" spans="1:7">
       <c r="A488" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B488" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C488" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D488" t="s">
         <v>26</v>
@@ -15616,15 +15609,15 @@
         <v>22</v>
       </c>
       <c r="G488" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="489" spans="1:7">
       <c r="A489" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B489" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C489" t="s">
         <v>349</v>
@@ -15639,15 +15632,15 @@
         <v>22</v>
       </c>
       <c r="G489" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="490" spans="1:7">
       <c r="A490" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B490" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C490" t="s">
         <v>236</v>
@@ -15659,18 +15652,18 @@
         <v>36</v>
       </c>
       <c r="F490" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G490" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="491" spans="1:7">
       <c r="A491" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B491" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C491" t="s">
         <v>236</v>
@@ -15682,18 +15675,18 @@
         <v>36</v>
       </c>
       <c r="F491" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G491" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="492" spans="1:7">
       <c r="A492" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B492" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C492" t="s">
         <v>236</v>
@@ -15705,18 +15698,18 @@
         <v>36</v>
       </c>
       <c r="F492" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G492" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="493" spans="1:7">
       <c r="A493" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B493" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C493" t="s">
         <v>349</v>
@@ -15731,15 +15724,15 @@
         <v>22</v>
       </c>
       <c r="G493" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="494" spans="1:7">
       <c r="A494" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B494" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C494" t="s">
         <v>236</v>
@@ -15751,18 +15744,18 @@
         <v>36</v>
       </c>
       <c r="F494" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G494" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="495" spans="1:7">
       <c r="A495" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B495" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C495" t="s">
         <v>349</v>
@@ -15774,21 +15767,21 @@
         <v>47</v>
       </c>
       <c r="F495" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G495" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="496" spans="1:7">
       <c r="A496" t="s">
+        <v>852</v>
+      </c>
+      <c r="B496" t="s">
+        <v>853</v>
+      </c>
+      <c r="C496" t="s">
         <v>854</v>
-      </c>
-      <c r="B496" t="s">
-        <v>855</v>
-      </c>
-      <c r="C496" t="s">
-        <v>856</v>
       </c>
       <c r="D496" t="s">
         <v>18</v>
@@ -15797,21 +15790,21 @@
         <v>47</v>
       </c>
       <c r="F496" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G496" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="497" spans="1:7">
       <c r="A497" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B497" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C497" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D497" t="s">
         <v>23</v>
@@ -15820,21 +15813,21 @@
         <v>47</v>
       </c>
       <c r="F497" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G497" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="498" spans="1:7">
       <c r="A498" t="s">
+        <v>834</v>
+      </c>
+      <c r="B498" t="s">
+        <v>835</v>
+      </c>
+      <c r="C498" t="s">
         <v>836</v>
-      </c>
-      <c r="B498" t="s">
-        <v>837</v>
-      </c>
-      <c r="C498" t="s">
-        <v>838</v>
       </c>
       <c r="D498" t="s">
         <v>25</v>
@@ -15843,18 +15836,18 @@
         <v>47</v>
       </c>
       <c r="F498" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G498" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="499" spans="1:7">
       <c r="A499" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B499" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C499" t="s">
         <v>294</v>
@@ -15869,18 +15862,18 @@
         <v>22</v>
       </c>
       <c r="G499" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="500" spans="1:7">
       <c r="A500" t="s">
+        <v>859</v>
+      </c>
+      <c r="B500" t="s">
+        <v>860</v>
+      </c>
+      <c r="C500" t="s">
         <v>861</v>
-      </c>
-      <c r="B500" t="s">
-        <v>862</v>
-      </c>
-      <c r="C500" t="s">
-        <v>863</v>
       </c>
       <c r="D500" t="s">
         <v>18</v>
@@ -15889,21 +15882,21 @@
         <v>54</v>
       </c>
       <c r="F500" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G500" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="501" spans="1:7">
       <c r="A501" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B501" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C501" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D501" t="s">
         <v>23</v>
@@ -15912,21 +15905,21 @@
         <v>54</v>
       </c>
       <c r="F501" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G501" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="502" spans="1:7">
       <c r="A502" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B502" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C502" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D502" t="s">
         <v>25</v>
@@ -15938,15 +15931,15 @@
         <v>22</v>
       </c>
       <c r="G502" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="503" spans="1:7">
       <c r="A503" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B503" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C503" t="s">
         <v>294</v>
@@ -15958,21 +15951,21 @@
         <v>54</v>
       </c>
       <c r="F503" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G503" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="504" spans="1:7">
       <c r="A504" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B504" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C504" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D504" t="s">
         <v>26</v>
@@ -15984,15 +15977,15 @@
         <v>22</v>
       </c>
       <c r="G504" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="505" spans="1:7">
       <c r="A505" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B505" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C505" t="s">
         <v>294</v>
@@ -16007,15 +16000,15 @@
         <v>22</v>
       </c>
       <c r="G505" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="506" spans="1:7">
       <c r="A506" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B506" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C506" t="s">
         <v>349</v>
@@ -16030,15 +16023,15 @@
         <v>365</v>
       </c>
       <c r="G506" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="507" spans="1:7">
       <c r="A507" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B507" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C507" t="s">
         <v>364</v>
@@ -16050,18 +16043,18 @@
         <v>11</v>
       </c>
       <c r="F507" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G507" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="508" spans="1:7">
       <c r="A508" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B508" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C508" t="s">
         <v>392</v>
@@ -16073,18 +16066,18 @@
         <v>11</v>
       </c>
       <c r="F508" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G508" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="509" spans="1:7">
       <c r="A509" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B509" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C509" t="s">
         <v>364</v>
@@ -16096,18 +16089,18 @@
         <v>11</v>
       </c>
       <c r="F509" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G509" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="510" spans="1:7">
       <c r="A510" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B510" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C510" t="s">
         <v>392</v>
@@ -16119,18 +16112,18 @@
         <v>11</v>
       </c>
       <c r="F510" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G510" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="511" spans="1:7">
       <c r="A511" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B511" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C511" t="s">
         <v>285</v>
@@ -16145,15 +16138,15 @@
         <v>365</v>
       </c>
       <c r="G511" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="512" spans="1:7">
       <c r="A512" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B512" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C512" t="s">
         <v>349</v>
@@ -16168,18 +16161,18 @@
         <v>365</v>
       </c>
       <c r="G512" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="513" spans="1:7">
       <c r="A513" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B513" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C513" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D513" t="s">
         <v>26</v>
@@ -16191,7 +16184,7 @@
         <v>22</v>
       </c>
       <c r="G513" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -16199,7 +16192,7 @@
         <v>401</v>
       </c>
       <c r="B514" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C514" t="s">
         <v>353</v>
@@ -16214,15 +16207,15 @@
         <v>365</v>
       </c>
       <c r="G514" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="515" spans="1:7">
       <c r="A515" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B515" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C515" t="s">
         <v>395</v>
@@ -16234,18 +16227,18 @@
         <v>36</v>
       </c>
       <c r="F515" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G515" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="516" spans="1:7">
       <c r="A516" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B516" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C516" t="s">
         <v>364</v>
@@ -16257,18 +16250,18 @@
         <v>36</v>
       </c>
       <c r="F516" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G516" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="517" spans="1:7">
       <c r="A517" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B517" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C517" t="s">
         <v>395</v>
@@ -16280,18 +16273,18 @@
         <v>36</v>
       </c>
       <c r="F517" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G517" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="518" spans="1:7">
       <c r="A518" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B518" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C518" t="s">
         <v>364</v>
@@ -16303,18 +16296,18 @@
         <v>36</v>
       </c>
       <c r="F518" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G518" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="519" spans="1:7">
       <c r="A519" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B519" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C519" t="s">
         <v>392</v>
@@ -16329,7 +16322,7 @@
         <v>365</v>
       </c>
       <c r="G519" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -16337,7 +16330,7 @@
         <v>399</v>
       </c>
       <c r="B520" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C520" t="s">
         <v>353</v>
@@ -16352,15 +16345,15 @@
         <v>365</v>
       </c>
       <c r="G520" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="521" spans="1:7">
       <c r="A521" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B521" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C521" t="s">
         <v>412</v>
@@ -16375,15 +16368,15 @@
         <v>365</v>
       </c>
       <c r="G521" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="522" spans="1:7">
       <c r="A522" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B522" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C522" t="s">
         <v>395</v>
@@ -16395,18 +16388,18 @@
         <v>47</v>
       </c>
       <c r="F522" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G522" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="523" spans="1:7">
       <c r="A523" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B523" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C523" t="s">
         <v>395</v>
@@ -16418,18 +16411,18 @@
         <v>47</v>
       </c>
       <c r="F523" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G523" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="524" spans="1:7">
       <c r="A524" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B524" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C524" t="s">
         <v>308</v>
@@ -16444,15 +16437,15 @@
         <v>365</v>
       </c>
       <c r="G524" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="525" spans="1:7">
       <c r="A525" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B525" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C525" t="s">
         <v>530</v>
@@ -16467,15 +16460,15 @@
         <v>365</v>
       </c>
       <c r="G525" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="526" spans="1:7">
       <c r="A526" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B526" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C526" t="s">
         <v>308</v>
@@ -16490,7 +16483,7 @@
         <v>365</v>
       </c>
       <c r="G526" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="527" spans="1:7">
@@ -16498,7 +16491,7 @@
         <v>360</v>
       </c>
       <c r="B527" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C527" t="s">
         <v>262</v>
@@ -16510,18 +16503,18 @@
         <v>11</v>
       </c>
       <c r="F527" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G527" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="528" spans="1:7">
       <c r="A528" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B528" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C528" t="s">
         <v>338</v>
@@ -16533,18 +16526,18 @@
         <v>11</v>
       </c>
       <c r="F528" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G528" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="529" spans="1:7">
       <c r="A529" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B529" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C529" t="s">
         <v>338</v>
@@ -16556,18 +16549,18 @@
         <v>11</v>
       </c>
       <c r="F529" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G529" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="530" spans="1:7">
       <c r="A530" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B530" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C530" t="s">
         <v>285</v>
@@ -16579,21 +16572,21 @@
         <v>11</v>
       </c>
       <c r="F530" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G530" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="531" spans="1:7">
       <c r="A531" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B531" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C531" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D531" t="s">
         <v>26</v>
@@ -16605,7 +16598,7 @@
         <v>22</v>
       </c>
       <c r="G531" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="532" spans="1:7">
@@ -16613,7 +16606,7 @@
         <v>339</v>
       </c>
       <c r="B532" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C532" t="s">
         <v>262</v>
@@ -16625,18 +16618,18 @@
         <v>36</v>
       </c>
       <c r="F532" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G532" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="533" spans="1:7">
       <c r="A533" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B533" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C533" t="s">
         <v>375</v>
@@ -16648,18 +16641,18 @@
         <v>36</v>
       </c>
       <c r="F533" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G533" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="534" spans="1:7">
       <c r="A534" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B534" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C534" t="s">
         <v>375</v>
@@ -16671,18 +16664,18 @@
         <v>36</v>
       </c>
       <c r="F534" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G534" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="535" spans="1:7">
       <c r="A535" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B535" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C535" t="s">
         <v>530</v>
@@ -16694,21 +16687,21 @@
         <v>36</v>
       </c>
       <c r="F535" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G535" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="536" spans="1:7">
       <c r="A536" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B536" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C536" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D536" t="s">
         <v>26</v>
@@ -16717,18 +16710,18 @@
         <v>36</v>
       </c>
       <c r="F536" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G536" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="537" spans="1:7">
       <c r="A537" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B537" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C537" t="s">
         <v>372</v>
@@ -16740,18 +16733,18 @@
         <v>47</v>
       </c>
       <c r="F537" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G537" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="538" spans="1:7">
       <c r="A538" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B538" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C538" t="s">
         <v>353</v>
@@ -16763,18 +16756,18 @@
         <v>47</v>
       </c>
       <c r="F538" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G538" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="539" spans="1:7">
       <c r="A539" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B539" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C539" t="s">
         <v>353</v>
@@ -16786,18 +16779,18 @@
         <v>47</v>
       </c>
       <c r="F539" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G539" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="540" spans="1:7">
       <c r="A540" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B540" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C540" t="s">
         <v>372</v>
@@ -16809,18 +16802,18 @@
         <v>47</v>
       </c>
       <c r="F540" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G540" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="541" spans="1:7">
       <c r="A541" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B541" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C541" t="s">
         <v>262</v>
@@ -16832,18 +16825,18 @@
         <v>54</v>
       </c>
       <c r="F541" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="G541" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="542" spans="1:7">
       <c r="A542" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B542" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C542" t="s">
         <v>384</v>
@@ -16855,21 +16848,21 @@
         <v>54</v>
       </c>
       <c r="F542" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G542" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="543" spans="1:7">
       <c r="A543" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B543" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C543" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D543" t="s">
         <v>18</v>
@@ -16878,18 +16871,18 @@
         <v>54</v>
       </c>
       <c r="F543" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="G543" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="544" spans="1:7">
       <c r="A544" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B544" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C544" t="s">
         <v>384</v>
@@ -16901,21 +16894,21 @@
         <v>54</v>
       </c>
       <c r="F544" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G544" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="545" spans="1:7">
       <c r="A545" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B545" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C545" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D545" t="s">
         <v>23</v>
@@ -16924,18 +16917,18 @@
         <v>54</v>
       </c>
       <c r="F545" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="G545" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="546" spans="1:7">
       <c r="A546" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B546" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C546" t="s">
         <v>262</v>
@@ -16947,21 +16940,21 @@
         <v>54</v>
       </c>
       <c r="F546" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="G546" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="547" spans="1:7">
       <c r="A547" t="s">
+        <v>950</v>
+      </c>
+      <c r="B547" t="s">
+        <v>951</v>
+      </c>
+      <c r="C547" t="s">
         <v>952</v>
-      </c>
-      <c r="B547" t="s">
-        <v>953</v>
-      </c>
-      <c r="C547" t="s">
-        <v>954</v>
       </c>
       <c r="D547" t="s">
         <v>10</v>
@@ -16973,18 +16966,18 @@
         <v>274</v>
       </c>
       <c r="G547" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="548" spans="1:7">
       <c r="A548" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B548" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C548" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D548" t="s">
         <v>18</v>
@@ -16993,21 +16986,21 @@
         <v>11</v>
       </c>
       <c r="F548" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="G548" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="549" spans="1:7">
       <c r="A549" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B549" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C549" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D549" t="s">
         <v>23</v>
@@ -17016,21 +17009,21 @@
         <v>11</v>
       </c>
       <c r="F549" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="G549" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="550" spans="1:7">
       <c r="A550" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B550" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C550" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D550" t="s">
         <v>25</v>
@@ -17042,18 +17035,18 @@
         <v>274</v>
       </c>
       <c r="G550" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="551" spans="1:7">
       <c r="A551" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B551" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C551" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D551" t="s">
         <v>26</v>
@@ -17065,18 +17058,18 @@
         <v>274</v>
       </c>
       <c r="G551" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="552" spans="1:7">
       <c r="A552" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B552" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C552" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D552" t="s">
         <v>26</v>
@@ -17088,15 +17081,15 @@
         <v>274</v>
       </c>
       <c r="G552" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="553" spans="1:7">
       <c r="A553" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B553" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C553" t="s">
         <v>591</v>
@@ -17108,21 +17101,21 @@
         <v>36</v>
       </c>
       <c r="F553" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="G553" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="554" spans="1:7">
       <c r="A554" t="s">
+        <v>967</v>
+      </c>
+      <c r="B554" t="s">
+        <v>968</v>
+      </c>
+      <c r="C554" t="s">
         <v>969</v>
-      </c>
-      <c r="B554" t="s">
-        <v>970</v>
-      </c>
-      <c r="C554" t="s">
-        <v>971</v>
       </c>
       <c r="D554" t="s">
         <v>10</v>
@@ -17131,21 +17124,21 @@
         <v>36</v>
       </c>
       <c r="F554" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="G554" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="555" spans="1:7">
       <c r="A555" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B555" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C555" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D555" t="s">
         <v>18</v>
@@ -17157,18 +17150,18 @@
         <v>274</v>
       </c>
       <c r="G555" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="556" spans="1:7">
       <c r="A556" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B556" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C556" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D556" t="s">
         <v>23</v>
@@ -17180,18 +17173,18 @@
         <v>274</v>
       </c>
       <c r="G556" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="557" spans="1:7">
       <c r="A557" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B557" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C557" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D557" t="s">
         <v>25</v>
@@ -17203,15 +17196,15 @@
         <v>274</v>
       </c>
       <c r="G557" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="558" spans="1:7">
       <c r="A558" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B558" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C558" t="s">
         <v>591</v>
@@ -17223,21 +17216,21 @@
         <v>36</v>
       </c>
       <c r="F558" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="G558" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="559" spans="1:7">
       <c r="A559" t="s">
+        <v>967</v>
+      </c>
+      <c r="B559" t="s">
+        <v>968</v>
+      </c>
+      <c r="C559" t="s">
         <v>969</v>
-      </c>
-      <c r="B559" t="s">
-        <v>970</v>
-      </c>
-      <c r="C559" t="s">
-        <v>971</v>
       </c>
       <c r="D559" t="s">
         <v>26</v>
@@ -17246,18 +17239,18 @@
         <v>36</v>
       </c>
       <c r="F559" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="G559" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="560" spans="1:7">
       <c r="A560" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B560" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C560" t="s">
         <v>349</v>
@@ -17269,21 +17262,21 @@
         <v>47</v>
       </c>
       <c r="F560" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G560" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="561" spans="1:7">
       <c r="A561" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B561" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C561" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D561" t="s">
         <v>18</v>
@@ -17292,21 +17285,21 @@
         <v>47</v>
       </c>
       <c r="F561" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="G561" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="562" spans="1:7">
       <c r="A562" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B562" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C562" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D562" t="s">
         <v>23</v>
@@ -17315,21 +17308,21 @@
         <v>47</v>
       </c>
       <c r="F562" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="G562" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="563" spans="1:7">
       <c r="A563" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B563" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C563" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D563" t="s">
         <v>25</v>
@@ -17341,18 +17334,18 @@
         <v>274</v>
       </c>
       <c r="G563" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="564" spans="1:7">
       <c r="A564" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B564" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C564" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D564" t="s">
         <v>26</v>
@@ -17364,18 +17357,18 @@
         <v>274</v>
       </c>
       <c r="G564" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="565" spans="1:7">
       <c r="A565" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B565" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C565" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D565" t="s">
         <v>18</v>
@@ -17384,21 +17377,21 @@
         <v>54</v>
       </c>
       <c r="F565" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G565" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="566" spans="1:7">
       <c r="A566" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B566" t="s">
+        <v>987</v>
+      </c>
+      <c r="C566" t="s">
         <v>989</v>
-      </c>
-      <c r="C566" t="s">
-        <v>991</v>
       </c>
       <c r="D566" t="s">
         <v>18</v>
@@ -17407,21 +17400,21 @@
         <v>54</v>
       </c>
       <c r="F566" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G566" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="567" spans="1:7">
       <c r="A567" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B567" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C567" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D567" t="s">
         <v>23</v>
@@ -17430,21 +17423,21 @@
         <v>54</v>
       </c>
       <c r="F567" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G567" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="568" spans="1:7">
       <c r="A568" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B568" t="s">
+        <v>987</v>
+      </c>
+      <c r="C568" t="s">
         <v>989</v>
-      </c>
-      <c r="C568" t="s">
-        <v>991</v>
       </c>
       <c r="D568" t="s">
         <v>23</v>
@@ -17453,18 +17446,18 @@
         <v>54</v>
       </c>
       <c r="F568" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G568" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="569" spans="1:7">
       <c r="A569" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B569" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C569" t="s">
         <v>530</v>
@@ -17479,18 +17472,18 @@
         <v>365</v>
       </c>
       <c r="G569" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="570" spans="1:7">
       <c r="A570" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B570" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C570" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D570" t="s">
         <v>26</v>
@@ -17502,15 +17495,15 @@
         <v>274</v>
       </c>
       <c r="G570" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="571" spans="1:7">
       <c r="A571" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B571" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C571" t="s">
         <v>530</v>
@@ -17522,18 +17515,18 @@
         <v>11</v>
       </c>
       <c r="F571" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G571" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="572" spans="1:7">
       <c r="A572" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B572" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C572" t="s">
         <v>384</v>
@@ -17545,18 +17538,18 @@
         <v>11</v>
       </c>
       <c r="F572" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G572" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="573" spans="1:7">
       <c r="A573" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B573" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C573" t="s">
         <v>384</v>
@@ -17568,10 +17561,10 @@
         <v>11</v>
       </c>
       <c r="F573" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G573" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="574" spans="1:7">
@@ -17579,7 +17572,7 @@
         <v>360</v>
       </c>
       <c r="B574" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C574" t="s">
         <v>262</v>
@@ -17591,10 +17584,10 @@
         <v>11</v>
       </c>
       <c r="F574" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G574" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="575" spans="1:7">
@@ -17602,7 +17595,7 @@
         <v>339</v>
       </c>
       <c r="B575" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C575" t="s">
         <v>262</v>
@@ -17614,21 +17607,21 @@
         <v>11</v>
       </c>
       <c r="F575" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G575" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="576" spans="1:7">
       <c r="A576" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B576" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C576" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D576" t="s">
         <v>26</v>
@@ -17640,18 +17633,18 @@
         <v>22</v>
       </c>
       <c r="G576" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="577" spans="1:7">
       <c r="A577" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B577" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C577" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D577" t="s">
         <v>10</v>
@@ -17660,18 +17653,18 @@
         <v>36</v>
       </c>
       <c r="F577" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G577" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="578" spans="1:7">
       <c r="A578" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B578" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C578" t="s">
         <v>280</v>
@@ -17683,18 +17676,18 @@
         <v>36</v>
       </c>
       <c r="F578" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G578" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="579" spans="1:7">
       <c r="A579" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B579" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C579" t="s">
         <v>280</v>
@@ -17706,21 +17699,21 @@
         <v>36</v>
       </c>
       <c r="F579" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G579" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="580" spans="1:7">
       <c r="A580" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B580" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C580" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D580" t="s">
         <v>25</v>
@@ -17729,18 +17722,18 @@
         <v>36</v>
       </c>
       <c r="F580" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="G580" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="581" spans="1:7">
       <c r="A581" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B581" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C581" t="s">
         <v>262</v>
@@ -17752,21 +17745,21 @@
         <v>36</v>
       </c>
       <c r="F581" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="G581" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="582" spans="1:7">
       <c r="A582" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B582" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C582" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D582" t="s">
         <v>26</v>
@@ -17775,18 +17768,18 @@
         <v>36</v>
       </c>
       <c r="F582" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="G582" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="583" spans="1:7">
       <c r="A583" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B583" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C583" t="s">
         <v>262</v>
@@ -17798,18 +17791,18 @@
         <v>36</v>
       </c>
       <c r="F583" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G583" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="584" spans="1:7">
       <c r="A584" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B584" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C584" t="s">
         <v>375</v>
@@ -17821,18 +17814,18 @@
         <v>47</v>
       </c>
       <c r="F584" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G584" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="585" spans="1:7">
       <c r="A585" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B585" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C585" t="s">
         <v>372</v>
@@ -17844,18 +17837,18 @@
         <v>47</v>
       </c>
       <c r="F585" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G585" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="586" spans="1:7">
       <c r="A586" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B586" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C586" t="s">
         <v>372</v>
@@ -17867,18 +17860,18 @@
         <v>47</v>
       </c>
       <c r="F586" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G586" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="587" spans="1:7">
       <c r="A587" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B587" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C587" t="s">
         <v>375</v>
@@ -17890,10 +17883,10 @@
         <v>47</v>
       </c>
       <c r="F587" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G587" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="588" spans="1:7">
@@ -17901,7 +17894,7 @@
         <v>408</v>
       </c>
       <c r="B588" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C588" t="s">
         <v>158</v>
@@ -17913,18 +17906,18 @@
         <v>54</v>
       </c>
       <c r="F588" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G588" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="589" spans="1:7">
       <c r="A589" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B589" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C589" t="s">
         <v>280</v>
@@ -17936,18 +17929,18 @@
         <v>54</v>
       </c>
       <c r="F589" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G589" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="590" spans="1:7">
       <c r="A590" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B590" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C590" t="s">
         <v>280</v>
@@ -17959,18 +17952,18 @@
         <v>54</v>
       </c>
       <c r="F590" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G590" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="591" spans="1:7">
       <c r="A591" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B591" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C591" t="s">
         <v>364</v>
@@ -17982,10 +17975,10 @@
         <v>11</v>
       </c>
       <c r="F591" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G591" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="592" spans="1:7">
@@ -17993,10 +17986,10 @@
         <v>100</v>
       </c>
       <c r="B592" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C592" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="D592" t="s">
         <v>14</v>
@@ -18008,7 +18001,7 @@
         <v>416</v>
       </c>
       <c r="G592" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="593" spans="1:7">
@@ -18016,7 +18009,7 @@
         <v>100</v>
       </c>
       <c r="B593" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C593" t="s">
         <v>58</v>
@@ -18028,10 +18021,10 @@
         <v>11</v>
       </c>
       <c r="F593" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G593" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="594" spans="1:7">
@@ -18039,7 +18032,7 @@
         <v>103</v>
       </c>
       <c r="B594" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C594" t="s">
         <v>22</v>
@@ -18051,10 +18044,10 @@
         <v>11</v>
       </c>
       <c r="F594" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="G594" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="595" spans="1:7">
@@ -18062,7 +18055,7 @@
         <v>100</v>
       </c>
       <c r="B595" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C595" t="s">
         <v>58</v>
@@ -18074,10 +18067,10 @@
         <v>11</v>
       </c>
       <c r="F595" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G595" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="596" spans="1:7">
@@ -18085,7 +18078,7 @@
         <v>103</v>
       </c>
       <c r="B596" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C596" t="s">
         <v>22</v>
@@ -18097,18 +18090,18 @@
         <v>11</v>
       </c>
       <c r="F596" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G596" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="597" spans="1:7">
       <c r="A597" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B597" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C597" t="s">
         <v>38</v>
@@ -18120,10 +18113,10 @@
         <v>11</v>
       </c>
       <c r="F597" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G597" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="598" spans="1:7">
@@ -18131,7 +18124,7 @@
         <v>107</v>
       </c>
       <c r="B598" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C598" t="s">
         <v>58</v>
@@ -18143,10 +18136,10 @@
         <v>11</v>
       </c>
       <c r="F598" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G598" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="599" spans="1:7">
@@ -18154,7 +18147,7 @@
         <v>100</v>
       </c>
       <c r="B599" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C599" t="s">
         <v>58</v>
@@ -18169,7 +18162,7 @@
         <v>592</v>
       </c>
       <c r="G599" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="600" spans="1:7">
@@ -18177,7 +18170,7 @@
         <v>103</v>
       </c>
       <c r="B600" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C600" t="s">
         <v>38</v>
@@ -18192,18 +18185,18 @@
         <v>505</v>
       </c>
       <c r="G600" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="601" spans="1:7">
       <c r="A601" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C601" t="s">
         <v>1045</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1047</v>
       </c>
       <c r="D601" t="s">
         <v>10</v>
@@ -18212,18 +18205,18 @@
         <v>27</v>
       </c>
       <c r="F601" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G601" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="602" spans="1:7">
       <c r="A602" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B602" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C602" t="s">
         <v>236</v>
@@ -18235,21 +18228,21 @@
         <v>27</v>
       </c>
       <c r="F602" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G602" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="603" spans="1:7">
       <c r="A603" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C603" t="s">
         <v>1045</v>
-      </c>
-      <c r="B603" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1047</v>
       </c>
       <c r="D603" t="s">
         <v>14</v>
@@ -18258,18 +18251,18 @@
         <v>27</v>
       </c>
       <c r="F603" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G603" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="604" spans="1:7">
       <c r="A604" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B604" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C604" t="s">
         <v>236</v>
@@ -18281,18 +18274,18 @@
         <v>27</v>
       </c>
       <c r="F604" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G604" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="605" spans="1:7">
       <c r="A605" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B605" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C605" t="s">
         <v>22</v>
@@ -18304,10 +18297,10 @@
         <v>27</v>
       </c>
       <c r="F605" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G605" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="606" spans="1:7">
@@ -18315,10 +18308,10 @@
         <v>120</v>
       </c>
       <c r="B606" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C606" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D606" t="s">
         <v>18</v>
@@ -18327,18 +18320,18 @@
         <v>27</v>
       </c>
       <c r="F606" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G606" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="607" spans="1:7">
       <c r="A607" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B607" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C607" t="s">
         <v>22</v>
@@ -18350,21 +18343,21 @@
         <v>27</v>
       </c>
       <c r="F607" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G607" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="608" spans="1:7">
       <c r="A608" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C608" t="s">
         <v>1045</v>
-      </c>
-      <c r="B608" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1047</v>
       </c>
       <c r="D608" t="s">
         <v>25</v>
@@ -18373,21 +18366,21 @@
         <v>27</v>
       </c>
       <c r="F608" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G608" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="609" spans="1:7">
       <c r="A609" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B609" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C609" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D609" t="s">
         <v>25</v>
@@ -18396,18 +18389,18 @@
         <v>27</v>
       </c>
       <c r="F609" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G609" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="610" spans="1:7">
       <c r="A610" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B610" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C610" t="s">
         <v>22</v>
@@ -18419,21 +18412,21 @@
         <v>27</v>
       </c>
       <c r="F610" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="G610" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="611" spans="1:7">
       <c r="A611" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C611" t="s">
         <v>1045</v>
-      </c>
-      <c r="B611" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1047</v>
       </c>
       <c r="D611" t="s">
         <v>26</v>
@@ -18442,21 +18435,21 @@
         <v>27</v>
       </c>
       <c r="F611" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G611" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="612" spans="1:7">
       <c r="A612" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B612" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C612" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D612" t="s">
         <v>26</v>
@@ -18465,18 +18458,18 @@
         <v>27</v>
       </c>
       <c r="F612" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G612" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="613" spans="1:7">
       <c r="A613" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B613" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C613" t="s">
         <v>22</v>
@@ -18488,18 +18481,18 @@
         <v>27</v>
       </c>
       <c r="F613" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="G613" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="614" spans="1:7">
       <c r="A614" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B614" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C614" t="s">
         <v>375</v>
@@ -18511,10 +18504,10 @@
         <v>36</v>
       </c>
       <c r="F614" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G614" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="615" spans="1:7">
@@ -18522,7 +18515,7 @@
         <v>100</v>
       </c>
       <c r="B615" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C615" t="s">
         <v>58</v>
@@ -18534,21 +18527,21 @@
         <v>36</v>
       </c>
       <c r="F615" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G615" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="616" spans="1:7">
       <c r="A616" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B616" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C616" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D616" t="s">
         <v>18</v>
@@ -18557,18 +18550,18 @@
         <v>36</v>
       </c>
       <c r="F616" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G616" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="617" spans="1:7">
       <c r="A617" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B617" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C617" t="s">
         <v>22</v>
@@ -18580,18 +18573,18 @@
         <v>36</v>
       </c>
       <c r="F617" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G617" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="618" spans="1:7">
       <c r="A618" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B618" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C618" t="s">
         <v>587</v>
@@ -18603,21 +18596,21 @@
         <v>36</v>
       </c>
       <c r="F618" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G618" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="619" spans="1:7">
       <c r="A619" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B619" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C619" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D619" t="s">
         <v>23</v>
@@ -18626,18 +18619,18 @@
         <v>36</v>
       </c>
       <c r="F619" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G619" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="620" spans="1:7">
       <c r="A620" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B620" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C620" t="s">
         <v>22</v>
@@ -18649,18 +18642,18 @@
         <v>36</v>
       </c>
       <c r="F620" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G620" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="621" spans="1:7">
       <c r="A621" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B621" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C621" t="s">
         <v>587</v>
@@ -18675,7 +18668,7 @@
         <v>592</v>
       </c>
       <c r="G621" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="622" spans="1:7">
@@ -18683,7 +18676,7 @@
         <v>113</v>
       </c>
       <c r="B622" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C622" t="s">
         <v>318</v>
@@ -18695,18 +18688,18 @@
         <v>36</v>
       </c>
       <c r="F622" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G622" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="623" spans="1:7">
       <c r="A623" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B623" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C623" t="s">
         <v>22</v>
@@ -18718,10 +18711,10 @@
         <v>36</v>
       </c>
       <c r="F623" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G623" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="624" spans="1:7">
@@ -18729,7 +18722,7 @@
         <v>103</v>
       </c>
       <c r="B624" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C624" t="s">
         <v>22</v>
@@ -18744,15 +18737,15 @@
         <v>520</v>
       </c>
       <c r="G624" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="625" spans="1:7">
       <c r="A625" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B625" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C625" t="s">
         <v>375</v>
@@ -18767,15 +18760,15 @@
         <v>486</v>
       </c>
       <c r="G625" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="626" spans="1:7">
       <c r="A626" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B626" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C626" t="s">
         <v>566</v>
@@ -18787,10 +18780,10 @@
         <v>47</v>
       </c>
       <c r="F626" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G626" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="627" spans="1:7">
@@ -18798,7 +18791,7 @@
         <v>100</v>
       </c>
       <c r="B627" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C627" t="s">
         <v>58</v>
@@ -18810,10 +18803,10 @@
         <v>47</v>
       </c>
       <c r="F627" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G627" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="628" spans="1:7">
@@ -18821,10 +18814,10 @@
         <v>78</v>
       </c>
       <c r="B628" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C628" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D628" t="s">
         <v>18</v>
@@ -18833,21 +18826,21 @@
         <v>47</v>
       </c>
       <c r="F628" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G628" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="629" spans="1:7">
       <c r="A629" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B629" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C629" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D629" t="s">
         <v>18</v>
@@ -18856,10 +18849,10 @@
         <v>47</v>
       </c>
       <c r="F629" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G629" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="630" spans="1:7">
@@ -18867,7 +18860,7 @@
         <v>574</v>
       </c>
       <c r="B630" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C630" t="s">
         <v>22</v>
@@ -18879,18 +18872,18 @@
         <v>47</v>
       </c>
       <c r="F630" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G630" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="631" spans="1:7">
       <c r="A631" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B631" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C631" t="s">
         <v>542</v>
@@ -18902,10 +18895,10 @@
         <v>47</v>
       </c>
       <c r="F631" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="G631" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="632" spans="1:7">
@@ -18913,10 +18906,10 @@
         <v>78</v>
       </c>
       <c r="B632" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C632" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D632" t="s">
         <v>23</v>
@@ -18925,10 +18918,10 @@
         <v>47</v>
       </c>
       <c r="F632" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G632" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="633" spans="1:7">
@@ -18936,7 +18929,7 @@
         <v>574</v>
       </c>
       <c r="B633" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C633" t="s">
         <v>22</v>
@@ -18948,10 +18941,10 @@
         <v>47</v>
       </c>
       <c r="F633" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G633" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="634" spans="1:7">
@@ -18959,10 +18952,10 @@
         <v>562</v>
       </c>
       <c r="B634" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C634" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D634" t="s">
         <v>25</v>
@@ -18971,10 +18964,10 @@
         <v>47</v>
       </c>
       <c r="F634" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G634" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -18982,7 +18975,7 @@
         <v>66</v>
       </c>
       <c r="B635" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C635" t="s">
         <v>38</v>
@@ -18994,10 +18987,10 @@
         <v>47</v>
       </c>
       <c r="F635" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G635" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="636" spans="1:7">
@@ -19005,10 +18998,10 @@
         <v>120</v>
       </c>
       <c r="B636" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C636" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="D636" t="s">
         <v>10</v>
@@ -19017,18 +19010,18 @@
         <v>54</v>
       </c>
       <c r="F636" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="G636" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="637" spans="1:7">
       <c r="A637" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B637" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C637" t="s">
         <v>22</v>
@@ -19040,10 +19033,10 @@
         <v>54</v>
       </c>
       <c r="F637" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G637" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="638" spans="1:7">
@@ -19051,10 +19044,10 @@
         <v>120</v>
       </c>
       <c r="B638" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C638" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D638" t="s">
         <v>14</v>
@@ -19063,10 +19056,10 @@
         <v>54</v>
       </c>
       <c r="F638" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="G638" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -19074,10 +19067,10 @@
         <v>120</v>
       </c>
       <c r="B639" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C639" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="D639" t="s">
         <v>14</v>
@@ -19086,10 +19079,10 @@
         <v>54</v>
       </c>
       <c r="F639" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="G639" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="640" spans="1:7">
@@ -19097,10 +19090,10 @@
         <v>120</v>
       </c>
       <c r="B640" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C640" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D640" t="s">
         <v>18</v>
@@ -19109,10 +19102,10 @@
         <v>54</v>
       </c>
       <c r="F640" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="G640" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="641" spans="1:7">
@@ -19120,10 +19113,10 @@
         <v>100</v>
       </c>
       <c r="B641" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C641" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="D641" t="s">
         <v>18</v>
@@ -19135,7 +19128,7 @@
         <v>416</v>
       </c>
       <c r="G641" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="642" spans="1:7">
@@ -19143,7 +19136,7 @@
         <v>574</v>
       </c>
       <c r="B642" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C642" t="s">
         <v>22</v>
@@ -19158,7 +19151,7 @@
         <v>592</v>
       </c>
       <c r="G642" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="643" spans="1:7">
@@ -19166,7 +19159,7 @@
         <v>574</v>
       </c>
       <c r="B643" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C643" t="s">
         <v>22</v>
@@ -19178,10 +19171,10 @@
         <v>54</v>
       </c>
       <c r="F643" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G643" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="644" spans="1:7">
@@ -19189,7 +19182,7 @@
         <v>100</v>
       </c>
       <c r="B644" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C644" t="s">
         <v>58</v>
@@ -19204,15 +19197,15 @@
         <v>592</v>
       </c>
       <c r="G644" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="645" spans="1:7">
       <c r="A645" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B645" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C645" t="s">
         <v>587</v>
@@ -19224,21 +19217,21 @@
         <v>54</v>
       </c>
       <c r="F645" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G645" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="646" spans="1:7">
       <c r="A646" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B646" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C646" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D646" t="s">
         <v>10</v>
@@ -19250,15 +19243,15 @@
         <v>175</v>
       </c>
       <c r="G646" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="647" spans="1:7">
       <c r="A647" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B647" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C647" t="s">
         <v>181</v>
@@ -19273,15 +19266,15 @@
         <v>274</v>
       </c>
       <c r="G647" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="648" spans="1:7">
       <c r="A648" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B648" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="C648" t="s">
         <v>181</v>
@@ -19296,7 +19289,7 @@
         <v>274</v>
       </c>
       <c r="G648" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="649" spans="1:7">
@@ -19304,7 +19297,7 @@
         <v>620</v>
       </c>
       <c r="B649" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C649" t="s">
         <v>148</v>
@@ -19319,7 +19312,7 @@
         <v>175</v>
       </c>
       <c r="G649" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="650" spans="1:7">
@@ -19327,7 +19320,7 @@
         <v>589</v>
       </c>
       <c r="B650" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C650" t="s">
         <v>148</v>
@@ -19342,7 +19335,7 @@
         <v>175</v>
       </c>
       <c r="G650" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="651" spans="1:7">
@@ -19350,7 +19343,7 @@
         <v>20</v>
       </c>
       <c r="B651" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C651" t="s">
         <v>22</v>
@@ -19365,7 +19358,7 @@
         <v>24</v>
       </c>
       <c r="G651" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="652" spans="1:7">
@@ -19373,7 +19366,7 @@
         <v>20</v>
       </c>
       <c r="B652" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C652" t="s">
         <v>22</v>
@@ -19388,7 +19381,7 @@
         <v>24</v>
       </c>
       <c r="G652" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="653" spans="1:7">
@@ -19396,7 +19389,7 @@
         <v>20</v>
       </c>
       <c r="B653" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C653" t="s">
         <v>22</v>
@@ -19411,15 +19404,15 @@
         <v>24</v>
       </c>
       <c r="G653" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="654" spans="1:7">
       <c r="A654" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B654" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C654" t="s">
         <v>625</v>
@@ -19434,7 +19427,7 @@
         <v>175</v>
       </c>
       <c r="G654" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="655" spans="1:7">
@@ -19442,7 +19435,7 @@
         <v>20</v>
       </c>
       <c r="B655" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C655" t="s">
         <v>22</v>
@@ -19457,15 +19450,15 @@
         <v>24</v>
       </c>
       <c r="G655" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="656" spans="1:7">
       <c r="A656" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B656" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C656" t="s">
         <v>174</v>
@@ -19480,15 +19473,15 @@
         <v>175</v>
       </c>
       <c r="G656" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="657" spans="1:7">
       <c r="A657" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B657" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C657" t="s">
         <v>148</v>
@@ -19500,18 +19493,18 @@
         <v>36</v>
       </c>
       <c r="F657" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="G657" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="658" spans="1:7">
       <c r="A658" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B658" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C658" t="s">
         <v>148</v>
@@ -19523,18 +19516,18 @@
         <v>36</v>
       </c>
       <c r="F658" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="G658" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="659" spans="1:7">
       <c r="A659" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B659" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C659" t="s">
         <v>227</v>
@@ -19549,7 +19542,7 @@
         <v>175</v>
       </c>
       <c r="G659" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="660" spans="1:7">
@@ -19557,7 +19550,7 @@
         <v>170</v>
       </c>
       <c r="B660" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C660" t="s">
         <v>158</v>
@@ -19572,15 +19565,15 @@
         <v>175</v>
       </c>
       <c r="G660" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="661" spans="1:7">
       <c r="A661" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B661" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C661" t="s">
         <v>353</v>
@@ -19595,15 +19588,15 @@
         <v>175</v>
       </c>
       <c r="G661" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="662" spans="1:7">
       <c r="A662" t="s">
-        <v>1116</v>
+        <v>614</v>
       </c>
       <c r="B662" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C662" t="s">
         <v>560</v>
@@ -19615,18 +19608,18 @@
         <v>47</v>
       </c>
       <c r="F662" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="G662" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="663" spans="1:7">
       <c r="A663" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="B663" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C663" t="s">
         <v>227</v>
@@ -19638,18 +19631,18 @@
         <v>47</v>
       </c>
       <c r="F663" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="G663" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="664" spans="1:7">
       <c r="A664" t="s">
-        <v>1116</v>
+        <v>614</v>
       </c>
       <c r="B664" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C664" t="s">
         <v>560</v>
@@ -19661,18 +19654,18 @@
         <v>47</v>
       </c>
       <c r="F664" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="G664" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="665" spans="1:7">
       <c r="A665" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="B665" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C665" t="s">
         <v>227</v>
@@ -19684,10 +19677,10 @@
         <v>47</v>
       </c>
       <c r="F665" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="G665" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="666" spans="1:7">
@@ -19695,7 +19688,7 @@
         <v>156</v>
       </c>
       <c r="B666" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="C666" t="s">
         <v>158</v>
@@ -19710,15 +19703,15 @@
         <v>175</v>
       </c>
       <c r="G666" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="667" spans="1:7">
       <c r="A667" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="B667" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="C667" t="s">
         <v>353</v>
@@ -19733,7 +19726,7 @@
         <v>175</v>
       </c>
       <c r="G667" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="668" spans="1:7">
@@ -19741,7 +19734,7 @@
         <v>162</v>
       </c>
       <c r="B668" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C668" t="s">
         <v>164</v>
@@ -19753,10 +19746,10 @@
         <v>54</v>
       </c>
       <c r="F668" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="G668" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="669" spans="1:7">
@@ -19764,7 +19757,7 @@
         <v>603</v>
       </c>
       <c r="B669" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="C669" t="s">
         <v>353</v>
@@ -19776,10 +19769,10 @@
         <v>54</v>
       </c>
       <c r="F669" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="G669" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="670" spans="1:7">
@@ -19787,7 +19780,7 @@
         <v>20</v>
       </c>
       <c r="B670" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C670" t="s">
         <v>22</v>
@@ -19802,7 +19795,7 @@
         <v>24</v>
       </c>
       <c r="G670" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="671" spans="1:7">
@@ -19810,7 +19803,7 @@
         <v>20</v>
       </c>
       <c r="B671" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C671" t="s">
         <v>22</v>
@@ -19825,15 +19818,15 @@
         <v>24</v>
       </c>
       <c r="G671" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="672" spans="1:7">
       <c r="A672" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="B672" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="C672" t="s">
         <v>353</v>
@@ -19848,7 +19841,7 @@
         <v>175</v>
       </c>
       <c r="G672" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="673" spans="1:7">
@@ -19856,7 +19849,7 @@
         <v>162</v>
       </c>
       <c r="B673" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C673" t="s">
         <v>164</v>
@@ -19868,10 +19861,10 @@
         <v>54</v>
       </c>
       <c r="F673" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="G673" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="674" spans="1:7">
@@ -19879,7 +19872,7 @@
         <v>603</v>
       </c>
       <c r="B674" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="C674" t="s">
         <v>353</v>
@@ -19891,14 +19884,37 @@
         <v>54</v>
       </c>
       <c r="F674" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="G674" t="s">
-        <v>1096</v>
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="675" spans="1:7">
+      <c r="A675" t="s">
+        <v>113</v>
+      </c>
+      <c r="B675" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C675" t="s">
+        <v>318</v>
+      </c>
+      <c r="D675" t="s">
+        <v>25</v>
+      </c>
+      <c r="E675" t="s">
+        <v>36</v>
+      </c>
+      <c r="F675" t="s">
+        <v>543</v>
+      </c>
+      <c r="G675" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G674" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G675" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -13938,7 +13938,7 @@
         <v>338</v>
       </c>
       <c r="D414" t="s">
-        <v>415</v>
+        <v>18</v>
       </c>
       <c r="E414" t="s">
         <v>11</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -2231,7 +2231,7 @@
     <t>TP-μPμC-M1MCIL</t>
   </si>
   <si>
-    <t>14h-15h</t>
+    <t>14h - 15h</t>
   </si>
   <si>
     <t>Labo μ-processeurs G2</t>
@@ -2240,7 +2240,7 @@
     <t>TP-μ-processeurs et μ-contrôleurs-G2</t>
   </si>
   <si>
-    <t>15h-16h</t>
+    <t>15h - 16h</t>
   </si>
   <si>
     <t>Labo μ-processeurs G1</t>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1139">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2234,270 +2234,267 @@
     <t>14h - 15h</t>
   </si>
   <si>
+    <t>TP-μ-processeurs et μ-contrôleurs-G2</t>
+  </si>
+  <si>
+    <t>15h - 16h</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-Exploitation des Réseaux électriques</t>
+  </si>
+  <si>
+    <t>Cours-ERE-M1MCIL</t>
+  </si>
+  <si>
+    <t>TD-Exploitation des Réseaux électriques</t>
+  </si>
+  <si>
+    <t>TD-ERE-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-Compatibilité électromagnétique</t>
+  </si>
+  <si>
+    <t>Cours-EM-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-Exploitation des Réseaux électriques-G1</t>
+  </si>
+  <si>
+    <t>TP-ERE-M1MCIL</t>
+  </si>
+  <si>
+    <t>NEMMICH SAID</t>
+  </si>
+  <si>
+    <t>Salle micro 2</t>
+  </si>
+  <si>
+    <t>TP-Exploitation des Réseaux électriques-G2</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques approfondies -G1</t>
+  </si>
+  <si>
+    <t>TP-MEA-M1MCIL</t>
+  </si>
+  <si>
+    <t>Labo machine 1 &amp; Salle de micros 03</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques approfondies -G2</t>
+  </si>
+  <si>
+    <t>Cours-Technologie d'Élclairage</t>
+  </si>
+  <si>
+    <t>Cours-TE-M1MCIL</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1MCIL</t>
+  </si>
+  <si>
+    <t>SAHALI YAMINA</t>
+  </si>
+  <si>
+    <t>TD-Méthodes numériques appliquées</t>
+  </si>
+  <si>
+    <t>TD-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>TD-MEA-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-Méthodes numériques appliquées</t>
+  </si>
+  <si>
+    <t>Cours-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-EPA-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance avancée-G1</t>
+  </si>
+  <si>
+    <t>TP-EPA-M1MCIL</t>
+  </si>
+  <si>
+    <t>Salle de micros 02 dept</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance avancée-G2</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées-G2</t>
+  </si>
+  <si>
+    <t>TP-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-PAP-M1ME</t>
+  </si>
+  <si>
+    <t>M1ME</t>
+  </si>
+  <si>
+    <t>Cours-RTsDEE-M1ME</t>
+  </si>
+  <si>
+    <t>TD-RTsDEE-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-EPA-M1ME</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1ME</t>
+  </si>
+  <si>
+    <t>TP-Programmation avancée en Python TP</t>
+  </si>
+  <si>
+    <t>TP-PAP-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1ME</t>
+  </si>
+  <si>
+    <t>RAMI ABDELKADER</t>
+  </si>
+  <si>
+    <t>Labo Réseaux</t>
+  </si>
+  <si>
+    <t>TP-MEA-M1ME</t>
+  </si>
+  <si>
+    <t>Salle de micro 2 DEP</t>
+  </si>
+  <si>
+    <t>Salle de micro  2 DEP</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-M1ME</t>
+  </si>
+  <si>
+    <t>TP-EPA-M1ME</t>
+  </si>
+  <si>
+    <t>Salle de micros 1</t>
+  </si>
+  <si>
+    <t>TP-MNAO-M1ME</t>
+  </si>
+  <si>
+    <t>TOUHAMI SEDDIK</t>
+  </si>
+  <si>
+    <t>Cours-ER-M1ME</t>
+  </si>
+  <si>
+    <t>TP-μ-processeurs et μ-contrôleurs TP G2/G1</t>
+  </si>
+  <si>
+    <t>TP-μPμC-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1ME</t>
+  </si>
+  <si>
+    <t>TD-MEA-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-MNAO-M1ME</t>
+  </si>
+  <si>
+    <t>TD-MNAO-M1ME</t>
+  </si>
+  <si>
+    <t>TD-Réseaux de transport et de distribution d'énergie élet. TD</t>
+  </si>
+  <si>
+    <t>TD-RTsDEE-RE</t>
+  </si>
+  <si>
+    <t>M1RE</t>
+  </si>
+  <si>
+    <t>TP-MEA-RE</t>
+  </si>
+  <si>
+    <t>Salle micro 2 DEP &amp; labo machine 02 G2</t>
+  </si>
+  <si>
+    <t>TP-MNAO-RE</t>
+  </si>
+  <si>
+    <t>Salle de micros 02 G1/G2</t>
+  </si>
+  <si>
+    <t>Cours-EPA-RE</t>
+  </si>
+  <si>
+    <t>Cours-Réseaux de transport et de distribution d'énergie électrique</t>
+  </si>
+  <si>
+    <t>Cours-RTsDEE-RE</t>
+  </si>
+  <si>
+    <t>TP-PAP-RE</t>
+  </si>
+  <si>
+    <t>Salle Micros 1 DEP</t>
+  </si>
+  <si>
+    <t>Cours-PAP-RE</t>
+  </si>
+  <si>
+    <t>Cours-MPM-RE</t>
+  </si>
+  <si>
+    <t>TP-EPA-RE</t>
+  </si>
+  <si>
+    <t>Salle de micros 01</t>
+  </si>
+  <si>
+    <t>TP-Réseaux de transport et de distribution d'énergie élet. TP G1</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-RE</t>
+  </si>
+  <si>
+    <t>Salle micro 1 G1</t>
+  </si>
+  <si>
+    <t>TP-μ-processeurs et μ-contrôleurs TP G2</t>
+  </si>
+  <si>
+    <t>TP-MPM-RE</t>
+  </si>
+  <si>
     <t>Labo μ-processeurs G2</t>
   </si>
   <si>
-    <t>TP-μ-processeurs et μ-contrôleurs-G2</t>
-  </si>
-  <si>
-    <t>15h - 16h</t>
+    <t>TP-Réseaux de transport et de distribution d'énergie élet. TP G2</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-M1RE</t>
+  </si>
+  <si>
+    <t>Salle micro 1 G2</t>
+  </si>
+  <si>
+    <t>TP-μ-processeurs et μ-contrôleurs TP G1</t>
   </si>
   <si>
     <t>Labo μ-processeurs G1</t>
   </si>
   <si>
-    <t>Cours-MEA-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-Exploitation des Réseaux électriques</t>
-  </si>
-  <si>
-    <t>Cours-ERE-M1MCIL</t>
-  </si>
-  <si>
-    <t>TD-Exploitation des Réseaux électriques</t>
-  </si>
-  <si>
-    <t>TD-ERE-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-Compatibilité électromagnétique</t>
-  </si>
-  <si>
-    <t>Cours-EM-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-Exploitation des Réseaux électriques-G1</t>
-  </si>
-  <si>
-    <t>TP-ERE-M1MCIL</t>
-  </si>
-  <si>
-    <t>NEMMICH SAID</t>
-  </si>
-  <si>
-    <t>Salle micro 2 G1/G2</t>
-  </si>
-  <si>
-    <t>TP-Exploitation des Réseaux électriques-G2</t>
-  </si>
-  <si>
-    <t>TP-Machines électriques approfondies -G1</t>
-  </si>
-  <si>
-    <t>TP-MEA-M1MCIL</t>
-  </si>
-  <si>
-    <t>Labo machine 1 &amp; Salle de micros 03</t>
-  </si>
-  <si>
-    <t>TP-Machines électriques approfondies -G2</t>
-  </si>
-  <si>
-    <t>Cours-Technologie d'Élclairage</t>
-  </si>
-  <si>
-    <t>Cours-TE-M1MCIL</t>
-  </si>
-  <si>
-    <t>TD-EPA-M1MCIL</t>
-  </si>
-  <si>
-    <t>SAHALI YAMINA</t>
-  </si>
-  <si>
-    <t>TD-Méthodes numériques appliquées</t>
-  </si>
-  <si>
-    <t>TD-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>TD-MEA-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-Méthodes numériques appliquées</t>
-  </si>
-  <si>
-    <t>Cours-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-EPA-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-Électronique de puissance avancée-G1</t>
-  </si>
-  <si>
-    <t>TP-EPA-M1MCIL</t>
-  </si>
-  <si>
-    <t>Salle de micros 02 dept</t>
-  </si>
-  <si>
-    <t>TP-Électronique de puissance avancée-G2</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées-G2</t>
-  </si>
-  <si>
-    <t>TP-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>Salle de micros 03 G1</t>
-  </si>
-  <si>
-    <t>Cours-PAP-M1ME</t>
-  </si>
-  <si>
-    <t>M1ME</t>
-  </si>
-  <si>
-    <t>Cours-RTsDEE-M1ME</t>
-  </si>
-  <si>
-    <t>TD-RTsDEE-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-EPA-M1ME</t>
-  </si>
-  <si>
-    <t>TD-EPA-M1ME</t>
-  </si>
-  <si>
-    <t>TP-Programmation avancée en Python TP</t>
-  </si>
-  <si>
-    <t>TP-PAP-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1ME</t>
-  </si>
-  <si>
-    <t>RAMI ABDELKADER</t>
-  </si>
-  <si>
-    <t>Labo Réseaux</t>
-  </si>
-  <si>
-    <t>TP-MEA-M1ME</t>
-  </si>
-  <si>
-    <t>Salle de micro 2 DEP</t>
-  </si>
-  <si>
-    <t>Salle de micro  2 DEP</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-M1ME</t>
-  </si>
-  <si>
-    <t>TP-EPA-M1ME</t>
-  </si>
-  <si>
-    <t>Salle de micros 1</t>
-  </si>
-  <si>
-    <t>TP-MNAO-M1ME</t>
-  </si>
-  <si>
-    <t>TOUHAMI SEDDIK</t>
-  </si>
-  <si>
-    <t>Cours-ER-M1ME</t>
-  </si>
-  <si>
-    <t>TP-μ-processeurs et μ-contrôleurs TP G2/G1</t>
-  </si>
-  <si>
-    <t>TP-μPμC-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1ME</t>
-  </si>
-  <si>
-    <t>TD-MEA-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-MNAO-M1ME</t>
-  </si>
-  <si>
-    <t>TD-MNAO-M1ME</t>
-  </si>
-  <si>
-    <t>TD-Réseaux de transport et de distribution d'énergie élet. TD</t>
-  </si>
-  <si>
-    <t>TD-RTsDEE-RE</t>
-  </si>
-  <si>
-    <t>M1RE</t>
-  </si>
-  <si>
-    <t>TP-MEA-RE</t>
-  </si>
-  <si>
-    <t>Salle micro 2 DEP &amp; labo machine 02 G2</t>
-  </si>
-  <si>
-    <t>TP-MNAO-RE</t>
-  </si>
-  <si>
-    <t>Salle de micros 02 G1/G2</t>
-  </si>
-  <si>
-    <t>Cours-EPA-RE</t>
-  </si>
-  <si>
-    <t>Cours-Réseaux de transport et de distribution d'énergie électrique</t>
-  </si>
-  <si>
-    <t>Cours-RTsDEE-RE</t>
-  </si>
-  <si>
-    <t>TP-PAP-RE</t>
-  </si>
-  <si>
-    <t>Salle Micros 1 DEP</t>
-  </si>
-  <si>
-    <t>Cours-PAP-RE</t>
-  </si>
-  <si>
-    <t>Cours-MPM-RE</t>
-  </si>
-  <si>
-    <t>TP-EPA-RE</t>
-  </si>
-  <si>
-    <t>Salle de micros 01</t>
-  </si>
-  <si>
-    <t>TP-Réseaux de transport et de distribution d'énergie élet. TP G1</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-RE</t>
-  </si>
-  <si>
-    <t>Salle micro 1 G1</t>
-  </si>
-  <si>
-    <t>TP-μ-processeurs et μ-contrôleurs TP G2</t>
-  </si>
-  <si>
-    <t>TP-MPM-RE</t>
-  </si>
-  <si>
-    <t>TP-Réseaux de transport et de distribution d'énergie élet. TP G2</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-M1RE</t>
-  </si>
-  <si>
-    <t>Salle micro 1 G2</t>
-  </si>
-  <si>
-    <t>TP-μ-processeurs et μ-contrôleurs TP G1</t>
-  </si>
-  <si>
     <t>TD-Méthodes numériques appliquées et optimisation TD</t>
   </si>
   <si>
@@ -3449,7 +3446,7 @@
     <t>TP-Méthodes numériques appliquées-G1</t>
   </si>
   <si>
-    <t>Salle de micros 03 G2</t>
+    <t>Salle micros 3</t>
   </si>
 </sst>
 </file>
@@ -4426,6 +4423,7 @@
     <col min="3" max="3" width="27.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="20.7142857142857" customWidth="1"/>
     <col min="5" max="5" width="23.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="32.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -13812,7 +13810,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" hidden="1" spans="1:7">
       <c r="A409" t="s">
         <v>697</v>
       </c>
@@ -13835,7 +13833,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" hidden="1" spans="1:7">
       <c r="A410" t="s">
         <v>731</v>
       </c>
@@ -13852,15 +13850,15 @@
         <v>11</v>
       </c>
       <c r="F410" t="s">
-        <v>734</v>
+        <v>690</v>
       </c>
       <c r="G410" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" hidden="1" spans="1:7">
       <c r="A411" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B411" t="s">
         <v>732</v>
@@ -13869,24 +13867,24 @@
         <v>17</v>
       </c>
       <c r="D411" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E411" t="s">
         <v>11</v>
       </c>
       <c r="F411" t="s">
-        <v>737</v>
+        <v>690</v>
       </c>
       <c r="G411" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" hidden="1" spans="1:7">
       <c r="A412" t="s">
         <v>269</v>
       </c>
       <c r="B412" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C412" t="s">
         <v>207</v>
@@ -13904,12 +13902,12 @@
         <v>730</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" hidden="1" spans="1:7">
       <c r="A413" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B413" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C413" t="s">
         <v>338</v>
@@ -13927,12 +13925,12 @@
         <v>730</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" hidden="1" spans="1:7">
       <c r="A414" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B414" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C414" t="s">
         <v>338</v>
@@ -13950,12 +13948,12 @@
         <v>730</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" hidden="1" spans="1:7">
       <c r="A415" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B415" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C415" t="s">
         <v>197</v>
@@ -13975,13 +13973,13 @@
     </row>
     <row r="416" spans="1:7">
       <c r="A416" t="s">
+        <v>743</v>
+      </c>
+      <c r="B416" t="s">
+        <v>744</v>
+      </c>
+      <c r="C416" t="s">
         <v>745</v>
-      </c>
-      <c r="B416" t="s">
-        <v>746</v>
-      </c>
-      <c r="C416" t="s">
-        <v>747</v>
       </c>
       <c r="D416" t="s">
         <v>18</v>
@@ -13990,7 +13988,7 @@
         <v>36</v>
       </c>
       <c r="F416" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G416" t="s">
         <v>730</v>
@@ -13998,13 +13996,13 @@
     </row>
     <row r="417" spans="1:7">
       <c r="A417" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B417" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C417" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D417" t="s">
         <v>23</v>
@@ -14013,18 +14011,18 @@
         <v>36</v>
       </c>
       <c r="F417" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G417" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" hidden="1" spans="1:7">
       <c r="A418" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B418" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C418" t="s">
         <v>686</v>
@@ -14036,18 +14034,18 @@
         <v>36</v>
       </c>
       <c r="F418" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G418" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" hidden="1" spans="1:7">
       <c r="A419" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B419" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C419" t="s">
         <v>313</v>
@@ -14059,18 +14057,18 @@
         <v>36</v>
       </c>
       <c r="F419" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G419" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" hidden="1" spans="1:7">
       <c r="A420" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B420" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C420" t="s">
         <v>197</v>
@@ -14088,15 +14086,15 @@
         <v>730</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" hidden="1" spans="1:7">
       <c r="A421" t="s">
         <v>341</v>
       </c>
       <c r="B421" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C421" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D421" t="s">
         <v>18</v>
@@ -14111,12 +14109,12 @@
         <v>730</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" hidden="1" spans="1:7">
       <c r="A422" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B422" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C422" t="s">
         <v>318</v>
@@ -14134,12 +14132,12 @@
         <v>730</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" hidden="1" spans="1:7">
       <c r="A423" t="s">
         <v>272</v>
       </c>
       <c r="B423" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C423" t="s">
         <v>271</v>
@@ -14157,12 +14155,12 @@
         <v>730</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" hidden="1" spans="1:7">
       <c r="A424" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B424" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C424" t="s">
         <v>318</v>
@@ -14180,15 +14178,15 @@
         <v>730</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" hidden="1" spans="1:7">
       <c r="A425" t="s">
         <v>316</v>
       </c>
       <c r="B425" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C425" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D425" t="s">
         <v>10</v>
@@ -14203,12 +14201,12 @@
         <v>730</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" hidden="1" spans="1:7">
       <c r="A426" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B426" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C426" t="s">
         <v>556</v>
@@ -14220,18 +14218,18 @@
         <v>54</v>
       </c>
       <c r="F426" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G426" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" hidden="1" spans="1:7">
       <c r="A427" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B427" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C427" t="s">
         <v>556</v>
@@ -14243,18 +14241,18 @@
         <v>54</v>
       </c>
       <c r="F427" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G427" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" hidden="1" spans="1:7">
       <c r="A428" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B428" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C428" t="s">
         <v>9</v>
@@ -14266,7 +14264,7 @@
         <v>54</v>
       </c>
       <c r="F428" t="s">
-        <v>770</v>
+        <v>678</v>
       </c>
       <c r="G428" t="s">
         <v>730</v>
@@ -14277,7 +14275,7 @@
         <v>673</v>
       </c>
       <c r="B429" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C429" t="s">
         <v>285</v>
@@ -14292,7 +14290,7 @@
         <v>258</v>
       </c>
       <c r="G429" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="430" hidden="1" spans="1:7">
@@ -14300,7 +14298,7 @@
         <v>661</v>
       </c>
       <c r="B430" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C430" t="s">
         <v>280</v>
@@ -14315,7 +14313,7 @@
         <v>258</v>
       </c>
       <c r="G430" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="431" hidden="1" spans="1:7">
@@ -14323,7 +14321,7 @@
         <v>665</v>
       </c>
       <c r="B431" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C431" t="s">
         <v>280</v>
@@ -14338,7 +14336,7 @@
         <v>258</v>
       </c>
       <c r="G431" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="432" hidden="1" spans="1:7">
@@ -14346,10 +14344,10 @@
         <v>316</v>
       </c>
       <c r="B432" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C432" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D432" t="s">
         <v>25</v>
@@ -14361,7 +14359,7 @@
         <v>675</v>
       </c>
       <c r="G432" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="433" hidden="1" spans="1:7">
@@ -14369,10 +14367,10 @@
         <v>341</v>
       </c>
       <c r="B433" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C433" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D433" t="s">
         <v>26</v>
@@ -14384,15 +14382,15 @@
         <v>675</v>
       </c>
       <c r="G433" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="434" hidden="1" spans="1:7">
       <c r="A434" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B434" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C434" t="s">
         <v>285</v>
@@ -14407,15 +14405,15 @@
         <v>672</v>
       </c>
       <c r="G434" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="435" hidden="1" spans="1:7">
       <c r="A435" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B435" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C435" t="s">
         <v>285</v>
@@ -14430,7 +14428,7 @@
         <v>672</v>
       </c>
       <c r="G435" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="436" hidden="1" spans="1:7">
@@ -14438,10 +14436,10 @@
         <v>697</v>
       </c>
       <c r="B436" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C436" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D436" t="s">
         <v>10</v>
@@ -14450,10 +14448,10 @@
         <v>36</v>
       </c>
       <c r="F436" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="G436" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="437" hidden="1" spans="1:7">
@@ -14461,10 +14459,10 @@
         <v>718</v>
       </c>
       <c r="B437" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C437" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D437" t="s">
         <v>18</v>
@@ -14473,10 +14471,10 @@
         <v>36</v>
       </c>
       <c r="F437" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="G437" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="438" hidden="1" spans="1:7">
@@ -14484,10 +14482,10 @@
         <v>718</v>
       </c>
       <c r="B438" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C438" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D438" t="s">
         <v>23</v>
@@ -14496,10 +14494,10 @@
         <v>36</v>
       </c>
       <c r="F438" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="G438" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="439" hidden="1" spans="1:7">
@@ -14507,10 +14505,10 @@
         <v>714</v>
       </c>
       <c r="B439" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C439" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D439" t="s">
         <v>10</v>
@@ -14519,10 +14517,10 @@
         <v>47</v>
       </c>
       <c r="F439" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="G439" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="440" hidden="1" spans="1:7">
@@ -14530,10 +14528,10 @@
         <v>721</v>
       </c>
       <c r="B440" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C440" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D440" t="s">
         <v>10</v>
@@ -14545,7 +14543,7 @@
         <v>690</v>
       </c>
       <c r="G440" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="441" hidden="1" spans="1:7">
@@ -14553,7 +14551,7 @@
         <v>721</v>
       </c>
       <c r="B441" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C441" t="s">
         <v>556</v>
@@ -14565,10 +14563,10 @@
         <v>47</v>
       </c>
       <c r="F441" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="G441" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="442" hidden="1" spans="1:7">
@@ -14576,10 +14574,10 @@
         <v>712</v>
       </c>
       <c r="B442" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C442" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D442" t="s">
         <v>18</v>
@@ -14591,7 +14589,7 @@
         <v>723</v>
       </c>
       <c r="G442" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="443" hidden="1" spans="1:7">
@@ -14599,7 +14597,7 @@
         <v>721</v>
       </c>
       <c r="B443" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C443" t="s">
         <v>556</v>
@@ -14614,7 +14612,7 @@
         <v>723</v>
       </c>
       <c r="G443" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="444" hidden="1" spans="1:7">
@@ -14622,10 +14620,10 @@
         <v>712</v>
       </c>
       <c r="B444" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C444" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D444" t="s">
         <v>23</v>
@@ -14637,7 +14635,7 @@
         <v>723</v>
       </c>
       <c r="G444" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="445" hidden="1" spans="1:7">
@@ -14645,7 +14643,7 @@
         <v>683</v>
       </c>
       <c r="B445" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C445" t="s">
         <v>308</v>
@@ -14660,7 +14658,7 @@
         <v>675</v>
       </c>
       <c r="G445" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="446" hidden="1" spans="1:7">
@@ -14668,10 +14666,10 @@
         <v>714</v>
       </c>
       <c r="B446" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C446" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D446" t="s">
         <v>26</v>
@@ -14680,21 +14678,21 @@
         <v>47</v>
       </c>
       <c r="F446" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="G446" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="447" hidden="1" spans="1:7">
       <c r="A447" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B447" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C447" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D447" t="s">
         <v>26</v>
@@ -14706,7 +14704,7 @@
         <v>690</v>
       </c>
       <c r="G447" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="448" hidden="1" spans="1:7">
@@ -14714,7 +14712,7 @@
         <v>269</v>
       </c>
       <c r="B448" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C448" t="s">
         <v>271</v>
@@ -14729,7 +14727,7 @@
         <v>675</v>
       </c>
       <c r="G448" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="449" hidden="1" spans="1:7">
@@ -14737,7 +14735,7 @@
         <v>272</v>
       </c>
       <c r="B449" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C449" t="s">
         <v>271</v>
@@ -14752,7 +14750,7 @@
         <v>309</v>
       </c>
       <c r="G449" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="450" hidden="1" spans="1:7">
@@ -14760,10 +14758,10 @@
         <v>681</v>
       </c>
       <c r="B450" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C450" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D450" t="s">
         <v>25</v>
@@ -14775,7 +14773,7 @@
         <v>675</v>
       </c>
       <c r="G450" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="451" hidden="1" spans="1:7">
@@ -14783,10 +14781,10 @@
         <v>663</v>
       </c>
       <c r="B451" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C451" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D451" t="s">
         <v>26</v>
@@ -14798,15 +14796,15 @@
         <v>675</v>
       </c>
       <c r="G451" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="452" hidden="1" spans="1:7">
       <c r="A452" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B452" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C452" t="s">
         <v>227</v>
@@ -14821,7 +14819,7 @@
         <v>19</v>
       </c>
       <c r="G452" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="453" hidden="1" spans="1:7">
@@ -14829,10 +14827,10 @@
         <v>718</v>
       </c>
       <c r="B453" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C453" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D453" t="s">
         <v>18</v>
@@ -14841,10 +14839,10 @@
         <v>11</v>
       </c>
       <c r="F453" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="G453" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="454" hidden="1" spans="1:7">
@@ -14852,10 +14850,10 @@
         <v>712</v>
       </c>
       <c r="B454" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C454" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D454" t="s">
         <v>18</v>
@@ -14864,10 +14862,10 @@
         <v>11</v>
       </c>
       <c r="F454" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="G454" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="455" hidden="1" spans="1:7">
@@ -14875,10 +14873,10 @@
         <v>718</v>
       </c>
       <c r="B455" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C455" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D455" t="s">
         <v>23</v>
@@ -14887,10 +14885,10 @@
         <v>11</v>
       </c>
       <c r="F455" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="G455" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="456" hidden="1" spans="1:7">
@@ -14898,10 +14896,10 @@
         <v>712</v>
       </c>
       <c r="B456" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C456" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D456" t="s">
         <v>23</v>
@@ -14910,10 +14908,10 @@
         <v>11</v>
       </c>
       <c r="F456" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="G456" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="457" hidden="1" spans="1:7">
@@ -14921,10 +14919,10 @@
         <v>316</v>
       </c>
       <c r="B457" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C457" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D457" t="s">
         <v>25</v>
@@ -14936,15 +14934,15 @@
         <v>675</v>
       </c>
       <c r="G457" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="458" hidden="1" spans="1:7">
       <c r="A458" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B458" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="C458" t="s">
         <v>227</v>
@@ -14959,15 +14957,15 @@
         <v>19</v>
       </c>
       <c r="G458" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="459" hidden="1" spans="1:7">
       <c r="A459" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B459" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C459" t="s">
         <v>285</v>
@@ -14979,10 +14977,10 @@
         <v>27</v>
       </c>
       <c r="F459" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="G459" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="460" hidden="1" spans="1:7">
@@ -14990,7 +14988,7 @@
         <v>673</v>
       </c>
       <c r="B460" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C460" t="s">
         <v>285</v>
@@ -15005,15 +15003,15 @@
         <v>675</v>
       </c>
       <c r="G460" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="461" hidden="1" spans="1:7">
       <c r="A461" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B461" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C461" t="s">
         <v>285</v>
@@ -15025,10 +15023,10 @@
         <v>27</v>
       </c>
       <c r="F461" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="G461" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="462" hidden="1" spans="1:7">
@@ -15036,10 +15034,10 @@
         <v>697</v>
       </c>
       <c r="B462" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C462" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D462" t="s">
         <v>10</v>
@@ -15051,7 +15049,7 @@
         <v>675</v>
       </c>
       <c r="G462" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="463" hidden="1" spans="1:7">
@@ -15059,7 +15057,7 @@
         <v>721</v>
       </c>
       <c r="B463" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C463" t="s">
         <v>556</v>
@@ -15071,10 +15069,10 @@
         <v>36</v>
       </c>
       <c r="F463" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="G463" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="464" hidden="1" spans="1:7">
@@ -15082,7 +15080,7 @@
         <v>721</v>
       </c>
       <c r="B464" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C464" t="s">
         <v>556</v>
@@ -15094,18 +15092,18 @@
         <v>36</v>
       </c>
       <c r="F464" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="G464" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="465" hidden="1" spans="1:7">
       <c r="A465" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B465" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C465" t="s">
         <v>280</v>
@@ -15117,21 +15115,21 @@
         <v>36</v>
       </c>
       <c r="F465" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="G465" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="466" hidden="1" spans="1:7">
       <c r="A466" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B466" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C466" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D466" t="s">
         <v>25</v>
@@ -15140,18 +15138,18 @@
         <v>36</v>
       </c>
       <c r="F466" t="s">
-        <v>734</v>
+        <v>815</v>
       </c>
       <c r="G466" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="467" hidden="1" spans="1:7">
       <c r="A467" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B467" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C467" t="s">
         <v>280</v>
@@ -15163,21 +15161,21 @@
         <v>36</v>
       </c>
       <c r="F467" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="G467" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="468" hidden="1" spans="1:7">
       <c r="A468" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B468" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C468" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D468" t="s">
         <v>26</v>
@@ -15186,21 +15184,21 @@
         <v>36</v>
       </c>
       <c r="F468" t="s">
-        <v>737</v>
+        <v>820</v>
       </c>
       <c r="G468" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="469" hidden="1" spans="1:7">
       <c r="A469" t="s">
+        <v>821</v>
+      </c>
+      <c r="B469" t="s">
         <v>822</v>
       </c>
-      <c r="B469" t="s">
-        <v>823</v>
-      </c>
       <c r="C469" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D469" t="s">
         <v>10</v>
@@ -15212,7 +15210,7 @@
         <v>675</v>
       </c>
       <c r="G469" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="470" hidden="1" spans="1:7">
@@ -15220,7 +15218,7 @@
         <v>683</v>
       </c>
       <c r="B470" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C470" t="s">
         <v>308</v>
@@ -15235,7 +15233,7 @@
         <v>675</v>
       </c>
       <c r="G470" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="471" hidden="1" spans="1:7">
@@ -15243,10 +15241,10 @@
         <v>316</v>
       </c>
       <c r="B471" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C471" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D471" t="s">
         <v>26</v>
@@ -15258,15 +15256,15 @@
         <v>675</v>
       </c>
       <c r="G471" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="472" hidden="1" spans="1:7">
       <c r="A472" t="s">
+        <v>824</v>
+      </c>
+      <c r="B472" t="s">
         <v>825</v>
-      </c>
-      <c r="B472" t="s">
-        <v>826</v>
       </c>
       <c r="C472" t="s">
         <v>271</v>
@@ -15281,7 +15279,7 @@
         <v>675</v>
       </c>
       <c r="G472" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="473" hidden="1" spans="1:7">
@@ -15289,10 +15287,10 @@
         <v>681</v>
       </c>
       <c r="B473" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C473" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D473" t="s">
         <v>25</v>
@@ -15304,15 +15302,15 @@
         <v>675</v>
       </c>
       <c r="G473" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="474" hidden="1" spans="1:7">
       <c r="A474" t="s">
+        <v>827</v>
+      </c>
+      <c r="B474" t="s">
         <v>828</v>
-      </c>
-      <c r="B474" t="s">
-        <v>829</v>
       </c>
       <c r="C474" t="s">
         <v>530</v>
@@ -15324,18 +15322,18 @@
         <v>11</v>
       </c>
       <c r="F474" t="s">
+        <v>829</v>
+      </c>
+      <c r="G474" t="s">
         <v>830</v>
-      </c>
-      <c r="G474" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="475" hidden="1" spans="1:7">
       <c r="A475" t="s">
+        <v>831</v>
+      </c>
+      <c r="B475" t="s">
         <v>832</v>
-      </c>
-      <c r="B475" t="s">
-        <v>833</v>
       </c>
       <c r="C475" t="s">
         <v>212</v>
@@ -15347,18 +15345,18 @@
         <v>11</v>
       </c>
       <c r="F475" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G475" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="476" hidden="1" spans="1:7">
       <c r="A476" t="s">
+        <v>834</v>
+      </c>
+      <c r="B476" t="s">
         <v>835</v>
-      </c>
-      <c r="B476" t="s">
-        <v>836</v>
       </c>
       <c r="C476" t="s">
         <v>395</v>
@@ -15370,21 +15368,21 @@
         <v>11</v>
       </c>
       <c r="F476" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G476" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="477" hidden="1" spans="1:7">
       <c r="A477" t="s">
+        <v>831</v>
+      </c>
+      <c r="B477" t="s">
         <v>832</v>
       </c>
-      <c r="B477" t="s">
-        <v>833</v>
-      </c>
       <c r="C477" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D477" t="s">
         <v>18</v>
@@ -15393,18 +15391,18 @@
         <v>11</v>
       </c>
       <c r="F477" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G477" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="478" hidden="1" spans="1:7">
       <c r="A478" t="s">
+        <v>831</v>
+      </c>
+      <c r="B478" t="s">
         <v>832</v>
-      </c>
-      <c r="B478" t="s">
-        <v>833</v>
       </c>
       <c r="C478" t="s">
         <v>212</v>
@@ -15416,18 +15414,18 @@
         <v>11</v>
       </c>
       <c r="F478" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G478" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="479" hidden="1" spans="1:7">
       <c r="A479" t="s">
+        <v>834</v>
+      </c>
+      <c r="B479" t="s">
         <v>835</v>
-      </c>
-      <c r="B479" t="s">
-        <v>836</v>
       </c>
       <c r="C479" t="s">
         <v>395</v>
@@ -15439,21 +15437,21 @@
         <v>11</v>
       </c>
       <c r="F479" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G479" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="480" hidden="1" spans="1:7">
       <c r="A480" t="s">
+        <v>831</v>
+      </c>
+      <c r="B480" t="s">
         <v>832</v>
       </c>
-      <c r="B480" t="s">
-        <v>833</v>
-      </c>
       <c r="C480" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D480" t="s">
         <v>23</v>
@@ -15462,21 +15460,21 @@
         <v>11</v>
       </c>
       <c r="F480" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G480" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="481" hidden="1" spans="1:7">
       <c r="A481" t="s">
+        <v>840</v>
+      </c>
+      <c r="B481" t="s">
         <v>841</v>
       </c>
-      <c r="B481" t="s">
+      <c r="C481" t="s">
         <v>842</v>
-      </c>
-      <c r="C481" t="s">
-        <v>843</v>
       </c>
       <c r="D481" t="s">
         <v>25</v>
@@ -15488,15 +15486,15 @@
         <v>651</v>
       </c>
       <c r="G481" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="482" hidden="1" spans="1:7">
       <c r="A482" t="s">
+        <v>843</v>
+      </c>
+      <c r="B482" t="s">
         <v>844</v>
-      </c>
-      <c r="B482" t="s">
-        <v>845</v>
       </c>
       <c r="C482" t="s">
         <v>207</v>
@@ -15511,18 +15509,18 @@
         <v>651</v>
       </c>
       <c r="G482" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="483" hidden="1" spans="1:7">
       <c r="A483" t="s">
+        <v>845</v>
+      </c>
+      <c r="B483" t="s">
         <v>846</v>
       </c>
-      <c r="B483" t="s">
-        <v>847</v>
-      </c>
       <c r="C483" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D483" t="s">
         <v>26</v>
@@ -15534,15 +15532,15 @@
         <v>22</v>
       </c>
       <c r="G483" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="484" hidden="1" spans="1:7">
       <c r="A484" t="s">
+        <v>847</v>
+      </c>
+      <c r="B484" t="s">
         <v>848</v>
-      </c>
-      <c r="B484" t="s">
-        <v>849</v>
       </c>
       <c r="C484" t="s">
         <v>349</v>
@@ -15557,15 +15555,15 @@
         <v>22</v>
       </c>
       <c r="G484" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="485" hidden="1" spans="1:7">
       <c r="A485" t="s">
+        <v>849</v>
+      </c>
+      <c r="B485" t="s">
         <v>850</v>
-      </c>
-      <c r="B485" t="s">
-        <v>851</v>
       </c>
       <c r="C485" t="s">
         <v>236</v>
@@ -15577,18 +15575,18 @@
         <v>36</v>
       </c>
       <c r="F485" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G485" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="486" hidden="1" spans="1:7">
       <c r="A486" t="s">
+        <v>852</v>
+      </c>
+      <c r="B486" t="s">
         <v>853</v>
-      </c>
-      <c r="B486" t="s">
-        <v>854</v>
       </c>
       <c r="C486" t="s">
         <v>236</v>
@@ -15603,15 +15601,15 @@
         <v>651</v>
       </c>
       <c r="G486" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="487" hidden="1" spans="1:7">
       <c r="A487" t="s">
+        <v>854</v>
+      </c>
+      <c r="B487" t="s">
         <v>855</v>
-      </c>
-      <c r="B487" t="s">
-        <v>856</v>
       </c>
       <c r="C487" t="s">
         <v>236</v>
@@ -15626,15 +15624,15 @@
         <v>651</v>
       </c>
       <c r="G487" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="488" hidden="1" spans="1:7">
       <c r="A488" t="s">
+        <v>847</v>
+      </c>
+      <c r="B488" t="s">
         <v>848</v>
-      </c>
-      <c r="B488" t="s">
-        <v>849</v>
       </c>
       <c r="C488" t="s">
         <v>349</v>
@@ -15649,15 +15647,15 @@
         <v>22</v>
       </c>
       <c r="G488" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="489" hidden="1" spans="1:7">
       <c r="A489" t="s">
+        <v>849</v>
+      </c>
+      <c r="B489" t="s">
         <v>850</v>
-      </c>
-      <c r="B489" t="s">
-        <v>851</v>
       </c>
       <c r="C489" t="s">
         <v>236</v>
@@ -15669,18 +15667,18 @@
         <v>36</v>
       </c>
       <c r="F489" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G489" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="490" hidden="1" spans="1:7">
       <c r="A490" t="s">
+        <v>856</v>
+      </c>
+      <c r="B490" t="s">
         <v>857</v>
-      </c>
-      <c r="B490" t="s">
-        <v>858</v>
       </c>
       <c r="C490" t="s">
         <v>349</v>
@@ -15695,18 +15693,18 @@
         <v>651</v>
       </c>
       <c r="G490" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="491" hidden="1" spans="1:7">
       <c r="A491" t="s">
+        <v>858</v>
+      </c>
+      <c r="B491" t="s">
         <v>859</v>
       </c>
-      <c r="B491" t="s">
+      <c r="C491" t="s">
         <v>860</v>
-      </c>
-      <c r="C491" t="s">
-        <v>861</v>
       </c>
       <c r="D491" t="s">
         <v>18</v>
@@ -15718,18 +15716,18 @@
         <v>651</v>
       </c>
       <c r="G491" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="492" hidden="1" spans="1:7">
       <c r="A492" t="s">
+        <v>861</v>
+      </c>
+      <c r="B492" t="s">
         <v>862</v>
       </c>
-      <c r="B492" t="s">
-        <v>863</v>
-      </c>
       <c r="C492" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D492" t="s">
         <v>23</v>
@@ -15741,18 +15739,18 @@
         <v>651</v>
       </c>
       <c r="G492" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="493" hidden="1" spans="1:7">
       <c r="A493" t="s">
+        <v>840</v>
+      </c>
+      <c r="B493" t="s">
         <v>841</v>
       </c>
-      <c r="B493" t="s">
+      <c r="C493" t="s">
         <v>842</v>
-      </c>
-      <c r="C493" t="s">
-        <v>843</v>
       </c>
       <c r="D493" t="s">
         <v>25</v>
@@ -15764,15 +15762,15 @@
         <v>651</v>
       </c>
       <c r="G493" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="494" hidden="1" spans="1:7">
       <c r="A494" t="s">
+        <v>863</v>
+      </c>
+      <c r="B494" t="s">
         <v>864</v>
-      </c>
-      <c r="B494" t="s">
-        <v>865</v>
       </c>
       <c r="C494" t="s">
         <v>294</v>
@@ -15787,18 +15785,18 @@
         <v>22</v>
       </c>
       <c r="G494" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="495" hidden="1" spans="1:7">
       <c r="A495" t="s">
+        <v>865</v>
+      </c>
+      <c r="B495" t="s">
         <v>866</v>
       </c>
-      <c r="B495" t="s">
+      <c r="C495" t="s">
         <v>867</v>
-      </c>
-      <c r="C495" t="s">
-        <v>868</v>
       </c>
       <c r="D495" t="s">
         <v>18</v>
@@ -15810,18 +15808,18 @@
         <v>651</v>
       </c>
       <c r="G495" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="496" hidden="1" spans="1:7">
       <c r="A496" t="s">
+        <v>868</v>
+      </c>
+      <c r="B496" t="s">
         <v>869</v>
       </c>
-      <c r="B496" t="s">
-        <v>870</v>
-      </c>
       <c r="C496" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D496" t="s">
         <v>23</v>
@@ -15833,18 +15831,18 @@
         <v>651</v>
       </c>
       <c r="G496" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="497" hidden="1" spans="1:7">
       <c r="A497" t="s">
+        <v>870</v>
+      </c>
+      <c r="B497" t="s">
         <v>871</v>
       </c>
-      <c r="B497" t="s">
-        <v>872</v>
-      </c>
       <c r="C497" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D497" t="s">
         <v>25</v>
@@ -15856,15 +15854,15 @@
         <v>22</v>
       </c>
       <c r="G497" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="498" hidden="1" spans="1:7">
       <c r="A498" t="s">
+        <v>872</v>
+      </c>
+      <c r="B498" t="s">
         <v>873</v>
-      </c>
-      <c r="B498" t="s">
-        <v>874</v>
       </c>
       <c r="C498" t="s">
         <v>294</v>
@@ -15879,18 +15877,18 @@
         <v>651</v>
       </c>
       <c r="G498" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="499" hidden="1" spans="1:7">
       <c r="A499" t="s">
+        <v>870</v>
+      </c>
+      <c r="B499" t="s">
         <v>871</v>
       </c>
-      <c r="B499" t="s">
-        <v>872</v>
-      </c>
       <c r="C499" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D499" t="s">
         <v>26</v>
@@ -15902,15 +15900,15 @@
         <v>22</v>
       </c>
       <c r="G499" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="500" hidden="1" spans="1:7">
       <c r="A500" t="s">
+        <v>863</v>
+      </c>
+      <c r="B500" t="s">
         <v>864</v>
-      </c>
-      <c r="B500" t="s">
-        <v>865</v>
       </c>
       <c r="C500" t="s">
         <v>294</v>
@@ -15925,15 +15923,15 @@
         <v>22</v>
       </c>
       <c r="G500" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="501" hidden="1" spans="1:7">
       <c r="A501" t="s">
+        <v>874</v>
+      </c>
+      <c r="B501" t="s">
         <v>875</v>
-      </c>
-      <c r="B501" t="s">
-        <v>876</v>
       </c>
       <c r="C501" t="s">
         <v>349</v>
@@ -15948,15 +15946,15 @@
         <v>365</v>
       </c>
       <c r="G501" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="502" hidden="1" spans="1:7">
       <c r="A502" t="s">
+        <v>877</v>
+      </c>
+      <c r="B502" t="s">
         <v>878</v>
-      </c>
-      <c r="B502" t="s">
-        <v>879</v>
       </c>
       <c r="C502" t="s">
         <v>364</v>
@@ -15968,18 +15966,18 @@
         <v>11</v>
       </c>
       <c r="F502" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G502" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="503" hidden="1" spans="1:7">
       <c r="A503" t="s">
+        <v>880</v>
+      </c>
+      <c r="B503" t="s">
         <v>881</v>
-      </c>
-      <c r="B503" t="s">
-        <v>882</v>
       </c>
       <c r="C503" t="s">
         <v>392</v>
@@ -15991,18 +15989,18 @@
         <v>11</v>
       </c>
       <c r="F503" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G503" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="504" hidden="1" spans="1:7">
       <c r="A504" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B504" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C504" t="s">
         <v>364</v>
@@ -16014,18 +16012,18 @@
         <v>11</v>
       </c>
       <c r="F504" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G504" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="505" hidden="1" spans="1:7">
       <c r="A505" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B505" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C505" t="s">
         <v>392</v>
@@ -16037,18 +16035,18 @@
         <v>11</v>
       </c>
       <c r="F505" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G505" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="506" hidden="1" spans="1:7">
       <c r="A506" t="s">
+        <v>886</v>
+      </c>
+      <c r="B506" t="s">
         <v>887</v>
-      </c>
-      <c r="B506" t="s">
-        <v>888</v>
       </c>
       <c r="C506" t="s">
         <v>285</v>
@@ -16063,15 +16061,15 @@
         <v>365</v>
       </c>
       <c r="G506" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="507" hidden="1" spans="1:7">
       <c r="A507" t="s">
+        <v>888</v>
+      </c>
+      <c r="B507" t="s">
         <v>889</v>
-      </c>
-      <c r="B507" t="s">
-        <v>890</v>
       </c>
       <c r="C507" t="s">
         <v>349</v>
@@ -16086,18 +16084,18 @@
         <v>365</v>
       </c>
       <c r="G507" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="508" hidden="1" spans="1:7">
       <c r="A508" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B508" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C508" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D508" t="s">
         <v>26</v>
@@ -16109,7 +16107,7 @@
         <v>22</v>
       </c>
       <c r="G508" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="509" hidden="1" spans="1:7">
@@ -16117,7 +16115,7 @@
         <v>401</v>
       </c>
       <c r="B509" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C509" t="s">
         <v>353</v>
@@ -16132,15 +16130,15 @@
         <v>365</v>
       </c>
       <c r="G509" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="510" hidden="1" spans="1:7">
       <c r="A510" t="s">
+        <v>892</v>
+      </c>
+      <c r="B510" t="s">
         <v>893</v>
-      </c>
-      <c r="B510" t="s">
-        <v>894</v>
       </c>
       <c r="C510" t="s">
         <v>395</v>
@@ -16152,18 +16150,18 @@
         <v>36</v>
       </c>
       <c r="F510" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G510" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="511" hidden="1" spans="1:7">
       <c r="A511" t="s">
+        <v>895</v>
+      </c>
+      <c r="B511" t="s">
         <v>896</v>
-      </c>
-      <c r="B511" t="s">
-        <v>897</v>
       </c>
       <c r="C511" t="s">
         <v>364</v>
@@ -16175,18 +16173,18 @@
         <v>36</v>
       </c>
       <c r="F511" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G511" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="512" hidden="1" spans="1:7">
       <c r="A512" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B512" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C512" t="s">
         <v>395</v>
@@ -16198,18 +16196,18 @@
         <v>36</v>
       </c>
       <c r="F512" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G512" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="513" hidden="1" spans="1:7">
       <c r="A513" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B513" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C513" t="s">
         <v>364</v>
@@ -16221,18 +16219,18 @@
         <v>36</v>
       </c>
       <c r="F513" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G513" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="514" hidden="1" spans="1:7">
       <c r="A514" t="s">
+        <v>900</v>
+      </c>
+      <c r="B514" t="s">
         <v>901</v>
-      </c>
-      <c r="B514" t="s">
-        <v>902</v>
       </c>
       <c r="C514" t="s">
         <v>392</v>
@@ -16247,7 +16245,7 @@
         <v>365</v>
       </c>
       <c r="G514" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="515" hidden="1" spans="1:7">
@@ -16255,7 +16253,7 @@
         <v>399</v>
       </c>
       <c r="B515" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C515" t="s">
         <v>353</v>
@@ -16270,15 +16268,15 @@
         <v>365</v>
       </c>
       <c r="G515" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="516" hidden="1" spans="1:7">
       <c r="A516" t="s">
+        <v>903</v>
+      </c>
+      <c r="B516" t="s">
         <v>904</v>
-      </c>
-      <c r="B516" t="s">
-        <v>905</v>
       </c>
       <c r="C516" t="s">
         <v>412</v>
@@ -16293,15 +16291,15 @@
         <v>365</v>
       </c>
       <c r="G516" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="517" hidden="1" spans="1:7">
       <c r="A517" t="s">
+        <v>905</v>
+      </c>
+      <c r="B517" t="s">
         <v>906</v>
-      </c>
-      <c r="B517" t="s">
-        <v>907</v>
       </c>
       <c r="C517" t="s">
         <v>395</v>
@@ -16313,18 +16311,18 @@
         <v>47</v>
       </c>
       <c r="F517" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G517" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="518" hidden="1" spans="1:7">
       <c r="A518" t="s">
+        <v>907</v>
+      </c>
+      <c r="B518" t="s">
         <v>908</v>
-      </c>
-      <c r="B518" t="s">
-        <v>909</v>
       </c>
       <c r="C518" t="s">
         <v>395</v>
@@ -16336,18 +16334,18 @@
         <v>47</v>
       </c>
       <c r="F518" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G518" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="519" hidden="1" spans="1:7">
       <c r="A519" t="s">
+        <v>909</v>
+      </c>
+      <c r="B519" t="s">
         <v>910</v>
-      </c>
-      <c r="B519" t="s">
-        <v>911</v>
       </c>
       <c r="C519" t="s">
         <v>308</v>
@@ -16362,15 +16360,15 @@
         <v>365</v>
       </c>
       <c r="G519" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="520" hidden="1" spans="1:7">
       <c r="A520" t="s">
+        <v>911</v>
+      </c>
+      <c r="B520" t="s">
         <v>912</v>
-      </c>
-      <c r="B520" t="s">
-        <v>913</v>
       </c>
       <c r="C520" t="s">
         <v>530</v>
@@ -16385,15 +16383,15 @@
         <v>365</v>
       </c>
       <c r="G520" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="521" hidden="1" spans="1:7">
       <c r="A521" t="s">
+        <v>913</v>
+      </c>
+      <c r="B521" t="s">
         <v>914</v>
-      </c>
-      <c r="B521" t="s">
-        <v>915</v>
       </c>
       <c r="C521" t="s">
         <v>308</v>
@@ -16408,7 +16406,7 @@
         <v>365</v>
       </c>
       <c r="G521" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="522" hidden="1" spans="1:7">
@@ -16416,7 +16414,7 @@
         <v>360</v>
       </c>
       <c r="B522" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C522" t="s">
         <v>262</v>
@@ -16428,18 +16426,18 @@
         <v>11</v>
       </c>
       <c r="F522" t="s">
+        <v>916</v>
+      </c>
+      <c r="G522" t="s">
         <v>917</v>
-      </c>
-      <c r="G522" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="523" hidden="1" spans="1:7">
       <c r="A523" t="s">
+        <v>918</v>
+      </c>
+      <c r="B523" t="s">
         <v>919</v>
-      </c>
-      <c r="B523" t="s">
-        <v>920</v>
       </c>
       <c r="C523" t="s">
         <v>338</v>
@@ -16451,18 +16449,18 @@
         <v>11</v>
       </c>
       <c r="F523" t="s">
+        <v>916</v>
+      </c>
+      <c r="G523" t="s">
         <v>917</v>
-      </c>
-      <c r="G523" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="524" hidden="1" spans="1:7">
       <c r="A524" t="s">
+        <v>920</v>
+      </c>
+      <c r="B524" t="s">
         <v>921</v>
-      </c>
-      <c r="B524" t="s">
-        <v>922</v>
       </c>
       <c r="C524" t="s">
         <v>338</v>
@@ -16474,18 +16472,18 @@
         <v>11</v>
       </c>
       <c r="F524" t="s">
+        <v>916</v>
+      </c>
+      <c r="G524" t="s">
         <v>917</v>
-      </c>
-      <c r="G524" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="525" hidden="1" spans="1:7">
       <c r="A525" t="s">
+        <v>922</v>
+      </c>
+      <c r="B525" t="s">
         <v>923</v>
-      </c>
-      <c r="B525" t="s">
-        <v>924</v>
       </c>
       <c r="C525" t="s">
         <v>285</v>
@@ -16497,21 +16495,21 @@
         <v>11</v>
       </c>
       <c r="F525" t="s">
+        <v>916</v>
+      </c>
+      <c r="G525" t="s">
         <v>917</v>
-      </c>
-      <c r="G525" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="526" hidden="1" spans="1:7">
       <c r="A526" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B526" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C526" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D526" t="s">
         <v>26</v>
@@ -16523,7 +16521,7 @@
         <v>22</v>
       </c>
       <c r="G526" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="527" hidden="1" spans="1:7">
@@ -16531,7 +16529,7 @@
         <v>339</v>
       </c>
       <c r="B527" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C527" t="s">
         <v>262</v>
@@ -16543,18 +16541,18 @@
         <v>36</v>
       </c>
       <c r="F527" t="s">
+        <v>916</v>
+      </c>
+      <c r="G527" t="s">
         <v>917</v>
-      </c>
-      <c r="G527" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="528" hidden="1" spans="1:7">
       <c r="A528" t="s">
+        <v>926</v>
+      </c>
+      <c r="B528" t="s">
         <v>927</v>
-      </c>
-      <c r="B528" t="s">
-        <v>928</v>
       </c>
       <c r="C528" t="s">
         <v>375</v>
@@ -16566,18 +16564,18 @@
         <v>36</v>
       </c>
       <c r="F528" t="s">
+        <v>916</v>
+      </c>
+      <c r="G528" t="s">
         <v>917</v>
-      </c>
-      <c r="G528" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="529" hidden="1" spans="1:7">
       <c r="A529" t="s">
+        <v>928</v>
+      </c>
+      <c r="B529" t="s">
         <v>929</v>
-      </c>
-      <c r="B529" t="s">
-        <v>930</v>
       </c>
       <c r="C529" t="s">
         <v>375</v>
@@ -16589,18 +16587,18 @@
         <v>36</v>
       </c>
       <c r="F529" t="s">
+        <v>916</v>
+      </c>
+      <c r="G529" t="s">
         <v>917</v>
-      </c>
-      <c r="G529" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="530" hidden="1" spans="1:7">
       <c r="A530" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B530" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C530" t="s">
         <v>530</v>
@@ -16612,21 +16610,21 @@
         <v>36</v>
       </c>
       <c r="F530" t="s">
+        <v>916</v>
+      </c>
+      <c r="G530" t="s">
         <v>917</v>
-      </c>
-      <c r="G530" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="531" hidden="1" spans="1:7">
       <c r="A531" t="s">
+        <v>931</v>
+      </c>
+      <c r="B531" t="s">
         <v>932</v>
       </c>
-      <c r="B531" t="s">
-        <v>933</v>
-      </c>
       <c r="C531" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D531" t="s">
         <v>26</v>
@@ -16635,18 +16633,18 @@
         <v>36</v>
       </c>
       <c r="F531" t="s">
+        <v>916</v>
+      </c>
+      <c r="G531" t="s">
         <v>917</v>
-      </c>
-      <c r="G531" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="532" hidden="1" spans="1:7">
       <c r="A532" t="s">
+        <v>933</v>
+      </c>
+      <c r="B532" t="s">
         <v>934</v>
-      </c>
-      <c r="B532" t="s">
-        <v>935</v>
       </c>
       <c r="C532" t="s">
         <v>372</v>
@@ -16658,18 +16656,18 @@
         <v>47</v>
       </c>
       <c r="F532" t="s">
+        <v>916</v>
+      </c>
+      <c r="G532" t="s">
         <v>917</v>
-      </c>
-      <c r="G532" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="533" hidden="1" spans="1:7">
       <c r="A533" t="s">
+        <v>935</v>
+      </c>
+      <c r="B533" t="s">
         <v>936</v>
-      </c>
-      <c r="B533" t="s">
-        <v>937</v>
       </c>
       <c r="C533" t="s">
         <v>353</v>
@@ -16681,18 +16679,18 @@
         <v>47</v>
       </c>
       <c r="F533" t="s">
+        <v>916</v>
+      </c>
+      <c r="G533" t="s">
         <v>917</v>
-      </c>
-      <c r="G533" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="534" hidden="1" spans="1:7">
       <c r="A534" t="s">
+        <v>937</v>
+      </c>
+      <c r="B534" t="s">
         <v>938</v>
-      </c>
-      <c r="B534" t="s">
-        <v>939</v>
       </c>
       <c r="C534" t="s">
         <v>353</v>
@@ -16704,18 +16702,18 @@
         <v>47</v>
       </c>
       <c r="F534" t="s">
+        <v>916</v>
+      </c>
+      <c r="G534" t="s">
         <v>917</v>
-      </c>
-      <c r="G534" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="535" hidden="1" spans="1:7">
       <c r="A535" t="s">
+        <v>939</v>
+      </c>
+      <c r="B535" t="s">
         <v>940</v>
-      </c>
-      <c r="B535" t="s">
-        <v>941</v>
       </c>
       <c r="C535" t="s">
         <v>372</v>
@@ -16727,18 +16725,18 @@
         <v>47</v>
       </c>
       <c r="F535" t="s">
+        <v>916</v>
+      </c>
+      <c r="G535" t="s">
         <v>917</v>
-      </c>
-      <c r="G535" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="536" hidden="1" spans="1:7">
       <c r="A536" t="s">
+        <v>941</v>
+      </c>
+      <c r="B536" t="s">
         <v>942</v>
-      </c>
-      <c r="B536" t="s">
-        <v>943</v>
       </c>
       <c r="C536" t="s">
         <v>262</v>
@@ -16750,18 +16748,18 @@
         <v>54</v>
       </c>
       <c r="F536" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G536" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="537" hidden="1" spans="1:7">
       <c r="A537" t="s">
+        <v>944</v>
+      </c>
+      <c r="B537" t="s">
         <v>945</v>
-      </c>
-      <c r="B537" t="s">
-        <v>946</v>
       </c>
       <c r="C537" t="s">
         <v>384</v>
@@ -16773,21 +16771,21 @@
         <v>54</v>
       </c>
       <c r="F537" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G537" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="538" hidden="1" spans="1:7">
       <c r="A538" t="s">
+        <v>947</v>
+      </c>
+      <c r="B538" t="s">
         <v>948</v>
       </c>
-      <c r="B538" t="s">
-        <v>949</v>
-      </c>
       <c r="C538" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D538" t="s">
         <v>18</v>
@@ -16796,18 +16794,18 @@
         <v>54</v>
       </c>
       <c r="F538" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G538" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="539" hidden="1" spans="1:7">
       <c r="A539" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B539" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C539" t="s">
         <v>384</v>
@@ -16819,21 +16817,21 @@
         <v>54</v>
       </c>
       <c r="F539" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G539" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="540" hidden="1" spans="1:7">
       <c r="A540" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B540" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C540" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D540" t="s">
         <v>23</v>
@@ -16842,18 +16840,18 @@
         <v>54</v>
       </c>
       <c r="F540" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G540" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="541" hidden="1" spans="1:7">
       <c r="A541" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B541" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C541" t="s">
         <v>262</v>
@@ -16865,21 +16863,21 @@
         <v>54</v>
       </c>
       <c r="F541" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G541" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="542" hidden="1" spans="1:7">
       <c r="A542" t="s">
+        <v>956</v>
+      </c>
+      <c r="B542" t="s">
         <v>957</v>
       </c>
-      <c r="B542" t="s">
+      <c r="C542" t="s">
         <v>958</v>
-      </c>
-      <c r="C542" t="s">
-        <v>959</v>
       </c>
       <c r="D542" t="s">
         <v>10</v>
@@ -16891,18 +16889,18 @@
         <v>274</v>
       </c>
       <c r="G542" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="543" hidden="1" spans="1:7">
       <c r="A543" t="s">
+        <v>960</v>
+      </c>
+      <c r="B543" t="s">
         <v>961</v>
       </c>
-      <c r="B543" t="s">
-        <v>962</v>
-      </c>
       <c r="C543" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D543" t="s">
         <v>18</v>
@@ -16911,21 +16909,21 @@
         <v>11</v>
       </c>
       <c r="F543" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G543" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="544" hidden="1" spans="1:7">
       <c r="A544" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B544" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C544" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D544" t="s">
         <v>23</v>
@@ -16934,21 +16932,21 @@
         <v>11</v>
       </c>
       <c r="F544" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G544" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="545" hidden="1" spans="1:7">
       <c r="A545" t="s">
+        <v>964</v>
+      </c>
+      <c r="B545" t="s">
         <v>965</v>
       </c>
-      <c r="B545" t="s">
-        <v>966</v>
-      </c>
       <c r="C545" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D545" t="s">
         <v>25</v>
@@ -16960,18 +16958,18 @@
         <v>274</v>
       </c>
       <c r="G545" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="546" hidden="1" spans="1:7">
       <c r="A546" t="s">
+        <v>966</v>
+      </c>
+      <c r="B546" t="s">
         <v>967</v>
       </c>
-      <c r="B546" t="s">
-        <v>968</v>
-      </c>
       <c r="C546" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D546" t="s">
         <v>26</v>
@@ -16983,18 +16981,18 @@
         <v>274</v>
       </c>
       <c r="G546" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="547" hidden="1" spans="1:7">
       <c r="A547" t="s">
+        <v>968</v>
+      </c>
+      <c r="B547" t="s">
         <v>969</v>
       </c>
-      <c r="B547" t="s">
-        <v>970</v>
-      </c>
       <c r="C547" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D547" t="s">
         <v>26</v>
@@ -17006,15 +17004,15 @@
         <v>274</v>
       </c>
       <c r="G547" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="548" hidden="1" spans="1:7">
       <c r="A548" t="s">
+        <v>970</v>
+      </c>
+      <c r="B548" t="s">
         <v>971</v>
-      </c>
-      <c r="B548" t="s">
-        <v>972</v>
       </c>
       <c r="C548" t="s">
         <v>591</v>
@@ -17026,21 +17024,21 @@
         <v>36</v>
       </c>
       <c r="F548" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G548" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="549" hidden="1" spans="1:7">
       <c r="A549" t="s">
+        <v>973</v>
+      </c>
+      <c r="B549" t="s">
         <v>974</v>
       </c>
-      <c r="B549" t="s">
+      <c r="C549" t="s">
         <v>975</v>
-      </c>
-      <c r="C549" t="s">
-        <v>976</v>
       </c>
       <c r="D549" t="s">
         <v>10</v>
@@ -17049,18 +17047,18 @@
         <v>36</v>
       </c>
       <c r="F549" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G549" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="550" hidden="1" spans="1:7">
       <c r="A550" t="s">
+        <v>976</v>
+      </c>
+      <c r="B550" t="s">
         <v>977</v>
-      </c>
-      <c r="B550" t="s">
-        <v>978</v>
       </c>
       <c r="C550" t="s">
         <v>686</v>
@@ -17075,15 +17073,15 @@
         <v>274</v>
       </c>
       <c r="G550" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="551" hidden="1" spans="1:7">
       <c r="A551" t="s">
+        <v>978</v>
+      </c>
+      <c r="B551" t="s">
         <v>979</v>
-      </c>
-      <c r="B551" t="s">
-        <v>980</v>
       </c>
       <c r="C551" t="s">
         <v>686</v>
@@ -17098,18 +17096,18 @@
         <v>274</v>
       </c>
       <c r="G551" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="552" hidden="1" spans="1:7">
       <c r="A552" t="s">
+        <v>980</v>
+      </c>
+      <c r="B552" t="s">
         <v>981</v>
       </c>
-      <c r="B552" t="s">
-        <v>982</v>
-      </c>
       <c r="C552" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D552" t="s">
         <v>25</v>
@@ -17121,15 +17119,15 @@
         <v>274</v>
       </c>
       <c r="G552" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="553" hidden="1" spans="1:7">
       <c r="A553" t="s">
+        <v>970</v>
+      </c>
+      <c r="B553" t="s">
         <v>971</v>
-      </c>
-      <c r="B553" t="s">
-        <v>972</v>
       </c>
       <c r="C553" t="s">
         <v>591</v>
@@ -17141,21 +17139,21 @@
         <v>36</v>
       </c>
       <c r="F553" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G553" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="554" hidden="1" spans="1:7">
       <c r="A554" t="s">
+        <v>973</v>
+      </c>
+      <c r="B554" t="s">
         <v>974</v>
       </c>
-      <c r="B554" t="s">
+      <c r="C554" t="s">
         <v>975</v>
-      </c>
-      <c r="C554" t="s">
-        <v>976</v>
       </c>
       <c r="D554" t="s">
         <v>26</v>
@@ -17164,18 +17162,18 @@
         <v>36</v>
       </c>
       <c r="F554" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G554" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="555" hidden="1" spans="1:7">
       <c r="A555" t="s">
+        <v>982</v>
+      </c>
+      <c r="B555" t="s">
         <v>983</v>
-      </c>
-      <c r="B555" t="s">
-        <v>984</v>
       </c>
       <c r="C555" t="s">
         <v>349</v>
@@ -17190,18 +17188,18 @@
         <v>651</v>
       </c>
       <c r="G555" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="556" hidden="1" spans="1:7">
       <c r="A556" t="s">
+        <v>984</v>
+      </c>
+      <c r="B556" t="s">
         <v>985</v>
       </c>
-      <c r="B556" t="s">
-        <v>986</v>
-      </c>
       <c r="C556" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D556" t="s">
         <v>18</v>
@@ -17210,21 +17208,21 @@
         <v>47</v>
       </c>
       <c r="F556" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G556" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="557" hidden="1" spans="1:7">
       <c r="A557" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B557" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C557" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D557" t="s">
         <v>23</v>
@@ -17233,21 +17231,21 @@
         <v>47</v>
       </c>
       <c r="F557" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G557" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="558" hidden="1" spans="1:7">
       <c r="A558" t="s">
+        <v>988</v>
+      </c>
+      <c r="B558" t="s">
         <v>989</v>
       </c>
-      <c r="B558" t="s">
-        <v>990</v>
-      </c>
       <c r="C558" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D558" t="s">
         <v>25</v>
@@ -17259,18 +17257,18 @@
         <v>274</v>
       </c>
       <c r="G558" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="559" hidden="1" spans="1:7">
       <c r="A559" t="s">
+        <v>990</v>
+      </c>
+      <c r="B559" t="s">
         <v>991</v>
       </c>
-      <c r="B559" t="s">
-        <v>992</v>
-      </c>
       <c r="C559" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D559" t="s">
         <v>26</v>
@@ -17282,15 +17280,15 @@
         <v>274</v>
       </c>
       <c r="G559" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="560" hidden="1" spans="1:7">
       <c r="A560" t="s">
+        <v>992</v>
+      </c>
+      <c r="B560" t="s">
         <v>993</v>
-      </c>
-      <c r="B560" t="s">
-        <v>994</v>
       </c>
       <c r="C560" t="s">
         <v>686</v>
@@ -17302,21 +17300,21 @@
         <v>54</v>
       </c>
       <c r="F560" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G560" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="561" hidden="1" spans="1:7">
       <c r="A561" t="s">
+        <v>992</v>
+      </c>
+      <c r="B561" t="s">
         <v>993</v>
       </c>
-      <c r="B561" t="s">
-        <v>994</v>
-      </c>
       <c r="C561" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D561" t="s">
         <v>18</v>
@@ -17325,18 +17323,18 @@
         <v>54</v>
       </c>
       <c r="F561" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G561" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="562" hidden="1" spans="1:7">
       <c r="A562" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B562" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C562" t="s">
         <v>686</v>
@@ -17348,21 +17346,21 @@
         <v>54</v>
       </c>
       <c r="F562" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G562" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="563" hidden="1" spans="1:7">
       <c r="A563" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B563" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C563" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D563" t="s">
         <v>23</v>
@@ -17371,18 +17369,18 @@
         <v>54</v>
       </c>
       <c r="F563" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G563" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="564" hidden="1" spans="1:7">
       <c r="A564" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B564" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C564" t="s">
         <v>530</v>
@@ -17397,18 +17395,18 @@
         <v>365</v>
       </c>
       <c r="G564" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="565" hidden="1" spans="1:7">
       <c r="A565" t="s">
+        <v>998</v>
+      </c>
+      <c r="B565" t="s">
         <v>999</v>
       </c>
-      <c r="B565" t="s">
-        <v>1000</v>
-      </c>
       <c r="C565" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D565" t="s">
         <v>26</v>
@@ -17420,15 +17418,15 @@
         <v>274</v>
       </c>
       <c r="G565" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="566" hidden="1" spans="1:7">
       <c r="A566" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B566" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C566" t="s">
         <v>530</v>
@@ -17440,18 +17438,18 @@
         <v>11</v>
       </c>
       <c r="F566" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G566" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="567" hidden="1" spans="1:7">
       <c r="A567" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B567" t="s">
         <v>1003</v>
-      </c>
-      <c r="B567" t="s">
-        <v>1004</v>
       </c>
       <c r="C567" t="s">
         <v>384</v>
@@ -17463,18 +17461,18 @@
         <v>11</v>
       </c>
       <c r="F567" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G567" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="568" hidden="1" spans="1:7">
       <c r="A568" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B568" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C568" t="s">
         <v>384</v>
@@ -17486,10 +17484,10 @@
         <v>11</v>
       </c>
       <c r="F568" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G568" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="569" hidden="1" spans="1:7">
@@ -17497,7 +17495,7 @@
         <v>360</v>
       </c>
       <c r="B569" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C569" t="s">
         <v>262</v>
@@ -17509,10 +17507,10 @@
         <v>11</v>
       </c>
       <c r="F569" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G569" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="570" hidden="1" spans="1:7">
@@ -17520,7 +17518,7 @@
         <v>339</v>
       </c>
       <c r="B570" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C570" t="s">
         <v>262</v>
@@ -17532,21 +17530,21 @@
         <v>11</v>
       </c>
       <c r="F570" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G570" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="571" hidden="1" spans="1:7">
       <c r="A571" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B571" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C571" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D571" t="s">
         <v>26</v>
@@ -17558,18 +17556,18 @@
         <v>22</v>
       </c>
       <c r="G571" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="572" hidden="1" spans="1:7">
       <c r="A572" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B572" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C572" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D572" t="s">
         <v>10</v>
@@ -17578,18 +17576,18 @@
         <v>36</v>
       </c>
       <c r="F572" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G572" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="573" hidden="1" spans="1:7">
       <c r="A573" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B573" t="s">
         <v>1010</v>
-      </c>
-      <c r="B573" t="s">
-        <v>1011</v>
       </c>
       <c r="C573" t="s">
         <v>280</v>
@@ -17601,18 +17599,18 @@
         <v>36</v>
       </c>
       <c r="F573" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G573" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="574" hidden="1" spans="1:7">
       <c r="A574" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B574" t="s">
         <v>1012</v>
-      </c>
-      <c r="B574" t="s">
-        <v>1013</v>
       </c>
       <c r="C574" t="s">
         <v>280</v>
@@ -17624,21 +17622,21 @@
         <v>36</v>
       </c>
       <c r="F574" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G574" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="575" hidden="1" spans="1:7">
       <c r="A575" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B575" t="s">
         <v>1014</v>
       </c>
-      <c r="B575" t="s">
-        <v>1015</v>
-      </c>
       <c r="C575" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D575" t="s">
         <v>25</v>
@@ -17647,18 +17645,18 @@
         <v>36</v>
       </c>
       <c r="F575" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G575" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="576" hidden="1" spans="1:7">
       <c r="A576" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B576" t="s">
         <v>1016</v>
-      </c>
-      <c r="B576" t="s">
-        <v>1017</v>
       </c>
       <c r="C576" t="s">
         <v>262</v>
@@ -17670,21 +17668,21 @@
         <v>36</v>
       </c>
       <c r="F576" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G576" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="577" hidden="1" spans="1:7">
       <c r="A577" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B577" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C577" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D577" t="s">
         <v>26</v>
@@ -17693,18 +17691,18 @@
         <v>36</v>
       </c>
       <c r="F577" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G577" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="578" hidden="1" spans="1:7">
       <c r="A578" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B578" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C578" t="s">
         <v>262</v>
@@ -17716,18 +17714,18 @@
         <v>36</v>
       </c>
       <c r="F578" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="G578" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="579" hidden="1" spans="1:7">
       <c r="A579" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B579" t="s">
         <v>1022</v>
-      </c>
-      <c r="B579" t="s">
-        <v>1023</v>
       </c>
       <c r="C579" t="s">
         <v>375</v>
@@ -17739,18 +17737,18 @@
         <v>47</v>
       </c>
       <c r="F579" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G579" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="580" hidden="1" spans="1:7">
       <c r="A580" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B580" t="s">
         <v>1024</v>
-      </c>
-      <c r="B580" t="s">
-        <v>1025</v>
       </c>
       <c r="C580" t="s">
         <v>372</v>
@@ -17762,18 +17760,18 @@
         <v>47</v>
       </c>
       <c r="F580" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G580" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="581" hidden="1" spans="1:7">
       <c r="A581" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B581" t="s">
         <v>1026</v>
-      </c>
-      <c r="B581" t="s">
-        <v>1027</v>
       </c>
       <c r="C581" t="s">
         <v>372</v>
@@ -17785,18 +17783,18 @@
         <v>47</v>
       </c>
       <c r="F581" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G581" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="582" hidden="1" spans="1:7">
       <c r="A582" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B582" t="s">
         <v>1028</v>
-      </c>
-      <c r="B582" t="s">
-        <v>1029</v>
       </c>
       <c r="C582" t="s">
         <v>375</v>
@@ -17808,10 +17806,10 @@
         <v>47</v>
       </c>
       <c r="F582" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G582" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="583" hidden="1" spans="1:7">
@@ -17819,7 +17817,7 @@
         <v>408</v>
       </c>
       <c r="B583" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C583" t="s">
         <v>158</v>
@@ -17831,18 +17829,18 @@
         <v>54</v>
       </c>
       <c r="F583" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G583" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="584" hidden="1" spans="1:7">
       <c r="A584" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B584" t="s">
         <v>1031</v>
-      </c>
-      <c r="B584" t="s">
-        <v>1032</v>
       </c>
       <c r="C584" t="s">
         <v>280</v>
@@ -17854,18 +17852,18 @@
         <v>54</v>
       </c>
       <c r="F584" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G584" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="585" hidden="1" spans="1:7">
       <c r="A585" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B585" t="s">
         <v>1033</v>
-      </c>
-      <c r="B585" t="s">
-        <v>1034</v>
       </c>
       <c r="C585" t="s">
         <v>280</v>
@@ -17877,18 +17875,18 @@
         <v>54</v>
       </c>
       <c r="F585" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G585" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="586" hidden="1" spans="1:7">
       <c r="A586" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B586" t="s">
         <v>1035</v>
-      </c>
-      <c r="B586" t="s">
-        <v>1036</v>
       </c>
       <c r="C586" t="s">
         <v>364</v>
@@ -17900,10 +17898,10 @@
         <v>11</v>
       </c>
       <c r="F586" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G586" t="s">
         <v>1037</v>
-      </c>
-      <c r="G586" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="587" hidden="1" spans="1:7">
@@ -17911,10 +17909,10 @@
         <v>100</v>
       </c>
       <c r="B587" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C587" t="s">
         <v>1039</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1040</v>
       </c>
       <c r="D587" t="s">
         <v>14</v>
@@ -17926,7 +17924,7 @@
         <v>416</v>
       </c>
       <c r="G587" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="588" hidden="1" spans="1:7">
@@ -17934,7 +17932,7 @@
         <v>100</v>
       </c>
       <c r="B588" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C588" t="s">
         <v>58</v>
@@ -17946,10 +17944,10 @@
         <v>11</v>
       </c>
       <c r="F588" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G588" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="589" hidden="1" spans="1:7">
@@ -17957,7 +17955,7 @@
         <v>103</v>
       </c>
       <c r="B589" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C589" t="s">
         <v>22</v>
@@ -17969,10 +17967,10 @@
         <v>11</v>
       </c>
       <c r="F589" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="G589" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="590" hidden="1" spans="1:7">
@@ -17980,7 +17978,7 @@
         <v>100</v>
       </c>
       <c r="B590" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C590" t="s">
         <v>58</v>
@@ -17992,10 +17990,10 @@
         <v>11</v>
       </c>
       <c r="F590" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G590" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="591" hidden="1" spans="1:7">
@@ -18003,7 +18001,7 @@
         <v>103</v>
       </c>
       <c r="B591" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C591" t="s">
         <v>22</v>
@@ -18015,18 +18013,18 @@
         <v>11</v>
       </c>
       <c r="F591" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G591" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="592" hidden="1" spans="1:7">
       <c r="A592" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B592" t="s">
         <v>1045</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1046</v>
       </c>
       <c r="C592" t="s">
         <v>38</v>
@@ -18038,10 +18036,10 @@
         <v>11</v>
       </c>
       <c r="F592" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G592" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="593" hidden="1" spans="1:7">
@@ -18049,7 +18047,7 @@
         <v>107</v>
       </c>
       <c r="B593" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C593" t="s">
         <v>58</v>
@@ -18061,10 +18059,10 @@
         <v>11</v>
       </c>
       <c r="F593" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G593" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="594" hidden="1" spans="1:7">
@@ -18072,7 +18070,7 @@
         <v>100</v>
       </c>
       <c r="B594" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C594" t="s">
         <v>58</v>
@@ -18087,7 +18085,7 @@
         <v>592</v>
       </c>
       <c r="G594" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="595" hidden="1" spans="1:7">
@@ -18095,7 +18093,7 @@
         <v>103</v>
       </c>
       <c r="B595" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C595" t="s">
         <v>38</v>
@@ -18110,18 +18108,18 @@
         <v>505</v>
       </c>
       <c r="G595" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="596" hidden="1" spans="1:7">
       <c r="A596" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B596" t="s">
         <v>1050</v>
       </c>
-      <c r="B596" t="s">
+      <c r="C596" t="s">
         <v>1051</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1052</v>
       </c>
       <c r="D596" t="s">
         <v>10</v>
@@ -18130,18 +18128,18 @@
         <v>27</v>
       </c>
       <c r="F596" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G596" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="597" hidden="1" spans="1:7">
       <c r="A597" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B597" t="s">
         <v>1054</v>
-      </c>
-      <c r="B597" t="s">
-        <v>1055</v>
       </c>
       <c r="C597" t="s">
         <v>236</v>
@@ -18153,21 +18151,21 @@
         <v>27</v>
       </c>
       <c r="F597" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G597" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="598" hidden="1" spans="1:7">
       <c r="A598" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B598" t="s">
         <v>1050</v>
       </c>
-      <c r="B598" t="s">
+      <c r="C598" t="s">
         <v>1051</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1052</v>
       </c>
       <c r="D598" t="s">
         <v>14</v>
@@ -18176,18 +18174,18 @@
         <v>27</v>
       </c>
       <c r="F598" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G598" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="599" hidden="1" spans="1:7">
       <c r="A599" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B599" t="s">
         <v>1054</v>
-      </c>
-      <c r="B599" t="s">
-        <v>1055</v>
       </c>
       <c r="C599" t="s">
         <v>236</v>
@@ -18199,18 +18197,18 @@
         <v>27</v>
       </c>
       <c r="F599" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G599" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="600" hidden="1" spans="1:7">
       <c r="A600" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B600" t="s">
         <v>1058</v>
-      </c>
-      <c r="B600" t="s">
-        <v>1059</v>
       </c>
       <c r="C600" t="s">
         <v>22</v>
@@ -18222,10 +18220,10 @@
         <v>27</v>
       </c>
       <c r="F600" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G600" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="601" hidden="1" spans="1:7">
@@ -18233,10 +18231,10 @@
         <v>120</v>
       </c>
       <c r="B601" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C601" t="s">
         <v>1061</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1062</v>
       </c>
       <c r="D601" t="s">
         <v>18</v>
@@ -18245,18 +18243,18 @@
         <v>27</v>
       </c>
       <c r="F601" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G601" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="602" hidden="1" spans="1:7">
       <c r="A602" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B602" t="s">
         <v>1058</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1059</v>
       </c>
       <c r="C602" t="s">
         <v>22</v>
@@ -18268,21 +18266,21 @@
         <v>27</v>
       </c>
       <c r="F602" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G602" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="603" hidden="1" spans="1:7">
       <c r="A603" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B603" t="s">
         <v>1050</v>
       </c>
-      <c r="B603" t="s">
+      <c r="C603" t="s">
         <v>1051</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1052</v>
       </c>
       <c r="D603" t="s">
         <v>25</v>
@@ -18291,21 +18289,21 @@
         <v>27</v>
       </c>
       <c r="F603" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G603" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="604" hidden="1" spans="1:7">
       <c r="A604" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B604" t="s">
         <v>1054</v>
       </c>
-      <c r="B604" t="s">
-        <v>1055</v>
-      </c>
       <c r="C604" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D604" t="s">
         <v>25</v>
@@ -18314,18 +18312,18 @@
         <v>27</v>
       </c>
       <c r="F604" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G604" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="605" hidden="1" spans="1:7">
       <c r="A605" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B605" t="s">
         <v>1058</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1059</v>
       </c>
       <c r="C605" t="s">
         <v>22</v>
@@ -18337,21 +18335,21 @@
         <v>27</v>
       </c>
       <c r="F605" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G605" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="606" hidden="1" spans="1:7">
       <c r="A606" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B606" t="s">
         <v>1050</v>
       </c>
-      <c r="B606" t="s">
+      <c r="C606" t="s">
         <v>1051</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1052</v>
       </c>
       <c r="D606" t="s">
         <v>26</v>
@@ -18360,21 +18358,21 @@
         <v>27</v>
       </c>
       <c r="F606" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G606" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="607" hidden="1" spans="1:7">
       <c r="A607" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B607" t="s">
         <v>1054</v>
       </c>
-      <c r="B607" t="s">
-        <v>1055</v>
-      </c>
       <c r="C607" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D607" t="s">
         <v>26</v>
@@ -18383,18 +18381,18 @@
         <v>27</v>
       </c>
       <c r="F607" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G607" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="608" hidden="1" spans="1:7">
       <c r="A608" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B608" t="s">
         <v>1058</v>
-      </c>
-      <c r="B608" t="s">
-        <v>1059</v>
       </c>
       <c r="C608" t="s">
         <v>22</v>
@@ -18406,18 +18404,18 @@
         <v>27</v>
       </c>
       <c r="F608" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G608" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="609" hidden="1" spans="1:7">
       <c r="A609" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B609" t="s">
         <v>1070</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1071</v>
       </c>
       <c r="C609" t="s">
         <v>375</v>
@@ -18429,10 +18427,10 @@
         <v>36</v>
       </c>
       <c r="F609" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G609" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="610" hidden="1" spans="1:7">
@@ -18440,7 +18438,7 @@
         <v>100</v>
       </c>
       <c r="B610" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C610" t="s">
         <v>58</v>
@@ -18452,21 +18450,21 @@
         <v>36</v>
       </c>
       <c r="F610" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G610" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="611" hidden="1" spans="1:7">
       <c r="A611" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B611" t="s">
         <v>1058</v>
       </c>
-      <c r="B611" t="s">
-        <v>1059</v>
-      </c>
       <c r="C611" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D611" t="s">
         <v>18</v>
@@ -18475,18 +18473,18 @@
         <v>36</v>
       </c>
       <c r="F611" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G611" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="612" hidden="1" spans="1:7">
       <c r="A612" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B612" t="s">
         <v>1050</v>
-      </c>
-      <c r="B612" t="s">
-        <v>1051</v>
       </c>
       <c r="C612" t="s">
         <v>22</v>
@@ -18498,18 +18496,18 @@
         <v>36</v>
       </c>
       <c r="F612" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G612" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="613" hidden="1" spans="1:7">
       <c r="A613" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B613" t="s">
         <v>1076</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1077</v>
       </c>
       <c r="C613" t="s">
         <v>587</v>
@@ -18521,21 +18519,21 @@
         <v>36</v>
       </c>
       <c r="F613" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G613" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="614" hidden="1" spans="1:7">
       <c r="A614" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B614" t="s">
         <v>1058</v>
       </c>
-      <c r="B614" t="s">
-        <v>1059</v>
-      </c>
       <c r="C614" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D614" t="s">
         <v>23</v>
@@ -18544,18 +18542,18 @@
         <v>36</v>
       </c>
       <c r="F614" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G614" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="615" hidden="1" spans="1:7">
       <c r="A615" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B615" t="s">
         <v>1050</v>
-      </c>
-      <c r="B615" t="s">
-        <v>1051</v>
       </c>
       <c r="C615" t="s">
         <v>22</v>
@@ -18567,18 +18565,18 @@
         <v>36</v>
       </c>
       <c r="F615" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G615" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="616" hidden="1" spans="1:7">
       <c r="A616" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B616" t="s">
         <v>1076</v>
-      </c>
-      <c r="B616" t="s">
-        <v>1077</v>
       </c>
       <c r="C616" t="s">
         <v>587</v>
@@ -18593,7 +18591,7 @@
         <v>592</v>
       </c>
       <c r="G616" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="617" hidden="1" spans="1:7">
@@ -18601,7 +18599,7 @@
         <v>113</v>
       </c>
       <c r="B617" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C617" t="s">
         <v>318</v>
@@ -18613,18 +18611,18 @@
         <v>36</v>
       </c>
       <c r="F617" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G617" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="618" hidden="1" spans="1:7">
       <c r="A618" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B618" t="s">
         <v>1076</v>
-      </c>
-      <c r="B618" t="s">
-        <v>1077</v>
       </c>
       <c r="C618" t="s">
         <v>22</v>
@@ -18636,10 +18634,10 @@
         <v>36</v>
       </c>
       <c r="F618" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G618" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="619" hidden="1" spans="1:7">
@@ -18647,7 +18645,7 @@
         <v>103</v>
       </c>
       <c r="B619" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C619" t="s">
         <v>22</v>
@@ -18662,15 +18660,15 @@
         <v>520</v>
       </c>
       <c r="G619" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="620" hidden="1" spans="1:7">
       <c r="A620" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B620" t="s">
         <v>1045</v>
-      </c>
-      <c r="B620" t="s">
-        <v>1046</v>
       </c>
       <c r="C620" t="s">
         <v>375</v>
@@ -18685,15 +18683,15 @@
         <v>486</v>
       </c>
       <c r="G620" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="621" hidden="1" spans="1:7">
       <c r="A621" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B621" t="s">
         <v>1081</v>
-      </c>
-      <c r="B621" t="s">
-        <v>1082</v>
       </c>
       <c r="C621" t="s">
         <v>566</v>
@@ -18705,10 +18703,10 @@
         <v>47</v>
       </c>
       <c r="F621" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G621" t="s">
         <v>1037</v>
-      </c>
-      <c r="G621" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="622" hidden="1" spans="1:7">
@@ -18716,7 +18714,7 @@
         <v>100</v>
       </c>
       <c r="B622" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C622" t="s">
         <v>58</v>
@@ -18728,10 +18726,10 @@
         <v>47</v>
       </c>
       <c r="F622" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G622" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="623" hidden="1" spans="1:7">
@@ -18739,10 +18737,10 @@
         <v>78</v>
       </c>
       <c r="B623" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C623" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D623" t="s">
         <v>18</v>
@@ -18751,21 +18749,21 @@
         <v>47</v>
       </c>
       <c r="F623" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G623" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="624" hidden="1" spans="1:7">
       <c r="A624" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B624" t="s">
         <v>1045</v>
       </c>
-      <c r="B624" t="s">
-        <v>1046</v>
-      </c>
       <c r="C624" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D624" t="s">
         <v>18</v>
@@ -18774,10 +18772,10 @@
         <v>47</v>
       </c>
       <c r="F624" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G624" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="625" hidden="1" spans="1:7">
@@ -18785,7 +18783,7 @@
         <v>574</v>
       </c>
       <c r="B625" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C625" t="s">
         <v>22</v>
@@ -18797,18 +18795,18 @@
         <v>47</v>
       </c>
       <c r="F625" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G625" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="626" hidden="1" spans="1:7">
       <c r="A626" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B626" t="s">
         <v>1045</v>
-      </c>
-      <c r="B626" t="s">
-        <v>1046</v>
       </c>
       <c r="C626" t="s">
         <v>542</v>
@@ -18820,10 +18818,10 @@
         <v>47</v>
       </c>
       <c r="F626" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G626" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="627" hidden="1" spans="1:7">
@@ -18831,10 +18829,10 @@
         <v>78</v>
       </c>
       <c r="B627" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C627" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D627" t="s">
         <v>23</v>
@@ -18843,10 +18841,10 @@
         <v>47</v>
       </c>
       <c r="F627" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G627" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="628" hidden="1" spans="1:7">
@@ -18854,7 +18852,7 @@
         <v>574</v>
       </c>
       <c r="B628" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C628" t="s">
         <v>22</v>
@@ -18866,10 +18864,10 @@
         <v>47</v>
       </c>
       <c r="F628" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G628" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="629" hidden="1" spans="1:7">
@@ -18877,10 +18875,10 @@
         <v>562</v>
       </c>
       <c r="B629" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C629" t="s">
         <v>1089</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1090</v>
       </c>
       <c r="D629" t="s">
         <v>25</v>
@@ -18889,10 +18887,10 @@
         <v>47</v>
       </c>
       <c r="F629" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G629" t="s">
         <v>1037</v>
-      </c>
-      <c r="G629" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="630" hidden="1" spans="1:7">
@@ -18900,7 +18898,7 @@
         <v>66</v>
       </c>
       <c r="B630" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C630" t="s">
         <v>38</v>
@@ -18912,10 +18910,10 @@
         <v>47</v>
       </c>
       <c r="F630" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G630" t="s">
         <v>1037</v>
-      </c>
-      <c r="G630" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="631" hidden="1" spans="1:7">
@@ -18923,10 +18921,10 @@
         <v>120</v>
       </c>
       <c r="B631" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C631" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D631" t="s">
         <v>10</v>
@@ -18935,18 +18933,18 @@
         <v>54</v>
       </c>
       <c r="F631" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G631" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="632" hidden="1" spans="1:7">
       <c r="A632" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B632" t="s">
         <v>1076</v>
-      </c>
-      <c r="B632" t="s">
-        <v>1077</v>
       </c>
       <c r="C632" t="s">
         <v>22</v>
@@ -18958,10 +18956,10 @@
         <v>54</v>
       </c>
       <c r="F632" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G632" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="633" hidden="1" spans="1:7">
@@ -18969,10 +18967,10 @@
         <v>120</v>
       </c>
       <c r="B633" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C633" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D633" t="s">
         <v>14</v>
@@ -18981,10 +18979,10 @@
         <v>54</v>
       </c>
       <c r="F633" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G633" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="634" hidden="1" spans="1:7">
@@ -18992,10 +18990,10 @@
         <v>120</v>
       </c>
       <c r="B634" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C634" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D634" t="s">
         <v>14</v>
@@ -19004,10 +19002,10 @@
         <v>54</v>
       </c>
       <c r="F634" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G634" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="635" hidden="1" spans="1:7">
@@ -19015,10 +19013,10 @@
         <v>120</v>
       </c>
       <c r="B635" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C635" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D635" t="s">
         <v>18</v>
@@ -19027,10 +19025,10 @@
         <v>54</v>
       </c>
       <c r="F635" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G635" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="636" hidden="1" spans="1:7">
@@ -19038,10 +19036,10 @@
         <v>100</v>
       </c>
       <c r="B636" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C636" t="s">
         <v>1039</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1040</v>
       </c>
       <c r="D636" t="s">
         <v>18</v>
@@ -19053,7 +19051,7 @@
         <v>416</v>
       </c>
       <c r="G636" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="637" hidden="1" spans="1:7">
@@ -19061,7 +19059,7 @@
         <v>574</v>
       </c>
       <c r="B637" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C637" t="s">
         <v>22</v>
@@ -19076,7 +19074,7 @@
         <v>592</v>
       </c>
       <c r="G637" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="638" hidden="1" spans="1:7">
@@ -19084,7 +19082,7 @@
         <v>574</v>
       </c>
       <c r="B638" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C638" t="s">
         <v>22</v>
@@ -19096,10 +19094,10 @@
         <v>54</v>
       </c>
       <c r="F638" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G638" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="639" hidden="1" spans="1:7">
@@ -19107,7 +19105,7 @@
         <v>100</v>
       </c>
       <c r="B639" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C639" t="s">
         <v>58</v>
@@ -19122,15 +19120,15 @@
         <v>592</v>
       </c>
       <c r="G639" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="640" hidden="1" spans="1:7">
       <c r="A640" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B640" t="s">
         <v>1097</v>
-      </c>
-      <c r="B640" t="s">
-        <v>1098</v>
       </c>
       <c r="C640" t="s">
         <v>587</v>
@@ -19142,21 +19140,21 @@
         <v>54</v>
       </c>
       <c r="F640" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G640" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="641" hidden="1" spans="1:7">
       <c r="A641" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B641" t="s">
         <v>1099</v>
       </c>
-      <c r="B641" t="s">
-        <v>1100</v>
-      </c>
       <c r="C641" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D641" t="s">
         <v>10</v>
@@ -19168,15 +19166,15 @@
         <v>175</v>
       </c>
       <c r="G641" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="642" hidden="1" spans="1:7">
       <c r="A642" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B642" t="s">
         <v>1102</v>
-      </c>
-      <c r="B642" t="s">
-        <v>1103</v>
       </c>
       <c r="C642" t="s">
         <v>181</v>
@@ -19191,15 +19189,15 @@
         <v>274</v>
       </c>
       <c r="G642" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="643" hidden="1" spans="1:7">
       <c r="A643" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B643" t="s">
         <v>1104</v>
-      </c>
-      <c r="B643" t="s">
-        <v>1105</v>
       </c>
       <c r="C643" t="s">
         <v>181</v>
@@ -19214,7 +19212,7 @@
         <v>274</v>
       </c>
       <c r="G643" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="644" hidden="1" spans="1:7">
@@ -19222,7 +19220,7 @@
         <v>620</v>
       </c>
       <c r="B644" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C644" t="s">
         <v>148</v>
@@ -19237,7 +19235,7 @@
         <v>175</v>
       </c>
       <c r="G644" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="645" hidden="1" spans="1:7">
@@ -19245,7 +19243,7 @@
         <v>589</v>
       </c>
       <c r="B645" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C645" t="s">
         <v>148</v>
@@ -19260,7 +19258,7 @@
         <v>175</v>
       </c>
       <c r="G645" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="646" hidden="1" spans="1:7">
@@ -19268,7 +19266,7 @@
         <v>20</v>
       </c>
       <c r="B646" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C646" t="s">
         <v>22</v>
@@ -19283,7 +19281,7 @@
         <v>24</v>
       </c>
       <c r="G646" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="647" hidden="1" spans="1:7">
@@ -19291,7 +19289,7 @@
         <v>20</v>
       </c>
       <c r="B647" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C647" t="s">
         <v>22</v>
@@ -19306,7 +19304,7 @@
         <v>24</v>
       </c>
       <c r="G647" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="648" hidden="1" spans="1:7">
@@ -19314,7 +19312,7 @@
         <v>20</v>
       </c>
       <c r="B648" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C648" t="s">
         <v>22</v>
@@ -19329,15 +19327,15 @@
         <v>24</v>
       </c>
       <c r="G648" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="649" hidden="1" spans="1:7">
       <c r="A649" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B649" t="s">
         <v>1109</v>
-      </c>
-      <c r="B649" t="s">
-        <v>1110</v>
       </c>
       <c r="C649" t="s">
         <v>625</v>
@@ -19352,7 +19350,7 @@
         <v>175</v>
       </c>
       <c r="G649" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="650" hidden="1" spans="1:7">
@@ -19360,7 +19358,7 @@
         <v>20</v>
       </c>
       <c r="B650" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C650" t="s">
         <v>22</v>
@@ -19375,15 +19373,15 @@
         <v>24</v>
       </c>
       <c r="G650" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="651" hidden="1" spans="1:7">
       <c r="A651" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B651" t="s">
         <v>1111</v>
-      </c>
-      <c r="B651" t="s">
-        <v>1112</v>
       </c>
       <c r="C651" t="s">
         <v>174</v>
@@ -19398,15 +19396,15 @@
         <v>175</v>
       </c>
       <c r="G651" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="652" hidden="1" spans="1:7">
       <c r="A652" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B652" t="s">
         <v>1113</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1114</v>
       </c>
       <c r="C652" t="s">
         <v>148</v>
@@ -19418,18 +19416,18 @@
         <v>36</v>
       </c>
       <c r="F652" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G652" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="653" hidden="1" spans="1:7">
       <c r="A653" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B653" t="s">
         <v>1113</v>
-      </c>
-      <c r="B653" t="s">
-        <v>1114</v>
       </c>
       <c r="C653" t="s">
         <v>148</v>
@@ -19441,18 +19439,18 @@
         <v>36</v>
       </c>
       <c r="F653" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G653" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="654" hidden="1" spans="1:7">
       <c r="A654" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B654" t="s">
         <v>1116</v>
-      </c>
-      <c r="B654" t="s">
-        <v>1117</v>
       </c>
       <c r="C654" t="s">
         <v>227</v>
@@ -19467,7 +19465,7 @@
         <v>175</v>
       </c>
       <c r="G654" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="655" hidden="1" spans="1:7">
@@ -19475,7 +19473,7 @@
         <v>170</v>
       </c>
       <c r="B655" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C655" t="s">
         <v>158</v>
@@ -19490,15 +19488,15 @@
         <v>175</v>
       </c>
       <c r="G655" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="656" hidden="1" spans="1:7">
       <c r="A656" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B656" t="s">
         <v>1119</v>
-      </c>
-      <c r="B656" t="s">
-        <v>1120</v>
       </c>
       <c r="C656" t="s">
         <v>353</v>
@@ -19513,7 +19511,7 @@
         <v>175</v>
       </c>
       <c r="G656" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="657" hidden="1" spans="1:7">
@@ -19521,7 +19519,7 @@
         <v>614</v>
       </c>
       <c r="B657" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C657" t="s">
         <v>560</v>
@@ -19533,18 +19531,18 @@
         <v>47</v>
       </c>
       <c r="F657" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G657" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="658" hidden="1" spans="1:7">
       <c r="A658" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B658" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C658" t="s">
         <v>227</v>
@@ -19556,10 +19554,10 @@
         <v>47</v>
       </c>
       <c r="F658" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G658" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="659" hidden="1" spans="1:7">
@@ -19567,7 +19565,7 @@
         <v>614</v>
       </c>
       <c r="B659" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C659" t="s">
         <v>560</v>
@@ -19579,18 +19577,18 @@
         <v>47</v>
       </c>
       <c r="F659" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G659" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="660" hidden="1" spans="1:7">
       <c r="A660" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B660" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C660" t="s">
         <v>227</v>
@@ -19602,10 +19600,10 @@
         <v>47</v>
       </c>
       <c r="F660" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G660" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="661" hidden="1" spans="1:7">
@@ -19613,7 +19611,7 @@
         <v>156</v>
       </c>
       <c r="B661" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C661" t="s">
         <v>158</v>
@@ -19628,15 +19626,15 @@
         <v>175</v>
       </c>
       <c r="G661" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="662" hidden="1" spans="1:7">
       <c r="A662" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B662" t="s">
         <v>1126</v>
-      </c>
-      <c r="B662" t="s">
-        <v>1127</v>
       </c>
       <c r="C662" t="s">
         <v>353</v>
@@ -19651,7 +19649,7 @@
         <v>175</v>
       </c>
       <c r="G662" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="663" hidden="1" spans="1:7">
@@ -19659,7 +19657,7 @@
         <v>162</v>
       </c>
       <c r="B663" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C663" t="s">
         <v>164</v>
@@ -19671,10 +19669,10 @@
         <v>54</v>
       </c>
       <c r="F663" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G663" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="664" hidden="1" spans="1:7">
@@ -19682,7 +19680,7 @@
         <v>603</v>
       </c>
       <c r="B664" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C664" t="s">
         <v>353</v>
@@ -19694,10 +19692,10 @@
         <v>54</v>
       </c>
       <c r="F664" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G664" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="665" hidden="1" spans="1:7">
@@ -19705,7 +19703,7 @@
         <v>20</v>
       </c>
       <c r="B665" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C665" t="s">
         <v>22</v>
@@ -19720,7 +19718,7 @@
         <v>24</v>
       </c>
       <c r="G665" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="666" hidden="1" spans="1:7">
@@ -19728,7 +19726,7 @@
         <v>20</v>
       </c>
       <c r="B666" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C666" t="s">
         <v>22</v>
@@ -19743,15 +19741,15 @@
         <v>24</v>
       </c>
       <c r="G666" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="667" hidden="1" spans="1:7">
       <c r="A667" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B667" t="s">
         <v>1126</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1127</v>
       </c>
       <c r="C667" t="s">
         <v>353</v>
@@ -19766,7 +19764,7 @@
         <v>175</v>
       </c>
       <c r="G667" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="668" hidden="1" spans="1:7">
@@ -19774,7 +19772,7 @@
         <v>162</v>
       </c>
       <c r="B668" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C668" t="s">
         <v>164</v>
@@ -19786,10 +19784,10 @@
         <v>54</v>
       </c>
       <c r="F668" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G668" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="669" hidden="1" spans="1:7">
@@ -19797,7 +19795,7 @@
         <v>603</v>
       </c>
       <c r="B669" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C669" t="s">
         <v>353</v>
@@ -19809,10 +19807,10 @@
         <v>54</v>
       </c>
       <c r="F669" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G669" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="670" hidden="1" spans="1:7">
@@ -19820,7 +19818,7 @@
         <v>113</v>
       </c>
       <c r="B670" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C670" t="s">
         <v>318</v>
@@ -19843,7 +19841,7 @@
         <v>269</v>
       </c>
       <c r="B671" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C671" t="s">
         <v>271</v>
@@ -19858,15 +19856,15 @@
         <v>675</v>
       </c>
       <c r="G671" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="672" spans="1:7">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="672" hidden="1" spans="1:7">
       <c r="A672" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B672" t="s">
         <v>1136</v>
-      </c>
-      <c r="B672" t="s">
-        <v>1137</v>
       </c>
       <c r="C672" t="s">
         <v>35</v>
@@ -19886,10 +19884,10 @@
     </row>
     <row r="673" spans="1:7">
       <c r="A673" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B673" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C673" t="s">
         <v>9</v>
@@ -19901,7 +19899,7 @@
         <v>54</v>
       </c>
       <c r="F673" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G673" t="s">
         <v>730</v>
@@ -19909,6 +19907,12 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G673" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Salle micro 2 G1/G2"/>
+        <filter val="Salle de micros 03 G2"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="6">
       <filters>
         <filter val="M1MCIL"/>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1138">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2270,7 +2270,7 @@
     <t>NEMMICH SAID</t>
   </si>
   <si>
-    <t>Salle micro 2</t>
+    <t>Salle micro 02</t>
   </si>
   <si>
     <t>TP-Exploitation des Réseaux électriques-G2</t>
@@ -2324,9 +2324,6 @@
     <t>TP-EPA-M1MCIL</t>
   </si>
   <si>
-    <t>Salle de micros 02 dept</t>
-  </si>
-  <si>
     <t>TP-Électronique de puissance avancée-G2</t>
   </si>
   <si>
@@ -2336,6 +2333,9 @@
     <t>TP-MNAP-M1MCIL</t>
   </si>
   <si>
+    <t>Salle micro 03</t>
+  </si>
+  <si>
     <t>Cours-PAP-M1ME</t>
   </si>
   <si>
@@ -3444,9 +3444,6 @@
   </si>
   <si>
     <t>TP-Méthodes numériques appliquées-G1</t>
-  </si>
-  <si>
-    <t>Salle micros 3</t>
   </si>
 </sst>
 </file>
@@ -14201,7 +14198,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:7">
+    <row r="426" spans="1:7">
       <c r="A426" t="s">
         <v>762</v>
       </c>
@@ -14218,15 +14215,15 @@
         <v>54</v>
       </c>
       <c r="F426" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="G426" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="427" hidden="1" spans="1:7">
+    <row r="427" spans="1:7">
       <c r="A427" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B427" t="s">
         <v>763</v>
@@ -14241,18 +14238,18 @@
         <v>54</v>
       </c>
       <c r="F427" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="G427" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="428" hidden="1" spans="1:7">
+    <row r="428" spans="1:7">
       <c r="A428" t="s">
+        <v>765</v>
+      </c>
+      <c r="B428" t="s">
         <v>766</v>
-      </c>
-      <c r="B428" t="s">
-        <v>767</v>
       </c>
       <c r="C428" t="s">
         <v>9</v>
@@ -14264,7 +14261,7 @@
         <v>54</v>
       </c>
       <c r="F428" t="s">
-        <v>678</v>
+        <v>767</v>
       </c>
       <c r="G428" t="s">
         <v>730</v>
@@ -19887,7 +19884,7 @@
         <v>1137</v>
       </c>
       <c r="B673" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C673" t="s">
         <v>9</v>
@@ -19899,7 +19896,7 @@
         <v>54</v>
       </c>
       <c r="F673" t="s">
-        <v>1138</v>
+        <v>767</v>
       </c>
       <c r="G673" t="s">
         <v>730</v>
@@ -19909,8 +19906,10 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G673" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="5">
       <filters>
-        <filter val="Salle micro 2 G1/G2"/>
-        <filter val="Salle de micros 03 G2"/>
+        <filter val="Salle micro 2"/>
+        <filter val="Salle micros 02"/>
+        <filter val="Salle micros 03"/>
+        <filter val="Salle micros 3"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -13295,7 +13295,7 @@
         <v>178</v>
       </c>
       <c r="D388" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E388" t="s">
         <v>54</v>
@@ -13318,7 +13318,7 @@
         <v>178</v>
       </c>
       <c r="D389" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E389" t="s">
         <v>54</v>
@@ -13433,7 +13433,7 @@
         <v>313</v>
       </c>
       <c r="D394" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E394" t="s">
         <v>54</v>
@@ -13456,7 +13456,7 @@
         <v>313</v>
       </c>
       <c r="D395" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E395" t="s">
         <v>54</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$673</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$672</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4704" uniqueCount="1117">
   <si>
     <t>Enseignements</t>
   </si>
@@ -4372,7 +4372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G673"/>
+  <dimension ref="A1:G672"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="76.8571428571429" customWidth="1"/>
@@ -12755,7 +12755,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:7">
+    <row r="365" spans="1:7">
       <c r="A365" t="s">
         <v>661</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:7">
+    <row r="384" spans="1:7">
       <c r="A384" t="s">
         <v>316</v>
       </c>
@@ -13217,76 +13217,76 @@
     </row>
     <row r="385" hidden="1" spans="1:7">
       <c r="A385" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="B385" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C385" t="s">
         <v>668</v>
       </c>
       <c r="D385" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E385" t="s">
         <v>47</v>
       </c>
       <c r="F385" t="s">
-        <v>686</v>
+        <v>663</v>
       </c>
       <c r="G385" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="386" hidden="1" spans="1:7">
-      <c r="A386" t="s">
-        <v>341</v>
+      <c r="A386" s="2" t="s">
+        <v>709</v>
       </c>
       <c r="B386" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C386" t="s">
-        <v>668</v>
+        <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E386" t="s">
         <v>47</v>
       </c>
       <c r="F386" t="s">
-        <v>663</v>
+        <v>686</v>
       </c>
       <c r="G386" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
     </row>
     <row r="387" hidden="1" spans="1:7">
-      <c r="A387" s="2" t="s">
-        <v>709</v>
+      <c r="A387" t="s">
+        <v>691</v>
       </c>
       <c r="B387" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C387" t="s">
-        <v>308</v>
+        <v>178</v>
       </c>
       <c r="D387" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E387" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F387" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="G387" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="388" spans="1:7">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="388" hidden="1" spans="1:7">
       <c r="A388" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B388" t="s">
         <v>711</v>
@@ -13295,7 +13295,7 @@
         <v>178</v>
       </c>
       <c r="D388" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E388" t="s">
         <v>54</v>
@@ -13307,124 +13307,124 @@
         <v>666</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" hidden="1" spans="1:7">
       <c r="A389" t="s">
-        <v>689</v>
+        <v>712</v>
       </c>
       <c r="B389" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C389" t="s">
-        <v>178</v>
+        <v>338</v>
       </c>
       <c r="D389" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E389" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F389" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="G389" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="390" hidden="1" spans="1:7">
       <c r="A390" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B390" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C390" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="D390" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E390" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F390" t="s">
-        <v>663</v>
+        <v>686</v>
       </c>
       <c r="G390" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="391" hidden="1" spans="1:7">
       <c r="A391" t="s">
+        <v>272</v>
+      </c>
+      <c r="B391" t="s">
+        <v>715</v>
+      </c>
+      <c r="C391" t="s">
+        <v>271</v>
+      </c>
+      <c r="D391" t="s">
+        <v>26</v>
+      </c>
+      <c r="E391" t="s">
+        <v>36</v>
+      </c>
+      <c r="F391" t="s">
+        <v>274</v>
+      </c>
+      <c r="G391" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="392" hidden="1" spans="1:7">
+      <c r="A392" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="B391" t="s">
-        <v>714</v>
-      </c>
-      <c r="C391" t="s">
+      <c r="B392" t="s">
+        <v>716</v>
+      </c>
+      <c r="C392" t="s">
         <v>308</v>
       </c>
-      <c r="D391" t="s">
+      <c r="D392" t="s">
         <v>25</v>
       </c>
-      <c r="E391" t="s">
+      <c r="E392" t="s">
         <v>47</v>
       </c>
-      <c r="F391" t="s">
+      <c r="F392" t="s">
         <v>686</v>
       </c>
-      <c r="G391" t="s">
+      <c r="G392" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="393" hidden="1" spans="1:7">
+      <c r="A393" t="s">
+        <v>717</v>
+      </c>
+      <c r="B393" t="s">
+        <v>718</v>
+      </c>
+      <c r="C393" t="s">
+        <v>313</v>
+      </c>
+      <c r="D393" t="s">
+        <v>18</v>
+      </c>
+      <c r="E393" t="s">
+        <v>54</v>
+      </c>
+      <c r="F393" t="s">
+        <v>719</v>
+      </c>
+      <c r="G393" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:7">
-      <c r="A392" t="s">
-        <v>272</v>
-      </c>
-      <c r="B392" t="s">
-        <v>715</v>
-      </c>
-      <c r="C392" t="s">
-        <v>271</v>
-      </c>
-      <c r="D392" t="s">
-        <v>26</v>
-      </c>
-      <c r="E392" t="s">
-        <v>36</v>
-      </c>
-      <c r="F392" t="s">
-        <v>274</v>
-      </c>
-      <c r="G392" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="393" hidden="1" spans="1:7">
-      <c r="A393" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B393" t="s">
-        <v>716</v>
-      </c>
-      <c r="C393" t="s">
-        <v>308</v>
-      </c>
-      <c r="D393" t="s">
-        <v>25</v>
-      </c>
-      <c r="E393" t="s">
-        <v>47</v>
-      </c>
-      <c r="F393" t="s">
-        <v>686</v>
-      </c>
-      <c r="G393" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="394" spans="1:7">
+    <row r="394" hidden="1" spans="1:7">
       <c r="A394" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B394" t="s">
         <v>718</v>
@@ -13433,7 +13433,7 @@
         <v>313</v>
       </c>
       <c r="D394" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E394" t="s">
         <v>54</v>
@@ -13445,32 +13445,32 @@
         <v>666</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" hidden="1" spans="1:7">
       <c r="A395" t="s">
-        <v>720</v>
+        <v>680</v>
       </c>
       <c r="B395" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C395" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D395" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E395" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F395" t="s">
-        <v>719</v>
+        <v>682</v>
       </c>
       <c r="G395" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" hidden="1" spans="1:7">
       <c r="A396" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B396" t="s">
         <v>721</v>
@@ -13479,7 +13479,7 @@
         <v>318</v>
       </c>
       <c r="D396" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E396" t="s">
         <v>47</v>
@@ -13493,76 +13493,76 @@
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>683</v>
+        <v>709</v>
       </c>
       <c r="B397" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C397" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D397" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E397" t="s">
         <v>47</v>
       </c>
       <c r="F397" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="G397" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
     </row>
     <row r="398" hidden="1" spans="1:7">
       <c r="A398" t="s">
-        <v>709</v>
+        <v>272</v>
       </c>
       <c r="B398" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C398" t="s">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="D398" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E398" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F398" t="s">
-        <v>686</v>
+        <v>258</v>
       </c>
       <c r="G398" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
     </row>
     <row r="399" hidden="1" spans="1:7">
       <c r="A399" t="s">
-        <v>272</v>
+        <v>669</v>
       </c>
       <c r="B399" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C399" t="s">
-        <v>271</v>
+        <v>22</v>
       </c>
       <c r="D399" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E399" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F399" t="s">
-        <v>258</v>
+        <v>725</v>
       </c>
       <c r="G399" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" hidden="1" spans="1:7">
       <c r="A400" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="B400" t="s">
         <v>724</v>
@@ -13571,7 +13571,7 @@
         <v>22</v>
       </c>
       <c r="D400" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -13583,32 +13583,32 @@
         <v>666</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" hidden="1" spans="1:7">
       <c r="A401" t="s">
-        <v>679</v>
+        <v>701</v>
       </c>
       <c r="B401" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C401" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="D401" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E401" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F401" t="s">
-        <v>725</v>
+        <v>700</v>
       </c>
       <c r="G401" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" hidden="1" spans="1:7">
       <c r="A402" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B402" t="s">
         <v>726</v>
@@ -13617,7 +13617,7 @@
         <v>280</v>
       </c>
       <c r="D402" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E402" t="s">
         <v>47</v>
@@ -13629,55 +13629,55 @@
         <v>666</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" hidden="1" spans="1:7">
       <c r="A403" t="s">
-        <v>698</v>
+        <v>727</v>
       </c>
       <c r="B403" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C403" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="D403" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E403" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F403" t="s">
-        <v>700</v>
+        <v>663</v>
       </c>
       <c r="G403" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="404" hidden="1" spans="1:7">
       <c r="A404" t="s">
-        <v>727</v>
+        <v>702</v>
       </c>
       <c r="B404" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C404" t="s">
-        <v>338</v>
+        <v>17</v>
       </c>
       <c r="D404" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E404" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F404" t="s">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="G404" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="405" spans="1:7">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="405" hidden="1" spans="1:7">
       <c r="A405" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B405" t="s">
         <v>729</v>
@@ -13686,7 +13686,7 @@
         <v>17</v>
       </c>
       <c r="D405" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E405" t="s">
         <v>27</v>
@@ -13698,55 +13698,55 @@
         <v>666</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
-      <c r="A406" t="s">
+    <row r="406" hidden="1" spans="1:7">
+      <c r="A406" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B406" t="s">
+        <v>730</v>
+      </c>
+      <c r="C406" t="s">
+        <v>271</v>
+      </c>
+      <c r="D406" t="s">
+        <v>25</v>
+      </c>
+      <c r="E406" t="s">
+        <v>36</v>
+      </c>
+      <c r="F406" t="s">
+        <v>258</v>
+      </c>
+      <c r="G406" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="407" hidden="1" spans="1:7">
+      <c r="A407" t="s">
         <v>706</v>
       </c>
-      <c r="B406" t="s">
-        <v>729</v>
-      </c>
-      <c r="C406" t="s">
+      <c r="B407" t="s">
+        <v>731</v>
+      </c>
+      <c r="C407" t="s">
         <v>17</v>
       </c>
-      <c r="D406" t="s">
-        <v>23</v>
-      </c>
-      <c r="E406" t="s">
-        <v>27</v>
-      </c>
-      <c r="F406" t="s">
+      <c r="D407" t="s">
+        <v>732</v>
+      </c>
+      <c r="E407" t="s">
+        <v>11</v>
+      </c>
+      <c r="F407" t="s">
         <v>704</v>
       </c>
-      <c r="G406" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="407" hidden="1" spans="1:7">
-      <c r="A407" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B407" t="s">
-        <v>730</v>
-      </c>
-      <c r="C407" t="s">
-        <v>271</v>
-      </c>
-      <c r="D407" t="s">
-        <v>25</v>
-      </c>
-      <c r="E407" t="s">
-        <v>36</v>
-      </c>
-      <c r="F407" t="s">
-        <v>258</v>
-      </c>
       <c r="G407" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="408" hidden="1" spans="1:7">
       <c r="A408" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B408" t="s">
         <v>731</v>
@@ -13755,7 +13755,7 @@
         <v>17</v>
       </c>
       <c r="D408" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E408" t="s">
         <v>11</v>
@@ -13769,65 +13769,65 @@
     </row>
     <row r="409" hidden="1" spans="1:7">
       <c r="A409" t="s">
-        <v>702</v>
+        <v>734</v>
       </c>
       <c r="B409" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C409" t="s">
-        <v>17</v>
+        <v>271</v>
       </c>
       <c r="D409" t="s">
-        <v>733</v>
+        <v>25</v>
       </c>
       <c r="E409" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F409" t="s">
-        <v>704</v>
+        <v>258</v>
       </c>
       <c r="G409" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="410" hidden="1" spans="1:7">
       <c r="A410" t="s">
-        <v>734</v>
+        <v>269</v>
       </c>
       <c r="B410" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C410" t="s">
-        <v>271</v>
+        <v>207</v>
       </c>
       <c r="D410" t="s">
         <v>25</v>
       </c>
       <c r="E410" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F410" t="s">
-        <v>258</v>
+        <v>663</v>
       </c>
       <c r="G410" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="411" hidden="1" spans="1:7">
       <c r="A411" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B411" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C411" t="s">
-        <v>207</v>
+        <v>271</v>
       </c>
       <c r="D411" t="s">
-        <v>25</v>
+        <v>415</v>
       </c>
       <c r="E411" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F411" t="s">
         <v>663</v>
@@ -13838,53 +13838,53 @@
     </row>
     <row r="412" hidden="1" spans="1:7">
       <c r="A412" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B412" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C412" t="s">
         <v>271</v>
       </c>
       <c r="D412" t="s">
-        <v>415</v>
+        <v>10</v>
       </c>
       <c r="E412" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F412" t="s">
-        <v>663</v>
+        <v>686</v>
       </c>
       <c r="G412" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="413" hidden="1" spans="1:7">
       <c r="A413" t="s">
-        <v>269</v>
+        <v>739</v>
       </c>
       <c r="B413" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C413" t="s">
-        <v>271</v>
+        <v>741</v>
       </c>
       <c r="D413" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E413" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F413" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="G413" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
     </row>
     <row r="414" hidden="1" spans="1:7">
       <c r="A414" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B414" t="s">
         <v>740</v>
@@ -13893,7 +13893,7 @@
         <v>741</v>
       </c>
       <c r="D414" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E414" t="s">
         <v>36</v>
@@ -13907,22 +13907,22 @@
     </row>
     <row r="415" hidden="1" spans="1:7">
       <c r="A415" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="B415" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C415" t="s">
-        <v>741</v>
+        <v>695</v>
       </c>
       <c r="D415" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E415" t="s">
         <v>36</v>
       </c>
       <c r="F415" t="s">
-        <v>671</v>
+        <v>744</v>
       </c>
       <c r="G415" t="s">
         <v>664</v>
@@ -13930,16 +13930,16 @@
     </row>
     <row r="416" hidden="1" spans="1:7">
       <c r="A416" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B416" t="s">
         <v>743</v>
       </c>
       <c r="C416" t="s">
-        <v>695</v>
+        <v>313</v>
       </c>
       <c r="D416" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E416" t="s">
         <v>36</v>
@@ -13951,50 +13951,50 @@
         <v>664</v>
       </c>
     </row>
-    <row r="417" hidden="1" spans="1:7">
+    <row r="417" spans="1:7">
       <c r="A417" t="s">
-        <v>717</v>
+        <v>269</v>
       </c>
       <c r="B417" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C417" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="D417" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E417" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F417" t="s">
-        <v>744</v>
+        <v>686</v>
       </c>
       <c r="G417" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
     </row>
     <row r="418" hidden="1" spans="1:7">
       <c r="A418" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B418" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C418" t="s">
         <v>271</v>
       </c>
       <c r="D418" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E418" t="s">
         <v>54</v>
       </c>
       <c r="F418" t="s">
-        <v>686</v>
+        <v>309</v>
       </c>
       <c r="G418" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="419" hidden="1" spans="1:7">
@@ -14002,59 +14002,59 @@
         <v>272</v>
       </c>
       <c r="B419" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C419" t="s">
         <v>271</v>
       </c>
       <c r="D419" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E419" t="s">
         <v>54</v>
       </c>
       <c r="F419" t="s">
-        <v>309</v>
+        <v>686</v>
       </c>
       <c r="G419" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="420" hidden="1" spans="1:7">
       <c r="A420" t="s">
-        <v>272</v>
+        <v>748</v>
       </c>
       <c r="B420" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C420" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="D420" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E420" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F420" t="s">
-        <v>686</v>
+        <v>663</v>
       </c>
       <c r="G420" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
     </row>
     <row r="421" hidden="1" spans="1:7">
       <c r="A421" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B421" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C421" t="s">
         <v>318</v>
       </c>
       <c r="D421" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E421" t="s">
         <v>47</v>
@@ -14067,54 +14067,54 @@
       </c>
     </row>
     <row r="422" hidden="1" spans="1:7">
-      <c r="A422" t="s">
-        <v>750</v>
+      <c r="A422" s="1" t="s">
+        <v>752</v>
       </c>
       <c r="B422" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C422" t="s">
         <v>318</v>
       </c>
       <c r="D422" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E422" t="s">
         <v>47</v>
       </c>
       <c r="F422" t="s">
-        <v>663</v>
+        <v>258</v>
       </c>
       <c r="G422" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="423" hidden="1" spans="1:7">
+      <c r="A423" t="s">
+        <v>691</v>
+      </c>
+      <c r="B423" t="s">
+        <v>754</v>
+      </c>
+      <c r="C423" t="s">
+        <v>556</v>
+      </c>
+      <c r="D423" t="s">
+        <v>18</v>
+      </c>
+      <c r="E423" t="s">
+        <v>54</v>
+      </c>
+      <c r="F423" t="s">
+        <v>671</v>
+      </c>
+      <c r="G423" t="s">
         <v>664</v>
-      </c>
-    </row>
-    <row r="423" hidden="1" spans="1:7">
-      <c r="A423" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="B423" t="s">
-        <v>753</v>
-      </c>
-      <c r="C423" t="s">
-        <v>318</v>
-      </c>
-      <c r="D423" t="s">
-        <v>10</v>
-      </c>
-      <c r="E423" t="s">
-        <v>47</v>
-      </c>
-      <c r="F423" t="s">
-        <v>258</v>
-      </c>
-      <c r="G423" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="424" hidden="1" spans="1:7">
       <c r="A424" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B424" t="s">
         <v>754</v>
@@ -14123,7 +14123,7 @@
         <v>556</v>
       </c>
       <c r="D424" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E424" t="s">
         <v>54</v>
@@ -14137,22 +14137,22 @@
     </row>
     <row r="425" hidden="1" spans="1:7">
       <c r="A425" t="s">
-        <v>689</v>
+        <v>755</v>
       </c>
       <c r="B425" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C425" t="s">
-        <v>556</v>
+        <v>9</v>
       </c>
       <c r="D425" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E425" t="s">
         <v>54</v>
       </c>
       <c r="F425" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="G425" t="s">
         <v>664</v>
@@ -14160,25 +14160,25 @@
     </row>
     <row r="426" hidden="1" spans="1:7">
       <c r="A426" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B426" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C426" t="s">
-        <v>9</v>
+        <v>318</v>
       </c>
       <c r="D426" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E426" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F426" t="s">
-        <v>682</v>
+        <v>258</v>
       </c>
       <c r="G426" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="427" hidden="1" spans="1:7">
@@ -14186,177 +14186,177 @@
         <v>752</v>
       </c>
       <c r="B427" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C427" t="s">
-        <v>318</v>
+        <v>759</v>
       </c>
       <c r="D427" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E427" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F427" t="s">
-        <v>258</v>
+        <v>686</v>
       </c>
       <c r="G427" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
     </row>
     <row r="428" hidden="1" spans="1:7">
       <c r="A428" t="s">
+        <v>760</v>
+      </c>
+      <c r="B428" t="s">
+        <v>761</v>
+      </c>
+      <c r="C428" t="s">
+        <v>318</v>
+      </c>
+      <c r="D428" t="s">
+        <v>23</v>
+      </c>
+      <c r="E428" t="s">
+        <v>11</v>
+      </c>
+      <c r="F428" t="s">
+        <v>309</v>
+      </c>
+      <c r="G428" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7">
+      <c r="A429" t="s">
         <v>752</v>
       </c>
-      <c r="B428" t="s">
-        <v>758</v>
-      </c>
-      <c r="C428" t="s">
+      <c r="B429" t="s">
+        <v>762</v>
+      </c>
+      <c r="C429" t="s">
         <v>759</v>
       </c>
-      <c r="D428" t="s">
+      <c r="D429" t="s">
         <v>25</v>
       </c>
-      <c r="E428" t="s">
+      <c r="E429" t="s">
         <v>54</v>
       </c>
-      <c r="F428" t="s">
+      <c r="F429" t="s">
         <v>686</v>
       </c>
-      <c r="G428" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="429" hidden="1" spans="1:7">
-      <c r="A429" t="s">
-        <v>760</v>
-      </c>
-      <c r="B429" t="s">
-        <v>761</v>
-      </c>
-      <c r="C429" t="s">
-        <v>318</v>
-      </c>
-      <c r="D429" t="s">
-        <v>23</v>
-      </c>
-      <c r="E429" t="s">
-        <v>11</v>
-      </c>
-      <c r="F429" t="s">
-        <v>309</v>
-      </c>
       <c r="G429" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
     </row>
     <row r="430" hidden="1" spans="1:7">
       <c r="A430" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="B430" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C430" t="s">
-        <v>759</v>
+        <v>318</v>
       </c>
       <c r="D430" t="s">
+        <v>26</v>
+      </c>
+      <c r="E430" t="s">
+        <v>36</v>
+      </c>
+      <c r="F430" t="s">
+        <v>258</v>
+      </c>
+      <c r="G430" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="431" hidden="1" spans="1:7">
+      <c r="A431" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E431" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F431" t="s">
+        <v>700</v>
+      </c>
+      <c r="G431" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="432" hidden="1" spans="1:7">
+      <c r="A432" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B432" t="s">
+        <v>766</v>
+      </c>
+      <c r="C432" t="s">
+        <v>285</v>
+      </c>
+      <c r="D432" t="s">
         <v>25</v>
       </c>
-      <c r="E430" t="s">
-        <v>54</v>
-      </c>
-      <c r="F430" t="s">
+      <c r="E432" t="s">
+        <v>27</v>
+      </c>
+      <c r="F432" t="s">
         <v>686</v>
       </c>
-      <c r="G430" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="431" hidden="1" spans="1:7">
-      <c r="A431" t="s">
-        <v>760</v>
-      </c>
-      <c r="B431" t="s">
-        <v>763</v>
-      </c>
-      <c r="C431" t="s">
-        <v>318</v>
-      </c>
-      <c r="D431" t="s">
-        <v>26</v>
-      </c>
-      <c r="E431" t="s">
+      <c r="G432" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="433" hidden="1" spans="1:7">
+      <c r="A433" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E433" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F433" t="s">
+        <v>767</v>
+      </c>
+      <c r="G433" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="434" hidden="1" spans="1:7">
+      <c r="A434" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="D434" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E434" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="F431" t="s">
-        <v>258</v>
-      </c>
-      <c r="G431" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="432" hidden="1" spans="1:7">
-      <c r="A432" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="C432" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="D432" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E432" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F432" t="s">
-        <v>700</v>
-      </c>
-      <c r="G432" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="433" hidden="1" spans="1:7">
-      <c r="A433" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="B433" t="s">
-        <v>766</v>
-      </c>
-      <c r="C433" t="s">
-        <v>285</v>
-      </c>
-      <c r="D433" t="s">
-        <v>25</v>
-      </c>
-      <c r="E433" t="s">
-        <v>27</v>
-      </c>
-      <c r="F433" t="s">
-        <v>686</v>
-      </c>
-      <c r="G433" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="434" hidden="1" spans="1:7">
-      <c r="A434" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="B434" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="D434" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E434" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="F434" t="s">
         <v>767</v>
@@ -14367,7 +14367,7 @@
     </row>
     <row r="435" hidden="1" spans="1:7">
       <c r="A435" s="4" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B435" s="4" t="s">
         <v>768</v>
@@ -14376,33 +14376,33 @@
         <v>769</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E435" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F435" t="s">
-        <v>767</v>
+        <v>671</v>
       </c>
       <c r="G435" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="436" hidden="1" spans="1:7">
-      <c r="A436" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="B436" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="C436" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="D436" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E436" s="4" t="s">
-        <v>36</v>
+      <c r="A436" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="D436" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E436" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="F436" t="s">
         <v>671</v>
@@ -14413,7 +14413,7 @@
     </row>
     <row r="437" hidden="1" spans="1:7">
       <c r="A437" s="3" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>770</v>
@@ -14422,7 +14422,7 @@
         <v>759</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E437" s="3" t="s">
         <v>47</v>
@@ -14435,20 +14435,20 @@
       </c>
     </row>
     <row r="438" hidden="1" spans="1:7">
-      <c r="A438" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="B438" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="C438" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="D438" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E438" s="3" t="s">
-        <v>47</v>
+      <c r="A438" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E438" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="F438" t="s">
         <v>671</v>
@@ -14459,7 +14459,7 @@
     </row>
     <row r="439" hidden="1" spans="1:7">
       <c r="A439" s="4" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="B439" s="4" t="s">
         <v>771</v>
@@ -14468,7 +14468,7 @@
         <v>285</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E439" s="4" t="s">
         <v>36</v>
@@ -14481,181 +14481,181 @@
       </c>
     </row>
     <row r="440" hidden="1" spans="1:7">
-      <c r="A440" s="4" t="s">
-        <v>669</v>
-      </c>
-      <c r="B440" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C440" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="D440" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E440" s="4" t="s">
-        <v>36</v>
+      <c r="A440" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="B440" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="C440" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="D440" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E440" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="F440" t="s">
-        <v>671</v>
+        <v>773</v>
       </c>
       <c r="G440" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="441" hidden="1" spans="1:7">
-      <c r="A441" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="B441" s="3" t="s">
+      <c r="A441" t="s">
+        <v>765</v>
+      </c>
+      <c r="B441" t="s">
+        <v>774</v>
+      </c>
+      <c r="C441" t="s">
+        <v>285</v>
+      </c>
+      <c r="D441" t="s">
+        <v>10</v>
+      </c>
+      <c r="E441" t="s">
+        <v>11</v>
+      </c>
+      <c r="F441" t="s">
+        <v>258</v>
+      </c>
+      <c r="G441" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="442" hidden="1" spans="1:7">
+      <c r="A442" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="B442" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="C441" s="3" t="s">
+      <c r="C442" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="D441" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E441" s="3" t="s">
+      <c r="D442" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E442" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F441" t="s">
+      <c r="F442" t="s">
         <v>773</v>
       </c>
-      <c r="G441" t="s">
+      <c r="G442" t="s">
         <v>676</v>
-      </c>
-    </row>
-    <row r="442" hidden="1" spans="1:7">
-      <c r="A442" t="s">
-        <v>765</v>
-      </c>
-      <c r="B442" t="s">
-        <v>774</v>
-      </c>
-      <c r="C442" t="s">
-        <v>285</v>
-      </c>
-      <c r="D442" t="s">
-        <v>10</v>
-      </c>
-      <c r="E442" t="s">
-        <v>11</v>
-      </c>
-      <c r="F442" t="s">
-        <v>258</v>
-      </c>
-      <c r="G442" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="443" hidden="1" spans="1:7">
       <c r="A443" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>741</v>
+        <v>769</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E443" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F443" t="s">
-        <v>773</v>
+        <v>704</v>
       </c>
       <c r="G443" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="444" hidden="1" spans="1:7">
-      <c r="A444" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="B444" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C444" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="D444" s="3" t="s">
+      <c r="A444" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B444" t="s">
+        <v>776</v>
+      </c>
+      <c r="C444" t="s">
+        <v>285</v>
+      </c>
+      <c r="D444" t="s">
         <v>10</v>
       </c>
-      <c r="E444" s="3" t="s">
-        <v>47</v>
+      <c r="E444" t="s">
+        <v>11</v>
       </c>
       <c r="F444" t="s">
-        <v>704</v>
+        <v>258</v>
       </c>
       <c r="G444" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="445" hidden="1" spans="1:7">
-      <c r="A445" s="2" t="s">
-        <v>765</v>
+      <c r="A445" t="s">
+        <v>760</v>
       </c>
       <c r="B445" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C445" t="s">
-        <v>285</v>
+        <v>759</v>
       </c>
       <c r="D445" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E445" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="F445" t="s">
-        <v>258</v>
+        <v>686</v>
       </c>
       <c r="G445" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="446" hidden="1" spans="1:7">
+    <row r="446" spans="1:7">
       <c r="A446" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="B446" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C446" t="s">
-        <v>759</v>
+        <v>285</v>
       </c>
       <c r="D446" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E446" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="F446" t="s">
         <v>686</v>
       </c>
       <c r="G446" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="447" hidden="1" spans="1:7">
       <c r="A447" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B447" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C447" t="s">
-        <v>285</v>
+        <v>759</v>
       </c>
       <c r="D447" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E447" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F447" t="s">
         <v>686</v>
@@ -14666,53 +14666,53 @@
     </row>
     <row r="448" hidden="1" spans="1:7">
       <c r="A448" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
       <c r="B448" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C448" t="s">
-        <v>759</v>
+        <v>280</v>
       </c>
       <c r="D448" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E448" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F448" t="s">
-        <v>686</v>
+        <v>782</v>
       </c>
       <c r="G448" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="449" hidden="1" spans="1:7">
+      <c r="A449" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C449" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E449" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F449" t="s">
+        <v>784</v>
+      </c>
+      <c r="G449" t="s">
         <v>674</v>
-      </c>
-    </row>
-    <row r="449" hidden="1" spans="1:7">
-      <c r="A449" t="s">
-        <v>780</v>
-      </c>
-      <c r="B449" t="s">
-        <v>781</v>
-      </c>
-      <c r="C449" t="s">
-        <v>280</v>
-      </c>
-      <c r="D449" t="s">
-        <v>25</v>
-      </c>
-      <c r="E449" t="s">
-        <v>11</v>
-      </c>
-      <c r="F449" t="s">
-        <v>782</v>
-      </c>
-      <c r="G449" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="450" hidden="1" spans="1:7">
       <c r="A450" s="2" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>783</v>
@@ -14721,7 +14721,7 @@
         <v>769</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>11</v>
@@ -14735,22 +14735,22 @@
     </row>
     <row r="451" hidden="1" spans="1:7">
       <c r="A451" s="2" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F451" t="s">
-        <v>784</v>
+        <v>671</v>
       </c>
       <c r="G451" t="s">
         <v>674</v>
@@ -14758,7 +14758,7 @@
     </row>
     <row r="452" hidden="1" spans="1:7">
       <c r="A452" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>785</v>
@@ -14767,7 +14767,7 @@
         <v>759</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>11</v>
@@ -14780,69 +14780,69 @@
       </c>
     </row>
     <row r="453" hidden="1" spans="1:7">
-      <c r="A453" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="B453" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="C453" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="D453" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E453" s="2" t="s">
+      <c r="A453" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B453" t="s">
+        <v>787</v>
+      </c>
+      <c r="C453" t="s">
+        <v>280</v>
+      </c>
+      <c r="D453" t="s">
+        <v>18</v>
+      </c>
+      <c r="E453" t="s">
         <v>11</v>
       </c>
       <c r="F453" t="s">
-        <v>671</v>
+        <v>258</v>
       </c>
       <c r="G453" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="454" hidden="1" spans="1:7">
-      <c r="A454" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7">
+      <c r="A454" t="s">
         <v>786</v>
       </c>
       <c r="B454" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C454" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
       <c r="D454" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E454" t="s">
         <v>11</v>
       </c>
       <c r="F454" t="s">
-        <v>258</v>
+        <v>19</v>
       </c>
       <c r="G454" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
     </row>
     <row r="455" hidden="1" spans="1:7">
       <c r="A455" t="s">
-        <v>786</v>
+        <v>679</v>
       </c>
       <c r="B455" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C455" t="s">
-        <v>227</v>
+        <v>285</v>
       </c>
       <c r="D455" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E455" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F455" t="s">
-        <v>19</v>
+        <v>700</v>
       </c>
       <c r="G455" t="s">
         <v>674</v>
@@ -14850,99 +14850,99 @@
     </row>
     <row r="456" hidden="1" spans="1:7">
       <c r="A456" t="s">
-        <v>679</v>
+        <v>790</v>
       </c>
       <c r="B456" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C456" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D456" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E456" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F456" t="s">
-        <v>700</v>
+        <v>258</v>
       </c>
       <c r="G456" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
     </row>
     <row r="457" hidden="1" spans="1:7">
       <c r="A457" t="s">
-        <v>790</v>
+        <v>669</v>
       </c>
       <c r="B457" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C457" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D457" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E457" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F457" t="s">
-        <v>258</v>
+        <v>700</v>
       </c>
       <c r="G457" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
     </row>
     <row r="458" hidden="1" spans="1:7">
       <c r="A458" t="s">
-        <v>669</v>
+        <v>786</v>
       </c>
       <c r="B458" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C458" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D458" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E458" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F458" t="s">
-        <v>700</v>
+        <v>258</v>
       </c>
       <c r="G458" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="459" hidden="1" spans="1:7">
       <c r="A459" t="s">
-        <v>790</v>
+        <v>691</v>
       </c>
       <c r="B459" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C459" t="s">
-        <v>280</v>
+        <v>556</v>
       </c>
       <c r="D459" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E459" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F459" t="s">
-        <v>258</v>
+        <v>700</v>
       </c>
       <c r="G459" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="460" hidden="1" spans="1:7">
       <c r="A460" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B460" t="s">
         <v>793</v>
@@ -14951,7 +14951,7 @@
         <v>556</v>
       </c>
       <c r="D460" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E460" t="s">
         <v>27</v>
@@ -14964,20 +14964,20 @@
       </c>
     </row>
     <row r="461" hidden="1" spans="1:7">
-      <c r="A461" t="s">
-        <v>689</v>
-      </c>
-      <c r="B461" t="s">
-        <v>793</v>
-      </c>
-      <c r="C461" t="s">
-        <v>556</v>
-      </c>
-      <c r="D461" t="s">
-        <v>26</v>
-      </c>
-      <c r="E461" t="s">
-        <v>27</v>
+      <c r="A461" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C461" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D461" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E461" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F461" t="s">
         <v>700</v>
@@ -14988,16 +14988,16 @@
     </row>
     <row r="462" hidden="1" spans="1:7">
       <c r="A462" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>280</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>36</v>
@@ -15011,13 +15011,13 @@
     </row>
     <row r="463" hidden="1" spans="1:7">
       <c r="A463" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>280</v>
+        <v>769</v>
       </c>
       <c r="D463" s="2" t="s">
         <v>26</v>
@@ -15026,7 +15026,7 @@
         <v>36</v>
       </c>
       <c r="F463" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G463" t="s">
         <v>674</v>
@@ -15034,7 +15034,7 @@
     </row>
     <row r="464" hidden="1" spans="1:7">
       <c r="A464" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>796</v>
@@ -15043,7 +15043,7 @@
         <v>769</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>36</v>
@@ -15056,129 +15056,129 @@
       </c>
     </row>
     <row r="465" hidden="1" spans="1:7">
-      <c r="A465" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="B465" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="C465" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="D465" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E465" s="2" t="s">
-        <v>36</v>
+      <c r="A465" t="s">
+        <v>780</v>
+      </c>
+      <c r="B465" t="s">
+        <v>797</v>
+      </c>
+      <c r="C465" t="s">
+        <v>280</v>
+      </c>
+      <c r="D465" t="s">
+        <v>26</v>
+      </c>
+      <c r="E465" t="s">
+        <v>47</v>
       </c>
       <c r="F465" t="s">
-        <v>704</v>
+        <v>258</v>
       </c>
       <c r="G465" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
     </row>
     <row r="466" hidden="1" spans="1:7">
       <c r="A466" t="s">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="B466" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C466" t="s">
-        <v>280</v>
+        <v>197</v>
       </c>
       <c r="D466" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E466" t="s">
         <v>47</v>
       </c>
       <c r="F466" t="s">
+        <v>663</v>
+      </c>
+      <c r="G466" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="467" hidden="1" spans="1:7">
+      <c r="A467" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="B467" t="s">
+        <v>801</v>
+      </c>
+      <c r="C467" t="s">
+        <v>17</v>
+      </c>
+      <c r="D467" t="s">
+        <v>25</v>
+      </c>
+      <c r="E467" t="s">
+        <v>54</v>
+      </c>
+      <c r="F467" t="s">
         <v>258</v>
       </c>
-      <c r="G466" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="467" hidden="1" spans="1:7">
-      <c r="A467" t="s">
-        <v>798</v>
-      </c>
-      <c r="B467" t="s">
-        <v>799</v>
-      </c>
-      <c r="C467" t="s">
-        <v>197</v>
-      </c>
-      <c r="D467" t="s">
+      <c r="G467" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="468" hidden="1" spans="1:7">
+      <c r="A468" t="s">
+        <v>780</v>
+      </c>
+      <c r="B468" t="s">
+        <v>802</v>
+      </c>
+      <c r="C468" t="s">
+        <v>280</v>
+      </c>
+      <c r="D468" t="s">
         <v>23</v>
       </c>
-      <c r="E467" t="s">
-        <v>47</v>
-      </c>
-      <c r="F467" t="s">
-        <v>663</v>
-      </c>
-      <c r="G467" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="468" hidden="1" spans="1:7">
-      <c r="A468" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="B468" t="s">
-        <v>801</v>
-      </c>
-      <c r="C468" t="s">
-        <v>17</v>
-      </c>
-      <c r="D468" t="s">
-        <v>25</v>
-      </c>
       <c r="E468" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F468" t="s">
         <v>258</v>
       </c>
       <c r="G468" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
     </row>
     <row r="469" hidden="1" spans="1:7">
       <c r="A469" t="s">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="B469" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C469" t="s">
-        <v>280</v>
+        <v>17</v>
       </c>
       <c r="D469" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E469" t="s">
         <v>11</v>
       </c>
       <c r="F469" t="s">
-        <v>258</v>
+        <v>663</v>
       </c>
       <c r="G469" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
     </row>
     <row r="470" hidden="1" spans="1:7">
       <c r="A470" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B470" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C470" t="s">
-        <v>17</v>
+        <v>530</v>
       </c>
       <c r="D470" t="s">
         <v>10</v>
@@ -15187,30 +15187,30 @@
         <v>11</v>
       </c>
       <c r="F470" t="s">
-        <v>663</v>
+        <v>806</v>
       </c>
       <c r="G470" t="s">
-        <v>664</v>
+        <v>807</v>
       </c>
     </row>
     <row r="471" hidden="1" spans="1:7">
       <c r="A471" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B471" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C471" t="s">
-        <v>530</v>
+        <v>212</v>
       </c>
       <c r="D471" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E471" t="s">
         <v>11</v>
       </c>
       <c r="F471" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="G471" t="s">
         <v>807</v>
@@ -15218,13 +15218,13 @@
     </row>
     <row r="472" hidden="1" spans="1:7">
       <c r="A472" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B472" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C472" t="s">
-        <v>212</v>
+        <v>395</v>
       </c>
       <c r="D472" t="s">
         <v>18</v>
@@ -15233,7 +15233,7 @@
         <v>11</v>
       </c>
       <c r="F472" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="G472" t="s">
         <v>807</v>
@@ -15241,13 +15241,13 @@
     </row>
     <row r="473" hidden="1" spans="1:7">
       <c r="A473" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B473" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C473" t="s">
-        <v>395</v>
+        <v>814</v>
       </c>
       <c r="D473" t="s">
         <v>18</v>
@@ -15256,7 +15256,7 @@
         <v>11</v>
       </c>
       <c r="F473" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="G473" t="s">
         <v>807</v>
@@ -15270,16 +15270,16 @@
         <v>809</v>
       </c>
       <c r="C474" t="s">
-        <v>814</v>
+        <v>212</v>
       </c>
       <c r="D474" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E474" t="s">
         <v>11</v>
       </c>
       <c r="F474" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="G474" t="s">
         <v>807</v>
@@ -15287,13 +15287,13 @@
     </row>
     <row r="475" hidden="1" spans="1:7">
       <c r="A475" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B475" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C475" t="s">
-        <v>212</v>
+        <v>395</v>
       </c>
       <c r="D475" t="s">
         <v>23</v>
@@ -15302,7 +15302,7 @@
         <v>11</v>
       </c>
       <c r="F475" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G475" t="s">
         <v>807</v>
@@ -15310,13 +15310,13 @@
     </row>
     <row r="476" hidden="1" spans="1:7">
       <c r="A476" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B476" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C476" t="s">
-        <v>395</v>
+        <v>814</v>
       </c>
       <c r="D476" t="s">
         <v>23</v>
@@ -15325,7 +15325,7 @@
         <v>11</v>
       </c>
       <c r="F476" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G476" t="s">
         <v>807</v>
@@ -15333,22 +15333,22 @@
     </row>
     <row r="477" hidden="1" spans="1:7">
       <c r="A477" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="B477" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="C477" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D477" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E477" t="s">
         <v>11</v>
       </c>
       <c r="F477" t="s">
-        <v>815</v>
+        <v>651</v>
       </c>
       <c r="G477" t="s">
         <v>807</v>
@@ -15356,16 +15356,16 @@
     </row>
     <row r="478" hidden="1" spans="1:7">
       <c r="A478" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B478" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C478" t="s">
-        <v>819</v>
+        <v>207</v>
       </c>
       <c r="D478" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E478" t="s">
         <v>11</v>
@@ -15379,22 +15379,22 @@
     </row>
     <row r="479" hidden="1" spans="1:7">
       <c r="A479" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B479" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C479" t="s">
-        <v>207</v>
+        <v>741</v>
       </c>
       <c r="D479" t="s">
         <v>26</v>
       </c>
       <c r="E479" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F479" t="s">
-        <v>651</v>
+        <v>22</v>
       </c>
       <c r="G479" t="s">
         <v>807</v>
@@ -15402,19 +15402,19 @@
     </row>
     <row r="480" hidden="1" spans="1:7">
       <c r="A480" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B480" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C480" t="s">
-        <v>741</v>
+        <v>349</v>
       </c>
       <c r="D480" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E480" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F480" t="s">
         <v>22</v>
@@ -15425,13 +15425,13 @@
     </row>
     <row r="481" hidden="1" spans="1:7">
       <c r="A481" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B481" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C481" t="s">
-        <v>349</v>
+        <v>236</v>
       </c>
       <c r="D481" t="s">
         <v>10</v>
@@ -15440,7 +15440,7 @@
         <v>36</v>
       </c>
       <c r="F481" t="s">
-        <v>22</v>
+        <v>828</v>
       </c>
       <c r="G481" t="s">
         <v>807</v>
@@ -15448,22 +15448,22 @@
     </row>
     <row r="482" hidden="1" spans="1:7">
       <c r="A482" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B482" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C482" t="s">
         <v>236</v>
       </c>
       <c r="D482" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E482" t="s">
         <v>36</v>
       </c>
       <c r="F482" t="s">
-        <v>828</v>
+        <v>651</v>
       </c>
       <c r="G482" t="s">
         <v>807</v>
@@ -15471,16 +15471,16 @@
     </row>
     <row r="483" hidden="1" spans="1:7">
       <c r="A483" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B483" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C483" t="s">
         <v>236</v>
       </c>
       <c r="D483" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E483" t="s">
         <v>36</v>
@@ -15494,22 +15494,22 @@
     </row>
     <row r="484" hidden="1" spans="1:7">
       <c r="A484" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B484" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="C484" t="s">
-        <v>236</v>
+        <v>349</v>
       </c>
       <c r="D484" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E484" t="s">
         <v>36</v>
       </c>
       <c r="F484" t="s">
-        <v>651</v>
+        <v>22</v>
       </c>
       <c r="G484" t="s">
         <v>807</v>
@@ -15517,13 +15517,13 @@
     </row>
     <row r="485" hidden="1" spans="1:7">
       <c r="A485" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B485" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C485" t="s">
-        <v>349</v>
+        <v>236</v>
       </c>
       <c r="D485" t="s">
         <v>26</v>
@@ -15532,7 +15532,7 @@
         <v>36</v>
       </c>
       <c r="F485" t="s">
-        <v>22</v>
+        <v>828</v>
       </c>
       <c r="G485" t="s">
         <v>807</v>
@@ -15540,22 +15540,22 @@
     </row>
     <row r="486" hidden="1" spans="1:7">
       <c r="A486" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="B486" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="C486" t="s">
-        <v>236</v>
+        <v>349</v>
       </c>
       <c r="D486" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E486" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F486" t="s">
-        <v>828</v>
+        <v>651</v>
       </c>
       <c r="G486" t="s">
         <v>807</v>
@@ -15563,16 +15563,16 @@
     </row>
     <row r="487" hidden="1" spans="1:7">
       <c r="A487" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B487" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C487" t="s">
-        <v>349</v>
+        <v>837</v>
       </c>
       <c r="D487" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E487" t="s">
         <v>47</v>
@@ -15586,16 +15586,16 @@
     </row>
     <row r="488" hidden="1" spans="1:7">
       <c r="A488" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B488" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C488" t="s">
         <v>837</v>
       </c>
       <c r="D488" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E488" t="s">
         <v>47</v>
@@ -15609,16 +15609,16 @@
     </row>
     <row r="489" hidden="1" spans="1:7">
       <c r="A489" t="s">
-        <v>838</v>
+        <v>817</v>
       </c>
       <c r="B489" t="s">
-        <v>839</v>
+        <v>818</v>
       </c>
       <c r="C489" t="s">
-        <v>837</v>
+        <v>819</v>
       </c>
       <c r="D489" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E489" t="s">
         <v>47</v>
@@ -15632,22 +15632,22 @@
     </row>
     <row r="490" hidden="1" spans="1:7">
       <c r="A490" t="s">
-        <v>817</v>
+        <v>840</v>
       </c>
       <c r="B490" t="s">
-        <v>818</v>
+        <v>841</v>
       </c>
       <c r="C490" t="s">
-        <v>819</v>
+        <v>294</v>
       </c>
       <c r="D490" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E490" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F490" t="s">
-        <v>651</v>
+        <v>22</v>
       </c>
       <c r="G490" t="s">
         <v>807</v>
@@ -15655,22 +15655,22 @@
     </row>
     <row r="491" hidden="1" spans="1:7">
       <c r="A491" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B491" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C491" t="s">
-        <v>294</v>
+        <v>844</v>
       </c>
       <c r="D491" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E491" t="s">
         <v>54</v>
       </c>
       <c r="F491" t="s">
-        <v>22</v>
+        <v>651</v>
       </c>
       <c r="G491" t="s">
         <v>807</v>
@@ -15678,16 +15678,16 @@
     </row>
     <row r="492" hidden="1" spans="1:7">
       <c r="A492" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B492" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C492" t="s">
         <v>844</v>
       </c>
       <c r="D492" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E492" t="s">
         <v>54</v>
@@ -15701,22 +15701,22 @@
     </row>
     <row r="493" hidden="1" spans="1:7">
       <c r="A493" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B493" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C493" t="s">
         <v>844</v>
       </c>
       <c r="D493" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E493" t="s">
         <v>54</v>
       </c>
       <c r="F493" t="s">
-        <v>651</v>
+        <v>22</v>
       </c>
       <c r="G493" t="s">
         <v>807</v>
@@ -15724,13 +15724,13 @@
     </row>
     <row r="494" hidden="1" spans="1:7">
       <c r="A494" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B494" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C494" t="s">
-        <v>844</v>
+        <v>294</v>
       </c>
       <c r="D494" t="s">
         <v>25</v>
@@ -15739,7 +15739,7 @@
         <v>54</v>
       </c>
       <c r="F494" t="s">
-        <v>22</v>
+        <v>651</v>
       </c>
       <c r="G494" t="s">
         <v>807</v>
@@ -15747,22 +15747,22 @@
     </row>
     <row r="495" hidden="1" spans="1:7">
       <c r="A495" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B495" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C495" t="s">
-        <v>294</v>
+        <v>844</v>
       </c>
       <c r="D495" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E495" t="s">
         <v>54</v>
       </c>
       <c r="F495" t="s">
-        <v>651</v>
+        <v>22</v>
       </c>
       <c r="G495" t="s">
         <v>807</v>
@@ -15770,13 +15770,13 @@
     </row>
     <row r="496" hidden="1" spans="1:7">
       <c r="A496" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="B496" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="C496" t="s">
-        <v>844</v>
+        <v>294</v>
       </c>
       <c r="D496" t="s">
         <v>26</v>
@@ -15793,45 +15793,45 @@
     </row>
     <row r="497" hidden="1" spans="1:7">
       <c r="A497" t="s">
-        <v>840</v>
+        <v>851</v>
       </c>
       <c r="B497" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="C497" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="D497" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E497" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F497" t="s">
-        <v>22</v>
+        <v>365</v>
       </c>
       <c r="G497" t="s">
-        <v>807</v>
+        <v>853</v>
       </c>
     </row>
     <row r="498" hidden="1" spans="1:7">
       <c r="A498" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B498" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C498" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="D498" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E498" t="s">
         <v>11</v>
       </c>
       <c r="F498" t="s">
-        <v>365</v>
+        <v>856</v>
       </c>
       <c r="G498" t="s">
         <v>853</v>
@@ -15839,13 +15839,13 @@
     </row>
     <row r="499" hidden="1" spans="1:7">
       <c r="A499" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B499" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C499" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="D499" t="s">
         <v>18</v>
@@ -15854,7 +15854,7 @@
         <v>11</v>
       </c>
       <c r="F499" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="G499" t="s">
         <v>853</v>
@@ -15862,22 +15862,22 @@
     </row>
     <row r="500" hidden="1" spans="1:7">
       <c r="A500" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B500" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C500" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="D500" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E500" t="s">
         <v>11</v>
       </c>
       <c r="F500" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="G500" t="s">
         <v>853</v>
@@ -15885,13 +15885,13 @@
     </row>
     <row r="501" hidden="1" spans="1:7">
       <c r="A501" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B501" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C501" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="D501" t="s">
         <v>23</v>
@@ -15900,7 +15900,7 @@
         <v>11</v>
       </c>
       <c r="F501" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="G501" t="s">
         <v>853</v>
@@ -15908,22 +15908,22 @@
     </row>
     <row r="502" hidden="1" spans="1:7">
       <c r="A502" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B502" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="C502" t="s">
-        <v>392</v>
+        <v>285</v>
       </c>
       <c r="D502" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E502" t="s">
         <v>11</v>
       </c>
       <c r="F502" t="s">
-        <v>862</v>
+        <v>365</v>
       </c>
       <c r="G502" t="s">
         <v>853</v>
@@ -15931,16 +15931,16 @@
     </row>
     <row r="503" hidden="1" spans="1:7">
       <c r="A503" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B503" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C503" t="s">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="D503" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E503" t="s">
         <v>11</v>
@@ -15954,22 +15954,22 @@
     </row>
     <row r="504" hidden="1" spans="1:7">
       <c r="A504" t="s">
-        <v>865</v>
+        <v>822</v>
       </c>
       <c r="B504" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C504" t="s">
-        <v>349</v>
+        <v>741</v>
       </c>
       <c r="D504" t="s">
         <v>26</v>
       </c>
       <c r="E504" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F504" t="s">
-        <v>365</v>
+        <v>22</v>
       </c>
       <c r="G504" t="s">
         <v>853</v>
@@ -15977,22 +15977,22 @@
     </row>
     <row r="505" hidden="1" spans="1:7">
       <c r="A505" t="s">
-        <v>822</v>
+        <v>401</v>
       </c>
       <c r="B505" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C505" t="s">
-        <v>741</v>
+        <v>353</v>
       </c>
       <c r="D505" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E505" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F505" t="s">
-        <v>22</v>
+        <v>365</v>
       </c>
       <c r="G505" t="s">
         <v>853</v>
@@ -16000,22 +16000,22 @@
     </row>
     <row r="506" hidden="1" spans="1:7">
       <c r="A506" t="s">
-        <v>401</v>
+        <v>869</v>
       </c>
       <c r="B506" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C506" t="s">
-        <v>353</v>
+        <v>395</v>
       </c>
       <c r="D506" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E506" t="s">
         <v>36</v>
       </c>
       <c r="F506" t="s">
-        <v>365</v>
+        <v>871</v>
       </c>
       <c r="G506" t="s">
         <v>853</v>
@@ -16023,13 +16023,13 @@
     </row>
     <row r="507" hidden="1" spans="1:7">
       <c r="A507" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B507" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C507" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="D507" t="s">
         <v>18</v>
@@ -16038,7 +16038,7 @@
         <v>36</v>
       </c>
       <c r="F507" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="G507" t="s">
         <v>853</v>
@@ -16046,22 +16046,22 @@
     </row>
     <row r="508" hidden="1" spans="1:7">
       <c r="A508" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B508" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C508" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="D508" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E508" t="s">
         <v>36</v>
       </c>
       <c r="F508" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="G508" t="s">
         <v>853</v>
@@ -16069,13 +16069,13 @@
     </row>
     <row r="509" hidden="1" spans="1:7">
       <c r="A509" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B509" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C509" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="D509" t="s">
         <v>23</v>
@@ -16084,7 +16084,7 @@
         <v>36</v>
       </c>
       <c r="F509" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="G509" t="s">
         <v>853</v>
@@ -16092,22 +16092,22 @@
     </row>
     <row r="510" hidden="1" spans="1:7">
       <c r="A510" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B510" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C510" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="D510" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E510" t="s">
         <v>36</v>
       </c>
       <c r="F510" t="s">
-        <v>874</v>
+        <v>365</v>
       </c>
       <c r="G510" t="s">
         <v>853</v>
@@ -16115,16 +16115,16 @@
     </row>
     <row r="511" hidden="1" spans="1:7">
       <c r="A511" t="s">
-        <v>877</v>
+        <v>399</v>
       </c>
       <c r="B511" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C511" t="s">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="D511" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E511" t="s">
         <v>36</v>
@@ -16138,19 +16138,19 @@
     </row>
     <row r="512" hidden="1" spans="1:7">
       <c r="A512" t="s">
-        <v>399</v>
+        <v>880</v>
       </c>
       <c r="B512" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C512" t="s">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="D512" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E512" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F512" t="s">
         <v>365</v>
@@ -16161,22 +16161,22 @@
     </row>
     <row r="513" hidden="1" spans="1:7">
       <c r="A513" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B513" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C513" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="D513" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E513" t="s">
         <v>47</v>
       </c>
       <c r="F513" t="s">
-        <v>365</v>
+        <v>806</v>
       </c>
       <c r="G513" t="s">
         <v>853</v>
@@ -16184,16 +16184,16 @@
     </row>
     <row r="514" hidden="1" spans="1:7">
       <c r="A514" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B514" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C514" t="s">
         <v>395</v>
       </c>
       <c r="D514" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E514" t="s">
         <v>47</v>
@@ -16207,22 +16207,22 @@
     </row>
     <row r="515" hidden="1" spans="1:7">
       <c r="A515" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B515" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C515" t="s">
-        <v>395</v>
+        <v>308</v>
       </c>
       <c r="D515" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E515" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F515" t="s">
-        <v>806</v>
+        <v>365</v>
       </c>
       <c r="G515" t="s">
         <v>853</v>
@@ -16230,16 +16230,16 @@
     </row>
     <row r="516" hidden="1" spans="1:7">
       <c r="A516" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B516" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C516" t="s">
-        <v>308</v>
+        <v>530</v>
       </c>
       <c r="D516" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E516" t="s">
         <v>54</v>
@@ -16253,16 +16253,16 @@
     </row>
     <row r="517" hidden="1" spans="1:7">
       <c r="A517" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B517" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C517" t="s">
-        <v>530</v>
+        <v>308</v>
       </c>
       <c r="D517" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E517" t="s">
         <v>54</v>
@@ -16276,39 +16276,39 @@
     </row>
     <row r="518" hidden="1" spans="1:7">
       <c r="A518" t="s">
-        <v>890</v>
+        <v>360</v>
       </c>
       <c r="B518" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C518" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="D518" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E518" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F518" t="s">
-        <v>365</v>
+        <v>893</v>
       </c>
       <c r="G518" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
     </row>
     <row r="519" hidden="1" spans="1:7">
       <c r="A519" t="s">
-        <v>360</v>
+        <v>895</v>
       </c>
       <c r="B519" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="C519" t="s">
-        <v>262</v>
+        <v>338</v>
       </c>
       <c r="D519" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E519" t="s">
         <v>11</v>
@@ -16322,16 +16322,16 @@
     </row>
     <row r="520" hidden="1" spans="1:7">
       <c r="A520" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B520" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C520" t="s">
         <v>338</v>
       </c>
       <c r="D520" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E520" t="s">
         <v>11</v>
@@ -16345,16 +16345,16 @@
     </row>
     <row r="521" hidden="1" spans="1:7">
       <c r="A521" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B521" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C521" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="D521" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E521" t="s">
         <v>11</v>
@@ -16368,22 +16368,22 @@
     </row>
     <row r="522" hidden="1" spans="1:7">
       <c r="A522" t="s">
-        <v>899</v>
+        <v>822</v>
       </c>
       <c r="B522" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C522" t="s">
-        <v>285</v>
+        <v>741</v>
       </c>
       <c r="D522" t="s">
         <v>26</v>
       </c>
       <c r="E522" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F522" t="s">
-        <v>893</v>
+        <v>22</v>
       </c>
       <c r="G522" t="s">
         <v>894</v>
@@ -16391,22 +16391,22 @@
     </row>
     <row r="523" hidden="1" spans="1:7">
       <c r="A523" t="s">
-        <v>822</v>
+        <v>339</v>
       </c>
       <c r="B523" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C523" t="s">
-        <v>741</v>
+        <v>262</v>
       </c>
       <c r="D523" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E523" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F523" t="s">
-        <v>22</v>
+        <v>893</v>
       </c>
       <c r="G523" t="s">
         <v>894</v>
@@ -16414,16 +16414,16 @@
     </row>
     <row r="524" hidden="1" spans="1:7">
       <c r="A524" t="s">
-        <v>339</v>
+        <v>903</v>
       </c>
       <c r="B524" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C524" t="s">
-        <v>262</v>
+        <v>375</v>
       </c>
       <c r="D524" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E524" t="s">
         <v>36</v>
@@ -16437,16 +16437,16 @@
     </row>
     <row r="525" hidden="1" spans="1:7">
       <c r="A525" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B525" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C525" t="s">
         <v>375</v>
       </c>
       <c r="D525" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E525" t="s">
         <v>36</v>
@@ -16460,16 +16460,16 @@
     </row>
     <row r="526" hidden="1" spans="1:7">
       <c r="A526" t="s">
-        <v>905</v>
+        <v>804</v>
       </c>
       <c r="B526" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C526" t="s">
-        <v>375</v>
+        <v>530</v>
       </c>
       <c r="D526" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E526" t="s">
         <v>36</v>
@@ -16483,16 +16483,16 @@
     </row>
     <row r="527" hidden="1" spans="1:7">
       <c r="A527" t="s">
-        <v>804</v>
+        <v>908</v>
       </c>
       <c r="B527" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C527" t="s">
-        <v>530</v>
+        <v>741</v>
       </c>
       <c r="D527" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E527" t="s">
         <v>36</v>
@@ -16506,19 +16506,19 @@
     </row>
     <row r="528" hidden="1" spans="1:7">
       <c r="A528" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B528" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C528" t="s">
-        <v>741</v>
+        <v>372</v>
       </c>
       <c r="D528" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E528" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F528" t="s">
         <v>893</v>
@@ -16529,16 +16529,16 @@
     </row>
     <row r="529" hidden="1" spans="1:7">
       <c r="A529" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B529" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C529" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="D529" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E529" t="s">
         <v>47</v>
@@ -16552,16 +16552,16 @@
     </row>
     <row r="530" hidden="1" spans="1:7">
       <c r="A530" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B530" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C530" t="s">
         <v>353</v>
       </c>
       <c r="D530" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E530" t="s">
         <v>47</v>
@@ -16575,16 +16575,16 @@
     </row>
     <row r="531" hidden="1" spans="1:7">
       <c r="A531" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B531" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C531" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="D531" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E531" t="s">
         <v>47</v>
@@ -16598,22 +16598,22 @@
     </row>
     <row r="532" hidden="1" spans="1:7">
       <c r="A532" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B532" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C532" t="s">
-        <v>372</v>
+        <v>262</v>
       </c>
       <c r="D532" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E532" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F532" t="s">
-        <v>893</v>
+        <v>920</v>
       </c>
       <c r="G532" t="s">
         <v>894</v>
@@ -16621,22 +16621,22 @@
     </row>
     <row r="533" hidden="1" spans="1:7">
       <c r="A533" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="B533" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C533" t="s">
-        <v>262</v>
+        <v>384</v>
       </c>
       <c r="D533" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E533" t="s">
         <v>54</v>
       </c>
       <c r="F533" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G533" t="s">
         <v>894</v>
@@ -16644,13 +16644,13 @@
     </row>
     <row r="534" hidden="1" spans="1:7">
       <c r="A534" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="B534" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C534" t="s">
-        <v>384</v>
+        <v>741</v>
       </c>
       <c r="D534" t="s">
         <v>18</v>
@@ -16659,7 +16659,7 @@
         <v>54</v>
       </c>
       <c r="F534" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="G534" t="s">
         <v>894</v>
@@ -16667,22 +16667,22 @@
     </row>
     <row r="535" hidden="1" spans="1:7">
       <c r="A535" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B535" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C535" t="s">
-        <v>741</v>
+        <v>384</v>
       </c>
       <c r="D535" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E535" t="s">
         <v>54</v>
       </c>
       <c r="F535" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="G535" t="s">
         <v>894</v>
@@ -16690,13 +16690,13 @@
     </row>
     <row r="536" hidden="1" spans="1:7">
       <c r="A536" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B536" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C536" t="s">
-        <v>384</v>
+        <v>741</v>
       </c>
       <c r="D536" t="s">
         <v>23</v>
@@ -16705,7 +16705,7 @@
         <v>54</v>
       </c>
       <c r="F536" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="G536" t="s">
         <v>894</v>
@@ -16713,22 +16713,22 @@
     </row>
     <row r="537" hidden="1" spans="1:7">
       <c r="A537" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B537" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C537" t="s">
-        <v>741</v>
+        <v>262</v>
       </c>
       <c r="D537" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E537" t="s">
         <v>54</v>
       </c>
       <c r="F537" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="G537" t="s">
         <v>894</v>
@@ -16736,45 +16736,45 @@
     </row>
     <row r="538" hidden="1" spans="1:7">
       <c r="A538" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B538" t="s">
-        <v>919</v>
+        <v>934</v>
       </c>
       <c r="C538" t="s">
-        <v>262</v>
+        <v>935</v>
       </c>
       <c r="D538" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E538" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F538" t="s">
-        <v>932</v>
+        <v>274</v>
       </c>
       <c r="G538" t="s">
-        <v>894</v>
+        <v>936</v>
       </c>
     </row>
     <row r="539" hidden="1" spans="1:7">
       <c r="A539" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B539" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C539" t="s">
         <v>935</v>
       </c>
       <c r="D539" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E539" t="s">
         <v>11</v>
       </c>
       <c r="F539" t="s">
-        <v>274</v>
+        <v>939</v>
       </c>
       <c r="G539" t="s">
         <v>936</v>
@@ -16782,7 +16782,7 @@
     </row>
     <row r="540" hidden="1" spans="1:7">
       <c r="A540" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B540" t="s">
         <v>938</v>
@@ -16791,7 +16791,7 @@
         <v>935</v>
       </c>
       <c r="D540" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E540" t="s">
         <v>11</v>
@@ -16805,22 +16805,22 @@
     </row>
     <row r="541" hidden="1" spans="1:7">
       <c r="A541" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B541" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="C541" t="s">
         <v>935</v>
       </c>
       <c r="D541" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E541" t="s">
         <v>11</v>
       </c>
       <c r="F541" t="s">
-        <v>939</v>
+        <v>274</v>
       </c>
       <c r="G541" t="s">
         <v>936</v>
@@ -16828,16 +16828,16 @@
     </row>
     <row r="542" hidden="1" spans="1:7">
       <c r="A542" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B542" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C542" t="s">
         <v>935</v>
       </c>
       <c r="D542" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E542" t="s">
         <v>11</v>
@@ -16851,19 +16851,19 @@
     </row>
     <row r="543" hidden="1" spans="1:7">
       <c r="A543" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B543" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C543" t="s">
-        <v>935</v>
+        <v>741</v>
       </c>
       <c r="D543" t="s">
         <v>26</v>
       </c>
       <c r="E543" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F543" t="s">
         <v>274</v>
@@ -16874,22 +16874,22 @@
     </row>
     <row r="544" hidden="1" spans="1:7">
       <c r="A544" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B544" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C544" t="s">
-        <v>741</v>
+        <v>591</v>
       </c>
       <c r="D544" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E544" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F544" t="s">
-        <v>274</v>
+        <v>949</v>
       </c>
       <c r="G544" t="s">
         <v>936</v>
@@ -16897,13 +16897,13 @@
     </row>
     <row r="545" hidden="1" spans="1:7">
       <c r="A545" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B545" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C545" t="s">
-        <v>591</v>
+        <v>952</v>
       </c>
       <c r="D545" t="s">
         <v>10</v>
@@ -16920,22 +16920,22 @@
     </row>
     <row r="546" hidden="1" spans="1:7">
       <c r="A546" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B546" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C546" t="s">
-        <v>952</v>
+        <v>695</v>
       </c>
       <c r="D546" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E546" t="s">
         <v>36</v>
       </c>
       <c r="F546" t="s">
-        <v>949</v>
+        <v>274</v>
       </c>
       <c r="G546" t="s">
         <v>936</v>
@@ -16943,16 +16943,16 @@
     </row>
     <row r="547" hidden="1" spans="1:7">
       <c r="A547" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B547" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C547" t="s">
         <v>695</v>
       </c>
       <c r="D547" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E547" t="s">
         <v>36</v>
@@ -16966,16 +16966,16 @@
     </row>
     <row r="548" hidden="1" spans="1:7">
       <c r="A548" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B548" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C548" t="s">
-        <v>695</v>
+        <v>759</v>
       </c>
       <c r="D548" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E548" t="s">
         <v>36</v>
@@ -16989,22 +16989,22 @@
     </row>
     <row r="549" hidden="1" spans="1:7">
       <c r="A549" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
       <c r="B549" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
       <c r="C549" t="s">
-        <v>759</v>
+        <v>591</v>
       </c>
       <c r="D549" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E549" t="s">
         <v>36</v>
       </c>
       <c r="F549" t="s">
-        <v>274</v>
+        <v>949</v>
       </c>
       <c r="G549" t="s">
         <v>936</v>
@@ -17012,13 +17012,13 @@
     </row>
     <row r="550" hidden="1" spans="1:7">
       <c r="A550" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B550" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C550" t="s">
-        <v>591</v>
+        <v>952</v>
       </c>
       <c r="D550" t="s">
         <v>26</v>
@@ -17035,22 +17035,22 @@
     </row>
     <row r="551" hidden="1" spans="1:7">
       <c r="A551" t="s">
-        <v>950</v>
+        <v>959</v>
       </c>
       <c r="B551" t="s">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="C551" t="s">
-        <v>952</v>
+        <v>349</v>
       </c>
       <c r="D551" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E551" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F551" t="s">
-        <v>949</v>
+        <v>651</v>
       </c>
       <c r="G551" t="s">
         <v>936</v>
@@ -17058,22 +17058,22 @@
     </row>
     <row r="552" hidden="1" spans="1:7">
       <c r="A552" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B552" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C552" t="s">
-        <v>349</v>
+        <v>769</v>
       </c>
       <c r="D552" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E552" t="s">
         <v>47</v>
       </c>
       <c r="F552" t="s">
-        <v>651</v>
+        <v>963</v>
       </c>
       <c r="G552" t="s">
         <v>936</v>
@@ -17081,7 +17081,7 @@
     </row>
     <row r="553" hidden="1" spans="1:7">
       <c r="A553" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B553" t="s">
         <v>962</v>
@@ -17090,7 +17090,7 @@
         <v>769</v>
       </c>
       <c r="D553" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E553" t="s">
         <v>47</v>
@@ -17104,22 +17104,22 @@
     </row>
     <row r="554" hidden="1" spans="1:7">
       <c r="A554" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B554" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="C554" t="s">
-        <v>769</v>
+        <v>952</v>
       </c>
       <c r="D554" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E554" t="s">
         <v>47</v>
       </c>
       <c r="F554" t="s">
-        <v>963</v>
+        <v>274</v>
       </c>
       <c r="G554" t="s">
         <v>936</v>
@@ -17127,16 +17127,16 @@
     </row>
     <row r="555" hidden="1" spans="1:7">
       <c r="A555" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B555" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C555" t="s">
         <v>952</v>
       </c>
       <c r="D555" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E555" t="s">
         <v>47</v>
@@ -17150,22 +17150,22 @@
     </row>
     <row r="556" hidden="1" spans="1:7">
       <c r="A556" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B556" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C556" t="s">
-        <v>952</v>
+        <v>695</v>
       </c>
       <c r="D556" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E556" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F556" t="s">
-        <v>274</v>
+        <v>971</v>
       </c>
       <c r="G556" t="s">
         <v>936</v>
@@ -17179,7 +17179,7 @@
         <v>970</v>
       </c>
       <c r="C557" t="s">
-        <v>695</v>
+        <v>972</v>
       </c>
       <c r="D557" t="s">
         <v>18</v>
@@ -17196,16 +17196,16 @@
     </row>
     <row r="558" hidden="1" spans="1:7">
       <c r="A558" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="B558" t="s">
         <v>970</v>
       </c>
       <c r="C558" t="s">
-        <v>972</v>
+        <v>695</v>
       </c>
       <c r="D558" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E558" t="s">
         <v>54</v>
@@ -17225,7 +17225,7 @@
         <v>970</v>
       </c>
       <c r="C559" t="s">
-        <v>695</v>
+        <v>972</v>
       </c>
       <c r="D559" t="s">
         <v>23</v>
@@ -17242,22 +17242,22 @@
     </row>
     <row r="560" hidden="1" spans="1:7">
       <c r="A560" t="s">
-        <v>973</v>
+        <v>804</v>
       </c>
       <c r="B560" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="C560" t="s">
-        <v>972</v>
+        <v>530</v>
       </c>
       <c r="D560" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E560" t="s">
         <v>54</v>
       </c>
       <c r="F560" t="s">
-        <v>971</v>
+        <v>365</v>
       </c>
       <c r="G560" t="s">
         <v>936</v>
@@ -17265,22 +17265,22 @@
     </row>
     <row r="561" hidden="1" spans="1:7">
       <c r="A561" t="s">
-        <v>804</v>
+        <v>975</v>
       </c>
       <c r="B561" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C561" t="s">
-        <v>530</v>
+        <v>769</v>
       </c>
       <c r="D561" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E561" t="s">
         <v>54</v>
       </c>
       <c r="F561" t="s">
-        <v>365</v>
+        <v>274</v>
       </c>
       <c r="G561" t="s">
         <v>936</v>
@@ -17288,45 +17288,45 @@
     </row>
     <row r="562" hidden="1" spans="1:7">
       <c r="A562" t="s">
-        <v>975</v>
+        <v>804</v>
       </c>
       <c r="B562" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C562" t="s">
-        <v>769</v>
+        <v>530</v>
       </c>
       <c r="D562" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E562" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F562" t="s">
-        <v>274</v>
+        <v>806</v>
       </c>
       <c r="G562" t="s">
-        <v>936</v>
+        <v>978</v>
       </c>
     </row>
     <row r="563" hidden="1" spans="1:7">
       <c r="A563" t="s">
-        <v>804</v>
+        <v>979</v>
       </c>
       <c r="B563" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C563" t="s">
-        <v>530</v>
+        <v>384</v>
       </c>
       <c r="D563" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E563" t="s">
         <v>11</v>
       </c>
       <c r="F563" t="s">
-        <v>806</v>
+        <v>923</v>
       </c>
       <c r="G563" t="s">
         <v>978</v>
@@ -17334,7 +17334,7 @@
     </row>
     <row r="564" hidden="1" spans="1:7">
       <c r="A564" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B564" t="s">
         <v>980</v>
@@ -17343,13 +17343,13 @@
         <v>384</v>
       </c>
       <c r="D564" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E564" t="s">
         <v>11</v>
       </c>
       <c r="F564" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="G564" t="s">
         <v>978</v>
@@ -17357,22 +17357,22 @@
     </row>
     <row r="565" hidden="1" spans="1:7">
       <c r="A565" t="s">
-        <v>981</v>
+        <v>360</v>
       </c>
       <c r="B565" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C565" t="s">
-        <v>384</v>
+        <v>262</v>
       </c>
       <c r="D565" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E565" t="s">
         <v>11</v>
       </c>
       <c r="F565" t="s">
-        <v>928</v>
+        <v>806</v>
       </c>
       <c r="G565" t="s">
         <v>978</v>
@@ -17380,16 +17380,16 @@
     </row>
     <row r="566" hidden="1" spans="1:7">
       <c r="A566" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="B566" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C566" t="s">
         <v>262</v>
       </c>
       <c r="D566" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E566" t="s">
         <v>11</v>
@@ -17403,22 +17403,22 @@
     </row>
     <row r="567" hidden="1" spans="1:7">
       <c r="A567" t="s">
-        <v>339</v>
+        <v>822</v>
       </c>
       <c r="B567" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C567" t="s">
-        <v>262</v>
+        <v>741</v>
       </c>
       <c r="D567" t="s">
         <v>26</v>
       </c>
       <c r="E567" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F567" t="s">
-        <v>806</v>
+        <v>22</v>
       </c>
       <c r="G567" t="s">
         <v>978</v>
@@ -17426,22 +17426,22 @@
     </row>
     <row r="568" hidden="1" spans="1:7">
       <c r="A568" t="s">
-        <v>822</v>
+        <v>835</v>
       </c>
       <c r="B568" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C568" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="D568" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E568" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F568" t="s">
-        <v>22</v>
+        <v>806</v>
       </c>
       <c r="G568" t="s">
         <v>978</v>
@@ -17449,16 +17449,16 @@
     </row>
     <row r="569" hidden="1" spans="1:7">
       <c r="A569" t="s">
-        <v>835</v>
+        <v>986</v>
       </c>
       <c r="B569" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C569" t="s">
-        <v>759</v>
+        <v>280</v>
       </c>
       <c r="D569" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E569" t="s">
         <v>36</v>
@@ -17472,16 +17472,16 @@
     </row>
     <row r="570" hidden="1" spans="1:7">
       <c r="A570" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B570" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C570" t="s">
         <v>280</v>
       </c>
       <c r="D570" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E570" t="s">
         <v>36</v>
@@ -17495,22 +17495,22 @@
     </row>
     <row r="571" hidden="1" spans="1:7">
       <c r="A571" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B571" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C571" t="s">
-        <v>280</v>
+        <v>741</v>
       </c>
       <c r="D571" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E571" t="s">
         <v>36</v>
       </c>
       <c r="F571" t="s">
-        <v>806</v>
+        <v>920</v>
       </c>
       <c r="G571" t="s">
         <v>978</v>
@@ -17518,13 +17518,13 @@
     </row>
     <row r="572" hidden="1" spans="1:7">
       <c r="A572" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B572" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C572" t="s">
-        <v>741</v>
+        <v>262</v>
       </c>
       <c r="D572" t="s">
         <v>25</v>
@@ -17533,7 +17533,7 @@
         <v>36</v>
       </c>
       <c r="F572" t="s">
-        <v>920</v>
+        <v>994</v>
       </c>
       <c r="G572" t="s">
         <v>978</v>
@@ -17541,22 +17541,22 @@
     </row>
     <row r="573" hidden="1" spans="1:7">
       <c r="A573" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B573" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C573" t="s">
-        <v>262</v>
+        <v>741</v>
       </c>
       <c r="D573" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E573" t="s">
         <v>36</v>
       </c>
       <c r="F573" t="s">
-        <v>994</v>
+        <v>932</v>
       </c>
       <c r="G573" t="s">
         <v>978</v>
@@ -17564,13 +17564,13 @@
     </row>
     <row r="574" hidden="1" spans="1:7">
       <c r="A574" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B574" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C574" t="s">
-        <v>741</v>
+        <v>262</v>
       </c>
       <c r="D574" t="s">
         <v>26</v>
@@ -17579,7 +17579,7 @@
         <v>36</v>
       </c>
       <c r="F574" t="s">
-        <v>932</v>
+        <v>997</v>
       </c>
       <c r="G574" t="s">
         <v>978</v>
@@ -17587,22 +17587,22 @@
     </row>
     <row r="575" hidden="1" spans="1:7">
       <c r="A575" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B575" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="C575" t="s">
-        <v>262</v>
+        <v>375</v>
       </c>
       <c r="D575" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E575" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F575" t="s">
-        <v>997</v>
+        <v>806</v>
       </c>
       <c r="G575" t="s">
         <v>978</v>
@@ -17610,16 +17610,16 @@
     </row>
     <row r="576" hidden="1" spans="1:7">
       <c r="A576" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B576" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C576" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D576" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E576" t="s">
         <v>47</v>
@@ -17633,16 +17633,16 @@
     </row>
     <row r="577" hidden="1" spans="1:7">
       <c r="A577" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B577" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C577" t="s">
         <v>372</v>
       </c>
       <c r="D577" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E577" t="s">
         <v>47</v>
@@ -17656,16 +17656,16 @@
     </row>
     <row r="578" hidden="1" spans="1:7">
       <c r="A578" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B578" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C578" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D578" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E578" t="s">
         <v>47</v>
@@ -17679,19 +17679,19 @@
     </row>
     <row r="579" hidden="1" spans="1:7">
       <c r="A579" t="s">
-        <v>1004</v>
+        <v>408</v>
       </c>
       <c r="B579" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C579" t="s">
-        <v>375</v>
+        <v>158</v>
       </c>
       <c r="D579" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E579" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F579" t="s">
         <v>806</v>
@@ -17702,16 +17702,16 @@
     </row>
     <row r="580" hidden="1" spans="1:7">
       <c r="A580" t="s">
-        <v>408</v>
+        <v>1007</v>
       </c>
       <c r="B580" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C580" t="s">
-        <v>158</v>
+        <v>280</v>
       </c>
       <c r="D580" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E580" t="s">
         <v>54</v>
@@ -17725,16 +17725,16 @@
     </row>
     <row r="581" hidden="1" spans="1:7">
       <c r="A581" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B581" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C581" t="s">
         <v>280</v>
       </c>
       <c r="D581" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E581" t="s">
         <v>54</v>
@@ -17748,45 +17748,45 @@
     </row>
     <row r="582" hidden="1" spans="1:7">
       <c r="A582" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B582" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C582" t="s">
-        <v>280</v>
+        <v>364</v>
       </c>
       <c r="D582" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E582" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F582" t="s">
-        <v>806</v>
+        <v>1013</v>
       </c>
       <c r="G582" t="s">
-        <v>978</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="583" hidden="1" spans="1:7">
       <c r="A583" t="s">
-        <v>1011</v>
+        <v>100</v>
       </c>
       <c r="B583" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C583" t="s">
-        <v>364</v>
+        <v>1016</v>
       </c>
       <c r="D583" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E583" t="s">
         <v>11</v>
       </c>
       <c r="F583" t="s">
-        <v>1013</v>
+        <v>416</v>
       </c>
       <c r="G583" t="s">
         <v>1014</v>
@@ -17800,16 +17800,16 @@
         <v>1015</v>
       </c>
       <c r="C584" t="s">
-        <v>1016</v>
+        <v>58</v>
       </c>
       <c r="D584" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E584" t="s">
         <v>11</v>
       </c>
       <c r="F584" t="s">
-        <v>416</v>
+        <v>1017</v>
       </c>
       <c r="G584" t="s">
         <v>1014</v>
@@ -17817,13 +17817,13 @@
     </row>
     <row r="585" hidden="1" spans="1:7">
       <c r="A585" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B585" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="C585" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D585" t="s">
         <v>18</v>
@@ -17832,7 +17832,7 @@
         <v>11</v>
       </c>
       <c r="F585" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="G585" t="s">
         <v>1014</v>
@@ -17840,22 +17840,22 @@
     </row>
     <row r="586" hidden="1" spans="1:7">
       <c r="A586" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B586" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C586" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D586" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E586" t="s">
         <v>11</v>
       </c>
       <c r="F586" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G586" t="s">
         <v>1014</v>
@@ -17863,13 +17863,13 @@
     </row>
     <row r="587" hidden="1" spans="1:7">
       <c r="A587" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B587" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="C587" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D587" t="s">
         <v>23</v>
@@ -17878,7 +17878,7 @@
         <v>11</v>
       </c>
       <c r="F587" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="G587" t="s">
         <v>1014</v>
@@ -17886,13 +17886,13 @@
     </row>
     <row r="588" hidden="1" spans="1:7">
       <c r="A588" t="s">
-        <v>103</v>
+        <v>1021</v>
       </c>
       <c r="B588" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C588" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D588" t="s">
         <v>23</v>
@@ -17901,7 +17901,7 @@
         <v>11</v>
       </c>
       <c r="F588" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="G588" t="s">
         <v>1014</v>
@@ -17909,22 +17909,22 @@
     </row>
     <row r="589" hidden="1" spans="1:7">
       <c r="A589" t="s">
-        <v>1021</v>
+        <v>107</v>
       </c>
       <c r="B589" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C589" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D589" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E589" t="s">
         <v>11</v>
       </c>
       <c r="F589" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="G589" t="s">
         <v>1014</v>
@@ -17932,22 +17932,22 @@
     </row>
     <row r="590" hidden="1" spans="1:7">
       <c r="A590" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B590" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
       <c r="C590" t="s">
         <v>58</v>
       </c>
       <c r="D590" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E590" t="s">
         <v>11</v>
       </c>
       <c r="F590" t="s">
-        <v>1025</v>
+        <v>592</v>
       </c>
       <c r="G590" t="s">
         <v>1014</v>
@@ -17955,13 +17955,13 @@
     </row>
     <row r="591" hidden="1" spans="1:7">
       <c r="A591" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B591" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="C591" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D591" t="s">
         <v>26</v>
@@ -17970,7 +17970,7 @@
         <v>11</v>
       </c>
       <c r="F591" t="s">
-        <v>592</v>
+        <v>505</v>
       </c>
       <c r="G591" t="s">
         <v>1014</v>
@@ -17978,22 +17978,22 @@
     </row>
     <row r="592" hidden="1" spans="1:7">
       <c r="A592" t="s">
-        <v>103</v>
+        <v>1026</v>
       </c>
       <c r="B592" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="C592" t="s">
-        <v>38</v>
+        <v>1028</v>
       </c>
       <c r="D592" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E592" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F592" t="s">
-        <v>505</v>
+        <v>1029</v>
       </c>
       <c r="G592" t="s">
         <v>1014</v>
@@ -18001,13 +18001,13 @@
     </row>
     <row r="593" hidden="1" spans="1:7">
       <c r="A593" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B593" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C593" t="s">
-        <v>1028</v>
+        <v>236</v>
       </c>
       <c r="D593" t="s">
         <v>10</v>
@@ -18016,7 +18016,7 @@
         <v>27</v>
       </c>
       <c r="F593" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="G593" t="s">
         <v>1014</v>
@@ -18024,22 +18024,22 @@
     </row>
     <row r="594" hidden="1" spans="1:7">
       <c r="A594" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="B594" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="C594" t="s">
-        <v>236</v>
+        <v>1028</v>
       </c>
       <c r="D594" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E594" t="s">
         <v>27</v>
       </c>
       <c r="F594" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="G594" t="s">
         <v>1014</v>
@@ -18047,13 +18047,13 @@
     </row>
     <row r="595" hidden="1" spans="1:7">
       <c r="A595" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B595" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C595" t="s">
-        <v>1028</v>
+        <v>236</v>
       </c>
       <c r="D595" t="s">
         <v>14</v>
@@ -18062,7 +18062,7 @@
         <v>27</v>
       </c>
       <c r="F595" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G595" t="s">
         <v>1014</v>
@@ -18070,13 +18070,13 @@
     </row>
     <row r="596" hidden="1" spans="1:7">
       <c r="A596" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="B596" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C596" t="s">
-        <v>236</v>
+        <v>22</v>
       </c>
       <c r="D596" t="s">
         <v>14</v>
@@ -18085,7 +18085,7 @@
         <v>27</v>
       </c>
       <c r="F596" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="G596" t="s">
         <v>1014</v>
@@ -18093,22 +18093,22 @@
     </row>
     <row r="597" hidden="1" spans="1:7">
       <c r="A597" t="s">
-        <v>1034</v>
+        <v>120</v>
       </c>
       <c r="B597" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C597" t="s">
-        <v>22</v>
+        <v>1038</v>
       </c>
       <c r="D597" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E597" t="s">
         <v>27</v>
       </c>
       <c r="F597" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="G597" t="s">
         <v>1014</v>
@@ -18116,13 +18116,13 @@
     </row>
     <row r="598" hidden="1" spans="1:7">
       <c r="A598" t="s">
-        <v>120</v>
+        <v>1034</v>
       </c>
       <c r="B598" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C598" t="s">
-        <v>1038</v>
+        <v>22</v>
       </c>
       <c r="D598" t="s">
         <v>18</v>
@@ -18131,7 +18131,7 @@
         <v>27</v>
       </c>
       <c r="F598" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="G598" t="s">
         <v>1014</v>
@@ -18139,22 +18139,22 @@
     </row>
     <row r="599" hidden="1" spans="1:7">
       <c r="A599" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="B599" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="C599" t="s">
-        <v>22</v>
+        <v>1028</v>
       </c>
       <c r="D599" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E599" t="s">
         <v>27</v>
       </c>
       <c r="F599" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="G599" t="s">
         <v>1014</v>
@@ -18162,13 +18162,13 @@
     </row>
     <row r="600" hidden="1" spans="1:7">
       <c r="A600" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B600" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C600" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="D600" t="s">
         <v>25</v>
@@ -18177,7 +18177,7 @@
         <v>27</v>
       </c>
       <c r="F600" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="G600" t="s">
         <v>1014</v>
@@ -18185,13 +18185,13 @@
     </row>
     <row r="601" hidden="1" spans="1:7">
       <c r="A601" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="B601" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C601" t="s">
-        <v>1041</v>
+        <v>22</v>
       </c>
       <c r="D601" t="s">
         <v>25</v>
@@ -18200,7 +18200,7 @@
         <v>27</v>
       </c>
       <c r="F601" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="G601" t="s">
         <v>1014</v>
@@ -18208,22 +18208,22 @@
     </row>
     <row r="602" hidden="1" spans="1:7">
       <c r="A602" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="B602" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="C602" t="s">
-        <v>22</v>
+        <v>1028</v>
       </c>
       <c r="D602" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E602" t="s">
         <v>27</v>
       </c>
       <c r="F602" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="G602" t="s">
         <v>1014</v>
@@ -18231,13 +18231,13 @@
     </row>
     <row r="603" hidden="1" spans="1:7">
       <c r="A603" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B603" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C603" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="D603" t="s">
         <v>26</v>
@@ -18246,7 +18246,7 @@
         <v>27</v>
       </c>
       <c r="F603" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="G603" t="s">
         <v>1014</v>
@@ -18254,13 +18254,13 @@
     </row>
     <row r="604" hidden="1" spans="1:7">
       <c r="A604" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="B604" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C604" t="s">
-        <v>1041</v>
+        <v>22</v>
       </c>
       <c r="D604" t="s">
         <v>26</v>
@@ -18269,7 +18269,7 @@
         <v>27</v>
       </c>
       <c r="F604" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G604" t="s">
         <v>1014</v>
@@ -18277,22 +18277,22 @@
     </row>
     <row r="605" hidden="1" spans="1:7">
       <c r="A605" t="s">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="B605" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="C605" t="s">
-        <v>22</v>
+        <v>375</v>
       </c>
       <c r="D605" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E605" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F605" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="G605" t="s">
         <v>1014</v>
@@ -18300,22 +18300,22 @@
     </row>
     <row r="606" hidden="1" spans="1:7">
       <c r="A606" t="s">
-        <v>1046</v>
+        <v>100</v>
       </c>
       <c r="B606" t="s">
-        <v>1047</v>
+        <v>1015</v>
       </c>
       <c r="C606" t="s">
-        <v>375</v>
+        <v>58</v>
       </c>
       <c r="D606" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E606" t="s">
         <v>36</v>
       </c>
       <c r="F606" t="s">
-        <v>1048</v>
+        <v>1020</v>
       </c>
       <c r="G606" t="s">
         <v>1014</v>
@@ -18323,22 +18323,22 @@
     </row>
     <row r="607" hidden="1" spans="1:7">
       <c r="A607" t="s">
-        <v>100</v>
+        <v>1034</v>
       </c>
       <c r="B607" t="s">
-        <v>1015</v>
+        <v>1035</v>
       </c>
       <c r="C607" t="s">
-        <v>58</v>
+        <v>1049</v>
       </c>
       <c r="D607" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E607" t="s">
         <v>36</v>
       </c>
       <c r="F607" t="s">
-        <v>1020</v>
+        <v>1050</v>
       </c>
       <c r="G607" t="s">
         <v>1014</v>
@@ -18346,13 +18346,13 @@
     </row>
     <row r="608" hidden="1" spans="1:7">
       <c r="A608" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="B608" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="C608" t="s">
-        <v>1049</v>
+        <v>22</v>
       </c>
       <c r="D608" t="s">
         <v>18</v>
@@ -18361,7 +18361,7 @@
         <v>36</v>
       </c>
       <c r="F608" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G608" t="s">
         <v>1014</v>
@@ -18369,13 +18369,13 @@
     </row>
     <row r="609" hidden="1" spans="1:7">
       <c r="A609" t="s">
-        <v>1026</v>
+        <v>1052</v>
       </c>
       <c r="B609" t="s">
-        <v>1027</v>
+        <v>1053</v>
       </c>
       <c r="C609" t="s">
-        <v>22</v>
+        <v>587</v>
       </c>
       <c r="D609" t="s">
         <v>18</v>
@@ -18384,7 +18384,7 @@
         <v>36</v>
       </c>
       <c r="F609" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="G609" t="s">
         <v>1014</v>
@@ -18392,22 +18392,22 @@
     </row>
     <row r="610" hidden="1" spans="1:7">
       <c r="A610" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="B610" t="s">
-        <v>1053</v>
+        <v>1035</v>
       </c>
       <c r="C610" t="s">
-        <v>587</v>
+        <v>1049</v>
       </c>
       <c r="D610" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E610" t="s">
         <v>36</v>
       </c>
       <c r="F610" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="G610" t="s">
         <v>1014</v>
@@ -18415,13 +18415,13 @@
     </row>
     <row r="611" hidden="1" spans="1:7">
       <c r="A611" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="B611" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="C611" t="s">
-        <v>1049</v>
+        <v>22</v>
       </c>
       <c r="D611" t="s">
         <v>23</v>
@@ -18430,7 +18430,7 @@
         <v>36</v>
       </c>
       <c r="F611" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G611" t="s">
         <v>1014</v>
@@ -18438,13 +18438,13 @@
     </row>
     <row r="612" hidden="1" spans="1:7">
       <c r="A612" t="s">
-        <v>1026</v>
+        <v>1052</v>
       </c>
       <c r="B612" t="s">
-        <v>1027</v>
+        <v>1053</v>
       </c>
       <c r="C612" t="s">
-        <v>22</v>
+        <v>587</v>
       </c>
       <c r="D612" t="s">
         <v>23</v>
@@ -18453,7 +18453,7 @@
         <v>36</v>
       </c>
       <c r="F612" t="s">
-        <v>1051</v>
+        <v>592</v>
       </c>
       <c r="G612" t="s">
         <v>1014</v>
@@ -18461,22 +18461,22 @@
     </row>
     <row r="613" hidden="1" spans="1:7">
       <c r="A613" t="s">
-        <v>1052</v>
+        <v>113</v>
       </c>
       <c r="B613" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C613" t="s">
-        <v>587</v>
+        <v>318</v>
       </c>
       <c r="D613" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E613" t="s">
         <v>36</v>
       </c>
       <c r="F613" t="s">
-        <v>592</v>
+        <v>1048</v>
       </c>
       <c r="G613" t="s">
         <v>1014</v>
@@ -18484,22 +18484,22 @@
     </row>
     <row r="614" hidden="1" spans="1:7">
       <c r="A614" t="s">
-        <v>113</v>
+        <v>1052</v>
       </c>
       <c r="B614" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C614" t="s">
-        <v>318</v>
+        <v>22</v>
       </c>
       <c r="D614" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E614" t="s">
         <v>36</v>
       </c>
       <c r="F614" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="G614" t="s">
         <v>1014</v>
@@ -18507,10 +18507,10 @@
     </row>
     <row r="615" hidden="1" spans="1:7">
       <c r="A615" t="s">
-        <v>1052</v>
+        <v>103</v>
       </c>
       <c r="B615" t="s">
-        <v>1053</v>
+        <v>1018</v>
       </c>
       <c r="C615" t="s">
         <v>22</v>
@@ -18522,7 +18522,7 @@
         <v>36</v>
       </c>
       <c r="F615" t="s">
-        <v>1056</v>
+        <v>520</v>
       </c>
       <c r="G615" t="s">
         <v>1014</v>
@@ -18530,13 +18530,13 @@
     </row>
     <row r="616" hidden="1" spans="1:7">
       <c r="A616" t="s">
-        <v>103</v>
+        <v>1021</v>
       </c>
       <c r="B616" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C616" t="s">
-        <v>22</v>
+        <v>375</v>
       </c>
       <c r="D616" t="s">
         <v>26</v>
@@ -18545,7 +18545,7 @@
         <v>36</v>
       </c>
       <c r="F616" t="s">
-        <v>520</v>
+        <v>486</v>
       </c>
       <c r="G616" t="s">
         <v>1014</v>
@@ -18553,22 +18553,22 @@
     </row>
     <row r="617" hidden="1" spans="1:7">
       <c r="A617" t="s">
-        <v>1021</v>
+        <v>1057</v>
       </c>
       <c r="B617" t="s">
-        <v>1022</v>
+        <v>1058</v>
       </c>
       <c r="C617" t="s">
-        <v>375</v>
+        <v>566</v>
       </c>
       <c r="D617" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E617" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F617" t="s">
-        <v>486</v>
+        <v>1013</v>
       </c>
       <c r="G617" t="s">
         <v>1014</v>
@@ -18576,22 +18576,22 @@
     </row>
     <row r="618" hidden="1" spans="1:7">
       <c r="A618" t="s">
-        <v>1057</v>
+        <v>100</v>
       </c>
       <c r="B618" t="s">
-        <v>1058</v>
+        <v>1015</v>
       </c>
       <c r="C618" t="s">
-        <v>566</v>
+        <v>58</v>
       </c>
       <c r="D618" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E618" t="s">
         <v>47</v>
       </c>
       <c r="F618" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G618" t="s">
         <v>1014</v>
@@ -18599,22 +18599,22 @@
     </row>
     <row r="619" hidden="1" spans="1:7">
       <c r="A619" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="B619" t="s">
-        <v>1015</v>
+        <v>1031</v>
       </c>
       <c r="C619" t="s">
-        <v>58</v>
+        <v>1059</v>
       </c>
       <c r="D619" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E619" t="s">
         <v>47</v>
       </c>
       <c r="F619" t="s">
-        <v>1017</v>
+        <v>1060</v>
       </c>
       <c r="G619" t="s">
         <v>1014</v>
@@ -18622,13 +18622,13 @@
     </row>
     <row r="620" hidden="1" spans="1:7">
       <c r="A620" t="s">
-        <v>78</v>
+        <v>1021</v>
       </c>
       <c r="B620" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
       <c r="C620" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D620" t="s">
         <v>18</v>
@@ -18637,7 +18637,7 @@
         <v>47</v>
       </c>
       <c r="F620" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="G620" t="s">
         <v>1014</v>
@@ -18645,13 +18645,13 @@
     </row>
     <row r="621" hidden="1" spans="1:7">
       <c r="A621" t="s">
-        <v>1021</v>
+        <v>574</v>
       </c>
       <c r="B621" t="s">
-        <v>1022</v>
+        <v>1063</v>
       </c>
       <c r="C621" t="s">
-        <v>1061</v>
+        <v>22</v>
       </c>
       <c r="D621" t="s">
         <v>18</v>
@@ -18660,7 +18660,7 @@
         <v>47</v>
       </c>
       <c r="F621" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="G621" t="s">
         <v>1014</v>
@@ -18668,22 +18668,22 @@
     </row>
     <row r="622" hidden="1" spans="1:7">
       <c r="A622" t="s">
-        <v>574</v>
+        <v>1021</v>
       </c>
       <c r="B622" t="s">
-        <v>1063</v>
+        <v>1022</v>
       </c>
       <c r="C622" t="s">
-        <v>22</v>
+        <v>542</v>
       </c>
       <c r="D622" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E622" t="s">
         <v>47</v>
       </c>
       <c r="F622" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="G622" t="s">
         <v>1014</v>
@@ -18691,13 +18691,13 @@
     </row>
     <row r="623" hidden="1" spans="1:7">
       <c r="A623" t="s">
-        <v>1021</v>
+        <v>78</v>
       </c>
       <c r="B623" t="s">
-        <v>1022</v>
+        <v>1031</v>
       </c>
       <c r="C623" t="s">
-        <v>542</v>
+        <v>1059</v>
       </c>
       <c r="D623" t="s">
         <v>23</v>
@@ -18706,7 +18706,7 @@
         <v>47</v>
       </c>
       <c r="F623" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="G623" t="s">
         <v>1014</v>
@@ -18714,13 +18714,13 @@
     </row>
     <row r="624" hidden="1" spans="1:7">
       <c r="A624" t="s">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="B624" t="s">
-        <v>1031</v>
+        <v>1063</v>
       </c>
       <c r="C624" t="s">
-        <v>1059</v>
+        <v>22</v>
       </c>
       <c r="D624" t="s">
         <v>23</v>
@@ -18729,7 +18729,7 @@
         <v>47</v>
       </c>
       <c r="F624" t="s">
-        <v>1060</v>
+        <v>1017</v>
       </c>
       <c r="G624" t="s">
         <v>1014</v>
@@ -18737,22 +18737,22 @@
     </row>
     <row r="625" hidden="1" spans="1:7">
       <c r="A625" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="B625" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C625" t="s">
-        <v>22</v>
+        <v>1066</v>
       </c>
       <c r="D625" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E625" t="s">
         <v>47</v>
       </c>
       <c r="F625" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G625" t="s">
         <v>1014</v>
@@ -18760,16 +18760,16 @@
     </row>
     <row r="626" hidden="1" spans="1:7">
       <c r="A626" t="s">
-        <v>562</v>
+        <v>66</v>
       </c>
       <c r="B626" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C626" t="s">
-        <v>1066</v>
+        <v>38</v>
       </c>
       <c r="D626" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E626" t="s">
         <v>47</v>
@@ -18783,22 +18783,22 @@
     </row>
     <row r="627" hidden="1" spans="1:7">
       <c r="A627" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="B627" t="s">
-        <v>1067</v>
+        <v>1037</v>
       </c>
       <c r="C627" t="s">
-        <v>38</v>
+        <v>1068</v>
       </c>
       <c r="D627" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E627" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F627" t="s">
-        <v>1013</v>
+        <v>1069</v>
       </c>
       <c r="G627" t="s">
         <v>1014</v>
@@ -18806,13 +18806,13 @@
     </row>
     <row r="628" hidden="1" spans="1:7">
       <c r="A628" t="s">
-        <v>120</v>
+        <v>1052</v>
       </c>
       <c r="B628" t="s">
-        <v>1037</v>
+        <v>1053</v>
       </c>
       <c r="C628" t="s">
-        <v>1068</v>
+        <v>22</v>
       </c>
       <c r="D628" t="s">
         <v>10</v>
@@ -18821,7 +18821,7 @@
         <v>54</v>
       </c>
       <c r="F628" t="s">
-        <v>1069</v>
+        <v>1017</v>
       </c>
       <c r="G628" t="s">
         <v>1014</v>
@@ -18829,22 +18829,22 @@
     </row>
     <row r="629" hidden="1" spans="1:7">
       <c r="A629" t="s">
-        <v>1052</v>
+        <v>120</v>
       </c>
       <c r="B629" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="C629" t="s">
-        <v>22</v>
+        <v>1070</v>
       </c>
       <c r="D629" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E629" t="s">
         <v>54</v>
       </c>
       <c r="F629" t="s">
-        <v>1017</v>
+        <v>1071</v>
       </c>
       <c r="G629" t="s">
         <v>1014</v>
@@ -18858,7 +18858,7 @@
         <v>1037</v>
       </c>
       <c r="C630" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="D630" t="s">
         <v>14</v>
@@ -18867,7 +18867,7 @@
         <v>54</v>
       </c>
       <c r="F630" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G630" t="s">
         <v>1014</v>
@@ -18881,16 +18881,16 @@
         <v>1037</v>
       </c>
       <c r="C631" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D631" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E631" t="s">
         <v>54</v>
       </c>
       <c r="F631" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="G631" t="s">
         <v>1014</v>
@@ -18898,13 +18898,13 @@
     </row>
     <row r="632" hidden="1" spans="1:7">
       <c r="A632" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B632" t="s">
-        <v>1037</v>
+        <v>1015</v>
       </c>
       <c r="C632" t="s">
-        <v>1070</v>
+        <v>1016</v>
       </c>
       <c r="D632" t="s">
         <v>18</v>
@@ -18913,7 +18913,7 @@
         <v>54</v>
       </c>
       <c r="F632" t="s">
-        <v>1072</v>
+        <v>416</v>
       </c>
       <c r="G632" t="s">
         <v>1014</v>
@@ -18921,13 +18921,13 @@
     </row>
     <row r="633" hidden="1" spans="1:7">
       <c r="A633" t="s">
-        <v>100</v>
+        <v>574</v>
       </c>
       <c r="B633" t="s">
-        <v>1015</v>
+        <v>1063</v>
       </c>
       <c r="C633" t="s">
-        <v>1016</v>
+        <v>22</v>
       </c>
       <c r="D633" t="s">
         <v>18</v>
@@ -18936,7 +18936,7 @@
         <v>54</v>
       </c>
       <c r="F633" t="s">
-        <v>416</v>
+        <v>592</v>
       </c>
       <c r="G633" t="s">
         <v>1014</v>
@@ -18953,13 +18953,13 @@
         <v>22</v>
       </c>
       <c r="D634" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E634" t="s">
         <v>54</v>
       </c>
       <c r="F634" t="s">
-        <v>592</v>
+        <v>1054</v>
       </c>
       <c r="G634" t="s">
         <v>1014</v>
@@ -18967,22 +18967,22 @@
     </row>
     <row r="635" hidden="1" spans="1:7">
       <c r="A635" t="s">
-        <v>574</v>
+        <v>100</v>
       </c>
       <c r="B635" t="s">
-        <v>1063</v>
+        <v>1015</v>
       </c>
       <c r="C635" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D635" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E635" t="s">
         <v>54</v>
       </c>
       <c r="F635" t="s">
-        <v>1054</v>
+        <v>592</v>
       </c>
       <c r="G635" t="s">
         <v>1014</v>
@@ -18990,22 +18990,22 @@
     </row>
     <row r="636" hidden="1" spans="1:7">
       <c r="A636" t="s">
-        <v>100</v>
+        <v>1073</v>
       </c>
       <c r="B636" t="s">
-        <v>1015</v>
+        <v>1074</v>
       </c>
       <c r="C636" t="s">
-        <v>58</v>
+        <v>587</v>
       </c>
       <c r="D636" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E636" t="s">
         <v>54</v>
       </c>
       <c r="F636" t="s">
-        <v>592</v>
+        <v>1048</v>
       </c>
       <c r="G636" t="s">
         <v>1014</v>
@@ -19013,45 +19013,45 @@
     </row>
     <row r="637" hidden="1" spans="1:7">
       <c r="A637" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B637" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C637" t="s">
-        <v>587</v>
+        <v>814</v>
       </c>
       <c r="D637" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E637" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F637" t="s">
-        <v>1048</v>
+        <v>175</v>
       </c>
       <c r="G637" t="s">
-        <v>1014</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="638" hidden="1" spans="1:7">
       <c r="A638" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="B638" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="C638" t="s">
-        <v>814</v>
+        <v>181</v>
       </c>
       <c r="D638" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E638" t="s">
         <v>11</v>
       </c>
       <c r="F638" t="s">
-        <v>175</v>
+        <v>274</v>
       </c>
       <c r="G638" t="s">
         <v>1077</v>
@@ -19059,16 +19059,16 @@
     </row>
     <row r="639" hidden="1" spans="1:7">
       <c r="A639" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B639" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C639" t="s">
         <v>181</v>
       </c>
       <c r="D639" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E639" t="s">
         <v>11</v>
@@ -19082,22 +19082,22 @@
     </row>
     <row r="640" hidden="1" spans="1:7">
       <c r="A640" t="s">
-        <v>1080</v>
+        <v>620</v>
       </c>
       <c r="B640" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C640" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="D640" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E640" t="s">
         <v>11</v>
       </c>
       <c r="F640" t="s">
-        <v>274</v>
+        <v>175</v>
       </c>
       <c r="G640" t="s">
         <v>1077</v>
@@ -19105,16 +19105,16 @@
     </row>
     <row r="641" hidden="1" spans="1:7">
       <c r="A641" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
       <c r="B641" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C641" t="s">
         <v>148</v>
       </c>
       <c r="D641" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E641" t="s">
         <v>11</v>
@@ -19128,22 +19128,22 @@
     </row>
     <row r="642" hidden="1" spans="1:7">
       <c r="A642" t="s">
-        <v>589</v>
+        <v>20</v>
       </c>
       <c r="B642" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C642" t="s">
-        <v>148</v>
+        <v>22</v>
       </c>
       <c r="D642" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E642" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F642" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="G642" t="s">
         <v>1077</v>
@@ -19160,7 +19160,7 @@
         <v>22</v>
       </c>
       <c r="D643" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E643" t="s">
         <v>27</v>
@@ -19183,7 +19183,7 @@
         <v>22</v>
       </c>
       <c r="D644" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E644" t="s">
         <v>27</v>
@@ -19197,22 +19197,22 @@
     </row>
     <row r="645" hidden="1" spans="1:7">
       <c r="A645" t="s">
-        <v>20</v>
+        <v>1085</v>
       </c>
       <c r="B645" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C645" t="s">
-        <v>22</v>
+        <v>625</v>
       </c>
       <c r="D645" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E645" t="s">
         <v>27</v>
       </c>
       <c r="F645" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="G645" t="s">
         <v>1077</v>
@@ -19220,22 +19220,22 @@
     </row>
     <row r="646" hidden="1" spans="1:7">
       <c r="A646" t="s">
-        <v>1085</v>
+        <v>20</v>
       </c>
       <c r="B646" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C646" t="s">
-        <v>625</v>
+        <v>22</v>
       </c>
       <c r="D646" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E646" t="s">
         <v>27</v>
       </c>
       <c r="F646" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="G646" t="s">
         <v>1077</v>
@@ -19243,22 +19243,22 @@
     </row>
     <row r="647" hidden="1" spans="1:7">
       <c r="A647" t="s">
-        <v>20</v>
+        <v>1087</v>
       </c>
       <c r="B647" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="C647" t="s">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="D647" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E647" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F647" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="G647" t="s">
         <v>1077</v>
@@ -19266,22 +19266,22 @@
     </row>
     <row r="648" hidden="1" spans="1:7">
       <c r="A648" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B648" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C648" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="D648" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E648" t="s">
         <v>36</v>
       </c>
       <c r="F648" t="s">
-        <v>175</v>
+        <v>1091</v>
       </c>
       <c r="G648" t="s">
         <v>1077</v>
@@ -19298,7 +19298,7 @@
         <v>148</v>
       </c>
       <c r="D649" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E649" t="s">
         <v>36</v>
@@ -19312,22 +19312,22 @@
     </row>
     <row r="650" hidden="1" spans="1:7">
       <c r="A650" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B650" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="C650" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="D650" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E650" t="s">
         <v>36</v>
       </c>
       <c r="F650" t="s">
-        <v>1091</v>
+        <v>175</v>
       </c>
       <c r="G650" t="s">
         <v>1077</v>
@@ -19335,16 +19335,16 @@
     </row>
     <row r="651" hidden="1" spans="1:7">
       <c r="A651" t="s">
-        <v>1092</v>
+        <v>170</v>
       </c>
       <c r="B651" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C651" t="s">
-        <v>227</v>
+        <v>158</v>
       </c>
       <c r="D651" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E651" t="s">
         <v>36</v>
@@ -19358,19 +19358,19 @@
     </row>
     <row r="652" hidden="1" spans="1:7">
       <c r="A652" t="s">
-        <v>170</v>
+        <v>1095</v>
       </c>
       <c r="B652" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C652" t="s">
-        <v>158</v>
+        <v>353</v>
       </c>
       <c r="D652" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E652" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F652" t="s">
         <v>175</v>
@@ -19381,22 +19381,22 @@
     </row>
     <row r="653" hidden="1" spans="1:7">
       <c r="A653" t="s">
-        <v>1095</v>
+        <v>614</v>
       </c>
       <c r="B653" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C653" t="s">
-        <v>353</v>
+        <v>560</v>
       </c>
       <c r="D653" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E653" t="s">
         <v>47</v>
       </c>
       <c r="F653" t="s">
-        <v>175</v>
+        <v>1098</v>
       </c>
       <c r="G653" t="s">
         <v>1077</v>
@@ -19404,13 +19404,13 @@
     </row>
     <row r="654" hidden="1" spans="1:7">
       <c r="A654" t="s">
-        <v>614</v>
+        <v>1099</v>
       </c>
       <c r="B654" t="s">
         <v>1097</v>
       </c>
       <c r="C654" t="s">
-        <v>560</v>
+        <v>227</v>
       </c>
       <c r="D654" t="s">
         <v>18</v>
@@ -19419,7 +19419,7 @@
         <v>47</v>
       </c>
       <c r="F654" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="G654" t="s">
         <v>1077</v>
@@ -19427,22 +19427,22 @@
     </row>
     <row r="655" hidden="1" spans="1:7">
       <c r="A655" t="s">
-        <v>1099</v>
+        <v>614</v>
       </c>
       <c r="B655" t="s">
         <v>1097</v>
       </c>
       <c r="C655" t="s">
-        <v>227</v>
+        <v>560</v>
       </c>
       <c r="D655" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E655" t="s">
         <v>47</v>
       </c>
       <c r="F655" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G655" t="s">
         <v>1077</v>
@@ -19450,13 +19450,13 @@
     </row>
     <row r="656" hidden="1" spans="1:7">
       <c r="A656" t="s">
-        <v>614</v>
+        <v>1099</v>
       </c>
       <c r="B656" t="s">
         <v>1097</v>
       </c>
       <c r="C656" t="s">
-        <v>560</v>
+        <v>227</v>
       </c>
       <c r="D656" t="s">
         <v>23</v>
@@ -19465,7 +19465,7 @@
         <v>47</v>
       </c>
       <c r="F656" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="G656" t="s">
         <v>1077</v>
@@ -19473,22 +19473,22 @@
     </row>
     <row r="657" hidden="1" spans="1:7">
       <c r="A657" t="s">
-        <v>1099</v>
+        <v>156</v>
       </c>
       <c r="B657" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="C657" t="s">
-        <v>227</v>
+        <v>158</v>
       </c>
       <c r="D657" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E657" t="s">
         <v>47</v>
       </c>
       <c r="F657" t="s">
-        <v>1100</v>
+        <v>175</v>
       </c>
       <c r="G657" t="s">
         <v>1077</v>
@@ -19496,16 +19496,16 @@
     </row>
     <row r="658" hidden="1" spans="1:7">
       <c r="A658" t="s">
-        <v>156</v>
+        <v>1102</v>
       </c>
       <c r="B658" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C658" t="s">
-        <v>158</v>
+        <v>353</v>
       </c>
       <c r="D658" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E658" t="s">
         <v>47</v>
@@ -19519,22 +19519,22 @@
     </row>
     <row r="659" hidden="1" spans="1:7">
       <c r="A659" t="s">
-        <v>1102</v>
+        <v>162</v>
       </c>
       <c r="B659" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C659" t="s">
-        <v>353</v>
+        <v>164</v>
       </c>
       <c r="D659" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E659" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F659" t="s">
-        <v>175</v>
+        <v>1105</v>
       </c>
       <c r="G659" t="s">
         <v>1077</v>
@@ -19542,13 +19542,13 @@
     </row>
     <row r="660" hidden="1" spans="1:7">
       <c r="A660" t="s">
-        <v>162</v>
+        <v>603</v>
       </c>
       <c r="B660" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C660" t="s">
-        <v>164</v>
+        <v>353</v>
       </c>
       <c r="D660" t="s">
         <v>10</v>
@@ -19557,7 +19557,7 @@
         <v>54</v>
       </c>
       <c r="F660" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="G660" t="s">
         <v>1077</v>
@@ -19565,22 +19565,22 @@
     </row>
     <row r="661" hidden="1" spans="1:7">
       <c r="A661" t="s">
-        <v>603</v>
+        <v>20</v>
       </c>
       <c r="B661" t="s">
-        <v>1106</v>
+        <v>1084</v>
       </c>
       <c r="C661" t="s">
-        <v>353</v>
+        <v>22</v>
       </c>
       <c r="D661" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E661" t="s">
         <v>54</v>
       </c>
       <c r="F661" t="s">
-        <v>1107</v>
+        <v>24</v>
       </c>
       <c r="G661" t="s">
         <v>1077</v>
@@ -19597,7 +19597,7 @@
         <v>22</v>
       </c>
       <c r="D662" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E662" t="s">
         <v>54</v>
@@ -19611,22 +19611,22 @@
     </row>
     <row r="663" hidden="1" spans="1:7">
       <c r="A663" t="s">
-        <v>20</v>
+        <v>1102</v>
       </c>
       <c r="B663" t="s">
-        <v>1084</v>
+        <v>1103</v>
       </c>
       <c r="C663" t="s">
-        <v>22</v>
+        <v>353</v>
       </c>
       <c r="D663" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E663" t="s">
         <v>54</v>
       </c>
       <c r="F663" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="G663" t="s">
         <v>1077</v>
@@ -19634,22 +19634,22 @@
     </row>
     <row r="664" hidden="1" spans="1:7">
       <c r="A664" t="s">
-        <v>1102</v>
+        <v>162</v>
       </c>
       <c r="B664" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C664" t="s">
-        <v>353</v>
+        <v>164</v>
       </c>
       <c r="D664" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E664" t="s">
         <v>54</v>
       </c>
       <c r="F664" t="s">
-        <v>175</v>
+        <v>1108</v>
       </c>
       <c r="G664" t="s">
         <v>1077</v>
@@ -19657,13 +19657,13 @@
     </row>
     <row r="665" hidden="1" spans="1:7">
       <c r="A665" t="s">
-        <v>162</v>
+        <v>603</v>
       </c>
       <c r="B665" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C665" t="s">
-        <v>164</v>
+        <v>353</v>
       </c>
       <c r="D665" t="s">
         <v>26</v>
@@ -19672,7 +19672,7 @@
         <v>54</v>
       </c>
       <c r="F665" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="G665" t="s">
         <v>1077</v>
@@ -19680,56 +19680,56 @@
     </row>
     <row r="666" hidden="1" spans="1:7">
       <c r="A666" t="s">
-        <v>603</v>
+        <v>113</v>
       </c>
       <c r="B666" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C666" t="s">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="D666" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E666" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F666" t="s">
-        <v>1109</v>
+        <v>543</v>
       </c>
       <c r="G666" t="s">
-        <v>1077</v>
+        <v>531</v>
       </c>
     </row>
     <row r="667" hidden="1" spans="1:7">
       <c r="A667" t="s">
-        <v>113</v>
+        <v>800</v>
       </c>
       <c r="B667" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C667" t="s">
-        <v>318</v>
+        <v>769</v>
       </c>
       <c r="D667" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E667" t="s">
         <v>36</v>
       </c>
       <c r="F667" t="s">
-        <v>543</v>
+        <v>773</v>
       </c>
       <c r="G667" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="668" hidden="1" spans="1:7">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="668" spans="1:7">
       <c r="A668" t="s">
         <v>800</v>
       </c>
       <c r="B668" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C668" t="s">
         <v>769</v>
@@ -19741,163 +19741,124 @@
         <v>36</v>
       </c>
       <c r="F668" t="s">
-        <v>773</v>
+        <v>686</v>
       </c>
       <c r="G668" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="669" hidden="1" spans="1:7">
       <c r="A669" t="s">
-        <v>800</v>
+        <v>1113</v>
       </c>
       <c r="B669" t="s">
-        <v>1112</v>
+        <v>756</v>
       </c>
       <c r="C669" t="s">
-        <v>769</v>
+        <v>9</v>
       </c>
       <c r="D669" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E669" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F669" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="G669" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
     </row>
     <row r="670" hidden="1" spans="1:7">
       <c r="A670" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B670" t="s">
-        <v>756</v>
+        <v>1115</v>
       </c>
       <c r="C670" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D670" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E670" t="s">
         <v>54</v>
       </c>
       <c r="F670" t="s">
-        <v>682</v>
+        <v>258</v>
       </c>
       <c r="G670" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="671" hidden="1" spans="1:7">
-      <c r="A671" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B671" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C671" t="s">
-        <v>17</v>
-      </c>
-      <c r="D671" t="s">
-        <v>25</v>
-      </c>
-      <c r="E671" t="s">
-        <v>54</v>
+      <c r="A671" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="D671" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E671" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="F671" t="s">
-        <v>258</v>
+        <v>704</v>
       </c>
       <c r="G671" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
     </row>
     <row r="672" hidden="1" spans="1:7">
-      <c r="A672" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="B672" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C672" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="D672" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E672" s="3" t="s">
-        <v>47</v>
+      <c r="A672" t="s">
+        <v>780</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C672" t="s">
+        <v>227</v>
+      </c>
+      <c r="D672" t="s">
+        <v>10</v>
+      </c>
+      <c r="E672" t="s">
+        <v>11</v>
       </c>
       <c r="F672" t="s">
-        <v>704</v>
+        <v>19</v>
       </c>
       <c r="G672" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="673" hidden="1" spans="1:7">
-      <c r="A673" t="s">
-        <v>780</v>
-      </c>
-      <c r="B673" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C673" t="s">
-        <v>227</v>
-      </c>
-      <c r="D673" t="s">
-        <v>10</v>
-      </c>
-      <c r="E673" t="s">
-        <v>11</v>
-      </c>
-      <c r="F673" t="s">
-        <v>19</v>
-      </c>
-      <c r="G673" t="s">
         <v>674</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G673" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G672" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="TP-Machines électriques approfondies -G1"/>
-        <filter val="TP-Machines électriques approfondies-G1"/>
-        <filter val="TP-μ-processeurs et μ-contrôleurs TP G1/G2"/>
-        <filter val="TP-Programmation avancée en Python TP G1/G2"/>
-        <filter val="TP-Machines électriques approfondies -G2"/>
-        <filter val="TP-Machines électriques approfondies-G2"/>
-        <filter val="TP-μ-processeurs et μ-contrôleurs-G1"/>
-        <filter val="TP-Réseaux de transport et de distribution d'énergie électrique-G1"/>
-        <filter val="TP-Programmation avancée en Python-G1"/>
-        <filter val="TP-μ-processeurs et μ-contrôleurs-G2"/>
-        <filter val="TP-Réseaux de transport et de distribution d'énergie électrique-G2"/>
-        <filter val="TP-Programmation avancée en Python-G2"/>
-        <filter val="TP-Machines électriques approfondies TP G1/G2"/>
-        <filter val="TP-Méthodes numériques appliquées-G1"/>
-        <filter val="TP-Exploitation des Réseaux électriques-G1"/>
-        <filter val="TP-Méthodes numériques appliquées-G2"/>
-        <filter val="TP-Méthodes numériques appliquées et optimisation TP G1/G2"/>
-        <filter val="TP-Électronique de puissance avancée TP G1/G2"/>
-        <filter val="TP-Exploitation des Réseaux électriques-G2"/>
-        <filter val="TP-Méthodes numériques appliquées et optimisation-G1"/>
-        <filter val="TP-Électronique de puissance avancée-G1"/>
-        <filter val="TP-Méthodes numériques appliquées et optimisation-G2"/>
-        <filter val="TP-Réseaux de transport et de distribution d'énergie élet. TP G1/G2"/>
-        <filter val="TP-Électronique de puissance avancée-G2"/>
+        <filter val="Cours-μ-processeurs et μ-contrôleurs"/>
+        <filter val="Cours-Machines électriques approfondies"/>
+        <filter val="Cours-Énergies renouvelables"/>
+        <filter val="Cours-Réseaux de transport et de distribution d'énergie électrique"/>
+        <filter val="Cours-Électronique de puissance avancée"/>
+        <filter val="Cours-Anglais technique et terminologie"/>
+        <filter val="Cours-Méthodes numériques appliquées et optimisation"/>
+        <filter val="Cours-Programmation avancée en Python"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="M1ER"/>
+        <filter val="M1RE"/>
       </filters>
     </filterColumn>
-    <sortState ref="A2:G673">
+    <sortState ref="A2:G672">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4704" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4704" uniqueCount="1113">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2663,7 +2663,7 @@
     <t>TP-ADS-M2ER</t>
   </si>
   <si>
-    <t>Cours-Maintenance et fiabilité des systèmes à énergies renouvelables Cours</t>
+    <t>Cours-Maintenance et fiabilité des systèmes à énergies renouvelables</t>
   </si>
   <si>
     <t>Cours-MFS-M2ER</t>
@@ -3360,9 +3360,6 @@
   </si>
   <si>
     <t>TP-Méthodes numériques appliquées-G1</t>
-  </si>
-  <si>
-    <t>Cours-μ-processeurs et μ-contrôleurs Cours</t>
   </si>
   <si>
     <t>Cours-μPμC-M1ER</t>
@@ -4673,7 +4670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" hidden="1" spans="1:7">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -4696,7 +4693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" hidden="1" spans="1:7">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -4719,7 +4716,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" hidden="1" spans="1:7">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -4742,7 +4739,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" hidden="1" spans="1:7">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -4788,7 +4785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" hidden="1" spans="1:7">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -4811,7 +4808,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" hidden="1" spans="1:7">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -4949,7 +4946,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" hidden="1" spans="1:7">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -4995,7 +4992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" hidden="1" spans="1:7">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -5041,7 +5038,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" hidden="1" spans="1:7">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -5087,7 +5084,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" hidden="1" spans="1:7">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -5110,7 +5107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" hidden="1" spans="1:7">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -5225,7 +5222,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" hidden="1" spans="1:7">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -5271,7 +5268,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" hidden="1" spans="1:7">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -5294,7 +5291,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" hidden="1" spans="1:7">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -5317,7 +5314,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" hidden="1" spans="1:7">
       <c r="A42" t="s">
         <v>79</v>
       </c>
@@ -5524,7 +5521,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" hidden="1" spans="1:7">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -5547,7 +5544,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" hidden="1" spans="1:7">
       <c r="A52" t="s">
         <v>79</v>
       </c>
@@ -5662,7 +5659,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" hidden="1" spans="1:7">
       <c r="A57" t="s">
         <v>79</v>
       </c>
@@ -5708,7 +5705,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" hidden="1" spans="1:7">
       <c r="A59" t="s">
         <v>79</v>
       </c>
@@ -5731,7 +5728,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" hidden="1" spans="1:7">
       <c r="A60" t="s">
         <v>79</v>
       </c>
@@ -5754,7 +5751,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" hidden="1" spans="1:7">
       <c r="A61" t="s">
         <v>79</v>
       </c>
@@ -6076,7 +6073,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" hidden="1" spans="1:7">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -6260,7 +6257,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" hidden="1" spans="1:7">
       <c r="A83" t="s">
         <v>79</v>
       </c>
@@ -6283,7 +6280,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" hidden="1" spans="1:7">
       <c r="A84" t="s">
         <v>79</v>
       </c>
@@ -6329,7 +6326,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" hidden="1" spans="1:7">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -6490,7 +6487,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" hidden="1" spans="1:7">
       <c r="A93" t="s">
         <v>79</v>
       </c>
@@ -6513,7 +6510,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" hidden="1" spans="1:7">
       <c r="A94" t="s">
         <v>79</v>
       </c>
@@ -6766,7 +6763,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" hidden="1" spans="1:7">
       <c r="A105" t="s">
         <v>205</v>
       </c>
@@ -6858,7 +6855,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" hidden="1" spans="1:7">
       <c r="A109" t="s">
         <v>205</v>
       </c>
@@ -6927,7 +6924,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" hidden="1" spans="1:7">
       <c r="A112" t="s">
         <v>205</v>
       </c>
@@ -6950,7 +6947,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" hidden="1" spans="1:7">
       <c r="A113" t="s">
         <v>205</v>
       </c>
@@ -7065,7 +7062,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" hidden="1" spans="1:7">
       <c r="A118" t="s">
         <v>205</v>
       </c>
@@ -7111,7 +7108,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" hidden="1" spans="1:7">
       <c r="A120" t="s">
         <v>205</v>
       </c>
@@ -7157,7 +7154,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" hidden="1" spans="1:7">
       <c r="A122" t="s">
         <v>205</v>
       </c>
@@ -7226,7 +7223,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" hidden="1" spans="1:7">
       <c r="A125" t="s">
         <v>205</v>
       </c>
@@ -7272,7 +7269,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" hidden="1" spans="1:7">
       <c r="A127" t="s">
         <v>205</v>
       </c>
@@ -7318,7 +7315,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" hidden="1" spans="1:7">
       <c r="A129" t="s">
         <v>205</v>
       </c>
@@ -7387,7 +7384,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" hidden="1" spans="1:7">
       <c r="A132" t="s">
         <v>205</v>
       </c>
@@ -7548,7 +7545,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" hidden="1" spans="1:7">
       <c r="A139" t="s">
         <v>205</v>
       </c>
@@ -7594,7 +7591,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" hidden="1" spans="1:7">
       <c r="A141" t="s">
         <v>205</v>
       </c>
@@ -7640,7 +7637,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" hidden="1" spans="1:7">
       <c r="A143" t="s">
         <v>205</v>
       </c>
@@ -7870,7 +7867,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" hidden="1" spans="1:7">
       <c r="A153" t="s">
         <v>205</v>
       </c>
@@ -7893,7 +7890,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" hidden="1" spans="1:7">
       <c r="A154" t="s">
         <v>205</v>
       </c>
@@ -7939,7 +7936,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" hidden="1" spans="1:7">
       <c r="A156" t="s">
         <v>314</v>
       </c>
@@ -7985,7 +7982,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" hidden="1" spans="1:7">
       <c r="A158" t="s">
         <v>314</v>
       </c>
@@ -8307,7 +8304,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" hidden="1" spans="1:7">
       <c r="A172" t="s">
         <v>350</v>
       </c>
@@ -8353,7 +8350,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" hidden="1" spans="1:7">
       <c r="A174" t="s">
         <v>355</v>
       </c>
@@ -8422,7 +8419,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" hidden="1" spans="1:7">
       <c r="A177" t="s">
         <v>364</v>
       </c>
@@ -8491,7 +8488,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" hidden="1" spans="1:7">
       <c r="A180" t="s">
         <v>373</v>
       </c>
@@ -8537,7 +8534,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" hidden="1" spans="1:7">
       <c r="A182" t="s">
         <v>377</v>
       </c>
@@ -8652,7 +8649,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" hidden="1" spans="1:7">
       <c r="A187" t="s">
         <v>392</v>
       </c>
@@ -8698,7 +8695,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" hidden="1" spans="1:7">
       <c r="A189" t="s">
         <v>399</v>
       </c>
@@ -8721,7 +8718,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" hidden="1" spans="1:7">
       <c r="A190" t="s">
         <v>401</v>
       </c>
@@ -8744,7 +8741,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" hidden="1" spans="1:7">
       <c r="A191" t="s">
         <v>405</v>
       </c>
@@ -8790,7 +8787,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" hidden="1" spans="1:7">
       <c r="A193" t="s">
         <v>412</v>
       </c>
@@ -8813,7 +8810,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" hidden="1" spans="1:7">
       <c r="A194" t="s">
         <v>414</v>
       </c>
@@ -8859,7 +8856,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" hidden="1" spans="1:7">
       <c r="A196" t="s">
         <v>421</v>
       </c>
@@ -8882,7 +8879,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" hidden="1" spans="1:7">
       <c r="A197" t="s">
         <v>425</v>
       </c>
@@ -8905,7 +8902,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" hidden="1" spans="1:7">
       <c r="A198" t="s">
         <v>427</v>
       </c>
@@ -8974,7 +8971,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" hidden="1" spans="1:7">
       <c r="A201" t="s">
         <v>432</v>
       </c>
@@ -8997,7 +8994,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" hidden="1" spans="1:7">
       <c r="A202" t="s">
         <v>434</v>
       </c>
@@ -9020,7 +9017,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" hidden="1" spans="1:7">
       <c r="A203" t="s">
         <v>434</v>
       </c>
@@ -9089,7 +9086,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" hidden="1" spans="1:7">
       <c r="A206" t="s">
         <v>443</v>
       </c>
@@ -9112,7 +9109,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" hidden="1" spans="1:7">
       <c r="A207" t="s">
         <v>445</v>
       </c>
@@ -9135,7 +9132,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" hidden="1" spans="1:7">
       <c r="A208" t="s">
         <v>445</v>
       </c>
@@ -9158,7 +9155,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" hidden="1" spans="1:7">
       <c r="A209" t="s">
         <v>445</v>
       </c>
@@ -9181,7 +9178,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" hidden="1" spans="1:7">
       <c r="A210" t="s">
         <v>445</v>
       </c>
@@ -9204,7 +9201,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" hidden="1" spans="1:7">
       <c r="A211" t="s">
         <v>445</v>
       </c>
@@ -9227,7 +9224,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" hidden="1" spans="1:7">
       <c r="A212" t="s">
         <v>445</v>
       </c>
@@ -9273,7 +9270,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" hidden="1" spans="1:7">
       <c r="A214" t="s">
         <v>457</v>
       </c>
@@ -9319,7 +9316,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" hidden="1" spans="1:7">
       <c r="A216" t="s">
         <v>457</v>
       </c>
@@ -9342,7 +9339,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" hidden="1" spans="1:7">
       <c r="A217" t="s">
         <v>457</v>
       </c>
@@ -9365,7 +9362,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" hidden="1" spans="1:7">
       <c r="A218" t="s">
         <v>457</v>
       </c>
@@ -9411,7 +9408,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" hidden="1" spans="1:7">
       <c r="A220" t="s">
         <v>457</v>
       </c>
@@ -9526,7 +9523,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" hidden="1" spans="1:7">
       <c r="A225" t="s">
         <v>457</v>
       </c>
@@ -9595,7 +9592,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" hidden="1" spans="1:7">
       <c r="A228" t="s">
         <v>487</v>
       </c>
@@ -9641,7 +9638,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" hidden="1" spans="1:7">
       <c r="A230" t="s">
         <v>491</v>
       </c>
@@ -9687,7 +9684,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" hidden="1" spans="1:7">
       <c r="A232" t="s">
         <v>491</v>
       </c>
@@ -9710,7 +9707,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" hidden="1" spans="1:7">
       <c r="A233" t="s">
         <v>491</v>
       </c>
@@ -9733,7 +9730,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" hidden="1" spans="1:7">
       <c r="A234" t="s">
         <v>491</v>
       </c>
@@ -9802,7 +9799,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" hidden="1" spans="1:7">
       <c r="A237" t="s">
         <v>501</v>
       </c>
@@ -9871,7 +9868,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" hidden="1" spans="1:7">
       <c r="A240" t="s">
         <v>501</v>
       </c>
@@ -9940,7 +9937,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" hidden="1" spans="1:7">
       <c r="A243" t="s">
         <v>501</v>
       </c>
@@ -10009,7 +10006,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" hidden="1" spans="1:7">
       <c r="A246" t="s">
         <v>501</v>
       </c>
@@ -10032,7 +10029,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" hidden="1" spans="1:7">
       <c r="A247" t="s">
         <v>518</v>
       </c>
@@ -10055,7 +10052,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" hidden="1" spans="1:7">
       <c r="A248" t="s">
         <v>518</v>
       </c>
@@ -10078,7 +10075,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" hidden="1" spans="1:7">
       <c r="A249" t="s">
         <v>518</v>
       </c>
@@ -10124,7 +10121,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" hidden="1" spans="1:7">
       <c r="A251" t="s">
         <v>518</v>
       </c>
@@ -10147,7 +10144,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" hidden="1" spans="1:7">
       <c r="A252" t="s">
         <v>518</v>
       </c>
@@ -10193,7 +10190,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" hidden="1" spans="1:7">
       <c r="A254" t="s">
         <v>518</v>
       </c>
@@ -10216,7 +10213,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" hidden="1" spans="1:7">
       <c r="A255" t="s">
         <v>518</v>
       </c>
@@ -10239,7 +10236,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" hidden="1" spans="1:7">
       <c r="A256" t="s">
         <v>518</v>
       </c>
@@ -10377,7 +10374,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" hidden="1" spans="1:7">
       <c r="A262" t="s">
         <v>518</v>
       </c>
@@ -10400,7 +10397,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" hidden="1" spans="1:7">
       <c r="A263" t="s">
         <v>518</v>
       </c>
@@ -10423,7 +10420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" hidden="1" spans="1:7">
       <c r="A264" t="s">
         <v>518</v>
       </c>
@@ -10446,7 +10443,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" hidden="1" spans="1:7">
       <c r="A265" t="s">
         <v>518</v>
       </c>
@@ -10469,7 +10466,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" hidden="1" spans="1:7">
       <c r="A266" t="s">
         <v>518</v>
       </c>
@@ -10492,7 +10489,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" hidden="1" spans="1:7">
       <c r="A267" t="s">
         <v>518</v>
       </c>
@@ -10561,7 +10558,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" hidden="1" spans="1:7">
       <c r="A270" t="s">
         <v>518</v>
       </c>
@@ -10584,7 +10581,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" hidden="1" spans="1:7">
       <c r="A271" t="s">
         <v>518</v>
       </c>
@@ -10607,7 +10604,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" hidden="1" spans="1:7">
       <c r="A272" t="s">
         <v>536</v>
       </c>
@@ -10630,7 +10627,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" hidden="1" spans="1:7">
       <c r="A273" t="s">
         <v>536</v>
       </c>
@@ -10722,7 +10719,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" hidden="1" spans="1:7">
       <c r="A277" t="s">
         <v>536</v>
       </c>
@@ -10745,7 +10742,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" hidden="1" spans="1:7">
       <c r="A278" t="s">
         <v>536</v>
       </c>
@@ -10768,7 +10765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" hidden="1" spans="1:7">
       <c r="A279" t="s">
         <v>547</v>
       </c>
@@ -10791,7 +10788,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" hidden="1" spans="1:7">
       <c r="A280" t="s">
         <v>549</v>
       </c>
@@ -10814,7 +10811,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" hidden="1" spans="1:7">
       <c r="A281" t="s">
         <v>549</v>
       </c>
@@ -10837,7 +10834,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" hidden="1" spans="1:7">
       <c r="A282" t="s">
         <v>553</v>
       </c>
@@ -10860,7 +10857,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" hidden="1" spans="1:7">
       <c r="A283" t="s">
         <v>553</v>
       </c>
@@ -11251,7 +11248,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" hidden="1" spans="1:7">
       <c r="A300" t="s">
         <v>593</v>
       </c>
@@ -11274,7 +11271,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" hidden="1" spans="1:7">
       <c r="A301" t="s">
         <v>595</v>
       </c>
@@ -11297,7 +11294,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" hidden="1" spans="1:7">
       <c r="A302" t="s">
         <v>595</v>
       </c>
@@ -11320,7 +11317,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" hidden="1" spans="1:7">
       <c r="A303" t="s">
         <v>598</v>
       </c>
@@ -11389,7 +11386,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" hidden="1" spans="1:7">
       <c r="A306" t="s">
         <v>602</v>
       </c>
@@ -11412,7 +11409,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" hidden="1" spans="1:7">
       <c r="A307" t="s">
         <v>604</v>
       </c>
@@ -11435,7 +11432,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" hidden="1" spans="1:7">
       <c r="A308" t="s">
         <v>604</v>
       </c>
@@ -11481,7 +11478,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" hidden="1" spans="1:7">
       <c r="A310" t="s">
         <v>608</v>
       </c>
@@ -11504,7 +11501,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" hidden="1" spans="1:7">
       <c r="A311" t="s">
         <v>608</v>
       </c>
@@ -11527,7 +11524,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" hidden="1" spans="1:7">
       <c r="A312" t="s">
         <v>608</v>
       </c>
@@ -11550,7 +11547,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" hidden="1" spans="1:7">
       <c r="A313" t="s">
         <v>608</v>
       </c>
@@ -11964,7 +11961,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" hidden="1" spans="1:7">
       <c r="A331" t="s">
         <v>608</v>
       </c>
@@ -11987,7 +11984,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" hidden="1" spans="1:7">
       <c r="A332" t="s">
         <v>608</v>
       </c>
@@ -12010,7 +12007,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" hidden="1" spans="1:7">
       <c r="A333" t="s">
         <v>641</v>
       </c>
@@ -12056,7 +12053,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" hidden="1" spans="1:7">
       <c r="A335" t="s">
         <v>646</v>
       </c>
@@ -12125,7 +12122,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" hidden="1" spans="1:7">
       <c r="A338" t="s">
         <v>646</v>
       </c>
@@ -12148,7 +12145,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" hidden="1" spans="1:7">
       <c r="A339" t="s">
         <v>651</v>
       </c>
@@ -12171,7 +12168,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" hidden="1" spans="1:7">
       <c r="A340" t="s">
         <v>653</v>
       </c>
@@ -12378,7 +12375,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" hidden="1" spans="1:7">
       <c r="A349" t="s">
         <v>653</v>
       </c>
@@ -12562,7 +12559,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" hidden="1" spans="1:7">
       <c r="A357" t="s">
         <v>653</v>
       </c>
@@ -12585,7 +12582,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" hidden="1" spans="1:7">
       <c r="A358" t="s">
         <v>653</v>
       </c>
@@ -12608,7 +12605,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" hidden="1" spans="1:7">
       <c r="A359" t="s">
         <v>676</v>
       </c>
@@ -12654,7 +12651,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" hidden="1" spans="1:7">
       <c r="A361" t="s">
         <v>680</v>
       </c>
@@ -12677,7 +12674,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" hidden="1" spans="1:7">
       <c r="A362" t="s">
         <v>680</v>
       </c>
@@ -12723,7 +12720,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:7">
+    <row r="364" spans="1:7">
       <c r="A364" t="s">
         <v>678</v>
       </c>
@@ -12907,7 +12904,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" hidden="1" spans="1:7">
       <c r="A372" t="s">
         <v>680</v>
       </c>
@@ -12930,7 +12927,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="373" hidden="1" spans="1:7">
+    <row r="373" spans="1:7">
       <c r="A373" t="s">
         <v>293</v>
       </c>
@@ -13206,7 +13203,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" hidden="1" spans="1:7">
       <c r="A385" t="s">
         <v>680</v>
       </c>
@@ -13298,7 +13295,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" hidden="1" spans="1:7">
       <c r="A389" t="s">
         <v>680</v>
       </c>
@@ -13321,7 +13318,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:7">
+    <row r="390" spans="1:7">
       <c r="A390" t="s">
         <v>715</v>
       </c>
@@ -13344,7 +13341,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" hidden="1" spans="1:7">
       <c r="A391" t="s">
         <v>680</v>
       </c>
@@ -13505,7 +13502,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" hidden="1" spans="1:7">
       <c r="A398" t="s">
         <v>680</v>
       </c>
@@ -13758,7 +13755,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="409" hidden="1" spans="1:7">
+    <row r="409" spans="1:7">
       <c r="A409" t="s">
         <v>255</v>
       </c>
@@ -13804,7 +13801,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" hidden="1" spans="1:7">
       <c r="A411" t="s">
         <v>680</v>
       </c>
@@ -13965,7 +13962,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" hidden="1" spans="1:7">
       <c r="A418" t="s">
         <v>751</v>
       </c>
@@ -13988,7 +13985,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" hidden="1" spans="1:7">
       <c r="A419" t="s">
         <v>753</v>
       </c>
@@ -14011,7 +14008,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" hidden="1" spans="1:7">
       <c r="A420" t="s">
         <v>756</v>
       </c>
@@ -14149,7 +14146,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:7">
+    <row r="426" spans="1:7">
       <c r="A426" t="s">
         <v>760</v>
       </c>
@@ -14195,7 +14192,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" hidden="1" spans="1:7">
       <c r="A428" t="s">
         <v>756</v>
       </c>
@@ -14241,7 +14238,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" hidden="1" spans="1:7">
       <c r="A430" t="s">
         <v>756</v>
       </c>
@@ -14494,7 +14491,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="441" hidden="1" spans="1:7">
+    <row r="441" spans="1:7">
       <c r="A441" t="s">
         <v>771</v>
       </c>
@@ -14586,7 +14583,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="445" spans="1:7">
+    <row r="445" hidden="1" spans="1:7">
       <c r="A445" t="s">
         <v>756</v>
       </c>
@@ -14632,7 +14629,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
+    <row r="447" hidden="1" spans="1:7">
       <c r="A447" t="s">
         <v>756</v>
       </c>
@@ -14655,7 +14652,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" hidden="1" spans="1:7">
       <c r="A448" t="s">
         <v>756</v>
       </c>
@@ -14839,7 +14836,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="456" hidden="1" spans="1:7">
+    <row r="456" spans="1:7">
       <c r="A456" t="s">
         <v>787</v>
       </c>
@@ -15046,7 +15043,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="465" spans="1:7">
+    <row r="465" hidden="1" spans="1:7">
       <c r="A465" t="s">
         <v>799</v>
       </c>
@@ -15115,7 +15112,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="468" spans="1:7">
+    <row r="468" hidden="1" spans="1:7">
       <c r="A468" t="s">
         <v>805</v>
       </c>
@@ -15345,7 +15342,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="478" spans="1:7">
+    <row r="478" hidden="1" spans="1:7">
       <c r="A478" t="s">
         <v>822</v>
       </c>
@@ -15437,7 +15434,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="482" spans="1:7">
+    <row r="482" hidden="1" spans="1:7">
       <c r="A482" t="s">
         <v>822</v>
       </c>
@@ -15575,7 +15572,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="488" spans="1:7">
+    <row r="488" hidden="1" spans="1:7">
       <c r="A488" t="s">
         <v>822</v>
       </c>
@@ -15667,7 +15664,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="492" spans="1:7">
+    <row r="492" hidden="1" spans="1:7">
       <c r="A492" t="s">
         <v>822</v>
       </c>
@@ -15782,7 +15779,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="497" spans="1:7">
+    <row r="497" hidden="1" spans="1:7">
       <c r="A497" t="s">
         <v>850</v>
       </c>
@@ -15966,7 +15963,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="505" spans="1:7">
+    <row r="505" hidden="1" spans="1:7">
       <c r="A505" t="s">
         <v>866</v>
       </c>
@@ -16173,7 +16170,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="514" spans="1:7">
+    <row r="514" hidden="1" spans="1:7">
       <c r="A514" t="s">
         <v>866</v>
       </c>
@@ -16196,7 +16193,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="515" spans="1:7">
+    <row r="515" hidden="1" spans="1:7">
       <c r="A515" t="s">
         <v>866</v>
       </c>
@@ -16311,7 +16308,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="520" spans="1:7">
+    <row r="520" hidden="1" spans="1:7">
       <c r="A520" t="s">
         <v>893</v>
       </c>
@@ -16380,7 +16377,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="523" spans="1:7">
+    <row r="523" hidden="1" spans="1:7">
       <c r="A523" t="s">
         <v>898</v>
       </c>
@@ -16426,7 +16423,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="525" spans="1:7">
+    <row r="525" hidden="1" spans="1:7">
       <c r="A525" t="s">
         <v>902</v>
       </c>
@@ -16495,7 +16492,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="528" spans="1:7">
+    <row r="528" hidden="1" spans="1:7">
       <c r="A528" t="s">
         <v>902</v>
       </c>
@@ -16541,7 +16538,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="530" spans="1:7">
+    <row r="530" hidden="1" spans="1:7">
       <c r="A530" t="s">
         <v>902</v>
       </c>
@@ -16817,7 +16814,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="542" spans="1:7">
+    <row r="542" hidden="1" spans="1:7">
       <c r="A542" t="s">
         <v>936</v>
       </c>
@@ -16932,7 +16929,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="547" spans="1:7">
+    <row r="547" hidden="1" spans="1:7">
       <c r="A547" t="s">
         <v>936</v>
       </c>
@@ -17116,7 +17113,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="555" spans="1:7">
+    <row r="555" hidden="1" spans="1:7">
       <c r="A555" t="s">
         <v>936</v>
       </c>
@@ -17369,7 +17366,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="566" spans="1:7">
+    <row r="566" hidden="1" spans="1:7">
       <c r="A566" t="s">
         <v>936</v>
       </c>
@@ -17461,7 +17458,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="570" spans="1:7">
+    <row r="570" hidden="1" spans="1:7">
       <c r="A570" t="s">
         <v>936</v>
       </c>
@@ -17576,7 +17573,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="575" spans="1:7">
+    <row r="575" hidden="1" spans="1:7">
       <c r="A575" t="s">
         <v>936</v>
       </c>
@@ -17622,7 +17619,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="577" spans="1:7">
+    <row r="577" hidden="1" spans="1:7">
       <c r="A577" t="s">
         <v>936</v>
       </c>
@@ -17714,7 +17711,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="581" spans="1:7">
+    <row r="581" hidden="1" spans="1:7">
       <c r="A581" t="s">
         <v>936</v>
       </c>
@@ -17760,7 +17757,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="583" spans="1:7">
+    <row r="583" hidden="1" spans="1:7">
       <c r="A583" t="s">
         <v>936</v>
       </c>
@@ -17783,7 +17780,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="584" spans="1:7">
+    <row r="584" hidden="1" spans="1:7">
       <c r="A584" t="s">
         <v>936</v>
       </c>
@@ -17806,7 +17803,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="585" spans="1:7">
+    <row r="585" hidden="1" spans="1:7">
       <c r="A585" t="s">
         <v>936</v>
       </c>
@@ -17829,7 +17826,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="586" spans="1:7">
+    <row r="586" hidden="1" spans="1:7">
       <c r="A586" t="s">
         <v>936</v>
       </c>
@@ -17852,7 +17849,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="587" spans="1:7">
+    <row r="587" hidden="1" spans="1:7">
       <c r="A587" t="s">
         <v>936</v>
       </c>
@@ -17875,7 +17872,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="588" spans="1:7">
+    <row r="588" hidden="1" spans="1:7">
       <c r="A588" t="s">
         <v>936</v>
       </c>
@@ -17921,7 +17918,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="590" spans="1:7">
+    <row r="590" hidden="1" spans="1:7">
       <c r="A590" t="s">
         <v>936</v>
       </c>
@@ -17944,7 +17941,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="591" spans="1:7">
+    <row r="591" hidden="1" spans="1:7">
       <c r="A591" t="s">
         <v>936</v>
       </c>
@@ -18289,7 +18286,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="606" spans="1:7">
+    <row r="606" hidden="1" spans="1:7">
       <c r="A606" t="s">
         <v>1025</v>
       </c>
@@ -18358,7 +18355,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="609" spans="1:7">
+    <row r="609" hidden="1" spans="1:7">
       <c r="A609" t="s">
         <v>1025</v>
       </c>
@@ -18427,7 +18424,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="612" spans="1:7">
+    <row r="612" hidden="1" spans="1:7">
       <c r="A612" t="s">
         <v>1025</v>
       </c>
@@ -18473,7 +18470,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="614" spans="1:7">
+    <row r="614" hidden="1" spans="1:7">
       <c r="A614" t="s">
         <v>1025</v>
       </c>
@@ -18496,7 +18493,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="615" spans="1:7">
+    <row r="615" hidden="1" spans="1:7">
       <c r="A615" t="s">
         <v>1034</v>
       </c>
@@ -18519,7 +18516,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="616" spans="1:7">
+    <row r="616" hidden="1" spans="1:7">
       <c r="A616" t="s">
         <v>1036</v>
       </c>
@@ -18565,7 +18562,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="618" spans="1:7">
+    <row r="618" hidden="1" spans="1:7">
       <c r="A618" t="s">
         <v>1036</v>
       </c>
@@ -18611,7 +18608,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="620" spans="1:7">
+    <row r="620" hidden="1" spans="1:7">
       <c r="A620" t="s">
         <v>1042</v>
       </c>
@@ -18634,7 +18631,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="621" spans="1:7">
+    <row r="621" hidden="1" spans="1:7">
       <c r="A621" t="s">
         <v>1044</v>
       </c>
@@ -18657,7 +18654,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="622" spans="1:7">
+    <row r="622" hidden="1" spans="1:7">
       <c r="A622" t="s">
         <v>1046</v>
       </c>
@@ -18703,7 +18700,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="624" spans="1:7">
+    <row r="624" hidden="1" spans="1:7">
       <c r="A624" t="s">
         <v>1048</v>
       </c>
@@ -18795,7 +18792,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="628" spans="1:7">
+    <row r="628" hidden="1" spans="1:7">
       <c r="A628" t="s">
         <v>1055</v>
       </c>
@@ -18887,7 +18884,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="632" spans="1:7">
+    <row r="632" hidden="1" spans="1:7">
       <c r="A632" t="s">
         <v>1060</v>
       </c>
@@ -18910,7 +18907,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="633" spans="1:7">
+    <row r="633" hidden="1" spans="1:7">
       <c r="A633" t="s">
         <v>1062</v>
       </c>
@@ -18933,7 +18930,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="634" spans="1:7">
+    <row r="634" hidden="1" spans="1:7">
       <c r="A634" t="s">
         <v>1064</v>
       </c>
@@ -18956,7 +18953,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="635" spans="1:7">
+    <row r="635" hidden="1" spans="1:7">
       <c r="A635" t="s">
         <v>1067</v>
       </c>
@@ -19048,7 +19045,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="639" spans="1:7">
+    <row r="639" hidden="1" spans="1:7">
       <c r="A639" t="s">
         <v>1076</v>
       </c>
@@ -19094,7 +19091,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="641" spans="1:7">
+    <row r="641" hidden="1" spans="1:7">
       <c r="A641" t="s">
         <v>1076</v>
       </c>
@@ -19347,7 +19344,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="652" spans="1:7">
+    <row r="652" hidden="1" spans="1:7">
       <c r="A652" t="s">
         <v>1076</v>
       </c>
@@ -19462,7 +19459,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="657" spans="1:7">
+    <row r="657" hidden="1" spans="1:7">
       <c r="A657" t="s">
         <v>1096</v>
       </c>
@@ -19761,12 +19758,12 @@
         <v>468</v>
       </c>
     </row>
-    <row r="670" hidden="1" spans="1:7">
+    <row r="670" spans="1:7">
       <c r="A670" t="s">
+        <v>803</v>
+      </c>
+      <c r="B670" t="s">
         <v>1110</v>
-      </c>
-      <c r="B670" t="s">
-        <v>1111</v>
       </c>
       <c r="C670" t="s">
         <v>17</v>
@@ -19807,12 +19804,12 @@
         <v>481</v>
       </c>
     </row>
-    <row r="672" spans="1:7">
+    <row r="672" hidden="1" spans="1:7">
       <c r="A672" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B672" t="s">
         <v>1112</v>
-      </c>
-      <c r="B672" t="s">
-        <v>1113</v>
       </c>
       <c r="C672" t="s">
         <v>189</v>
@@ -19834,75 +19831,19 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G672" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="TD-Dimensionnement des systèmes à énergies renouvelables"/>
-        <filter val="TD-Réseaux électriques Industriels"/>
-        <filter val="TD-Systèmes de conversion de l'énergie éolienne"/>
-        <filter val="TD-Intégration des énergies renouvelables aux réseaux"/>
-        <filter val="TD-Analyse 1"/>
-        <filter val="TD-Analyse 3"/>
-        <filter val="TD-Electricité fondamentale"/>
-        <filter val="TD-Théorie du champ"/>
-        <filter val="TD-Algèbre 1"/>
-        <filter val="TD-Électronique fondamentale 1"/>
-        <filter val="TD-Systèmes Asservis"/>
-        <filter val="TD-Ondes et vibrations"/>
-        <filter val="TD-Planification des réseaux électriques"/>
-        <filter val="TD-Réseaux de transport et distribution"/>
-        <filter val="TD-Théorie de champ"/>
-        <filter val="TD-Commande électrique des mécanismes industriels"/>
-        <filter val="TD-Commande électrique"/>
-        <filter val="TD-Techniques de la Haute tension"/>
-        <filter val="TD-Technique de la haute tension"/>
-        <filter val="TD-Réseaux électriques 2"/>
-        <filter val="TD-Stabilité et dynamique des réseaux électriques"/>
-        <filter val="TD-Automates Programmables Industriels PLC"/>
-        <filter val="TD-Structure de la matière"/>
-        <filter val="TD-Machines électriques approfondies"/>
-        <filter val="TD-Commande des systèmes à énergies renouvelables"/>
-        <filter val="TD-Systèmes de conversion de l'énergie Photovoltaïque"/>
-        <filter val="TD-Méthodes numériques appliquées et optimisation"/>
-        <filter val="TD-Exploitation des Réseaux électriques"/>
-        <filter val="TD-Techniques d'intelligene artificielle"/>
-        <filter val="TD-Systèmes Asservis 1"/>
-        <filter val="TD-Anglais technique"/>
-        <filter val="TD-Machines Électriques"/>
-        <filter val="TD-Diagnostic et maintenance des systèmes électriques"/>
-        <filter val="TD-Association onvertisseurs machines"/>
-        <filter val="TD-Machines électriques spéciales"/>
-        <filter val="TD-Modélisation des Réseaux électriques"/>
-        <filter val="TD-Électronique de puissance"/>
-        <filter val="TD-Electrotechnique fondamentale 1"/>
-        <filter val="TD-Systèmes multi sources à énergies renouvelables"/>
-        <filter val="TD-Commande des machines électriques"/>
-        <filter val="TD-Constrution des réseaux électriques"/>
-        <filter val="TD-Dimensionnement des Réseaux électriques industriels"/>
-        <filter val="TD-Mécanique rationnelle"/>
-        <filter val="TD-ELN fondamentale 1"/>
-        <filter val="TD-ELT Fondamentale 1"/>
-        <filter val="TD-Analyse numérique 1"/>
-        <filter val="TD-Intégration des ressoures renouvelables aux réseaux électriques"/>
-        <filter val="TD-Probabilités et Statistiques"/>
-        <filter val="TD-Réseaux électriques"/>
-        <filter val="TD-Techniques de protection des réseaux électriques"/>
-        <filter val="TD-Électronique de puissance avancée"/>
-        <filter val="TD-Éléments de Mécanique"/>
-        <filter val="TD-Életrotechnique fondamentale"/>
-        <filter val="TD-Théorie du champ électromagnétique"/>
-        <filter val="TD-Théorie du champ Électromagnétique"/>
-        <filter val="TD-Électrification des entreprises industrielles"/>
-        <filter val="TD-applications et dimensionnement des systèmes à énergies renouvelables"/>
-        <filter val="TD-Élément de mécanique"/>
-        <filter val="TD-Régime transitoire des machines électriques"/>
-        <filter val="TD-Réseaux de transport et de distribution d'énergie électrique"/>
-        <filter val="TD-Logique combinatoire et séquentielle"/>
-        <filter val="TD-Transfert thermique"/>
-        <filter val="TD-Conduite des réseaux électriques"/>
-        <filter val="TD-Méthodes numériques appliquées"/>
-        <filter val="TD-Commande non linéaire et avancées"/>
-        <filter val="TD-Systèmes asservis linéaires continus"/>
-        <filter val="TD-Protection des réseaux électriques"/>
-        <filter val="TD-Commandes avancées"/>
-        <filter val="TD-Electronique de puissance II"/>
+        <filter val="Cours-μ-processeurs et μ-contrôleurs Cours"/>
+        <filter val="Cours-Machines électriques approfondies"/>
+        <filter val="Cours-Énergies renouvelables"/>
+        <filter val="Cours-Réseaux de transport et de distribution d'énergie électrique"/>
+        <filter val="Cours-Électronique de puissance avancée"/>
+        <filter val="Cours-Anglais technique et terminologie"/>
+        <filter val="Cours-Méthodes numériques appliquées et optimisation"/>
+        <filter val="Cours-Programmation avancée en Python"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="M1ER"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:G672">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4704" uniqueCount="1113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1114">
   <si>
     <t>Enseignements</t>
   </si>
@@ -3369,6 +3369,9 @@
   </si>
   <si>
     <t>TD-TT-ING3EI</t>
+  </si>
+  <si>
+    <t>Cours-ANGTT-M1CE</t>
   </si>
 </sst>
 </file>
@@ -4360,7 +4363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G672"/>
+  <dimension ref="A1:G673"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="76.8571428571429" customWidth="1"/>
@@ -12881,7 +12884,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="371" hidden="1" spans="1:7">
+    <row r="371" spans="1:7">
       <c r="A371" s="3" t="s">
         <v>293</v>
       </c>
@@ -13226,7 +13229,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:7">
+    <row r="386" spans="1:7">
       <c r="A386" s="4" t="s">
         <v>715</v>
       </c>
@@ -13686,7 +13689,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="406" hidden="1" spans="1:7">
+    <row r="406" spans="1:7">
       <c r="A406" s="3" t="s">
         <v>255</v>
       </c>
@@ -14054,7 +14057,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:7">
+    <row r="422" spans="1:7">
       <c r="A422" s="3" t="s">
         <v>760</v>
       </c>
@@ -14284,7 +14287,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:7">
+    <row r="432" spans="1:7">
       <c r="A432" s="5" t="s">
         <v>771</v>
       </c>
@@ -14767,7 +14770,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="453" hidden="1" spans="1:7">
+    <row r="453" spans="1:7">
       <c r="A453" s="3" t="s">
         <v>787</v>
       </c>
@@ -19758,7 +19761,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="670" spans="1:7">
+    <row r="670" hidden="1" spans="1:7">
       <c r="A670" t="s">
         <v>803</v>
       </c>
@@ -19825,6 +19828,29 @@
       </c>
       <c r="G672" t="s">
         <v>145</v>
+      </c>
+    </row>
+    <row r="673" spans="1:7">
+      <c r="A673" t="s">
+        <v>678</v>
+      </c>
+      <c r="B673" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C673" t="s">
+        <v>50</v>
+      </c>
+      <c r="D673" t="s">
+        <v>26</v>
+      </c>
+      <c r="E673" t="s">
+        <v>36</v>
+      </c>
+      <c r="F673" t="s">
+        <v>467</v>
+      </c>
+      <c r="G673" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -19844,6 +19870,7 @@
     <filterColumn colId="6">
       <filters>
         <filter val="M1ER"/>
+        <filter val="M1CE"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:G672">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$672</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$673</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -9411,7 +9411,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="220" hidden="1" spans="1:7">
+    <row r="220" spans="1:7">
       <c r="A220" t="s">
         <v>457</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="331" hidden="1" spans="1:7">
+    <row r="331" spans="1:7">
       <c r="A331" t="s">
         <v>608</v>
       </c>
@@ -11975,7 +11975,7 @@
         <v>257</v>
       </c>
       <c r="D331" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="E331" t="s">
         <v>36</v>
@@ -12562,7 +12562,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:7">
+    <row r="357" spans="1:7">
       <c r="A357" t="s">
         <v>653</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>26</v>
       </c>
       <c r="E357" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F357" t="s">
         <v>470</v>
@@ -12723,7 +12723,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" hidden="1" spans="1:7">
       <c r="A364" t="s">
         <v>678</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" hidden="1" spans="1:7">
       <c r="A371" s="3" t="s">
         <v>293</v>
       </c>
@@ -12930,7 +12930,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" hidden="1" spans="1:7">
       <c r="A373" t="s">
         <v>293</v>
       </c>
@@ -13229,7 +13229,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" hidden="1" spans="1:7">
       <c r="A386" s="4" t="s">
         <v>715</v>
       </c>
@@ -13321,7 +13321,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390" t="s">
         <v>715</v>
       </c>
@@ -13689,7 +13689,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" hidden="1" spans="1:7">
       <c r="A406" s="3" t="s">
         <v>255</v>
       </c>
@@ -13758,7 +13758,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" hidden="1" spans="1:7">
       <c r="A409" t="s">
         <v>255</v>
       </c>
@@ -14057,7 +14057,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" hidden="1" spans="1:7">
       <c r="A422" s="3" t="s">
         <v>760</v>
       </c>
@@ -14149,7 +14149,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" hidden="1" spans="1:7">
       <c r="A426" t="s">
         <v>760</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" hidden="1" spans="1:7">
       <c r="A432" s="5" t="s">
         <v>771</v>
       </c>
@@ -14494,7 +14494,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="441" spans="1:7">
+    <row r="441" hidden="1" spans="1:7">
       <c r="A441" t="s">
         <v>771</v>
       </c>
@@ -14770,7 +14770,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="453" spans="1:7">
+    <row r="453" hidden="1" spans="1:7">
       <c r="A453" s="3" t="s">
         <v>787</v>
       </c>
@@ -14839,7 +14839,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" hidden="1" spans="1:7">
       <c r="A456" t="s">
         <v>787</v>
       </c>
@@ -15575,7 +15575,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="488" hidden="1" spans="1:7">
+    <row r="488" spans="1:7">
       <c r="A488" t="s">
         <v>822</v>
       </c>
@@ -19830,7 +19830,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="673" spans="1:7">
+    <row r="673" hidden="1" spans="1:7">
       <c r="A673" t="s">
         <v>678</v>
       </c>
@@ -19854,26 +19854,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G672" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G673" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="Cours-μ-processeurs et μ-contrôleurs Cours"/>
-        <filter val="Cours-Machines électriques approfondies"/>
-        <filter val="Cours-Énergies renouvelables"/>
-        <filter val="Cours-Réseaux de transport et de distribution d'énergie électrique"/>
-        <filter val="Cours-Électronique de puissance avancée"/>
-        <filter val="Cours-Anglais technique et terminologie"/>
-        <filter val="Cours-Méthodes numériques appliquées et optimisation"/>
-        <filter val="Cours-Programmation avancée en Python"/>
+        <filter val="TD-Machines électriques approfondies"/>
+        <filter val="TD-Réseaux de transport et de distribution d'énergie électrique"/>
+        <filter val="TD-Électronique de puissance avancée"/>
+        <filter val="TD-Méthodes numériques appliquées et optimisation"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="M1ER"/>
-        <filter val="M1CE"/>
+        <filter val="M1ME"/>
       </filters>
     </filterColumn>
-    <sortState ref="A2:G672">
+    <sortState ref="A2:G673">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -2159,9 +2159,6 @@
     <t>Labo machine/Salle micro 02</t>
   </si>
   <si>
-    <t xml:space="preserve">Salle micro 02 </t>
-  </si>
-  <si>
     <t>Cours-EPA-M1ME</t>
   </si>
   <si>
@@ -2210,6 +2207,9 @@
     <t>RAMI ABDELKADER</t>
   </si>
   <si>
+    <t xml:space="preserve">Salle micro 01 </t>
+  </si>
+  <si>
     <t>TP-MEA-RE</t>
   </si>
   <si>
@@ -2228,21 +2228,21 @@
     <t>TP-MNAO-M1ER</t>
   </si>
   <si>
+    <t>TP-MNAO-RE</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées et optimisation-G2</t>
+  </si>
+  <si>
+    <t>Cours-Exploitation des Réseaux électriques</t>
+  </si>
+  <si>
+    <t>Cours-ERE-M1MCIL</t>
+  </si>
+  <si>
     <t>TP-MNAO-M1ME</t>
   </si>
   <si>
-    <t>TP-MNAO-RE</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées et optimisation-G2</t>
-  </si>
-  <si>
-    <t>Cours-Exploitation des Réseaux électriques</t>
-  </si>
-  <si>
-    <t>Cours-ERE-M1MCIL</t>
-  </si>
-  <si>
     <t>Cours-MEA-M1CE</t>
   </si>
   <si>
@@ -2318,37 +2318,37 @@
     <t>Cours-MNAO-M1CE</t>
   </si>
   <si>
+    <t>TP-PAP-RE</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées-G2</t>
+  </si>
+  <si>
+    <t>TP-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-MNAO-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-MNAO-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-MNAO-M1RE</t>
+  </si>
+  <si>
+    <t>TD-PS-MCIL2</t>
+  </si>
+  <si>
+    <t>TP-Programmation avancée en Python-G2</t>
+  </si>
+  <si>
+    <t>Cours-Programmation avancée en Python</t>
+  </si>
+  <si>
+    <t>Cours-PAP-M1CE</t>
+  </si>
+  <si>
     <t>TP-PAP-M1ME</t>
-  </si>
-  <si>
-    <t>TP-PAP-RE</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées-G2</t>
-  </si>
-  <si>
-    <t>TP-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-MNAO-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-MNAO-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-MNAO-M1RE</t>
-  </si>
-  <si>
-    <t>TD-PS-MCIL2</t>
-  </si>
-  <si>
-    <t>TP-Programmation avancée en Python-G2</t>
-  </si>
-  <si>
-    <t>Cours-Programmation avancée en Python</t>
-  </si>
-  <si>
-    <t>Cours-PAP-M1CE</t>
   </si>
   <si>
     <t>TP-Réseaux de transport et de distribution d'énergie électrique-G1</t>
@@ -9411,7 +9411,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" hidden="1" spans="1:7">
       <c r="A220" t="s">
         <v>457</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" hidden="1" spans="1:7">
       <c r="A331" t="s">
         <v>608</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" hidden="1" spans="1:7">
       <c r="A357" t="s">
         <v>653</v>
       </c>
@@ -12861,7 +12861,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:7">
+    <row r="370" spans="1:7">
       <c r="A370" s="1" t="s">
         <v>685</v>
       </c>
@@ -13091,7 +13091,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="380" hidden="1" spans="1:7">
+    <row r="380" spans="1:7">
       <c r="A380" s="1" t="s">
         <v>703</v>
       </c>
@@ -13108,7 +13108,7 @@
         <v>56</v>
       </c>
       <c r="F380" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="G380" t="s">
         <v>471</v>
@@ -13142,7 +13142,7 @@
         <v>293</v>
       </c>
       <c r="B382" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C382" t="s">
         <v>466</v>
@@ -13165,7 +13165,7 @@
         <v>705</v>
       </c>
       <c r="B383" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C383" t="s">
         <v>290</v>
@@ -13177,7 +13177,7 @@
         <v>36</v>
       </c>
       <c r="F383" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G383" t="s">
         <v>464</v>
@@ -13188,7 +13188,7 @@
         <v>293</v>
       </c>
       <c r="B384" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C384" t="s">
         <v>466</v>
@@ -13223,7 +13223,7 @@
         <v>11</v>
       </c>
       <c r="F385" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G385" t="s">
         <v>231</v>
@@ -13231,10 +13231,10 @@
     </row>
     <row r="386" hidden="1" spans="1:7">
       <c r="A386" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="B386" t="s">
         <v>715</v>
-      </c>
-      <c r="B386" t="s">
-        <v>716</v>
       </c>
       <c r="C386" t="s">
         <v>298</v>
@@ -13257,7 +13257,7 @@
         <v>705</v>
       </c>
       <c r="B387" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C387" t="s">
         <v>290</v>
@@ -13269,7 +13269,7 @@
         <v>41</v>
       </c>
       <c r="F387" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G387" t="s">
         <v>468</v>
@@ -13277,7 +13277,7 @@
     </row>
     <row r="388" hidden="1" spans="1:7">
       <c r="A388" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B388" t="s">
         <v>706</v>
@@ -13303,7 +13303,7 @@
         <v>680</v>
       </c>
       <c r="B389" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C389" t="s">
         <v>22</v>
@@ -13315,7 +13315,7 @@
         <v>11</v>
       </c>
       <c r="F389" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G389" t="s">
         <v>254</v>
@@ -13323,10 +13323,10 @@
     </row>
     <row r="390" hidden="1" spans="1:7">
       <c r="A390" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B390" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C390" t="s">
         <v>298</v>
@@ -13349,7 +13349,7 @@
         <v>680</v>
       </c>
       <c r="B391" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C391" t="s">
         <v>22</v>
@@ -13369,10 +13369,10 @@
     </row>
     <row r="392" hidden="1" spans="1:7">
       <c r="A392" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B392" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C392" t="s">
         <v>298</v>
@@ -13392,10 +13392,10 @@
     </row>
     <row r="393" hidden="1" spans="1:7">
       <c r="A393" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B393" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C393" t="s">
         <v>290</v>
@@ -13407,21 +13407,21 @@
         <v>36</v>
       </c>
       <c r="F393" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G393" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="394" hidden="1" spans="1:7">
+    <row r="394" spans="1:7">
       <c r="A394" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B394" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="C394" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="C394" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="D394" s="2" t="s">
         <v>18</v>
@@ -13430,7 +13430,7 @@
         <v>41</v>
       </c>
       <c r="F394" t="s">
-        <v>709</v>
+        <v>725</v>
       </c>
       <c r="G394" t="s">
         <v>471</v>
@@ -13438,13 +13438,13 @@
     </row>
     <row r="395" hidden="1" spans="1:7">
       <c r="A395" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B395" s="4" t="s">
         <v>726</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>18</v>
@@ -13484,7 +13484,7 @@
     </row>
     <row r="397" hidden="1" spans="1:7">
       <c r="A397" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B397" t="s">
         <v>730</v>
@@ -13510,7 +13510,7 @@
         <v>680</v>
       </c>
       <c r="B398" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C398" t="s">
         <v>59</v>
@@ -13551,24 +13551,24 @@
         <v>464</v>
       </c>
     </row>
-    <row r="400" hidden="1" spans="1:7">
-      <c r="A400" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="B400" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="C400" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="D400" s="1" t="s">
+    <row r="400" spans="1:7">
+      <c r="A400" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D400" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E400" s="1" t="s">
-        <v>56</v>
+      <c r="E400" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="F400" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="G400" t="s">
         <v>471</v>
@@ -13579,7 +13579,7 @@
         <v>728</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C401" s="4" t="s">
         <v>674</v>
@@ -13599,7 +13599,7 @@
     </row>
     <row r="402" hidden="1" spans="1:7">
       <c r="A402" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B402" t="s">
         <v>729</v>
@@ -13622,10 +13622,10 @@
     </row>
     <row r="403" hidden="1" spans="1:7">
       <c r="A403" t="s">
+        <v>734</v>
+      </c>
+      <c r="B403" t="s">
         <v>735</v>
-      </c>
-      <c r="B403" t="s">
-        <v>736</v>
       </c>
       <c r="C403" t="s">
         <v>319</v>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="404" hidden="1" spans="1:7">
       <c r="A404" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B404" t="s">
         <v>731</v>
@@ -13666,18 +13666,18 @@
         <v>464</v>
       </c>
     </row>
-    <row r="405" hidden="1" spans="1:7">
+    <row r="405" spans="1:7">
       <c r="A405" s="1" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>674</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>56</v>
@@ -13714,10 +13714,10 @@
     </row>
     <row r="407" hidden="1" spans="1:7">
       <c r="A407" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>674</v>
@@ -13809,7 +13809,7 @@
         <v>680</v>
       </c>
       <c r="B411" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C411" t="s">
         <v>22</v>
@@ -13901,7 +13901,7 @@
         <v>747</v>
       </c>
       <c r="B415" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C415" t="s">
         <v>707</v>
@@ -13913,7 +13913,7 @@
         <v>41</v>
       </c>
       <c r="F415" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G415" t="s">
         <v>468</v>
@@ -14028,7 +14028,7 @@
         <v>56</v>
       </c>
       <c r="F420" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G420" t="s">
         <v>231</v>
@@ -14080,21 +14080,21 @@
         <v>462</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:7">
-      <c r="A423" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="B423" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="C423" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D423" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E423" s="2" t="s">
-        <v>41</v>
+    <row r="423" spans="1:7">
+      <c r="A423" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E423" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="F423" t="s">
         <v>694</v>
@@ -14108,7 +14108,7 @@
         <v>738</v>
       </c>
       <c r="B424" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C424" t="s">
         <v>268</v>
@@ -14128,10 +14128,10 @@
     </row>
     <row r="425" hidden="1" spans="1:7">
       <c r="A425" t="s">
+        <v>763</v>
+      </c>
+      <c r="B425" t="s">
         <v>764</v>
-      </c>
-      <c r="B425" t="s">
-        <v>765</v>
       </c>
       <c r="C425" t="s">
         <v>9</v>
@@ -14154,7 +14154,7 @@
         <v>760</v>
       </c>
       <c r="B426" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C426" t="s">
         <v>295</v>
@@ -14177,7 +14177,7 @@
         <v>760</v>
       </c>
       <c r="B427" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C427" t="s">
         <v>674</v>
@@ -14223,7 +14223,7 @@
         <v>760</v>
       </c>
       <c r="B429" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C429" t="s">
         <v>674</v>
@@ -14246,7 +14246,7 @@
         <v>756</v>
       </c>
       <c r="B430" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C430" t="s">
         <v>22</v>
@@ -14266,7 +14266,7 @@
     </row>
     <row r="431" hidden="1" spans="1:7">
       <c r="A431" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B431" t="s">
         <v>739</v>
@@ -14289,10 +14289,10 @@
     </row>
     <row r="432" hidden="1" spans="1:7">
       <c r="A432" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="B432" t="s">
         <v>771</v>
-      </c>
-      <c r="B432" t="s">
-        <v>772</v>
       </c>
       <c r="C432" t="s">
         <v>268</v>
@@ -14312,7 +14312,7 @@
     </row>
     <row r="433" hidden="1" spans="1:7">
       <c r="A433" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B433" t="s">
         <v>748</v>
@@ -14333,18 +14333,18 @@
         <v>464</v>
       </c>
     </row>
-    <row r="434" hidden="1" spans="1:7">
+    <row r="434" spans="1:7">
       <c r="A434" s="2" t="s">
-        <v>770</v>
+        <v>738</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>268</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>41</v>
@@ -14356,18 +14356,18 @@
         <v>471</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:7">
+    <row r="435" spans="1:7">
       <c r="A435" s="2" t="s">
-        <v>705</v>
+        <v>769</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>724</v>
+        <v>772</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>725</v>
+        <v>268</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>41</v>
@@ -14381,10 +14381,10 @@
     </row>
     <row r="436" hidden="1" spans="1:7">
       <c r="A436" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B436" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C436" t="s">
         <v>268</v>
@@ -14448,7 +14448,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="439" hidden="1" spans="1:7">
+    <row r="439" spans="1:7">
       <c r="A439" s="1" t="s">
         <v>773</v>
       </c>
@@ -14496,7 +14496,7 @@
     </row>
     <row r="441" hidden="1" spans="1:7">
       <c r="A441" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B441" t="s">
         <v>779</v>
@@ -14565,7 +14565,7 @@
     </row>
     <row r="444" hidden="1" spans="1:7">
       <c r="A444" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B444" t="s">
         <v>781</v>
@@ -14591,7 +14591,7 @@
         <v>756</v>
       </c>
       <c r="B445" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C445" t="s">
         <v>22</v>
@@ -14611,7 +14611,7 @@
     </row>
     <row r="446" hidden="1" spans="1:7">
       <c r="A446" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B446" t="s">
         <v>782</v>
@@ -14637,7 +14637,7 @@
         <v>756</v>
       </c>
       <c r="B447" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C447" t="s">
         <v>22</v>
@@ -14660,7 +14660,7 @@
         <v>756</v>
       </c>
       <c r="B448" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C448" t="s">
         <v>22</v>
@@ -14678,7 +14678,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="449" hidden="1" spans="1:7">
+    <row r="449" spans="1:7">
       <c r="A449" s="1" t="s">
         <v>780</v>
       </c>
@@ -14709,7 +14709,7 @@
         <v>726</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>23</v>
@@ -14916,7 +14916,7 @@
         <v>795</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>25</v>
@@ -14931,7 +14931,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="460" hidden="1" spans="1:7">
+    <row r="460" spans="1:7">
       <c r="A460" s="1" t="s">
         <v>784</v>
       </c>
@@ -14939,7 +14939,7 @@
         <v>796</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D460" s="1" t="s">
         <v>26</v>
@@ -15023,7 +15023,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="464" hidden="1" spans="1:7">
+    <row r="464" spans="1:7">
       <c r="A464" s="1" t="s">
         <v>797</v>
       </c>
@@ -15031,7 +15031,7 @@
         <v>796</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D464" s="1" t="s">
         <v>10</v>
@@ -15575,7 +15575,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="488" spans="1:7">
+    <row r="488" hidden="1" spans="1:7">
       <c r="A488" t="s">
         <v>822</v>
       </c>
@@ -17055,7 +17055,7 @@
         <v>954</v>
       </c>
       <c r="C552" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D552" t="s">
         <v>18</v>
@@ -17078,7 +17078,7 @@
         <v>954</v>
       </c>
       <c r="C553" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D553" t="s">
         <v>23</v>
@@ -17262,7 +17262,7 @@
         <v>967</v>
       </c>
       <c r="C561" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D561" t="s">
         <v>26</v>
@@ -19700,7 +19700,7 @@
         <v>1107</v>
       </c>
       <c r="C667" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D667" t="s">
         <v>10</v>
@@ -19723,7 +19723,7 @@
         <v>1108</v>
       </c>
       <c r="C668" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D668" t="s">
         <v>10</v>
@@ -19743,7 +19743,7 @@
         <v>1109</v>
       </c>
       <c r="B669" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C669" t="s">
         <v>9</v>
@@ -19792,7 +19792,7 @@
         <v>795</v>
       </c>
       <c r="C671" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D671" s="4" t="s">
         <v>26</v>
@@ -19857,10 +19857,18 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G673" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="TD-Machines électriques approfondies"/>
-        <filter val="TD-Réseaux de transport et de distribution d'énergie électrique"/>
-        <filter val="TD-Électronique de puissance avancée"/>
-        <filter val="TD-Méthodes numériques appliquées et optimisation"/>
+        <filter val="TP-Méthodes numériques appliquées et optimisation-G1"/>
+        <filter val="TP-μ-processeurs et μ-contrôleurs-G1"/>
+        <filter val="TP-Réseaux de transport et de distribution d'énergie électrique-G1"/>
+        <filter val="TP-Programmation avancée en Python-G1"/>
+        <filter val="TP-Électronique de puissance avancée-G1"/>
+        <filter val="TP-Machines électriques approfondies-G1"/>
+        <filter val="TP-Méthodes numériques appliquées et optimisation-G2"/>
+        <filter val="TP-μ-processeurs et μ-contrôleurs-G2"/>
+        <filter val="TP-Réseaux de transport et de distribution d'énergie électrique-G2"/>
+        <filter val="TP-Programmation avancée en Python-G2"/>
+        <filter val="TP-Électronique de puissance avancée-G2"/>
+        <filter val="TP-Machines électriques approfondies-G2"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1116">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2747,7 +2747,7 @@
     <t>Cours-LEDPA-M2MCIL</t>
   </si>
   <si>
-    <t>Cours-applications du plasma</t>
+    <t>Cours-Applications du plasma</t>
   </si>
   <si>
     <t>Cours-AP-M2MCIL</t>
@@ -2771,58 +2771,148 @@
     <t>Cours-THT-M2MCIL</t>
   </si>
   <si>
-    <t>TP-Techniques de protection des réseaux électriques /G2/G1</t>
+    <t>TP-Électrifiation des entreprises industrielles-G1</t>
+  </si>
+  <si>
+    <t>TP-EEI-M2MCIL</t>
+  </si>
+  <si>
+    <t>Salle de micro BIS G1</t>
+  </si>
+  <si>
+    <t>TP-Électrifiation des entreprises industrielles-G2</t>
+  </si>
+  <si>
+    <t>Salle de micro BIS G2</t>
+  </si>
+  <si>
+    <t>TP-Techniques de la Haute tension-G2</t>
+  </si>
+  <si>
+    <t>TP-THT-M2MCIL</t>
+  </si>
+  <si>
+    <t>Labo haute tension G2</t>
+  </si>
+  <si>
+    <t>TP-Techniques de la Haute tension-G1</t>
+  </si>
+  <si>
+    <t>Labo haute tension G1</t>
+  </si>
+  <si>
+    <t>TP-Techniques de protection des réseaux électriques-G2</t>
   </si>
   <si>
     <t>TP-TsPRE-M2MCIL</t>
   </si>
   <si>
+    <t>Labo réseaux G1</t>
+  </si>
+  <si>
+    <t>TP-Techniques de protection des réseaux électriques-G1</t>
+  </si>
+  <si>
     <t>Labo réseaux G2</t>
   </si>
   <si>
-    <t>TP-Techniques de la HT /TP G1</t>
-  </si>
-  <si>
-    <t>TP-THT-M2MCIL</t>
-  </si>
-  <si>
-    <t>Labo haute tension G1</t>
-  </si>
-  <si>
-    <t>TP-Électrifiation des entreprises industrielles /G2</t>
-  </si>
-  <si>
-    <t>TP-EEI-M2MCIL</t>
-  </si>
-  <si>
-    <t>Salle de micro BIS G2</t>
-  </si>
-  <si>
-    <t>TP-Techniques de la HT /G2</t>
-  </si>
-  <si>
-    <t>Labo haute tension G2</t>
-  </si>
-  <si>
-    <t>TP-Électrifiation des entreprises industrielles /G1</t>
-  </si>
-  <si>
-    <t>Salle de micro BIS G1</t>
-  </si>
-  <si>
-    <t>TP-Techniques de protection des réseaux électriques /G1/G2</t>
-  </si>
-  <si>
-    <t>Labo réseaux G1</t>
-  </si>
-  <si>
     <t>Cours-Identifiation et diagnostique des machines électriques</t>
   </si>
   <si>
     <t>Cours-IDME-M2ME</t>
   </si>
   <si>
-    <t>TP-Machines électriques spéciales TP G1</t>
+    <t>TP-Commande des machines électriques-G1</t>
+  </si>
+  <si>
+    <t>TP-CME-M2ME</t>
+  </si>
+  <si>
+    <t>Salle de micro AUTO DEP</t>
+  </si>
+  <si>
+    <t>TP-Commande des machines électriques-G2</t>
+  </si>
+  <si>
+    <t>Cours-Machines électriques spéciales</t>
+  </si>
+  <si>
+    <t>Cours-MES-M2ME</t>
+  </si>
+  <si>
+    <t>TD-Structure de la matière</t>
+  </si>
+  <si>
+    <t>TD-SM-L1MCIL</t>
+  </si>
+  <si>
+    <t>MECHETTEM KHALIDA</t>
+  </si>
+  <si>
+    <t>A10/G3</t>
+  </si>
+  <si>
+    <t>Cours-EAD-Recherche doumentaire et conception de mémoire EAD</t>
+  </si>
+  <si>
+    <t>Cours-EAD-RDCM-M2ME</t>
+  </si>
+  <si>
+    <t>TP-conception assistée par ordinateur des machines électriques-G1</t>
+  </si>
+  <si>
+    <t>TP-CAOME-M2ME</t>
+  </si>
+  <si>
+    <t>Salle micro 2 DEP, Labo machine 2</t>
+  </si>
+  <si>
+    <t>TP-conception assistée par ordinateur des machines électriques-G2</t>
+  </si>
+  <si>
+    <t>Cours-Régime transitoire des machines électriques</t>
+  </si>
+  <si>
+    <t>Cours-RTME-M2ME</t>
+  </si>
+  <si>
+    <t>Cours-Echaufement et refroidissement des actionneurs éléctromécaniques</t>
+  </si>
+  <si>
+    <t>Cours-ERAE-M2ME</t>
+  </si>
+  <si>
+    <t>TP-Identifiation et diagnostique des machines électriques-G1</t>
+  </si>
+  <si>
+    <t>TP-IDME-M2ME</t>
+  </si>
+  <si>
+    <t>Labo machine 2, Salle micro 2</t>
+  </si>
+  <si>
+    <t>TP-Identifiation et diagnostique des machines électriques-G2</t>
+  </si>
+  <si>
+    <t>ZERDANI MOHAMMED</t>
+  </si>
+  <si>
+    <t>Cours-Implémentation d'une Commande numérique en temps réel</t>
+  </si>
+  <si>
+    <t>Cours-ICNTR-M2ME</t>
+  </si>
+  <si>
+    <t>Cours-Commande des machines électriques</t>
+  </si>
+  <si>
+    <t>Cours-CME-M2ME</t>
+  </si>
+  <si>
+    <t>A10/G7</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques spéciales-G1</t>
   </si>
   <si>
     <t>TP-MES-M2ME</t>
@@ -2831,100 +2921,16 @@
     <t>Labo machine 1</t>
   </si>
   <si>
-    <t>TP-Machines électriques spéciales TP G2</t>
-  </si>
-  <si>
-    <t>Cours-Machines électriques spéciales</t>
-  </si>
-  <si>
-    <t>Cours-MES-M2ME</t>
-  </si>
-  <si>
-    <t>TD-Structure de la matière</t>
-  </si>
-  <si>
-    <t>TD-SM-L1MCIL</t>
-  </si>
-  <si>
-    <t>MECHETTEM KHALIDA</t>
-  </si>
-  <si>
-    <t>A10/G3</t>
-  </si>
-  <si>
-    <t>Cours-EAD-Recherche doumentaire et conception de mémoire EAD</t>
-  </si>
-  <si>
-    <t>Cours-EAD-RDCM-M2ME</t>
-  </si>
-  <si>
-    <t>TP-Régime transitoire des machines électriques TP 1/15</t>
+    <t>TP-Machines électriques spéciales-G2</t>
+  </si>
+  <si>
+    <t>TP-Régime transitoire des machines électriques-G2</t>
   </si>
   <si>
     <t>TP-RTME-M2ME</t>
   </si>
   <si>
-    <t>Salle de micro AUTO DEP</t>
-  </si>
-  <si>
-    <t>TP-Commande des machines électriques TP 1/15</t>
-  </si>
-  <si>
-    <t>TP-CME-M2ME</t>
-  </si>
-  <si>
-    <t>Cours-Régime transitoire des machines électriques</t>
-  </si>
-  <si>
-    <t>Cours-RTME-M2ME</t>
-  </si>
-  <si>
-    <t>Cours-Echaufement et refroidissement des actionneurs éléctromécaniques</t>
-  </si>
-  <si>
-    <t>Cours-ERAE-M2ME</t>
-  </si>
-  <si>
-    <t>Cours-Implémentation d'une Commande numérique en temps réel</t>
-  </si>
-  <si>
-    <t>Cours-ICNTR-M2ME</t>
-  </si>
-  <si>
-    <t>TP-conception assistée par ordinateur des machines électriques TP G1</t>
-  </si>
-  <si>
-    <t>TP-CAOME-M2ME</t>
-  </si>
-  <si>
-    <t>Salle micro 2 DEP, Labo machine 2</t>
-  </si>
-  <si>
-    <t>TP-conception assistée par ordinateur des machines électriques TP G2</t>
-  </si>
-  <si>
-    <t>Cours-Commande des machines électriques</t>
-  </si>
-  <si>
-    <t>Cours-CME-M2ME</t>
-  </si>
-  <si>
-    <t>A10/G7</t>
-  </si>
-  <si>
-    <t>TP-Identifiation et diagnostique des machines électriques TP G1</t>
-  </si>
-  <si>
-    <t>TP-IDME-M2ME</t>
-  </si>
-  <si>
-    <t>Labo machine 2, Salle micro 2</t>
-  </si>
-  <si>
-    <t>ZERDANI MOHAMMED</t>
-  </si>
-  <si>
-    <t>TP-Identifiation et diagnostique des machines électriques TP G2</t>
+    <t>TP-Régime transitoire des machines électriques-G1</t>
   </si>
   <si>
     <t>Cours-ELEDPA-M2ME</t>
@@ -2939,13 +2945,13 @@
     <t>Cours-ELEDPA-M2RE</t>
   </si>
   <si>
-    <t>TP-Technique de la haute tension G1</t>
+    <t>TP-Technique de la haute tension-G1</t>
   </si>
   <si>
     <t>TP-THT-M2RE</t>
   </si>
   <si>
-    <t>TP-Technique de la haute tension G2</t>
+    <t>TP-Technique de la haute tension-G2</t>
   </si>
   <si>
     <t>Cours-SDRE-M2RE</t>
@@ -2966,13 +2972,13 @@
     <t>HAMMAR MEHDI</t>
   </si>
   <si>
-    <t>TP-Dimensionnement des Réseaux électriques industriels G2</t>
+    <t>TP-Dimensionnement des Réseaux électriques industriels-G2</t>
   </si>
   <si>
     <t>TP-DREI-M2RE</t>
   </si>
   <si>
-    <t>TP-Stabilité et dynamique des réseaux électriques G1</t>
+    <t>TP-Stabilité et dynamique des réseaux électriques-G1</t>
   </si>
   <si>
     <t>TP-SDRE-M2RE</t>
@@ -2981,10 +2987,10 @@
     <t>Salle micro 1 Teleom  G1</t>
   </si>
   <si>
-    <t>TP-Dimensionnement des Réseaux électriques industriels G1</t>
-  </si>
-  <si>
-    <t>TP-Stabilité et dynamique des réseaux électriques G2</t>
+    <t>TP-Dimensionnement des Réseaux électriques industriels-G1</t>
+  </si>
+  <si>
+    <t>TP-Stabilité et dynamique des réseaux électriques-G2</t>
   </si>
   <si>
     <t>Salle micro 1 Teleom  G2</t>
@@ -12861,7 +12867,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" hidden="1" spans="1:7">
       <c r="A370" s="1" t="s">
         <v>685</v>
       </c>
@@ -13091,7 +13097,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" hidden="1" spans="1:7">
       <c r="A380" s="1" t="s">
         <v>703</v>
       </c>
@@ -13413,7 +13419,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" hidden="1" spans="1:7">
       <c r="A394" s="2" t="s">
         <v>718</v>
       </c>
@@ -13551,7 +13557,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" hidden="1" spans="1:7">
       <c r="A400" s="2" t="s">
         <v>705</v>
       </c>
@@ -13666,7 +13672,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" hidden="1" spans="1:7">
       <c r="A405" s="1" t="s">
         <v>728</v>
       </c>
@@ -14080,7 +14086,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" hidden="1" spans="1:7">
       <c r="A423" s="1" t="s">
         <v>733</v>
       </c>
@@ -14333,7 +14339,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" hidden="1" spans="1:7">
       <c r="A434" s="2" t="s">
         <v>738</v>
       </c>
@@ -14356,7 +14362,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" hidden="1" spans="1:7">
       <c r="A435" s="2" t="s">
         <v>769</v>
       </c>
@@ -14448,7 +14454,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" hidden="1" spans="1:7">
       <c r="A439" s="1" t="s">
         <v>773</v>
       </c>
@@ -14678,7 +14684,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" hidden="1" spans="1:7">
       <c r="A449" s="1" t="s">
         <v>780</v>
       </c>
@@ -14931,7 +14937,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" hidden="1" spans="1:7">
       <c r="A460" s="1" t="s">
         <v>784</v>
       </c>
@@ -15023,7 +15029,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="464" spans="1:7">
+    <row r="464" hidden="1" spans="1:7">
       <c r="A464" s="1" t="s">
         <v>797</v>
       </c>
@@ -16595,10 +16601,10 @@
         <v>914</v>
       </c>
       <c r="C532" t="s">
-        <v>248</v>
+        <v>745</v>
       </c>
       <c r="D532" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E532" t="s">
         <v>36</v>
@@ -16615,10 +16621,10 @@
         <v>916</v>
       </c>
       <c r="B533" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C533" t="s">
-        <v>360</v>
+        <v>745</v>
       </c>
       <c r="D533" t="s">
         <v>18</v>
@@ -16627,7 +16633,7 @@
         <v>36</v>
       </c>
       <c r="F533" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G533" t="s">
         <v>424</v>
@@ -16635,22 +16641,22 @@
     </row>
     <row r="534" hidden="1" spans="1:7">
       <c r="A534" t="s">
+        <v>918</v>
+      </c>
+      <c r="B534" t="s">
         <v>919</v>
       </c>
-      <c r="B534" t="s">
-        <v>920</v>
-      </c>
       <c r="C534" t="s">
-        <v>745</v>
+        <v>360</v>
       </c>
       <c r="D534" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E534" t="s">
         <v>36</v>
       </c>
       <c r="F534" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G534" t="s">
         <v>424</v>
@@ -16658,22 +16664,22 @@
     </row>
     <row r="535" hidden="1" spans="1:7">
       <c r="A535" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B535" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C535" t="s">
         <v>360</v>
       </c>
       <c r="D535" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E535" t="s">
         <v>36</v>
       </c>
       <c r="F535" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G535" t="s">
         <v>424</v>
@@ -16681,16 +16687,16 @@
     </row>
     <row r="536" hidden="1" spans="1:7">
       <c r="A536" t="s">
+        <v>923</v>
+      </c>
+      <c r="B536" t="s">
         <v>924</v>
       </c>
-      <c r="B536" t="s">
-        <v>920</v>
-      </c>
       <c r="C536" t="s">
-        <v>745</v>
+        <v>248</v>
       </c>
       <c r="D536" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E536" t="s">
         <v>36</v>
@@ -16707,13 +16713,13 @@
         <v>926</v>
       </c>
       <c r="B537" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="C537" t="s">
         <v>248</v>
       </c>
       <c r="D537" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E537" t="s">
         <v>36</v>
@@ -16748,7 +16754,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="539" hidden="1" spans="1:7">
+    <row r="539" spans="1:7">
       <c r="A539" t="s">
         <v>930</v>
       </c>
@@ -16756,13 +16762,13 @@
         <v>931</v>
       </c>
       <c r="C539" t="s">
-        <v>643</v>
+        <v>379</v>
       </c>
       <c r="D539" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E539" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F539" t="s">
         <v>932</v>
@@ -16771,7 +16777,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="540" hidden="1" spans="1:7">
+    <row r="540" spans="1:7">
       <c r="A540" t="s">
         <v>933</v>
       </c>
@@ -16779,13 +16785,13 @@
         <v>931</v>
       </c>
       <c r="C540" t="s">
-        <v>643</v>
+        <v>379</v>
       </c>
       <c r="D540" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E540" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F540" t="s">
         <v>932</v>
@@ -16863,7 +16869,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="544" hidden="1" spans="1:7">
+    <row r="544" spans="1:7">
       <c r="A544" t="s">
         <v>942</v>
       </c>
@@ -16871,13 +16877,13 @@
         <v>943</v>
       </c>
       <c r="C544" t="s">
-        <v>615</v>
+        <v>724</v>
       </c>
       <c r="D544" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E544" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F544" t="s">
         <v>944</v>
@@ -16886,21 +16892,21 @@
         <v>381</v>
       </c>
     </row>
-    <row r="545" hidden="1" spans="1:7">
+    <row r="545" spans="1:7">
       <c r="A545" t="s">
         <v>945</v>
       </c>
       <c r="B545" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="C545" t="s">
-        <v>379</v>
+        <v>724</v>
       </c>
       <c r="D545" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E545" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F545" t="s">
         <v>944</v>
@@ -16911,10 +16917,10 @@
     </row>
     <row r="546" hidden="1" spans="1:7">
       <c r="A546" t="s">
+        <v>946</v>
+      </c>
+      <c r="B546" t="s">
         <v>947</v>
-      </c>
-      <c r="B546" t="s">
-        <v>948</v>
       </c>
       <c r="C546" t="s">
         <v>707</v>
@@ -16957,10 +16963,10 @@
     </row>
     <row r="548" hidden="1" spans="1:7">
       <c r="A548" t="s">
+        <v>948</v>
+      </c>
+      <c r="B548" t="s">
         <v>949</v>
-      </c>
-      <c r="B548" t="s">
-        <v>950</v>
       </c>
       <c r="C548" t="s">
         <v>674</v>
@@ -16978,47 +16984,47 @@
         <v>381</v>
       </c>
     </row>
-    <row r="549" hidden="1" spans="1:7">
+    <row r="549" spans="1:7">
       <c r="A549" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="B549" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="C549" t="s">
-        <v>615</v>
+        <v>707</v>
       </c>
       <c r="D549" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E549" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F549" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="G549" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="550" hidden="1" spans="1:7">
+    <row r="550" spans="1:7">
       <c r="A550" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="B550" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="C550" t="s">
-        <v>379</v>
+        <v>954</v>
       </c>
       <c r="D550" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E550" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F550" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="G550" t="s">
         <v>381</v>
@@ -17026,10 +17032,10 @@
     </row>
     <row r="551" hidden="1" spans="1:7">
       <c r="A551" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="B551" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="C551" t="s">
         <v>323</v>
@@ -17047,47 +17053,47 @@
         <v>381</v>
       </c>
     </row>
-    <row r="552" hidden="1" spans="1:7">
+    <row r="552" spans="1:7">
       <c r="A552" t="s">
         <v>953</v>
       </c>
       <c r="B552" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="C552" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="D552" t="s">
         <v>18</v>
       </c>
       <c r="E552" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F552" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="G552" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="553" hidden="1" spans="1:7">
+    <row r="553" spans="1:7">
       <c r="A553" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="B553" t="s">
+        <v>951</v>
+      </c>
+      <c r="C553" t="s">
         <v>954</v>
-      </c>
-      <c r="C553" t="s">
-        <v>724</v>
       </c>
       <c r="D553" t="s">
         <v>23</v>
       </c>
       <c r="E553" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F553" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="G553" t="s">
         <v>381</v>
@@ -17139,7 +17145,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="556" hidden="1" spans="1:7">
+    <row r="556" spans="1:7">
       <c r="A556" t="s">
         <v>960</v>
       </c>
@@ -17147,13 +17153,13 @@
         <v>961</v>
       </c>
       <c r="C556" t="s">
-        <v>707</v>
+        <v>643</v>
       </c>
       <c r="D556" t="s">
         <v>18</v>
       </c>
       <c r="E556" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F556" t="s">
         <v>962</v>
@@ -17162,21 +17168,21 @@
         <v>381</v>
       </c>
     </row>
-    <row r="557" hidden="1" spans="1:7">
+    <row r="557" spans="1:7">
       <c r="A557" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="B557" t="s">
         <v>961</v>
       </c>
       <c r="C557" t="s">
-        <v>963</v>
+        <v>643</v>
       </c>
       <c r="D557" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E557" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F557" t="s">
         <v>962</v>
@@ -17185,47 +17191,47 @@
         <v>381</v>
       </c>
     </row>
-    <row r="558" hidden="1" spans="1:7">
+    <row r="558" spans="1:7">
       <c r="A558" t="s">
         <v>964</v>
       </c>
       <c r="B558" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C558" t="s">
-        <v>707</v>
+        <v>615</v>
       </c>
       <c r="D558" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E558" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F558" t="s">
-        <v>962</v>
+        <v>932</v>
       </c>
       <c r="G558" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="559" hidden="1" spans="1:7">
+    <row r="559" spans="1:7">
       <c r="A559" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B559" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C559" t="s">
-        <v>963</v>
+        <v>615</v>
       </c>
       <c r="D559" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E559" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F559" t="s">
-        <v>962</v>
+        <v>932</v>
       </c>
       <c r="G559" t="s">
         <v>381</v>
@@ -17236,7 +17242,7 @@
         <v>808</v>
       </c>
       <c r="B560" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C560" t="s">
         <v>555</v>
@@ -17256,10 +17262,10 @@
     </row>
     <row r="561" hidden="1" spans="1:7">
       <c r="A561" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B561" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C561" t="s">
         <v>724</v>
@@ -17282,7 +17288,7 @@
         <v>808</v>
       </c>
       <c r="B562" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C562" t="s">
         <v>555</v>
@@ -17302,10 +17308,10 @@
     </row>
     <row r="563" hidden="1" spans="1:7">
       <c r="A563" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B563" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C563" t="s">
         <v>360</v>
@@ -17317,7 +17323,7 @@
         <v>11</v>
       </c>
       <c r="F563" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="G563" t="s">
         <v>416</v>
@@ -17325,10 +17331,10 @@
     </row>
     <row r="564" hidden="1" spans="1:7">
       <c r="A564" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B564" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C564" t="s">
         <v>360</v>
@@ -17340,7 +17346,7 @@
         <v>11</v>
       </c>
       <c r="F564" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="G564" t="s">
         <v>416</v>
@@ -17351,7 +17357,7 @@
         <v>334</v>
       </c>
       <c r="B565" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C565" t="s">
         <v>248</v>
@@ -17397,7 +17403,7 @@
         <v>825</v>
       </c>
       <c r="B567" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C567" t="s">
         <v>745</v>
@@ -17420,7 +17426,7 @@
         <v>837</v>
       </c>
       <c r="B568" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C568" t="s">
         <v>674</v>
@@ -17440,10 +17446,10 @@
     </row>
     <row r="569" hidden="1" spans="1:7">
       <c r="A569" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B569" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C569" t="s">
         <v>264</v>
@@ -17469,7 +17475,7 @@
         <v>937</v>
       </c>
       <c r="C570" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D570" t="s">
         <v>40</v>
@@ -17486,10 +17492,10 @@
     </row>
     <row r="571" hidden="1" spans="1:7">
       <c r="A571" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B571" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C571" t="s">
         <v>745</v>
@@ -17501,7 +17507,7 @@
         <v>41</v>
       </c>
       <c r="F571" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="G571" t="s">
         <v>416</v>
@@ -17509,10 +17515,10 @@
     </row>
     <row r="572" hidden="1" spans="1:7">
       <c r="A572" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B572" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C572" t="s">
         <v>248</v>
@@ -17524,7 +17530,7 @@
         <v>41</v>
       </c>
       <c r="F572" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="G572" t="s">
         <v>416</v>
@@ -17532,10 +17538,10 @@
     </row>
     <row r="573" hidden="1" spans="1:7">
       <c r="A573" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B573" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C573" t="s">
         <v>745</v>
@@ -17547,7 +17553,7 @@
         <v>41</v>
       </c>
       <c r="F573" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G573" t="s">
         <v>416</v>
@@ -17555,10 +17561,10 @@
     </row>
     <row r="574" hidden="1" spans="1:7">
       <c r="A574" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B574" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C574" t="s">
         <v>248</v>
@@ -17570,7 +17576,7 @@
         <v>41</v>
       </c>
       <c r="F574" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="G574" t="s">
         <v>416</v>
@@ -17584,7 +17590,7 @@
         <v>937</v>
       </c>
       <c r="C575" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D575" t="s">
         <v>44</v>
@@ -17601,10 +17607,10 @@
     </row>
     <row r="576" hidden="1" spans="1:7">
       <c r="A576" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B576" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C576" t="s">
         <v>346</v>
@@ -17630,7 +17636,7 @@
         <v>937</v>
       </c>
       <c r="C577" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D577" t="s">
         <v>53</v>
@@ -17639,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="F577" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="G577" t="s">
         <v>43</v>
@@ -17647,10 +17653,10 @@
     </row>
     <row r="578" hidden="1" spans="1:7">
       <c r="A578" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B578" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C578" t="s">
         <v>349</v>
@@ -17673,7 +17679,7 @@
         <v>387</v>
       </c>
       <c r="B579" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C579" t="s">
         <v>165</v>
@@ -17693,10 +17699,10 @@
     </row>
     <row r="580" hidden="1" spans="1:7">
       <c r="A580" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B580" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C580" t="s">
         <v>264</v>
@@ -17722,7 +17728,7 @@
         <v>937</v>
       </c>
       <c r="C581" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D581" t="s">
         <v>65</v>
@@ -17731,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="F581" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="G581" t="s">
         <v>43</v>
@@ -17739,10 +17745,10 @@
     </row>
     <row r="582" hidden="1" spans="1:7">
       <c r="A582" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B582" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C582" t="s">
         <v>338</v>
@@ -17754,7 +17760,7 @@
         <v>11</v>
       </c>
       <c r="F582" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="G582" t="s">
         <v>254</v>
@@ -17823,7 +17829,7 @@
         <v>56</v>
       </c>
       <c r="F585" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="G585" t="s">
         <v>43</v>
@@ -17846,7 +17852,7 @@
         <v>56</v>
       </c>
       <c r="F586" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="G586" t="s">
         <v>43</v>
@@ -17869,7 +17875,7 @@
         <v>36</v>
       </c>
       <c r="F587" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="G587" t="s">
         <v>43</v>
@@ -17903,7 +17909,7 @@
         <v>103</v>
       </c>
       <c r="B589" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C589" t="s">
         <v>69</v>
@@ -17915,7 +17921,7 @@
         <v>11</v>
       </c>
       <c r="F589" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="G589" t="s">
         <v>254</v>
@@ -17938,7 +17944,7 @@
         <v>36</v>
       </c>
       <c r="F590" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="G590" t="s">
         <v>43</v>
@@ -17961,7 +17967,7 @@
         <v>36</v>
       </c>
       <c r="F591" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="G591" t="s">
         <v>43</v>
@@ -17969,13 +17975,13 @@
     </row>
     <row r="592" hidden="1" spans="1:7">
       <c r="A592" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B592" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C592" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D592" t="s">
         <v>10</v>
@@ -17984,7 +17990,7 @@
         <v>27</v>
       </c>
       <c r="F592" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="G592" t="s">
         <v>254</v>
@@ -17992,10 +17998,10 @@
     </row>
     <row r="593" hidden="1" spans="1:7">
       <c r="A593" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B593" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C593" t="s">
         <v>219</v>
@@ -18007,7 +18013,7 @@
         <v>27</v>
       </c>
       <c r="F593" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="G593" t="s">
         <v>254</v>
@@ -18015,13 +18021,13 @@
     </row>
     <row r="594" hidden="1" spans="1:7">
       <c r="A594" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B594" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C594" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D594" t="s">
         <v>14</v>
@@ -18030,7 +18036,7 @@
         <v>27</v>
       </c>
       <c r="F594" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="G594" t="s">
         <v>254</v>
@@ -18038,10 +18044,10 @@
     </row>
     <row r="595" hidden="1" spans="1:7">
       <c r="A595" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B595" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C595" t="s">
         <v>219</v>
@@ -18053,7 +18059,7 @@
         <v>27</v>
       </c>
       <c r="F595" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="G595" t="s">
         <v>254</v>
@@ -18061,10 +18067,10 @@
     </row>
     <row r="596" hidden="1" spans="1:7">
       <c r="A596" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B596" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C596" t="s">
         <v>22</v>
@@ -18076,7 +18082,7 @@
         <v>27</v>
       </c>
       <c r="F596" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="G596" t="s">
         <v>254</v>
@@ -18087,10 +18093,10 @@
         <v>117</v>
       </c>
       <c r="B597" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C597" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D597" t="s">
         <v>18</v>
@@ -18099,7 +18105,7 @@
         <v>27</v>
       </c>
       <c r="F597" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="G597" t="s">
         <v>254</v>
@@ -18107,10 +18113,10 @@
     </row>
     <row r="598" hidden="1" spans="1:7">
       <c r="A598" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B598" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C598" t="s">
         <v>22</v>
@@ -18122,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="F598" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="G598" t="s">
         <v>254</v>
@@ -18130,13 +18136,13 @@
     </row>
     <row r="599" hidden="1" spans="1:7">
       <c r="A599" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B599" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C599" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D599" t="s">
         <v>25</v>
@@ -18145,7 +18151,7 @@
         <v>27</v>
       </c>
       <c r="F599" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="G599" t="s">
         <v>254</v>
@@ -18153,13 +18159,13 @@
     </row>
     <row r="600" hidden="1" spans="1:7">
       <c r="A600" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B600" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C600" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D600" t="s">
         <v>25</v>
@@ -18168,7 +18174,7 @@
         <v>27</v>
       </c>
       <c r="F600" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="G600" t="s">
         <v>254</v>
@@ -18176,10 +18182,10 @@
     </row>
     <row r="601" hidden="1" spans="1:7">
       <c r="A601" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B601" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C601" t="s">
         <v>22</v>
@@ -18191,7 +18197,7 @@
         <v>27</v>
       </c>
       <c r="F601" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G601" t="s">
         <v>254</v>
@@ -18199,13 +18205,13 @@
     </row>
     <row r="602" hidden="1" spans="1:7">
       <c r="A602" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B602" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C602" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D602" t="s">
         <v>26</v>
@@ -18214,7 +18220,7 @@
         <v>27</v>
       </c>
       <c r="F602" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="G602" t="s">
         <v>254</v>
@@ -18222,13 +18228,13 @@
     </row>
     <row r="603" hidden="1" spans="1:7">
       <c r="A603" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B603" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C603" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D603" t="s">
         <v>26</v>
@@ -18237,7 +18243,7 @@
         <v>27</v>
       </c>
       <c r="F603" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="G603" t="s">
         <v>254</v>
@@ -18245,10 +18251,10 @@
     </row>
     <row r="604" hidden="1" spans="1:7">
       <c r="A604" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B604" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C604" t="s">
         <v>22</v>
@@ -18260,7 +18266,7 @@
         <v>27</v>
       </c>
       <c r="F604" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="G604" t="s">
         <v>254</v>
@@ -18268,10 +18274,10 @@
     </row>
     <row r="605" hidden="1" spans="1:7">
       <c r="A605" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B605" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C605" t="s">
         <v>349</v>
@@ -18283,7 +18289,7 @@
         <v>41</v>
       </c>
       <c r="F605" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="G605" t="s">
         <v>254</v>
@@ -18291,10 +18297,10 @@
     </row>
     <row r="606" hidden="1" spans="1:7">
       <c r="A606" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B606" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C606" t="s">
         <v>615</v>
@@ -18314,13 +18320,13 @@
     </row>
     <row r="607" hidden="1" spans="1:7">
       <c r="A607" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B607" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C607" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D607" t="s">
         <v>18</v>
@@ -18329,7 +18335,7 @@
         <v>41</v>
       </c>
       <c r="F607" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="G607" t="s">
         <v>254</v>
@@ -18337,10 +18343,10 @@
     </row>
     <row r="608" hidden="1" spans="1:7">
       <c r="A608" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B608" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C608" t="s">
         <v>22</v>
@@ -18352,7 +18358,7 @@
         <v>41</v>
       </c>
       <c r="F608" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="G608" t="s">
         <v>254</v>
@@ -18360,10 +18366,10 @@
     </row>
     <row r="609" hidden="1" spans="1:7">
       <c r="A609" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B609" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C609" t="s">
         <v>243</v>
@@ -18375,7 +18381,7 @@
         <v>41</v>
       </c>
       <c r="F609" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="G609" t="s">
         <v>449</v>
@@ -18383,13 +18389,13 @@
     </row>
     <row r="610" hidden="1" spans="1:7">
       <c r="A610" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B610" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C610" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D610" t="s">
         <v>23</v>
@@ -18398,7 +18404,7 @@
         <v>41</v>
       </c>
       <c r="F610" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="G610" t="s">
         <v>254</v>
@@ -18406,10 +18412,10 @@
     </row>
     <row r="611" hidden="1" spans="1:7">
       <c r="A611" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B611" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C611" t="s">
         <v>22</v>
@@ -18421,7 +18427,7 @@
         <v>41</v>
       </c>
       <c r="F611" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="G611" t="s">
         <v>254</v>
@@ -18429,10 +18435,10 @@
     </row>
     <row r="612" hidden="1" spans="1:7">
       <c r="A612" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B612" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C612" t="s">
         <v>310</v>
@@ -18444,7 +18450,7 @@
         <v>41</v>
       </c>
       <c r="F612" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="G612" t="s">
         <v>449</v>
@@ -18455,7 +18461,7 @@
         <v>109</v>
       </c>
       <c r="B613" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C613" t="s">
         <v>295</v>
@@ -18467,7 +18473,7 @@
         <v>41</v>
       </c>
       <c r="F613" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="G613" t="s">
         <v>254</v>
@@ -18475,10 +18481,10 @@
     </row>
     <row r="614" hidden="1" spans="1:7">
       <c r="A614" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B614" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C614" t="s">
         <v>143</v>
@@ -18498,10 +18504,10 @@
     </row>
     <row r="615" hidden="1" spans="1:7">
       <c r="A615" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B615" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C615" t="s">
         <v>143</v>
@@ -18521,10 +18527,10 @@
     </row>
     <row r="616" hidden="1" spans="1:7">
       <c r="A616" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B616" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C616" t="s">
         <v>219</v>
@@ -18544,10 +18550,10 @@
     </row>
     <row r="617" hidden="1" spans="1:7">
       <c r="A617" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B617" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C617" t="s">
         <v>588</v>
@@ -18559,7 +18565,7 @@
         <v>56</v>
       </c>
       <c r="F617" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="G617" t="s">
         <v>254</v>
@@ -18567,10 +18573,10 @@
     </row>
     <row r="618" hidden="1" spans="1:7">
       <c r="A618" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B618" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C618" t="s">
         <v>219</v>
@@ -18593,10 +18599,10 @@
         <v>81</v>
       </c>
       <c r="B619" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C619" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D619" t="s">
         <v>18</v>
@@ -18605,7 +18611,7 @@
         <v>56</v>
       </c>
       <c r="F619" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="G619" t="s">
         <v>254</v>
@@ -18613,10 +18619,10 @@
     </row>
     <row r="620" hidden="1" spans="1:7">
       <c r="A620" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B620" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C620" t="s">
         <v>290</v>
@@ -18636,10 +18642,10 @@
     </row>
     <row r="621" hidden="1" spans="1:7">
       <c r="A621" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B621" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C621" t="s">
         <v>298</v>
@@ -18659,10 +18665,10 @@
     </row>
     <row r="622" hidden="1" spans="1:7">
       <c r="A622" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B622" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C622" t="s">
         <v>298</v>
@@ -18685,10 +18691,10 @@
         <v>81</v>
       </c>
       <c r="B623" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C623" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D623" t="s">
         <v>23</v>
@@ -18697,7 +18703,7 @@
         <v>56</v>
       </c>
       <c r="F623" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="G623" t="s">
         <v>254</v>
@@ -18705,10 +18711,10 @@
     </row>
     <row r="624" hidden="1" spans="1:7">
       <c r="A624" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B624" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C624" t="s">
         <v>346</v>
@@ -18731,10 +18737,10 @@
         <v>584</v>
       </c>
       <c r="B625" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="C625" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D625" t="s">
         <v>25</v>
@@ -18743,7 +18749,7 @@
         <v>56</v>
       </c>
       <c r="F625" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="G625" t="s">
         <v>254</v>
@@ -18754,7 +18760,7 @@
         <v>74</v>
       </c>
       <c r="B626" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="C626" t="s">
         <v>59</v>
@@ -18766,7 +18772,7 @@
         <v>56</v>
       </c>
       <c r="F626" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="G626" t="s">
         <v>254</v>
@@ -18777,10 +18783,10 @@
         <v>117</v>
       </c>
       <c r="B627" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C627" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D627" t="s">
         <v>10</v>
@@ -18789,7 +18795,7 @@
         <v>36</v>
       </c>
       <c r="F627" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G627" t="s">
         <v>254</v>
@@ -18797,10 +18803,10 @@
     </row>
     <row r="628" hidden="1" spans="1:7">
       <c r="A628" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B628" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C628" t="s">
         <v>346</v>
@@ -18823,10 +18829,10 @@
         <v>117</v>
       </c>
       <c r="B629" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C629" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D629" t="s">
         <v>14</v>
@@ -18835,7 +18841,7 @@
         <v>36</v>
       </c>
       <c r="F629" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="G629" t="s">
         <v>254</v>
@@ -18846,10 +18852,10 @@
         <v>117</v>
       </c>
       <c r="B630" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C630" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D630" t="s">
         <v>14</v>
@@ -18858,7 +18864,7 @@
         <v>36</v>
       </c>
       <c r="F630" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G630" t="s">
         <v>254</v>
@@ -18869,10 +18875,10 @@
         <v>117</v>
       </c>
       <c r="B631" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C631" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D631" t="s">
         <v>18</v>
@@ -18881,7 +18887,7 @@
         <v>36</v>
       </c>
       <c r="F631" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="G631" t="s">
         <v>254</v>
@@ -18889,10 +18895,10 @@
     </row>
     <row r="632" hidden="1" spans="1:7">
       <c r="A632" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B632" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C632" t="s">
         <v>327</v>
@@ -18912,10 +18918,10 @@
     </row>
     <row r="633" hidden="1" spans="1:7">
       <c r="A633" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B633" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C633" t="s">
         <v>839</v>
@@ -18935,13 +18941,13 @@
     </row>
     <row r="634" hidden="1" spans="1:7">
       <c r="A634" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B634" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C634" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D634" t="s">
         <v>23</v>
@@ -18958,13 +18964,13 @@
     </row>
     <row r="635" hidden="1" spans="1:7">
       <c r="A635" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B635" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C635" t="s">
         <v>1068</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1066</v>
       </c>
       <c r="D635" t="s">
         <v>26</v>
@@ -18973,7 +18979,7 @@
         <v>41</v>
       </c>
       <c r="F635" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="G635" t="s">
         <v>449</v>
@@ -18981,10 +18987,10 @@
     </row>
     <row r="636" hidden="1" spans="1:7">
       <c r="A636" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B636" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C636" t="s">
         <v>493</v>
@@ -18996,7 +19002,7 @@
         <v>36</v>
       </c>
       <c r="F636" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="G636" t="s">
         <v>254</v>
@@ -19004,10 +19010,10 @@
     </row>
     <row r="637" hidden="1" spans="1:7">
       <c r="A637" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B637" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C637" t="s">
         <v>816</v>
@@ -19027,13 +19033,13 @@
     </row>
     <row r="638" hidden="1" spans="1:7">
       <c r="A638" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B638" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C638" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D638" t="s">
         <v>18</v>
@@ -19050,13 +19056,13 @@
     </row>
     <row r="639" hidden="1" spans="1:7">
       <c r="A639" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B639" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C639" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D639" t="s">
         <v>23</v>
@@ -19076,7 +19082,7 @@
         <v>633</v>
       </c>
       <c r="B640" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C640" t="s">
         <v>143</v>
@@ -19096,13 +19102,13 @@
     </row>
     <row r="641" hidden="1" spans="1:7">
       <c r="A641" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B641" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C641" t="s">
         <v>1068</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1066</v>
       </c>
       <c r="D641" t="s">
         <v>10</v>
@@ -19111,7 +19117,7 @@
         <v>41</v>
       </c>
       <c r="F641" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="G641" t="s">
         <v>449</v>
@@ -19122,7 +19128,7 @@
         <v>20</v>
       </c>
       <c r="B642" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C642" t="s">
         <v>22</v>
@@ -19145,7 +19151,7 @@
         <v>20</v>
       </c>
       <c r="B643" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C643" t="s">
         <v>22</v>
@@ -19168,7 +19174,7 @@
         <v>20</v>
       </c>
       <c r="B644" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C644" t="s">
         <v>22</v>
@@ -19188,10 +19194,10 @@
     </row>
     <row r="645" hidden="1" spans="1:7">
       <c r="A645" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B645" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C645" t="s">
         <v>638</v>
@@ -19214,7 +19220,7 @@
         <v>20</v>
       </c>
       <c r="B646" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C646" t="s">
         <v>22</v>
@@ -19234,10 +19240,10 @@
     </row>
     <row r="647" hidden="1" spans="1:7">
       <c r="A647" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B647" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C647" t="s">
         <v>168</v>
@@ -19257,10 +19263,10 @@
     </row>
     <row r="648" hidden="1" spans="1:7">
       <c r="A648" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B648" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C648" t="s">
         <v>143</v>
@@ -19272,7 +19278,7 @@
         <v>41</v>
       </c>
       <c r="F648" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="G648" t="s">
         <v>454</v>
@@ -19280,10 +19286,10 @@
     </row>
     <row r="649" hidden="1" spans="1:7">
       <c r="A649" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B649" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C649" t="s">
         <v>143</v>
@@ -19295,7 +19301,7 @@
         <v>41</v>
       </c>
       <c r="F649" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="G649" t="s">
         <v>454</v>
@@ -19303,10 +19309,10 @@
     </row>
     <row r="650" hidden="1" spans="1:7">
       <c r="A650" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B650" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C650" t="s">
         <v>213</v>
@@ -19329,7 +19335,7 @@
         <v>163</v>
       </c>
       <c r="B651" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C651" t="s">
         <v>165</v>
@@ -19349,13 +19355,13 @@
     </row>
     <row r="652" hidden="1" spans="1:7">
       <c r="A652" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B652" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C652" t="s">
         <v>1068</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1066</v>
       </c>
       <c r="D652" t="s">
         <v>18</v>
@@ -19364,7 +19370,7 @@
         <v>41</v>
       </c>
       <c r="F652" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="G652" t="s">
         <v>449</v>
@@ -19375,7 +19381,7 @@
         <v>627</v>
       </c>
       <c r="B653" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C653" t="s">
         <v>582</v>
@@ -19387,7 +19393,7 @@
         <v>56</v>
       </c>
       <c r="F653" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="G653" t="s">
         <v>454</v>
@@ -19395,10 +19401,10 @@
     </row>
     <row r="654" hidden="1" spans="1:7">
       <c r="A654" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B654" t="s">
         <v>1094</v>
-      </c>
-      <c r="B654" t="s">
-        <v>1092</v>
       </c>
       <c r="C654" t="s">
         <v>213</v>
@@ -19410,7 +19416,7 @@
         <v>56</v>
       </c>
       <c r="F654" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="G654" t="s">
         <v>454</v>
@@ -19421,7 +19427,7 @@
         <v>627</v>
       </c>
       <c r="B655" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C655" t="s">
         <v>582</v>
@@ -19433,7 +19439,7 @@
         <v>56</v>
       </c>
       <c r="F655" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="G655" t="s">
         <v>454</v>
@@ -19441,10 +19447,10 @@
     </row>
     <row r="656" hidden="1" spans="1:7">
       <c r="A656" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B656" t="s">
         <v>1094</v>
-      </c>
-      <c r="B656" t="s">
-        <v>1092</v>
       </c>
       <c r="C656" t="s">
         <v>213</v>
@@ -19456,7 +19462,7 @@
         <v>56</v>
       </c>
       <c r="F656" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="G656" t="s">
         <v>454</v>
@@ -19464,13 +19470,13 @@
     </row>
     <row r="657" hidden="1" spans="1:7">
       <c r="A657" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B657" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C657" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D657" t="s">
         <v>23</v>
@@ -19487,10 +19493,10 @@
     </row>
     <row r="658" hidden="1" spans="1:7">
       <c r="A658" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B658" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C658" t="s">
         <v>327</v>
@@ -19513,7 +19519,7 @@
         <v>155</v>
       </c>
       <c r="B659" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C659" t="s">
         <v>157</v>
@@ -19525,7 +19531,7 @@
         <v>36</v>
       </c>
       <c r="F659" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="G659" t="s">
         <v>454</v>
@@ -19536,7 +19542,7 @@
         <v>617</v>
       </c>
       <c r="B660" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="C660" t="s">
         <v>327</v>
@@ -19548,7 +19554,7 @@
         <v>36</v>
       </c>
       <c r="F660" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="G660" t="s">
         <v>454</v>
@@ -19559,7 +19565,7 @@
         <v>20</v>
       </c>
       <c r="B661" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C661" t="s">
         <v>22</v>
@@ -19582,7 +19588,7 @@
         <v>20</v>
       </c>
       <c r="B662" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C662" t="s">
         <v>22</v>
@@ -19602,10 +19608,10 @@
     </row>
     <row r="663" hidden="1" spans="1:7">
       <c r="A663" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B663" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C663" t="s">
         <v>327</v>
@@ -19628,7 +19634,7 @@
         <v>155</v>
       </c>
       <c r="B664" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C664" t="s">
         <v>157</v>
@@ -19640,7 +19646,7 @@
         <v>36</v>
       </c>
       <c r="F664" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="G664" t="s">
         <v>454</v>
@@ -19651,7 +19657,7 @@
         <v>617</v>
       </c>
       <c r="B665" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="C665" t="s">
         <v>327</v>
@@ -19663,7 +19669,7 @@
         <v>36</v>
       </c>
       <c r="F665" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="G665" t="s">
         <v>454</v>
@@ -19674,7 +19680,7 @@
         <v>109</v>
       </c>
       <c r="B666" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="C666" t="s">
         <v>295</v>
@@ -19697,7 +19703,7 @@
         <v>803</v>
       </c>
       <c r="B667" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C667" t="s">
         <v>724</v>
@@ -19720,7 +19726,7 @@
         <v>803</v>
       </c>
       <c r="B668" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C668" t="s">
         <v>724</v>
@@ -19740,7 +19746,7 @@
     </row>
     <row r="669" hidden="1" spans="1:7">
       <c r="A669" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B669" t="s">
         <v>764</v>
@@ -19766,7 +19772,7 @@
         <v>803</v>
       </c>
       <c r="B670" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C670" t="s">
         <v>17</v>
@@ -19809,10 +19815,10 @@
     </row>
     <row r="672" hidden="1" spans="1:7">
       <c r="A672" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B672" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C672" t="s">
         <v>189</v>
@@ -19835,7 +19841,7 @@
         <v>678</v>
       </c>
       <c r="B673" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C673" t="s">
         <v>50</v>
@@ -19857,23 +19863,19 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G673" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="TP-Méthodes numériques appliquées et optimisation-G1"/>
-        <filter val="TP-μ-processeurs et μ-contrôleurs-G1"/>
-        <filter val="TP-Réseaux de transport et de distribution d'énergie électrique-G1"/>
-        <filter val="TP-Programmation avancée en Python-G1"/>
-        <filter val="TP-Électronique de puissance avancée-G1"/>
-        <filter val="TP-Machines électriques approfondies-G1"/>
-        <filter val="TP-Méthodes numériques appliquées et optimisation-G2"/>
-        <filter val="TP-μ-processeurs et μ-contrôleurs-G2"/>
-        <filter val="TP-Réseaux de transport et de distribution d'énergie électrique-G2"/>
-        <filter val="TP-Programmation avancée en Python-G2"/>
-        <filter val="TP-Électronique de puissance avancée-G2"/>
-        <filter val="TP-Machines électriques approfondies-G2"/>
+        <filter val="TP-conception assistée par ordinateur des machines électriques TP G1"/>
+        <filter val="TP-Identifiation et diagnostique des machines électriques TP G1"/>
+        <filter val="TP-Machines électriques spéciales TP G1"/>
+        <filter val="TP-conception assistée par ordinateur des machines électriques TP G2"/>
+        <filter val="TP-Identifiation et diagnostique des machines électriques TP G2"/>
+        <filter val="TP-Machines électriques spéciales TP G2"/>
+        <filter val="TP-Régime transitoire des machines électriques TP 1/15"/>
+        <filter val="TP-Commande des machines électriques TP 1/15"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="M1ME"/>
+        <filter val="M2ME"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:G673">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="1114">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2792,30 +2792,21 @@
     <t>TP-THT-M2MCIL</t>
   </si>
   <si>
-    <t>Labo haute tension G2</t>
+    <t>Labo haute tension</t>
   </si>
   <si>
     <t>TP-Techniques de la Haute tension-G1</t>
   </si>
   <si>
-    <t>Labo haute tension G1</t>
-  </si>
-  <si>
     <t>TP-Techniques de protection des réseaux électriques-G2</t>
   </si>
   <si>
     <t>TP-TsPRE-M2MCIL</t>
   </si>
   <si>
-    <t>Labo réseaux G1</t>
-  </si>
-  <si>
     <t>TP-Techniques de protection des réseaux électriques-G1</t>
   </si>
   <si>
-    <t>Labo réseaux G2</t>
-  </si>
-  <si>
     <t>Cours-Identifiation et diagnostique des machines électriques</t>
   </si>
   <si>
@@ -2828,7 +2819,7 @@
     <t>TP-CME-M2ME</t>
   </si>
   <si>
-    <t>Salle de micro AUTO DEP</t>
+    <t>Salle de micro AUTO</t>
   </si>
   <si>
     <t>TP-Commande des machines électriques-G2</t>
@@ -2864,7 +2855,7 @@
     <t>TP-CAOME-M2ME</t>
   </si>
   <si>
-    <t>Salle micro 2 DEP, Labo machine 2</t>
+    <t>Salle micro 2, Labo machine 2</t>
   </si>
   <si>
     <t>TP-conception assistée par ordinateur des machines électriques-G2</t>
@@ -2891,18 +2882,18 @@
     <t>Labo machine 2, Salle micro 2</t>
   </si>
   <si>
+    <t>ZERDANI MOHAMMED</t>
+  </si>
+  <si>
+    <t>Cours-Implémentation d'une Commande numérique en temps réel</t>
+  </si>
+  <si>
+    <t>Cours-ICNTR-M2ME</t>
+  </si>
+  <si>
     <t>TP-Identifiation et diagnostique des machines électriques-G2</t>
   </si>
   <si>
-    <t>ZERDANI MOHAMMED</t>
-  </si>
-  <si>
-    <t>Cours-Implémentation d'une Commande numérique en temps réel</t>
-  </si>
-  <si>
-    <t>Cours-ICNTR-M2ME</t>
-  </si>
-  <si>
     <t>Cours-Commande des machines électriques</t>
   </si>
   <si>
@@ -2924,15 +2915,18 @@
     <t>TP-Machines électriques spéciales-G2</t>
   </si>
   <si>
+    <t>TP-Régime transitoire des machines électriques-G1</t>
+  </si>
+  <si>
+    <t>TP-RTME-M2ME</t>
+  </si>
+  <si>
+    <t>Salle micro AUTO</t>
+  </si>
+  <si>
     <t>TP-Régime transitoire des machines électriques-G2</t>
   </si>
   <si>
-    <t>TP-RTME-M2ME</t>
-  </si>
-  <si>
-    <t>TP-Régime transitoire des machines électriques-G1</t>
-  </si>
-  <si>
     <t>Cours-ELEDPA-M2ME</t>
   </si>
   <si>
@@ -2984,16 +2978,16 @@
     <t>TP-SDRE-M2RE</t>
   </si>
   <si>
-    <t>Salle micro 1 Teleom  G1</t>
+    <t>Salle micro 1 Teleom</t>
   </si>
   <si>
     <t>TP-Dimensionnement des Réseaux électriques industriels-G1</t>
   </si>
   <si>
+    <t xml:space="preserve">Labo réseaux </t>
+  </si>
+  <si>
     <t>TP-Stabilité et dynamique des réseaux électriques-G2</t>
-  </si>
-  <si>
-    <t>Salle micro 1 Teleom  G2</t>
   </si>
   <si>
     <t>Cours-Technique de la haute tension</t>
@@ -3550,18 +3544,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -3892,7 +3880,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3916,16 +3904,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3934,95 +3922,94 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8819,7 +8806,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="194" hidden="1" spans="1:7">
+    <row r="194" spans="1:7">
       <c r="A194" t="s">
         <v>414</v>
       </c>
@@ -8911,7 +8898,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="198" hidden="1" spans="1:7">
+    <row r="198" spans="1:7">
       <c r="A198" t="s">
         <v>427</v>
       </c>
@@ -11326,7 +11313,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="303" hidden="1" spans="1:7">
+    <row r="303" spans="1:7">
       <c r="A303" t="s">
         <v>598</v>
       </c>
@@ -12871,16 +12858,16 @@
       <c r="A370" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B370" s="2" t="s">
+      <c r="B370" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="C370" s="2" t="s">
+      <c r="C370" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="D370" s="2" t="s">
+      <c r="D370" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E370" s="2" t="s">
+      <c r="E370" s="1" t="s">
         <v>56</v>
       </c>
       <c r="F370" t="s">
@@ -12891,7 +12878,7 @@
       </c>
     </row>
     <row r="371" hidden="1" spans="1:7">
-      <c r="A371" s="3" t="s">
+      <c r="A371" s="2" t="s">
         <v>293</v>
       </c>
       <c r="B371" t="s">
@@ -13101,16 +13088,16 @@
       <c r="A380" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B380" s="2" t="s">
+      <c r="B380" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="C380" s="2" t="s">
+      <c r="C380" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="D380" s="2" t="s">
+      <c r="D380" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E380" s="2" t="s">
+      <c r="E380" s="1" t="s">
         <v>56</v>
       </c>
       <c r="F380" t="s">
@@ -13236,7 +13223,7 @@
       </c>
     </row>
     <row r="386" hidden="1" spans="1:7">
-      <c r="A386" s="4" t="s">
+      <c r="A386" s="3" t="s">
         <v>714</v>
       </c>
       <c r="B386" t="s">
@@ -13374,7 +13361,7 @@
       </c>
     </row>
     <row r="392" hidden="1" spans="1:7">
-      <c r="A392" s="4" t="s">
+      <c r="A392" s="3" t="s">
         <v>714</v>
       </c>
       <c r="B392" t="s">
@@ -13420,19 +13407,19 @@
       </c>
     </row>
     <row r="394" hidden="1" spans="1:7">
-      <c r="A394" s="2" t="s">
+      <c r="A394" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B394" s="2" t="s">
+      <c r="B394" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="C394" s="2" t="s">
+      <c r="C394" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="D394" s="2" t="s">
+      <c r="D394" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E394" s="2" t="s">
+      <c r="E394" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F394" t="s">
@@ -13443,19 +13430,19 @@
       </c>
     </row>
     <row r="395" hidden="1" spans="1:7">
-      <c r="A395" s="4" t="s">
+      <c r="A395" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="B395" s="4" t="s">
+      <c r="B395" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="C395" s="4" t="s">
+      <c r="C395" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="D395" s="4" t="s">
+      <c r="D395" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E395" s="4" t="s">
+      <c r="E395" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F395" t="s">
@@ -13558,19 +13545,19 @@
       </c>
     </row>
     <row r="400" hidden="1" spans="1:7">
-      <c r="A400" s="2" t="s">
+      <c r="A400" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B400" s="2" t="s">
+      <c r="B400" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="C400" s="2" t="s">
+      <c r="C400" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="D400" s="2" t="s">
+      <c r="D400" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E400" s="2" t="s">
+      <c r="E400" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F400" t="s">
@@ -13581,19 +13568,19 @@
       </c>
     </row>
     <row r="401" hidden="1" spans="1:7">
-      <c r="A401" s="4" t="s">
+      <c r="A401" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="B401" s="4" t="s">
+      <c r="B401" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="C401" s="4" t="s">
+      <c r="C401" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="D401" s="4" t="s">
+      <c r="D401" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E401" s="4" t="s">
+      <c r="E401" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F401" t="s">
@@ -13696,7 +13683,7 @@
       </c>
     </row>
     <row r="406" hidden="1" spans="1:7">
-      <c r="A406" s="3" t="s">
+      <c r="A406" s="2" t="s">
         <v>255</v>
       </c>
       <c r="B406" t="s">
@@ -13719,19 +13706,19 @@
       </c>
     </row>
     <row r="407" hidden="1" spans="1:7">
-      <c r="A407" s="4" t="s">
+      <c r="A407" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="B407" s="4" t="s">
+      <c r="B407" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="C407" s="4" t="s">
+      <c r="C407" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="D407" s="4" t="s">
+      <c r="D407" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E407" s="4" t="s">
+      <c r="E407" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F407" t="s">
@@ -14064,7 +14051,7 @@
       </c>
     </row>
     <row r="422" hidden="1" spans="1:7">
-      <c r="A422" s="3" t="s">
+      <c r="A422" s="2" t="s">
         <v>760</v>
       </c>
       <c r="B422" t="s">
@@ -14294,7 +14281,7 @@
       </c>
     </row>
     <row r="432" hidden="1" spans="1:7">
-      <c r="A432" s="5" t="s">
+      <c r="A432" s="4" t="s">
         <v>770</v>
       </c>
       <c r="B432" t="s">
@@ -14340,19 +14327,19 @@
       </c>
     </row>
     <row r="434" hidden="1" spans="1:7">
-      <c r="A434" s="2" t="s">
+      <c r="A434" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="B434" s="2" t="s">
+      <c r="B434" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="C434" s="2" t="s">
+      <c r="C434" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D434" s="2" t="s">
+      <c r="D434" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E434" s="2" t="s">
+      <c r="E434" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F434" t="s">
@@ -14363,19 +14350,19 @@
       </c>
     </row>
     <row r="435" hidden="1" spans="1:7">
-      <c r="A435" s="2" t="s">
+      <c r="A435" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="B435" s="2" t="s">
+      <c r="B435" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="C435" s="2" t="s">
+      <c r="C435" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D435" s="2" t="s">
+      <c r="D435" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E435" s="2" t="s">
+      <c r="E435" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F435" t="s">
@@ -14478,19 +14465,19 @@
       </c>
     </row>
     <row r="440" hidden="1" spans="1:7">
-      <c r="A440" s="4" t="s">
+      <c r="A440" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="B440" s="4" t="s">
+      <c r="B440" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="C440" s="4" t="s">
+      <c r="C440" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="D440" s="4" t="s">
+      <c r="D440" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E440" s="4" t="s">
+      <c r="E440" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F440" t="s">
@@ -14570,7 +14557,7 @@
       </c>
     </row>
     <row r="444" hidden="1" spans="1:7">
-      <c r="A444" s="4" t="s">
+      <c r="A444" s="3" t="s">
         <v>770</v>
       </c>
       <c r="B444" t="s">
@@ -14708,19 +14695,19 @@
       </c>
     </row>
     <row r="450" hidden="1" spans="1:7">
-      <c r="A450" s="4" t="s">
+      <c r="A450" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="B450" s="4" t="s">
+      <c r="B450" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="C450" s="4" t="s">
+      <c r="C450" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="D450" s="4" t="s">
+      <c r="D450" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E450" s="4" t="s">
+      <c r="E450" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F450" t="s">
@@ -14731,19 +14718,19 @@
       </c>
     </row>
     <row r="451" hidden="1" spans="1:7">
-      <c r="A451" s="4" t="s">
+      <c r="A451" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="B451" s="4" t="s">
+      <c r="B451" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="C451" s="4" t="s">
+      <c r="C451" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="D451" s="4" t="s">
+      <c r="D451" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E451" s="4" t="s">
+      <c r="E451" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F451" t="s">
@@ -14777,7 +14764,7 @@
       </c>
     </row>
     <row r="453" hidden="1" spans="1:7">
-      <c r="A453" s="3" t="s">
+      <c r="A453" s="2" t="s">
         <v>787</v>
       </c>
       <c r="B453" t="s">
@@ -14915,19 +14902,19 @@
       </c>
     </row>
     <row r="459" hidden="1" spans="1:7">
-      <c r="A459" s="4" t="s">
+      <c r="A459" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="B459" s="4" t="s">
+      <c r="B459" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="C459" s="4" t="s">
+      <c r="C459" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="D459" s="4" t="s">
+      <c r="D459" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E459" s="4" t="s">
+      <c r="E459" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F459" t="s">
@@ -15099,7 +15086,7 @@
       </c>
     </row>
     <row r="467" hidden="1" spans="1:7">
-      <c r="A467" s="3" t="s">
+      <c r="A467" s="2" t="s">
         <v>803</v>
       </c>
       <c r="B467" t="s">
@@ -16547,7 +16534,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="530" hidden="1" spans="1:7">
+    <row r="530" spans="1:7">
       <c r="A530" t="s">
         <v>902</v>
       </c>
@@ -16679,7 +16666,7 @@
         <v>36</v>
       </c>
       <c r="F535" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G535" t="s">
         <v>424</v>
@@ -16687,10 +16674,10 @@
     </row>
     <row r="536" hidden="1" spans="1:7">
       <c r="A536" t="s">
+        <v>922</v>
+      </c>
+      <c r="B536" t="s">
         <v>923</v>
-      </c>
-      <c r="B536" t="s">
-        <v>924</v>
       </c>
       <c r="C536" t="s">
         <v>248</v>
@@ -16702,7 +16689,7 @@
         <v>36</v>
       </c>
       <c r="F536" t="s">
-        <v>925</v>
+        <v>386</v>
       </c>
       <c r="G536" t="s">
         <v>424</v>
@@ -16710,10 +16697,10 @@
     </row>
     <row r="537" hidden="1" spans="1:7">
       <c r="A537" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B537" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C537" t="s">
         <v>248</v>
@@ -16725,7 +16712,7 @@
         <v>36</v>
       </c>
       <c r="F537" t="s">
-        <v>927</v>
+        <v>386</v>
       </c>
       <c r="G537" t="s">
         <v>424</v>
@@ -16733,10 +16720,10 @@
     </row>
     <row r="538" hidden="1" spans="1:7">
       <c r="A538" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B538" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="C538" t="s">
         <v>643</v>
@@ -16754,12 +16741,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="539" spans="1:7">
+    <row r="539" hidden="1" spans="1:7">
       <c r="A539" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B539" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C539" t="s">
         <v>379</v>
@@ -16771,18 +16758,18 @@
         <v>41</v>
       </c>
       <c r="F539" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="G539" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="540" spans="1:7">
+    <row r="540" hidden="1" spans="1:7">
       <c r="A540" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="B540" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C540" t="s">
         <v>379</v>
@@ -16794,7 +16781,7 @@
         <v>41</v>
       </c>
       <c r="F540" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="G540" t="s">
         <v>381</v>
@@ -16802,10 +16789,10 @@
     </row>
     <row r="541" hidden="1" spans="1:7">
       <c r="A541" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B541" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C541" t="s">
         <v>643</v>
@@ -16825,13 +16812,13 @@
     </row>
     <row r="542" hidden="1" spans="1:7">
       <c r="A542" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B542" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C542" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D542" t="s">
         <v>40</v>
@@ -16840,7 +16827,7 @@
         <v>11</v>
       </c>
       <c r="F542" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="G542" t="s">
         <v>43</v>
@@ -16848,10 +16835,10 @@
     </row>
     <row r="543" hidden="1" spans="1:7">
       <c r="A543" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B543" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="C543" t="s">
         <v>745</v>
@@ -16869,12 +16856,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="544" spans="1:7">
+    <row r="544" hidden="1" spans="1:7">
       <c r="A544" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="B544" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="C544" t="s">
         <v>724</v>
@@ -16886,18 +16873,18 @@
         <v>56</v>
       </c>
       <c r="F544" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="G544" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="545" spans="1:7">
+    <row r="545" hidden="1" spans="1:7">
       <c r="A545" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B545" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="C545" t="s">
         <v>724</v>
@@ -16909,7 +16896,7 @@
         <v>56</v>
       </c>
       <c r="F545" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="G545" t="s">
         <v>381</v>
@@ -16917,10 +16904,10 @@
     </row>
     <row r="546" hidden="1" spans="1:7">
       <c r="A546" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B546" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C546" t="s">
         <v>707</v>
@@ -16940,13 +16927,13 @@
     </row>
     <row r="547" hidden="1" spans="1:7">
       <c r="A547" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B547" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C547" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D547" t="s">
         <v>44</v>
@@ -16955,7 +16942,7 @@
         <v>11</v>
       </c>
       <c r="F547" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="G547" t="s">
         <v>43</v>
@@ -16963,10 +16950,10 @@
     </row>
     <row r="548" hidden="1" spans="1:7">
       <c r="A548" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="B548" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="C548" t="s">
         <v>674</v>
@@ -16984,12 +16971,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="549" spans="1:7">
+    <row r="549" hidden="1" spans="1:7">
       <c r="A549" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B549" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="C549" t="s">
         <v>707</v>
@@ -17001,21 +16988,21 @@
         <v>36</v>
       </c>
       <c r="F549" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="G549" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="550" spans="1:7">
+    <row r="550" hidden="1" spans="1:7">
       <c r="A550" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="B550" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="C550" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="D550" t="s">
         <v>23</v>
@@ -17024,7 +17011,7 @@
         <v>36</v>
       </c>
       <c r="F550" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="G550" t="s">
         <v>381</v>
@@ -17032,10 +17019,10 @@
     </row>
     <row r="551" hidden="1" spans="1:7">
       <c r="A551" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B551" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C551" t="s">
         <v>323</v>
@@ -17053,47 +17040,47 @@
         <v>381</v>
       </c>
     </row>
-    <row r="552" spans="1:7">
+    <row r="552" hidden="1" spans="1:7">
       <c r="A552" t="s">
         <v>953</v>
       </c>
       <c r="B552" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="C552" t="s">
-        <v>707</v>
+        <v>950</v>
       </c>
       <c r="D552" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E552" t="s">
         <v>36</v>
       </c>
       <c r="F552" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="G552" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="553" spans="1:7">
+    <row r="553" hidden="1" spans="1:7">
       <c r="A553" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B553" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="C553" t="s">
-        <v>954</v>
+        <v>707</v>
       </c>
       <c r="D553" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E553" t="s">
         <v>36</v>
       </c>
       <c r="F553" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="G553" t="s">
         <v>381</v>
@@ -17101,10 +17088,10 @@
     </row>
     <row r="554" hidden="1" spans="1:7">
       <c r="A554" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B554" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C554" t="s">
         <v>379</v>
@@ -17124,13 +17111,13 @@
     </row>
     <row r="555" hidden="1" spans="1:7">
       <c r="A555" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B555" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C555" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D555" t="s">
         <v>53</v>
@@ -17139,18 +17126,18 @@
         <v>11</v>
       </c>
       <c r="F555" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="G555" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="556" spans="1:7">
+    <row r="556" hidden="1" spans="1:7">
       <c r="A556" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B556" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="C556" t="s">
         <v>643</v>
@@ -17162,18 +17149,18 @@
         <v>11</v>
       </c>
       <c r="F556" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="G556" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="557" spans="1:7">
+    <row r="557" hidden="1" spans="1:7">
       <c r="A557" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B557" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="C557" t="s">
         <v>643</v>
@@ -17185,53 +17172,53 @@
         <v>11</v>
       </c>
       <c r="F557" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="G557" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="558" spans="1:7">
+    <row r="558" hidden="1" spans="1:7">
       <c r="A558" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B558" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C558" t="s">
         <v>615</v>
       </c>
       <c r="D558" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E558" t="s">
         <v>41</v>
       </c>
       <c r="F558" t="s">
-        <v>932</v>
+        <v>963</v>
       </c>
       <c r="G558" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="559" spans="1:7">
+    <row r="559" hidden="1" spans="1:7">
       <c r="A559" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B559" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C559" t="s">
         <v>615</v>
       </c>
       <c r="D559" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E559" t="s">
         <v>41</v>
       </c>
       <c r="F559" t="s">
-        <v>932</v>
+        <v>963</v>
       </c>
       <c r="G559" t="s">
         <v>381</v>
@@ -17242,7 +17229,7 @@
         <v>808</v>
       </c>
       <c r="B560" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C560" t="s">
         <v>555</v>
@@ -17262,10 +17249,10 @@
     </row>
     <row r="561" hidden="1" spans="1:7">
       <c r="A561" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B561" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C561" t="s">
         <v>724</v>
@@ -17288,7 +17275,7 @@
         <v>808</v>
       </c>
       <c r="B562" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C562" t="s">
         <v>555</v>
@@ -17308,10 +17295,10 @@
     </row>
     <row r="563" hidden="1" spans="1:7">
       <c r="A563" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B563" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C563" t="s">
         <v>360</v>
@@ -17323,7 +17310,7 @@
         <v>11</v>
       </c>
       <c r="F563" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G563" t="s">
         <v>416</v>
@@ -17331,10 +17318,10 @@
     </row>
     <row r="564" hidden="1" spans="1:7">
       <c r="A564" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B564" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C564" t="s">
         <v>360</v>
@@ -17357,7 +17344,7 @@
         <v>334</v>
       </c>
       <c r="B565" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C565" t="s">
         <v>248</v>
@@ -17377,13 +17364,13 @@
     </row>
     <row r="566" hidden="1" spans="1:7">
       <c r="A566" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B566" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C566" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D566" t="s">
         <v>65</v>
@@ -17392,7 +17379,7 @@
         <v>11</v>
       </c>
       <c r="F566" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="G566" t="s">
         <v>43</v>
@@ -17403,7 +17390,7 @@
         <v>825</v>
       </c>
       <c r="B567" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C567" t="s">
         <v>745</v>
@@ -17426,7 +17413,7 @@
         <v>837</v>
       </c>
       <c r="B568" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C568" t="s">
         <v>674</v>
@@ -17446,10 +17433,10 @@
     </row>
     <row r="569" hidden="1" spans="1:7">
       <c r="A569" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B569" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C569" t="s">
         <v>264</v>
@@ -17469,13 +17456,13 @@
     </row>
     <row r="570" hidden="1" spans="1:7">
       <c r="A570" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B570" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C570" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D570" t="s">
         <v>40</v>
@@ -17492,10 +17479,10 @@
     </row>
     <row r="571" hidden="1" spans="1:7">
       <c r="A571" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B571" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C571" t="s">
         <v>745</v>
@@ -17507,7 +17494,7 @@
         <v>41</v>
       </c>
       <c r="F571" t="s">
-        <v>927</v>
+        <v>386</v>
       </c>
       <c r="G571" t="s">
         <v>416</v>
@@ -17515,10 +17502,10 @@
     </row>
     <row r="572" hidden="1" spans="1:7">
       <c r="A572" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B572" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C572" t="s">
         <v>248</v>
@@ -17530,7 +17517,7 @@
         <v>41</v>
       </c>
       <c r="F572" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="G572" t="s">
         <v>416</v>
@@ -17538,10 +17525,10 @@
     </row>
     <row r="573" hidden="1" spans="1:7">
       <c r="A573" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B573" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C573" t="s">
         <v>745</v>
@@ -17553,7 +17540,7 @@
         <v>41</v>
       </c>
       <c r="F573" t="s">
-        <v>925</v>
+        <v>984</v>
       </c>
       <c r="G573" t="s">
         <v>416</v>
@@ -17561,10 +17548,10 @@
     </row>
     <row r="574" hidden="1" spans="1:7">
       <c r="A574" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B574" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C574" t="s">
         <v>248</v>
@@ -17576,7 +17563,7 @@
         <v>41</v>
       </c>
       <c r="F574" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="G574" t="s">
         <v>416</v>
@@ -17584,13 +17571,13 @@
     </row>
     <row r="575" hidden="1" spans="1:7">
       <c r="A575" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B575" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C575" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D575" t="s">
         <v>44</v>
@@ -17607,10 +17594,10 @@
     </row>
     <row r="576" hidden="1" spans="1:7">
       <c r="A576" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B576" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C576" t="s">
         <v>346</v>
@@ -17630,13 +17617,13 @@
     </row>
     <row r="577" hidden="1" spans="1:7">
       <c r="A577" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B577" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C577" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D577" t="s">
         <v>53</v>
@@ -17645,7 +17632,7 @@
         <v>27</v>
       </c>
       <c r="F577" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G577" t="s">
         <v>43</v>
@@ -17653,10 +17640,10 @@
     </row>
     <row r="578" hidden="1" spans="1:7">
       <c r="A578" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B578" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C578" t="s">
         <v>349</v>
@@ -17679,7 +17666,7 @@
         <v>387</v>
       </c>
       <c r="B579" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C579" t="s">
         <v>165</v>
@@ -17699,10 +17686,10 @@
     </row>
     <row r="580" hidden="1" spans="1:7">
       <c r="A580" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B580" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C580" t="s">
         <v>264</v>
@@ -17722,13 +17709,13 @@
     </row>
     <row r="581" hidden="1" spans="1:7">
       <c r="A581" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B581" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C581" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D581" t="s">
         <v>65</v>
@@ -17737,7 +17724,7 @@
         <v>27</v>
       </c>
       <c r="F581" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G581" t="s">
         <v>43</v>
@@ -17745,10 +17732,10 @@
     </row>
     <row r="582" hidden="1" spans="1:7">
       <c r="A582" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B582" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C582" t="s">
         <v>338</v>
@@ -17760,7 +17747,7 @@
         <v>11</v>
       </c>
       <c r="F582" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G582" t="s">
         <v>254</v>
@@ -17768,10 +17755,10 @@
     </row>
     <row r="583" hidden="1" spans="1:7">
       <c r="A583" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B583" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C583" t="s">
         <v>51</v>
@@ -17791,10 +17778,10 @@
     </row>
     <row r="584" hidden="1" spans="1:7">
       <c r="A584" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B584" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C584" t="s">
         <v>51</v>
@@ -17814,10 +17801,10 @@
     </row>
     <row r="585" hidden="1" spans="1:7">
       <c r="A585" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B585" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C585" t="s">
         <v>419</v>
@@ -17829,7 +17816,7 @@
         <v>56</v>
       </c>
       <c r="F585" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G585" t="s">
         <v>43</v>
@@ -17837,10 +17824,10 @@
     </row>
     <row r="586" hidden="1" spans="1:7">
       <c r="A586" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B586" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C586" t="s">
         <v>419</v>
@@ -17852,7 +17839,7 @@
         <v>56</v>
       </c>
       <c r="F586" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G586" t="s">
         <v>43</v>
@@ -17860,10 +17847,10 @@
     </row>
     <row r="587" hidden="1" spans="1:7">
       <c r="A587" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B587" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C587" t="s">
         <v>51</v>
@@ -17875,7 +17862,7 @@
         <v>36</v>
       </c>
       <c r="F587" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="G587" t="s">
         <v>43</v>
@@ -17883,10 +17870,10 @@
     </row>
     <row r="588" hidden="1" spans="1:7">
       <c r="A588" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B588" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C588" t="s">
         <v>51</v>
@@ -17909,7 +17896,7 @@
         <v>103</v>
       </c>
       <c r="B589" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C589" t="s">
         <v>69</v>
@@ -17921,7 +17908,7 @@
         <v>11</v>
       </c>
       <c r="F589" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="G589" t="s">
         <v>254</v>
@@ -17929,10 +17916,10 @@
     </row>
     <row r="590" hidden="1" spans="1:7">
       <c r="A590" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B590" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C590" t="s">
         <v>51</v>
@@ -17944,7 +17931,7 @@
         <v>36</v>
       </c>
       <c r="F590" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G590" t="s">
         <v>43</v>
@@ -17952,10 +17939,10 @@
     </row>
     <row r="591" hidden="1" spans="1:7">
       <c r="A591" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B591" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C591" t="s">
         <v>51</v>
@@ -17967,7 +17954,7 @@
         <v>36</v>
       </c>
       <c r="F591" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="G591" t="s">
         <v>43</v>
@@ -17975,13 +17962,13 @@
     </row>
     <row r="592" hidden="1" spans="1:7">
       <c r="A592" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C592" t="s">
         <v>1004</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1006</v>
       </c>
       <c r="D592" t="s">
         <v>10</v>
@@ -17990,7 +17977,7 @@
         <v>27</v>
       </c>
       <c r="F592" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G592" t="s">
         <v>254</v>
@@ -17998,10 +17985,10 @@
     </row>
     <row r="593" hidden="1" spans="1:7">
       <c r="A593" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B593" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C593" t="s">
         <v>219</v>
@@ -18013,7 +18000,7 @@
         <v>27</v>
       </c>
       <c r="F593" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G593" t="s">
         <v>254</v>
@@ -18021,13 +18008,13 @@
     </row>
     <row r="594" hidden="1" spans="1:7">
       <c r="A594" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C594" t="s">
         <v>1004</v>
-      </c>
-      <c r="B594" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1006</v>
       </c>
       <c r="D594" t="s">
         <v>14</v>
@@ -18036,7 +18023,7 @@
         <v>27</v>
       </c>
       <c r="F594" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G594" t="s">
         <v>254</v>
@@ -18044,10 +18031,10 @@
     </row>
     <row r="595" hidden="1" spans="1:7">
       <c r="A595" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B595" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C595" t="s">
         <v>219</v>
@@ -18059,7 +18046,7 @@
         <v>27</v>
       </c>
       <c r="F595" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G595" t="s">
         <v>254</v>
@@ -18067,10 +18054,10 @@
     </row>
     <row r="596" hidden="1" spans="1:7">
       <c r="A596" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B596" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C596" t="s">
         <v>22</v>
@@ -18082,7 +18069,7 @@
         <v>27</v>
       </c>
       <c r="F596" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G596" t="s">
         <v>254</v>
@@ -18093,10 +18080,10 @@
         <v>117</v>
       </c>
       <c r="B597" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C597" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D597" t="s">
         <v>18</v>
@@ -18105,7 +18092,7 @@
         <v>27</v>
       </c>
       <c r="F597" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G597" t="s">
         <v>254</v>
@@ -18113,10 +18100,10 @@
     </row>
     <row r="598" hidden="1" spans="1:7">
       <c r="A598" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B598" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C598" t="s">
         <v>22</v>
@@ -18128,7 +18115,7 @@
         <v>27</v>
       </c>
       <c r="F598" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G598" t="s">
         <v>254</v>
@@ -18136,13 +18123,13 @@
     </row>
     <row r="599" hidden="1" spans="1:7">
       <c r="A599" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C599" t="s">
         <v>1004</v>
-      </c>
-      <c r="B599" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1006</v>
       </c>
       <c r="D599" t="s">
         <v>25</v>
@@ -18151,7 +18138,7 @@
         <v>27</v>
       </c>
       <c r="F599" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G599" t="s">
         <v>254</v>
@@ -18159,13 +18146,13 @@
     </row>
     <row r="600" hidden="1" spans="1:7">
       <c r="A600" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B600" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C600" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D600" t="s">
         <v>25</v>
@@ -18174,7 +18161,7 @@
         <v>27</v>
       </c>
       <c r="F600" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="G600" t="s">
         <v>254</v>
@@ -18182,10 +18169,10 @@
     </row>
     <row r="601" hidden="1" spans="1:7">
       <c r="A601" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B601" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C601" t="s">
         <v>22</v>
@@ -18197,7 +18184,7 @@
         <v>27</v>
       </c>
       <c r="F601" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G601" t="s">
         <v>254</v>
@@ -18205,13 +18192,13 @@
     </row>
     <row r="602" hidden="1" spans="1:7">
       <c r="A602" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C602" t="s">
         <v>1004</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1006</v>
       </c>
       <c r="D602" t="s">
         <v>26</v>
@@ -18220,7 +18207,7 @@
         <v>27</v>
       </c>
       <c r="F602" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G602" t="s">
         <v>254</v>
@@ -18228,13 +18215,13 @@
     </row>
     <row r="603" hidden="1" spans="1:7">
       <c r="A603" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B603" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C603" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D603" t="s">
         <v>26</v>
@@ -18243,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="F603" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G603" t="s">
         <v>254</v>
@@ -18251,10 +18238,10 @@
     </row>
     <row r="604" hidden="1" spans="1:7">
       <c r="A604" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B604" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C604" t="s">
         <v>22</v>
@@ -18266,7 +18253,7 @@
         <v>27</v>
       </c>
       <c r="F604" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G604" t="s">
         <v>254</v>
@@ -18274,10 +18261,10 @@
     </row>
     <row r="605" hidden="1" spans="1:7">
       <c r="A605" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B605" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C605" t="s">
         <v>349</v>
@@ -18289,7 +18276,7 @@
         <v>41</v>
       </c>
       <c r="F605" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G605" t="s">
         <v>254</v>
@@ -18297,10 +18284,10 @@
     </row>
     <row r="606" hidden="1" spans="1:7">
       <c r="A606" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B606" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C606" t="s">
         <v>615</v>
@@ -18320,13 +18307,13 @@
     </row>
     <row r="607" hidden="1" spans="1:7">
       <c r="A607" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B607" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C607" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D607" t="s">
         <v>18</v>
@@ -18335,7 +18322,7 @@
         <v>41</v>
       </c>
       <c r="F607" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G607" t="s">
         <v>254</v>
@@ -18343,10 +18330,10 @@
     </row>
     <row r="608" hidden="1" spans="1:7">
       <c r="A608" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B608" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C608" t="s">
         <v>22</v>
@@ -18358,7 +18345,7 @@
         <v>41</v>
       </c>
       <c r="F608" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G608" t="s">
         <v>254</v>
@@ -18366,10 +18353,10 @@
     </row>
     <row r="609" hidden="1" spans="1:7">
       <c r="A609" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B609" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C609" t="s">
         <v>243</v>
@@ -18381,7 +18368,7 @@
         <v>41</v>
       </c>
       <c r="F609" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G609" t="s">
         <v>449</v>
@@ -18389,13 +18376,13 @@
     </row>
     <row r="610" hidden="1" spans="1:7">
       <c r="A610" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B610" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C610" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D610" t="s">
         <v>23</v>
@@ -18404,7 +18391,7 @@
         <v>41</v>
       </c>
       <c r="F610" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G610" t="s">
         <v>254</v>
@@ -18412,10 +18399,10 @@
     </row>
     <row r="611" hidden="1" spans="1:7">
       <c r="A611" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B611" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C611" t="s">
         <v>22</v>
@@ -18427,7 +18414,7 @@
         <v>41</v>
       </c>
       <c r="F611" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G611" t="s">
         <v>254</v>
@@ -18435,10 +18422,10 @@
     </row>
     <row r="612" hidden="1" spans="1:7">
       <c r="A612" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B612" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C612" t="s">
         <v>310</v>
@@ -18450,7 +18437,7 @@
         <v>41</v>
       </c>
       <c r="F612" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="G612" t="s">
         <v>449</v>
@@ -18461,7 +18448,7 @@
         <v>109</v>
       </c>
       <c r="B613" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C613" t="s">
         <v>295</v>
@@ -18473,7 +18460,7 @@
         <v>41</v>
       </c>
       <c r="F613" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G613" t="s">
         <v>254</v>
@@ -18481,10 +18468,10 @@
     </row>
     <row r="614" hidden="1" spans="1:7">
       <c r="A614" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B614" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C614" t="s">
         <v>143</v>
@@ -18504,10 +18491,10 @@
     </row>
     <row r="615" hidden="1" spans="1:7">
       <c r="A615" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B615" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C615" t="s">
         <v>143</v>
@@ -18527,10 +18514,10 @@
     </row>
     <row r="616" hidden="1" spans="1:7">
       <c r="A616" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B616" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C616" t="s">
         <v>219</v>
@@ -18550,10 +18537,10 @@
     </row>
     <row r="617" hidden="1" spans="1:7">
       <c r="A617" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B617" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C617" t="s">
         <v>588</v>
@@ -18565,7 +18552,7 @@
         <v>56</v>
       </c>
       <c r="F617" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G617" t="s">
         <v>254</v>
@@ -18573,10 +18560,10 @@
     </row>
     <row r="618" hidden="1" spans="1:7">
       <c r="A618" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B618" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C618" t="s">
         <v>219</v>
@@ -18599,10 +18586,10 @@
         <v>81</v>
       </c>
       <c r="B619" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C619" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="D619" t="s">
         <v>18</v>
@@ -18611,7 +18598,7 @@
         <v>56</v>
       </c>
       <c r="F619" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G619" t="s">
         <v>254</v>
@@ -18619,10 +18606,10 @@
     </row>
     <row r="620" hidden="1" spans="1:7">
       <c r="A620" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B620" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C620" t="s">
         <v>290</v>
@@ -18642,10 +18629,10 @@
     </row>
     <row r="621" hidden="1" spans="1:7">
       <c r="A621" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B621" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C621" t="s">
         <v>298</v>
@@ -18665,10 +18652,10 @@
     </row>
     <row r="622" hidden="1" spans="1:7">
       <c r="A622" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B622" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C622" t="s">
         <v>298</v>
@@ -18691,10 +18678,10 @@
         <v>81</v>
       </c>
       <c r="B623" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C623" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="D623" t="s">
         <v>23</v>
@@ -18703,18 +18690,18 @@
         <v>56</v>
       </c>
       <c r="F623" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G623" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="624" hidden="1" spans="1:7">
+    <row r="624" spans="1:7">
       <c r="A624" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B624" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C624" t="s">
         <v>346</v>
@@ -18737,10 +18724,10 @@
         <v>584</v>
       </c>
       <c r="B625" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C625" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D625" t="s">
         <v>25</v>
@@ -18749,7 +18736,7 @@
         <v>56</v>
       </c>
       <c r="F625" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G625" t="s">
         <v>254</v>
@@ -18760,7 +18747,7 @@
         <v>74</v>
       </c>
       <c r="B626" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C626" t="s">
         <v>59</v>
@@ -18772,7 +18759,7 @@
         <v>56</v>
       </c>
       <c r="F626" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G626" t="s">
         <v>254</v>
@@ -18783,10 +18770,10 @@
         <v>117</v>
       </c>
       <c r="B627" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C627" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D627" t="s">
         <v>10</v>
@@ -18795,7 +18782,7 @@
         <v>36</v>
       </c>
       <c r="F627" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G627" t="s">
         <v>254</v>
@@ -18803,10 +18790,10 @@
     </row>
     <row r="628" hidden="1" spans="1:7">
       <c r="A628" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B628" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C628" t="s">
         <v>346</v>
@@ -18829,10 +18816,10 @@
         <v>117</v>
       </c>
       <c r="B629" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C629" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D629" t="s">
         <v>14</v>
@@ -18841,7 +18828,7 @@
         <v>36</v>
       </c>
       <c r="F629" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="G629" t="s">
         <v>254</v>
@@ -18852,10 +18839,10 @@
         <v>117</v>
       </c>
       <c r="B630" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C630" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D630" t="s">
         <v>14</v>
@@ -18864,7 +18851,7 @@
         <v>36</v>
       </c>
       <c r="F630" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G630" t="s">
         <v>254</v>
@@ -18875,10 +18862,10 @@
         <v>117</v>
       </c>
       <c r="B631" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C631" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D631" t="s">
         <v>18</v>
@@ -18887,7 +18874,7 @@
         <v>36</v>
       </c>
       <c r="F631" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G631" t="s">
         <v>254</v>
@@ -18895,10 +18882,10 @@
     </row>
     <row r="632" hidden="1" spans="1:7">
       <c r="A632" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B632" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C632" t="s">
         <v>327</v>
@@ -18918,10 +18905,10 @@
     </row>
     <row r="633" hidden="1" spans="1:7">
       <c r="A633" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B633" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C633" t="s">
         <v>839</v>
@@ -18941,13 +18928,13 @@
     </row>
     <row r="634" hidden="1" spans="1:7">
       <c r="A634" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C634" t="s">
         <v>1066</v>
-      </c>
-      <c r="B634" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1068</v>
       </c>
       <c r="D634" t="s">
         <v>23</v>
@@ -18964,13 +18951,13 @@
     </row>
     <row r="635" hidden="1" spans="1:7">
       <c r="A635" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B635" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C635" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D635" t="s">
         <v>26</v>
@@ -18979,7 +18966,7 @@
         <v>41</v>
       </c>
       <c r="F635" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G635" t="s">
         <v>449</v>
@@ -18987,10 +18974,10 @@
     </row>
     <row r="636" hidden="1" spans="1:7">
       <c r="A636" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B636" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C636" t="s">
         <v>493</v>
@@ -19002,7 +18989,7 @@
         <v>36</v>
       </c>
       <c r="F636" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G636" t="s">
         <v>254</v>
@@ -19010,10 +18997,10 @@
     </row>
     <row r="637" hidden="1" spans="1:7">
       <c r="A637" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B637" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C637" t="s">
         <v>816</v>
@@ -19033,13 +19020,13 @@
     </row>
     <row r="638" hidden="1" spans="1:7">
       <c r="A638" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B638" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C638" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D638" t="s">
         <v>18</v>
@@ -19056,13 +19043,13 @@
     </row>
     <row r="639" hidden="1" spans="1:7">
       <c r="A639" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B639" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C639" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D639" t="s">
         <v>23</v>
@@ -19082,7 +19069,7 @@
         <v>633</v>
       </c>
       <c r="B640" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C640" t="s">
         <v>143</v>
@@ -19102,13 +19089,13 @@
     </row>
     <row r="641" hidden="1" spans="1:7">
       <c r="A641" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B641" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C641" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D641" t="s">
         <v>10</v>
@@ -19117,7 +19104,7 @@
         <v>41</v>
       </c>
       <c r="F641" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G641" t="s">
         <v>449</v>
@@ -19128,7 +19115,7 @@
         <v>20</v>
       </c>
       <c r="B642" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C642" t="s">
         <v>22</v>
@@ -19151,7 +19138,7 @@
         <v>20</v>
       </c>
       <c r="B643" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C643" t="s">
         <v>22</v>
@@ -19174,7 +19161,7 @@
         <v>20</v>
       </c>
       <c r="B644" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C644" t="s">
         <v>22</v>
@@ -19194,10 +19181,10 @@
     </row>
     <row r="645" hidden="1" spans="1:7">
       <c r="A645" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B645" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C645" t="s">
         <v>638</v>
@@ -19220,7 +19207,7 @@
         <v>20</v>
       </c>
       <c r="B646" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C646" t="s">
         <v>22</v>
@@ -19240,10 +19227,10 @@
     </row>
     <row r="647" hidden="1" spans="1:7">
       <c r="A647" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B647" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C647" t="s">
         <v>168</v>
@@ -19263,10 +19250,10 @@
     </row>
     <row r="648" hidden="1" spans="1:7">
       <c r="A648" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B648" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C648" t="s">
         <v>143</v>
@@ -19278,7 +19265,7 @@
         <v>41</v>
       </c>
       <c r="F648" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="G648" t="s">
         <v>454</v>
@@ -19286,10 +19273,10 @@
     </row>
     <row r="649" hidden="1" spans="1:7">
       <c r="A649" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B649" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C649" t="s">
         <v>143</v>
@@ -19301,7 +19288,7 @@
         <v>41</v>
       </c>
       <c r="F649" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="G649" t="s">
         <v>454</v>
@@ -19309,10 +19296,10 @@
     </row>
     <row r="650" hidden="1" spans="1:7">
       <c r="A650" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B650" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C650" t="s">
         <v>213</v>
@@ -19335,7 +19322,7 @@
         <v>163</v>
       </c>
       <c r="B651" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C651" t="s">
         <v>165</v>
@@ -19355,13 +19342,13 @@
     </row>
     <row r="652" hidden="1" spans="1:7">
       <c r="A652" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B652" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C652" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D652" t="s">
         <v>18</v>
@@ -19370,7 +19357,7 @@
         <v>41</v>
       </c>
       <c r="F652" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="G652" t="s">
         <v>449</v>
@@ -19381,7 +19368,7 @@
         <v>627</v>
       </c>
       <c r="B653" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C653" t="s">
         <v>582</v>
@@ -19393,7 +19380,7 @@
         <v>56</v>
       </c>
       <c r="F653" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G653" t="s">
         <v>454</v>
@@ -19401,10 +19388,10 @@
     </row>
     <row r="654" hidden="1" spans="1:7">
       <c r="A654" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B654" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C654" t="s">
         <v>213</v>
@@ -19416,7 +19403,7 @@
         <v>56</v>
       </c>
       <c r="F654" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="G654" t="s">
         <v>454</v>
@@ -19427,7 +19414,7 @@
         <v>627</v>
       </c>
       <c r="B655" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C655" t="s">
         <v>582</v>
@@ -19439,7 +19426,7 @@
         <v>56</v>
       </c>
       <c r="F655" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G655" t="s">
         <v>454</v>
@@ -19447,10 +19434,10 @@
     </row>
     <row r="656" hidden="1" spans="1:7">
       <c r="A656" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B656" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C656" t="s">
         <v>213</v>
@@ -19462,7 +19449,7 @@
         <v>56</v>
       </c>
       <c r="F656" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="G656" t="s">
         <v>454</v>
@@ -19470,13 +19457,13 @@
     </row>
     <row r="657" hidden="1" spans="1:7">
       <c r="A657" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B657" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C657" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D657" t="s">
         <v>23</v>
@@ -19493,10 +19480,10 @@
     </row>
     <row r="658" hidden="1" spans="1:7">
       <c r="A658" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B658" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C658" t="s">
         <v>327</v>
@@ -19519,7 +19506,7 @@
         <v>155</v>
       </c>
       <c r="B659" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C659" t="s">
         <v>157</v>
@@ -19531,7 +19518,7 @@
         <v>36</v>
       </c>
       <c r="F659" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="G659" t="s">
         <v>454</v>
@@ -19542,7 +19529,7 @@
         <v>617</v>
       </c>
       <c r="B660" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C660" t="s">
         <v>327</v>
@@ -19554,7 +19541,7 @@
         <v>36</v>
       </c>
       <c r="F660" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G660" t="s">
         <v>454</v>
@@ -19565,7 +19552,7 @@
         <v>20</v>
       </c>
       <c r="B661" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C661" t="s">
         <v>22</v>
@@ -19588,7 +19575,7 @@
         <v>20</v>
       </c>
       <c r="B662" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C662" t="s">
         <v>22</v>
@@ -19608,10 +19595,10 @@
     </row>
     <row r="663" hidden="1" spans="1:7">
       <c r="A663" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B663" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C663" t="s">
         <v>327</v>
@@ -19634,7 +19621,7 @@
         <v>155</v>
       </c>
       <c r="B664" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C664" t="s">
         <v>157</v>
@@ -19646,7 +19633,7 @@
         <v>36</v>
       </c>
       <c r="F664" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="G664" t="s">
         <v>454</v>
@@ -19657,7 +19644,7 @@
         <v>617</v>
       </c>
       <c r="B665" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C665" t="s">
         <v>327</v>
@@ -19669,7 +19656,7 @@
         <v>36</v>
       </c>
       <c r="F665" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G665" t="s">
         <v>454</v>
@@ -19680,7 +19667,7 @@
         <v>109</v>
       </c>
       <c r="B666" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C666" t="s">
         <v>295</v>
@@ -19703,7 +19690,7 @@
         <v>803</v>
       </c>
       <c r="B667" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C667" t="s">
         <v>724</v>
@@ -19726,7 +19713,7 @@
         <v>803</v>
       </c>
       <c r="B668" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C668" t="s">
         <v>724</v>
@@ -19746,7 +19733,7 @@
     </row>
     <row r="669" hidden="1" spans="1:7">
       <c r="A669" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B669" t="s">
         <v>764</v>
@@ -19772,7 +19759,7 @@
         <v>803</v>
       </c>
       <c r="B670" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C670" t="s">
         <v>17</v>
@@ -19791,19 +19778,19 @@
       </c>
     </row>
     <row r="671" hidden="1" spans="1:7">
-      <c r="A671" s="4" t="s">
+      <c r="A671" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="B671" s="4" t="s">
+      <c r="B671" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="C671" s="4" t="s">
+      <c r="C671" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="D671" s="4" t="s">
+      <c r="D671" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E671" s="4" t="s">
+      <c r="E671" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F671" t="s">
@@ -19815,10 +19802,10 @@
     </row>
     <row r="672" hidden="1" spans="1:7">
       <c r="A672" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B672" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="C672" t="s">
         <v>189</v>
@@ -19841,7 +19828,7 @@
         <v>678</v>
       </c>
       <c r="B673" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C673" t="s">
         <v>50</v>
@@ -19863,19 +19850,16 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G673" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="TP-conception assistée par ordinateur des machines électriques TP G1"/>
-        <filter val="TP-Identifiation et diagnostique des machines électriques TP G1"/>
-        <filter val="TP-Machines électriques spéciales TP G1"/>
-        <filter val="TP-conception assistée par ordinateur des machines électriques TP G2"/>
-        <filter val="TP-Identifiation et diagnostique des machines électriques TP G2"/>
-        <filter val="TP-Machines électriques spéciales TP G2"/>
-        <filter val="TP-Régime transitoire des machines électriques TP 1/15"/>
-        <filter val="TP-Commande des machines électriques TP 1/15"/>
+        <filter val="TD-Intégration des ressoures renouvelables aux réseaux électriques"/>
+        <filter val="TD-Conduite des réseaux électriques"/>
+        <filter val="TD-Stabilité et dynamique des réseaux électriques"/>
+        <filter val="TD-Dimensionnement des Réseaux électriques industriels"/>
+        <filter val="TD-Technique de la haute tension"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="M2ME"/>
+        <filter val="M2RE"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:G673">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -4555,10 +4555,10 @@
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -4785,7 +4785,7 @@
         <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
         <v>22</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -1928,7 +1928,7 @@
     <t>TP-S &amp; A-3ELT</t>
   </si>
   <si>
-    <t>BENTAALLAH ABDERRAHIM + BENDAOUD ABDELBER</t>
+    <t>BENTAALLAH ABDERRAHIM</t>
   </si>
   <si>
     <t>Labo Shémas SG21 &amp; SG11/SG12</t>
@@ -4498,7 +4498,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" hidden="1" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" hidden="1" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" hidden="1" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" hidden="1" spans="1:7">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" hidden="1" spans="1:7">
       <c r="A27" s="2" t="s">
         <v>64</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" hidden="1" spans="1:7">
       <c r="A28" s="2" t="s">
         <v>71</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" hidden="1" spans="1:7">
       <c r="A29" s="2" t="s">
         <v>73</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" hidden="1" spans="1:7">
       <c r="A30" s="2" t="s">
         <v>74</v>
       </c>
@@ -8845,7 +8845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" hidden="1" spans="1:7">
       <c r="A196" t="s">
         <v>422</v>
       </c>
@@ -9696,7 +9696,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" hidden="1" spans="1:7">
       <c r="A233" t="s">
         <v>515</v>
       </c>
@@ -10593,7 +10593,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" hidden="1" spans="1:7">
       <c r="A272" t="s">
         <v>422</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" hidden="1" spans="1:7">
       <c r="A280" t="s">
         <v>83</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" hidden="1" spans="1:7">
       <c r="A287" t="s">
         <v>133</v>
       </c>
@@ -11053,7 +11053,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" hidden="1" spans="1:7">
       <c r="A292" t="s">
         <v>133</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="313" hidden="1" spans="1:7">
+    <row r="313" spans="1:7">
       <c r="A313" t="s">
         <v>630</v>
       </c>
@@ -11651,7 +11651,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="318" hidden="1" spans="1:7">
+    <row r="318" spans="1:7">
       <c r="A318" t="s">
         <v>630</v>
       </c>
@@ -13307,7 +13307,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390" t="s">
         <v>686</v>
       </c>
@@ -18551,7 +18551,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="618" spans="1:7">
+    <row r="618" hidden="1" spans="1:7">
       <c r="A618" t="s">
         <v>83</v>
       </c>
@@ -19521,11 +19521,10 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G659" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="ZENASNI MERIEM + MEKHALEF SOUMIA"/>
-        <filter val="ZENASNI MERIEM"/>
+        <filter val="BENTAALLAH ABDERRAHIM + BENDAOUD ABDELBER"/>
       </filters>
     </filterColumn>
-    <sortState ref="A2:G659">
+    <sortState ref="A1:G659">
       <sortCondition ref="E1"/>
     </sortState>
     <extLst/>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -2012,6 +2012,303 @@
     <t>M1RE</t>
   </si>
   <si>
+    <t>Cours-Programmation avancée en Python</t>
+  </si>
+  <si>
+    <t>Cours-PAP-M1CE</t>
+  </si>
+  <si>
+    <t>Cours-PAP-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-PAP-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-PAP-M1RE</t>
+  </si>
+  <si>
+    <t>Cours-Réseaux de transport et de distribution d'énergie électrique</t>
+  </si>
+  <si>
+    <t>Cours-RTsDEE-M1CE</t>
+  </si>
+  <si>
+    <t>Cours-RTsDEE-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-RTsDEE-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-RTsDEE-M1RE</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1CE</t>
+  </si>
+  <si>
+    <t>AS4</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1ER</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1ME</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1RE</t>
+  </si>
+  <si>
+    <t>TD-Réseaux de transport et de distribution d'énergie électrique</t>
+  </si>
+  <si>
+    <t>TD-RTsDEE-M1ME</t>
+  </si>
+  <si>
+    <t>TD-RTsDEE-RE</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques approfondies-G1</t>
+  </si>
+  <si>
+    <t>TP-MEA-RE</t>
+  </si>
+  <si>
+    <t>RAMI ABDELKADER</t>
+  </si>
+  <si>
+    <t>Salle micro 02 &amp; labo machine 02</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques approfondies-G2</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées et optimisation-G1</t>
+  </si>
+  <si>
+    <t>TP-MNAO-RE</t>
+  </si>
+  <si>
+    <t>TOUHAMI SEDDIK</t>
+  </si>
+  <si>
+    <t>Salle micro 02</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées et optimisation-G2</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance avancée-G1</t>
+  </si>
+  <si>
+    <t>TP-EPA-RE</t>
+  </si>
+  <si>
+    <t>Salle micro 01</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance avancée-G2</t>
+  </si>
+  <si>
+    <t>TP-Programmation avancée en Python-G1</t>
+  </si>
+  <si>
+    <t>TP-PAP-M1CE</t>
+  </si>
+  <si>
+    <t>TP-PAP-M1ER</t>
+  </si>
+  <si>
+    <t>M1 ER</t>
+  </si>
+  <si>
+    <t>TP-PAP-RE</t>
+  </si>
+  <si>
+    <t>TP-Programmation avancée en Python-G2</t>
+  </si>
+  <si>
+    <t>TP-μ-processeurs et μ-contrôleurs-G1</t>
+  </si>
+  <si>
+    <t>TP-μPμC-M1ER</t>
+  </si>
+  <si>
+    <t>Labo μ-processeurs</t>
+  </si>
+  <si>
+    <t>TP-μ-processeurs et μ-contrôleurs-G2</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1CE</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1RE</t>
+  </si>
+  <si>
+    <t>Cours-μ-processeurs et μ-contrôleurs</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1CE</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1RE</t>
+  </si>
+  <si>
+    <t>TD-MEA-M1CE</t>
+  </si>
+  <si>
+    <t>TD-MEA-M1ER</t>
+  </si>
+  <si>
+    <t>TD-Méthodes numériques appliquées et optimisation</t>
+  </si>
+  <si>
+    <t>TD-MNAO-M1CE</t>
+  </si>
+  <si>
+    <t>TD-MNAO-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1MCIL</t>
+  </si>
+  <si>
+    <t>M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-μPμC-M1MCIL</t>
+  </si>
+  <si>
+    <t>14h - 15h</t>
+  </si>
+  <si>
+    <t>TD-Exploitation des Réseaux électriques</t>
+  </si>
+  <si>
+    <t>TD-ERE-M1MCIL</t>
+  </si>
+  <si>
+    <t>15h - 16h</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-Exploitation des Réseaux électriques</t>
+  </si>
+  <si>
+    <t>Cours-ERE-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-Compatibilité électromagnétique</t>
+  </si>
+  <si>
+    <t>Cours-EM-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-Exploitation des Réseaux électriques-G1</t>
+  </si>
+  <si>
+    <t>TP-ERE-M1MCIL</t>
+  </si>
+  <si>
+    <t>NEMMICH SAID</t>
+  </si>
+  <si>
+    <t>TP-Exploitation des Réseaux électriques-G2</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques approfondies -G1</t>
+  </si>
+  <si>
+    <t>TP-MEA-M1MCIL</t>
+  </si>
+  <si>
+    <t>DJELLOULI YOUNES</t>
+  </si>
+  <si>
+    <t>Labo machine 1 &amp; Salle de micros 03</t>
+  </si>
+  <si>
+    <t>TD-MEA-M1MCIL</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-Technologie d'Élclairage</t>
+  </si>
+  <si>
+    <t>Cours-TE-M1MCIL</t>
+  </si>
+  <si>
+    <t>TD-Méthodes numériques appliquées</t>
+  </si>
+  <si>
+    <t>TD-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-EPA-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-EPA-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées-G2</t>
+  </si>
+  <si>
+    <t>TP-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>Salle micro 03</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées-G1</t>
+  </si>
+  <si>
+    <t>Cours-Anglais technique et terminologie</t>
+  </si>
+  <si>
+    <t>Cours-ANGTT-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-MEA-M1ME</t>
+  </si>
+  <si>
+    <t>TP-MNAO-M1CE</t>
+  </si>
+  <si>
+    <t>TP-PAP-M1ME</t>
+  </si>
+  <si>
+    <t>TP-Réseaux de transport et de distribution d'énergie électrique-G1</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-RE</t>
+  </si>
+  <si>
+    <t>TP-Réseaux de transport et de distribution d'énergie électrique-G2</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-M1RE</t>
+  </si>
+  <si>
+    <t>TP-μPμC-RE</t>
+  </si>
+  <si>
     <t>Cours-Énergies renouvelables</t>
   </si>
   <si>
@@ -2027,16 +2324,37 @@
     <t>Cours-ER-M1RE</t>
   </si>
   <si>
-    <t>Cours-MEA-M1CE</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1RE</t>
+    <t>TD-MNAO-M1ME</t>
+  </si>
+  <si>
+    <t>TD-MNAO-RE</t>
+  </si>
+  <si>
+    <t>TD-RTDEE-M1CE</t>
+  </si>
+  <si>
+    <t>TD-RTsDEE-M1ER</t>
+  </si>
+  <si>
+    <t>TP-EPA-M1ME</t>
+  </si>
+  <si>
+    <t>TP-MNAO-M1ER</t>
+  </si>
+  <si>
+    <t>TP-MNAO-M1ME</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-M1ER</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-M1ME</t>
+  </si>
+  <si>
+    <t>Labo Réseaux</t>
+  </si>
+  <si>
+    <t>TP-μPμC-M1ME</t>
   </si>
   <si>
     <t>Cours-Méthodes numériques appliquées et optimisation</t>
@@ -2051,264 +2369,24 @@
     <t>Cours-MNAO-M1ME</t>
   </si>
   <si>
-    <t>TOUHAMI SEDDIK</t>
-  </si>
-  <si>
     <t>Cours-MNAO-M1RE</t>
   </si>
   <si>
-    <t>Cours-Programmation avancée en Python</t>
-  </si>
-  <si>
-    <t>Cours-PAP-M1CE</t>
-  </si>
-  <si>
-    <t>Cours-PAP-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-PAP-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-PAP-M1RE</t>
-  </si>
-  <si>
-    <t>Cours-Réseaux de transport et de distribution d'énergie électrique</t>
-  </si>
-  <si>
-    <t>Cours-RTsDEE-M1CE</t>
-  </si>
-  <si>
-    <t>Cours-RTsDEE-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-RTsDEE-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-RTsDEE-M1RE</t>
-  </si>
-  <si>
-    <t>Cours-μ-processeurs et μ-contrôleurs</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1CE</t>
-  </si>
-  <si>
-    <t>RAMI ABDELKADER</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1RE</t>
-  </si>
-  <si>
-    <t>TD-EPA-M1CE</t>
-  </si>
-  <si>
-    <t>AS4</t>
-  </si>
-  <si>
-    <t>TD-EPA-M1ER</t>
-  </si>
-  <si>
-    <t>TD-EPA-M1ME</t>
-  </si>
-  <si>
-    <t>TD-EPA-M1RE</t>
-  </si>
-  <si>
-    <t>TD-MEA-M1CE</t>
-  </si>
-  <si>
-    <t>TD-MEA-M1ER</t>
-  </si>
-  <si>
     <t>TD-MEA-M1ME</t>
   </si>
   <si>
     <t>TD-MEA-RE</t>
   </si>
   <si>
-    <t>TD-Méthodes numériques appliquées et optimisation</t>
-  </si>
-  <si>
-    <t>TD-MNAO-M1CE</t>
-  </si>
-  <si>
-    <t>TD-MNAO-M1ER</t>
-  </si>
-  <si>
-    <t>TD-MNAO-M1ME</t>
-  </si>
-  <si>
-    <t>TD-MNAO-RE</t>
-  </si>
-  <si>
-    <t>TD-Réseaux de transport et de distribution d'énergie électrique</t>
-  </si>
-  <si>
-    <t>TD-RTDEE-M1CE</t>
-  </si>
-  <si>
-    <t>TD-RTsDEE-M1ER</t>
-  </si>
-  <si>
-    <t>TD-RTsDEE-M1ME</t>
-  </si>
-  <si>
-    <t>TD-RTsDEE-RE</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1MCIL</t>
-  </si>
-  <si>
-    <t>M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-μ-processeurs et μ-contrôleurs-G1</t>
-  </si>
-  <si>
-    <t>TP-μPμC-M1MCIL</t>
-  </si>
-  <si>
-    <t>14h - 15h</t>
-  </si>
-  <si>
-    <t>Labo μ-processeurs</t>
-  </si>
-  <si>
-    <t>TD-Exploitation des Réseaux électriques</t>
-  </si>
-  <si>
-    <t>TD-ERE-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-μ-processeurs et μ-contrôleurs-G2</t>
-  </si>
-  <si>
-    <t>15h - 16h</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-Exploitation des Réseaux électriques</t>
-  </si>
-  <si>
-    <t>Cours-ERE-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-Compatibilité électromagnétique</t>
-  </si>
-  <si>
-    <t>Cours-EM-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-Exploitation des Réseaux électriques-G1</t>
-  </si>
-  <si>
-    <t>TP-ERE-M1MCIL</t>
-  </si>
-  <si>
-    <t>NEMMICH SAID</t>
-  </si>
-  <si>
-    <t>Salle micro 02</t>
-  </si>
-  <si>
-    <t>TP-Exploitation des Réseaux électriques-G2</t>
-  </si>
-  <si>
-    <t>TP-Machines électriques approfondies -G1</t>
-  </si>
-  <si>
-    <t>TP-MEA-M1MCIL</t>
-  </si>
-  <si>
-    <t>DJELLOULI YOUNES</t>
-  </si>
-  <si>
-    <t>Labo machine 1 &amp; Salle de micros 03</t>
-  </si>
-  <si>
-    <t>TP-Machines électriques approfondies-G2</t>
-  </si>
-  <si>
-    <t>TD-MEA-M1MCIL</t>
-  </si>
-  <si>
-    <t>TD-EPA-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-Technologie d'Élclairage</t>
-  </si>
-  <si>
-    <t>Cours-TE-M1MCIL</t>
-  </si>
-  <si>
-    <t>TD-Méthodes numériques appliquées</t>
-  </si>
-  <si>
-    <t>TD-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-EPA-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-Électronique de puissance avancée-G1</t>
-  </si>
-  <si>
-    <t>TP-EPA-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées-G2</t>
-  </si>
-  <si>
-    <t>TP-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>Salle micro 03</t>
-  </si>
-  <si>
-    <t>TP-Électronique de puissance avancée-G2</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées-G1</t>
-  </si>
-  <si>
-    <t>Cours-Anglais technique et terminologie</t>
-  </si>
-  <si>
-    <t>Cours-ANGTT-M1MCIL</t>
-  </si>
-  <si>
     <t>TP-CEPA-M1CE</t>
   </si>
   <si>
     <t>TP-EPA-M1ER</t>
   </si>
   <si>
-    <t>TP-EPA-M1ME</t>
-  </si>
-  <si>
-    <t>Salle micro 01</t>
-  </si>
-  <si>
-    <t>TP-EPA-RE</t>
-  </si>
-  <si>
     <t>TP-EPA-M1CE</t>
   </si>
   <si>
-    <t>TP-Machines électriques approfondies-G1</t>
-  </si>
-  <si>
     <t>TP-MEA-M1CE</t>
   </si>
   <si>
@@ -2321,88 +2399,10 @@
     <t>Salle micro 03, Labo machine</t>
   </si>
   <si>
-    <t>TP-MEA-M1ME</t>
-  </si>
-  <si>
-    <t>TP-MEA-RE</t>
-  </si>
-  <si>
-    <t>Salle micro 02 &amp; labo machine 02</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées et optimisation-G1</t>
-  </si>
-  <si>
-    <t>TP-MNAO-M1CE</t>
-  </si>
-  <si>
-    <t>TP-MNAO-M1ER</t>
-  </si>
-  <si>
-    <t>TP-MNAO-M1ME</t>
-  </si>
-  <si>
-    <t>TP-MNAO-RE</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées et optimisation-G2</t>
-  </si>
-  <si>
-    <t>TP-Programmation avancée en Python-G1</t>
-  </si>
-  <si>
-    <t>TP-PAP-M1CE</t>
-  </si>
-  <si>
-    <t>TP-PAP-M1ER</t>
-  </si>
-  <si>
-    <t>M1 ER</t>
-  </si>
-  <si>
-    <t>TP-PAP-M1ME</t>
-  </si>
-  <si>
-    <t>TP-PAP-RE</t>
-  </si>
-  <si>
-    <t>TP-Programmation avancée en Python-G2</t>
-  </si>
-  <si>
-    <t>TP-Réseaux de transport et de distribution d'énergie électrique-G1</t>
-  </si>
-  <si>
     <t>TP-RTsDEE-M1CE</t>
   </si>
   <si>
-    <t>TP-RTsDEE-M1ER</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-M1ME</t>
-  </si>
-  <si>
-    <t>Labo Réseaux</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-RE</t>
-  </si>
-  <si>
-    <t>TP-Réseaux de transport et de distribution d'énergie électrique-G2</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-M1RE</t>
-  </si>
-  <si>
     <t>TP-μPμC-M1CE</t>
-  </si>
-  <si>
-    <t>TP-μPμC-M1ER</t>
-  </si>
-  <si>
-    <t>TP-μPμC-M1ME</t>
-  </si>
-  <si>
-    <t>TP-μPμC-RE</t>
   </si>
   <si>
     <t>Cours-Éclairage LED: Principes et applications</t>
@@ -3445,12 +3445,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -3769,7 +3781,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3793,16 +3805,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3811,91 +3823,94 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4241,7 +4256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G651"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
@@ -4276,7 +4291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" hidden="1" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -4299,7 +4314,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" hidden="1" spans="1:7">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -4322,7 +4337,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" hidden="1" spans="1:7">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4345,7 +4360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" hidden="1" spans="1:7">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -4368,7 +4383,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" hidden="1" spans="1:7">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4391,7 +4406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" hidden="1" spans="1:7">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -4414,7 +4429,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" hidden="1" spans="1:7">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4437,7 +4452,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" hidden="1" spans="1:7">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -4460,7 +4475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" hidden="1" spans="1:7">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -4483,7 +4498,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" hidden="1" spans="1:7">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -4506,7 +4521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" hidden="1" spans="1:7">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -4529,7 +4544,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" hidden="1" spans="1:7">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -4552,7 +4567,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" hidden="1" spans="1:7">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -4575,7 +4590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" hidden="1" spans="1:7">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -4598,7 +4613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" hidden="1" spans="1:7">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -4621,7 +4636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" hidden="1" spans="1:7">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -4644,7 +4659,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" hidden="1" spans="1:7">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -4667,7 +4682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" hidden="1" spans="1:7">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -4690,7 +4705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" hidden="1" spans="1:7">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -4713,7 +4728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" hidden="1" spans="1:7">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -4736,7 +4751,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" hidden="1" spans="1:7">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -4759,7 +4774,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" hidden="1" spans="1:7">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -4782,7 +4797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" hidden="1" spans="1:7">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -4805,7 +4820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" hidden="1" spans="1:7">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -4828,7 +4843,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" hidden="1" spans="1:7">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -4851,7 +4866,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" hidden="1" spans="1:7">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -4874,7 +4889,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" hidden="1" spans="1:7">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -4897,7 +4912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" hidden="1" spans="1:7">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -4920,7 +4935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" hidden="1" spans="1:7">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -4943,7 +4958,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" hidden="1" spans="1:7">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -4966,7 +4981,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" hidden="1" spans="1:7">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -4989,7 +5004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" hidden="1" spans="1:7">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -5012,7 +5027,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" hidden="1" spans="1:7">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -5035,7 +5050,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" hidden="1" spans="1:7">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -5058,7 +5073,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" hidden="1" spans="1:7">
       <c r="A36" t="s">
         <v>76</v>
       </c>
@@ -5081,7 +5096,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" hidden="1" spans="1:7">
       <c r="A37" t="s">
         <v>81</v>
       </c>
@@ -5104,7 +5119,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" hidden="1" spans="1:7">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -5127,7 +5142,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" hidden="1" spans="1:7">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -5150,7 +5165,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" hidden="1" spans="1:7">
       <c r="A40" t="s">
         <v>92</v>
       </c>
@@ -5173,7 +5188,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" hidden="1" spans="1:7">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -5196,7 +5211,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" hidden="1" spans="1:7">
       <c r="A42" t="s">
         <v>100</v>
       </c>
@@ -5219,7 +5234,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" hidden="1" spans="1:7">
       <c r="A43" t="s">
         <v>104</v>
       </c>
@@ -5242,7 +5257,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" hidden="1" spans="1:7">
       <c r="A44" t="s">
         <v>108</v>
       </c>
@@ -5265,7 +5280,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" hidden="1" spans="1:7">
       <c r="A45" t="s">
         <v>110</v>
       </c>
@@ -5288,7 +5303,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" hidden="1" spans="1:7">
       <c r="A46" t="s">
         <v>110</v>
       </c>
@@ -5311,7 +5326,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" hidden="1" spans="1:7">
       <c r="A47" t="s">
         <v>113</v>
       </c>
@@ -5334,7 +5349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" hidden="1" spans="1:7">
       <c r="A48" t="s">
         <v>117</v>
       </c>
@@ -5357,7 +5372,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" hidden="1" spans="1:7">
       <c r="A49" t="s">
         <v>120</v>
       </c>
@@ -5380,7 +5395,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" hidden="1" spans="1:7">
       <c r="A50" t="s">
         <v>123</v>
       </c>
@@ -5403,7 +5418,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" hidden="1" spans="1:7">
       <c r="A51" t="s">
         <v>126</v>
       </c>
@@ -5426,7 +5441,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" hidden="1" spans="1:7">
       <c r="A52" t="s">
         <v>128</v>
       </c>
@@ -5449,7 +5464,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" hidden="1" spans="1:7">
       <c r="A53" t="s">
         <v>130</v>
       </c>
@@ -5472,7 +5487,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" hidden="1" spans="1:7">
       <c r="A54" t="s">
         <v>133</v>
       </c>
@@ -5495,7 +5510,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" hidden="1" spans="1:7">
       <c r="A55" t="s">
         <v>76</v>
       </c>
@@ -5518,7 +5533,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" hidden="1" spans="1:7">
       <c r="A56" t="s">
         <v>81</v>
       </c>
@@ -5541,7 +5556,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" hidden="1" spans="1:7">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -5564,7 +5579,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" hidden="1" spans="1:7">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -5587,7 +5602,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" hidden="1" spans="1:7">
       <c r="A59" t="s">
         <v>92</v>
       </c>
@@ -5610,7 +5625,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" hidden="1" spans="1:7">
       <c r="A60" t="s">
         <v>96</v>
       </c>
@@ -5633,7 +5648,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" hidden="1" spans="1:7">
       <c r="A61" t="s">
         <v>100</v>
       </c>
@@ -5656,7 +5671,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" hidden="1" spans="1:7">
       <c r="A62" t="s">
         <v>104</v>
       </c>
@@ -5679,7 +5694,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" hidden="1" spans="1:7">
       <c r="A63" t="s">
         <v>108</v>
       </c>
@@ -5702,7 +5717,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" hidden="1" spans="1:7">
       <c r="A64" t="s">
         <v>110</v>
       </c>
@@ -5725,7 +5740,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" hidden="1" spans="1:7">
       <c r="A65" t="s">
         <v>110</v>
       </c>
@@ -5748,7 +5763,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" hidden="1" spans="1:7">
       <c r="A66" t="s">
         <v>113</v>
       </c>
@@ -5771,7 +5786,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" hidden="1" spans="1:7">
       <c r="A67" t="s">
         <v>117</v>
       </c>
@@ -5794,7 +5809,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" hidden="1" spans="1:7">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -5817,7 +5832,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" hidden="1" spans="1:7">
       <c r="A69" t="s">
         <v>123</v>
       </c>
@@ -5840,7 +5855,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" hidden="1" spans="1:7">
       <c r="A70" t="s">
         <v>126</v>
       </c>
@@ -5863,7 +5878,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" hidden="1" spans="1:7">
       <c r="A71" t="s">
         <v>128</v>
       </c>
@@ -5886,7 +5901,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" hidden="1" spans="1:7">
       <c r="A72" t="s">
         <v>130</v>
       </c>
@@ -5909,7 +5924,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" hidden="1" spans="1:7">
       <c r="A73" t="s">
         <v>133</v>
       </c>
@@ -5932,7 +5947,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" hidden="1" spans="1:7">
       <c r="A74" t="s">
         <v>156</v>
       </c>
@@ -5955,7 +5970,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" hidden="1" spans="1:7">
       <c r="A75" t="s">
         <v>156</v>
       </c>
@@ -5978,7 +5993,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" hidden="1" spans="1:7">
       <c r="A76" t="s">
         <v>161</v>
       </c>
@@ -6001,7 +6016,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" hidden="1" spans="1:7">
       <c r="A77" t="s">
         <v>165</v>
       </c>
@@ -6024,7 +6039,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" hidden="1" spans="1:7">
       <c r="A78" t="s">
         <v>168</v>
       </c>
@@ -6047,7 +6062,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" hidden="1" spans="1:7">
       <c r="A79" t="s">
         <v>171</v>
       </c>
@@ -6070,7 +6085,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" hidden="1" spans="1:7">
       <c r="A80" t="s">
         <v>168</v>
       </c>
@@ -6093,7 +6108,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" hidden="1" spans="1:7">
       <c r="A81" t="s">
         <v>171</v>
       </c>
@@ -6116,7 +6131,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" hidden="1" spans="1:7">
       <c r="A82" t="s">
         <v>177</v>
       </c>
@@ -6139,7 +6154,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" hidden="1" spans="1:7">
       <c r="A83" t="s">
         <v>179</v>
       </c>
@@ -6162,7 +6177,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" hidden="1" spans="1:7">
       <c r="A84" t="s">
         <v>181</v>
       </c>
@@ -6185,7 +6200,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" hidden="1" spans="1:7">
       <c r="A85" t="s">
         <v>185</v>
       </c>
@@ -6208,7 +6223,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" hidden="1" spans="1:7">
       <c r="A86" t="s">
         <v>188</v>
       </c>
@@ -6231,7 +6246,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" hidden="1" spans="1:7">
       <c r="A87" t="s">
         <v>191</v>
       </c>
@@ -6254,7 +6269,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" hidden="1" spans="1:7">
       <c r="A88" t="s">
         <v>193</v>
       </c>
@@ -6277,7 +6292,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" hidden="1" spans="1:7">
       <c r="A89" t="s">
         <v>195</v>
       </c>
@@ -6300,7 +6315,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" hidden="1" spans="1:7">
       <c r="A90" t="s">
         <v>198</v>
       </c>
@@ -6323,7 +6338,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" hidden="1" spans="1:7">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -6346,7 +6361,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" hidden="1" spans="1:7">
       <c r="A92" t="s">
         <v>198</v>
       </c>
@@ -6369,7 +6384,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" hidden="1" spans="1:7">
       <c r="A93" t="s">
         <v>198</v>
       </c>
@@ -6392,7 +6407,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" hidden="1" spans="1:7">
       <c r="A94" t="s">
         <v>205</v>
       </c>
@@ -6415,7 +6430,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" hidden="1" spans="1:7">
       <c r="A95" t="s">
         <v>208</v>
       </c>
@@ -6438,7 +6453,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" hidden="1" spans="1:7">
       <c r="A96" t="s">
         <v>210</v>
       </c>
@@ -6461,7 +6476,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" hidden="1" spans="1:7">
       <c r="A97" t="s">
         <v>213</v>
       </c>
@@ -6484,7 +6499,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" hidden="1" spans="1:7">
       <c r="A98" t="s">
         <v>215</v>
       </c>
@@ -6507,7 +6522,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" hidden="1" spans="1:7">
       <c r="A99" t="s">
         <v>220</v>
       </c>
@@ -6530,7 +6545,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" hidden="1" spans="1:7">
       <c r="A100" t="s">
         <v>224</v>
       </c>
@@ -6553,7 +6568,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" hidden="1" spans="1:7">
       <c r="A101" t="s">
         <v>220</v>
       </c>
@@ -6576,7 +6591,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" hidden="1" spans="1:7">
       <c r="A102" t="s">
         <v>224</v>
       </c>
@@ -6599,7 +6614,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" hidden="1" spans="1:7">
       <c r="A103" t="s">
         <v>227</v>
       </c>
@@ -6622,7 +6637,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" hidden="1" spans="1:7">
       <c r="A104" t="s">
         <v>230</v>
       </c>
@@ -6645,7 +6660,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" hidden="1" spans="1:7">
       <c r="A105" t="s">
         <v>232</v>
       </c>
@@ -6668,7 +6683,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" hidden="1" spans="1:7">
       <c r="A106" t="s">
         <v>235</v>
       </c>
@@ -6691,7 +6706,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" hidden="1" spans="1:7">
       <c r="A107" t="s">
         <v>235</v>
       </c>
@@ -6714,7 +6729,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" hidden="1" spans="1:7">
       <c r="A108" t="s">
         <v>239</v>
       </c>
@@ -6737,7 +6752,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" hidden="1" spans="1:7">
       <c r="A109" t="s">
         <v>242</v>
       </c>
@@ -6760,7 +6775,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" hidden="1" spans="1:7">
       <c r="A110" t="s">
         <v>244</v>
       </c>
@@ -6783,7 +6798,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" hidden="1" spans="1:7">
       <c r="A111" t="s">
         <v>248</v>
       </c>
@@ -6806,7 +6821,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" hidden="1" spans="1:7">
       <c r="A112" t="s">
         <v>248</v>
       </c>
@@ -6829,7 +6844,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" hidden="1" spans="1:7">
       <c r="A113" t="s">
         <v>250</v>
       </c>
@@ -6852,7 +6867,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" hidden="1" spans="1:7">
       <c r="A114" t="s">
         <v>253</v>
       </c>
@@ -6875,7 +6890,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" hidden="1" spans="1:7">
       <c r="A115" t="s">
         <v>250</v>
       </c>
@@ -6898,7 +6913,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" hidden="1" spans="1:7">
       <c r="A116" t="s">
         <v>253</v>
       </c>
@@ -6921,7 +6936,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" hidden="1" spans="1:7">
       <c r="A117" t="s">
         <v>256</v>
       </c>
@@ -6944,7 +6959,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" hidden="1" spans="1:7">
       <c r="A118" t="s">
         <v>259</v>
       </c>
@@ -6967,7 +6982,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" hidden="1" spans="1:7">
       <c r="A119" t="s">
         <v>262</v>
       </c>
@@ -6990,7 +7005,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" hidden="1" spans="1:7">
       <c r="A120" t="s">
         <v>264</v>
       </c>
@@ -7013,7 +7028,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" hidden="1" spans="1:7">
       <c r="A121" t="s">
         <v>256</v>
       </c>
@@ -7036,7 +7051,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" hidden="1" spans="1:7">
       <c r="A122" t="s">
         <v>266</v>
       </c>
@@ -7059,7 +7074,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" hidden="1" spans="1:7">
       <c r="A123" t="s">
         <v>270</v>
       </c>
@@ -7082,7 +7097,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" hidden="1" spans="1:7">
       <c r="A124" t="s">
         <v>273</v>
       </c>
@@ -7105,7 +7120,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" hidden="1" spans="1:7">
       <c r="A125" t="s">
         <v>275</v>
       </c>
@@ -7128,7 +7143,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" hidden="1" spans="1:7">
       <c r="A126" t="s">
         <v>277</v>
       </c>
@@ -7151,7 +7166,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" hidden="1" spans="1:7">
       <c r="A127" t="s">
         <v>279</v>
       </c>
@@ -7174,7 +7189,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" hidden="1" spans="1:7">
       <c r="A128" t="s">
         <v>282</v>
       </c>
@@ -7197,7 +7212,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" hidden="1" spans="1:7">
       <c r="A129" t="s">
         <v>285</v>
       </c>
@@ -7220,7 +7235,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" hidden="1" spans="1:7">
       <c r="A130" t="s">
         <v>288</v>
       </c>
@@ -7243,7 +7258,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" hidden="1" spans="1:7">
       <c r="A131" t="s">
         <v>291</v>
       </c>
@@ -7266,7 +7281,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" hidden="1" spans="1:7">
       <c r="A132" t="s">
         <v>293</v>
       </c>
@@ -7289,7 +7304,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" hidden="1" spans="1:7">
       <c r="A133" t="s">
         <v>296</v>
       </c>
@@ -7312,7 +7327,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" hidden="1" spans="1:7">
       <c r="A134" t="s">
         <v>299</v>
       </c>
@@ -7335,7 +7350,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" hidden="1" spans="1:7">
       <c r="A135" t="s">
         <v>302</v>
       </c>
@@ -7358,7 +7373,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" hidden="1" spans="1:7">
       <c r="A136" t="s">
         <v>305</v>
       </c>
@@ -7381,7 +7396,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" hidden="1" spans="1:7">
       <c r="A137" t="s">
         <v>308</v>
       </c>
@@ -7404,7 +7419,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" hidden="1" spans="1:7">
       <c r="A138" t="s">
         <v>311</v>
       </c>
@@ -7427,7 +7442,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" hidden="1" spans="1:7">
       <c r="A139" t="s">
         <v>313</v>
       </c>
@@ -7450,7 +7465,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" hidden="1" spans="1:7">
       <c r="A140" t="s">
         <v>316</v>
       </c>
@@ -7473,7 +7488,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" hidden="1" spans="1:7">
       <c r="A141" t="s">
         <v>321</v>
       </c>
@@ -7496,7 +7511,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" hidden="1" spans="1:7">
       <c r="A142" t="s">
         <v>324</v>
       </c>
@@ -7519,7 +7534,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" hidden="1" spans="1:7">
       <c r="A143" t="s">
         <v>326</v>
       </c>
@@ -7542,7 +7557,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" hidden="1" spans="1:7">
       <c r="A144" t="s">
         <v>329</v>
       </c>
@@ -7565,7 +7580,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" hidden="1" spans="1:7">
       <c r="A145" t="s">
         <v>331</v>
       </c>
@@ -7588,7 +7603,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" hidden="1" spans="1:7">
       <c r="A146" t="s">
         <v>335</v>
       </c>
@@ -7611,7 +7626,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" hidden="1" spans="1:7">
       <c r="A147" t="s">
         <v>338</v>
       </c>
@@ -7634,7 +7649,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" hidden="1" spans="1:7">
       <c r="A148" t="s">
         <v>335</v>
       </c>
@@ -7657,7 +7672,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" hidden="1" spans="1:7">
       <c r="A149" t="s">
         <v>338</v>
       </c>
@@ -7680,7 +7695,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" hidden="1" spans="1:7">
       <c r="A150" t="s">
         <v>344</v>
       </c>
@@ -7703,7 +7718,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" hidden="1" spans="1:7">
       <c r="A151" t="s">
         <v>347</v>
       </c>
@@ -7726,7 +7741,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" hidden="1" spans="1:7">
       <c r="A152" t="s">
         <v>349</v>
       </c>
@@ -7749,7 +7764,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" hidden="1" spans="1:7">
       <c r="A153" t="s">
         <v>351</v>
       </c>
@@ -7772,7 +7787,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" hidden="1" spans="1:7">
       <c r="A154" t="s">
         <v>353</v>
       </c>
@@ -7795,7 +7810,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" hidden="1" spans="1:7">
       <c r="A155" t="s">
         <v>355</v>
       </c>
@@ -7818,7 +7833,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" hidden="1" spans="1:7">
       <c r="A156" t="s">
         <v>355</v>
       </c>
@@ -7841,7 +7856,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" hidden="1" spans="1:7">
       <c r="A157" t="s">
         <v>359</v>
       </c>
@@ -7864,7 +7879,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" hidden="1" spans="1:7">
       <c r="A158" t="s">
         <v>362</v>
       </c>
@@ -7887,7 +7902,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" hidden="1" spans="1:7">
       <c r="A159" t="s">
         <v>364</v>
       </c>
@@ -7910,7 +7925,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" hidden="1" spans="1:7">
       <c r="A160" t="s">
         <v>367</v>
       </c>
@@ -7933,7 +7948,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" hidden="1" spans="1:7">
       <c r="A161" t="s">
         <v>364</v>
       </c>
@@ -7956,7 +7971,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" hidden="1" spans="1:7">
       <c r="A162" t="s">
         <v>368</v>
       </c>
@@ -7979,7 +7994,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" hidden="1" spans="1:7">
       <c r="A163" t="s">
         <v>364</v>
       </c>
@@ -8002,7 +8017,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" hidden="1" spans="1:7">
       <c r="A164" t="s">
         <v>370</v>
       </c>
@@ -8025,7 +8040,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" hidden="1" spans="1:7">
       <c r="A165" t="s">
         <v>375</v>
       </c>
@@ -8048,7 +8063,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" hidden="1" spans="1:7">
       <c r="A166" t="s">
         <v>378</v>
       </c>
@@ -8071,7 +8086,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" hidden="1" spans="1:7">
       <c r="A167" t="s">
         <v>381</v>
       </c>
@@ -8094,7 +8109,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" hidden="1" spans="1:7">
       <c r="A168" t="s">
         <v>385</v>
       </c>
@@ -8117,7 +8132,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" hidden="1" spans="1:7">
       <c r="A169" t="s">
         <v>387</v>
       </c>
@@ -8140,7 +8155,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" hidden="1" spans="1:7">
       <c r="A170" t="s">
         <v>389</v>
       </c>
@@ -8163,7 +8178,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" hidden="1" spans="1:7">
       <c r="A171" t="s">
         <v>394</v>
       </c>
@@ -8186,7 +8201,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" hidden="1" spans="1:7">
       <c r="A172" t="s">
         <v>397</v>
       </c>
@@ -8209,7 +8224,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" hidden="1" spans="1:7">
       <c r="A173" t="s">
         <v>401</v>
       </c>
@@ -8232,7 +8247,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" hidden="1" spans="1:7">
       <c r="A174" t="s">
         <v>403</v>
       </c>
@@ -8255,7 +8270,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" hidden="1" spans="1:7">
       <c r="A175" t="s">
         <v>405</v>
       </c>
@@ -8278,7 +8293,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" hidden="1" spans="1:7">
       <c r="A176" t="s">
         <v>409</v>
       </c>
@@ -8301,7 +8316,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" hidden="1" spans="1:7">
       <c r="A177" t="s">
         <v>411</v>
       </c>
@@ -8324,7 +8339,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" hidden="1" spans="1:7">
       <c r="A178" t="s">
         <v>413</v>
       </c>
@@ -8347,7 +8362,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" hidden="1" spans="1:7">
       <c r="A179" t="s">
         <v>416</v>
       </c>
@@ -8370,7 +8385,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" hidden="1" spans="1:7">
       <c r="A180" t="s">
         <v>418</v>
       </c>
@@ -8393,7 +8408,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" hidden="1" spans="1:7">
       <c r="A181" t="s">
         <v>46</v>
       </c>
@@ -8416,7 +8431,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" hidden="1" spans="1:7">
       <c r="A182" t="s">
         <v>425</v>
       </c>
@@ -8439,7 +8454,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" hidden="1" spans="1:7">
       <c r="A183" t="s">
         <v>429</v>
       </c>
@@ -8462,7 +8477,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" hidden="1" spans="1:7">
       <c r="A184" t="s">
         <v>16</v>
       </c>
@@ -8485,7 +8500,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" hidden="1" spans="1:7">
       <c r="A185" t="s">
         <v>46</v>
       </c>
@@ -8508,7 +8523,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" hidden="1" spans="1:7">
       <c r="A186" t="s">
         <v>436</v>
       </c>
@@ -8531,7 +8546,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" hidden="1" spans="1:7">
       <c r="A187" t="s">
         <v>439</v>
       </c>
@@ -8554,7 +8569,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" hidden="1" spans="1:7">
       <c r="A188" t="s">
         <v>429</v>
       </c>
@@ -8577,7 +8592,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" hidden="1" spans="1:7">
       <c r="A189" t="s">
         <v>16</v>
       </c>
@@ -8600,7 +8615,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" hidden="1" spans="1:7">
       <c r="A190" t="s">
         <v>46</v>
       </c>
@@ -8623,7 +8638,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" hidden="1" spans="1:7">
       <c r="A191" t="s">
         <v>439</v>
       </c>
@@ -8646,7 +8661,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" hidden="1" spans="1:7">
       <c r="A192" t="s">
         <v>436</v>
       </c>
@@ -8669,7 +8684,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" hidden="1" spans="1:7">
       <c r="A193" t="s">
         <v>429</v>
       </c>
@@ -8692,7 +8707,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" hidden="1" spans="1:7">
       <c r="A194" t="s">
         <v>16</v>
       </c>
@@ -8715,7 +8730,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" hidden="1" spans="1:7">
       <c r="A195" t="s">
         <v>46</v>
       </c>
@@ -8738,7 +8753,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" hidden="1" spans="1:7">
       <c r="A196" t="s">
         <v>429</v>
       </c>
@@ -8761,7 +8776,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" hidden="1" spans="1:7">
       <c r="A197" t="s">
         <v>16</v>
       </c>
@@ -8784,7 +8799,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" hidden="1" spans="1:7">
       <c r="A198" t="s">
         <v>70</v>
       </c>
@@ -8807,7 +8822,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" hidden="1" spans="1:7">
       <c r="A199" t="s">
         <v>60</v>
       </c>
@@ -8830,7 +8845,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" hidden="1" spans="1:7">
       <c r="A200" t="s">
         <v>46</v>
       </c>
@@ -8853,7 +8868,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" hidden="1" spans="1:7">
       <c r="A201" t="s">
         <v>429</v>
       </c>
@@ -8876,7 +8891,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" hidden="1" spans="1:7">
       <c r="A202" t="s">
         <v>16</v>
       </c>
@@ -8899,7 +8914,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" hidden="1" spans="1:7">
       <c r="A203" t="s">
         <v>46</v>
       </c>
@@ -8922,7 +8937,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" hidden="1" spans="1:7">
       <c r="A204" t="s">
         <v>429</v>
       </c>
@@ -8945,7 +8960,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" hidden="1" spans="1:7">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -8968,7 +8983,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" hidden="1" spans="1:7">
       <c r="A206" t="s">
         <v>46</v>
       </c>
@@ -8991,7 +9006,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" hidden="1" spans="1:7">
       <c r="A207" t="s">
         <v>436</v>
       </c>
@@ -9014,7 +9029,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" hidden="1" spans="1:7">
       <c r="A208" t="s">
         <v>439</v>
       </c>
@@ -9037,7 +9052,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" hidden="1" spans="1:7">
       <c r="A209" t="s">
         <v>429</v>
       </c>
@@ -9060,7 +9075,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" hidden="1" spans="1:7">
       <c r="A210" t="s">
         <v>16</v>
       </c>
@@ -9083,7 +9098,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" hidden="1" spans="1:7">
       <c r="A211" t="s">
         <v>46</v>
       </c>
@@ -9106,7 +9121,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" hidden="1" spans="1:7">
       <c r="A212" t="s">
         <v>439</v>
       </c>
@@ -9129,7 +9144,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" hidden="1" spans="1:7">
       <c r="A213" t="s">
         <v>429</v>
       </c>
@@ -9152,7 +9167,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" hidden="1" spans="1:7">
       <c r="A214" t="s">
         <v>16</v>
       </c>
@@ -9175,7 +9190,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" hidden="1" spans="1:7">
       <c r="A215" t="s">
         <v>425</v>
       </c>
@@ -9198,7 +9213,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" hidden="1" spans="1:7">
       <c r="A216" t="s">
         <v>467</v>
       </c>
@@ -9221,7 +9236,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" hidden="1" spans="1:7">
       <c r="A217" t="s">
         <v>470</v>
       </c>
@@ -9244,7 +9259,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" hidden="1" spans="1:7">
       <c r="A218" t="s">
         <v>467</v>
       </c>
@@ -9267,7 +9282,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" hidden="1" spans="1:7">
       <c r="A219" t="s">
         <v>73</v>
       </c>
@@ -9290,7 +9305,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" hidden="1" spans="1:7">
       <c r="A220" t="s">
         <v>475</v>
       </c>
@@ -9313,7 +9328,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" hidden="1" spans="1:7">
       <c r="A221" t="s">
         <v>475</v>
       </c>
@@ -9336,7 +9351,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" hidden="1" spans="1:7">
       <c r="A222" t="s">
         <v>73</v>
       </c>
@@ -9359,7 +9374,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" hidden="1" spans="1:7">
       <c r="A223" t="s">
         <v>439</v>
       </c>
@@ -9382,7 +9397,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" hidden="1" spans="1:7">
       <c r="A224" t="s">
         <v>436</v>
       </c>
@@ -9405,7 +9420,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" hidden="1" spans="1:7">
       <c r="A225" t="s">
         <v>429</v>
       </c>
@@ -9428,7 +9443,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" hidden="1" spans="1:7">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -9451,7 +9466,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" hidden="1" spans="1:7">
       <c r="A227" t="s">
         <v>46</v>
       </c>
@@ -9474,7 +9489,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" hidden="1" spans="1:7">
       <c r="A228" t="s">
         <v>436</v>
       </c>
@@ -9497,7 +9512,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" hidden="1" spans="1:7">
       <c r="A229" t="s">
         <v>439</v>
       </c>
@@ -9520,7 +9535,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" hidden="1" spans="1:7">
       <c r="A230" t="s">
         <v>429</v>
       </c>
@@ -9543,7 +9558,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" hidden="1" spans="1:7">
       <c r="A231" t="s">
         <v>16</v>
       </c>
@@ -9566,7 +9581,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" hidden="1" spans="1:7">
       <c r="A232" t="s">
         <v>475</v>
       </c>
@@ -9589,7 +9604,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" hidden="1" spans="1:7">
       <c r="A233" t="s">
         <v>493</v>
       </c>
@@ -9612,7 +9627,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" hidden="1" spans="1:7">
       <c r="A234" t="s">
         <v>73</v>
       </c>
@@ -9635,7 +9650,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" hidden="1" spans="1:7">
       <c r="A235" t="s">
         <v>475</v>
       </c>
@@ -9658,7 +9673,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" hidden="1" spans="1:7">
       <c r="A236" t="s">
         <v>475</v>
       </c>
@@ -9681,7 +9696,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" hidden="1" spans="1:7">
       <c r="A237" t="s">
         <v>46</v>
       </c>
@@ -9704,7 +9719,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" hidden="1" spans="1:7">
       <c r="A238" t="s">
         <v>475</v>
       </c>
@@ -9727,7 +9742,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" hidden="1" spans="1:7">
       <c r="A239" t="s">
         <v>475</v>
       </c>
@@ -9750,7 +9765,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" hidden="1" spans="1:7">
       <c r="A240" t="s">
         <v>429</v>
       </c>
@@ -9773,7 +9788,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" hidden="1" spans="1:7">
       <c r="A241" t="s">
         <v>46</v>
       </c>
@@ -9796,7 +9811,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" hidden="1" spans="1:7">
       <c r="A242" t="s">
         <v>429</v>
       </c>
@@ -9819,7 +9834,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" hidden="1" spans="1:7">
       <c r="A243" t="s">
         <v>46</v>
       </c>
@@ -9842,7 +9857,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" hidden="1" spans="1:7">
       <c r="A244" t="s">
         <v>436</v>
       </c>
@@ -9865,7 +9880,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" hidden="1" spans="1:7">
       <c r="A245" t="s">
         <v>439</v>
       </c>
@@ -9888,7 +9903,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" hidden="1" spans="1:7">
       <c r="A246" t="s">
         <v>429</v>
       </c>
@@ -9911,7 +9926,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" hidden="1" spans="1:7">
       <c r="A247" t="s">
         <v>16</v>
       </c>
@@ -9934,7 +9949,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" hidden="1" spans="1:7">
       <c r="A248" t="s">
         <v>46</v>
       </c>
@@ -9957,7 +9972,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" hidden="1" spans="1:7">
       <c r="A249" t="s">
         <v>429</v>
       </c>
@@ -9980,7 +9995,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" hidden="1" spans="1:7">
       <c r="A250" t="s">
         <v>16</v>
       </c>
@@ -10003,7 +10018,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" hidden="1" spans="1:7">
       <c r="A251" t="s">
         <v>21</v>
       </c>
@@ -10026,7 +10041,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" hidden="1" spans="1:7">
       <c r="A252" t="s">
         <v>70</v>
       </c>
@@ -10049,7 +10064,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" hidden="1" spans="1:7">
       <c r="A253" t="s">
         <v>60</v>
       </c>
@@ -10072,7 +10087,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" hidden="1" spans="1:7">
       <c r="A254" t="s">
         <v>470</v>
       </c>
@@ -10095,7 +10110,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" hidden="1" spans="1:7">
       <c r="A255" t="s">
         <v>46</v>
       </c>
@@ -10118,7 +10133,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" hidden="1" spans="1:7">
       <c r="A256" t="s">
         <v>21</v>
       </c>
@@ -10141,7 +10156,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" hidden="1" spans="1:7">
       <c r="A257" t="s">
         <v>429</v>
       </c>
@@ -10164,7 +10179,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" hidden="1" spans="1:7">
       <c r="A258" t="s">
         <v>16</v>
       </c>
@@ -10187,7 +10202,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" hidden="1" spans="1:7">
       <c r="A259" t="s">
         <v>73</v>
       </c>
@@ -10210,7 +10225,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" hidden="1" spans="1:7">
       <c r="A260" t="s">
         <v>16</v>
       </c>
@@ -10233,7 +10248,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" hidden="1" spans="1:7">
       <c r="A261" t="s">
         <v>73</v>
       </c>
@@ -10256,7 +10271,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" hidden="1" spans="1:7">
       <c r="A262" t="s">
         <v>439</v>
       </c>
@@ -10279,7 +10294,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" hidden="1" spans="1:7">
       <c r="A263" t="s">
         <v>436</v>
       </c>
@@ -10302,7 +10317,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" hidden="1" spans="1:7">
       <c r="A264" t="s">
         <v>73</v>
       </c>
@@ -10325,7 +10340,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" hidden="1" spans="1:7">
       <c r="A265" t="s">
         <v>73</v>
       </c>
@@ -10348,7 +10363,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" hidden="1" spans="1:7">
       <c r="A266" t="s">
         <v>73</v>
       </c>
@@ -10371,7 +10386,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" hidden="1" spans="1:7">
       <c r="A267" t="s">
         <v>51</v>
       </c>
@@ -10394,7 +10409,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" hidden="1" spans="1:7">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -10417,7 +10432,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" hidden="1" spans="1:7">
       <c r="A269" t="s">
         <v>439</v>
       </c>
@@ -10440,7 +10455,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" hidden="1" spans="1:7">
       <c r="A270" t="s">
         <v>436</v>
       </c>
@@ -10463,7 +10478,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" hidden="1" spans="1:7">
       <c r="A271" t="s">
         <v>46</v>
       </c>
@@ -10486,7 +10501,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" hidden="1" spans="1:7">
       <c r="A272" t="s">
         <v>429</v>
       </c>
@@ -10509,7 +10524,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" hidden="1" spans="1:7">
       <c r="A273" t="s">
         <v>16</v>
       </c>
@@ -10532,7 +10547,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" hidden="1" spans="1:7">
       <c r="A274" t="s">
         <v>520</v>
       </c>
@@ -10555,7 +10570,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" hidden="1" spans="1:7">
       <c r="A275" t="s">
         <v>113</v>
       </c>
@@ -10578,7 +10593,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" hidden="1" spans="1:7">
       <c r="A276" t="s">
         <v>520</v>
       </c>
@@ -10601,7 +10616,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" hidden="1" spans="1:7">
       <c r="A277" t="s">
         <v>113</v>
       </c>
@@ -10624,7 +10639,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" hidden="1" spans="1:7">
       <c r="A278" t="s">
         <v>76</v>
       </c>
@@ -10647,7 +10662,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" hidden="1" spans="1:7">
       <c r="A279" t="s">
         <v>529</v>
       </c>
@@ -10670,7 +10685,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" hidden="1" spans="1:7">
       <c r="A280" t="s">
         <v>532</v>
       </c>
@@ -10693,7 +10708,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" hidden="1" spans="1:7">
       <c r="A281" t="s">
         <v>130</v>
       </c>
@@ -10716,7 +10731,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" hidden="1" spans="1:7">
       <c r="A282" t="s">
         <v>540</v>
       </c>
@@ -10739,7 +10754,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" hidden="1" spans="1:7">
       <c r="A283" t="s">
         <v>130</v>
       </c>
@@ -10762,7 +10777,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" hidden="1" spans="1:7">
       <c r="A284" t="s">
         <v>540</v>
       </c>
@@ -10785,7 +10800,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" hidden="1" spans="1:7">
       <c r="A285" t="s">
         <v>130</v>
       </c>
@@ -10808,7 +10823,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" hidden="1" spans="1:7">
       <c r="A286" t="s">
         <v>540</v>
       </c>
@@ -10831,7 +10846,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" hidden="1" spans="1:7">
       <c r="A287" t="s">
         <v>550</v>
       </c>
@@ -10854,7 +10869,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" hidden="1" spans="1:7">
       <c r="A288" t="s">
         <v>554</v>
       </c>
@@ -10877,7 +10892,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" hidden="1" spans="1:7">
       <c r="A289" t="s">
         <v>556</v>
       </c>
@@ -10900,7 +10915,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" hidden="1" spans="1:7">
       <c r="A290" t="s">
         <v>123</v>
       </c>
@@ -10923,7 +10938,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" hidden="1" spans="1:7">
       <c r="A291" t="s">
         <v>130</v>
       </c>
@@ -10946,7 +10961,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" hidden="1" spans="1:7">
       <c r="A292" t="s">
         <v>540</v>
       </c>
@@ -10969,7 +10984,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" hidden="1" spans="1:7">
       <c r="A293" t="s">
         <v>550</v>
       </c>
@@ -10992,7 +11007,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" hidden="1" spans="1:7">
       <c r="A294" t="s">
         <v>117</v>
       </c>
@@ -11015,7 +11030,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" hidden="1" spans="1:7">
       <c r="A295" t="s">
         <v>110</v>
       </c>
@@ -11038,7 +11053,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" hidden="1" spans="1:7">
       <c r="A296" t="s">
         <v>567</v>
       </c>
@@ -11061,7 +11076,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" hidden="1" spans="1:7">
       <c r="A297" t="s">
         <v>567</v>
       </c>
@@ -11084,7 +11099,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" hidden="1" spans="1:7">
       <c r="A298" t="s">
         <v>110</v>
       </c>
@@ -11107,7 +11122,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" hidden="1" spans="1:7">
       <c r="A299" t="s">
         <v>550</v>
       </c>
@@ -11130,7 +11145,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" hidden="1" spans="1:7">
       <c r="A300" t="s">
         <v>550</v>
       </c>
@@ -11153,7 +11168,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" hidden="1" spans="1:7">
       <c r="A301" t="s">
         <v>572</v>
       </c>
@@ -11176,7 +11191,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" hidden="1" spans="1:7">
       <c r="A302" t="s">
         <v>110</v>
       </c>
@@ -11199,7 +11214,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" hidden="1" spans="1:7">
       <c r="A303" t="s">
         <v>572</v>
       </c>
@@ -11222,7 +11237,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" hidden="1" spans="1:7">
       <c r="A304" t="s">
         <v>578</v>
       </c>
@@ -11245,7 +11260,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" hidden="1" spans="1:7">
       <c r="A305" t="s">
         <v>110</v>
       </c>
@@ -11268,7 +11283,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" hidden="1" spans="1:7">
       <c r="A306" t="s">
         <v>165</v>
       </c>
@@ -11291,7 +11306,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" hidden="1" spans="1:7">
       <c r="A307" t="s">
         <v>585</v>
       </c>
@@ -11314,7 +11329,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" hidden="1" spans="1:7">
       <c r="A308" t="s">
         <v>589</v>
       </c>
@@ -11337,7 +11352,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" hidden="1" spans="1:7">
       <c r="A309" t="s">
         <v>593</v>
       </c>
@@ -11360,7 +11375,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" hidden="1" spans="1:7">
       <c r="A310" t="s">
         <v>596</v>
       </c>
@@ -11383,7 +11398,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" hidden="1" spans="1:7">
       <c r="A311" t="s">
         <v>599</v>
       </c>
@@ -11406,7 +11421,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" hidden="1" spans="1:7">
       <c r="A312" t="s">
         <v>603</v>
       </c>
@@ -11429,7 +11444,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" hidden="1" spans="1:7">
       <c r="A313" t="s">
         <v>607</v>
       </c>
@@ -11452,7 +11467,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" hidden="1" spans="1:7">
       <c r="A314" t="s">
         <v>593</v>
       </c>
@@ -11475,7 +11490,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" hidden="1" spans="1:7">
       <c r="A315" t="s">
         <v>596</v>
       </c>
@@ -11498,7 +11513,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" hidden="1" spans="1:7">
       <c r="A316" t="s">
         <v>599</v>
       </c>
@@ -11521,7 +11536,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" hidden="1" spans="1:7">
       <c r="A317" t="s">
         <v>603</v>
       </c>
@@ -11544,7 +11559,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" hidden="1" spans="1:7">
       <c r="A318" t="s">
         <v>607</v>
       </c>
@@ -11567,7 +11582,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" hidden="1" spans="1:7">
       <c r="A319" t="s">
         <v>610</v>
       </c>
@@ -11590,7 +11605,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" hidden="1" spans="1:7">
       <c r="A320" t="s">
         <v>613</v>
       </c>
@@ -11613,7 +11628,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" hidden="1" spans="1:7">
       <c r="A321" t="s">
         <v>615</v>
       </c>
@@ -11636,7 +11651,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" hidden="1" spans="1:7">
       <c r="A322" t="s">
         <v>585</v>
       </c>
@@ -11659,7 +11674,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" hidden="1" spans="1:7">
       <c r="A323" t="s">
         <v>589</v>
       </c>
@@ -11682,7 +11697,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" hidden="1" spans="1:7">
       <c r="A324" t="s">
         <v>262</v>
       </c>
@@ -11705,7 +11720,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" hidden="1" spans="1:7">
       <c r="A325" t="s">
         <v>596</v>
       </c>
@@ -11728,7 +11743,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" hidden="1" spans="1:7">
       <c r="A326" t="s">
         <v>262</v>
       </c>
@@ -11751,7 +11766,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" hidden="1" spans="1:7">
       <c r="A327" t="s">
         <v>596</v>
       </c>
@@ -11774,7 +11789,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" hidden="1" spans="1:7">
       <c r="A328" t="s">
         <v>610</v>
       </c>
@@ -11797,7 +11812,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" hidden="1" spans="1:7">
       <c r="A329" t="s">
         <v>585</v>
       </c>
@@ -11820,7 +11835,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" hidden="1" spans="1:7">
       <c r="A330" t="s">
         <v>589</v>
       </c>
@@ -11843,7 +11858,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" hidden="1" spans="1:7">
       <c r="A331" t="s">
         <v>628</v>
       </c>
@@ -11866,7 +11881,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" hidden="1" spans="1:7">
       <c r="A332" t="s">
         <v>630</v>
       </c>
@@ -11889,7 +11904,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" hidden="1" spans="1:7">
       <c r="A333" t="s">
         <v>596</v>
       </c>
@@ -11912,7 +11927,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" hidden="1" spans="1:7">
       <c r="A334" t="s">
         <v>599</v>
       </c>
@@ -11935,7 +11950,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" hidden="1" spans="1:7">
       <c r="A335" t="s">
         <v>596</v>
       </c>
@@ -11958,7 +11973,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" hidden="1" spans="1:7">
       <c r="A336" t="s">
         <v>599</v>
       </c>
@@ -11981,7 +11996,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" hidden="1" spans="1:7">
       <c r="A337" t="s">
         <v>638</v>
       </c>
@@ -12004,7 +12019,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" hidden="1" spans="1:7">
       <c r="A338" t="s">
         <v>232</v>
       </c>
@@ -12027,7 +12042,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" hidden="1" spans="1:7">
       <c r="A339" t="s">
         <v>165</v>
       </c>
@@ -12050,7 +12065,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" hidden="1" spans="1:7">
       <c r="A340" t="s">
         <v>642</v>
       </c>
@@ -12073,7 +12088,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" hidden="1" spans="1:7">
       <c r="A341" t="s">
         <v>593</v>
       </c>
@@ -12096,7 +12111,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" hidden="1" spans="1:7">
       <c r="A342" t="s">
         <v>607</v>
       </c>
@@ -12119,7 +12134,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" hidden="1" spans="1:7">
       <c r="A343" t="s">
         <v>603</v>
       </c>
@@ -12142,7 +12157,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" hidden="1" spans="1:7">
       <c r="A344" t="s">
         <v>593</v>
       </c>
@@ -12165,7 +12180,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" hidden="1" spans="1:7">
       <c r="A345" t="s">
         <v>607</v>
       </c>
@@ -12188,7 +12203,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" hidden="1" spans="1:7">
       <c r="A346" t="s">
         <v>603</v>
       </c>
@@ -12211,7 +12226,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" hidden="1" spans="1:7">
       <c r="A347" t="s">
         <v>179</v>
       </c>
@@ -12234,7 +12249,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" hidden="1" spans="1:7">
       <c r="A348" t="s">
         <v>165</v>
       </c>
@@ -12257,7 +12272,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" hidden="1" spans="1:7">
       <c r="A349" t="s">
         <v>165</v>
       </c>
@@ -12281,22 +12296,22 @@
       </c>
     </row>
     <row r="350" spans="1:7">
-      <c r="A350" t="s">
+      <c r="A350" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B350" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="C350" t="s">
+      <c r="C350" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="D350" t="s">
+      <c r="D350" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E350" t="s">
+      <c r="E350" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F350" s="1" t="s">
+      <c r="F350" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G350" t="s">
@@ -12304,22 +12319,22 @@
       </c>
     </row>
     <row r="351" spans="1:7">
-      <c r="A351" t="s">
+      <c r="A351" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B351" t="s">
+      <c r="B351" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="C351" t="s">
+      <c r="C351" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="D351" t="s">
+      <c r="D351" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E351" t="s">
+      <c r="E351" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F351" s="1" t="s">
+      <c r="F351" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G351" t="s">
@@ -12327,22 +12342,22 @@
       </c>
     </row>
     <row r="352" spans="1:7">
-      <c r="A352" t="s">
+      <c r="A352" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B352" t="s">
+      <c r="B352" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="C352" t="s">
+      <c r="C352" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="D352" t="s">
+      <c r="D352" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E352" t="s">
+      <c r="E352" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F352" s="1" t="s">
+      <c r="F352" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G352" t="s">
@@ -12350,22 +12365,22 @@
       </c>
     </row>
     <row r="353" spans="1:7">
-      <c r="A353" t="s">
+      <c r="A353" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B353" t="s">
+      <c r="B353" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="C353" t="s">
+      <c r="C353" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="D353" t="s">
+      <c r="D353" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E353" t="s">
+      <c r="E353" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F353" s="1" t="s">
+      <c r="F353" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G353" t="s">
@@ -12373,22 +12388,22 @@
       </c>
     </row>
     <row r="354" spans="1:7">
-      <c r="A354" t="s">
+      <c r="A354" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B354" t="s">
+      <c r="B354" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C354" t="s">
-        <v>318</v>
-      </c>
-      <c r="D354" t="s">
-        <v>25</v>
-      </c>
-      <c r="E354" t="s">
-        <v>55</v>
-      </c>
-      <c r="F354" t="s">
+      <c r="C354" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F354" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G354" t="s">
@@ -12396,22 +12411,22 @@
       </c>
     </row>
     <row r="355" spans="1:7">
-      <c r="A355" t="s">
+      <c r="A355" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B355" t="s">
+      <c r="B355" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="C355" t="s">
-        <v>318</v>
-      </c>
-      <c r="D355" t="s">
-        <v>25</v>
-      </c>
-      <c r="E355" t="s">
-        <v>55</v>
-      </c>
-      <c r="F355" t="s">
+      <c r="C355" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F355" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G355" t="s">
@@ -12419,22 +12434,22 @@
       </c>
     </row>
     <row r="356" spans="1:7">
-      <c r="A356" t="s">
+      <c r="A356" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B356" t="s">
+      <c r="B356" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C356" t="s">
-        <v>318</v>
-      </c>
-      <c r="D356" t="s">
-        <v>25</v>
-      </c>
-      <c r="E356" t="s">
-        <v>55</v>
-      </c>
-      <c r="F356" t="s">
+      <c r="C356" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F356" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G356" t="s">
@@ -12442,22 +12457,22 @@
       </c>
     </row>
     <row r="357" spans="1:7">
-      <c r="A357" t="s">
+      <c r="A357" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B357" t="s">
+      <c r="B357" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C357" t="s">
-        <v>318</v>
-      </c>
-      <c r="D357" t="s">
-        <v>25</v>
-      </c>
-      <c r="E357" t="s">
-        <v>55</v>
-      </c>
-      <c r="F357" t="s">
+      <c r="C357" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F357" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G357" t="s">
@@ -12465,22 +12480,22 @@
       </c>
     </row>
     <row r="358" spans="1:7">
-      <c r="A358" t="s">
-        <v>279</v>
-      </c>
-      <c r="B358" t="s">
+      <c r="A358" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C358" t="s">
-        <v>281</v>
-      </c>
-      <c r="D358" t="s">
-        <v>25</v>
-      </c>
-      <c r="E358" t="s">
-        <v>42</v>
-      </c>
-      <c r="F358" t="s">
+      <c r="B358" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E358" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F358" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G358" t="s">
@@ -12488,22 +12503,22 @@
       </c>
     </row>
     <row r="359" spans="1:7">
-      <c r="A359" t="s">
-        <v>279</v>
-      </c>
-      <c r="B359" t="s">
-        <v>666</v>
-      </c>
-      <c r="C359" t="s">
-        <v>281</v>
-      </c>
-      <c r="D359" t="s">
-        <v>25</v>
-      </c>
-      <c r="E359" t="s">
-        <v>42</v>
-      </c>
-      <c r="F359" t="s">
+      <c r="A359" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E359" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F359" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G359" t="s">
@@ -12511,22 +12526,22 @@
       </c>
     </row>
     <row r="360" spans="1:7">
-      <c r="A360" t="s">
-        <v>279</v>
-      </c>
-      <c r="B360" t="s">
-        <v>667</v>
-      </c>
-      <c r="C360" t="s">
-        <v>281</v>
-      </c>
-      <c r="D360" t="s">
-        <v>25</v>
-      </c>
-      <c r="E360" t="s">
-        <v>42</v>
-      </c>
-      <c r="F360" t="s">
+      <c r="A360" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E360" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F360" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G360" t="s">
@@ -12534,22 +12549,22 @@
       </c>
     </row>
     <row r="361" spans="1:7">
-      <c r="A361" t="s">
-        <v>279</v>
-      </c>
-      <c r="B361" t="s">
-        <v>668</v>
-      </c>
-      <c r="C361" t="s">
-        <v>281</v>
-      </c>
-      <c r="D361" t="s">
-        <v>25</v>
-      </c>
-      <c r="E361" t="s">
-        <v>42</v>
-      </c>
-      <c r="F361" t="s">
+      <c r="A361" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E361" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F361" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G361" t="s">
@@ -12557,184 +12572,184 @@
       </c>
     </row>
     <row r="362" spans="1:7">
-      <c r="A362" t="s">
-        <v>669</v>
-      </c>
-      <c r="B362" t="s">
+      <c r="A362" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B362" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="C362" t="s">
-        <v>328</v>
-      </c>
-      <c r="D362" t="s">
-        <v>25</v>
-      </c>
-      <c r="E362" t="s">
-        <v>62</v>
-      </c>
-      <c r="F362" t="s">
-        <v>268</v>
+      <c r="C362" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D362" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E362" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F362" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G362" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="363" spans="1:7">
-      <c r="A363" t="s">
-        <v>669</v>
-      </c>
-      <c r="B363" t="s">
+      <c r="A363" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D363" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E363" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F363" s="4" t="s">
         <v>671</v>
-      </c>
-      <c r="C363" t="s">
-        <v>328</v>
-      </c>
-      <c r="D363" t="s">
-        <v>25</v>
-      </c>
-      <c r="E363" t="s">
-        <v>62</v>
-      </c>
-      <c r="F363" t="s">
-        <v>268</v>
       </c>
       <c r="G363" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="364" spans="1:7">
-      <c r="A364" t="s">
-        <v>669</v>
-      </c>
-      <c r="B364" t="s">
-        <v>672</v>
-      </c>
-      <c r="C364" t="s">
+      <c r="A364" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B364" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="D364" t="s">
-        <v>25</v>
-      </c>
-      <c r="E364" t="s">
-        <v>62</v>
-      </c>
-      <c r="F364" t="s">
-        <v>652</v>
+      <c r="C364" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D364" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E364" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F364" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G364" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="365" spans="1:7">
-      <c r="A365" t="s">
-        <v>669</v>
-      </c>
-      <c r="B365" t="s">
+      <c r="A365" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B365" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="C365" t="s">
-        <v>673</v>
-      </c>
-      <c r="D365" t="s">
-        <v>25</v>
-      </c>
-      <c r="E365" t="s">
-        <v>62</v>
-      </c>
-      <c r="F365" t="s">
-        <v>652</v>
+      <c r="C365" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D365" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E365" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F365" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G365" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="366" spans="1:7">
-      <c r="A366" t="s">
+      <c r="A366" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B366" t="s">
+      <c r="B366" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="C366" t="s">
-        <v>295</v>
-      </c>
-      <c r="D366" t="s">
-        <v>27</v>
-      </c>
-      <c r="E366" s="1" t="s">
+      <c r="C366" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D366" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E366" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F366" s="1" t="s">
-        <v>652</v>
+      <c r="F366" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G366" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="367" spans="1:7">
-      <c r="A367" t="s">
+      <c r="A367" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B367" t="s">
+      <c r="B367" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="C367" t="s">
-        <v>295</v>
-      </c>
-      <c r="D367" t="s">
-        <v>27</v>
-      </c>
-      <c r="E367" s="1" t="s">
+      <c r="C367" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D367" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E367" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F367" s="1" t="s">
-        <v>652</v>
+      <c r="F367" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G367" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B368" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C368" t="s">
-        <v>295</v>
+        <v>680</v>
       </c>
       <c r="D368" t="s">
-        <v>27</v>
-      </c>
-      <c r="E368" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E368" t="s">
         <v>11</v>
       </c>
-      <c r="F368" s="1" t="s">
-        <v>652</v>
+      <c r="F368" t="s">
+        <v>681</v>
       </c>
       <c r="G368" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="B369" t="s">
         <v>679</v>
       </c>
       <c r="C369" t="s">
-        <v>295</v>
+        <v>680</v>
       </c>
       <c r="D369" t="s">
-        <v>27</v>
-      </c>
-      <c r="E369" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E369" t="s">
         <v>11</v>
       </c>
-      <c r="F369" s="1" t="s">
-        <v>652</v>
+      <c r="F369" t="s">
+        <v>681</v>
       </c>
       <c r="G369" t="s">
         <v>659</v>
@@ -12742,36 +12757,36 @@
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B370" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C370" t="s">
-        <v>290</v>
+        <v>685</v>
       </c>
       <c r="D370" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E370" t="s">
         <v>11</v>
       </c>
-      <c r="F370" s="1" t="s">
-        <v>652</v>
+      <c r="F370" t="s">
+        <v>686</v>
       </c>
       <c r="G370" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="B371" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C371" t="s">
-        <v>290</v>
+        <v>685</v>
       </c>
       <c r="D371" t="s">
         <v>19</v>
@@ -12779,54 +12794,54 @@
       <c r="E371" t="s">
         <v>11</v>
       </c>
-      <c r="F371" s="1" t="s">
-        <v>652</v>
+      <c r="F371" t="s">
+        <v>686</v>
       </c>
       <c r="G371" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="B372" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C372" t="s">
-        <v>290</v>
+        <v>548</v>
       </c>
       <c r="D372" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E372" t="s">
-        <v>11</v>
-      </c>
-      <c r="F372" s="1" t="s">
-        <v>652</v>
+        <v>28</v>
+      </c>
+      <c r="F372" t="s">
+        <v>690</v>
       </c>
       <c r="G372" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="B373" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C373" t="s">
-        <v>290</v>
+        <v>548</v>
       </c>
       <c r="D373" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E373" t="s">
-        <v>11</v>
-      </c>
-      <c r="F373" s="1" t="s">
-        <v>652</v>
+        <v>28</v>
+      </c>
+      <c r="F373" t="s">
+        <v>690</v>
       </c>
       <c r="G373" t="s">
         <v>659</v>
@@ -12834,22 +12849,22 @@
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B374" t="s">
+        <v>693</v>
+      </c>
+      <c r="C374" t="s">
+        <v>9</v>
+      </c>
+      <c r="D374" t="s">
+        <v>27</v>
+      </c>
+      <c r="E374" t="s">
+        <v>28</v>
+      </c>
+      <c r="F374" t="s">
         <v>686</v>
-      </c>
-      <c r="C374" t="s">
-        <v>687</v>
-      </c>
-      <c r="D374" t="s">
-        <v>10</v>
-      </c>
-      <c r="E374" t="s">
-        <v>42</v>
-      </c>
-      <c r="F374" t="s">
-        <v>652</v>
       </c>
       <c r="G374" t="s">
         <v>653</v>
@@ -12857,22 +12872,22 @@
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B375" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="C375" t="s">
-        <v>687</v>
+        <v>83</v>
       </c>
       <c r="D375" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E375" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F375" t="s">
-        <v>652</v>
+        <v>695</v>
       </c>
       <c r="G375" t="s">
         <v>655</v>
@@ -12880,424 +12895,424 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B376" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="C376" t="s">
-        <v>687</v>
+        <v>295</v>
       </c>
       <c r="D376" t="s">
-        <v>10</v>
-      </c>
-      <c r="E376" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F376" s="1" t="s">
-        <v>652</v>
+        <v>27</v>
+      </c>
+      <c r="E376" t="s">
+        <v>28</v>
+      </c>
+      <c r="F376" t="s">
+        <v>690</v>
       </c>
       <c r="G376" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="B377" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C377" t="s">
-        <v>687</v>
+        <v>9</v>
       </c>
       <c r="D377" t="s">
         <v>10</v>
       </c>
-      <c r="E377" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F377" s="1" t="s">
-        <v>652</v>
+      <c r="E377" t="s">
+        <v>28</v>
+      </c>
+      <c r="F377" t="s">
+        <v>686</v>
       </c>
       <c r="G377" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>349</v>
+        <v>697</v>
       </c>
       <c r="B378" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C378" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="D378" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E378" t="s">
-        <v>11</v>
-      </c>
-      <c r="F378" s="1" t="s">
-        <v>692</v>
+        <v>28</v>
+      </c>
+      <c r="F378" t="s">
+        <v>695</v>
       </c>
       <c r="G378" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>349</v>
+        <v>697</v>
       </c>
       <c r="B379" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C379" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="D379" t="s">
         <v>10</v>
       </c>
       <c r="E379" t="s">
-        <v>11</v>
-      </c>
-      <c r="F379" s="1" t="s">
-        <v>692</v>
+        <v>28</v>
+      </c>
+      <c r="F379" t="s">
+        <v>690</v>
       </c>
       <c r="G379" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="380" spans="1:7">
       <c r="A380" t="s">
-        <v>349</v>
+        <v>698</v>
       </c>
       <c r="B380" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="C380" t="s">
-        <v>651</v>
+        <v>197</v>
       </c>
       <c r="D380" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E380" t="s">
-        <v>11</v>
-      </c>
-      <c r="F380" s="1" t="s">
-        <v>692</v>
+        <v>28</v>
+      </c>
+      <c r="F380" t="s">
+        <v>700</v>
       </c>
       <c r="G380" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>349</v>
+        <v>701</v>
       </c>
       <c r="B381" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C381" t="s">
-        <v>651</v>
+        <v>197</v>
       </c>
       <c r="D381" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E381" t="s">
-        <v>11</v>
-      </c>
-      <c r="F381" s="1" t="s">
-        <v>692</v>
+        <v>28</v>
+      </c>
+      <c r="F381" t="s">
+        <v>700</v>
       </c>
       <c r="G381" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="382" spans="1:7">
-      <c r="A382" t="s">
-        <v>282</v>
-      </c>
-      <c r="B382" t="s">
-        <v>696</v>
-      </c>
-      <c r="C382" t="s">
+      <c r="A382" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C382" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D382" t="s">
-        <v>27</v>
-      </c>
-      <c r="E382" t="s">
+      <c r="D382" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E382" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="G382" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="383" spans="1:7">
-      <c r="A383" t="s">
-        <v>282</v>
-      </c>
-      <c r="B383" t="s">
-        <v>697</v>
-      </c>
-      <c r="C383" t="s">
+      <c r="A383" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C383" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D383" t="s">
-        <v>27</v>
-      </c>
-      <c r="E383" t="s">
+      <c r="D383" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E383" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="G383" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="384" spans="1:7">
-      <c r="A384" t="s">
-        <v>282</v>
-      </c>
-      <c r="B384" t="s">
-        <v>698</v>
-      </c>
-      <c r="C384" t="s">
+      <c r="A384" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C384" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D384" t="s">
-        <v>443</v>
-      </c>
-      <c r="E384" t="s">
-        <v>62</v>
+      <c r="D384" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E384" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="G384" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="385" spans="1:7">
-      <c r="A385" t="s">
-        <v>282</v>
-      </c>
-      <c r="B385" t="s">
-        <v>699</v>
-      </c>
-      <c r="C385" t="s">
+      <c r="A385" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="C385" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D385" t="s">
-        <v>19</v>
-      </c>
-      <c r="E385" t="s">
-        <v>62</v>
+      <c r="D385" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E385" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="G385" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="386" spans="1:7">
-      <c r="A386" t="s">
-        <v>700</v>
-      </c>
-      <c r="B386" t="s">
-        <v>701</v>
-      </c>
-      <c r="C386" t="s">
-        <v>328</v>
-      </c>
-      <c r="D386" t="s">
-        <v>23</v>
-      </c>
-      <c r="E386" t="s">
+      <c r="A386" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E386" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="G386" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="387" spans="1:7">
-      <c r="A387" t="s">
-        <v>700</v>
-      </c>
-      <c r="B387" t="s">
-        <v>702</v>
-      </c>
-      <c r="C387" t="s">
-        <v>328</v>
-      </c>
-      <c r="D387" t="s">
-        <v>23</v>
-      </c>
-      <c r="E387" t="s">
+      <c r="A387" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E387" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="G387" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="388" spans="1:7">
-      <c r="A388" t="s">
-        <v>700</v>
-      </c>
-      <c r="B388" t="s">
-        <v>703</v>
-      </c>
-      <c r="C388" t="s">
-        <v>673</v>
-      </c>
-      <c r="D388" t="s">
+      <c r="A388" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D388" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E388" t="s">
-        <v>55</v>
-      </c>
-      <c r="F388" s="1" t="s">
-        <v>692</v>
+      <c r="E388" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F388" s="2" t="s">
+        <v>652</v>
       </c>
       <c r="G388" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="389" spans="1:7">
-      <c r="A389" t="s">
-        <v>700</v>
-      </c>
-      <c r="B389" t="s">
-        <v>704</v>
-      </c>
-      <c r="C389" t="s">
-        <v>673</v>
-      </c>
-      <c r="D389" t="s">
+      <c r="A389" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D389" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E389" t="s">
-        <v>55</v>
-      </c>
-      <c r="F389" s="1" t="s">
-        <v>692</v>
+      <c r="E389" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F389" s="2" t="s">
+        <v>652</v>
       </c>
       <c r="G389" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="390" spans="1:7">
-      <c r="A390" t="s">
-        <v>705</v>
-      </c>
-      <c r="B390" t="s">
-        <v>706</v>
-      </c>
-      <c r="C390" t="s">
-        <v>290</v>
-      </c>
-      <c r="D390" t="s">
-        <v>25</v>
-      </c>
-      <c r="E390" t="s">
-        <v>55</v>
-      </c>
-      <c r="F390" s="1" t="s">
-        <v>692</v>
+      <c r="A390" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D390" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E390" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F390" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G390" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="391" spans="1:7">
-      <c r="A391" t="s">
-        <v>705</v>
-      </c>
-      <c r="B391" t="s">
-        <v>707</v>
-      </c>
-      <c r="C391" t="s">
-        <v>290</v>
-      </c>
-      <c r="D391" t="s">
-        <v>25</v>
-      </c>
-      <c r="E391" t="s">
-        <v>55</v>
-      </c>
-      <c r="F391" s="1" t="s">
-        <v>692</v>
+      <c r="A391" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D391" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E391" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F391" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G391" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="392" spans="1:7">
-      <c r="A392" t="s">
-        <v>705</v>
-      </c>
-      <c r="B392" t="s">
-        <v>708</v>
-      </c>
-      <c r="C392" t="s">
-        <v>290</v>
-      </c>
-      <c r="D392" t="s">
+      <c r="A392" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D392" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E392" t="s">
-        <v>11</v>
-      </c>
-      <c r="F392" s="1" t="s">
-        <v>692</v>
+      <c r="E392" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F392" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G392" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="393" spans="1:7">
-      <c r="A393" t="s">
-        <v>705</v>
-      </c>
-      <c r="B393" t="s">
-        <v>709</v>
-      </c>
-      <c r="C393" t="s">
-        <v>290</v>
-      </c>
-      <c r="D393" t="s">
+      <c r="A393" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B393" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D393" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E393" t="s">
-        <v>11</v>
-      </c>
-      <c r="F393" s="1" t="s">
-        <v>692</v>
+      <c r="E393" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F393" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G393" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="394" spans="1:7">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="394" hidden="1" spans="1:7">
       <c r="A394" t="s">
-        <v>685</v>
+        <v>706</v>
       </c>
       <c r="B394" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="C394" t="s">
         <v>197</v>
@@ -13312,38 +13327,38 @@
         <v>393</v>
       </c>
       <c r="G394" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="395" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="395" hidden="1" spans="1:7">
       <c r="A395" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="B395" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="C395" t="s">
         <v>197</v>
       </c>
       <c r="D395" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="E395" t="s">
         <v>11</v>
       </c>
       <c r="F395" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="G395" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="396" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="396" hidden="1" spans="1:7">
       <c r="A396" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B396" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C396" t="s">
         <v>346</v>
@@ -13358,38 +13373,38 @@
         <v>393</v>
       </c>
       <c r="G396" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="397" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="397" hidden="1" spans="1:7">
       <c r="A397" t="s">
+        <v>701</v>
+      </c>
+      <c r="B397" t="s">
         <v>718</v>
-      </c>
-      <c r="B397" t="s">
-        <v>713</v>
       </c>
       <c r="C397" t="s">
         <v>197</v>
       </c>
       <c r="D397" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E397" t="s">
         <v>11</v>
       </c>
       <c r="F397" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="G397" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="398" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="398" hidden="1" spans="1:7">
       <c r="A398" t="s">
         <v>279</v>
       </c>
       <c r="B398" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C398" t="s">
         <v>217</v>
@@ -13404,15 +13419,15 @@
         <v>393</v>
       </c>
       <c r="G398" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="399" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="399" hidden="1" spans="1:7">
       <c r="A399" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B399" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C399" t="s">
         <v>346</v>
@@ -13427,15 +13442,15 @@
         <v>393</v>
       </c>
       <c r="G399" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="400" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="400" hidden="1" spans="1:7">
       <c r="A400" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B400" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C400" t="s">
         <v>207</v>
@@ -13450,18 +13465,18 @@
         <v>393</v>
       </c>
       <c r="G400" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="401" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="401" hidden="1" spans="1:7">
       <c r="A401" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B401" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C401" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D401" t="s">
         <v>19</v>
@@ -13470,21 +13485,21 @@
         <v>42</v>
       </c>
       <c r="F401" t="s">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="G401" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="402" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="402" hidden="1" spans="1:7">
       <c r="A402" t="s">
+        <v>731</v>
+      </c>
+      <c r="B402" t="s">
         <v>729</v>
       </c>
-      <c r="B402" t="s">
-        <v>726</v>
-      </c>
       <c r="C402" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D402" t="s">
         <v>23</v>
@@ -13493,21 +13508,21 @@
         <v>42</v>
       </c>
       <c r="F402" t="s">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="G402" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="403" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="403" hidden="1" spans="1:7">
       <c r="A403" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B403" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C403" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D403" t="s">
         <v>25</v>
@@ -13516,18 +13531,18 @@
         <v>42</v>
       </c>
       <c r="F403" t="s">
+        <v>735</v>
+      </c>
+      <c r="G403" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="404" hidden="1" spans="1:7">
+      <c r="A404" t="s">
+        <v>682</v>
+      </c>
+      <c r="B404" t="s">
         <v>733</v>
-      </c>
-      <c r="G403" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="404" spans="1:7">
-      <c r="A404" t="s">
-        <v>734</v>
-      </c>
-      <c r="B404" t="s">
-        <v>731</v>
       </c>
       <c r="C404" t="s">
         <v>323</v>
@@ -13539,18 +13554,18 @@
         <v>42</v>
       </c>
       <c r="F404" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G404" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="405" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="405" hidden="1" spans="1:7">
       <c r="A405" t="s">
         <v>282</v>
       </c>
       <c r="B405" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C405" t="s">
         <v>281</v>
@@ -13565,15 +13580,15 @@
         <v>393</v>
       </c>
       <c r="G405" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="406" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="406" hidden="1" spans="1:7">
       <c r="A406" t="s">
         <v>349</v>
       </c>
       <c r="B406" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C406" t="s">
         <v>651</v>
@@ -13588,15 +13603,15 @@
         <v>393</v>
       </c>
       <c r="G406" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="407" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="407" hidden="1" spans="1:7">
       <c r="A407" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B407" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C407" t="s">
         <v>207</v>
@@ -13611,15 +13626,15 @@
         <v>393</v>
       </c>
       <c r="G407" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="408" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="408" hidden="1" spans="1:7">
       <c r="A408" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B408" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C408" t="s">
         <v>328</v>
@@ -13634,15 +13649,15 @@
         <v>393</v>
       </c>
       <c r="G408" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="409" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="409" hidden="1" spans="1:7">
       <c r="A409" t="s">
         <v>177</v>
       </c>
       <c r="B409" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C409" t="s">
         <v>328</v>
@@ -13657,15 +13672,15 @@
         <v>393</v>
       </c>
       <c r="G409" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="410" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="410" hidden="1" spans="1:7">
       <c r="A410" t="s">
         <v>326</v>
       </c>
       <c r="B410" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C410" t="s">
         <v>651</v>
@@ -13680,12 +13695,12 @@
         <v>393</v>
       </c>
       <c r="G410" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="411" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="411" hidden="1" spans="1:7">
       <c r="A411" t="s">
-        <v>743</v>
+        <v>688</v>
       </c>
       <c r="B411" t="s">
         <v>744</v>
@@ -13700,13 +13715,13 @@
         <v>62</v>
       </c>
       <c r="F411" t="s">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="G411" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="412" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="412" hidden="1" spans="1:7">
       <c r="A412" t="s">
         <v>745</v>
       </c>
@@ -13726,12 +13741,12 @@
         <v>747</v>
       </c>
       <c r="G412" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="413" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="413" hidden="1" spans="1:7">
       <c r="A413" t="s">
-        <v>748</v>
+        <v>691</v>
       </c>
       <c r="B413" t="s">
         <v>744</v>
@@ -13746,15 +13761,15 @@
         <v>62</v>
       </c>
       <c r="F413" t="s">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="G413" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="414" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="414" hidden="1" spans="1:7">
       <c r="A414" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B414" t="s">
         <v>746</v>
@@ -13772,15 +13787,15 @@
         <v>747</v>
       </c>
       <c r="G414" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="415" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="415" hidden="1" spans="1:7">
       <c r="A415" t="s">
+        <v>749</v>
+      </c>
+      <c r="B415" t="s">
         <v>750</v>
-      </c>
-      <c r="B415" t="s">
-        <v>751</v>
       </c>
       <c r="C415" t="s">
         <v>41</v>
@@ -13795,188 +13810,188 @@
         <v>393</v>
       </c>
       <c r="G415" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
     </row>
     <row r="416" spans="1:7">
       <c r="A416" t="s">
-        <v>743</v>
+        <v>678</v>
       </c>
       <c r="B416" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C416" t="s">
-        <v>187</v>
+        <v>680</v>
       </c>
       <c r="D416" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E416" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F416" t="s">
-        <v>747</v>
+        <v>690</v>
       </c>
       <c r="G416" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="417" spans="1:7">
       <c r="A417" t="s">
-        <v>743</v>
+        <v>682</v>
       </c>
       <c r="B417" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C417" t="s">
-        <v>187</v>
+        <v>680</v>
       </c>
       <c r="D417" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E417" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F417" t="s">
-        <v>728</v>
+        <v>690</v>
       </c>
       <c r="G417" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
-        <v>743</v>
+        <v>683</v>
       </c>
       <c r="B418" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C418" t="s">
-        <v>548</v>
+        <v>328</v>
       </c>
       <c r="D418" t="s">
         <v>19</v>
       </c>
       <c r="E418" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F418" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="G418" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="419" spans="1:7">
       <c r="A419" t="s">
-        <v>743</v>
+        <v>687</v>
       </c>
       <c r="B419" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C419" t="s">
-        <v>548</v>
+        <v>328</v>
       </c>
       <c r="D419" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E419" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F419" t="s">
-        <v>755</v>
+        <v>686</v>
       </c>
       <c r="G419" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="420" spans="1:7">
       <c r="A420" t="s">
-        <v>748</v>
+        <v>692</v>
       </c>
       <c r="B420" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="C420" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="D420" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E420" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F420" t="s">
-        <v>747</v>
+        <v>686</v>
       </c>
       <c r="G420" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="421" spans="1:7">
       <c r="A421" t="s">
-        <v>748</v>
+        <v>697</v>
       </c>
       <c r="B421" t="s">
         <v>753</v>
       </c>
       <c r="C421" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="D421" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E421" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F421" t="s">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="G421" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="422" spans="1:7">
       <c r="A422" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="B422" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C422" t="s">
-        <v>548</v>
+        <v>290</v>
       </c>
       <c r="D422" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E422" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F422" t="s">
-        <v>755</v>
+        <v>690</v>
       </c>
       <c r="G422" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="423" spans="1:7">
       <c r="A423" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="B423" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C423" t="s">
-        <v>548</v>
+        <v>290</v>
       </c>
       <c r="D423" t="s">
         <v>27</v>
       </c>
       <c r="E423" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F423" t="s">
-        <v>755</v>
+        <v>690</v>
       </c>
       <c r="G423" t="s">
         <v>659</v>
@@ -13984,229 +13999,229 @@
     </row>
     <row r="424" spans="1:7">
       <c r="A424" t="s">
+        <v>698</v>
+      </c>
+      <c r="B424" t="s">
         <v>758</v>
       </c>
-      <c r="B424" t="s">
-        <v>759</v>
-      </c>
       <c r="C424" t="s">
-        <v>732</v>
+        <v>680</v>
       </c>
       <c r="D424" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E424" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F424" t="s">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="G424" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="425" spans="1:7">
       <c r="A425" t="s">
+        <v>701</v>
+      </c>
+      <c r="B425" t="s">
         <v>758</v>
       </c>
-      <c r="B425" t="s">
+      <c r="C425" t="s">
+        <v>680</v>
+      </c>
+      <c r="D425" t="s">
+        <v>27</v>
+      </c>
+      <c r="E425" t="s">
+        <v>42</v>
+      </c>
+      <c r="F425" t="s">
+        <v>700</v>
+      </c>
+      <c r="G425" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7">
+      <c r="A426" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E426" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F426" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G426" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7">
+      <c r="A427" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B427" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="C425" t="s">
-        <v>323</v>
-      </c>
-      <c r="D425" t="s">
-        <v>23</v>
-      </c>
-      <c r="E425" t="s">
-        <v>62</v>
-      </c>
-      <c r="F425" t="s">
+      <c r="C427" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E427" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F427" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G427" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7">
+      <c r="A428" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B428" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="G425" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="426" spans="1:7">
-      <c r="A426" t="s">
-        <v>758</v>
-      </c>
-      <c r="B426" t="s">
+      <c r="C428" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E428" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F428" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G428" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7">
+      <c r="A429" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B429" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="C426" t="s">
-        <v>687</v>
-      </c>
-      <c r="D426" t="s">
-        <v>19</v>
-      </c>
-      <c r="E426" t="s">
-        <v>42</v>
-      </c>
-      <c r="F426" t="s">
-        <v>755</v>
-      </c>
-      <c r="G426" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="427" spans="1:7">
-      <c r="A427" t="s">
-        <v>758</v>
-      </c>
-      <c r="B427" t="s">
+      <c r="C429" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E429" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F429" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G429" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7">
+      <c r="A430" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B430" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="C427" t="s">
-        <v>687</v>
-      </c>
-      <c r="D427" t="s">
-        <v>19</v>
-      </c>
-      <c r="E427" t="s">
-        <v>11</v>
-      </c>
-      <c r="F427" t="s">
-        <v>765</v>
-      </c>
-      <c r="G427" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="428" spans="1:7">
-      <c r="A428" t="s">
-        <v>734</v>
-      </c>
-      <c r="B428" t="s">
-        <v>759</v>
-      </c>
-      <c r="C428" t="s">
-        <v>732</v>
-      </c>
-      <c r="D428" t="s">
+      <c r="C430" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="D430" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E428" t="s">
-        <v>62</v>
-      </c>
-      <c r="F428" t="s">
-        <v>760</v>
-      </c>
-      <c r="G428" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="429" spans="1:7">
-      <c r="A429" t="s">
-        <v>734</v>
-      </c>
-      <c r="B429" t="s">
-        <v>761</v>
-      </c>
-      <c r="C429" t="s">
-        <v>323</v>
-      </c>
-      <c r="D429" t="s">
-        <v>19</v>
-      </c>
-      <c r="E429" t="s">
-        <v>62</v>
-      </c>
-      <c r="F429" t="s">
-        <v>762</v>
-      </c>
-      <c r="G429" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="430" spans="1:7">
-      <c r="A430" t="s">
-        <v>734</v>
-      </c>
-      <c r="B430" t="s">
-        <v>763</v>
-      </c>
-      <c r="C430" t="s">
-        <v>687</v>
-      </c>
-      <c r="D430" t="s">
-        <v>23</v>
-      </c>
-      <c r="E430" t="s">
-        <v>42</v>
-      </c>
-      <c r="F430" t="s">
-        <v>755</v>
+      <c r="E430" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F430" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G430" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="431" spans="1:7">
-      <c r="A431" t="s">
-        <v>734</v>
-      </c>
-      <c r="B431" t="s">
-        <v>764</v>
-      </c>
-      <c r="C431" t="s">
-        <v>687</v>
-      </c>
-      <c r="D431" t="s">
-        <v>23</v>
-      </c>
-      <c r="E431" t="s">
-        <v>11</v>
-      </c>
-      <c r="F431" t="s">
+      <c r="A431" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B431" s="3" t="s">
         <v>765</v>
+      </c>
+      <c r="C431" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="D431" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E431" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F431" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G431" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="432" spans="1:7">
-      <c r="A432" t="s">
+      <c r="A432" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="B432" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="B432" t="s">
-        <v>767</v>
-      </c>
-      <c r="C432" t="s">
-        <v>328</v>
-      </c>
-      <c r="D432" t="s">
-        <v>19</v>
-      </c>
-      <c r="E432" t="s">
-        <v>42</v>
-      </c>
-      <c r="F432" t="s">
-        <v>747</v>
+      <c r="C432" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D432" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E432" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F432" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G432" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="433" spans="1:7">
-      <c r="A433" t="s">
-        <v>766</v>
-      </c>
-      <c r="B433" t="s">
-        <v>768</v>
-      </c>
-      <c r="C433" t="s">
-        <v>328</v>
-      </c>
-      <c r="D433" t="s">
-        <v>19</v>
-      </c>
-      <c r="E433" t="s">
+      <c r="A433" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="B433" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="C433" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D433" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E433" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F433" t="s">
-        <v>747</v>
+      <c r="F433" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G433" t="s">
         <v>655</v>
@@ -14214,22 +14229,22 @@
     </row>
     <row r="434" spans="1:7">
       <c r="A434" t="s">
-        <v>766</v>
+        <v>688</v>
       </c>
       <c r="B434" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C434" t="s">
-        <v>673</v>
+        <v>548</v>
       </c>
       <c r="D434" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E434" t="s">
         <v>55</v>
       </c>
       <c r="F434" t="s">
-        <v>728</v>
+        <v>690</v>
       </c>
       <c r="G434" t="s">
         <v>657</v>
@@ -14237,59 +14252,59 @@
     </row>
     <row r="435" spans="1:7">
       <c r="A435" t="s">
-        <v>766</v>
+        <v>691</v>
       </c>
       <c r="B435" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C435" t="s">
-        <v>673</v>
+        <v>548</v>
       </c>
       <c r="D435" t="s">
         <v>23</v>
       </c>
       <c r="E435" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F435" t="s">
-        <v>728</v>
+        <v>690</v>
       </c>
       <c r="G435" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="436" spans="1:7">
       <c r="A436" t="s">
-        <v>771</v>
+        <v>683</v>
       </c>
       <c r="B436" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C436" t="s">
         <v>328</v>
       </c>
       <c r="D436" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E436" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F436" t="s">
-        <v>728</v>
+        <v>747</v>
       </c>
       <c r="G436" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="437" spans="1:7">
       <c r="A437" t="s">
-        <v>771</v>
+        <v>683</v>
       </c>
       <c r="B437" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C437" t="s">
-        <v>328</v>
+        <v>685</v>
       </c>
       <c r="D437" t="s">
         <v>23</v>
@@ -14298,329 +14313,329 @@
         <v>55</v>
       </c>
       <c r="F437" t="s">
-        <v>747</v>
+        <v>686</v>
       </c>
       <c r="G437" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="438" spans="1:7">
       <c r="A438" t="s">
-        <v>771</v>
+        <v>687</v>
       </c>
       <c r="B438" t="s">
         <v>769</v>
       </c>
       <c r="C438" t="s">
-        <v>673</v>
+        <v>328</v>
       </c>
       <c r="D438" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E438" t="s">
         <v>55</v>
       </c>
       <c r="F438" t="s">
-        <v>728</v>
+        <v>747</v>
       </c>
       <c r="G438" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="439" spans="1:7">
       <c r="A439" t="s">
-        <v>771</v>
+        <v>687</v>
       </c>
       <c r="B439" t="s">
         <v>770</v>
       </c>
       <c r="C439" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="D439" t="s">
         <v>19</v>
       </c>
       <c r="E439" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F439" t="s">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="G439" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="440" spans="1:7">
       <c r="A440" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="B440" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C440" t="s">
-        <v>9</v>
+        <v>290</v>
       </c>
       <c r="D440" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E440" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F440" t="s">
-        <v>728</v>
+        <v>690</v>
       </c>
       <c r="G440" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="441" spans="1:7">
       <c r="A441" t="s">
+        <v>754</v>
+      </c>
+      <c r="B441" t="s">
         <v>772</v>
       </c>
-      <c r="B441" t="s">
-        <v>774</v>
-      </c>
       <c r="C441" t="s">
-        <v>83</v>
+        <v>730</v>
       </c>
       <c r="D441" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E441" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F441" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G441" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="442" spans="1:7">
       <c r="A442" t="s">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="B442" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C442" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D442" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E442" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F442" t="s">
-        <v>728</v>
+        <v>690</v>
       </c>
       <c r="G442" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="443" spans="1:7">
       <c r="A443" t="s">
+        <v>756</v>
+      </c>
+      <c r="B443" t="s">
         <v>772</v>
       </c>
-      <c r="B443" t="s">
-        <v>777</v>
-      </c>
       <c r="C443" t="s">
-        <v>295</v>
+        <v>730</v>
       </c>
       <c r="D443" t="s">
         <v>27</v>
       </c>
       <c r="E443" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F443" t="s">
-        <v>755</v>
+        <v>773</v>
       </c>
       <c r="G443" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="444" spans="1:7">
       <c r="A444" t="s">
-        <v>778</v>
+        <v>698</v>
       </c>
       <c r="B444" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C444" t="s">
-        <v>9</v>
+        <v>680</v>
       </c>
       <c r="D444" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E444" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F444" t="s">
-        <v>728</v>
+        <v>700</v>
       </c>
       <c r="G444" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="445" spans="1:7">
       <c r="A445" t="s">
-        <v>778</v>
+        <v>701</v>
       </c>
       <c r="B445" t="s">
         <v>774</v>
       </c>
       <c r="C445" t="s">
-        <v>83</v>
+        <v>680</v>
       </c>
       <c r="D445" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E445" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F445" t="s">
+        <v>700</v>
+      </c>
+      <c r="G445" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7">
+      <c r="A446" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="G445" t="s">
+      <c r="B446" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="C446" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D446" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E446" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F446" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G446" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7">
+      <c r="A447" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B447" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="C447" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D447" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E447" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F447" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G447" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="446" spans="1:7">
-      <c r="A446" t="s">
+    <row r="448" spans="1:7">
+      <c r="A448" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B448" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="B446" t="s">
-        <v>776</v>
-      </c>
-      <c r="C446" t="s">
-        <v>295</v>
-      </c>
-      <c r="D446" t="s">
-        <v>19</v>
-      </c>
-      <c r="E446" t="s">
-        <v>42</v>
-      </c>
-      <c r="F446" t="s">
-        <v>728</v>
-      </c>
-      <c r="G446" t="s">
+      <c r="C448" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D448" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E448" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F448" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G448" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
-      <c r="A447" t="s">
-        <v>778</v>
-      </c>
-      <c r="B447" t="s">
-        <v>777</v>
-      </c>
-      <c r="C447" t="s">
-        <v>295</v>
-      </c>
-      <c r="D447" t="s">
-        <v>10</v>
-      </c>
-      <c r="E447" t="s">
-        <v>28</v>
-      </c>
-      <c r="F447" t="s">
-        <v>755</v>
-      </c>
-      <c r="G447" t="s">
+    <row r="449" spans="1:7">
+      <c r="A449" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C449" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D449" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E449" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F449" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G449" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
-      <c r="A448" t="s">
-        <v>779</v>
-      </c>
-      <c r="B448" t="s">
+    <row r="450" spans="1:7">
+      <c r="A450" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B450" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="C448" t="s">
-        <v>290</v>
-      </c>
-      <c r="D448" t="s">
-        <v>19</v>
-      </c>
-      <c r="E448" t="s">
+      <c r="C450" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D450" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="E450" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F448" t="s">
-        <v>755</v>
-      </c>
-      <c r="G448" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="449" spans="1:7">
-      <c r="A449" t="s">
-        <v>779</v>
-      </c>
-      <c r="B449" t="s">
-        <v>781</v>
-      </c>
-      <c r="C449" t="s">
-        <v>290</v>
-      </c>
-      <c r="D449" t="s">
-        <v>23</v>
-      </c>
-      <c r="E449" t="s">
-        <v>55</v>
-      </c>
-      <c r="F449" t="s">
-        <v>755</v>
-      </c>
-      <c r="G449" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="450" spans="1:7">
-      <c r="A450" t="s">
-        <v>779</v>
-      </c>
-      <c r="B450" t="s">
-        <v>782</v>
-      </c>
-      <c r="C450" t="s">
-        <v>727</v>
-      </c>
-      <c r="D450" t="s">
-        <v>10</v>
-      </c>
-      <c r="E450" t="s">
-        <v>55</v>
-      </c>
-      <c r="F450" t="s">
-        <v>783</v>
+      <c r="F450" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G450" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="451" spans="1:7">
-      <c r="A451" t="s">
-        <v>779</v>
-      </c>
-      <c r="B451" t="s">
-        <v>784</v>
-      </c>
-      <c r="C451" t="s">
-        <v>290</v>
-      </c>
-      <c r="D451" t="s">
-        <v>25</v>
-      </c>
-      <c r="E451" t="s">
-        <v>42</v>
-      </c>
-      <c r="F451" t="s">
-        <v>755</v>
+      <c r="A451" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="C451" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D451" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E451" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F451" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="G451" t="s">
         <v>659</v>
@@ -14628,13 +14643,13 @@
     </row>
     <row r="452" spans="1:7">
       <c r="A452" t="s">
-        <v>785</v>
+        <v>688</v>
       </c>
       <c r="B452" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C452" t="s">
-        <v>290</v>
+        <v>187</v>
       </c>
       <c r="D452" t="s">
         <v>23</v>
@@ -14643,7 +14658,7 @@
         <v>62</v>
       </c>
       <c r="F452" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="G452" t="s">
         <v>653</v>
@@ -14651,22 +14666,22 @@
     </row>
     <row r="453" spans="1:7">
       <c r="A453" t="s">
-        <v>785</v>
+        <v>688</v>
       </c>
       <c r="B453" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C453" t="s">
-        <v>290</v>
+        <v>187</v>
       </c>
       <c r="D453" t="s">
         <v>19</v>
       </c>
       <c r="E453" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F453" t="s">
-        <v>755</v>
+        <v>686</v>
       </c>
       <c r="G453" t="s">
         <v>655</v>
@@ -14674,68 +14689,68 @@
     </row>
     <row r="454" spans="1:7">
       <c r="A454" t="s">
-        <v>785</v>
+        <v>691</v>
       </c>
       <c r="B454" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C454" t="s">
-        <v>727</v>
+        <v>187</v>
       </c>
       <c r="D454" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E454" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F454" t="s">
-        <v>783</v>
+        <v>747</v>
       </c>
       <c r="G454" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="455" spans="1:7">
       <c r="A455" t="s">
-        <v>785</v>
+        <v>691</v>
       </c>
       <c r="B455" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C455" t="s">
-        <v>290</v>
+        <v>187</v>
       </c>
       <c r="D455" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E455" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F455" t="s">
-        <v>755</v>
+        <v>686</v>
       </c>
       <c r="G455" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="456" spans="1:7">
       <c r="A456" t="s">
-        <v>712</v>
+        <v>678</v>
       </c>
       <c r="B456" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C456" t="s">
-        <v>197</v>
+        <v>734</v>
       </c>
       <c r="D456" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E456" t="s">
         <v>62</v>
       </c>
       <c r="F456" t="s">
-        <v>715</v>
+        <v>786</v>
       </c>
       <c r="G456" t="s">
         <v>653</v>
@@ -14743,22 +14758,22 @@
     </row>
     <row r="457" spans="1:7">
       <c r="A457" t="s">
-        <v>712</v>
+        <v>678</v>
       </c>
       <c r="B457" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C457" t="s">
-        <v>197</v>
+        <v>323</v>
       </c>
       <c r="D457" t="s">
         <v>23</v>
       </c>
       <c r="E457" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F457" t="s">
-        <v>715</v>
+        <v>788</v>
       </c>
       <c r="G457" t="s">
         <v>655</v>
@@ -14766,68 +14781,68 @@
     </row>
     <row r="458" spans="1:7">
       <c r="A458" t="s">
-        <v>712</v>
+        <v>682</v>
       </c>
       <c r="B458" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="C458" t="s">
-        <v>687</v>
+        <v>734</v>
       </c>
       <c r="D458" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E458" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F458" t="s">
-        <v>715</v>
+        <v>786</v>
       </c>
       <c r="G458" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="459" spans="1:7">
       <c r="A459" t="s">
-        <v>712</v>
+        <v>682</v>
       </c>
       <c r="B459" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C459" t="s">
-        <v>687</v>
+        <v>323</v>
       </c>
       <c r="D459" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E459" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F459" t="s">
-        <v>715</v>
+        <v>788</v>
       </c>
       <c r="G459" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="460" spans="1:7">
       <c r="A460" t="s">
-        <v>718</v>
+        <v>754</v>
       </c>
       <c r="B460" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C460" t="s">
-        <v>197</v>
+        <v>290</v>
       </c>
       <c r="D460" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E460" t="s">
         <v>62</v>
       </c>
       <c r="F460" t="s">
-        <v>715</v>
+        <v>690</v>
       </c>
       <c r="G460" t="s">
         <v>653</v>
@@ -14835,74 +14850,74 @@
     </row>
     <row r="461" spans="1:7">
       <c r="A461" t="s">
-        <v>718</v>
+        <v>756</v>
       </c>
       <c r="B461" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C461" t="s">
-        <v>197</v>
+        <v>290</v>
       </c>
       <c r="D461" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E461" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F461" t="s">
-        <v>715</v>
+        <v>690</v>
       </c>
       <c r="G461" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="462" spans="1:7">
       <c r="A462" t="s">
-        <v>718</v>
+        <v>698</v>
       </c>
       <c r="B462" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C462" t="s">
-        <v>687</v>
+        <v>197</v>
       </c>
       <c r="D462" t="s">
         <v>10</v>
       </c>
       <c r="E462" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F462" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="G462" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>718</v>
+        <v>701</v>
       </c>
       <c r="B463" t="s">
         <v>790</v>
       </c>
       <c r="C463" t="s">
-        <v>687</v>
+        <v>197</v>
       </c>
       <c r="D463" t="s">
         <v>27</v>
       </c>
       <c r="E463" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F463" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="G463" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="464" spans="1:7">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="464" hidden="1" spans="1:7">
       <c r="A464" t="s">
         <v>791</v>
       </c>
@@ -14925,7 +14940,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="465" spans="1:7">
+    <row r="465" hidden="1" spans="1:7">
       <c r="A465" t="s">
         <v>794</v>
       </c>
@@ -14948,7 +14963,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="466" spans="1:7">
+    <row r="466" hidden="1" spans="1:7">
       <c r="A466" t="s">
         <v>797</v>
       </c>
@@ -14971,7 +14986,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="467" spans="1:7">
+    <row r="467" hidden="1" spans="1:7">
       <c r="A467" t="s">
         <v>794</v>
       </c>
@@ -14994,7 +15009,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="468" spans="1:7">
+    <row r="468" hidden="1" spans="1:7">
       <c r="A468" t="s">
         <v>794</v>
       </c>
@@ -15017,7 +15032,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="469" spans="1:7">
+    <row r="469" hidden="1" spans="1:7">
       <c r="A469" t="s">
         <v>797</v>
       </c>
@@ -15040,7 +15055,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="470" spans="1:7">
+    <row r="470" hidden="1" spans="1:7">
       <c r="A470" t="s">
         <v>794</v>
       </c>
@@ -15063,7 +15078,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="471" spans="1:7">
+    <row r="471" hidden="1" spans="1:7">
       <c r="A471" t="s">
         <v>802</v>
       </c>
@@ -15086,7 +15101,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="472" spans="1:7">
+    <row r="472" hidden="1" spans="1:7">
       <c r="A472" t="s">
         <v>805</v>
       </c>
@@ -15109,7 +15124,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="473" spans="1:7">
+    <row r="473" hidden="1" spans="1:7">
       <c r="A473" t="s">
         <v>807</v>
       </c>
@@ -15117,7 +15132,7 @@
         <v>808</v>
       </c>
       <c r="C473" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D473" t="s">
         <v>27</v>
@@ -15132,7 +15147,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="474" spans="1:7">
+    <row r="474" hidden="1" spans="1:7">
       <c r="A474" t="s">
         <v>809</v>
       </c>
@@ -15155,7 +15170,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="475" spans="1:7">
+    <row r="475" hidden="1" spans="1:7">
       <c r="A475" t="s">
         <v>811</v>
       </c>
@@ -15178,7 +15193,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="476" spans="1:7">
+    <row r="476" hidden="1" spans="1:7">
       <c r="A476" t="s">
         <v>814</v>
       </c>
@@ -15201,7 +15216,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="477" spans="1:7">
+    <row r="477" hidden="1" spans="1:7">
       <c r="A477" t="s">
         <v>816</v>
       </c>
@@ -15224,7 +15239,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="478" spans="1:7">
+    <row r="478" hidden="1" spans="1:7">
       <c r="A478" t="s">
         <v>809</v>
       </c>
@@ -15247,7 +15262,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="479" spans="1:7">
+    <row r="479" hidden="1" spans="1:7">
       <c r="A479" t="s">
         <v>811</v>
       </c>
@@ -15270,7 +15285,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="480" spans="1:7">
+    <row r="480" hidden="1" spans="1:7">
       <c r="A480" t="s">
         <v>818</v>
       </c>
@@ -15293,7 +15308,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="481" spans="1:7">
+    <row r="481" hidden="1" spans="1:7">
       <c r="A481" t="s">
         <v>820</v>
       </c>
@@ -15316,7 +15331,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="482" spans="1:7">
+    <row r="482" hidden="1" spans="1:7">
       <c r="A482" t="s">
         <v>823</v>
       </c>
@@ -15339,7 +15354,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="483" spans="1:7">
+    <row r="483" hidden="1" spans="1:7">
       <c r="A483" t="s">
         <v>802</v>
       </c>
@@ -15362,7 +15377,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="484" spans="1:7">
+    <row r="484" hidden="1" spans="1:7">
       <c r="A484" t="s">
         <v>825</v>
       </c>
@@ -15385,7 +15400,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="485" spans="1:7">
+    <row r="485" hidden="1" spans="1:7">
       <c r="A485" t="s">
         <v>827</v>
       </c>
@@ -15408,7 +15423,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="486" spans="1:7">
+    <row r="486" hidden="1" spans="1:7">
       <c r="A486" t="s">
         <v>830</v>
       </c>
@@ -15431,7 +15446,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="487" spans="1:7">
+    <row r="487" hidden="1" spans="1:7">
       <c r="A487" t="s">
         <v>832</v>
       </c>
@@ -15454,7 +15469,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="488" spans="1:7">
+    <row r="488" hidden="1" spans="1:7">
       <c r="A488" t="s">
         <v>834</v>
       </c>
@@ -15477,7 +15492,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="489" spans="1:7">
+    <row r="489" hidden="1" spans="1:7">
       <c r="A489" t="s">
         <v>832</v>
       </c>
@@ -15500,7 +15515,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="490" spans="1:7">
+    <row r="490" hidden="1" spans="1:7">
       <c r="A490" t="s">
         <v>825</v>
       </c>
@@ -15523,7 +15538,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="491" spans="1:7">
+    <row r="491" hidden="1" spans="1:7">
       <c r="A491" t="s">
         <v>836</v>
       </c>
@@ -15546,7 +15561,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="492" spans="1:7">
+    <row r="492" hidden="1" spans="1:7">
       <c r="A492" t="s">
         <v>839</v>
       </c>
@@ -15569,7 +15584,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="493" spans="1:7">
+    <row r="493" hidden="1" spans="1:7">
       <c r="A493" t="s">
         <v>841</v>
       </c>
@@ -15586,13 +15601,13 @@
         <v>11</v>
       </c>
       <c r="F493" t="s">
-        <v>755</v>
+        <v>690</v>
       </c>
       <c r="G493" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="494" spans="1:7">
+    <row r="494" hidden="1" spans="1:7">
       <c r="A494" t="s">
         <v>843</v>
       </c>
@@ -15615,7 +15630,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="495" spans="1:7">
+    <row r="495" hidden="1" spans="1:7">
       <c r="A495" t="s">
         <v>844</v>
       </c>
@@ -15632,13 +15647,13 @@
         <v>11</v>
       </c>
       <c r="F495" t="s">
-        <v>755</v>
+        <v>690</v>
       </c>
       <c r="G495" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="496" spans="1:7">
+    <row r="496" hidden="1" spans="1:7">
       <c r="A496" t="s">
         <v>845</v>
       </c>
@@ -15661,7 +15676,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="497" spans="1:7">
+    <row r="497" hidden="1" spans="1:7">
       <c r="A497" t="s">
         <v>847</v>
       </c>
@@ -15684,7 +15699,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="498" spans="1:7">
+    <row r="498" hidden="1" spans="1:7">
       <c r="A498" t="s">
         <v>807</v>
       </c>
@@ -15692,7 +15707,7 @@
         <v>849</v>
       </c>
       <c r="C498" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D498" t="s">
         <v>27</v>
@@ -15707,7 +15722,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="499" spans="1:7">
+    <row r="499" hidden="1" spans="1:7">
       <c r="A499" t="s">
         <v>409</v>
       </c>
@@ -15730,7 +15745,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="500" spans="1:7">
+    <row r="500" hidden="1" spans="1:7">
       <c r="A500" t="s">
         <v>851</v>
       </c>
@@ -15753,7 +15768,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="501" spans="1:7">
+    <row r="501" hidden="1" spans="1:7">
       <c r="A501" t="s">
         <v>854</v>
       </c>
@@ -15776,7 +15791,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="502" spans="1:7">
+    <row r="502" hidden="1" spans="1:7">
       <c r="A502" t="s">
         <v>856</v>
       </c>
@@ -15799,7 +15814,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="503" spans="1:7">
+    <row r="503" hidden="1" spans="1:7">
       <c r="A503" t="s">
         <v>858</v>
       </c>
@@ -15822,7 +15837,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="504" spans="1:7">
+    <row r="504" hidden="1" spans="1:7">
       <c r="A504" t="s">
         <v>860</v>
       </c>
@@ -15845,7 +15860,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="505" spans="1:7">
+    <row r="505" hidden="1" spans="1:7">
       <c r="A505" t="s">
         <v>403</v>
       </c>
@@ -15868,7 +15883,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="506" spans="1:7">
+    <row r="506" hidden="1" spans="1:7">
       <c r="A506" t="s">
         <v>863</v>
       </c>
@@ -15891,7 +15906,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="507" spans="1:7">
+    <row r="507" hidden="1" spans="1:7">
       <c r="A507" t="s">
         <v>865</v>
       </c>
@@ -15914,7 +15929,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="508" spans="1:7">
+    <row r="508" hidden="1" spans="1:7">
       <c r="A508" t="s">
         <v>867</v>
       </c>
@@ -15937,7 +15952,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="509" spans="1:7">
+    <row r="509" hidden="1" spans="1:7">
       <c r="A509" t="s">
         <v>869</v>
       </c>
@@ -15960,7 +15975,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="510" spans="1:7">
+    <row r="510" hidden="1" spans="1:7">
       <c r="A510" t="s">
         <v>871</v>
       </c>
@@ -15983,7 +15998,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="511" spans="1:7">
+    <row r="511" hidden="1" spans="1:7">
       <c r="A511" t="s">
         <v>873</v>
       </c>
@@ -16006,7 +16021,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="512" spans="1:7">
+    <row r="512" hidden="1" spans="1:7">
       <c r="A512" t="s">
         <v>368</v>
       </c>
@@ -16029,7 +16044,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="513" spans="1:7">
+    <row r="513" hidden="1" spans="1:7">
       <c r="A513" t="s">
         <v>878</v>
       </c>
@@ -16052,7 +16067,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="514" spans="1:7">
+    <row r="514" hidden="1" spans="1:7">
       <c r="A514" t="s">
         <v>880</v>
       </c>
@@ -16075,7 +16090,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="515" spans="1:7">
+    <row r="515" hidden="1" spans="1:7">
       <c r="A515" t="s">
         <v>882</v>
       </c>
@@ -16098,7 +16113,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="516" spans="1:7">
+    <row r="516" hidden="1" spans="1:7">
       <c r="A516" t="s">
         <v>807</v>
       </c>
@@ -16106,7 +16121,7 @@
         <v>884</v>
       </c>
       <c r="C516" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D516" t="s">
         <v>27</v>
@@ -16121,7 +16136,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="517" spans="1:7">
+    <row r="517" hidden="1" spans="1:7">
       <c r="A517" t="s">
         <v>347</v>
       </c>
@@ -16144,7 +16159,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="518" spans="1:7">
+    <row r="518" hidden="1" spans="1:7">
       <c r="A518" t="s">
         <v>886</v>
       </c>
@@ -16167,7 +16182,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="519" spans="1:7">
+    <row r="519" hidden="1" spans="1:7">
       <c r="A519" t="s">
         <v>888</v>
       </c>
@@ -16190,7 +16205,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="520" spans="1:7">
+    <row r="520" hidden="1" spans="1:7">
       <c r="A520" t="s">
         <v>791</v>
       </c>
@@ -16213,7 +16228,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="521" spans="1:7">
+    <row r="521" hidden="1" spans="1:7">
       <c r="A521" t="s">
         <v>891</v>
       </c>
@@ -16221,7 +16236,7 @@
         <v>892</v>
       </c>
       <c r="C521" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D521" t="s">
         <v>27</v>
@@ -16236,7 +16251,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="522" spans="1:7">
+    <row r="522" hidden="1" spans="1:7">
       <c r="A522" t="s">
         <v>893</v>
       </c>
@@ -16259,7 +16274,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="523" spans="1:7">
+    <row r="523" hidden="1" spans="1:7">
       <c r="A523" t="s">
         <v>895</v>
       </c>
@@ -16282,7 +16297,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="524" spans="1:7">
+    <row r="524" hidden="1" spans="1:7">
       <c r="A524" t="s">
         <v>897</v>
       </c>
@@ -16305,7 +16320,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="525" spans="1:7">
+    <row r="525" hidden="1" spans="1:7">
       <c r="A525" t="s">
         <v>899</v>
       </c>
@@ -16328,7 +16343,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="526" spans="1:7">
+    <row r="526" hidden="1" spans="1:7">
       <c r="A526" t="s">
         <v>901</v>
       </c>
@@ -16351,7 +16366,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="527" spans="1:7">
+    <row r="527" hidden="1" spans="1:7">
       <c r="A527" t="s">
         <v>903</v>
       </c>
@@ -16359,7 +16374,7 @@
         <v>904</v>
       </c>
       <c r="C527" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D527" t="s">
         <v>19</v>
@@ -16374,7 +16389,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="528" spans="1:7">
+    <row r="528" hidden="1" spans="1:7">
       <c r="A528" t="s">
         <v>906</v>
       </c>
@@ -16397,7 +16412,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="529" spans="1:7">
+    <row r="529" hidden="1" spans="1:7">
       <c r="A529" t="s">
         <v>909</v>
       </c>
@@ -16405,7 +16420,7 @@
         <v>904</v>
       </c>
       <c r="C529" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D529" t="s">
         <v>23</v>
@@ -16420,7 +16435,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="530" spans="1:7">
+    <row r="530" hidden="1" spans="1:7">
       <c r="A530" t="s">
         <v>911</v>
       </c>
@@ -16443,7 +16458,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="531" spans="1:7">
+    <row r="531" hidden="1" spans="1:7">
       <c r="A531" t="s">
         <v>912</v>
       </c>
@@ -16466,7 +16481,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="532" spans="1:7">
+    <row r="532" hidden="1" spans="1:7">
       <c r="A532" t="s">
         <v>913</v>
       </c>
@@ -16489,7 +16504,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="533" spans="1:7">
+    <row r="533" hidden="1" spans="1:7">
       <c r="A533" t="s">
         <v>917</v>
       </c>
@@ -16512,7 +16527,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="534" spans="1:7">
+    <row r="534" hidden="1" spans="1:7">
       <c r="A534" t="s">
         <v>920</v>
       </c>
@@ -16535,7 +16550,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="535" spans="1:7">
+    <row r="535" hidden="1" spans="1:7">
       <c r="A535" t="s">
         <v>921</v>
       </c>
@@ -16558,7 +16573,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="536" spans="1:7">
+    <row r="536" hidden="1" spans="1:7">
       <c r="A536" t="s">
         <v>923</v>
       </c>
@@ -16581,7 +16596,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="537" spans="1:7">
+    <row r="537" hidden="1" spans="1:7">
       <c r="A537" t="s">
         <v>925</v>
       </c>
@@ -16589,7 +16604,7 @@
         <v>926</v>
       </c>
       <c r="C537" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D537" t="s">
         <v>27</v>
@@ -16604,7 +16619,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="538" spans="1:7">
+    <row r="538" hidden="1" spans="1:7">
       <c r="A538" t="s">
         <v>927</v>
       </c>
@@ -16627,7 +16642,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="539" spans="1:7">
+    <row r="539" hidden="1" spans="1:7">
       <c r="A539" t="s">
         <v>931</v>
       </c>
@@ -16650,7 +16665,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="540" spans="1:7">
+    <row r="540" hidden="1" spans="1:7">
       <c r="A540" t="s">
         <v>934</v>
       </c>
@@ -16658,7 +16673,7 @@
         <v>935</v>
       </c>
       <c r="C540" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D540" t="s">
         <v>19</v>
@@ -16673,7 +16688,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="541" spans="1:7">
+    <row r="541" hidden="1" spans="1:7">
       <c r="A541" t="s">
         <v>936</v>
       </c>
@@ -16681,7 +16696,7 @@
         <v>937</v>
       </c>
       <c r="C541" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D541" t="s">
         <v>23</v>
@@ -16696,7 +16711,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="542" spans="1:7">
+    <row r="542" hidden="1" spans="1:7">
       <c r="A542" t="s">
         <v>938</v>
       </c>
@@ -16704,7 +16719,7 @@
         <v>939</v>
       </c>
       <c r="C542" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="D542" t="s">
         <v>25</v>
@@ -16719,7 +16734,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="543" spans="1:7">
+    <row r="543" hidden="1" spans="1:7">
       <c r="A543" t="s">
         <v>940</v>
       </c>
@@ -16742,7 +16757,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="544" spans="1:7">
+    <row r="544" hidden="1" spans="1:7">
       <c r="A544" t="s">
         <v>941</v>
       </c>
@@ -16765,7 +16780,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="545" spans="1:7">
+    <row r="545" hidden="1" spans="1:7">
       <c r="A545" t="s">
         <v>942</v>
       </c>
@@ -16788,7 +16803,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="546" spans="1:7">
+    <row r="546" hidden="1" spans="1:7">
       <c r="A546" t="s">
         <v>944</v>
       </c>
@@ -16796,7 +16811,7 @@
         <v>945</v>
       </c>
       <c r="C546" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="D546" t="s">
         <v>19</v>
@@ -16811,7 +16826,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="547" spans="1:7">
+    <row r="547" hidden="1" spans="1:7">
       <c r="A547" t="s">
         <v>947</v>
       </c>
@@ -16819,7 +16834,7 @@
         <v>945</v>
       </c>
       <c r="C547" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="D547" t="s">
         <v>23</v>
@@ -16834,7 +16849,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="548" spans="1:7">
+    <row r="548" hidden="1" spans="1:7">
       <c r="A548" t="s">
         <v>948</v>
       </c>
@@ -16857,7 +16872,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="549" spans="1:7">
+    <row r="549" hidden="1" spans="1:7">
       <c r="A549" t="s">
         <v>950</v>
       </c>
@@ -16880,7 +16895,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="550" spans="1:7">
+    <row r="550" hidden="1" spans="1:7">
       <c r="A550" t="s">
         <v>952</v>
       </c>
@@ -16888,7 +16903,7 @@
         <v>953</v>
       </c>
       <c r="C550" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D550" t="s">
         <v>19</v>
@@ -16903,7 +16918,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="551" spans="1:7">
+    <row r="551" hidden="1" spans="1:7">
       <c r="A551" t="s">
         <v>955</v>
       </c>
@@ -16911,7 +16926,7 @@
         <v>953</v>
       </c>
       <c r="C551" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D551" t="s">
         <v>19</v>
@@ -16926,7 +16941,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="552" spans="1:7">
+    <row r="552" hidden="1" spans="1:7">
       <c r="A552" t="s">
         <v>952</v>
       </c>
@@ -16949,7 +16964,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="553" spans="1:7">
+    <row r="553" hidden="1" spans="1:7">
       <c r="A553" t="s">
         <v>955</v>
       </c>
@@ -16972,7 +16987,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="554" spans="1:7">
+    <row r="554" hidden="1" spans="1:7">
       <c r="A554" t="s">
         <v>791</v>
       </c>
@@ -16995,7 +17010,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="555" spans="1:7">
+    <row r="555" hidden="1" spans="1:7">
       <c r="A555" t="s">
         <v>958</v>
       </c>
@@ -17003,7 +17018,7 @@
         <v>959</v>
       </c>
       <c r="C555" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="D555" t="s">
         <v>27</v>
@@ -17018,7 +17033,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="556" spans="1:7">
+    <row r="556" hidden="1" spans="1:7">
       <c r="A556" t="s">
         <v>791</v>
       </c>
@@ -17041,7 +17056,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="557" spans="1:7">
+    <row r="557" hidden="1" spans="1:7">
       <c r="A557" t="s">
         <v>962</v>
       </c>
@@ -17064,7 +17079,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="558" spans="1:7">
+    <row r="558" hidden="1" spans="1:7">
       <c r="A558" t="s">
         <v>964</v>
       </c>
@@ -17087,7 +17102,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="559" spans="1:7">
+    <row r="559" hidden="1" spans="1:7">
       <c r="A559" t="s">
         <v>368</v>
       </c>
@@ -17110,7 +17125,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="560" spans="1:7">
+    <row r="560" hidden="1" spans="1:7">
       <c r="A560" t="s">
         <v>347</v>
       </c>
@@ -17133,7 +17148,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="561" spans="1:7">
+    <row r="561" hidden="1" spans="1:7">
       <c r="A561" t="s">
         <v>807</v>
       </c>
@@ -17141,7 +17156,7 @@
         <v>967</v>
       </c>
       <c r="C561" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D561" t="s">
         <v>27</v>
@@ -17156,7 +17171,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="562" spans="1:7">
+    <row r="562" hidden="1" spans="1:7">
       <c r="A562" t="s">
         <v>820</v>
       </c>
@@ -17164,7 +17179,7 @@
         <v>968</v>
       </c>
       <c r="C562" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="D562" t="s">
         <v>10</v>
@@ -17179,7 +17194,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="563" spans="1:7">
+    <row r="563" hidden="1" spans="1:7">
       <c r="A563" t="s">
         <v>969</v>
       </c>
@@ -17202,7 +17217,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="564" spans="1:7">
+    <row r="564" hidden="1" spans="1:7">
       <c r="A564" t="s">
         <v>971</v>
       </c>
@@ -17225,7 +17240,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="565" spans="1:7">
+    <row r="565" hidden="1" spans="1:7">
       <c r="A565" t="s">
         <v>973</v>
       </c>
@@ -17233,7 +17248,7 @@
         <v>974</v>
       </c>
       <c r="C565" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D565" t="s">
         <v>25</v>
@@ -17248,7 +17263,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="566" spans="1:7">
+    <row r="566" hidden="1" spans="1:7">
       <c r="A566" t="s">
         <v>975</v>
       </c>
@@ -17271,7 +17286,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="567" spans="1:7">
+    <row r="567" hidden="1" spans="1:7">
       <c r="A567" t="s">
         <v>978</v>
       </c>
@@ -17279,7 +17294,7 @@
         <v>974</v>
       </c>
       <c r="C567" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D567" t="s">
         <v>27</v>
@@ -17294,7 +17309,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="568" spans="1:7">
+    <row r="568" hidden="1" spans="1:7">
       <c r="A568" t="s">
         <v>979</v>
       </c>
@@ -17317,7 +17332,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="569" spans="1:7">
+    <row r="569" hidden="1" spans="1:7">
       <c r="A569" t="s">
         <v>980</v>
       </c>
@@ -17340,7 +17355,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="570" spans="1:7">
+    <row r="570" hidden="1" spans="1:7">
       <c r="A570" t="s">
         <v>982</v>
       </c>
@@ -17363,7 +17378,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="571" spans="1:7">
+    <row r="571" hidden="1" spans="1:7">
       <c r="A571" t="s">
         <v>984</v>
       </c>
@@ -17386,7 +17401,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="572" spans="1:7">
+    <row r="572" hidden="1" spans="1:7">
       <c r="A572" t="s">
         <v>416</v>
       </c>
@@ -17409,7 +17424,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="573" spans="1:7">
+    <row r="573" hidden="1" spans="1:7">
       <c r="A573" t="s">
         <v>987</v>
       </c>
@@ -17432,7 +17447,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="574" spans="1:7">
+    <row r="574" hidden="1" spans="1:7">
       <c r="A574" t="s">
         <v>989</v>
       </c>
@@ -17455,7 +17470,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="575" spans="1:7">
+    <row r="575" hidden="1" spans="1:7">
       <c r="A575" t="s">
         <v>991</v>
       </c>
@@ -17478,7 +17493,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="576" spans="1:7">
+    <row r="576" hidden="1" spans="1:7">
       <c r="A576" t="s">
         <v>110</v>
       </c>
@@ -17501,7 +17516,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="577" spans="1:7">
+    <row r="577" hidden="1" spans="1:7">
       <c r="A577" t="s">
         <v>110</v>
       </c>
@@ -17524,7 +17539,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="578" spans="1:7">
+    <row r="578" hidden="1" spans="1:7">
       <c r="A578" t="s">
         <v>113</v>
       </c>
@@ -17547,7 +17562,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="579" spans="1:7">
+    <row r="579" hidden="1" spans="1:7">
       <c r="A579" t="s">
         <v>110</v>
       </c>
@@ -17570,7 +17585,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="580" spans="1:7">
+    <row r="580" hidden="1" spans="1:7">
       <c r="A580" t="s">
         <v>1000</v>
       </c>
@@ -17593,7 +17608,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="581" spans="1:7">
+    <row r="581" hidden="1" spans="1:7">
       <c r="A581" t="s">
         <v>113</v>
       </c>
@@ -17616,7 +17631,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="582" spans="1:7">
+    <row r="582" hidden="1" spans="1:7">
       <c r="A582" t="s">
         <v>117</v>
       </c>
@@ -17639,7 +17654,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="583" spans="1:7">
+    <row r="583" hidden="1" spans="1:7">
       <c r="A583" t="s">
         <v>110</v>
       </c>
@@ -17662,7 +17677,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="584" spans="1:7">
+    <row r="584" hidden="1" spans="1:7">
       <c r="A584" t="s">
         <v>113</v>
       </c>
@@ -17685,7 +17700,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="585" spans="1:7">
+    <row r="585" hidden="1" spans="1:7">
       <c r="A585" t="s">
         <v>1005</v>
       </c>
@@ -17708,7 +17723,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="586" spans="1:7">
+    <row r="586" hidden="1" spans="1:7">
       <c r="A586" t="s">
         <v>1008</v>
       </c>
@@ -17731,7 +17746,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="587" spans="1:7">
+    <row r="587" hidden="1" spans="1:7">
       <c r="A587" t="s">
         <v>1005</v>
       </c>
@@ -17754,7 +17769,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="588" spans="1:7">
+    <row r="588" hidden="1" spans="1:7">
       <c r="A588" t="s">
         <v>1008</v>
       </c>
@@ -17777,7 +17792,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="589" spans="1:7">
+    <row r="589" hidden="1" spans="1:7">
       <c r="A589" t="s">
         <v>1012</v>
       </c>
@@ -17800,7 +17815,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="590" spans="1:7">
+    <row r="590" hidden="1" spans="1:7">
       <c r="A590" t="s">
         <v>130</v>
       </c>
@@ -17823,7 +17838,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="591" spans="1:7">
+    <row r="591" hidden="1" spans="1:7">
       <c r="A591" t="s">
         <v>1012</v>
       </c>
@@ -17846,7 +17861,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="592" spans="1:7">
+    <row r="592" hidden="1" spans="1:7">
       <c r="A592" t="s">
         <v>1005</v>
       </c>
@@ -17869,7 +17884,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="593" spans="1:7">
+    <row r="593" hidden="1" spans="1:7">
       <c r="A593" t="s">
         <v>1008</v>
       </c>
@@ -17892,7 +17907,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="594" spans="1:7">
+    <row r="594" hidden="1" spans="1:7">
       <c r="A594" t="s">
         <v>1012</v>
       </c>
@@ -17915,7 +17930,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="595" spans="1:7">
+    <row r="595" hidden="1" spans="1:7">
       <c r="A595" t="s">
         <v>1005</v>
       </c>
@@ -17938,7 +17953,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="596" spans="1:7">
+    <row r="596" hidden="1" spans="1:7">
       <c r="A596" t="s">
         <v>1008</v>
       </c>
@@ -17961,7 +17976,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="597" spans="1:7">
+    <row r="597" hidden="1" spans="1:7">
       <c r="A597" t="s">
         <v>1012</v>
       </c>
@@ -17984,7 +17999,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="598" spans="1:7">
+    <row r="598" hidden="1" spans="1:7">
       <c r="A598" t="s">
         <v>578</v>
       </c>
@@ -18007,7 +18022,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="599" spans="1:7">
+    <row r="599" hidden="1" spans="1:7">
       <c r="A599" t="s">
         <v>110</v>
       </c>
@@ -18030,7 +18045,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="600" spans="1:7">
+    <row r="600" hidden="1" spans="1:7">
       <c r="A600" t="s">
         <v>1024</v>
       </c>
@@ -18053,7 +18068,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="601" spans="1:7">
+    <row r="601" hidden="1" spans="1:7">
       <c r="A601" t="s">
         <v>1012</v>
       </c>
@@ -18076,7 +18091,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="602" spans="1:7">
+    <row r="602" hidden="1" spans="1:7">
       <c r="A602" t="s">
         <v>1005</v>
       </c>
@@ -18099,7 +18114,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="603" spans="1:7">
+    <row r="603" hidden="1" spans="1:7">
       <c r="A603" t="s">
         <v>1024</v>
       </c>
@@ -18122,7 +18137,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="604" spans="1:7">
+    <row r="604" hidden="1" spans="1:7">
       <c r="A604" t="s">
         <v>1012</v>
       </c>
@@ -18145,7 +18160,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="605" spans="1:7">
+    <row r="605" hidden="1" spans="1:7">
       <c r="A605" t="s">
         <v>1005</v>
       </c>
@@ -18168,7 +18183,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="606" spans="1:7">
+    <row r="606" hidden="1" spans="1:7">
       <c r="A606" t="s">
         <v>123</v>
       </c>
@@ -18191,7 +18206,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="607" spans="1:7">
+    <row r="607" hidden="1" spans="1:7">
       <c r="A607" t="s">
         <v>1024</v>
       </c>
@@ -18214,7 +18229,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="608" spans="1:7">
+    <row r="608" hidden="1" spans="1:7">
       <c r="A608" t="s">
         <v>113</v>
       </c>
@@ -18237,7 +18252,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="609" spans="1:7">
+    <row r="609" hidden="1" spans="1:7">
       <c r="A609" t="s">
         <v>1032</v>
       </c>
@@ -18260,7 +18275,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="610" spans="1:7">
+    <row r="610" hidden="1" spans="1:7">
       <c r="A610" t="s">
         <v>110</v>
       </c>
@@ -18283,7 +18298,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="611" spans="1:7">
+    <row r="611" hidden="1" spans="1:7">
       <c r="A611" t="s">
         <v>1000</v>
       </c>
@@ -18306,7 +18321,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="612" spans="1:7">
+    <row r="612" hidden="1" spans="1:7">
       <c r="A612" t="s">
         <v>567</v>
       </c>
@@ -18329,7 +18344,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="613" spans="1:7">
+    <row r="613" hidden="1" spans="1:7">
       <c r="A613" t="s">
         <v>88</v>
       </c>
@@ -18352,7 +18367,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="614" spans="1:7">
+    <row r="614" hidden="1" spans="1:7">
       <c r="A614" t="s">
         <v>1000</v>
       </c>
@@ -18375,7 +18390,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="615" spans="1:7">
+    <row r="615" hidden="1" spans="1:7">
       <c r="A615" t="s">
         <v>567</v>
       </c>
@@ -18398,7 +18413,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="616" spans="1:7">
+    <row r="616" hidden="1" spans="1:7">
       <c r="A616" t="s">
         <v>88</v>
       </c>
@@ -18421,7 +18436,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="617" spans="1:7">
+    <row r="617" hidden="1" spans="1:7">
       <c r="A617" t="s">
         <v>554</v>
       </c>
@@ -18444,7 +18459,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="618" spans="1:7">
+    <row r="618" hidden="1" spans="1:7">
       <c r="A618" t="s">
         <v>76</v>
       </c>
@@ -18467,7 +18482,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="619" spans="1:7">
+    <row r="619" hidden="1" spans="1:7">
       <c r="A619" t="s">
         <v>1024</v>
       </c>
@@ -18490,7 +18505,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="620" spans="1:7">
+    <row r="620" hidden="1" spans="1:7">
       <c r="A620" t="s">
         <v>130</v>
       </c>
@@ -18513,7 +18528,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="621" spans="1:7">
+    <row r="621" hidden="1" spans="1:7">
       <c r="A621" t="s">
         <v>130</v>
       </c>
@@ -18536,7 +18551,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="622" spans="1:7">
+    <row r="622" hidden="1" spans="1:7">
       <c r="A622" t="s">
         <v>130</v>
       </c>
@@ -18559,7 +18574,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="623" spans="1:7">
+    <row r="623" hidden="1" spans="1:7">
       <c r="A623" t="s">
         <v>110</v>
       </c>
@@ -18582,7 +18597,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="624" spans="1:7">
+    <row r="624" hidden="1" spans="1:7">
       <c r="A624" t="s">
         <v>567</v>
       </c>
@@ -18605,7 +18620,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="625" spans="1:7">
+    <row r="625" hidden="1" spans="1:7">
       <c r="A625" t="s">
         <v>130</v>
       </c>
@@ -18628,7 +18643,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="626" spans="1:7">
+    <row r="626" hidden="1" spans="1:7">
       <c r="A626" t="s">
         <v>567</v>
       </c>
@@ -18651,7 +18666,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="627" spans="1:7">
+    <row r="627" hidden="1" spans="1:7">
       <c r="A627" t="s">
         <v>110</v>
       </c>
@@ -18674,7 +18689,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="628" spans="1:7">
+    <row r="628" hidden="1" spans="1:7">
       <c r="A628" t="s">
         <v>1045</v>
       </c>
@@ -18697,7 +18712,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="629" spans="1:7">
+    <row r="629" hidden="1" spans="1:7">
       <c r="A629" t="s">
         <v>1047</v>
       </c>
@@ -18720,7 +18735,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="630" spans="1:7">
+    <row r="630" hidden="1" spans="1:7">
       <c r="A630" t="s">
         <v>1050</v>
       </c>
@@ -18743,7 +18758,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="631" spans="1:7">
+    <row r="631" hidden="1" spans="1:7">
       <c r="A631" t="s">
         <v>1052</v>
       </c>
@@ -18766,7 +18781,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="632" spans="1:7">
+    <row r="632" hidden="1" spans="1:7">
       <c r="A632" t="s">
         <v>613</v>
       </c>
@@ -18789,7 +18804,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="633" spans="1:7">
+    <row r="633" hidden="1" spans="1:7">
       <c r="A633" t="s">
         <v>589</v>
       </c>
@@ -18812,7 +18827,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="634" spans="1:7">
+    <row r="634" hidden="1" spans="1:7">
       <c r="A634" t="s">
         <v>1056</v>
       </c>
@@ -18835,7 +18850,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="635" spans="1:7">
+    <row r="635" hidden="1" spans="1:7">
       <c r="A635" t="s">
         <v>1058</v>
       </c>
@@ -18858,7 +18873,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="636" spans="1:7">
+    <row r="636" hidden="1" spans="1:7">
       <c r="A636" t="s">
         <v>1060</v>
       </c>
@@ -18881,7 +18896,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="637" spans="1:7">
+    <row r="637" hidden="1" spans="1:7">
       <c r="A637" t="s">
         <v>1060</v>
       </c>
@@ -18904,7 +18919,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="638" spans="1:7">
+    <row r="638" hidden="1" spans="1:7">
       <c r="A638" t="s">
         <v>1063</v>
       </c>
@@ -18927,7 +18942,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="639" spans="1:7">
+    <row r="639" hidden="1" spans="1:7">
       <c r="A639" t="s">
         <v>179</v>
       </c>
@@ -18950,7 +18965,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="640" spans="1:7">
+    <row r="640" hidden="1" spans="1:7">
       <c r="A640" t="s">
         <v>1066</v>
       </c>
@@ -18973,7 +18988,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="641" spans="1:7">
+    <row r="641" hidden="1" spans="1:7">
       <c r="A641" t="s">
         <v>607</v>
       </c>
@@ -18996,7 +19011,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="642" spans="1:7">
+    <row r="642" hidden="1" spans="1:7">
       <c r="A642" t="s">
         <v>1070</v>
       </c>
@@ -19019,7 +19034,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="643" spans="1:7">
+    <row r="643" hidden="1" spans="1:7">
       <c r="A643" t="s">
         <v>607</v>
       </c>
@@ -19042,7 +19057,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="644" spans="1:7">
+    <row r="644" hidden="1" spans="1:7">
       <c r="A644" t="s">
         <v>1070</v>
       </c>
@@ -19065,7 +19080,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="645" spans="1:7">
+    <row r="645" hidden="1" spans="1:7">
       <c r="A645" t="s">
         <v>165</v>
       </c>
@@ -19088,7 +19103,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="646" spans="1:7">
+    <row r="646" hidden="1" spans="1:7">
       <c r="A646" t="s">
         <v>1073</v>
       </c>
@@ -19111,7 +19126,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="647" spans="1:7">
+    <row r="647" hidden="1" spans="1:7">
       <c r="A647" t="s">
         <v>171</v>
       </c>
@@ -19134,7 +19149,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="648" spans="1:7">
+    <row r="648" hidden="1" spans="1:7">
       <c r="A648" t="s">
         <v>596</v>
       </c>
@@ -19157,7 +19172,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="649" spans="1:7">
+    <row r="649" hidden="1" spans="1:7">
       <c r="A649" t="s">
         <v>1073</v>
       </c>
@@ -19180,7 +19195,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="650" spans="1:7">
+    <row r="650" hidden="1" spans="1:7">
       <c r="A650" t="s">
         <v>171</v>
       </c>
@@ -19203,7 +19218,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="651" spans="1:7">
+    <row r="651" hidden="1" spans="1:7">
       <c r="A651" t="s">
         <v>596</v>
       </c>
@@ -19228,8 +19243,16 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="M1ER"/>
+        <filter val="M1CE"/>
+        <filter val="M1ME"/>
+        <filter val="M1RE"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A2:G651">
-      <sortCondition ref="A1"/>
+      <sortCondition ref="E1"/>
     </sortState>
     <extLst/>
   </autoFilter>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -12295,7 +12295,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" hidden="1" spans="1:7">
       <c r="A350" s="1" t="s">
         <v>326</v>
       </c>
@@ -12318,7 +12318,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" hidden="1" spans="1:7">
       <c r="A351" s="1" t="s">
         <v>326</v>
       </c>
@@ -12341,7 +12341,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" hidden="1" spans="1:7">
       <c r="A352" s="1" t="s">
         <v>326</v>
       </c>
@@ -12364,7 +12364,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" hidden="1" spans="1:7">
       <c r="A353" s="1" t="s">
         <v>326</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" hidden="1" spans="1:7">
       <c r="A354" s="1" t="s">
         <v>660</v>
       </c>
@@ -12410,7 +12410,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" hidden="1" spans="1:7">
       <c r="A355" s="1" t="s">
         <v>660</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" hidden="1" spans="1:7">
       <c r="A356" s="1" t="s">
         <v>660</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" hidden="1" spans="1:7">
       <c r="A357" s="1" t="s">
         <v>660</v>
       </c>
@@ -12479,7 +12479,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" hidden="1" spans="1:7">
       <c r="A358" s="1" t="s">
         <v>665</v>
       </c>
@@ -12502,7 +12502,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" hidden="1" spans="1:7">
       <c r="A359" s="1" t="s">
         <v>665</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" hidden="1" spans="1:7">
       <c r="A360" s="1" t="s">
         <v>665</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" hidden="1" spans="1:7">
       <c r="A361" s="1" t="s">
         <v>665</v>
       </c>
@@ -12571,7 +12571,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" hidden="1" spans="1:7">
       <c r="A362" s="3" t="s">
         <v>349</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" hidden="1" spans="1:7">
       <c r="A363" s="3" t="s">
         <v>349</v>
       </c>
@@ -12617,7 +12617,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" hidden="1" spans="1:7">
       <c r="A364" s="3" t="s">
         <v>349</v>
       </c>
@@ -12640,7 +12640,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" hidden="1" spans="1:7">
       <c r="A365" s="3" t="s">
         <v>349</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" hidden="1" spans="1:7">
       <c r="A366" s="3" t="s">
         <v>675</v>
       </c>
@@ -12686,7 +12686,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" hidden="1" spans="1:7">
       <c r="A367" s="3" t="s">
         <v>675</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" hidden="1" spans="1:7">
       <c r="A368" t="s">
         <v>678</v>
       </c>
@@ -12732,7 +12732,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" hidden="1" spans="1:7">
       <c r="A369" t="s">
         <v>682</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" hidden="1" spans="1:7">
       <c r="A370" t="s">
         <v>683</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" hidden="1" spans="1:7">
       <c r="A371" t="s">
         <v>687</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" hidden="1" spans="1:7">
       <c r="A372" t="s">
         <v>688</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" hidden="1" spans="1:7">
       <c r="A373" t="s">
         <v>691</v>
       </c>
@@ -12847,7 +12847,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" hidden="1" spans="1:7">
       <c r="A374" t="s">
         <v>692</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" hidden="1" spans="1:7">
       <c r="A375" t="s">
         <v>692</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" hidden="1" spans="1:7">
       <c r="A376" t="s">
         <v>692</v>
       </c>
@@ -12916,7 +12916,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" hidden="1" spans="1:7">
       <c r="A377" t="s">
         <v>697</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" hidden="1" spans="1:7">
       <c r="A378" t="s">
         <v>697</v>
       </c>
@@ -12962,7 +12962,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" hidden="1" spans="1:7">
       <c r="A379" t="s">
         <v>697</v>
       </c>
@@ -12985,7 +12985,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" hidden="1" spans="1:7">
       <c r="A380" t="s">
         <v>698</v>
       </c>
@@ -13008,7 +13008,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" hidden="1" spans="1:7">
       <c r="A381" t="s">
         <v>701</v>
       </c>
@@ -13031,7 +13031,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" hidden="1" spans="1:7">
       <c r="A382" s="1" t="s">
         <v>279</v>
       </c>
@@ -13054,7 +13054,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" hidden="1" spans="1:7">
       <c r="A383" s="1" t="s">
         <v>279</v>
       </c>
@@ -13077,7 +13077,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" hidden="1" spans="1:7">
       <c r="A384" s="1" t="s">
         <v>279</v>
       </c>
@@ -13100,7 +13100,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" hidden="1" spans="1:7">
       <c r="A385" s="1" t="s">
         <v>279</v>
       </c>
@@ -13123,7 +13123,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" hidden="1" spans="1:7">
       <c r="A386" s="1" t="s">
         <v>706</v>
       </c>
@@ -13146,7 +13146,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" hidden="1" spans="1:7">
       <c r="A387" s="1" t="s">
         <v>706</v>
       </c>
@@ -13169,7 +13169,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" hidden="1" spans="1:7">
       <c r="A388" s="1" t="s">
         <v>706</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" hidden="1" spans="1:7">
       <c r="A389" s="1" t="s">
         <v>706</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390" s="3" t="s">
         <v>282</v>
       </c>
@@ -13238,7 +13238,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" hidden="1" spans="1:7">
       <c r="A391" s="3" t="s">
         <v>282</v>
       </c>
@@ -13271,11 +13271,11 @@
       <c r="C392" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D392" s="3" t="s">
-        <v>23</v>
+      <c r="D392" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F392" s="4" t="s">
         <v>671</v>
@@ -13294,11 +13294,11 @@
       <c r="C393" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D393" s="3" t="s">
-        <v>23</v>
+      <c r="D393" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F393" s="4" t="s">
         <v>671</v>
@@ -13813,7 +13813,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" hidden="1" spans="1:7">
       <c r="A416" t="s">
         <v>678</v>
       </c>
@@ -13836,7 +13836,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" hidden="1" spans="1:7">
       <c r="A417" t="s">
         <v>682</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" hidden="1" spans="1:7">
       <c r="A420" t="s">
         <v>692</v>
       </c>
@@ -13928,7 +13928,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" hidden="1" spans="1:7">
       <c r="A421" t="s">
         <v>697</v>
       </c>
@@ -13951,7 +13951,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" hidden="1" spans="1:7">
       <c r="A422" t="s">
         <v>754</v>
       </c>
@@ -13974,7 +13974,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" hidden="1" spans="1:7">
       <c r="A423" t="s">
         <v>756</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" hidden="1" spans="1:7">
       <c r="A424" t="s">
         <v>698</v>
       </c>
@@ -14020,7 +14020,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" hidden="1" spans="1:7">
       <c r="A425" t="s">
         <v>701</v>
       </c>
@@ -14043,7 +14043,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" hidden="1" spans="1:7">
       <c r="A426" s="1" t="s">
         <v>759</v>
       </c>
@@ -14066,7 +14066,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" hidden="1" spans="1:7">
       <c r="A427" s="1" t="s">
         <v>759</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" hidden="1" spans="1:7">
       <c r="A428" s="1" t="s">
         <v>759</v>
       </c>
@@ -14112,7 +14112,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" hidden="1" spans="1:7">
       <c r="A429" s="1" t="s">
         <v>759</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" hidden="1" spans="1:7">
       <c r="A430" s="3" t="s">
         <v>713</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" hidden="1" spans="1:7">
       <c r="A431" s="3" t="s">
         <v>713</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" hidden="1" spans="1:7">
       <c r="A432" s="3" t="s">
         <v>675</v>
       </c>
@@ -14204,7 +14204,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" hidden="1" spans="1:7">
       <c r="A433" s="3" t="s">
         <v>675</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" hidden="1" spans="1:7">
       <c r="A434" t="s">
         <v>688</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" hidden="1" spans="1:7">
       <c r="A435" t="s">
         <v>691</v>
       </c>
@@ -14296,7 +14296,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" hidden="1" spans="1:7">
       <c r="A437" t="s">
         <v>683</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" hidden="1" spans="1:7">
       <c r="A439" t="s">
         <v>687</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="440" spans="1:7">
+    <row r="440" hidden="1" spans="1:7">
       <c r="A440" t="s">
         <v>754</v>
       </c>
@@ -14388,7 +14388,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="441" spans="1:7">
+    <row r="441" hidden="1" spans="1:7">
       <c r="A441" t="s">
         <v>754</v>
       </c>
@@ -14411,7 +14411,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" hidden="1" spans="1:7">
       <c r="A442" t="s">
         <v>756</v>
       </c>
@@ -14434,7 +14434,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="443" spans="1:7">
+    <row r="443" hidden="1" spans="1:7">
       <c r="A443" t="s">
         <v>756</v>
       </c>
@@ -14457,7 +14457,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="444" spans="1:7">
+    <row r="444" hidden="1" spans="1:7">
       <c r="A444" t="s">
         <v>698</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="445" spans="1:7">
+    <row r="445" hidden="1" spans="1:7">
       <c r="A445" t="s">
         <v>701</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" hidden="1" spans="1:7">
       <c r="A448" s="1" t="s">
         <v>775</v>
       </c>
@@ -14572,7 +14572,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" hidden="1" spans="1:7">
       <c r="A449" s="1" t="s">
         <v>775</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" hidden="1" spans="1:7">
       <c r="A450" s="3" t="s">
         <v>282</v>
       </c>
@@ -14618,7 +14618,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" hidden="1" spans="1:7">
       <c r="A451" s="3" t="s">
         <v>282</v>
       </c>
@@ -14641,7 +14641,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="452" spans="1:7">
+    <row r="452" hidden="1" spans="1:7">
       <c r="A452" t="s">
         <v>688</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="453" spans="1:7">
+    <row r="453" hidden="1" spans="1:7">
       <c r="A453" t="s">
         <v>688</v>
       </c>
@@ -14687,7 +14687,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="454" spans="1:7">
+    <row r="454" hidden="1" spans="1:7">
       <c r="A454" t="s">
         <v>691</v>
       </c>
@@ -14710,7 +14710,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="455" spans="1:7">
+    <row r="455" hidden="1" spans="1:7">
       <c r="A455" t="s">
         <v>691</v>
       </c>
@@ -14733,7 +14733,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" hidden="1" spans="1:7">
       <c r="A456" t="s">
         <v>678</v>
       </c>
@@ -14756,7 +14756,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="457" spans="1:7">
+    <row r="457" hidden="1" spans="1:7">
       <c r="A457" t="s">
         <v>678</v>
       </c>
@@ -14779,7 +14779,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="458" spans="1:7">
+    <row r="458" hidden="1" spans="1:7">
       <c r="A458" t="s">
         <v>682</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="459" spans="1:7">
+    <row r="459" hidden="1" spans="1:7">
       <c r="A459" t="s">
         <v>682</v>
       </c>
@@ -14825,7 +14825,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" hidden="1" spans="1:7">
       <c r="A460" t="s">
         <v>754</v>
       </c>
@@ -14848,7 +14848,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" hidden="1" spans="1:7">
       <c r="A461" t="s">
         <v>756</v>
       </c>
@@ -14871,7 +14871,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="462" spans="1:7">
+    <row r="462" hidden="1" spans="1:7">
       <c r="A462" t="s">
         <v>698</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="463" spans="1:7">
+    <row r="463" hidden="1" spans="1:7">
       <c r="A463" t="s">
         <v>701</v>
       </c>
@@ -19243,6 +19243,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="AYAD ABDELGHANI"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="6">
       <filters>
         <filter val="M1ER"/>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -12755,7 +12755,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:7">
+    <row r="370" spans="1:7">
       <c r="A370" t="s">
         <v>683</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="371" hidden="1" spans="1:7">
+    <row r="371" spans="1:7">
       <c r="A371" t="s">
         <v>687</v>
       </c>
@@ -13261,7 +13261,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" hidden="1" spans="1:7">
       <c r="A392" s="3" t="s">
         <v>713</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" hidden="1" spans="1:7">
       <c r="A393" s="3" t="s">
         <v>713</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" hidden="1" spans="1:7">
       <c r="A418" t="s">
         <v>683</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" hidden="1" spans="1:7">
       <c r="A419" t="s">
         <v>687</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:7">
+    <row r="430" spans="1:7">
       <c r="A430" s="3" t="s">
         <v>713</v>
       </c>
@@ -14148,8 +14148,8 @@
       <c r="D430" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E430" s="3" t="s">
-        <v>55</v>
+      <c r="E430" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="F430" s="4" t="s">
         <v>671</v>
@@ -14158,7 +14158,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="431" hidden="1" spans="1:7">
+    <row r="431" spans="1:7">
       <c r="A431" s="3" t="s">
         <v>713</v>
       </c>
@@ -14171,8 +14171,8 @@
       <c r="D431" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E431" s="3" t="s">
-        <v>55</v>
+      <c r="E431" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="F431" s="4" t="s">
         <v>671</v>
@@ -14273,7 +14273,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" hidden="1" spans="1:7">
       <c r="A436" t="s">
         <v>683</v>
       </c>
@@ -14296,7 +14296,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:7">
+    <row r="437" spans="1:7">
       <c r="A437" t="s">
         <v>683</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" hidden="1" spans="1:7">
       <c r="A438" t="s">
         <v>687</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="439" hidden="1" spans="1:7">
+    <row r="439" spans="1:7">
       <c r="A439" t="s">
         <v>687</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="446" spans="1:7">
+    <row r="446" hidden="1" spans="1:7">
       <c r="A446" s="1" t="s">
         <v>775</v>
       </c>
@@ -14526,7 +14526,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
+    <row r="447" hidden="1" spans="1:7">
       <c r="A447" s="1" t="s">
         <v>775</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="448" hidden="1" spans="1:7">
+    <row r="448" spans="1:7">
       <c r="A448" s="1" t="s">
         <v>775</v>
       </c>
@@ -14572,7 +14572,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="449" hidden="1" spans="1:7">
+    <row r="449" spans="1:7">
       <c r="A449" s="1" t="s">
         <v>775</v>
       </c>
@@ -19245,7 +19245,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="AYAD ABDELGHANI"/>
+        <filter val="TOUHAMI SEDDIK"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -12709,7 +12709,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="368" hidden="1" spans="1:7">
+    <row r="368" spans="1:7">
       <c r="A368" t="s">
         <v>678</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>19</v>
       </c>
       <c r="E368" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F368" t="s">
         <v>681</v>
@@ -12732,7 +12732,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="369" hidden="1" spans="1:7">
+    <row r="369" spans="1:7">
       <c r="A369" t="s">
         <v>682</v>
       </c>
@@ -12746,7 +12746,7 @@
         <v>23</v>
       </c>
       <c r="E369" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F369" t="s">
         <v>681</v>
@@ -12769,7 +12769,7 @@
         <v>23</v>
       </c>
       <c r="E370" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F370" t="s">
         <v>686</v>
@@ -12792,7 +12792,7 @@
         <v>19</v>
       </c>
       <c r="E371" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F371" t="s">
         <v>686</v>
@@ -13123,7 +13123,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:7">
+    <row r="386" spans="1:7">
       <c r="A386" s="1" t="s">
         <v>706</v>
       </c>
@@ -13146,7 +13146,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:7">
+    <row r="387" spans="1:7">
       <c r="A387" s="1" t="s">
         <v>706</v>
       </c>
@@ -13169,7 +13169,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:7">
+    <row r="388" spans="1:7">
       <c r="A388" s="1" t="s">
         <v>706</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:7">
+    <row r="389" spans="1:7">
       <c r="A389" s="1" t="s">
         <v>706</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="416" hidden="1" spans="1:7">
+    <row r="416" spans="1:7">
       <c r="A416" t="s">
         <v>678</v>
       </c>
@@ -13836,7 +13836,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="417" hidden="1" spans="1:7">
+    <row r="417" spans="1:7">
       <c r="A417" t="s">
         <v>682</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="424" hidden="1" spans="1:7">
+    <row r="424" spans="1:7">
       <c r="A424" t="s">
         <v>698</v>
       </c>
@@ -14020,7 +14020,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="425" hidden="1" spans="1:7">
+    <row r="425" spans="1:7">
       <c r="A425" t="s">
         <v>701</v>
       </c>
@@ -14402,7 +14402,7 @@
         <v>10</v>
       </c>
       <c r="E441" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F441" t="s">
         <v>773</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E443" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F443" t="s">
         <v>773</v>
@@ -14457,7 +14457,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="444" hidden="1" spans="1:7">
+    <row r="444" spans="1:7">
       <c r="A444" t="s">
         <v>698</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E444" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F444" t="s">
         <v>700</v>
@@ -14480,7 +14480,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="445" hidden="1" spans="1:7">
+    <row r="445" spans="1:7">
       <c r="A445" t="s">
         <v>701</v>
       </c>
@@ -14494,7 +14494,7 @@
         <v>10</v>
       </c>
       <c r="E445" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F445" t="s">
         <v>700</v>
@@ -19245,6 +19245,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
+        <filter val="RAMI ABDELKADER"/>
         <filter val="TOUHAMI SEDDIK"/>
       </filters>
     </filterColumn>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -3445,7 +3445,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3461,6 +3461,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3781,7 +3787,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3805,16 +3811,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3823,94 +3829,95 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12479,7 +12486,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:7">
+    <row r="358" spans="1:7">
       <c r="A358" s="1" t="s">
         <v>665</v>
       </c>
@@ -12502,7 +12509,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:7">
+    <row r="359" spans="1:7">
       <c r="A359" s="1" t="s">
         <v>665</v>
       </c>
@@ -12525,7 +12532,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:7">
+    <row r="360" spans="1:7">
       <c r="A360" s="1" t="s">
         <v>665</v>
       </c>
@@ -12548,7 +12555,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:7">
+    <row r="361" spans="1:7">
       <c r="A361" s="1" t="s">
         <v>665</v>
       </c>
@@ -12663,7 +12670,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:7">
+    <row r="366" spans="1:7">
       <c r="A366" s="3" t="s">
         <v>675</v>
       </c>
@@ -12686,7 +12693,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:7">
+    <row r="367" spans="1:7">
       <c r="A367" s="3" t="s">
         <v>675</v>
       </c>
@@ -12709,7 +12716,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" hidden="1" spans="1:7">
       <c r="A368" t="s">
         <v>678</v>
       </c>
@@ -12732,7 +12739,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" hidden="1" spans="1:7">
       <c r="A369" t="s">
         <v>682</v>
       </c>
@@ -12755,7 +12762,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" hidden="1" spans="1:7">
       <c r="A370" t="s">
         <v>683</v>
       </c>
@@ -12778,7 +12785,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" hidden="1" spans="1:7">
       <c r="A371" t="s">
         <v>687</v>
       </c>
@@ -12801,7 +12808,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="372" hidden="1" spans="1:7">
+    <row r="372" spans="1:7">
       <c r="A372" t="s">
         <v>688</v>
       </c>
@@ -12824,7 +12831,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="373" hidden="1" spans="1:7">
+    <row r="373" spans="1:7">
       <c r="A373" t="s">
         <v>691</v>
       </c>
@@ -13031,7 +13038,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:7">
+    <row r="382" spans="1:7">
       <c r="A382" s="1" t="s">
         <v>279</v>
       </c>
@@ -13054,7 +13061,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:7">
+    <row r="383" spans="1:7">
       <c r="A383" s="1" t="s">
         <v>279</v>
       </c>
@@ -13077,7 +13084,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:7">
+    <row r="384" spans="1:7">
       <c r="A384" s="1" t="s">
         <v>279</v>
       </c>
@@ -13100,7 +13107,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:7">
+    <row r="385" spans="1:7">
       <c r="A385" s="1" t="s">
         <v>279</v>
       </c>
@@ -13123,7 +13130,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" hidden="1" spans="1:7">
       <c r="A386" s="1" t="s">
         <v>706</v>
       </c>
@@ -13146,7 +13153,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" hidden="1" spans="1:7">
       <c r="A387" s="1" t="s">
         <v>706</v>
       </c>
@@ -13169,7 +13176,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" hidden="1" spans="1:7">
       <c r="A388" s="1" t="s">
         <v>706</v>
       </c>
@@ -13192,7 +13199,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" hidden="1" spans="1:7">
       <c r="A389" s="1" t="s">
         <v>706</v>
       </c>
@@ -13215,7 +13222,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:7">
+    <row r="390" spans="1:7">
       <c r="A390" s="3" t="s">
         <v>282</v>
       </c>
@@ -13238,7 +13245,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:7">
+    <row r="391" spans="1:7">
       <c r="A391" s="3" t="s">
         <v>282</v>
       </c>
@@ -13813,7 +13820,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" hidden="1" spans="1:7">
       <c r="A416" t="s">
         <v>678</v>
       </c>
@@ -13836,7 +13843,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" hidden="1" spans="1:7">
       <c r="A417" t="s">
         <v>682</v>
       </c>
@@ -13951,7 +13958,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:7">
+    <row r="422" spans="1:7">
       <c r="A422" t="s">
         <v>754</v>
       </c>
@@ -13974,7 +13981,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:7">
+    <row r="423" spans="1:7">
       <c r="A423" t="s">
         <v>756</v>
       </c>
@@ -13997,7 +14004,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" hidden="1" spans="1:7">
       <c r="A424" t="s">
         <v>698</v>
       </c>
@@ -14020,7 +14027,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" hidden="1" spans="1:7">
       <c r="A425" t="s">
         <v>701</v>
       </c>
@@ -14135,7 +14142,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" hidden="1" spans="1:7">
       <c r="A430" s="3" t="s">
         <v>713</v>
       </c>
@@ -14158,7 +14165,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" hidden="1" spans="1:7">
       <c r="A431" s="3" t="s">
         <v>713</v>
       </c>
@@ -14181,7 +14188,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:7">
+    <row r="432" spans="1:7">
       <c r="A432" s="3" t="s">
         <v>675</v>
       </c>
@@ -14204,7 +14211,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="433" hidden="1" spans="1:7">
+    <row r="433" spans="1:7">
       <c r="A433" s="3" t="s">
         <v>675</v>
       </c>
@@ -14227,7 +14234,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="434" hidden="1" spans="1:7">
+    <row r="434" spans="1:7">
       <c r="A434" t="s">
         <v>688</v>
       </c>
@@ -14250,7 +14257,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:7">
+    <row r="435" spans="1:7">
       <c r="A435" t="s">
         <v>691</v>
       </c>
@@ -14296,7 +14303,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" hidden="1" spans="1:7">
       <c r="A437" t="s">
         <v>683</v>
       </c>
@@ -14342,7 +14349,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" hidden="1" spans="1:7">
       <c r="A439" t="s">
         <v>687</v>
       </c>
@@ -14365,7 +14372,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="440" hidden="1" spans="1:7">
+    <row r="440" spans="1:7">
       <c r="A440" t="s">
         <v>754</v>
       </c>
@@ -14411,7 +14418,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="442" hidden="1" spans="1:7">
+    <row r="442" spans="1:7">
       <c r="A442" t="s">
         <v>756</v>
       </c>
@@ -14457,7 +14464,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="444" spans="1:7">
+    <row r="444" hidden="1" spans="1:7">
       <c r="A444" t="s">
         <v>698</v>
       </c>
@@ -14480,7 +14487,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="445" spans="1:7">
+    <row r="445" hidden="1" spans="1:7">
       <c r="A445" t="s">
         <v>701</v>
       </c>
@@ -14549,7 +14556,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" hidden="1" spans="1:7">
       <c r="A448" s="1" t="s">
         <v>775</v>
       </c>
@@ -14572,7 +14579,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" hidden="1" spans="1:7">
       <c r="A449" s="1" t="s">
         <v>775</v>
       </c>
@@ -14595,21 +14602,21 @@
         <v>659</v>
       </c>
     </row>
-    <row r="450" hidden="1" spans="1:7">
+    <row r="450" spans="1:7">
       <c r="A450" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="C450" s="3" t="s">
+      <c r="C450" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D450" s="3" t="s">
-        <v>443</v>
+      <c r="D450" t="s">
+        <v>10</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F450" s="4" t="s">
         <v>671</v>
@@ -14618,21 +14625,21 @@
         <v>657</v>
       </c>
     </row>
-    <row r="451" hidden="1" spans="1:7">
+    <row r="451" spans="1:7">
       <c r="A451" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="C451" s="3" t="s">
+      <c r="C451" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D451" s="3" t="s">
-        <v>19</v>
+      <c r="D451" t="s">
+        <v>10</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F451" s="4" t="s">
         <v>671</v>
@@ -14733,7 +14740,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="456" hidden="1" spans="1:7">
+    <row r="456" spans="1:7">
       <c r="A456" t="s">
         <v>678</v>
       </c>
@@ -14779,7 +14786,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="458" hidden="1" spans="1:7">
+    <row r="458" spans="1:7">
       <c r="A458" t="s">
         <v>682</v>
       </c>
@@ -14825,7 +14832,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="460" hidden="1" spans="1:7">
+    <row r="460" spans="1:7">
       <c r="A460" t="s">
         <v>754</v>
       </c>
@@ -14848,7 +14855,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="461" hidden="1" spans="1:7">
+    <row r="461" spans="1:7">
       <c r="A461" t="s">
         <v>756</v>
       </c>
@@ -19245,8 +19252,10 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="RAMI ABDELKADER"/>
-        <filter val="TOUHAMI SEDDIK"/>
+        <filter val="BENGRIT MALIKA"/>
+        <filter val="DJELLOULI YOUNES"/>
+        <filter val="BENHAMIDA FARID"/>
+        <filter val="BENDIMERAD SALAH EDDINE"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -13048,11 +13048,11 @@
       <c r="C382" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D382" s="1" t="s">
-        <v>25</v>
+      <c r="D382" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>652</v>
@@ -13071,11 +13071,11 @@
       <c r="C383" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D383" s="1" t="s">
-        <v>25</v>
+      <c r="D383" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F383" s="1" t="s">
         <v>652</v>
@@ -13094,11 +13094,11 @@
       <c r="C384" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D384" s="1" t="s">
-        <v>25</v>
+      <c r="D384" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>652</v>
@@ -13117,11 +13117,11 @@
       <c r="C385" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D385" s="1" t="s">
-        <v>25</v>
+      <c r="D385" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F385" s="1" t="s">
         <v>652</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -14613,10 +14613,10 @@
         <v>281</v>
       </c>
       <c r="D450" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="F450" s="4" t="s">
         <v>671</v>
@@ -14636,10 +14636,10 @@
         <v>281</v>
       </c>
       <c r="D451" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="F451" s="4" t="s">
         <v>671</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -12486,7 +12486,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" hidden="1" spans="1:7">
       <c r="A358" s="1" t="s">
         <v>665</v>
       </c>
@@ -12509,7 +12509,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" hidden="1" spans="1:7">
       <c r="A359" s="1" t="s">
         <v>665</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" hidden="1" spans="1:7">
       <c r="A360" s="1" t="s">
         <v>665</v>
       </c>
@@ -12555,7 +12555,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" hidden="1" spans="1:7">
       <c r="A361" s="1" t="s">
         <v>665</v>
       </c>
@@ -12670,7 +12670,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" hidden="1" spans="1:7">
       <c r="A366" s="3" t="s">
         <v>675</v>
       </c>
@@ -12693,7 +12693,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" hidden="1" spans="1:7">
       <c r="A367" s="3" t="s">
         <v>675</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="370" hidden="1" spans="1:7">
+    <row r="370" spans="1:7">
       <c r="A370" t="s">
         <v>683</v>
       </c>
@@ -12785,7 +12785,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="371" hidden="1" spans="1:7">
+    <row r="371" spans="1:7">
       <c r="A371" t="s">
         <v>687</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" hidden="1" spans="1:7">
       <c r="A372" t="s">
         <v>688</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" hidden="1" spans="1:7">
       <c r="A373" t="s">
         <v>691</v>
       </c>
@@ -13038,7 +13038,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" hidden="1" spans="1:7">
       <c r="A382" s="1" t="s">
         <v>279</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" hidden="1" spans="1:7">
       <c r="A383" s="1" t="s">
         <v>279</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" hidden="1" spans="1:7">
       <c r="A384" s="1" t="s">
         <v>279</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" hidden="1" spans="1:7">
       <c r="A385" s="1" t="s">
         <v>279</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390" s="3" t="s">
         <v>282</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" hidden="1" spans="1:7">
       <c r="A391" s="3" t="s">
         <v>282</v>
       </c>
@@ -13958,7 +13958,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" hidden="1" spans="1:7">
       <c r="A422" t="s">
         <v>754</v>
       </c>
@@ -13981,7 +13981,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" hidden="1" spans="1:7">
       <c r="A423" t="s">
         <v>756</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:7">
+    <row r="430" spans="1:7">
       <c r="A430" s="3" t="s">
         <v>713</v>
       </c>
@@ -14156,7 +14156,7 @@
         <v>10</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F430" s="4" t="s">
         <v>671</v>
@@ -14165,7 +14165,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="431" hidden="1" spans="1:7">
+    <row r="431" spans="1:7">
       <c r="A431" s="3" t="s">
         <v>713</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>10</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F431" s="4" t="s">
         <v>671</v>
@@ -14188,7 +14188,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" hidden="1" spans="1:7">
       <c r="A432" s="3" t="s">
         <v>675</v>
       </c>
@@ -14211,7 +14211,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" hidden="1" spans="1:7">
       <c r="A433" s="3" t="s">
         <v>675</v>
       </c>
@@ -14234,7 +14234,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" hidden="1" spans="1:7">
       <c r="A434" t="s">
         <v>688</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" hidden="1" spans="1:7">
       <c r="A435" t="s">
         <v>691</v>
       </c>
@@ -14303,7 +14303,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:7">
+    <row r="437" spans="1:7">
       <c r="A437" t="s">
         <v>683</v>
       </c>
@@ -14349,7 +14349,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="439" hidden="1" spans="1:7">
+    <row r="439" spans="1:7">
       <c r="A439" t="s">
         <v>687</v>
       </c>
@@ -14372,7 +14372,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="440" spans="1:7">
+    <row r="440" hidden="1" spans="1:7">
       <c r="A440" t="s">
         <v>754</v>
       </c>
@@ -14418,7 +14418,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" hidden="1" spans="1:7">
       <c r="A442" t="s">
         <v>756</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="448" hidden="1" spans="1:7">
+    <row r="448" spans="1:7">
       <c r="A448" s="1" t="s">
         <v>775</v>
       </c>
@@ -14579,7 +14579,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="449" hidden="1" spans="1:7">
+    <row r="449" spans="1:7">
       <c r="A449" s="1" t="s">
         <v>775</v>
       </c>
@@ -14602,7 +14602,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" hidden="1" spans="1:7">
       <c r="A450" s="3" t="s">
         <v>282</v>
       </c>
@@ -14625,7 +14625,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" hidden="1" spans="1:7">
       <c r="A451" s="3" t="s">
         <v>282</v>
       </c>
@@ -14740,7 +14740,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" hidden="1" spans="1:7">
       <c r="A456" t="s">
         <v>678</v>
       </c>
@@ -14786,7 +14786,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="458" spans="1:7">
+    <row r="458" hidden="1" spans="1:7">
       <c r="A458" t="s">
         <v>682</v>
       </c>
@@ -14832,7 +14832,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" hidden="1" spans="1:7">
       <c r="A460" t="s">
         <v>754</v>
       </c>
@@ -14855,7 +14855,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" hidden="1" spans="1:7">
       <c r="A461" t="s">
         <v>756</v>
       </c>
@@ -19252,10 +19252,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="BENGRIT MALIKA"/>
-        <filter val="DJELLOULI YOUNES"/>
-        <filter val="BENHAMIDA FARID"/>
-        <filter val="BENDIMERAD SALAH EDDINE"/>
+        <filter val="TOUHAMI SEDDIK"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -12762,7 +12762,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" hidden="1" spans="1:7">
       <c r="A370" t="s">
         <v>683</v>
       </c>
@@ -12785,7 +12785,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" hidden="1" spans="1:7">
       <c r="A371" t="s">
         <v>687</v>
       </c>
@@ -13268,7 +13268,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="392" hidden="1" spans="1:7">
+    <row r="392" spans="1:7">
       <c r="A392" s="3" t="s">
         <v>713</v>
       </c>
@@ -13278,11 +13278,11 @@
       <c r="C392" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D392" s="1" t="s">
-        <v>25</v>
+      <c r="D392" t="s">
+        <v>23</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F392" s="4" t="s">
         <v>671</v>
@@ -13291,7 +13291,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:7">
+    <row r="393" spans="1:7">
       <c r="A393" s="3" t="s">
         <v>713</v>
       </c>
@@ -13301,11 +13301,11 @@
       <c r="C393" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D393" s="1" t="s">
-        <v>25</v>
+      <c r="D393" t="s">
+        <v>23</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F393" s="4" t="s">
         <v>671</v>
@@ -13866,7 +13866,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="418" hidden="1" spans="1:7">
+    <row r="418" spans="1:7">
       <c r="A418" t="s">
         <v>683</v>
       </c>
@@ -13889,7 +13889,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="419" hidden="1" spans="1:7">
+    <row r="419" spans="1:7">
       <c r="A419" t="s">
         <v>687</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" hidden="1" spans="1:7">
       <c r="A430" s="3" t="s">
         <v>713</v>
       </c>
@@ -14165,7 +14165,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" hidden="1" spans="1:7">
       <c r="A431" s="3" t="s">
         <v>713</v>
       </c>
@@ -14280,7 +14280,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="436" hidden="1" spans="1:7">
+    <row r="436" spans="1:7">
       <c r="A436" t="s">
         <v>683</v>
       </c>
@@ -14303,7 +14303,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" hidden="1" spans="1:7">
       <c r="A437" t="s">
         <v>683</v>
       </c>
@@ -14326,7 +14326,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:7">
+    <row r="438" spans="1:7">
       <c r="A438" t="s">
         <v>687</v>
       </c>
@@ -14349,7 +14349,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" hidden="1" spans="1:7">
       <c r="A439" t="s">
         <v>687</v>
       </c>
@@ -14510,7 +14510,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="446" hidden="1" spans="1:7">
+    <row r="446" spans="1:7">
       <c r="A446" s="1" t="s">
         <v>775</v>
       </c>
@@ -14533,7 +14533,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="447" hidden="1" spans="1:7">
+    <row r="447" spans="1:7">
       <c r="A447" s="1" t="s">
         <v>775</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" hidden="1" spans="1:7">
       <c r="A448" s="1" t="s">
         <v>775</v>
       </c>
@@ -14579,7 +14579,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" hidden="1" spans="1:7">
       <c r="A449" s="1" t="s">
         <v>775</v>
       </c>
@@ -19252,7 +19252,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="TOUHAMI SEDDIK"/>
+        <filter val="AYAD ABDELGHANI"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -13038,7 +13038,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:7">
+    <row r="382" spans="1:7">
       <c r="A382" s="1" t="s">
         <v>279</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:7">
+    <row r="383" spans="1:7">
       <c r="A383" s="1" t="s">
         <v>279</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:7">
+    <row r="384" spans="1:7">
       <c r="A384" s="1" t="s">
         <v>279</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:7">
+    <row r="385" spans="1:7">
       <c r="A385" s="1" t="s">
         <v>279</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:7">
+    <row r="390" spans="1:7">
       <c r="A390" s="3" t="s">
         <v>282</v>
       </c>
@@ -13233,10 +13233,10 @@
         <v>281</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F390" s="4" t="s">
         <v>671</v>
@@ -13245,7 +13245,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="391" hidden="1" spans="1:7">
+    <row r="391" spans="1:7">
       <c r="A391" s="3" t="s">
         <v>282</v>
       </c>
@@ -13256,10 +13256,10 @@
         <v>281</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F391" s="4" t="s">
         <v>671</v>
@@ -13268,7 +13268,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" hidden="1" spans="1:7">
       <c r="A392" s="3" t="s">
         <v>713</v>
       </c>
@@ -13291,7 +13291,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" hidden="1" spans="1:7">
       <c r="A393" s="3" t="s">
         <v>713</v>
       </c>
@@ -13866,7 +13866,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" hidden="1" spans="1:7">
       <c r="A418" t="s">
         <v>683</v>
       </c>
@@ -13889,7 +13889,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" hidden="1" spans="1:7">
       <c r="A419" t="s">
         <v>687</v>
       </c>
@@ -14280,7 +14280,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" hidden="1" spans="1:7">
       <c r="A436" t="s">
         <v>683</v>
       </c>
@@ -14326,7 +14326,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" hidden="1" spans="1:7">
       <c r="A438" t="s">
         <v>687</v>
       </c>
@@ -14510,7 +14510,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="446" spans="1:7">
+    <row r="446" hidden="1" spans="1:7">
       <c r="A446" s="1" t="s">
         <v>775</v>
       </c>
@@ -14533,7 +14533,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
+    <row r="447" hidden="1" spans="1:7">
       <c r="A447" s="1" t="s">
         <v>775</v>
       </c>
@@ -14602,7 +14602,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="450" hidden="1" spans="1:7">
+    <row r="450" spans="1:7">
       <c r="A450" s="3" t="s">
         <v>282</v>
       </c>
@@ -14625,7 +14625,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="451" hidden="1" spans="1:7">
+    <row r="451" spans="1:7">
       <c r="A451" s="3" t="s">
         <v>282</v>
       </c>
@@ -19252,7 +19252,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="AYAD ABDELGHANI"/>
+        <filter val="BENDIMERAD SALAH EDDINE"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -12486,7 +12486,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:7">
+    <row r="358" spans="1:7">
       <c r="A358" s="1" t="s">
         <v>665</v>
       </c>
@@ -12509,7 +12509,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:7">
+    <row r="359" spans="1:7">
       <c r="A359" s="1" t="s">
         <v>665</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:7">
+    <row r="360" spans="1:7">
       <c r="A360" s="1" t="s">
         <v>665</v>
       </c>
@@ -12555,7 +12555,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:7">
+    <row r="361" spans="1:7">
       <c r="A361" s="1" t="s">
         <v>665</v>
       </c>
@@ -12670,7 +12670,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="366" hidden="1" spans="1:7">
+    <row r="366" spans="1:7">
       <c r="A366" s="3" t="s">
         <v>675</v>
       </c>
@@ -12680,11 +12680,11 @@
       <c r="C366" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D366" s="3" t="s">
-        <v>23</v>
+      <c r="D366" t="s">
+        <v>25</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F366" s="4" t="s">
         <v>671</v>
@@ -12693,7 +12693,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="367" hidden="1" spans="1:7">
+    <row r="367" spans="1:7">
       <c r="A367" s="3" t="s">
         <v>675</v>
       </c>
@@ -12703,11 +12703,11 @@
       <c r="C367" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D367" s="3" t="s">
-        <v>23</v>
+      <c r="D367" t="s">
+        <v>25</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>671</v>
@@ -13038,7 +13038,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" hidden="1" spans="1:7">
       <c r="A382" s="1" t="s">
         <v>279</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" hidden="1" spans="1:7">
       <c r="A383" s="1" t="s">
         <v>279</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" hidden="1" spans="1:7">
       <c r="A384" s="1" t="s">
         <v>279</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" hidden="1" spans="1:7">
       <c r="A385" s="1" t="s">
         <v>279</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390" s="3" t="s">
         <v>282</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" hidden="1" spans="1:7">
       <c r="A391" s="3" t="s">
         <v>282</v>
       </c>
@@ -13958,7 +13958,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="422" hidden="1" spans="1:7">
+    <row r="422" spans="1:7">
       <c r="A422" t="s">
         <v>754</v>
       </c>
@@ -13981,7 +13981,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="423" hidden="1" spans="1:7">
+    <row r="423" spans="1:7">
       <c r="A423" t="s">
         <v>756</v>
       </c>
@@ -14188,7 +14188,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:7">
+    <row r="432" spans="1:7">
       <c r="A432" s="3" t="s">
         <v>675</v>
       </c>
@@ -14211,7 +14211,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="433" hidden="1" spans="1:7">
+    <row r="433" spans="1:7">
       <c r="A433" s="3" t="s">
         <v>675</v>
       </c>
@@ -14372,7 +14372,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="440" hidden="1" spans="1:7">
+    <row r="440" spans="1:7">
       <c r="A440" t="s">
         <v>754</v>
       </c>
@@ -14418,7 +14418,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="442" hidden="1" spans="1:7">
+    <row r="442" spans="1:7">
       <c r="A442" t="s">
         <v>756</v>
       </c>
@@ -14602,7 +14602,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" hidden="1" spans="1:7">
       <c r="A450" s="3" t="s">
         <v>282</v>
       </c>
@@ -14625,7 +14625,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" hidden="1" spans="1:7">
       <c r="A451" s="3" t="s">
         <v>282</v>
       </c>
@@ -14832,7 +14832,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="460" hidden="1" spans="1:7">
+    <row r="460" spans="1:7">
       <c r="A460" t="s">
         <v>754</v>
       </c>
@@ -14855,7 +14855,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="461" hidden="1" spans="1:7">
+    <row r="461" spans="1:7">
       <c r="A461" t="s">
         <v>756</v>
       </c>
@@ -19252,7 +19252,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="BENDIMERAD SALAH EDDINE"/>
+        <filter val="BENHAMIDA FARID"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4557" uniqueCount="1081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4557" uniqueCount="1082">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2045,18 +2045,135 @@
     <t>TD-EPA-M1CE</t>
   </si>
   <si>
+    <t>AS8</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1ER</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1ME</t>
+  </si>
+  <si>
     <t>AS4</t>
   </si>
   <si>
-    <t>TD-EPA-M1ER</t>
-  </si>
-  <si>
-    <t>TD-EPA-M1ME</t>
-  </si>
-  <si>
     <t>TD-EPA-M1RE</t>
   </si>
   <si>
+    <t>TD-Méthodes numériques appliquées et optimisation</t>
+  </si>
+  <si>
+    <t>TD-MNAO-M1CE</t>
+  </si>
+  <si>
+    <t>TD-MNAO-M1ER</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques approfondies-G1</t>
+  </si>
+  <si>
+    <t>TP-MEA-RE</t>
+  </si>
+  <si>
+    <t>RAMI ABDELKADER</t>
+  </si>
+  <si>
+    <t>Salle micro 02 &amp; labo machine 02</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques approfondies-G2</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées et optimisation-G1</t>
+  </si>
+  <si>
+    <t>TP-MNAO-RE</t>
+  </si>
+  <si>
+    <t>TOUHAMI SEDDIK</t>
+  </si>
+  <si>
+    <t>Salle micro 02</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées et optimisation-G2</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance avancée-G1</t>
+  </si>
+  <si>
+    <t>TP-EPA-RE</t>
+  </si>
+  <si>
+    <t>Salle micro 01</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance avancée-G2</t>
+  </si>
+  <si>
+    <t>TP-Programmation avancée en Python-G1</t>
+  </si>
+  <si>
+    <t>TP-PAP-M1CE</t>
+  </si>
+  <si>
+    <t>TP-PAP-M1ER</t>
+  </si>
+  <si>
+    <t>M1 ER</t>
+  </si>
+  <si>
+    <t>TP-PAP-RE</t>
+  </si>
+  <si>
+    <t>TP-Programmation avancée en Python-G2</t>
+  </si>
+  <si>
+    <t>TP-μ-processeurs et μ-contrôleurs-G1</t>
+  </si>
+  <si>
+    <t>TP-μPμC-M1ER</t>
+  </si>
+  <si>
+    <t>Labo μ-processeurs</t>
+  </si>
+  <si>
+    <t>TP-μ-processeurs et μ-contrôleurs-G2</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1CE</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1RE</t>
+  </si>
+  <si>
+    <t>Cours-μ-processeurs et μ-contrôleurs</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1CE</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-μPμC-M1RE</t>
+  </si>
+  <si>
+    <t>TD-MEA-M1ME</t>
+  </si>
+  <si>
+    <t>TD-MEA-RE</t>
+  </si>
+  <si>
     <t>TD-Réseaux de transport et de distribution d'énergie électrique</t>
   </si>
   <si>
@@ -2066,103 +2183,148 @@
     <t>TD-RTsDEE-RE</t>
   </si>
   <si>
-    <t>TP-Machines électriques approfondies-G1</t>
-  </si>
-  <si>
-    <t>TP-MEA-RE</t>
-  </si>
-  <si>
-    <t>RAMI ABDELKADER</t>
-  </si>
-  <si>
-    <t>Salle micro 02 &amp; labo machine 02</t>
-  </si>
-  <si>
-    <t>TP-Machines électriques approfondies-G2</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées et optimisation-G1</t>
-  </si>
-  <si>
-    <t>TP-MNAO-RE</t>
-  </si>
-  <si>
-    <t>TOUHAMI SEDDIK</t>
-  </si>
-  <si>
-    <t>Salle micro 02</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées et optimisation-G2</t>
-  </si>
-  <si>
-    <t>TP-Électronique de puissance avancée-G1</t>
-  </si>
-  <si>
-    <t>TP-EPA-RE</t>
-  </si>
-  <si>
-    <t>Salle micro 01</t>
-  </si>
-  <si>
-    <t>TP-Électronique de puissance avancée-G2</t>
-  </si>
-  <si>
-    <t>TP-Programmation avancée en Python-G1</t>
-  </si>
-  <si>
-    <t>TP-PAP-M1CE</t>
-  </si>
-  <si>
-    <t>TP-PAP-M1ER</t>
-  </si>
-  <si>
-    <t>M1 ER</t>
-  </si>
-  <si>
-    <t>TP-PAP-RE</t>
-  </si>
-  <si>
-    <t>TP-Programmation avancée en Python-G2</t>
-  </si>
-  <si>
-    <t>TP-μ-processeurs et μ-contrôleurs-G1</t>
-  </si>
-  <si>
-    <t>TP-μPμC-M1ER</t>
-  </si>
-  <si>
-    <t>Labo μ-processeurs</t>
-  </si>
-  <si>
-    <t>TP-μ-processeurs et μ-contrôleurs-G2</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1CE</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1RE</t>
-  </si>
-  <si>
-    <t>Cours-μ-processeurs et μ-contrôleurs</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1CE</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1RE</t>
+    <t>Cours-μPμC-M1MCIL</t>
+  </si>
+  <si>
+    <t>M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-μPμC-M1MCIL</t>
+  </si>
+  <si>
+    <t>14h - 15h</t>
+  </si>
+  <si>
+    <t>TD-Exploitation des Réseaux électriques</t>
+  </si>
+  <si>
+    <t>TD-ERE-M1MCIL</t>
+  </si>
+  <si>
+    <t>15h - 16h</t>
+  </si>
+  <si>
+    <t>Cours-MEA-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-Exploitation des Réseaux électriques</t>
+  </si>
+  <si>
+    <t>Cours-ERE-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-Compatibilité électromagnétique</t>
+  </si>
+  <si>
+    <t>Cours-EM-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-Exploitation des Réseaux électriques-G1</t>
+  </si>
+  <si>
+    <t>TP-ERE-M1MCIL</t>
+  </si>
+  <si>
+    <t>NEMMICH SAID</t>
+  </si>
+  <si>
+    <t>TP-Exploitation des Réseaux électriques-G2</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques approfondies -G1</t>
+  </si>
+  <si>
+    <t>TP-MEA-M1MCIL</t>
+  </si>
+  <si>
+    <t>DJELLOULI YOUNES</t>
+  </si>
+  <si>
+    <t>Labo machine 1 &amp; Salle de micros 03</t>
+  </si>
+  <si>
+    <t>TD-MEA-M1MCIL</t>
+  </si>
+  <si>
+    <t>TD-EPA-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-Technologie d'Élclairage</t>
+  </si>
+  <si>
+    <t>Cours-TE-M1MCIL</t>
+  </si>
+  <si>
+    <t>TD-Méthodes numériques appliquées</t>
+  </si>
+  <si>
+    <t>TD-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>Cours-EPA-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-EPA-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées-G2</t>
+  </si>
+  <si>
+    <t>TP-MNAP-M1MCIL</t>
+  </si>
+  <si>
+    <t>Salle micro 03</t>
+  </si>
+  <si>
+    <t>TP-Méthodes numériques appliquées-G1</t>
+  </si>
+  <si>
+    <t>Cours-Anglais technique et terminologie</t>
+  </si>
+  <si>
+    <t>Cours-ANGTT-M1MCIL</t>
+  </si>
+  <si>
+    <t>TP-MEA-M1ME</t>
+  </si>
+  <si>
+    <t>TP-MNAO-M1CE</t>
+  </si>
+  <si>
+    <t>TP-PAP-M1ME</t>
+  </si>
+  <si>
+    <t>TP-Réseaux de transport et de distribution d'énergie électrique-G1</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-RE</t>
+  </si>
+  <si>
+    <t>TP-Réseaux de transport et de distribution d'énergie électrique-G2</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-M1RE</t>
+  </si>
+  <si>
+    <t>TP-μPμC-RE</t>
+  </si>
+  <si>
+    <t>Cours-Énergies renouvelables</t>
+  </si>
+  <si>
+    <t>Cours-ER-M1CE</t>
+  </si>
+  <si>
+    <t>Cours-ER-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-ER-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-ER-M1RE</t>
   </si>
   <si>
     <t>TD-MEA-M1CE</t>
@@ -2171,211 +2333,52 @@
     <t>TD-MEA-M1ER</t>
   </si>
   <si>
-    <t>TD-Méthodes numériques appliquées et optimisation</t>
-  </si>
-  <si>
-    <t>TD-MNAO-M1CE</t>
-  </si>
-  <si>
-    <t>TD-MNAO-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-μPμC-M1MCIL</t>
-  </si>
-  <si>
-    <t>M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-μPμC-M1MCIL</t>
-  </si>
-  <si>
-    <t>14h - 15h</t>
-  </si>
-  <si>
-    <t>TD-Exploitation des Réseaux électriques</t>
-  </si>
-  <si>
-    <t>TD-ERE-M1MCIL</t>
-  </si>
-  <si>
-    <t>15h - 16h</t>
-  </si>
-  <si>
-    <t>Cours-MEA-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-Exploitation des Réseaux électriques</t>
-  </si>
-  <si>
-    <t>Cours-ERE-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-Compatibilité électromagnétique</t>
-  </si>
-  <si>
-    <t>Cours-EM-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-Exploitation des Réseaux électriques-G1</t>
-  </si>
-  <si>
-    <t>TP-ERE-M1MCIL</t>
-  </si>
-  <si>
-    <t>NEMMICH SAID</t>
-  </si>
-  <si>
-    <t>TP-Exploitation des Réseaux électriques-G2</t>
-  </si>
-  <si>
-    <t>TP-Machines électriques approfondies -G1</t>
-  </si>
-  <si>
-    <t>TP-MEA-M1MCIL</t>
-  </si>
-  <si>
-    <t>DJELLOULI YOUNES</t>
-  </si>
-  <si>
-    <t>Labo machine 1 &amp; Salle de micros 03</t>
-  </si>
-  <si>
-    <t>TD-MEA-M1MCIL</t>
-  </si>
-  <si>
-    <t>TD-EPA-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-Technologie d'Élclairage</t>
-  </si>
-  <si>
-    <t>Cours-TE-M1MCIL</t>
-  </si>
-  <si>
-    <t>TD-Méthodes numériques appliquées</t>
-  </si>
-  <si>
-    <t>TD-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>Cours-EPA-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-EPA-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées-G2</t>
-  </si>
-  <si>
-    <t>TP-MNAP-M1MCIL</t>
-  </si>
-  <si>
-    <t>Salle micro 03</t>
-  </si>
-  <si>
-    <t>TP-Méthodes numériques appliquées-G1</t>
-  </si>
-  <si>
-    <t>Cours-Anglais technique et terminologie</t>
-  </si>
-  <si>
-    <t>Cours-ANGTT-M1MCIL</t>
-  </si>
-  <si>
-    <t>TP-MEA-M1ME</t>
-  </si>
-  <si>
-    <t>TP-MNAO-M1CE</t>
-  </si>
-  <si>
-    <t>TP-PAP-M1ME</t>
-  </si>
-  <si>
-    <t>TP-Réseaux de transport et de distribution d'énergie électrique-G1</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-RE</t>
-  </si>
-  <si>
-    <t>TP-Réseaux de transport et de distribution d'énergie électrique-G2</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-M1RE</t>
-  </si>
-  <si>
-    <t>TP-μPμC-RE</t>
-  </si>
-  <si>
-    <t>Cours-Énergies renouvelables</t>
-  </si>
-  <si>
-    <t>Cours-ER-M1CE</t>
-  </si>
-  <si>
-    <t>Cours-ER-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-ER-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-ER-M1RE</t>
-  </si>
-  <si>
     <t>TD-MNAO-M1ME</t>
   </si>
   <si>
     <t>TD-MNAO-RE</t>
   </si>
   <si>
+    <t>TP-EPA-M1ME</t>
+  </si>
+  <si>
+    <t>TP-MNAO-M1ER</t>
+  </si>
+  <si>
+    <t>TP-MNAO-M1ME</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-M1ER</t>
+  </si>
+  <si>
+    <t>TP-RTsDEE-M1ME</t>
+  </si>
+  <si>
+    <t>Labo Réseaux</t>
+  </si>
+  <si>
+    <t>TP-μPμC-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-Méthodes numériques appliquées et optimisation</t>
+  </si>
+  <si>
+    <t>Cours-MNAO-M1CE</t>
+  </si>
+  <si>
+    <t>Cours-MNAO-M1ER</t>
+  </si>
+  <si>
+    <t>Cours-MNAO-M1ME</t>
+  </si>
+  <si>
+    <t>Cours-MNAO-M1RE</t>
+  </si>
+  <si>
     <t>TD-RTDEE-M1CE</t>
   </si>
   <si>
     <t>TD-RTsDEE-M1ER</t>
-  </si>
-  <si>
-    <t>TP-EPA-M1ME</t>
-  </si>
-  <si>
-    <t>TP-MNAO-M1ER</t>
-  </si>
-  <si>
-    <t>TP-MNAO-M1ME</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-M1ER</t>
-  </si>
-  <si>
-    <t>TP-RTsDEE-M1ME</t>
-  </si>
-  <si>
-    <t>Labo Réseaux</t>
-  </si>
-  <si>
-    <t>TP-μPμC-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-Méthodes numériques appliquées et optimisation</t>
-  </si>
-  <si>
-    <t>Cours-MNAO-M1CE</t>
-  </si>
-  <si>
-    <t>Cours-MNAO-M1ER</t>
-  </si>
-  <si>
-    <t>Cours-MNAO-M1ME</t>
-  </si>
-  <si>
-    <t>Cours-MNAO-M1RE</t>
-  </si>
-  <si>
-    <t>TD-MEA-M1ME</t>
-  </si>
-  <si>
-    <t>TD-MEA-RE</t>
   </si>
   <si>
     <t>TP-CEPA-M1CE</t>
@@ -12486,7 +12489,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" hidden="1" spans="1:7">
       <c r="A358" s="1" t="s">
         <v>665</v>
       </c>
@@ -12509,7 +12512,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" hidden="1" spans="1:7">
       <c r="A359" s="1" t="s">
         <v>665</v>
       </c>
@@ -12532,7 +12535,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" hidden="1" spans="1:7">
       <c r="A360" s="1" t="s">
         <v>665</v>
       </c>
@@ -12555,7 +12558,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" hidden="1" spans="1:7">
       <c r="A361" s="1" t="s">
         <v>665</v>
       </c>
@@ -12578,7 +12581,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="362" hidden="1" spans="1:7">
+    <row r="362" spans="1:7">
       <c r="A362" s="3" t="s">
         <v>349</v>
       </c>
@@ -12601,7 +12604,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="363" hidden="1" spans="1:7">
+    <row r="363" spans="1:7">
       <c r="A363" s="3" t="s">
         <v>349</v>
       </c>
@@ -12624,7 +12627,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="364" hidden="1" spans="1:7">
+    <row r="364" spans="1:7">
       <c r="A364" s="3" t="s">
         <v>349</v>
       </c>
@@ -12641,18 +12644,18 @@
         <v>11</v>
       </c>
       <c r="F364" s="4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G364" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="365" hidden="1" spans="1:7">
+    <row r="365" spans="1:7">
       <c r="A365" s="3" t="s">
         <v>349</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C365" s="3" t="s">
         <v>651</v>
@@ -12664,7 +12667,7 @@
         <v>11</v>
       </c>
       <c r="F365" s="4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G365" t="s">
         <v>659</v>
@@ -12672,59 +12675,59 @@
     </row>
     <row r="366" spans="1:7">
       <c r="A366" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="D366" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F366" s="4" t="s">
         <v>671</v>
       </c>
       <c r="G366" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="D367" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>671</v>
       </c>
       <c r="G367" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="368" hidden="1" spans="1:7">
       <c r="A368" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B368" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C368" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D368" t="s">
         <v>19</v>
@@ -12733,7 +12736,7 @@
         <v>42</v>
       </c>
       <c r="F368" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G368" t="s">
         <v>659</v>
@@ -12741,13 +12744,13 @@
     </row>
     <row r="369" hidden="1" spans="1:7">
       <c r="A369" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B369" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C369" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D369" t="s">
         <v>23</v>
@@ -12756,7 +12759,7 @@
         <v>42</v>
       </c>
       <c r="F369" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G369" t="s">
         <v>659</v>
@@ -12764,13 +12767,13 @@
     </row>
     <row r="370" hidden="1" spans="1:7">
       <c r="A370" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B370" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C370" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D370" t="s">
         <v>23</v>
@@ -12779,7 +12782,7 @@
         <v>42</v>
       </c>
       <c r="F370" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G370" t="s">
         <v>659</v>
@@ -12787,13 +12790,13 @@
     </row>
     <row r="371" hidden="1" spans="1:7">
       <c r="A371" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B371" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C371" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D371" t="s">
         <v>19</v>
@@ -12802,7 +12805,7 @@
         <v>42</v>
       </c>
       <c r="F371" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G371" t="s">
         <v>659</v>
@@ -12810,10 +12813,10 @@
     </row>
     <row r="372" hidden="1" spans="1:7">
       <c r="A372" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B372" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C372" t="s">
         <v>548</v>
@@ -12825,7 +12828,7 @@
         <v>28</v>
       </c>
       <c r="F372" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G372" t="s">
         <v>659</v>
@@ -12833,10 +12836,10 @@
     </row>
     <row r="373" hidden="1" spans="1:7">
       <c r="A373" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B373" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C373" t="s">
         <v>548</v>
@@ -12848,7 +12851,7 @@
         <v>28</v>
       </c>
       <c r="F373" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G373" t="s">
         <v>659</v>
@@ -12856,10 +12859,10 @@
     </row>
     <row r="374" hidden="1" spans="1:7">
       <c r="A374" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B374" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C374" t="s">
         <v>9</v>
@@ -12871,7 +12874,7 @@
         <v>28</v>
       </c>
       <c r="F374" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G374" t="s">
         <v>653</v>
@@ -12879,10 +12882,10 @@
     </row>
     <row r="375" hidden="1" spans="1:7">
       <c r="A375" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B375" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C375" t="s">
         <v>83</v>
@@ -12894,7 +12897,7 @@
         <v>28</v>
       </c>
       <c r="F375" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G375" t="s">
         <v>655</v>
@@ -12902,10 +12905,10 @@
     </row>
     <row r="376" hidden="1" spans="1:7">
       <c r="A376" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B376" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C376" t="s">
         <v>295</v>
@@ -12917,7 +12920,7 @@
         <v>28</v>
       </c>
       <c r="F376" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G376" t="s">
         <v>659</v>
@@ -12925,10 +12928,10 @@
     </row>
     <row r="377" hidden="1" spans="1:7">
       <c r="A377" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B377" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C377" t="s">
         <v>9</v>
@@ -12940,7 +12943,7 @@
         <v>28</v>
       </c>
       <c r="F377" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G377" t="s">
         <v>653</v>
@@ -12948,10 +12951,10 @@
     </row>
     <row r="378" hidden="1" spans="1:7">
       <c r="A378" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B378" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C378" t="s">
         <v>83</v>
@@ -12963,7 +12966,7 @@
         <v>28</v>
       </c>
       <c r="F378" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G378" t="s">
         <v>655</v>
@@ -12971,10 +12974,10 @@
     </row>
     <row r="379" hidden="1" spans="1:7">
       <c r="A379" t="s">
+        <v>698</v>
+      </c>
+      <c r="B379" t="s">
         <v>697</v>
-      </c>
-      <c r="B379" t="s">
-        <v>696</v>
       </c>
       <c r="C379" t="s">
         <v>295</v>
@@ -12986,7 +12989,7 @@
         <v>28</v>
       </c>
       <c r="F379" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G379" t="s">
         <v>659</v>
@@ -12994,10 +12997,10 @@
     </row>
     <row r="380" hidden="1" spans="1:7">
       <c r="A380" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B380" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C380" t="s">
         <v>197</v>
@@ -13009,7 +13012,7 @@
         <v>28</v>
       </c>
       <c r="F380" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G380" t="s">
         <v>655</v>
@@ -13017,10 +13020,10 @@
     </row>
     <row r="381" hidden="1" spans="1:7">
       <c r="A381" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B381" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C381" t="s">
         <v>197</v>
@@ -13032,7 +13035,7 @@
         <v>28</v>
       </c>
       <c r="F381" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G381" t="s">
         <v>655</v>
@@ -13043,7 +13046,7 @@
         <v>279</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>281</v>
@@ -13066,7 +13069,7 @@
         <v>279</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>281</v>
@@ -13089,7 +13092,7 @@
         <v>279</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>281</v>
@@ -13112,7 +13115,7 @@
         <v>279</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>281</v>
@@ -13132,13 +13135,13 @@
     </row>
     <row r="386" hidden="1" spans="1:7">
       <c r="A386" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D386" s="1" t="s">
         <v>10</v>
@@ -13155,13 +13158,13 @@
     </row>
     <row r="387" hidden="1" spans="1:7">
       <c r="A387" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>10</v>
@@ -13178,13 +13181,13 @@
     </row>
     <row r="388" hidden="1" spans="1:7">
       <c r="A388" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>10</v>
@@ -13201,13 +13204,13 @@
     </row>
     <row r="389" hidden="1" spans="1:7">
       <c r="A389" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>10</v>
@@ -13222,104 +13225,104 @@
         <v>659</v>
       </c>
     </row>
-    <row r="390" hidden="1" spans="1:7">
+    <row r="390" spans="1:7">
       <c r="A390" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="C390" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="C390" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D390" s="3" t="s">
-        <v>25</v>
+      <c r="D390" t="s">
+        <v>23</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F390" s="4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G390" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="391" hidden="1" spans="1:7">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
       <c r="A391" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="C391" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C391" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D391" s="3" t="s">
+      <c r="D391" t="s">
+        <v>23</v>
+      </c>
+      <c r="E391" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F391" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G391" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D392" t="s">
         <v>25</v>
       </c>
-      <c r="E391" s="3" t="s">
+      <c r="E392" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F391" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="G391" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="392" hidden="1" spans="1:7">
-      <c r="A392" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="B392" s="3" t="s">
+      <c r="F392" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G392" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="C392" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D392" t="s">
-        <v>23</v>
-      </c>
-      <c r="E392" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F392" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="G392" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="393" hidden="1" spans="1:7">
-      <c r="A393" s="3" t="s">
-        <v>713</v>
-      </c>
       <c r="B393" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>328</v>
+        <v>290</v>
       </c>
       <c r="D393" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F393" s="4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G393" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="394" hidden="1" spans="1:7">
       <c r="A394" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B394" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C394" t="s">
         <v>197</v>
@@ -13334,38 +13337,38 @@
         <v>393</v>
       </c>
       <c r="G394" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="395" hidden="1" spans="1:7">
       <c r="A395" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B395" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C395" t="s">
         <v>197</v>
       </c>
       <c r="D395" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E395" t="s">
         <v>11</v>
       </c>
       <c r="F395" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G395" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="396" hidden="1" spans="1:7">
       <c r="A396" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B396" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C396" t="s">
         <v>346</v>
@@ -13380,30 +13383,30 @@
         <v>393</v>
       </c>
       <c r="G396" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="397" hidden="1" spans="1:7">
       <c r="A397" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B397" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C397" t="s">
         <v>197</v>
       </c>
       <c r="D397" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E397" t="s">
         <v>11</v>
       </c>
       <c r="F397" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G397" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="398" hidden="1" spans="1:7">
@@ -13411,7 +13414,7 @@
         <v>279</v>
       </c>
       <c r="B398" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C398" t="s">
         <v>217</v>
@@ -13426,15 +13429,15 @@
         <v>393</v>
       </c>
       <c r="G398" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="399" hidden="1" spans="1:7">
       <c r="A399" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B399" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C399" t="s">
         <v>346</v>
@@ -13449,15 +13452,15 @@
         <v>393</v>
       </c>
       <c r="G399" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="400" hidden="1" spans="1:7">
       <c r="A400" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B400" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C400" t="s">
         <v>207</v>
@@ -13472,18 +13475,18 @@
         <v>393</v>
       </c>
       <c r="G400" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="401" hidden="1" spans="1:7">
       <c r="A401" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B401" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C401" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D401" t="s">
         <v>19</v>
@@ -13492,21 +13495,21 @@
         <v>42</v>
       </c>
       <c r="F401" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G401" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="402" hidden="1" spans="1:7">
       <c r="A402" t="s">
+        <v>732</v>
+      </c>
+      <c r="B402" t="s">
+        <v>730</v>
+      </c>
+      <c r="C402" t="s">
         <v>731</v>
-      </c>
-      <c r="B402" t="s">
-        <v>729</v>
-      </c>
-      <c r="C402" t="s">
-        <v>730</v>
       </c>
       <c r="D402" t="s">
         <v>23</v>
@@ -13515,21 +13518,21 @@
         <v>42</v>
       </c>
       <c r="F402" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G402" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="403" hidden="1" spans="1:7">
       <c r="A403" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B403" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C403" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D403" t="s">
         <v>25</v>
@@ -13538,18 +13541,18 @@
         <v>42</v>
       </c>
       <c r="F403" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G403" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="404" hidden="1" spans="1:7">
       <c r="A404" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B404" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C404" t="s">
         <v>323</v>
@@ -13561,10 +13564,10 @@
         <v>42</v>
       </c>
       <c r="F404" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G404" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="405" hidden="1" spans="1:7">
@@ -13572,7 +13575,7 @@
         <v>282</v>
       </c>
       <c r="B405" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C405" t="s">
         <v>281</v>
@@ -13587,7 +13590,7 @@
         <v>393</v>
       </c>
       <c r="G405" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="406" hidden="1" spans="1:7">
@@ -13595,7 +13598,7 @@
         <v>349</v>
       </c>
       <c r="B406" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C406" t="s">
         <v>651</v>
@@ -13610,15 +13613,15 @@
         <v>393</v>
       </c>
       <c r="G406" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="407" hidden="1" spans="1:7">
       <c r="A407" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B407" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C407" t="s">
         <v>207</v>
@@ -13633,15 +13636,15 @@
         <v>393</v>
       </c>
       <c r="G407" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="408" hidden="1" spans="1:7">
       <c r="A408" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B408" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C408" t="s">
         <v>328</v>
@@ -13656,7 +13659,7 @@
         <v>393</v>
       </c>
       <c r="G408" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="409" hidden="1" spans="1:7">
@@ -13664,7 +13667,7 @@
         <v>177</v>
       </c>
       <c r="B409" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C409" t="s">
         <v>328</v>
@@ -13679,7 +13682,7 @@
         <v>393</v>
       </c>
       <c r="G409" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="410" hidden="1" spans="1:7">
@@ -13687,7 +13690,7 @@
         <v>326</v>
       </c>
       <c r="B410" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C410" t="s">
         <v>651</v>
@@ -13702,15 +13705,15 @@
         <v>393</v>
       </c>
       <c r="G410" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="411" hidden="1" spans="1:7">
       <c r="A411" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B411" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C411" t="s">
         <v>548</v>
@@ -13722,18 +13725,18 @@
         <v>62</v>
       </c>
       <c r="F411" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G411" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="412" hidden="1" spans="1:7">
       <c r="A412" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B412" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C412" t="s">
         <v>9</v>
@@ -13745,18 +13748,18 @@
         <v>62</v>
       </c>
       <c r="F412" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G412" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="413" hidden="1" spans="1:7">
       <c r="A413" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B413" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C413" t="s">
         <v>548</v>
@@ -13768,18 +13771,18 @@
         <v>62</v>
       </c>
       <c r="F413" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G413" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="414" hidden="1" spans="1:7">
       <c r="A414" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B414" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C414" t="s">
         <v>9</v>
@@ -13791,18 +13794,18 @@
         <v>62</v>
       </c>
       <c r="F414" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G414" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="415" hidden="1" spans="1:7">
       <c r="A415" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B415" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C415" t="s">
         <v>41</v>
@@ -13817,18 +13820,18 @@
         <v>393</v>
       </c>
       <c r="G415" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="416" hidden="1" spans="1:7">
       <c r="A416" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B416" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C416" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D416" t="s">
         <v>19</v>
@@ -13837,7 +13840,7 @@
         <v>42</v>
       </c>
       <c r="F416" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G416" t="s">
         <v>657</v>
@@ -13845,13 +13848,13 @@
     </row>
     <row r="417" hidden="1" spans="1:7">
       <c r="A417" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B417" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C417" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D417" t="s">
         <v>23</v>
@@ -13860,7 +13863,7 @@
         <v>42</v>
       </c>
       <c r="F417" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G417" t="s">
         <v>657</v>
@@ -13868,10 +13871,10 @@
     </row>
     <row r="418" hidden="1" spans="1:7">
       <c r="A418" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B418" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C418" t="s">
         <v>328</v>
@@ -13883,7 +13886,7 @@
         <v>42</v>
       </c>
       <c r="F418" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G418" t="s">
         <v>653</v>
@@ -13891,10 +13894,10 @@
     </row>
     <row r="419" hidden="1" spans="1:7">
       <c r="A419" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B419" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C419" t="s">
         <v>328</v>
@@ -13906,7 +13909,7 @@
         <v>42</v>
       </c>
       <c r="F419" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G419" t="s">
         <v>653</v>
@@ -13914,10 +13917,10 @@
     </row>
     <row r="420" hidden="1" spans="1:7">
       <c r="A420" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B420" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C420" t="s">
         <v>295</v>
@@ -13929,7 +13932,7 @@
         <v>42</v>
       </c>
       <c r="F420" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G420" t="s">
         <v>657</v>
@@ -13937,10 +13940,10 @@
     </row>
     <row r="421" hidden="1" spans="1:7">
       <c r="A421" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B421" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C421" t="s">
         <v>295</v>
@@ -13952,18 +13955,18 @@
         <v>42</v>
       </c>
       <c r="F421" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G421" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" hidden="1" spans="1:7">
       <c r="A422" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B422" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C422" t="s">
         <v>290</v>
@@ -13975,18 +13978,18 @@
         <v>42</v>
       </c>
       <c r="F422" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G422" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" hidden="1" spans="1:7">
       <c r="A423" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B423" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C423" t="s">
         <v>290</v>
@@ -13998,7 +14001,7 @@
         <v>42</v>
       </c>
       <c r="F423" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G423" t="s">
         <v>659</v>
@@ -14006,13 +14009,13 @@
     </row>
     <row r="424" hidden="1" spans="1:7">
       <c r="A424" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B424" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C424" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D424" t="s">
         <v>25</v>
@@ -14021,7 +14024,7 @@
         <v>42</v>
       </c>
       <c r="F424" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G424" t="s">
         <v>659</v>
@@ -14029,13 +14032,13 @@
     </row>
     <row r="425" hidden="1" spans="1:7">
       <c r="A425" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B425" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C425" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D425" t="s">
         <v>27</v>
@@ -14044,7 +14047,7 @@
         <v>42</v>
       </c>
       <c r="F425" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G425" t="s">
         <v>659</v>
@@ -14052,10 +14055,10 @@
     </row>
     <row r="426" hidden="1" spans="1:7">
       <c r="A426" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>318</v>
@@ -14075,10 +14078,10 @@
     </row>
     <row r="427" hidden="1" spans="1:7">
       <c r="A427" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>318</v>
@@ -14098,10 +14101,10 @@
     </row>
     <row r="428" hidden="1" spans="1:7">
       <c r="A428" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>318</v>
@@ -14121,10 +14124,10 @@
     </row>
     <row r="429" hidden="1" spans="1:7">
       <c r="A429" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>318</v>
@@ -14142,104 +14145,104 @@
         <v>659</v>
       </c>
     </row>
-    <row r="430" hidden="1" spans="1:7">
+    <row r="430" spans="1:7">
       <c r="A430" s="3" t="s">
-        <v>713</v>
+        <v>282</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>685</v>
+        <v>281</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E430" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
+      </c>
+      <c r="E430" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F430" s="4" t="s">
         <v>671</v>
       </c>
       <c r="G430" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="431" hidden="1" spans="1:7">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7">
       <c r="A431" s="3" t="s">
-        <v>713</v>
+        <v>282</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>685</v>
+        <v>281</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E431" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
+      </c>
+      <c r="E431" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F431" s="4" t="s">
         <v>671</v>
       </c>
       <c r="G431" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="432" spans="1:7">
       <c r="A432" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>290</v>
+        <v>686</v>
       </c>
       <c r="D432" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E432" s="3" t="s">
+      <c r="E432" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F432" s="4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G432" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="433" spans="1:7">
       <c r="A433" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>290</v>
+        <v>686</v>
       </c>
       <c r="D433" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E433" s="3" t="s">
+      <c r="E433" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F433" s="4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G433" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="434" hidden="1" spans="1:7">
       <c r="A434" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B434" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C434" t="s">
         <v>548</v>
@@ -14251,7 +14254,7 @@
         <v>55</v>
       </c>
       <c r="F434" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G434" t="s">
         <v>657</v>
@@ -14259,10 +14262,10 @@
     </row>
     <row r="435" hidden="1" spans="1:7">
       <c r="A435" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B435" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C435" t="s">
         <v>548</v>
@@ -14274,7 +14277,7 @@
         <v>55</v>
       </c>
       <c r="F435" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G435" t="s">
         <v>657</v>
@@ -14282,10 +14285,10 @@
     </row>
     <row r="436" hidden="1" spans="1:7">
       <c r="A436" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B436" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C436" t="s">
         <v>328</v>
@@ -14297,7 +14300,7 @@
         <v>55</v>
       </c>
       <c r="F436" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G436" t="s">
         <v>655</v>
@@ -14305,13 +14308,13 @@
     </row>
     <row r="437" hidden="1" spans="1:7">
       <c r="A437" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B437" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C437" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D437" t="s">
         <v>23</v>
@@ -14320,7 +14323,7 @@
         <v>55</v>
       </c>
       <c r="F437" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G437" t="s">
         <v>657</v>
@@ -14328,10 +14331,10 @@
     </row>
     <row r="438" hidden="1" spans="1:7">
       <c r="A438" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B438" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C438" t="s">
         <v>328</v>
@@ -14343,7 +14346,7 @@
         <v>55</v>
       </c>
       <c r="F438" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G438" t="s">
         <v>655</v>
@@ -14351,13 +14354,13 @@
     </row>
     <row r="439" hidden="1" spans="1:7">
       <c r="A439" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B439" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C439" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D439" t="s">
         <v>19</v>
@@ -14366,18 +14369,18 @@
         <v>55</v>
       </c>
       <c r="F439" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G439" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="440" spans="1:7">
+    <row r="440" hidden="1" spans="1:7">
       <c r="A440" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B440" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C440" t="s">
         <v>290</v>
@@ -14389,7 +14392,7 @@
         <v>55</v>
       </c>
       <c r="F440" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G440" t="s">
         <v>655</v>
@@ -14397,13 +14400,13 @@
     </row>
     <row r="441" hidden="1" spans="1:7">
       <c r="A441" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B441" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C441" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D441" t="s">
         <v>10</v>
@@ -14412,18 +14415,18 @@
         <v>28</v>
       </c>
       <c r="F441" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G441" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" hidden="1" spans="1:7">
       <c r="A442" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B442" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C442" t="s">
         <v>290</v>
@@ -14435,7 +14438,7 @@
         <v>55</v>
       </c>
       <c r="F442" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G442" t="s">
         <v>655</v>
@@ -14443,13 +14446,13 @@
     </row>
     <row r="443" hidden="1" spans="1:7">
       <c r="A443" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B443" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C443" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D443" t="s">
         <v>27</v>
@@ -14458,7 +14461,7 @@
         <v>28</v>
       </c>
       <c r="F443" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G443" t="s">
         <v>657</v>
@@ -14466,13 +14469,13 @@
     </row>
     <row r="444" hidden="1" spans="1:7">
       <c r="A444" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B444" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C444" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D444" t="s">
         <v>27</v>
@@ -14481,7 +14484,7 @@
         <v>28</v>
       </c>
       <c r="F444" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G444" t="s">
         <v>657</v>
@@ -14489,13 +14492,13 @@
     </row>
     <row r="445" hidden="1" spans="1:7">
       <c r="A445" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B445" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C445" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D445" t="s">
         <v>10</v>
@@ -14504,7 +14507,7 @@
         <v>28</v>
       </c>
       <c r="F445" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G445" t="s">
         <v>657</v>
@@ -14512,10 +14515,10 @@
     </row>
     <row r="446" hidden="1" spans="1:7">
       <c r="A446" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>328</v>
@@ -14535,10 +14538,10 @@
     </row>
     <row r="447" hidden="1" spans="1:7">
       <c r="A447" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>328</v>
@@ -14558,13 +14561,13 @@
     </row>
     <row r="448" hidden="1" spans="1:7">
       <c r="A448" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D448" s="1" t="s">
         <v>25</v>
@@ -14581,13 +14584,13 @@
     </row>
     <row r="449" hidden="1" spans="1:7">
       <c r="A449" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D449" s="1" t="s">
         <v>25</v>
@@ -14602,58 +14605,58 @@
         <v>659</v>
       </c>
     </row>
-    <row r="450" hidden="1" spans="1:7">
+    <row r="450" spans="1:7">
       <c r="A450" s="3" t="s">
-        <v>282</v>
+        <v>714</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="C450" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D450" t="s">
-        <v>23</v>
+        <v>781</v>
+      </c>
+      <c r="C450" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D450" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F450" s="4" t="s">
         <v>671</v>
       </c>
       <c r="G450" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="451" hidden="1" spans="1:7">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7">
       <c r="A451" s="3" t="s">
-        <v>282</v>
+        <v>714</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C451" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D451" t="s">
-        <v>23</v>
+        <v>782</v>
+      </c>
+      <c r="C451" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D451" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F451" s="4" t="s">
         <v>671</v>
       </c>
       <c r="G451" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="452" hidden="1" spans="1:7">
       <c r="A452" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B452" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C452" t="s">
         <v>187</v>
@@ -14665,7 +14668,7 @@
         <v>62</v>
       </c>
       <c r="F452" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G452" t="s">
         <v>653</v>
@@ -14673,10 +14676,10 @@
     </row>
     <row r="453" hidden="1" spans="1:7">
       <c r="A453" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B453" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C453" t="s">
         <v>187</v>
@@ -14688,7 +14691,7 @@
         <v>62</v>
       </c>
       <c r="F453" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G453" t="s">
         <v>655</v>
@@ -14696,10 +14699,10 @@
     </row>
     <row r="454" hidden="1" spans="1:7">
       <c r="A454" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B454" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C454" t="s">
         <v>187</v>
@@ -14711,7 +14714,7 @@
         <v>62</v>
       </c>
       <c r="F454" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G454" t="s">
         <v>653</v>
@@ -14719,10 +14722,10 @@
     </row>
     <row r="455" hidden="1" spans="1:7">
       <c r="A455" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B455" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C455" t="s">
         <v>187</v>
@@ -14734,7 +14737,7 @@
         <v>62</v>
       </c>
       <c r="F455" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G455" t="s">
         <v>655</v>
@@ -14742,13 +14745,13 @@
     </row>
     <row r="456" hidden="1" spans="1:7">
       <c r="A456" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B456" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C456" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D456" t="s">
         <v>27</v>
@@ -14757,7 +14760,7 @@
         <v>62</v>
       </c>
       <c r="F456" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G456" t="s">
         <v>653</v>
@@ -14765,10 +14768,10 @@
     </row>
     <row r="457" hidden="1" spans="1:7">
       <c r="A457" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B457" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C457" t="s">
         <v>323</v>
@@ -14780,7 +14783,7 @@
         <v>62</v>
       </c>
       <c r="F457" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G457" t="s">
         <v>655</v>
@@ -14788,13 +14791,13 @@
     </row>
     <row r="458" hidden="1" spans="1:7">
       <c r="A458" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B458" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C458" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D458" t="s">
         <v>10</v>
@@ -14803,7 +14806,7 @@
         <v>62</v>
       </c>
       <c r="F458" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G458" t="s">
         <v>653</v>
@@ -14811,10 +14814,10 @@
     </row>
     <row r="459" hidden="1" spans="1:7">
       <c r="A459" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B459" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C459" t="s">
         <v>323</v>
@@ -14826,18 +14829,18 @@
         <v>62</v>
       </c>
       <c r="F459" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G459" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" hidden="1" spans="1:7">
       <c r="A460" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B460" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C460" t="s">
         <v>290</v>
@@ -14849,18 +14852,18 @@
         <v>62</v>
       </c>
       <c r="F460" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G460" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" hidden="1" spans="1:7">
       <c r="A461" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B461" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C461" t="s">
         <v>290</v>
@@ -14872,7 +14875,7 @@
         <v>62</v>
       </c>
       <c r="F461" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G461" t="s">
         <v>653</v>
@@ -14880,10 +14883,10 @@
     </row>
     <row r="462" hidden="1" spans="1:7">
       <c r="A462" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B462" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C462" t="s">
         <v>197</v>
@@ -14895,7 +14898,7 @@
         <v>62</v>
       </c>
       <c r="F462" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G462" t="s">
         <v>653</v>
@@ -14903,10 +14906,10 @@
     </row>
     <row r="463" hidden="1" spans="1:7">
       <c r="A463" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B463" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C463" t="s">
         <v>197</v>
@@ -14918,7 +14921,7 @@
         <v>62</v>
       </c>
       <c r="F463" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G463" t="s">
         <v>653</v>
@@ -14926,10 +14929,10 @@
     </row>
     <row r="464" hidden="1" spans="1:7">
       <c r="A464" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B464" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C464" t="s">
         <v>522</v>
@@ -14944,15 +14947,15 @@
         <v>408</v>
       </c>
       <c r="G464" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="465" hidden="1" spans="1:7">
       <c r="A465" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B465" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C465" t="s">
         <v>222</v>
@@ -14964,18 +14967,18 @@
         <v>11</v>
       </c>
       <c r="F465" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G465" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="466" hidden="1" spans="1:7">
       <c r="A466" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B466" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C466" t="s">
         <v>399</v>
@@ -14987,18 +14990,18 @@
         <v>11</v>
       </c>
       <c r="F466" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G466" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="467" hidden="1" spans="1:7">
       <c r="A467" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B467" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C467" t="s">
         <v>200</v>
@@ -15010,18 +15013,18 @@
         <v>11</v>
       </c>
       <c r="F467" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G467" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="468" hidden="1" spans="1:7">
       <c r="A468" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B468" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C468" t="s">
         <v>222</v>
@@ -15033,18 +15036,18 @@
         <v>11</v>
       </c>
       <c r="F468" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G468" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="469" hidden="1" spans="1:7">
       <c r="A469" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B469" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C469" t="s">
         <v>399</v>
@@ -15056,18 +15059,18 @@
         <v>11</v>
       </c>
       <c r="F469" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G469" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="470" hidden="1" spans="1:7">
       <c r="A470" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B470" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C470" t="s">
         <v>200</v>
@@ -15079,21 +15082,21 @@
         <v>11</v>
       </c>
       <c r="F470" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G470" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="471" hidden="1" spans="1:7">
       <c r="A471" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B471" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C471" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D471" t="s">
         <v>25</v>
@@ -15105,15 +15108,15 @@
         <v>641</v>
       </c>
       <c r="G471" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="472" hidden="1" spans="1:7">
       <c r="A472" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B472" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C472" t="s">
         <v>217</v>
@@ -15128,18 +15131,18 @@
         <v>641</v>
       </c>
       <c r="G472" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="473" hidden="1" spans="1:7">
       <c r="A473" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B473" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C473" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D473" t="s">
         <v>27</v>
@@ -15151,15 +15154,15 @@
         <v>83</v>
       </c>
       <c r="G473" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="474" hidden="1" spans="1:7">
       <c r="A474" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B474" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C474" t="s">
         <v>357</v>
@@ -15174,15 +15177,15 @@
         <v>83</v>
       </c>
       <c r="G474" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="475" hidden="1" spans="1:7">
       <c r="A475" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B475" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C475" t="s">
         <v>246</v>
@@ -15194,18 +15197,18 @@
         <v>42</v>
       </c>
       <c r="F475" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G475" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="476" hidden="1" spans="1:7">
       <c r="A476" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B476" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C476" t="s">
         <v>246</v>
@@ -15220,15 +15223,15 @@
         <v>641</v>
       </c>
       <c r="G476" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="477" hidden="1" spans="1:7">
       <c r="A477" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B477" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C477" t="s">
         <v>246</v>
@@ -15243,15 +15246,15 @@
         <v>641</v>
       </c>
       <c r="G477" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="478" hidden="1" spans="1:7">
       <c r="A478" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B478" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C478" t="s">
         <v>357</v>
@@ -15266,15 +15269,15 @@
         <v>83</v>
       </c>
       <c r="G478" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="479" hidden="1" spans="1:7">
       <c r="A479" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B479" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C479" t="s">
         <v>246</v>
@@ -15286,18 +15289,18 @@
         <v>42</v>
       </c>
       <c r="F479" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G479" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="480" hidden="1" spans="1:7">
       <c r="A480" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B480" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C480" t="s">
         <v>357</v>
@@ -15312,18 +15315,18 @@
         <v>641</v>
       </c>
       <c r="G480" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="481" hidden="1" spans="1:7">
       <c r="A481" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B481" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C481" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D481" t="s">
         <v>19</v>
@@ -15335,18 +15338,18 @@
         <v>641</v>
       </c>
       <c r="G481" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="482" hidden="1" spans="1:7">
       <c r="A482" t="s">
+        <v>824</v>
+      </c>
+      <c r="B482" t="s">
+        <v>825</v>
+      </c>
+      <c r="C482" t="s">
         <v>823</v>
-      </c>
-      <c r="B482" t="s">
-        <v>824</v>
-      </c>
-      <c r="C482" t="s">
-        <v>822</v>
       </c>
       <c r="D482" t="s">
         <v>23</v>
@@ -15358,18 +15361,18 @@
         <v>641</v>
       </c>
       <c r="G482" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="483" hidden="1" spans="1:7">
       <c r="A483" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B483" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C483" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D483" t="s">
         <v>25</v>
@@ -15381,15 +15384,15 @@
         <v>641</v>
       </c>
       <c r="G483" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="484" hidden="1" spans="1:7">
       <c r="A484" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B484" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C484" t="s">
         <v>304</v>
@@ -15404,18 +15407,18 @@
         <v>83</v>
       </c>
       <c r="G484" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="485" hidden="1" spans="1:7">
       <c r="A485" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B485" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C485" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D485" t="s">
         <v>19</v>
@@ -15427,18 +15430,18 @@
         <v>641</v>
       </c>
       <c r="G485" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="486" hidden="1" spans="1:7">
       <c r="A486" t="s">
+        <v>831</v>
+      </c>
+      <c r="B486" t="s">
+        <v>832</v>
+      </c>
+      <c r="C486" t="s">
         <v>830</v>
-      </c>
-      <c r="B486" t="s">
-        <v>831</v>
-      </c>
-      <c r="C486" t="s">
-        <v>829</v>
       </c>
       <c r="D486" t="s">
         <v>23</v>
@@ -15450,18 +15453,18 @@
         <v>641</v>
       </c>
       <c r="G486" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="487" hidden="1" spans="1:7">
       <c r="A487" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B487" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C487" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D487" t="s">
         <v>25</v>
@@ -15473,15 +15476,15 @@
         <v>83</v>
       </c>
       <c r="G487" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="488" hidden="1" spans="1:7">
       <c r="A488" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B488" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C488" t="s">
         <v>304</v>
@@ -15496,18 +15499,18 @@
         <v>641</v>
       </c>
       <c r="G488" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="489" hidden="1" spans="1:7">
       <c r="A489" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B489" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C489" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D489" t="s">
         <v>27</v>
@@ -15519,15 +15522,15 @@
         <v>83</v>
       </c>
       <c r="G489" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="490" hidden="1" spans="1:7">
       <c r="A490" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B490" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C490" t="s">
         <v>304</v>
@@ -15542,15 +15545,15 @@
         <v>83</v>
       </c>
       <c r="G490" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="491" hidden="1" spans="1:7">
       <c r="A491" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B491" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C491" t="s">
         <v>357</v>
@@ -15565,15 +15568,15 @@
         <v>373</v>
       </c>
       <c r="G491" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="492" hidden="1" spans="1:7">
       <c r="A492" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B492" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C492" t="s">
         <v>396</v>
@@ -15585,18 +15588,18 @@
         <v>11</v>
       </c>
       <c r="F492" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G492" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="493" hidden="1" spans="1:7">
       <c r="A493" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B493" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C493" t="s">
         <v>372</v>
@@ -15608,18 +15611,18 @@
         <v>11</v>
       </c>
       <c r="F493" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G493" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="494" hidden="1" spans="1:7">
       <c r="A494" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B494" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C494" t="s">
         <v>396</v>
@@ -15631,18 +15634,18 @@
         <v>11</v>
       </c>
       <c r="F494" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G494" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="495" hidden="1" spans="1:7">
       <c r="A495" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B495" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C495" t="s">
         <v>372</v>
@@ -15654,18 +15657,18 @@
         <v>11</v>
       </c>
       <c r="F495" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G495" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="496" hidden="1" spans="1:7">
       <c r="A496" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B496" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C496" t="s">
         <v>295</v>
@@ -15680,15 +15683,15 @@
         <v>373</v>
       </c>
       <c r="G496" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="497" hidden="1" spans="1:7">
       <c r="A497" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B497" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C497" t="s">
         <v>357</v>
@@ -15703,18 +15706,18 @@
         <v>373</v>
       </c>
       <c r="G497" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="498" hidden="1" spans="1:7">
       <c r="A498" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B498" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C498" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D498" t="s">
         <v>27</v>
@@ -15726,7 +15729,7 @@
         <v>83</v>
       </c>
       <c r="G498" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="499" hidden="1" spans="1:7">
@@ -15734,7 +15737,7 @@
         <v>409</v>
       </c>
       <c r="B499" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C499" t="s">
         <v>361</v>
@@ -15749,15 +15752,15 @@
         <v>373</v>
       </c>
       <c r="G499" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="500" hidden="1" spans="1:7">
       <c r="A500" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B500" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C500" t="s">
         <v>372</v>
@@ -15769,18 +15772,18 @@
         <v>42</v>
       </c>
       <c r="F500" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G500" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="501" hidden="1" spans="1:7">
       <c r="A501" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B501" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C501" t="s">
         <v>399</v>
@@ -15792,18 +15795,18 @@
         <v>42</v>
       </c>
       <c r="F501" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G501" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="502" hidden="1" spans="1:7">
       <c r="A502" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B502" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C502" t="s">
         <v>372</v>
@@ -15815,18 +15818,18 @@
         <v>42</v>
       </c>
       <c r="F502" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G502" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="503" hidden="1" spans="1:7">
       <c r="A503" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B503" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C503" t="s">
         <v>399</v>
@@ -15838,18 +15841,18 @@
         <v>42</v>
       </c>
       <c r="F503" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G503" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="504" hidden="1" spans="1:7">
       <c r="A504" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B504" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C504" t="s">
         <v>396</v>
@@ -15864,7 +15867,7 @@
         <v>373</v>
       </c>
       <c r="G504" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="505" hidden="1" spans="1:7">
@@ -15872,7 +15875,7 @@
         <v>403</v>
       </c>
       <c r="B505" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C505" t="s">
         <v>361</v>
@@ -15887,15 +15890,15 @@
         <v>373</v>
       </c>
       <c r="G505" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="506" hidden="1" spans="1:7">
       <c r="A506" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B506" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C506" t="s">
         <v>420</v>
@@ -15910,15 +15913,15 @@
         <v>373</v>
       </c>
       <c r="G506" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="507" hidden="1" spans="1:7">
       <c r="A507" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B507" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C507" t="s">
         <v>399</v>
@@ -15933,15 +15936,15 @@
         <v>408</v>
       </c>
       <c r="G507" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="508" hidden="1" spans="1:7">
       <c r="A508" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B508" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C508" t="s">
         <v>399</v>
@@ -15956,15 +15959,15 @@
         <v>408</v>
       </c>
       <c r="G508" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="509" hidden="1" spans="1:7">
       <c r="A509" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B509" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C509" t="s">
         <v>318</v>
@@ -15979,15 +15982,15 @@
         <v>373</v>
       </c>
       <c r="G509" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="510" hidden="1" spans="1:7">
       <c r="A510" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B510" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C510" t="s">
         <v>522</v>
@@ -16002,15 +16005,15 @@
         <v>373</v>
       </c>
       <c r="G510" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="511" hidden="1" spans="1:7">
       <c r="A511" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B511" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C511" t="s">
         <v>318</v>
@@ -16025,7 +16028,7 @@
         <v>373</v>
       </c>
       <c r="G511" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="512" hidden="1" spans="1:7">
@@ -16033,7 +16036,7 @@
         <v>368</v>
       </c>
       <c r="B512" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C512" t="s">
         <v>272</v>
@@ -16045,18 +16048,18 @@
         <v>11</v>
       </c>
       <c r="F512" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G512" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="513" hidden="1" spans="1:7">
       <c r="A513" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B513" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C513" t="s">
         <v>346</v>
@@ -16068,18 +16071,18 @@
         <v>11</v>
       </c>
       <c r="F513" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G513" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="514" hidden="1" spans="1:7">
       <c r="A514" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B514" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C514" t="s">
         <v>346</v>
@@ -16091,18 +16094,18 @@
         <v>11</v>
       </c>
       <c r="F514" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G514" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="515" hidden="1" spans="1:7">
       <c r="A515" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B515" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C515" t="s">
         <v>295</v>
@@ -16114,21 +16117,21 @@
         <v>11</v>
       </c>
       <c r="F515" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G515" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="516" hidden="1" spans="1:7">
       <c r="A516" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B516" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C516" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D516" t="s">
         <v>27</v>
@@ -16140,7 +16143,7 @@
         <v>83</v>
       </c>
       <c r="G516" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="517" hidden="1" spans="1:7">
@@ -16148,7 +16151,7 @@
         <v>347</v>
       </c>
       <c r="B517" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C517" t="s">
         <v>272</v>
@@ -16160,18 +16163,18 @@
         <v>42</v>
       </c>
       <c r="F517" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G517" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="518" hidden="1" spans="1:7">
       <c r="A518" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B518" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C518" t="s">
         <v>391</v>
@@ -16186,15 +16189,15 @@
         <v>184</v>
       </c>
       <c r="G518" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="519" hidden="1" spans="1:7">
       <c r="A519" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B519" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C519" t="s">
         <v>391</v>
@@ -16209,15 +16212,15 @@
         <v>184</v>
       </c>
       <c r="G519" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="520" hidden="1" spans="1:7">
       <c r="A520" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B520" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C520" t="s">
         <v>522</v>
@@ -16229,21 +16232,21 @@
         <v>42</v>
       </c>
       <c r="F520" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G520" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="521" hidden="1" spans="1:7">
       <c r="A521" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B521" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C521" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D521" t="s">
         <v>27</v>
@@ -16252,18 +16255,18 @@
         <v>42</v>
       </c>
       <c r="F521" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G521" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="522" hidden="1" spans="1:7">
       <c r="A522" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B522" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C522" t="s">
         <v>380</v>
@@ -16275,18 +16278,18 @@
         <v>55</v>
       </c>
       <c r="F522" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G522" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="523" hidden="1" spans="1:7">
       <c r="A523" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B523" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C523" t="s">
         <v>361</v>
@@ -16298,18 +16301,18 @@
         <v>55</v>
       </c>
       <c r="F523" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G523" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="524" hidden="1" spans="1:7">
       <c r="A524" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B524" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C524" t="s">
         <v>361</v>
@@ -16321,18 +16324,18 @@
         <v>55</v>
       </c>
       <c r="F524" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G524" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="525" hidden="1" spans="1:7">
       <c r="A525" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B525" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C525" t="s">
         <v>380</v>
@@ -16344,18 +16347,18 @@
         <v>55</v>
       </c>
       <c r="F525" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G525" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="526" hidden="1" spans="1:7">
       <c r="A526" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B526" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C526" t="s">
         <v>272</v>
@@ -16370,18 +16373,18 @@
         <v>415</v>
       </c>
       <c r="G526" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="527" hidden="1" spans="1:7">
       <c r="A527" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B527" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C527" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D527" t="s">
         <v>19</v>
@@ -16390,18 +16393,18 @@
         <v>62</v>
       </c>
       <c r="F527" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G527" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="528" hidden="1" spans="1:7">
       <c r="A528" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B528" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C528" t="s">
         <v>383</v>
@@ -16413,21 +16416,21 @@
         <v>62</v>
       </c>
       <c r="F528" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="G528" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="529" hidden="1" spans="1:7">
       <c r="A529" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B529" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C529" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D529" t="s">
         <v>23</v>
@@ -16436,18 +16439,18 @@
         <v>62</v>
       </c>
       <c r="F529" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="G529" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="530" hidden="1" spans="1:7">
       <c r="A530" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B530" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C530" t="s">
         <v>383</v>
@@ -16459,18 +16462,18 @@
         <v>62</v>
       </c>
       <c r="F530" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="G530" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="531" hidden="1" spans="1:7">
       <c r="A531" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B531" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C531" t="s">
         <v>272</v>
@@ -16485,18 +16488,18 @@
         <v>415</v>
       </c>
       <c r="G531" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="532" hidden="1" spans="1:7">
       <c r="A532" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B532" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C532" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D532" t="s">
         <v>10</v>
@@ -16508,18 +16511,18 @@
         <v>284</v>
       </c>
       <c r="G532" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="533" hidden="1" spans="1:7">
       <c r="A533" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B533" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C533" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D533" t="s">
         <v>19</v>
@@ -16528,21 +16531,21 @@
         <v>11</v>
       </c>
       <c r="F533" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="G533" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="534" hidden="1" spans="1:7">
       <c r="A534" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B534" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C534" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D534" t="s">
         <v>23</v>
@@ -16551,21 +16554,21 @@
         <v>11</v>
       </c>
       <c r="F534" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="G534" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="535" hidden="1" spans="1:7">
       <c r="A535" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B535" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C535" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D535" t="s">
         <v>25</v>
@@ -16577,18 +16580,18 @@
         <v>284</v>
       </c>
       <c r="G535" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="536" hidden="1" spans="1:7">
       <c r="A536" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B536" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C536" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D536" t="s">
         <v>27</v>
@@ -16600,18 +16603,18 @@
         <v>284</v>
       </c>
       <c r="G536" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="537" hidden="1" spans="1:7">
       <c r="A537" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B537" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C537" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D537" t="s">
         <v>27</v>
@@ -16623,18 +16626,18 @@
         <v>284</v>
       </c>
       <c r="G537" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="538" hidden="1" spans="1:7">
       <c r="A538" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B538" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C538" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D538" t="s">
         <v>10</v>
@@ -16643,18 +16646,18 @@
         <v>42</v>
       </c>
       <c r="F538" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G538" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="539" hidden="1" spans="1:7">
       <c r="A539" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B539" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C539" t="s">
         <v>591</v>
@@ -16666,21 +16669,21 @@
         <v>42</v>
       </c>
       <c r="F539" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="G539" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="540" hidden="1" spans="1:7">
       <c r="A540" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B540" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C540" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D540" t="s">
         <v>19</v>
@@ -16692,18 +16695,18 @@
         <v>284</v>
       </c>
       <c r="G540" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="541" hidden="1" spans="1:7">
       <c r="A541" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B541" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C541" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D541" t="s">
         <v>23</v>
@@ -16715,18 +16718,18 @@
         <v>284</v>
       </c>
       <c r="G541" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="542" hidden="1" spans="1:7">
       <c r="A542" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B542" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C542" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D542" t="s">
         <v>25</v>
@@ -16738,18 +16741,18 @@
         <v>284</v>
       </c>
       <c r="G542" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="543" hidden="1" spans="1:7">
       <c r="A543" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B543" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C543" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D543" t="s">
         <v>27</v>
@@ -16758,18 +16761,18 @@
         <v>42</v>
       </c>
       <c r="F543" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G543" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="544" hidden="1" spans="1:7">
       <c r="A544" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B544" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C544" t="s">
         <v>591</v>
@@ -16781,18 +16784,18 @@
         <v>42</v>
       </c>
       <c r="F544" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="G544" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="545" hidden="1" spans="1:7">
       <c r="A545" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B545" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C545" t="s">
         <v>357</v>
@@ -16807,18 +16810,18 @@
         <v>641</v>
       </c>
       <c r="G545" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="546" hidden="1" spans="1:7">
       <c r="A546" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B546" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C546" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D546" t="s">
         <v>19</v>
@@ -16827,21 +16830,21 @@
         <v>55</v>
       </c>
       <c r="F546" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="G546" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="547" hidden="1" spans="1:7">
       <c r="A547" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B547" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C547" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D547" t="s">
         <v>23</v>
@@ -16850,21 +16853,21 @@
         <v>55</v>
       </c>
       <c r="F547" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="G547" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="548" hidden="1" spans="1:7">
       <c r="A548" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B548" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C548" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D548" t="s">
         <v>25</v>
@@ -16876,18 +16879,18 @@
         <v>284</v>
       </c>
       <c r="G548" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="549" hidden="1" spans="1:7">
       <c r="A549" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B549" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C549" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D549" t="s">
         <v>27</v>
@@ -16899,18 +16902,18 @@
         <v>284</v>
       </c>
       <c r="G549" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="550" hidden="1" spans="1:7">
       <c r="A550" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B550" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C550" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D550" t="s">
         <v>19</v>
@@ -16919,21 +16922,21 @@
         <v>62</v>
       </c>
       <c r="F550" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G550" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="551" hidden="1" spans="1:7">
       <c r="A551" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B551" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C551" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D551" t="s">
         <v>19</v>
@@ -16942,21 +16945,21 @@
         <v>62</v>
       </c>
       <c r="F551" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G551" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="552" hidden="1" spans="1:7">
       <c r="A552" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B552" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C552" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D552" t="s">
         <v>23</v>
@@ -16965,21 +16968,21 @@
         <v>62</v>
       </c>
       <c r="F552" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G552" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="553" hidden="1" spans="1:7">
       <c r="A553" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B553" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C553" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D553" t="s">
         <v>23</v>
@@ -16988,18 +16991,18 @@
         <v>62</v>
       </c>
       <c r="F553" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G553" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="554" hidden="1" spans="1:7">
       <c r="A554" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B554" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C554" t="s">
         <v>522</v>
@@ -17014,18 +17017,18 @@
         <v>373</v>
       </c>
       <c r="G554" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="555" hidden="1" spans="1:7">
       <c r="A555" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B555" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C555" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D555" t="s">
         <v>27</v>
@@ -17037,15 +17040,15 @@
         <v>284</v>
       </c>
       <c r="G555" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="556" hidden="1" spans="1:7">
       <c r="A556" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B556" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C556" t="s">
         <v>522</v>
@@ -17060,15 +17063,15 @@
         <v>408</v>
       </c>
       <c r="G556" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="557" hidden="1" spans="1:7">
       <c r="A557" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B557" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C557" t="s">
         <v>383</v>
@@ -17080,18 +17083,18 @@
         <v>11</v>
       </c>
       <c r="F557" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="G557" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="558" hidden="1" spans="1:7">
       <c r="A558" t="s">
+        <v>965</v>
+      </c>
+      <c r="B558" t="s">
         <v>964</v>
-      </c>
-      <c r="B558" t="s">
-        <v>963</v>
       </c>
       <c r="C558" t="s">
         <v>383</v>
@@ -17103,10 +17106,10 @@
         <v>11</v>
       </c>
       <c r="F558" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="G558" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="559" hidden="1" spans="1:7">
@@ -17114,7 +17117,7 @@
         <v>368</v>
       </c>
       <c r="B559" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C559" t="s">
         <v>272</v>
@@ -17129,7 +17132,7 @@
         <v>408</v>
       </c>
       <c r="G559" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="560" hidden="1" spans="1:7">
@@ -17137,7 +17140,7 @@
         <v>347</v>
       </c>
       <c r="B560" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C560" t="s">
         <v>272</v>
@@ -17152,18 +17155,18 @@
         <v>408</v>
       </c>
       <c r="G560" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="561" hidden="1" spans="1:7">
       <c r="A561" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B561" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C561" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D561" t="s">
         <v>27</v>
@@ -17175,18 +17178,18 @@
         <v>83</v>
       </c>
       <c r="G561" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="562" hidden="1" spans="1:7">
       <c r="A562" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B562" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C562" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D562" t="s">
         <v>10</v>
@@ -17198,15 +17201,15 @@
         <v>408</v>
       </c>
       <c r="G562" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="563" hidden="1" spans="1:7">
       <c r="A563" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B563" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C563" t="s">
         <v>290</v>
@@ -17221,15 +17224,15 @@
         <v>408</v>
       </c>
       <c r="G563" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="564" hidden="1" spans="1:7">
       <c r="A564" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B564" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C564" t="s">
         <v>290</v>
@@ -17244,18 +17247,18 @@
         <v>408</v>
       </c>
       <c r="G564" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="565" hidden="1" spans="1:7">
       <c r="A565" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B565" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C565" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D565" t="s">
         <v>25</v>
@@ -17267,15 +17270,15 @@
         <v>415</v>
       </c>
       <c r="G565" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="566" hidden="1" spans="1:7">
       <c r="A566" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B566" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C566" t="s">
         <v>272</v>
@@ -17287,21 +17290,21 @@
         <v>42</v>
       </c>
       <c r="F566" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G566" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="567" hidden="1" spans="1:7">
       <c r="A567" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B567" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C567" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D567" t="s">
         <v>27</v>
@@ -17313,15 +17316,15 @@
         <v>415</v>
       </c>
       <c r="G567" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="568" hidden="1" spans="1:7">
       <c r="A568" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B568" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C568" t="s">
         <v>272</v>
@@ -17333,18 +17336,18 @@
         <v>42</v>
       </c>
       <c r="F568" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G568" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="569" hidden="1" spans="1:7">
       <c r="A569" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B569" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C569" t="s">
         <v>380</v>
@@ -17359,15 +17362,15 @@
         <v>408</v>
       </c>
       <c r="G569" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="570" hidden="1" spans="1:7">
       <c r="A570" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B570" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C570" t="s">
         <v>380</v>
@@ -17382,15 +17385,15 @@
         <v>408</v>
       </c>
       <c r="G570" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="571" hidden="1" spans="1:7">
       <c r="A571" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B571" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C571" t="s">
         <v>391</v>
@@ -17405,7 +17408,7 @@
         <v>393</v>
       </c>
       <c r="G571" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="572" hidden="1" spans="1:7">
@@ -17413,7 +17416,7 @@
         <v>416</v>
       </c>
       <c r="B572" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C572" t="s">
         <v>167</v>
@@ -17428,15 +17431,15 @@
         <v>408</v>
       </c>
       <c r="G572" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="573" hidden="1" spans="1:7">
       <c r="A573" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B573" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C573" t="s">
         <v>290</v>
@@ -17451,15 +17454,15 @@
         <v>408</v>
       </c>
       <c r="G573" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="574" hidden="1" spans="1:7">
       <c r="A574" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B574" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C574" t="s">
         <v>290</v>
@@ -17474,15 +17477,15 @@
         <v>408</v>
       </c>
       <c r="G574" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="575" hidden="1" spans="1:7">
       <c r="A575" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B575" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C575" t="s">
         <v>372</v>
@@ -17494,10 +17497,10 @@
         <v>11</v>
       </c>
       <c r="F575" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G575" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="576" hidden="1" spans="1:7">
@@ -17505,7 +17508,7 @@
         <v>110</v>
       </c>
       <c r="B576" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C576" t="s">
         <v>575</v>
@@ -17520,7 +17523,7 @@
         <v>423</v>
       </c>
       <c r="G576" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="577" hidden="1" spans="1:7">
@@ -17528,7 +17531,7 @@
         <v>110</v>
       </c>
       <c r="B577" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C577" t="s">
         <v>68</v>
@@ -17540,10 +17543,10 @@
         <v>11</v>
       </c>
       <c r="F577" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G577" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="578" hidden="1" spans="1:7">
@@ -17551,7 +17554,7 @@
         <v>113</v>
       </c>
       <c r="B578" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C578" t="s">
         <v>83</v>
@@ -17563,10 +17566,10 @@
         <v>11</v>
       </c>
       <c r="F578" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="G578" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="579" hidden="1" spans="1:7">
@@ -17574,7 +17577,7 @@
         <v>110</v>
       </c>
       <c r="B579" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C579" t="s">
         <v>68</v>
@@ -17586,18 +17589,18 @@
         <v>11</v>
       </c>
       <c r="F579" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="G579" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="580" hidden="1" spans="1:7">
       <c r="A580" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B580" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C580" t="s">
         <v>18</v>
@@ -17609,10 +17612,10 @@
         <v>11</v>
       </c>
       <c r="F580" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G580" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="581" hidden="1" spans="1:7">
@@ -17620,7 +17623,7 @@
         <v>113</v>
       </c>
       <c r="B581" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C581" t="s">
         <v>83</v>
@@ -17632,10 +17635,10 @@
         <v>11</v>
       </c>
       <c r="F581" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G581" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="582" hidden="1" spans="1:7">
@@ -17643,7 +17646,7 @@
         <v>117</v>
       </c>
       <c r="B582" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C582" t="s">
         <v>68</v>
@@ -17655,10 +17658,10 @@
         <v>11</v>
       </c>
       <c r="F582" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="G582" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="583" hidden="1" spans="1:7">
@@ -17666,7 +17669,7 @@
         <v>110</v>
       </c>
       <c r="B583" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C583" t="s">
         <v>68</v>
@@ -17681,7 +17684,7 @@
         <v>592</v>
       </c>
       <c r="G583" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="584" hidden="1" spans="1:7">
@@ -17689,7 +17692,7 @@
         <v>113</v>
       </c>
       <c r="B584" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C584" t="s">
         <v>18</v>
@@ -17704,15 +17707,15 @@
         <v>505</v>
       </c>
       <c r="G584" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="585" hidden="1" spans="1:7">
       <c r="A585" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B585" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C585" t="s">
         <v>333</v>
@@ -17724,18 +17727,18 @@
         <v>28</v>
       </c>
       <c r="F585" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G585" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="586" hidden="1" spans="1:7">
       <c r="A586" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B586" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C586" t="s">
         <v>246</v>
@@ -17747,18 +17750,18 @@
         <v>28</v>
       </c>
       <c r="F586" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G586" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="587" hidden="1" spans="1:7">
       <c r="A587" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B587" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C587" t="s">
         <v>333</v>
@@ -17770,18 +17773,18 @@
         <v>28</v>
       </c>
       <c r="F587" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="G587" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="588" hidden="1" spans="1:7">
       <c r="A588" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B588" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C588" t="s">
         <v>246</v>
@@ -17793,18 +17796,18 @@
         <v>28</v>
       </c>
       <c r="F588" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G588" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="589" hidden="1" spans="1:7">
       <c r="A589" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B589" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C589" t="s">
         <v>83</v>
@@ -17816,10 +17819,10 @@
         <v>28</v>
       </c>
       <c r="F589" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="G589" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="590" hidden="1" spans="1:7">
@@ -17827,7 +17830,7 @@
         <v>130</v>
       </c>
       <c r="B590" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C590" t="s">
         <v>537</v>
@@ -17839,18 +17842,18 @@
         <v>28</v>
       </c>
       <c r="F590" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G590" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="591" hidden="1" spans="1:7">
       <c r="A591" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B591" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C591" t="s">
         <v>83</v>
@@ -17862,18 +17865,18 @@
         <v>28</v>
       </c>
       <c r="F591" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="G591" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="592" hidden="1" spans="1:7">
       <c r="A592" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B592" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C592" t="s">
         <v>229</v>
@@ -17885,21 +17888,21 @@
         <v>28</v>
       </c>
       <c r="F592" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G592" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="593" hidden="1" spans="1:7">
       <c r="A593" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B593" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C593" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D593" t="s">
         <v>25</v>
@@ -17908,18 +17911,18 @@
         <v>28</v>
       </c>
       <c r="F593" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G593" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="594" hidden="1" spans="1:7">
       <c r="A594" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B594" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C594" t="s">
         <v>83</v>
@@ -17931,18 +17934,18 @@
         <v>28</v>
       </c>
       <c r="F594" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="G594" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="595" hidden="1" spans="1:7">
       <c r="A595" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B595" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C595" t="s">
         <v>229</v>
@@ -17954,21 +17957,21 @@
         <v>28</v>
       </c>
       <c r="F595" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G595" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="596" hidden="1" spans="1:7">
       <c r="A596" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B596" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C596" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D596" t="s">
         <v>27</v>
@@ -17977,18 +17980,18 @@
         <v>28</v>
       </c>
       <c r="F596" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="G596" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="597" hidden="1" spans="1:7">
       <c r="A597" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B597" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C597" t="s">
         <v>83</v>
@@ -18000,10 +18003,10 @@
         <v>28</v>
       </c>
       <c r="F597" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="G597" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="598" hidden="1" spans="1:7">
@@ -18011,7 +18014,7 @@
         <v>578</v>
       </c>
       <c r="B598" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C598" t="s">
         <v>391</v>
@@ -18026,7 +18029,7 @@
         <v>535</v>
       </c>
       <c r="G598" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="599" hidden="1" spans="1:7">
@@ -18034,7 +18037,7 @@
         <v>110</v>
       </c>
       <c r="B599" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C599" t="s">
         <v>68</v>
@@ -18046,18 +18049,18 @@
         <v>42</v>
       </c>
       <c r="F599" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="G599" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="600" hidden="1" spans="1:7">
       <c r="A600" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B600" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C600" t="s">
         <v>580</v>
@@ -18069,18 +18072,18 @@
         <v>42</v>
       </c>
       <c r="F600" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="G600" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="601" hidden="1" spans="1:7">
       <c r="A601" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B601" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C601" t="s">
         <v>552</v>
@@ -18092,18 +18095,18 @@
         <v>42</v>
       </c>
       <c r="F601" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G601" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="602" hidden="1" spans="1:7">
       <c r="A602" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B602" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C602" t="s">
         <v>83</v>
@@ -18115,18 +18118,18 @@
         <v>42</v>
       </c>
       <c r="F602" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="G602" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="603" hidden="1" spans="1:7">
       <c r="A603" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B603" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C603" t="s">
         <v>580</v>
@@ -18141,15 +18144,15 @@
         <v>592</v>
       </c>
       <c r="G603" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="604" hidden="1" spans="1:7">
       <c r="A604" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B604" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C604" t="s">
         <v>552</v>
@@ -18161,18 +18164,18 @@
         <v>42</v>
       </c>
       <c r="F604" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G604" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="605" hidden="1" spans="1:7">
       <c r="A605" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B605" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C605" t="s">
         <v>83</v>
@@ -18184,10 +18187,10 @@
         <v>42</v>
       </c>
       <c r="F605" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="G605" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="606" hidden="1" spans="1:7">
@@ -18195,7 +18198,7 @@
         <v>123</v>
       </c>
       <c r="B606" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C606" t="s">
         <v>328</v>
@@ -18207,18 +18210,18 @@
         <v>42</v>
       </c>
       <c r="F606" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G606" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="607" hidden="1" spans="1:7">
       <c r="A607" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B607" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C607" t="s">
         <v>83</v>
@@ -18230,10 +18233,10 @@
         <v>42</v>
       </c>
       <c r="F607" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G607" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="608" hidden="1" spans="1:7">
@@ -18241,7 +18244,7 @@
         <v>113</v>
       </c>
       <c r="B608" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C608" t="s">
         <v>83</v>
@@ -18256,15 +18259,15 @@
         <v>514</v>
       </c>
       <c r="G608" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="609" hidden="1" spans="1:7">
       <c r="A609" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B609" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C609" t="s">
         <v>558</v>
@@ -18276,10 +18279,10 @@
         <v>55</v>
       </c>
       <c r="F609" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G609" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="610" hidden="1" spans="1:7">
@@ -18287,7 +18290,7 @@
         <v>110</v>
       </c>
       <c r="B610" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C610" t="s">
         <v>68</v>
@@ -18299,21 +18302,21 @@
         <v>55</v>
       </c>
       <c r="F610" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G610" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="611" hidden="1" spans="1:7">
       <c r="A611" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B611" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C611" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D611" t="s">
         <v>19</v>
@@ -18322,10 +18325,10 @@
         <v>55</v>
       </c>
       <c r="F611" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G611" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="612" hidden="1" spans="1:7">
@@ -18333,7 +18336,7 @@
         <v>567</v>
       </c>
       <c r="B612" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C612" t="s">
         <v>83</v>
@@ -18345,10 +18348,10 @@
         <v>55</v>
       </c>
       <c r="F612" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G612" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="613" hidden="1" spans="1:7">
@@ -18356,10 +18359,10 @@
         <v>88</v>
       </c>
       <c r="B613" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C613" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D613" t="s">
         <v>19</v>
@@ -18368,18 +18371,18 @@
         <v>55</v>
       </c>
       <c r="F613" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G613" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="614" hidden="1" spans="1:7">
       <c r="A614" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B614" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C614" t="s">
         <v>534</v>
@@ -18391,10 +18394,10 @@
         <v>55</v>
       </c>
       <c r="F614" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="G614" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="615" hidden="1" spans="1:7">
@@ -18402,7 +18405,7 @@
         <v>567</v>
       </c>
       <c r="B615" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C615" t="s">
         <v>83</v>
@@ -18414,10 +18417,10 @@
         <v>55</v>
       </c>
       <c r="F615" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G615" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="616" hidden="1" spans="1:7">
@@ -18425,10 +18428,10 @@
         <v>88</v>
       </c>
       <c r="B616" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C616" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D616" t="s">
         <v>23</v>
@@ -18437,10 +18440,10 @@
         <v>55</v>
       </c>
       <c r="F616" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G616" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="617" hidden="1" spans="1:7">
@@ -18448,7 +18451,7 @@
         <v>554</v>
       </c>
       <c r="B617" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C617" t="s">
         <v>65</v>
@@ -18460,10 +18463,10 @@
         <v>55</v>
       </c>
       <c r="F617" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G617" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="618" hidden="1" spans="1:7">
@@ -18471,7 +18474,7 @@
         <v>76</v>
       </c>
       <c r="B618" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C618" t="s">
         <v>18</v>
@@ -18483,18 +18486,18 @@
         <v>55</v>
       </c>
       <c r="F618" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G618" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="619" hidden="1" spans="1:7">
       <c r="A619" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B619" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C619" t="s">
         <v>83</v>
@@ -18506,10 +18509,10 @@
         <v>62</v>
       </c>
       <c r="F619" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G619" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="620" hidden="1" spans="1:7">
@@ -18517,10 +18520,10 @@
         <v>130</v>
       </c>
       <c r="B620" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C620" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D620" t="s">
         <v>10</v>
@@ -18529,10 +18532,10 @@
         <v>62</v>
       </c>
       <c r="F620" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="G620" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="621" hidden="1" spans="1:7">
@@ -18540,7 +18543,7 @@
         <v>130</v>
       </c>
       <c r="B621" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C621" t="s">
         <v>537</v>
@@ -18552,10 +18555,10 @@
         <v>62</v>
       </c>
       <c r="F621" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G621" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="622" hidden="1" spans="1:7">
@@ -18563,10 +18566,10 @@
         <v>130</v>
       </c>
       <c r="B622" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C622" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D622" t="s">
         <v>15</v>
@@ -18575,10 +18578,10 @@
         <v>62</v>
       </c>
       <c r="F622" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="G622" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="623" hidden="1" spans="1:7">
@@ -18586,7 +18589,7 @@
         <v>110</v>
       </c>
       <c r="B623" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C623" t="s">
         <v>575</v>
@@ -18601,7 +18604,7 @@
         <v>423</v>
       </c>
       <c r="G623" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="624" hidden="1" spans="1:7">
@@ -18609,7 +18612,7 @@
         <v>567</v>
       </c>
       <c r="B624" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C624" t="s">
         <v>83</v>
@@ -18624,7 +18627,7 @@
         <v>592</v>
       </c>
       <c r="G624" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="625" hidden="1" spans="1:7">
@@ -18632,7 +18635,7 @@
         <v>130</v>
       </c>
       <c r="B625" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C625" t="s">
         <v>537</v>
@@ -18644,10 +18647,10 @@
         <v>62</v>
       </c>
       <c r="F625" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G625" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="626" hidden="1" spans="1:7">
@@ -18655,7 +18658,7 @@
         <v>567</v>
       </c>
       <c r="B626" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C626" t="s">
         <v>83</v>
@@ -18667,10 +18670,10 @@
         <v>62</v>
       </c>
       <c r="F626" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="G626" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="627" hidden="1" spans="1:7">
@@ -18678,7 +18681,7 @@
         <v>110</v>
       </c>
       <c r="B627" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C627" t="s">
         <v>68</v>
@@ -18693,15 +18696,15 @@
         <v>592</v>
       </c>
       <c r="G627" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="628" hidden="1" spans="1:7">
       <c r="A628" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B628" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C628" t="s">
         <v>580</v>
@@ -18713,18 +18716,18 @@
         <v>62</v>
       </c>
       <c r="F628" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G628" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="629" hidden="1" spans="1:7">
       <c r="A629" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B629" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C629" t="s">
         <v>200</v>
@@ -18739,15 +18742,15 @@
         <v>184</v>
       </c>
       <c r="G629" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="630" hidden="1" spans="1:7">
       <c r="A630" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B630" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C630" t="s">
         <v>190</v>
@@ -18762,15 +18765,15 @@
         <v>284</v>
       </c>
       <c r="G630" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="631" hidden="1" spans="1:7">
       <c r="A631" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B631" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C631" t="s">
         <v>190</v>
@@ -18785,7 +18788,7 @@
         <v>284</v>
       </c>
       <c r="G631" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="632" hidden="1" spans="1:7">
@@ -18793,7 +18796,7 @@
         <v>613</v>
       </c>
       <c r="B632" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C632" t="s">
         <v>158</v>
@@ -18808,7 +18811,7 @@
         <v>184</v>
       </c>
       <c r="G632" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="633" hidden="1" spans="1:7">
@@ -18816,7 +18819,7 @@
         <v>589</v>
       </c>
       <c r="B633" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C633" t="s">
         <v>158</v>
@@ -18831,15 +18834,15 @@
         <v>184</v>
       </c>
       <c r="G633" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="634" hidden="1" spans="1:7">
       <c r="A634" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B634" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C634" t="s">
         <v>617</v>
@@ -18854,15 +18857,15 @@
         <v>184</v>
       </c>
       <c r="G634" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="635" hidden="1" spans="1:7">
       <c r="A635" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B635" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C635" t="s">
         <v>183</v>
@@ -18877,15 +18880,15 @@
         <v>184</v>
       </c>
       <c r="G635" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="636" hidden="1" spans="1:7">
       <c r="A636" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B636" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C636" t="s">
         <v>158</v>
@@ -18897,18 +18900,18 @@
         <v>42</v>
       </c>
       <c r="F636" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="G636" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="637" hidden="1" spans="1:7">
       <c r="A637" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B637" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C637" t="s">
         <v>158</v>
@@ -18920,18 +18923,18 @@
         <v>42</v>
       </c>
       <c r="F637" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="G637" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="638" hidden="1" spans="1:7">
       <c r="A638" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B638" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C638" t="s">
         <v>237</v>
@@ -18946,7 +18949,7 @@
         <v>184</v>
       </c>
       <c r="G638" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="639" hidden="1" spans="1:7">
@@ -18954,7 +18957,7 @@
         <v>179</v>
       </c>
       <c r="B639" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C639" t="s">
         <v>167</v>
@@ -18969,15 +18972,15 @@
         <v>184</v>
       </c>
       <c r="G639" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="640" hidden="1" spans="1:7">
       <c r="A640" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B640" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C640" t="s">
         <v>361</v>
@@ -18992,7 +18995,7 @@
         <v>184</v>
       </c>
       <c r="G640" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="641" hidden="1" spans="1:7">
@@ -19000,7 +19003,7 @@
         <v>607</v>
       </c>
       <c r="B641" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C641" t="s">
         <v>552</v>
@@ -19012,18 +19015,18 @@
         <v>55</v>
       </c>
       <c r="F641" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G641" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="642" hidden="1" spans="1:7">
       <c r="A642" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B642" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C642" t="s">
         <v>237</v>
@@ -19035,10 +19038,10 @@
         <v>55</v>
       </c>
       <c r="F642" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G642" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="643" hidden="1" spans="1:7">
@@ -19046,7 +19049,7 @@
         <v>607</v>
       </c>
       <c r="B643" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C643" t="s">
         <v>552</v>
@@ -19058,18 +19061,18 @@
         <v>55</v>
       </c>
       <c r="F643" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G643" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="644" hidden="1" spans="1:7">
       <c r="A644" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B644" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C644" t="s">
         <v>237</v>
@@ -19081,10 +19084,10 @@
         <v>55</v>
       </c>
       <c r="F644" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G644" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="645" hidden="1" spans="1:7">
@@ -19092,7 +19095,7 @@
         <v>165</v>
       </c>
       <c r="B645" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C645" t="s">
         <v>167</v>
@@ -19107,15 +19110,15 @@
         <v>184</v>
       </c>
       <c r="G645" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="646" hidden="1" spans="1:7">
       <c r="A646" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B646" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C646" t="s">
         <v>361</v>
@@ -19130,7 +19133,7 @@
         <v>184</v>
       </c>
       <c r="G646" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="647" hidden="1" spans="1:7">
@@ -19138,7 +19141,7 @@
         <v>171</v>
       </c>
       <c r="B647" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C647" t="s">
         <v>173</v>
@@ -19150,10 +19153,10 @@
         <v>62</v>
       </c>
       <c r="F647" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="G647" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="648" hidden="1" spans="1:7">
@@ -19161,7 +19164,7 @@
         <v>596</v>
       </c>
       <c r="B648" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C648" t="s">
         <v>361</v>
@@ -19173,18 +19176,18 @@
         <v>62</v>
       </c>
       <c r="F648" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G648" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="649" hidden="1" spans="1:7">
       <c r="A649" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B649" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C649" t="s">
         <v>361</v>
@@ -19199,7 +19202,7 @@
         <v>184</v>
       </c>
       <c r="G649" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="650" hidden="1" spans="1:7">
@@ -19207,7 +19210,7 @@
         <v>171</v>
       </c>
       <c r="B650" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C650" t="s">
         <v>173</v>
@@ -19219,10 +19222,10 @@
         <v>62</v>
       </c>
       <c r="F650" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G650" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="651" hidden="1" spans="1:7">
@@ -19230,7 +19233,7 @@
         <v>596</v>
       </c>
       <c r="B651" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C651" t="s">
         <v>361</v>
@@ -19242,17 +19245,20 @@
         <v>62</v>
       </c>
       <c r="F651" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G651" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="2">
+    <filterColumn colId="0">
       <filters>
-        <filter val="BENHAMIDA FARID"/>
+        <filter val="TD-Machines électriques approfondies"/>
+        <filter val="TD-Réseaux de transport et de distribution d'énergie électrique"/>
+        <filter val="TD-Électronique de puissance avancée"/>
+        <filter val="TD-Méthodes numériques appliquées et optimisation"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -1988,7 +1988,7 @@
     <t>SAHALI YAMINA</t>
   </si>
   <si>
-    <t>S04</t>
+    <t>AS2</t>
   </si>
   <si>
     <t>M1CE</t>
@@ -12305,7 +12305,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="350" hidden="1" spans="1:7">
+    <row r="350" spans="1:7">
       <c r="A350" s="1" t="s">
         <v>326</v>
       </c>
@@ -12328,7 +12328,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="351" hidden="1" spans="1:7">
+    <row r="351" spans="1:7">
       <c r="A351" s="1" t="s">
         <v>326</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="352" hidden="1" spans="1:7">
+    <row r="352" spans="1:7">
       <c r="A352" s="1" t="s">
         <v>326</v>
       </c>
@@ -12374,7 +12374,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="353" hidden="1" spans="1:7">
+    <row r="353" spans="1:7">
       <c r="A353" s="1" t="s">
         <v>326</v>
       </c>
@@ -12397,7 +12397,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="354" hidden="1" spans="1:7">
+    <row r="354" spans="1:7">
       <c r="A354" s="1" t="s">
         <v>660</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="355" hidden="1" spans="1:7">
+    <row r="355" spans="1:7">
       <c r="A355" s="1" t="s">
         <v>660</v>
       </c>
@@ -12443,7 +12443,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="356" hidden="1" spans="1:7">
+    <row r="356" spans="1:7">
       <c r="A356" s="1" t="s">
         <v>660</v>
       </c>
@@ -12466,7 +12466,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="357" hidden="1" spans="1:7">
+    <row r="357" spans="1:7">
       <c r="A357" s="1" t="s">
         <v>660</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="358" hidden="1" spans="1:7">
+    <row r="358" spans="1:7">
       <c r="A358" s="1" t="s">
         <v>665</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="359" hidden="1" spans="1:7">
+    <row r="359" spans="1:7">
       <c r="A359" s="1" t="s">
         <v>665</v>
       </c>
@@ -12535,7 +12535,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="360" hidden="1" spans="1:7">
+    <row r="360" spans="1:7">
       <c r="A360" s="1" t="s">
         <v>665</v>
       </c>
@@ -12558,7 +12558,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="361" hidden="1" spans="1:7">
+    <row r="361" spans="1:7">
       <c r="A361" s="1" t="s">
         <v>665</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" hidden="1" spans="1:7">
       <c r="A362" s="3" t="s">
         <v>349</v>
       </c>
@@ -12604,7 +12604,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" hidden="1" spans="1:7">
       <c r="A363" s="3" t="s">
         <v>349</v>
       </c>
@@ -12627,7 +12627,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" hidden="1" spans="1:7">
       <c r="A364" s="3" t="s">
         <v>349</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" hidden="1" spans="1:7">
       <c r="A365" s="3" t="s">
         <v>349</v>
       </c>
@@ -12673,7 +12673,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" hidden="1" spans="1:7">
       <c r="A366" s="3" t="s">
         <v>676</v>
       </c>
@@ -12696,7 +12696,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" hidden="1" spans="1:7">
       <c r="A367" s="3" t="s">
         <v>676</v>
       </c>
@@ -13041,7 +13041,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="382" hidden="1" spans="1:7">
+    <row r="382" spans="1:7">
       <c r="A382" s="1" t="s">
         <v>279</v>
       </c>
@@ -13057,14 +13057,14 @@
       <c r="E382" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F382" s="1" t="s">
+      <c r="F382" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G382" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="383" hidden="1" spans="1:7">
+    <row r="383" spans="1:7">
       <c r="A383" s="1" t="s">
         <v>279</v>
       </c>
@@ -13080,14 +13080,14 @@
       <c r="E383" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F383" s="1" t="s">
+      <c r="F383" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G383" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="384" hidden="1" spans="1:7">
+    <row r="384" spans="1:7">
       <c r="A384" s="1" t="s">
         <v>279</v>
       </c>
@@ -13103,14 +13103,14 @@
       <c r="E384" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F384" s="1" t="s">
+      <c r="F384" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G384" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="385" hidden="1" spans="1:7">
+    <row r="385" spans="1:7">
       <c r="A385" s="1" t="s">
         <v>279</v>
       </c>
@@ -13126,14 +13126,14 @@
       <c r="E385" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F385" s="1" t="s">
+      <c r="F385" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G385" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:7">
+    <row r="386" spans="1:7">
       <c r="A386" s="1" t="s">
         <v>707</v>
       </c>
@@ -13149,14 +13149,14 @@
       <c r="E386" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F386" s="1" t="s">
+      <c r="F386" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G386" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="387" hidden="1" spans="1:7">
+    <row r="387" spans="1:7">
       <c r="A387" s="1" t="s">
         <v>707</v>
       </c>
@@ -13172,14 +13172,14 @@
       <c r="E387" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F387" s="1" t="s">
+      <c r="F387" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G387" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:7">
+    <row r="388" spans="1:7">
       <c r="A388" s="1" t="s">
         <v>707</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="389" hidden="1" spans="1:7">
+    <row r="389" spans="1:7">
       <c r="A389" s="1" t="s">
         <v>707</v>
       </c>
@@ -13225,7 +13225,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390" s="3" t="s">
         <v>282</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" hidden="1" spans="1:7">
       <c r="A391" s="3" t="s">
         <v>282</v>
       </c>
@@ -13271,7 +13271,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" hidden="1" spans="1:7">
       <c r="A392" s="3" t="s">
         <v>714</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" hidden="1" spans="1:7">
       <c r="A393" s="3" t="s">
         <v>714</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="426" hidden="1" spans="1:7">
+    <row r="426" spans="1:7">
       <c r="A426" s="1" t="s">
         <v>760</v>
       </c>
@@ -14069,14 +14069,14 @@
       <c r="E426" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F426" s="1" t="s">
+      <c r="F426" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G426" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="427" hidden="1" spans="1:7">
+    <row r="427" spans="1:7">
       <c r="A427" s="1" t="s">
         <v>760</v>
       </c>
@@ -14092,14 +14092,14 @@
       <c r="E427" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F427" s="1" t="s">
+      <c r="F427" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G427" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="428" hidden="1" spans="1:7">
+    <row r="428" spans="1:7">
       <c r="A428" s="1" t="s">
         <v>760</v>
       </c>
@@ -14115,14 +14115,14 @@
       <c r="E428" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F428" s="1" t="s">
+      <c r="F428" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G428" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="429" hidden="1" spans="1:7">
+    <row r="429" spans="1:7">
       <c r="A429" s="1" t="s">
         <v>760</v>
       </c>
@@ -14138,14 +14138,14 @@
       <c r="E429" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F429" s="1" t="s">
+      <c r="F429" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G429" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" hidden="1" spans="1:7">
       <c r="A430" s="3" t="s">
         <v>282</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" hidden="1" spans="1:7">
       <c r="A431" s="3" t="s">
         <v>282</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" hidden="1" spans="1:7">
       <c r="A432" s="3" t="s">
         <v>676</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" hidden="1" spans="1:7">
       <c r="A433" s="3" t="s">
         <v>676</v>
       </c>
@@ -14513,7 +14513,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="446" hidden="1" spans="1:7">
+    <row r="446" spans="1:7">
       <c r="A446" s="1" t="s">
         <v>776</v>
       </c>
@@ -14529,14 +14529,14 @@
       <c r="E446" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F446" s="1" t="s">
-        <v>268</v>
+      <c r="F446" s="2" t="s">
+        <v>652</v>
       </c>
       <c r="G446" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="447" hidden="1" spans="1:7">
+    <row r="447" spans="1:7">
       <c r="A447" s="1" t="s">
         <v>776</v>
       </c>
@@ -14552,14 +14552,14 @@
       <c r="E447" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F447" s="1" t="s">
-        <v>268</v>
+      <c r="F447" s="2" t="s">
+        <v>652</v>
       </c>
       <c r="G447" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="448" hidden="1" spans="1:7">
+    <row r="448" spans="1:7">
       <c r="A448" s="1" t="s">
         <v>776</v>
       </c>
@@ -14575,14 +14575,14 @@
       <c r="E448" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F448" s="1" t="s">
+      <c r="F448" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G448" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="449" hidden="1" spans="1:7">
+    <row r="449" spans="1:7">
       <c r="A449" s="1" t="s">
         <v>776</v>
       </c>
@@ -14598,14 +14598,14 @@
       <c r="E449" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F449" s="1" t="s">
+      <c r="F449" s="2" t="s">
         <v>652</v>
       </c>
       <c r="G449" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" hidden="1" spans="1:7">
       <c r="A450" s="3" t="s">
         <v>714</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" hidden="1" spans="1:7">
       <c r="A451" s="3" t="s">
         <v>714</v>
       </c>
@@ -19255,10 +19255,13 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G651" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="TD-Machines électriques approfondies"/>
-        <filter val="TD-Réseaux de transport et de distribution d'énergie électrique"/>
-        <filter val="TD-Électronique de puissance avancée"/>
-        <filter val="TD-Méthodes numériques appliquées et optimisation"/>
+        <filter val="Cours-μ-processeurs et μ-contrôleurs"/>
+        <filter val="Cours-Machines électriques approfondies"/>
+        <filter val="Cours-Énergies renouvelables"/>
+        <filter val="Cours-Réseaux de transport et de distribution d'énergie électrique"/>
+        <filter val="Cours-Électronique de puissance avancée"/>
+        <filter val="Cours-Méthodes numériques appliquées et optimisation"/>
+        <filter val="Cours-Programmation avancée en Python"/>
       </filters>
     </filterColumn>
     <filterColumn colId="6">
